--- a/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Czech Republic First League_20242025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Czech Republic First League_20242025.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="980" uniqueCount="267">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1010" uniqueCount="269">
   <si>
     <t>Id_Jogo</t>
   </si>
@@ -589,6 +589,9 @@
     <t>['2', '15', '18', '28', '56', '59', '77']</t>
   </si>
   <si>
+    <t>['20', '27', '90+2']</t>
+  </si>
+  <si>
     <t>['25']</t>
   </si>
   <si>
@@ -815,6 +818,9 @@
   </si>
   <si>
     <t>['12', '58']</t>
+  </si>
+  <si>
+    <t>['4', '30']</t>
   </si>
 </sst>
 </file>
@@ -1176,7 +1182,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:BP153"/>
+  <dimension ref="A1:BP158"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:68">
@@ -1432,7 +1438,7 @@
         <v>86</v>
       </c>
       <c r="P2" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="Q2">
         <v>1.53</v>
@@ -1513,7 +1519,7 @@
         <v>2</v>
       </c>
       <c r="AQ2">
-        <v>0.6</v>
+        <v>0.55</v>
       </c>
       <c r="AR2">
         <v>0</v>
@@ -1844,7 +1850,7 @@
         <v>88</v>
       </c>
       <c r="P4" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="Q4">
         <v>2.88</v>
@@ -1922,7 +1928,7 @@
         <v>0</v>
       </c>
       <c r="AP4">
-        <v>0.2</v>
+        <v>0.27</v>
       </c>
       <c r="AQ4">
         <v>1.2</v>
@@ -2131,7 +2137,7 @@
         <v>1</v>
       </c>
       <c r="AQ5">
-        <v>1.5</v>
+        <v>1.64</v>
       </c>
       <c r="AR5">
         <v>0</v>
@@ -2256,7 +2262,7 @@
         <v>90</v>
       </c>
       <c r="P6" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="Q6">
         <v>5.5</v>
@@ -2462,7 +2468,7 @@
         <v>91</v>
       </c>
       <c r="P7" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="Q7">
         <v>3.2</v>
@@ -2540,7 +2546,7 @@
         <v>0</v>
       </c>
       <c r="AP7">
-        <v>1.5</v>
+        <v>1.45</v>
       </c>
       <c r="AQ7">
         <v>1.1</v>
@@ -2746,7 +2752,7 @@
         <v>0</v>
       </c>
       <c r="AP8">
-        <v>1.56</v>
+        <v>1.4</v>
       </c>
       <c r="AQ8">
         <v>2.3</v>
@@ -2952,10 +2958,10 @@
         <v>0</v>
       </c>
       <c r="AP9">
-        <v>1.56</v>
+        <v>1.7</v>
       </c>
       <c r="AQ9">
-        <v>0.89</v>
+        <v>0.9</v>
       </c>
       <c r="AR9">
         <v>0</v>
@@ -3286,7 +3292,7 @@
         <v>94</v>
       </c>
       <c r="P11" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="Q11">
         <v>6.5</v>
@@ -3367,7 +3373,7 @@
         <v>1.3</v>
       </c>
       <c r="AQ11">
-        <v>1.89</v>
+        <v>2</v>
       </c>
       <c r="AR11">
         <v>0</v>
@@ -3492,7 +3498,7 @@
         <v>88</v>
       </c>
       <c r="P12" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="Q12">
         <v>2.85</v>
@@ -3904,7 +3910,7 @@
         <v>96</v>
       </c>
       <c r="P14" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="Q14">
         <v>2.45</v>
@@ -3982,7 +3988,7 @@
         <v>3</v>
       </c>
       <c r="AP14">
-        <v>1.44</v>
+        <v>1.3</v>
       </c>
       <c r="AQ14">
         <v>1.2</v>
@@ -4728,7 +4734,7 @@
         <v>88</v>
       </c>
       <c r="P18" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="Q18">
         <v>5.4</v>
@@ -4806,7 +4812,7 @@
         <v>1</v>
       </c>
       <c r="AP18">
-        <v>1.44</v>
+        <v>1.3</v>
       </c>
       <c r="AQ18">
         <v>2.3</v>
@@ -5015,7 +5021,7 @@
         <v>2</v>
       </c>
       <c r="AQ19">
-        <v>0.22</v>
+        <v>0.3</v>
       </c>
       <c r="AR19">
         <v>1.9</v>
@@ -5218,7 +5224,7 @@
         <v>0</v>
       </c>
       <c r="AP20">
-        <v>1.56</v>
+        <v>1.4</v>
       </c>
       <c r="AQ20">
         <v>1.33</v>
@@ -5633,7 +5639,7 @@
         <v>1.56</v>
       </c>
       <c r="AQ22">
-        <v>0.89</v>
+        <v>0.9</v>
       </c>
       <c r="AR22">
         <v>0</v>
@@ -5758,7 +5764,7 @@
         <v>102</v>
       </c>
       <c r="P23" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="Q23">
         <v>2.6</v>
@@ -5836,10 +5842,10 @@
         <v>0</v>
       </c>
       <c r="AP23">
-        <v>0.2</v>
+        <v>0.27</v>
       </c>
       <c r="AQ23">
-        <v>0.6</v>
+        <v>0.55</v>
       </c>
       <c r="AR23">
         <v>1.33</v>
@@ -5964,7 +5970,7 @@
         <v>103</v>
       </c>
       <c r="P24" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="Q24">
         <v>2.75</v>
@@ -6042,7 +6048,7 @@
         <v>0</v>
       </c>
       <c r="AP24">
-        <v>1.56</v>
+        <v>1.7</v>
       </c>
       <c r="AQ24">
         <v>1.33</v>
@@ -6170,7 +6176,7 @@
         <v>88</v>
       </c>
       <c r="P25" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="Q25">
         <v>1.06</v>
@@ -6376,7 +6382,7 @@
         <v>104</v>
       </c>
       <c r="P26" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="Q26">
         <v>6.23</v>
@@ -6457,7 +6463,7 @@
         <v>1</v>
       </c>
       <c r="AQ26">
-        <v>1.89</v>
+        <v>2</v>
       </c>
       <c r="AR26">
         <v>1.73</v>
@@ -7896,10 +7902,10 @@
         <v>0</v>
       </c>
       <c r="AP33">
-        <v>1.56</v>
+        <v>1.7</v>
       </c>
       <c r="AQ33">
-        <v>0.22</v>
+        <v>0.3</v>
       </c>
       <c r="AR33">
         <v>1.08</v>
@@ -8024,7 +8030,7 @@
         <v>111</v>
       </c>
       <c r="P34" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="Q34">
         <v>1.45</v>
@@ -8105,7 +8111,7 @@
         <v>3</v>
       </c>
       <c r="AQ34">
-        <v>0.89</v>
+        <v>0.9</v>
       </c>
       <c r="AR34">
         <v>2.27</v>
@@ -8230,7 +8236,7 @@
         <v>112</v>
       </c>
       <c r="P35" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="Q35">
         <v>2.84</v>
@@ -8308,7 +8314,7 @@
         <v>0.5</v>
       </c>
       <c r="AP35">
-        <v>1.5</v>
+        <v>1.45</v>
       </c>
       <c r="AQ35">
         <v>1.33</v>
@@ -8436,7 +8442,7 @@
         <v>113</v>
       </c>
       <c r="P36" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="Q36">
         <v>5.63</v>
@@ -8517,7 +8523,7 @@
         <v>2.11</v>
       </c>
       <c r="AQ36">
-        <v>1.89</v>
+        <v>2</v>
       </c>
       <c r="AR36">
         <v>1.54</v>
@@ -8642,7 +8648,7 @@
         <v>114</v>
       </c>
       <c r="P37" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="Q37">
         <v>2.58</v>
@@ -8926,10 +8932,10 @@
         <v>1.5</v>
       </c>
       <c r="AP38">
-        <v>1.44</v>
+        <v>1.3</v>
       </c>
       <c r="AQ38">
-        <v>0.6</v>
+        <v>0.55</v>
       </c>
       <c r="AR38">
         <v>1.34</v>
@@ -9054,7 +9060,7 @@
         <v>88</v>
       </c>
       <c r="P39" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="Q39">
         <v>4.75</v>
@@ -9132,7 +9138,7 @@
         <v>2</v>
       </c>
       <c r="AP39">
-        <v>0.2</v>
+        <v>0.27</v>
       </c>
       <c r="AQ39">
         <v>1.89</v>
@@ -9338,10 +9344,10 @@
         <v>0</v>
       </c>
       <c r="AP40">
-        <v>1.56</v>
+        <v>1.4</v>
       </c>
       <c r="AQ40">
-        <v>1.5</v>
+        <v>1.64</v>
       </c>
       <c r="AR40">
         <v>1.19</v>
@@ -9466,7 +9472,7 @@
         <v>117</v>
       </c>
       <c r="P41" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="Q41">
         <v>2.4</v>
@@ -9672,7 +9678,7 @@
         <v>107</v>
       </c>
       <c r="P42" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="Q42">
         <v>2.61</v>
@@ -9878,7 +9884,7 @@
         <v>118</v>
       </c>
       <c r="P43" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="Q43">
         <v>1.69</v>
@@ -10780,10 +10786,10 @@
         <v>0</v>
       </c>
       <c r="AP47">
-        <v>1.5</v>
+        <v>1.45</v>
       </c>
       <c r="AQ47">
-        <v>1.5</v>
+        <v>1.64</v>
       </c>
       <c r="AR47">
         <v>1.77</v>
@@ -10986,7 +10992,7 @@
         <v>1.33</v>
       </c>
       <c r="AP48">
-        <v>0.2</v>
+        <v>0.27</v>
       </c>
       <c r="AQ48">
         <v>1.33</v>
@@ -11192,7 +11198,7 @@
         <v>2</v>
       </c>
       <c r="AP49">
-        <v>1.56</v>
+        <v>1.4</v>
       </c>
       <c r="AQ49">
         <v>1.1</v>
@@ -11320,7 +11326,7 @@
         <v>88</v>
       </c>
       <c r="P50" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="Q50">
         <v>5.1</v>
@@ -11398,10 +11404,10 @@
         <v>3</v>
       </c>
       <c r="AP50">
-        <v>1.56</v>
+        <v>1.7</v>
       </c>
       <c r="AQ50">
-        <v>1.89</v>
+        <v>2</v>
       </c>
       <c r="AR50">
         <v>1.24</v>
@@ -11604,10 +11610,10 @@
         <v>0</v>
       </c>
       <c r="AP51">
-        <v>1.5</v>
+        <v>1.45</v>
       </c>
       <c r="AQ51">
-        <v>0.22</v>
+        <v>0.3</v>
       </c>
       <c r="AR51">
         <v>1.76</v>
@@ -11732,7 +11738,7 @@
         <v>122</v>
       </c>
       <c r="P52" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="Q52">
         <v>3</v>
@@ -11813,7 +11819,7 @@
         <v>1.56</v>
       </c>
       <c r="AQ52">
-        <v>1.5</v>
+        <v>1.64</v>
       </c>
       <c r="AR52">
         <v>1.61</v>
@@ -12019,7 +12025,7 @@
         <v>3</v>
       </c>
       <c r="AQ53">
-        <v>0.6</v>
+        <v>0.55</v>
       </c>
       <c r="AR53">
         <v>2.35</v>
@@ -12144,7 +12150,7 @@
         <v>124</v>
       </c>
       <c r="P54" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="Q54">
         <v>3</v>
@@ -12428,7 +12434,7 @@
         <v>2.33</v>
       </c>
       <c r="AP55">
-        <v>1.44</v>
+        <v>1.3</v>
       </c>
       <c r="AQ55">
         <v>1.89</v>
@@ -12556,7 +12562,7 @@
         <v>125</v>
       </c>
       <c r="P56" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="Q56">
         <v>1.85</v>
@@ -12762,7 +12768,7 @@
         <v>88</v>
       </c>
       <c r="P57" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="Q57">
         <v>5.88</v>
@@ -13046,7 +13052,7 @@
         <v>1.33</v>
       </c>
       <c r="AP58">
-        <v>1.56</v>
+        <v>1.7</v>
       </c>
       <c r="AQ58">
         <v>1.1</v>
@@ -13174,7 +13180,7 @@
         <v>127</v>
       </c>
       <c r="P59" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="Q59">
         <v>3.86</v>
@@ -13255,7 +13261,7 @@
         <v>1.3</v>
       </c>
       <c r="AQ59">
-        <v>1.5</v>
+        <v>1.64</v>
       </c>
       <c r="AR59">
         <v>1.44</v>
@@ -13458,7 +13464,7 @@
         <v>1.75</v>
       </c>
       <c r="AP60">
-        <v>1.5</v>
+        <v>1.45</v>
       </c>
       <c r="AQ60">
         <v>1.1</v>
@@ -13792,7 +13798,7 @@
         <v>130</v>
       </c>
       <c r="P62" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="Q62">
         <v>1.83</v>
@@ -13873,7 +13879,7 @@
         <v>1.6</v>
       </c>
       <c r="AQ62">
-        <v>0.6</v>
+        <v>0.55</v>
       </c>
       <c r="AR62">
         <v>1.42</v>
@@ -13998,7 +14004,7 @@
         <v>88</v>
       </c>
       <c r="P63" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="Q63">
         <v>8.77</v>
@@ -14076,10 +14082,10 @@
         <v>3</v>
       </c>
       <c r="AP63">
-        <v>0.2</v>
+        <v>0.27</v>
       </c>
       <c r="AQ63">
-        <v>1.89</v>
+        <v>2</v>
       </c>
       <c r="AR63">
         <v>1.37</v>
@@ -14285,7 +14291,7 @@
         <v>1.56</v>
       </c>
       <c r="AQ64">
-        <v>0.22</v>
+        <v>0.3</v>
       </c>
       <c r="AR64">
         <v>1.75</v>
@@ -14410,7 +14416,7 @@
         <v>132</v>
       </c>
       <c r="P65" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="Q65">
         <v>2.4</v>
@@ -14488,7 +14494,7 @@
         <v>1.25</v>
       </c>
       <c r="AP65">
-        <v>1.44</v>
+        <v>1.3</v>
       </c>
       <c r="AQ65">
         <v>1.33</v>
@@ -14616,7 +14622,7 @@
         <v>133</v>
       </c>
       <c r="P66" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="Q66">
         <v>1.55</v>
@@ -14822,7 +14828,7 @@
         <v>134</v>
       </c>
       <c r="P67" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="Q67">
         <v>4</v>
@@ -15028,7 +15034,7 @@
         <v>88</v>
       </c>
       <c r="P68" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="Q68">
         <v>3.1</v>
@@ -15109,7 +15115,7 @@
         <v>1</v>
       </c>
       <c r="AQ68">
-        <v>0.89</v>
+        <v>0.9</v>
       </c>
       <c r="AR68">
         <v>1.23</v>
@@ -15312,7 +15318,7 @@
         <v>2</v>
       </c>
       <c r="AP69">
-        <v>1.56</v>
+        <v>1.4</v>
       </c>
       <c r="AQ69">
         <v>0.89</v>
@@ -15852,7 +15858,7 @@
         <v>124</v>
       </c>
       <c r="P72" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="Q72">
         <v>1.88</v>
@@ -16058,7 +16064,7 @@
         <v>88</v>
       </c>
       <c r="P73" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="Q73">
         <v>7</v>
@@ -16342,7 +16348,7 @@
         <v>0</v>
       </c>
       <c r="AP74">
-        <v>1.5</v>
+        <v>1.45</v>
       </c>
       <c r="AQ74">
         <v>1.1</v>
@@ -16470,7 +16476,7 @@
         <v>138</v>
       </c>
       <c r="P75" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="Q75">
         <v>2.3</v>
@@ -16551,7 +16557,7 @@
         <v>1.3</v>
       </c>
       <c r="AQ75">
-        <v>0.22</v>
+        <v>0.3</v>
       </c>
       <c r="AR75">
         <v>1.49</v>
@@ -16676,7 +16682,7 @@
         <v>88</v>
       </c>
       <c r="P76" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="Q76">
         <v>3.7</v>
@@ -16754,7 +16760,7 @@
         <v>1</v>
       </c>
       <c r="AP76">
-        <v>0.2</v>
+        <v>0.27</v>
       </c>
       <c r="AQ76">
         <v>1.1</v>
@@ -16882,7 +16888,7 @@
         <v>88</v>
       </c>
       <c r="P77" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="Q77">
         <v>2.47</v>
@@ -16960,7 +16966,7 @@
         <v>1.4</v>
       </c>
       <c r="AP77">
-        <v>1.44</v>
+        <v>1.3</v>
       </c>
       <c r="AQ77">
         <v>1.1</v>
@@ -17169,7 +17175,7 @@
         <v>2.6</v>
       </c>
       <c r="AQ78">
-        <v>0.6</v>
+        <v>0.55</v>
       </c>
       <c r="AR78">
         <v>1.78</v>
@@ -17375,7 +17381,7 @@
         <v>1.6</v>
       </c>
       <c r="AQ79">
-        <v>1.5</v>
+        <v>1.64</v>
       </c>
       <c r="AR79">
         <v>1.49</v>
@@ -17500,7 +17506,7 @@
         <v>140</v>
       </c>
       <c r="P80" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="Q80">
         <v>2.5</v>
@@ -17706,7 +17712,7 @@
         <v>141</v>
       </c>
       <c r="P81" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="Q81">
         <v>2.38</v>
@@ -17787,7 +17793,7 @@
         <v>3</v>
       </c>
       <c r="AQ81">
-        <v>1.89</v>
+        <v>2</v>
       </c>
       <c r="AR81">
         <v>2.43</v>
@@ -17912,7 +17918,7 @@
         <v>142</v>
       </c>
       <c r="P82" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="Q82">
         <v>2.8</v>
@@ -17990,7 +17996,7 @@
         <v>1.4</v>
       </c>
       <c r="AP82">
-        <v>1.56</v>
+        <v>1.7</v>
       </c>
       <c r="AQ82">
         <v>1.2</v>
@@ -18118,7 +18124,7 @@
         <v>143</v>
       </c>
       <c r="P83" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="Q83">
         <v>2.6</v>
@@ -18199,7 +18205,7 @@
         <v>1</v>
       </c>
       <c r="AQ83">
-        <v>0.6</v>
+        <v>0.55</v>
       </c>
       <c r="AR83">
         <v>1.14</v>
@@ -18324,7 +18330,7 @@
         <v>144</v>
       </c>
       <c r="P84" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="Q84">
         <v>3.4</v>
@@ -18530,7 +18536,7 @@
         <v>145</v>
       </c>
       <c r="P85" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="Q85">
         <v>1.65</v>
@@ -18736,7 +18742,7 @@
         <v>146</v>
       </c>
       <c r="P86" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="Q86">
         <v>2.88</v>
@@ -19020,7 +19026,7 @@
         <v>0</v>
       </c>
       <c r="AP87">
-        <v>1.5</v>
+        <v>1.45</v>
       </c>
       <c r="AQ87">
         <v>0.11</v>
@@ -19148,7 +19154,7 @@
         <v>88</v>
       </c>
       <c r="P88" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="Q88">
         <v>2.6</v>
@@ -19226,10 +19232,10 @@
         <v>0.75</v>
       </c>
       <c r="AP88">
-        <v>1.56</v>
+        <v>1.4</v>
       </c>
       <c r="AQ88">
-        <v>0.89</v>
+        <v>0.9</v>
       </c>
       <c r="AR88">
         <v>1.12</v>
@@ -19354,7 +19360,7 @@
         <v>93</v>
       </c>
       <c r="P89" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="Q89">
         <v>6.5</v>
@@ -19638,7 +19644,7 @@
         <v>1.4</v>
       </c>
       <c r="AP90">
-        <v>1.44</v>
+        <v>1.3</v>
       </c>
       <c r="AQ90">
         <v>1.1</v>
@@ -19766,7 +19772,7 @@
         <v>149</v>
       </c>
       <c r="P91" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="Q91">
         <v>4.7</v>
@@ -19847,7 +19853,7 @@
         <v>1</v>
       </c>
       <c r="AQ91">
-        <v>1.5</v>
+        <v>1.64</v>
       </c>
       <c r="AR91">
         <v>1.11</v>
@@ -19972,7 +19978,7 @@
         <v>88</v>
       </c>
       <c r="P92" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="Q92">
         <v>3.8</v>
@@ -20050,7 +20056,7 @@
         <v>0.2</v>
       </c>
       <c r="AP92">
-        <v>0.2</v>
+        <v>0.27</v>
       </c>
       <c r="AQ92">
         <v>1.1</v>
@@ -20384,7 +20390,7 @@
         <v>150</v>
       </c>
       <c r="P94" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="Q94">
         <v>3</v>
@@ -20877,7 +20883,7 @@
         <v>3</v>
       </c>
       <c r="AQ96">
-        <v>0.22</v>
+        <v>0.3</v>
       </c>
       <c r="AR96">
         <v>2.31</v>
@@ -21083,7 +21089,7 @@
         <v>2.6</v>
       </c>
       <c r="AQ97">
-        <v>1.89</v>
+        <v>2</v>
       </c>
       <c r="AR97">
         <v>1.81</v>
@@ -21495,7 +21501,7 @@
         <v>2.11</v>
       </c>
       <c r="AQ99">
-        <v>0.89</v>
+        <v>0.9</v>
       </c>
       <c r="AR99">
         <v>1.65</v>
@@ -21698,7 +21704,7 @@
         <v>1.33</v>
       </c>
       <c r="AP100">
-        <v>1.5</v>
+        <v>1.45</v>
       </c>
       <c r="AQ100">
         <v>1.2</v>
@@ -21826,7 +21832,7 @@
         <v>156</v>
       </c>
       <c r="P101" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="Q101">
         <v>1.83</v>
@@ -21907,7 +21913,7 @@
         <v>2</v>
       </c>
       <c r="AQ101">
-        <v>1.5</v>
+        <v>1.64</v>
       </c>
       <c r="AR101">
         <v>1.9</v>
@@ -22110,7 +22116,7 @@
         <v>1.2</v>
       </c>
       <c r="AP102">
-        <v>0.2</v>
+        <v>0.27</v>
       </c>
       <c r="AQ102">
         <v>1.1</v>
@@ -22319,7 +22325,7 @@
         <v>1</v>
       </c>
       <c r="AQ103">
-        <v>0.6</v>
+        <v>0.55</v>
       </c>
       <c r="AR103">
         <v>1.41</v>
@@ -22522,7 +22528,7 @@
         <v>1.83</v>
       </c>
       <c r="AP104">
-        <v>1.56</v>
+        <v>1.4</v>
       </c>
       <c r="AQ104">
         <v>1.89</v>
@@ -22728,7 +22734,7 @@
         <v>2.6</v>
       </c>
       <c r="AP105">
-        <v>1.56</v>
+        <v>1.7</v>
       </c>
       <c r="AQ105">
         <v>2.3</v>
@@ -22937,7 +22943,7 @@
         <v>2.33</v>
       </c>
       <c r="AQ106">
-        <v>0.22</v>
+        <v>0.3</v>
       </c>
       <c r="AR106">
         <v>1.87</v>
@@ -23346,7 +23352,7 @@
         <v>0.67</v>
       </c>
       <c r="AP108">
-        <v>1.44</v>
+        <v>1.3</v>
       </c>
       <c r="AQ108">
         <v>1.1</v>
@@ -23474,7 +23480,7 @@
         <v>161</v>
       </c>
       <c r="P109" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="Q109">
         <v>2.24</v>
@@ -23680,7 +23686,7 @@
         <v>162</v>
       </c>
       <c r="P110" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="Q110">
         <v>4.6</v>
@@ -23761,7 +23767,7 @@
         <v>1.6</v>
       </c>
       <c r="AQ110">
-        <v>1.89</v>
+        <v>2</v>
       </c>
       <c r="AR110">
         <v>1.51</v>
@@ -24092,7 +24098,7 @@
         <v>164</v>
       </c>
       <c r="P112" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="Q112">
         <v>1.44</v>
@@ -24298,7 +24304,7 @@
         <v>165</v>
       </c>
       <c r="P113" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="Q113">
         <v>3.25</v>
@@ -24379,7 +24385,7 @@
         <v>2.11</v>
       </c>
       <c r="AQ113">
-        <v>1.5</v>
+        <v>1.64</v>
       </c>
       <c r="AR113">
         <v>1.63</v>
@@ -24504,7 +24510,7 @@
         <v>99</v>
       </c>
       <c r="P114" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="Q114">
         <v>1.73</v>
@@ -24585,7 +24591,7 @@
         <v>2</v>
       </c>
       <c r="AQ114">
-        <v>0.89</v>
+        <v>0.9</v>
       </c>
       <c r="AR114">
         <v>1.87</v>
@@ -24710,7 +24716,7 @@
         <v>151</v>
       </c>
       <c r="P115" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="Q115">
         <v>2.88</v>
@@ -24788,7 +24794,7 @@
         <v>1.14</v>
       </c>
       <c r="AP115">
-        <v>1.56</v>
+        <v>1.4</v>
       </c>
       <c r="AQ115">
         <v>1.33</v>
@@ -24916,7 +24922,7 @@
         <v>88</v>
       </c>
       <c r="P116" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="Q116">
         <v>4.33</v>
@@ -24994,7 +25000,7 @@
         <v>1.57</v>
       </c>
       <c r="AP116">
-        <v>1.56</v>
+        <v>1.7</v>
       </c>
       <c r="AQ116">
         <v>1.89</v>
@@ -25203,7 +25209,7 @@
         <v>1</v>
       </c>
       <c r="AQ117">
-        <v>0.22</v>
+        <v>0.3</v>
       </c>
       <c r="AR117">
         <v>1.44</v>
@@ -25328,7 +25334,7 @@
         <v>88</v>
       </c>
       <c r="P118" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="Q118">
         <v>15</v>
@@ -25406,7 +25412,7 @@
         <v>2.33</v>
       </c>
       <c r="AP118">
-        <v>0.2</v>
+        <v>0.27</v>
       </c>
       <c r="AQ118">
         <v>2.3</v>
@@ -25612,10 +25618,10 @@
         <v>0.63</v>
       </c>
       <c r="AP119">
-        <v>1.5</v>
+        <v>1.45</v>
       </c>
       <c r="AQ119">
-        <v>0.6</v>
+        <v>0.55</v>
       </c>
       <c r="AR119">
         <v>1.64</v>
@@ -25740,7 +25746,7 @@
         <v>168</v>
       </c>
       <c r="P120" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="Q120">
         <v>3</v>
@@ -26152,7 +26158,7 @@
         <v>170</v>
       </c>
       <c r="P122" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="Q122">
         <v>3.25</v>
@@ -26358,7 +26364,7 @@
         <v>171</v>
       </c>
       <c r="P123" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="Q123">
         <v>1.83</v>
@@ -26770,7 +26776,7 @@
         <v>172</v>
       </c>
       <c r="P125" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="Q125">
         <v>6.3</v>
@@ -26851,7 +26857,7 @@
         <v>1</v>
       </c>
       <c r="AQ125">
-        <v>1.89</v>
+        <v>2</v>
       </c>
       <c r="AR125">
         <v>1.21</v>
@@ -27594,7 +27600,7 @@
         <v>174</v>
       </c>
       <c r="P129" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="Q129">
         <v>2.1</v>
@@ -27800,7 +27806,7 @@
         <v>175</v>
       </c>
       <c r="P130" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="Q130">
         <v>1.5</v>
@@ -28212,7 +28218,7 @@
         <v>177</v>
       </c>
       <c r="P132" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="Q132">
         <v>4.04</v>
@@ -28418,7 +28424,7 @@
         <v>178</v>
       </c>
       <c r="P133" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="Q133">
         <v>3.5</v>
@@ -28624,7 +28630,7 @@
         <v>88</v>
       </c>
       <c r="P134" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="Q134">
         <v>2.75</v>
@@ -29036,7 +29042,7 @@
         <v>88</v>
       </c>
       <c r="P136" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="Q136">
         <v>4.5</v>
@@ -29323,7 +29329,7 @@
         <v>2.6</v>
       </c>
       <c r="AQ137">
-        <v>0.89</v>
+        <v>0.9</v>
       </c>
       <c r="AR137">
         <v>1.7</v>
@@ -29448,7 +29454,7 @@
         <v>91</v>
       </c>
       <c r="P138" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="Q138">
         <v>2.25</v>
@@ -29526,10 +29532,10 @@
         <v>0.5600000000000001</v>
       </c>
       <c r="AP138">
-        <v>1.56</v>
+        <v>1.4</v>
       </c>
       <c r="AQ138">
-        <v>0.6</v>
+        <v>0.55</v>
       </c>
       <c r="AR138">
         <v>1.11</v>
@@ -29654,7 +29660,7 @@
         <v>179</v>
       </c>
       <c r="P139" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="Q139">
         <v>1.9</v>
@@ -29735,7 +29741,7 @@
         <v>2.11</v>
       </c>
       <c r="AQ139">
-        <v>0.22</v>
+        <v>0.3</v>
       </c>
       <c r="AR139">
         <v>1.71</v>
@@ -30066,7 +30072,7 @@
         <v>117</v>
       </c>
       <c r="P141" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="Q141">
         <v>4</v>
@@ -30144,7 +30150,7 @@
         <v>1.75</v>
       </c>
       <c r="AP141">
-        <v>1.5</v>
+        <v>1.45</v>
       </c>
       <c r="AQ141">
         <v>1.89</v>
@@ -30272,7 +30278,7 @@
         <v>88</v>
       </c>
       <c r="P142" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="Q142">
         <v>4</v>
@@ -30350,7 +30356,7 @@
         <v>1.13</v>
       </c>
       <c r="AP142">
-        <v>0.2</v>
+        <v>0.27</v>
       </c>
       <c r="AQ142">
         <v>1.33</v>
@@ -30556,10 +30562,10 @@
         <v>1</v>
       </c>
       <c r="AP143">
-        <v>1.44</v>
+        <v>1.3</v>
       </c>
       <c r="AQ143">
-        <v>0.89</v>
+        <v>0.9</v>
       </c>
       <c r="AR143">
         <v>1.52</v>
@@ -30684,7 +30690,7 @@
         <v>182</v>
       </c>
       <c r="P144" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="Q144">
         <v>6</v>
@@ -30890,7 +30896,7 @@
         <v>88</v>
       </c>
       <c r="P145" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="Q145">
         <v>3.5</v>
@@ -30968,10 +30974,10 @@
         <v>1.33</v>
       </c>
       <c r="AP145">
-        <v>1.56</v>
+        <v>1.7</v>
       </c>
       <c r="AQ145">
-        <v>1.5</v>
+        <v>1.64</v>
       </c>
       <c r="AR145">
         <v>1.32</v>
@@ -31096,7 +31102,7 @@
         <v>183</v>
       </c>
       <c r="P146" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="Q146">
         <v>4.33</v>
@@ -31302,7 +31308,7 @@
         <v>184</v>
       </c>
       <c r="P147" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="Q147">
         <v>3.8</v>
@@ -31508,7 +31514,7 @@
         <v>185</v>
       </c>
       <c r="P148" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="Q148">
         <v>2.5</v>
@@ -31714,7 +31720,7 @@
         <v>186</v>
       </c>
       <c r="P149" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="Q149">
         <v>2.05</v>
@@ -31920,7 +31926,7 @@
         <v>187</v>
       </c>
       <c r="P150" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="Q150">
         <v>1.95</v>
@@ -32126,7 +32132,7 @@
         <v>188</v>
       </c>
       <c r="P151" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="Q151">
         <v>2.48</v>
@@ -32538,7 +32544,7 @@
         <v>190</v>
       </c>
       <c r="P153" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="Q153">
         <v>1.4</v>
@@ -32695,6 +32701,1036 @@
       </c>
       <c r="BP153">
         <v>1.55</v>
+      </c>
+    </row>
+    <row r="154" spans="1:68">
+      <c r="A154" s="1">
+        <v>153</v>
+      </c>
+      <c r="B154">
+        <v>7468232</v>
+      </c>
+      <c r="C154" t="s">
+        <v>68</v>
+      </c>
+      <c r="D154" t="s">
+        <v>69</v>
+      </c>
+      <c r="E154" s="2">
+        <v>45689.39583333334</v>
+      </c>
+      <c r="F154">
+        <v>20</v>
+      </c>
+      <c r="G154" t="s">
+        <v>75</v>
+      </c>
+      <c r="H154" t="s">
+        <v>78</v>
+      </c>
+      <c r="I154">
+        <v>1</v>
+      </c>
+      <c r="J154">
+        <v>1</v>
+      </c>
+      <c r="K154">
+        <v>2</v>
+      </c>
+      <c r="L154">
+        <v>1</v>
+      </c>
+      <c r="M154">
+        <v>1</v>
+      </c>
+      <c r="N154">
+        <v>2</v>
+      </c>
+      <c r="O154" t="s">
+        <v>110</v>
+      </c>
+      <c r="P154" t="s">
+        <v>112</v>
+      </c>
+      <c r="Q154">
+        <v>3</v>
+      </c>
+      <c r="R154">
+        <v>2.1</v>
+      </c>
+      <c r="S154">
+        <v>3.6</v>
+      </c>
+      <c r="T154">
+        <v>1.4</v>
+      </c>
+      <c r="U154">
+        <v>2.75</v>
+      </c>
+      <c r="V154">
+        <v>3</v>
+      </c>
+      <c r="W154">
+        <v>1.36</v>
+      </c>
+      <c r="X154">
+        <v>8</v>
+      </c>
+      <c r="Y154">
+        <v>1.08</v>
+      </c>
+      <c r="Z154">
+        <v>1.98</v>
+      </c>
+      <c r="AA154">
+        <v>3.26</v>
+      </c>
+      <c r="AB154">
+        <v>3.25</v>
+      </c>
+      <c r="AC154">
+        <v>0</v>
+      </c>
+      <c r="AD154">
+        <v>0</v>
+      </c>
+      <c r="AE154">
+        <v>0</v>
+      </c>
+      <c r="AF154">
+        <v>0</v>
+      </c>
+      <c r="AG154">
+        <v>1.95</v>
+      </c>
+      <c r="AH154">
+        <v>1.83</v>
+      </c>
+      <c r="AI154">
+        <v>1.75</v>
+      </c>
+      <c r="AJ154">
+        <v>2</v>
+      </c>
+      <c r="AK154">
+        <v>0</v>
+      </c>
+      <c r="AL154">
+        <v>0</v>
+      </c>
+      <c r="AM154">
+        <v>0</v>
+      </c>
+      <c r="AN154">
+        <v>1.5</v>
+      </c>
+      <c r="AO154">
+        <v>0.89</v>
+      </c>
+      <c r="AP154">
+        <v>1.45</v>
+      </c>
+      <c r="AQ154">
+        <v>0.9</v>
+      </c>
+      <c r="AR154">
+        <v>1.58</v>
+      </c>
+      <c r="AS154">
+        <v>1.31</v>
+      </c>
+      <c r="AT154">
+        <v>2.89</v>
+      </c>
+      <c r="AU154">
+        <v>2</v>
+      </c>
+      <c r="AV154">
+        <v>6</v>
+      </c>
+      <c r="AW154">
+        <v>3</v>
+      </c>
+      <c r="AX154">
+        <v>5</v>
+      </c>
+      <c r="AY154">
+        <v>5</v>
+      </c>
+      <c r="AZ154">
+        <v>11</v>
+      </c>
+      <c r="BA154">
+        <v>0</v>
+      </c>
+      <c r="BB154">
+        <v>4</v>
+      </c>
+      <c r="BC154">
+        <v>4</v>
+      </c>
+      <c r="BD154">
+        <v>0</v>
+      </c>
+      <c r="BE154">
+        <v>0</v>
+      </c>
+      <c r="BF154">
+        <v>0</v>
+      </c>
+      <c r="BG154">
+        <v>0</v>
+      </c>
+      <c r="BH154">
+        <v>0</v>
+      </c>
+      <c r="BI154">
+        <v>0</v>
+      </c>
+      <c r="BJ154">
+        <v>0</v>
+      </c>
+      <c r="BK154">
+        <v>0</v>
+      </c>
+      <c r="BL154">
+        <v>0</v>
+      </c>
+      <c r="BM154">
+        <v>0</v>
+      </c>
+      <c r="BN154">
+        <v>0</v>
+      </c>
+      <c r="BO154">
+        <v>0</v>
+      </c>
+      <c r="BP154">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="155" spans="1:68">
+      <c r="A155" s="1">
+        <v>154</v>
+      </c>
+      <c r="B155">
+        <v>7468237</v>
+      </c>
+      <c r="C155" t="s">
+        <v>68</v>
+      </c>
+      <c r="D155" t="s">
+        <v>69</v>
+      </c>
+      <c r="E155" s="2">
+        <v>45689.5</v>
+      </c>
+      <c r="F155">
+        <v>20</v>
+      </c>
+      <c r="G155" t="s">
+        <v>72</v>
+      </c>
+      <c r="H155" t="s">
+        <v>74</v>
+      </c>
+      <c r="I155">
+        <v>0</v>
+      </c>
+      <c r="J155">
+        <v>0</v>
+      </c>
+      <c r="K155">
+        <v>0</v>
+      </c>
+      <c r="L155">
+        <v>0</v>
+      </c>
+      <c r="M155">
+        <v>0</v>
+      </c>
+      <c r="N155">
+        <v>0</v>
+      </c>
+      <c r="O155" t="s">
+        <v>88</v>
+      </c>
+      <c r="P155" t="s">
+        <v>88</v>
+      </c>
+      <c r="Q155">
+        <v>3.3</v>
+      </c>
+      <c r="R155">
+        <v>2.1</v>
+      </c>
+      <c r="S155">
+        <v>3.08</v>
+      </c>
+      <c r="T155">
+        <v>1.37</v>
+      </c>
+      <c r="U155">
+        <v>2.95</v>
+      </c>
+      <c r="V155">
+        <v>2.82</v>
+      </c>
+      <c r="W155">
+        <v>1.4</v>
+      </c>
+      <c r="X155">
+        <v>7.9</v>
+      </c>
+      <c r="Y155">
+        <v>1.06</v>
+      </c>
+      <c r="Z155">
+        <v>2.9</v>
+      </c>
+      <c r="AA155">
+        <v>3.36</v>
+      </c>
+      <c r="AB155">
+        <v>2.43</v>
+      </c>
+      <c r="AC155">
+        <v>1.03</v>
+      </c>
+      <c r="AD155">
+        <v>9</v>
+      </c>
+      <c r="AE155">
+        <v>1.23</v>
+      </c>
+      <c r="AF155">
+        <v>3.44</v>
+      </c>
+      <c r="AG155">
+        <v>1.9</v>
+      </c>
+      <c r="AH155">
+        <v>1.92</v>
+      </c>
+      <c r="AI155">
+        <v>1.69</v>
+      </c>
+      <c r="AJ155">
+        <v>2.04</v>
+      </c>
+      <c r="AK155">
+        <v>1.51</v>
+      </c>
+      <c r="AL155">
+        <v>1.29</v>
+      </c>
+      <c r="AM155">
+        <v>1.44</v>
+      </c>
+      <c r="AN155">
+        <v>0.2</v>
+      </c>
+      <c r="AO155">
+        <v>0.22</v>
+      </c>
+      <c r="AP155">
+        <v>0.27</v>
+      </c>
+      <c r="AQ155">
+        <v>0.3</v>
+      </c>
+      <c r="AR155">
+        <v>1.34</v>
+      </c>
+      <c r="AS155">
+        <v>0.93</v>
+      </c>
+      <c r="AT155">
+        <v>2.27</v>
+      </c>
+      <c r="AU155">
+        <v>3</v>
+      </c>
+      <c r="AV155">
+        <v>2</v>
+      </c>
+      <c r="AW155">
+        <v>4</v>
+      </c>
+      <c r="AX155">
+        <v>2</v>
+      </c>
+      <c r="AY155">
+        <v>7</v>
+      </c>
+      <c r="AZ155">
+        <v>4</v>
+      </c>
+      <c r="BA155">
+        <v>6</v>
+      </c>
+      <c r="BB155">
+        <v>6</v>
+      </c>
+      <c r="BC155">
+        <v>12</v>
+      </c>
+      <c r="BD155">
+        <v>2.12</v>
+      </c>
+      <c r="BE155">
+        <v>6.25</v>
+      </c>
+      <c r="BF155">
+        <v>1.9</v>
+      </c>
+      <c r="BG155">
+        <v>1.38</v>
+      </c>
+      <c r="BH155">
+        <v>2.75</v>
+      </c>
+      <c r="BI155">
+        <v>1.66</v>
+      </c>
+      <c r="BJ155">
+        <v>2.08</v>
+      </c>
+      <c r="BK155">
+        <v>2.05</v>
+      </c>
+      <c r="BL155">
+        <v>1.68</v>
+      </c>
+      <c r="BM155">
+        <v>2.63</v>
+      </c>
+      <c r="BN155">
+        <v>1.43</v>
+      </c>
+      <c r="BO155">
+        <v>3.45</v>
+      </c>
+      <c r="BP155">
+        <v>1.25</v>
+      </c>
+    </row>
+    <row r="156" spans="1:68">
+      <c r="A156" s="1">
+        <v>155</v>
+      </c>
+      <c r="B156">
+        <v>7468236</v>
+      </c>
+      <c r="C156" t="s">
+        <v>68</v>
+      </c>
+      <c r="D156" t="s">
+        <v>69</v>
+      </c>
+      <c r="E156" s="2">
+        <v>45689.5</v>
+      </c>
+      <c r="F156">
+        <v>20</v>
+      </c>
+      <c r="G156" t="s">
+        <v>81</v>
+      </c>
+      <c r="H156" t="s">
+        <v>83</v>
+      </c>
+      <c r="I156">
+        <v>0</v>
+      </c>
+      <c r="J156">
+        <v>1</v>
+      </c>
+      <c r="K156">
+        <v>1</v>
+      </c>
+      <c r="L156">
+        <v>0</v>
+      </c>
+      <c r="M156">
+        <v>1</v>
+      </c>
+      <c r="N156">
+        <v>1</v>
+      </c>
+      <c r="O156" t="s">
+        <v>88</v>
+      </c>
+      <c r="P156" t="s">
+        <v>201</v>
+      </c>
+      <c r="Q156">
+        <v>3.2</v>
+      </c>
+      <c r="R156">
+        <v>2.19</v>
+      </c>
+      <c r="S156">
+        <v>2.97</v>
+      </c>
+      <c r="T156">
+        <v>1.34</v>
+      </c>
+      <c r="U156">
+        <v>3.1</v>
+      </c>
+      <c r="V156">
+        <v>2.6</v>
+      </c>
+      <c r="W156">
+        <v>1.46</v>
+      </c>
+      <c r="X156">
+        <v>6.25</v>
+      </c>
+      <c r="Y156">
+        <v>1.1</v>
+      </c>
+      <c r="Z156">
+        <v>2.69</v>
+      </c>
+      <c r="AA156">
+        <v>3.55</v>
+      </c>
+      <c r="AB156">
+        <v>2.49</v>
+      </c>
+      <c r="AC156">
+        <v>1.01</v>
+      </c>
+      <c r="AD156">
+        <v>11</v>
+      </c>
+      <c r="AE156">
+        <v>1.21</v>
+      </c>
+      <c r="AF156">
+        <v>3.6</v>
+      </c>
+      <c r="AG156">
+        <v>1.77</v>
+      </c>
+      <c r="AH156">
+        <v>2.01</v>
+      </c>
+      <c r="AI156">
+        <v>1.61</v>
+      </c>
+      <c r="AJ156">
+        <v>2.17</v>
+      </c>
+      <c r="AK156">
+        <v>1.51</v>
+      </c>
+      <c r="AL156">
+        <v>1.28</v>
+      </c>
+      <c r="AM156">
+        <v>1.45</v>
+      </c>
+      <c r="AN156">
+        <v>1.44</v>
+      </c>
+      <c r="AO156">
+        <v>1.5</v>
+      </c>
+      <c r="AP156">
+        <v>1.3</v>
+      </c>
+      <c r="AQ156">
+        <v>1.64</v>
+      </c>
+      <c r="AR156">
+        <v>1.51</v>
+      </c>
+      <c r="AS156">
+        <v>1.63</v>
+      </c>
+      <c r="AT156">
+        <v>3.14</v>
+      </c>
+      <c r="AU156">
+        <v>2</v>
+      </c>
+      <c r="AV156">
+        <v>9</v>
+      </c>
+      <c r="AW156">
+        <v>1</v>
+      </c>
+      <c r="AX156">
+        <v>9</v>
+      </c>
+      <c r="AY156">
+        <v>3</v>
+      </c>
+      <c r="AZ156">
+        <v>18</v>
+      </c>
+      <c r="BA156">
+        <v>5</v>
+      </c>
+      <c r="BB156">
+        <v>6</v>
+      </c>
+      <c r="BC156">
+        <v>11</v>
+      </c>
+      <c r="BD156">
+        <v>2.07</v>
+      </c>
+      <c r="BE156">
+        <v>6.4</v>
+      </c>
+      <c r="BF156">
+        <v>1.94</v>
+      </c>
+      <c r="BG156">
+        <v>1.36</v>
+      </c>
+      <c r="BH156">
+        <v>2.8</v>
+      </c>
+      <c r="BI156">
+        <v>1.6</v>
+      </c>
+      <c r="BJ156">
+        <v>2.17</v>
+      </c>
+      <c r="BK156">
+        <v>1.98</v>
+      </c>
+      <c r="BL156">
+        <v>1.72</v>
+      </c>
+      <c r="BM156">
+        <v>2.55</v>
+      </c>
+      <c r="BN156">
+        <v>1.45</v>
+      </c>
+      <c r="BO156">
+        <v>3.3</v>
+      </c>
+      <c r="BP156">
+        <v>1.27</v>
+      </c>
+    </row>
+    <row r="157" spans="1:68">
+      <c r="A157" s="1">
+        <v>156</v>
+      </c>
+      <c r="B157">
+        <v>7468234</v>
+      </c>
+      <c r="C157" t="s">
+        <v>68</v>
+      </c>
+      <c r="D157" t="s">
+        <v>69</v>
+      </c>
+      <c r="E157" s="2">
+        <v>45689.625</v>
+      </c>
+      <c r="F157">
+        <v>20</v>
+      </c>
+      <c r="G157" t="s">
+        <v>77</v>
+      </c>
+      <c r="H157" t="s">
+        <v>79</v>
+      </c>
+      <c r="I157">
+        <v>2</v>
+      </c>
+      <c r="J157">
+        <v>0</v>
+      </c>
+      <c r="K157">
+        <v>2</v>
+      </c>
+      <c r="L157">
+        <v>3</v>
+      </c>
+      <c r="M157">
+        <v>0</v>
+      </c>
+      <c r="N157">
+        <v>3</v>
+      </c>
+      <c r="O157" t="s">
+        <v>191</v>
+      </c>
+      <c r="P157" t="s">
+        <v>88</v>
+      </c>
+      <c r="Q157">
+        <v>2.2</v>
+      </c>
+      <c r="R157">
+        <v>2</v>
+      </c>
+      <c r="S157">
+        <v>5.5</v>
+      </c>
+      <c r="T157">
+        <v>1.45</v>
+      </c>
+      <c r="U157">
+        <v>2.63</v>
+      </c>
+      <c r="V157">
+        <v>3.15</v>
+      </c>
+      <c r="W157">
+        <v>1.33</v>
+      </c>
+      <c r="X157">
+        <v>8.699999999999999</v>
+      </c>
+      <c r="Y157">
+        <v>1.05</v>
+      </c>
+      <c r="Z157">
+        <v>1.61</v>
+      </c>
+      <c r="AA157">
+        <v>3.69</v>
+      </c>
+      <c r="AB157">
+        <v>5.96</v>
+      </c>
+      <c r="AC157">
+        <v>1.05</v>
+      </c>
+      <c r="AD157">
+        <v>8</v>
+      </c>
+      <c r="AE157">
+        <v>1.33</v>
+      </c>
+      <c r="AF157">
+        <v>3</v>
+      </c>
+      <c r="AG157">
+        <v>2.2</v>
+      </c>
+      <c r="AH157">
+        <v>1.6</v>
+      </c>
+      <c r="AI157">
+        <v>2.15</v>
+      </c>
+      <c r="AJ157">
+        <v>1.67</v>
+      </c>
+      <c r="AK157">
+        <v>1.12</v>
+      </c>
+      <c r="AL157">
+        <v>1.25</v>
+      </c>
+      <c r="AM157">
+        <v>2.26</v>
+      </c>
+      <c r="AN157">
+        <v>1.56</v>
+      </c>
+      <c r="AO157">
+        <v>0.6</v>
+      </c>
+      <c r="AP157">
+        <v>1.7</v>
+      </c>
+      <c r="AQ157">
+        <v>0.55</v>
+      </c>
+      <c r="AR157">
+        <v>1.43</v>
+      </c>
+      <c r="AS157">
+        <v>1.06</v>
+      </c>
+      <c r="AT157">
+        <v>2.49</v>
+      </c>
+      <c r="AU157">
+        <v>8</v>
+      </c>
+      <c r="AV157">
+        <v>3</v>
+      </c>
+      <c r="AW157">
+        <v>5</v>
+      </c>
+      <c r="AX157">
+        <v>5</v>
+      </c>
+      <c r="AY157">
+        <v>13</v>
+      </c>
+      <c r="AZ157">
+        <v>8</v>
+      </c>
+      <c r="BA157">
+        <v>8</v>
+      </c>
+      <c r="BB157">
+        <v>1</v>
+      </c>
+      <c r="BC157">
+        <v>9</v>
+      </c>
+      <c r="BD157">
+        <v>1.48</v>
+      </c>
+      <c r="BE157">
+        <v>6.75</v>
+      </c>
+      <c r="BF157">
+        <v>3.05</v>
+      </c>
+      <c r="BG157">
+        <v>1.48</v>
+      </c>
+      <c r="BH157">
+        <v>2.43</v>
+      </c>
+      <c r="BI157">
+        <v>1.79</v>
+      </c>
+      <c r="BJ157">
+        <v>1.9</v>
+      </c>
+      <c r="BK157">
+        <v>2.28</v>
+      </c>
+      <c r="BL157">
+        <v>1.54</v>
+      </c>
+      <c r="BM157">
+        <v>2.95</v>
+      </c>
+      <c r="BN157">
+        <v>1.33</v>
+      </c>
+      <c r="BO157">
+        <v>3.95</v>
+      </c>
+      <c r="BP157">
+        <v>1.2</v>
+      </c>
+    </row>
+    <row r="158" spans="1:68">
+      <c r="A158" s="1">
+        <v>157</v>
+      </c>
+      <c r="B158">
+        <v>7468239</v>
+      </c>
+      <c r="C158" t="s">
+        <v>68</v>
+      </c>
+      <c r="D158" t="s">
+        <v>69</v>
+      </c>
+      <c r="E158" s="2">
+        <v>45690.375</v>
+      </c>
+      <c r="F158">
+        <v>20</v>
+      </c>
+      <c r="G158" t="s">
+        <v>76</v>
+      </c>
+      <c r="H158" t="s">
+        <v>70</v>
+      </c>
+      <c r="I158">
+        <v>0</v>
+      </c>
+      <c r="J158">
+        <v>2</v>
+      </c>
+      <c r="K158">
+        <v>2</v>
+      </c>
+      <c r="L158">
+        <v>0</v>
+      </c>
+      <c r="M158">
+        <v>2</v>
+      </c>
+      <c r="N158">
+        <v>2</v>
+      </c>
+      <c r="O158" t="s">
+        <v>88</v>
+      </c>
+      <c r="P158" t="s">
+        <v>268</v>
+      </c>
+      <c r="Q158">
+        <v>5</v>
+      </c>
+      <c r="R158">
+        <v>2.2</v>
+      </c>
+      <c r="S158">
+        <v>2.38</v>
+      </c>
+      <c r="T158">
+        <v>1.4</v>
+      </c>
+      <c r="U158">
+        <v>2.75</v>
+      </c>
+      <c r="V158">
+        <v>2.75</v>
+      </c>
+      <c r="W158">
+        <v>1.4</v>
+      </c>
+      <c r="X158">
+        <v>8</v>
+      </c>
+      <c r="Y158">
+        <v>1.08</v>
+      </c>
+      <c r="Z158">
+        <v>4.6</v>
+      </c>
+      <c r="AA158">
+        <v>3.72</v>
+      </c>
+      <c r="AB158">
+        <v>1.75</v>
+      </c>
+      <c r="AC158">
+        <v>1.05</v>
+      </c>
+      <c r="AD158">
+        <v>8.5</v>
+      </c>
+      <c r="AE158">
+        <v>1.28</v>
+      </c>
+      <c r="AF158">
+        <v>3.5</v>
+      </c>
+      <c r="AG158">
+        <v>1.93</v>
+      </c>
+      <c r="AH158">
+        <v>1.89</v>
+      </c>
+      <c r="AI158">
+        <v>1.8</v>
+      </c>
+      <c r="AJ158">
+        <v>1.95</v>
+      </c>
+      <c r="AK158">
+        <v>2.05</v>
+      </c>
+      <c r="AL158">
+        <v>1.26</v>
+      </c>
+      <c r="AM158">
+        <v>1.2</v>
+      </c>
+      <c r="AN158">
+        <v>1.56</v>
+      </c>
+      <c r="AO158">
+        <v>1.89</v>
+      </c>
+      <c r="AP158">
+        <v>1.4</v>
+      </c>
+      <c r="AQ158">
+        <v>2</v>
+      </c>
+      <c r="AR158">
+        <v>1.21</v>
+      </c>
+      <c r="AS158">
+        <v>1.67</v>
+      </c>
+      <c r="AT158">
+        <v>2.88</v>
+      </c>
+      <c r="AU158">
+        <v>0</v>
+      </c>
+      <c r="AV158">
+        <v>3</v>
+      </c>
+      <c r="AW158">
+        <v>0</v>
+      </c>
+      <c r="AX158">
+        <v>1</v>
+      </c>
+      <c r="AY158">
+        <v>0</v>
+      </c>
+      <c r="AZ158">
+        <v>4</v>
+      </c>
+      <c r="BA158">
+        <v>3</v>
+      </c>
+      <c r="BB158">
+        <v>8</v>
+      </c>
+      <c r="BC158">
+        <v>11</v>
+      </c>
+      <c r="BD158">
+        <v>2.65</v>
+      </c>
+      <c r="BE158">
+        <v>6.5</v>
+      </c>
+      <c r="BF158">
+        <v>1.58</v>
+      </c>
+      <c r="BG158">
+        <v>1.42</v>
+      </c>
+      <c r="BH158">
+        <v>2.65</v>
+      </c>
+      <c r="BI158">
+        <v>1.71</v>
+      </c>
+      <c r="BJ158">
+        <v>2</v>
+      </c>
+      <c r="BK158">
+        <v>2.12</v>
+      </c>
+      <c r="BL158">
+        <v>1.64</v>
+      </c>
+      <c r="BM158">
+        <v>2.7</v>
+      </c>
+      <c r="BN158">
+        <v>1.38</v>
+      </c>
+      <c r="BO158">
+        <v>3.55</v>
+      </c>
+      <c r="BP158">
+        <v>1.24</v>
       </c>
     </row>
   </sheetData>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Czech Republic First League_20242025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Czech Republic First League_20242025.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1010" uniqueCount="269">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1028" uniqueCount="270">
   <si>
     <t>Id_Jogo</t>
   </si>
@@ -592,6 +592,12 @@
     <t>['20', '27', '90+2']</t>
   </si>
   <si>
+    <t>['63']</t>
+  </si>
+  <si>
+    <t>['17', '35']</t>
+  </si>
+  <si>
     <t>['25']</t>
   </si>
   <si>
@@ -716,9 +722,6 @@
   </si>
   <si>
     <t>['5', '43', '89']</t>
-  </si>
-  <si>
-    <t>['63']</t>
   </si>
   <si>
     <t>['38', '83']</t>
@@ -1182,7 +1185,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:BP158"/>
+  <dimension ref="A1:BP161"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:68">
@@ -1438,7 +1441,7 @@
         <v>86</v>
       </c>
       <c r="P2" t="s">
-        <v>192</v>
+        <v>194</v>
       </c>
       <c r="Q2">
         <v>1.53</v>
@@ -1722,10 +1725,10 @@
         <v>0</v>
       </c>
       <c r="AP3">
-        <v>2.11</v>
+        <v>1.9</v>
       </c>
       <c r="AQ3">
-        <v>1.33</v>
+        <v>1.2</v>
       </c>
       <c r="AR3">
         <v>0</v>
@@ -1850,7 +1853,7 @@
         <v>88</v>
       </c>
       <c r="P4" t="s">
-        <v>193</v>
+        <v>195</v>
       </c>
       <c r="Q4">
         <v>2.88</v>
@@ -2262,7 +2265,7 @@
         <v>90</v>
       </c>
       <c r="P6" t="s">
-        <v>194</v>
+        <v>196</v>
       </c>
       <c r="Q6">
         <v>5.5</v>
@@ -2343,7 +2346,7 @@
         <v>1</v>
       </c>
       <c r="AQ6">
-        <v>1.89</v>
+        <v>1.7</v>
       </c>
       <c r="AR6">
         <v>0</v>
@@ -2468,7 +2471,7 @@
         <v>91</v>
       </c>
       <c r="P7" t="s">
-        <v>195</v>
+        <v>197</v>
       </c>
       <c r="Q7">
         <v>3.2</v>
@@ -3167,7 +3170,7 @@
         <v>1</v>
       </c>
       <c r="AQ10">
-        <v>1.33</v>
+        <v>1.5</v>
       </c>
       <c r="AR10">
         <v>0.98</v>
@@ -3292,7 +3295,7 @@
         <v>94</v>
       </c>
       <c r="P11" t="s">
-        <v>196</v>
+        <v>198</v>
       </c>
       <c r="Q11">
         <v>6.5</v>
@@ -3498,7 +3501,7 @@
         <v>88</v>
       </c>
       <c r="P12" t="s">
-        <v>197</v>
+        <v>199</v>
       </c>
       <c r="Q12">
         <v>2.85</v>
@@ -3910,7 +3913,7 @@
         <v>96</v>
       </c>
       <c r="P14" t="s">
-        <v>198</v>
+        <v>200</v>
       </c>
       <c r="Q14">
         <v>2.45</v>
@@ -4734,7 +4737,7 @@
         <v>88</v>
       </c>
       <c r="P18" t="s">
-        <v>199</v>
+        <v>201</v>
       </c>
       <c r="Q18">
         <v>5.4</v>
@@ -5227,7 +5230,7 @@
         <v>1.4</v>
       </c>
       <c r="AQ20">
-        <v>1.33</v>
+        <v>1.5</v>
       </c>
       <c r="AR20">
         <v>1</v>
@@ -5430,10 +5433,10 @@
         <v>3</v>
       </c>
       <c r="AP21">
-        <v>2.11</v>
+        <v>1.9</v>
       </c>
       <c r="AQ21">
-        <v>1.89</v>
+        <v>1.7</v>
       </c>
       <c r="AR21">
         <v>1.81</v>
@@ -5636,7 +5639,7 @@
         <v>0</v>
       </c>
       <c r="AP22">
-        <v>1.56</v>
+        <v>1.7</v>
       </c>
       <c r="AQ22">
         <v>0.9</v>
@@ -5764,7 +5767,7 @@
         <v>102</v>
       </c>
       <c r="P23" t="s">
-        <v>200</v>
+        <v>202</v>
       </c>
       <c r="Q23">
         <v>2.6</v>
@@ -5970,7 +5973,7 @@
         <v>103</v>
       </c>
       <c r="P24" t="s">
-        <v>201</v>
+        <v>203</v>
       </c>
       <c r="Q24">
         <v>2.75</v>
@@ -6051,7 +6054,7 @@
         <v>1.7</v>
       </c>
       <c r="AQ24">
-        <v>1.33</v>
+        <v>1.2</v>
       </c>
       <c r="AR24">
         <v>1.19</v>
@@ -6176,7 +6179,7 @@
         <v>88</v>
       </c>
       <c r="P25" t="s">
-        <v>202</v>
+        <v>204</v>
       </c>
       <c r="Q25">
         <v>1.06</v>
@@ -6382,7 +6385,7 @@
         <v>104</v>
       </c>
       <c r="P26" t="s">
-        <v>203</v>
+        <v>205</v>
       </c>
       <c r="Q26">
         <v>6.23</v>
@@ -8030,7 +8033,7 @@
         <v>111</v>
       </c>
       <c r="P34" t="s">
-        <v>204</v>
+        <v>206</v>
       </c>
       <c r="Q34">
         <v>1.45</v>
@@ -8236,7 +8239,7 @@
         <v>112</v>
       </c>
       <c r="P35" t="s">
-        <v>205</v>
+        <v>207</v>
       </c>
       <c r="Q35">
         <v>2.84</v>
@@ -8317,7 +8320,7 @@
         <v>1.45</v>
       </c>
       <c r="AQ35">
-        <v>1.33</v>
+        <v>1.5</v>
       </c>
       <c r="AR35">
         <v>1.93</v>
@@ -8442,7 +8445,7 @@
         <v>113</v>
       </c>
       <c r="P36" t="s">
-        <v>206</v>
+        <v>208</v>
       </c>
       <c r="Q36">
         <v>5.63</v>
@@ -8520,7 +8523,7 @@
         <v>3</v>
       </c>
       <c r="AP36">
-        <v>2.11</v>
+        <v>1.9</v>
       </c>
       <c r="AQ36">
         <v>2</v>
@@ -8648,7 +8651,7 @@
         <v>114</v>
       </c>
       <c r="P37" t="s">
-        <v>207</v>
+        <v>209</v>
       </c>
       <c r="Q37">
         <v>2.58</v>
@@ -8726,10 +8729,10 @@
         <v>0</v>
       </c>
       <c r="AP37">
-        <v>1.56</v>
+        <v>1.7</v>
       </c>
       <c r="AQ37">
-        <v>1.33</v>
+        <v>1.2</v>
       </c>
       <c r="AR37">
         <v>1.25</v>
@@ -9060,7 +9063,7 @@
         <v>88</v>
       </c>
       <c r="P39" t="s">
-        <v>208</v>
+        <v>210</v>
       </c>
       <c r="Q39">
         <v>4.75</v>
@@ -9141,7 +9144,7 @@
         <v>0.27</v>
       </c>
       <c r="AQ39">
-        <v>1.89</v>
+        <v>1.7</v>
       </c>
       <c r="AR39">
         <v>1.46</v>
@@ -9472,7 +9475,7 @@
         <v>117</v>
       </c>
       <c r="P41" t="s">
-        <v>209</v>
+        <v>211</v>
       </c>
       <c r="Q41">
         <v>2.4</v>
@@ -9678,7 +9681,7 @@
         <v>107</v>
       </c>
       <c r="P42" t="s">
-        <v>210</v>
+        <v>212</v>
       </c>
       <c r="Q42">
         <v>2.61</v>
@@ -9884,7 +9887,7 @@
         <v>118</v>
       </c>
       <c r="P43" t="s">
-        <v>211</v>
+        <v>213</v>
       </c>
       <c r="Q43">
         <v>1.69</v>
@@ -10995,7 +10998,7 @@
         <v>0.27</v>
       </c>
       <c r="AQ48">
-        <v>1.33</v>
+        <v>1.5</v>
       </c>
       <c r="AR48">
         <v>1.34</v>
@@ -11326,7 +11329,7 @@
         <v>88</v>
       </c>
       <c r="P50" t="s">
-        <v>212</v>
+        <v>214</v>
       </c>
       <c r="Q50">
         <v>5.1</v>
@@ -11738,7 +11741,7 @@
         <v>122</v>
       </c>
       <c r="P52" t="s">
-        <v>213</v>
+        <v>215</v>
       </c>
       <c r="Q52">
         <v>3</v>
@@ -11816,7 +11819,7 @@
         <v>0.33</v>
       </c>
       <c r="AP52">
-        <v>1.56</v>
+        <v>1.7</v>
       </c>
       <c r="AQ52">
         <v>1.64</v>
@@ -12150,7 +12153,7 @@
         <v>124</v>
       </c>
       <c r="P54" t="s">
-        <v>214</v>
+        <v>216</v>
       </c>
       <c r="Q54">
         <v>3</v>
@@ -12231,7 +12234,7 @@
         <v>1.3</v>
       </c>
       <c r="AQ54">
-        <v>1.33</v>
+        <v>1.2</v>
       </c>
       <c r="AR54">
         <v>1.4</v>
@@ -12437,7 +12440,7 @@
         <v>1.3</v>
       </c>
       <c r="AQ55">
-        <v>1.89</v>
+        <v>1.7</v>
       </c>
       <c r="AR55">
         <v>1.32</v>
@@ -12562,7 +12565,7 @@
         <v>125</v>
       </c>
       <c r="P56" t="s">
-        <v>215</v>
+        <v>217</v>
       </c>
       <c r="Q56">
         <v>1.85</v>
@@ -12768,7 +12771,7 @@
         <v>88</v>
       </c>
       <c r="P57" t="s">
-        <v>216</v>
+        <v>218</v>
       </c>
       <c r="Q57">
         <v>5.88</v>
@@ -13180,7 +13183,7 @@
         <v>127</v>
       </c>
       <c r="P59" t="s">
-        <v>217</v>
+        <v>219</v>
       </c>
       <c r="Q59">
         <v>3.86</v>
@@ -13673,7 +13676,7 @@
         <v>3</v>
       </c>
       <c r="AQ61">
-        <v>1.89</v>
+        <v>1.7</v>
       </c>
       <c r="AR61">
         <v>2.33</v>
@@ -13798,7 +13801,7 @@
         <v>130</v>
       </c>
       <c r="P62" t="s">
-        <v>218</v>
+        <v>220</v>
       </c>
       <c r="Q62">
         <v>1.83</v>
@@ -14004,7 +14007,7 @@
         <v>88</v>
       </c>
       <c r="P63" t="s">
-        <v>219</v>
+        <v>221</v>
       </c>
       <c r="Q63">
         <v>8.77</v>
@@ -14288,7 +14291,7 @@
         <v>0.33</v>
       </c>
       <c r="AP64">
-        <v>1.56</v>
+        <v>1.7</v>
       </c>
       <c r="AQ64">
         <v>0.3</v>
@@ -14416,7 +14419,7 @@
         <v>132</v>
       </c>
       <c r="P65" t="s">
-        <v>220</v>
+        <v>222</v>
       </c>
       <c r="Q65">
         <v>2.4</v>
@@ -14497,7 +14500,7 @@
         <v>1.3</v>
       </c>
       <c r="AQ65">
-        <v>1.33</v>
+        <v>1.5</v>
       </c>
       <c r="AR65">
         <v>1.42</v>
@@ -14622,7 +14625,7 @@
         <v>133</v>
       </c>
       <c r="P66" t="s">
-        <v>221</v>
+        <v>223</v>
       </c>
       <c r="Q66">
         <v>1.55</v>
@@ -14828,7 +14831,7 @@
         <v>134</v>
       </c>
       <c r="P67" t="s">
-        <v>222</v>
+        <v>224</v>
       </c>
       <c r="Q67">
         <v>4</v>
@@ -15034,7 +15037,7 @@
         <v>88</v>
       </c>
       <c r="P68" t="s">
-        <v>223</v>
+        <v>225</v>
       </c>
       <c r="Q68">
         <v>3.1</v>
@@ -15524,7 +15527,7 @@
         <v>0</v>
       </c>
       <c r="AP70">
-        <v>2.11</v>
+        <v>1.9</v>
       </c>
       <c r="AQ70">
         <v>1.1</v>
@@ -15858,7 +15861,7 @@
         <v>124</v>
       </c>
       <c r="P72" t="s">
-        <v>224</v>
+        <v>226</v>
       </c>
       <c r="Q72">
         <v>1.88</v>
@@ -15939,7 +15942,7 @@
         <v>2.6</v>
       </c>
       <c r="AQ72">
-        <v>1.33</v>
+        <v>1.2</v>
       </c>
       <c r="AR72">
         <v>1.84</v>
@@ -16064,7 +16067,7 @@
         <v>88</v>
       </c>
       <c r="P73" t="s">
-        <v>225</v>
+        <v>227</v>
       </c>
       <c r="Q73">
         <v>7</v>
@@ -16476,7 +16479,7 @@
         <v>138</v>
       </c>
       <c r="P75" t="s">
-        <v>226</v>
+        <v>228</v>
       </c>
       <c r="Q75">
         <v>2.3</v>
@@ -16682,7 +16685,7 @@
         <v>88</v>
       </c>
       <c r="P76" t="s">
-        <v>227</v>
+        <v>229</v>
       </c>
       <c r="Q76">
         <v>3.7</v>
@@ -16888,7 +16891,7 @@
         <v>88</v>
       </c>
       <c r="P77" t="s">
-        <v>228</v>
+        <v>230</v>
       </c>
       <c r="Q77">
         <v>2.47</v>
@@ -17506,7 +17509,7 @@
         <v>140</v>
       </c>
       <c r="P80" t="s">
-        <v>229</v>
+        <v>231</v>
       </c>
       <c r="Q80">
         <v>2.5</v>
@@ -17584,10 +17587,10 @@
         <v>1.2</v>
       </c>
       <c r="AP80">
-        <v>1.56</v>
+        <v>1.7</v>
       </c>
       <c r="AQ80">
-        <v>1.33</v>
+        <v>1.5</v>
       </c>
       <c r="AR80">
         <v>1.66</v>
@@ -17712,7 +17715,7 @@
         <v>141</v>
       </c>
       <c r="P81" t="s">
-        <v>230</v>
+        <v>232</v>
       </c>
       <c r="Q81">
         <v>2.38</v>
@@ -17918,7 +17921,7 @@
         <v>142</v>
       </c>
       <c r="P82" t="s">
-        <v>231</v>
+        <v>233</v>
       </c>
       <c r="Q82">
         <v>2.8</v>
@@ -18124,7 +18127,7 @@
         <v>143</v>
       </c>
       <c r="P83" t="s">
-        <v>232</v>
+        <v>234</v>
       </c>
       <c r="Q83">
         <v>2.6</v>
@@ -18330,7 +18333,7 @@
         <v>144</v>
       </c>
       <c r="P84" t="s">
-        <v>233</v>
+        <v>235</v>
       </c>
       <c r="Q84">
         <v>3.4</v>
@@ -18411,7 +18414,7 @@
         <v>2.33</v>
       </c>
       <c r="AQ84">
-        <v>1.89</v>
+        <v>1.7</v>
       </c>
       <c r="AR84">
         <v>1.81</v>
@@ -18536,7 +18539,7 @@
         <v>145</v>
       </c>
       <c r="P85" t="s">
-        <v>234</v>
+        <v>192</v>
       </c>
       <c r="Q85">
         <v>1.65</v>
@@ -18742,7 +18745,7 @@
         <v>146</v>
       </c>
       <c r="P86" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="Q86">
         <v>2.88</v>
@@ -18823,7 +18826,7 @@
         <v>1</v>
       </c>
       <c r="AQ86">
-        <v>1.33</v>
+        <v>1.2</v>
       </c>
       <c r="AR86">
         <v>1.41</v>
@@ -19154,7 +19157,7 @@
         <v>88</v>
       </c>
       <c r="P88" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="Q88">
         <v>2.6</v>
@@ -19360,7 +19363,7 @@
         <v>93</v>
       </c>
       <c r="P89" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="Q89">
         <v>6.5</v>
@@ -19438,7 +19441,7 @@
         <v>2.5</v>
       </c>
       <c r="AP89">
-        <v>2.11</v>
+        <v>1.9</v>
       </c>
       <c r="AQ89">
         <v>2.3</v>
@@ -19772,7 +19775,7 @@
         <v>149</v>
       </c>
       <c r="P91" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="Q91">
         <v>4.7</v>
@@ -19978,7 +19981,7 @@
         <v>88</v>
       </c>
       <c r="P92" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="Q92">
         <v>3.8</v>
@@ -20262,7 +20265,7 @@
         <v>1.67</v>
       </c>
       <c r="AP93">
-        <v>1.56</v>
+        <v>1.7</v>
       </c>
       <c r="AQ93">
         <v>1.1</v>
@@ -20390,7 +20393,7 @@
         <v>150</v>
       </c>
       <c r="P94" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="Q94">
         <v>3</v>
@@ -20471,7 +20474,7 @@
         <v>1.3</v>
       </c>
       <c r="AQ94">
-        <v>1.33</v>
+        <v>1.5</v>
       </c>
       <c r="AR94">
         <v>1.52</v>
@@ -21295,7 +21298,7 @@
         <v>1</v>
       </c>
       <c r="AQ98">
-        <v>1.33</v>
+        <v>1.2</v>
       </c>
       <c r="AR98">
         <v>1.15</v>
@@ -21498,7 +21501,7 @@
         <v>1.2</v>
       </c>
       <c r="AP99">
-        <v>2.11</v>
+        <v>1.9</v>
       </c>
       <c r="AQ99">
         <v>0.9</v>
@@ -21832,7 +21835,7 @@
         <v>156</v>
       </c>
       <c r="P101" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="Q101">
         <v>1.83</v>
@@ -22531,7 +22534,7 @@
         <v>1.4</v>
       </c>
       <c r="AQ104">
-        <v>1.89</v>
+        <v>1.7</v>
       </c>
       <c r="AR104">
         <v>1.15</v>
@@ -23480,7 +23483,7 @@
         <v>161</v>
       </c>
       <c r="P109" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="Q109">
         <v>2.24</v>
@@ -23686,7 +23689,7 @@
         <v>162</v>
       </c>
       <c r="P110" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="Q110">
         <v>4.6</v>
@@ -23973,7 +23976,7 @@
         <v>2.6</v>
       </c>
       <c r="AQ111">
-        <v>1.33</v>
+        <v>1.5</v>
       </c>
       <c r="AR111">
         <v>1.73</v>
@@ -24098,7 +24101,7 @@
         <v>164</v>
       </c>
       <c r="P112" t="s">
-        <v>198</v>
+        <v>200</v>
       </c>
       <c r="Q112">
         <v>1.44</v>
@@ -24304,7 +24307,7 @@
         <v>165</v>
       </c>
       <c r="P113" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="Q113">
         <v>3.25</v>
@@ -24382,7 +24385,7 @@
         <v>1.5</v>
       </c>
       <c r="AP113">
-        <v>2.11</v>
+        <v>1.9</v>
       </c>
       <c r="AQ113">
         <v>1.64</v>
@@ -24510,7 +24513,7 @@
         <v>99</v>
       </c>
       <c r="P114" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="Q114">
         <v>1.73</v>
@@ -24716,7 +24719,7 @@
         <v>151</v>
       </c>
       <c r="P115" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="Q115">
         <v>2.88</v>
@@ -24797,7 +24800,7 @@
         <v>1.4</v>
       </c>
       <c r="AQ115">
-        <v>1.33</v>
+        <v>1.2</v>
       </c>
       <c r="AR115">
         <v>1.11</v>
@@ -24922,7 +24925,7 @@
         <v>88</v>
       </c>
       <c r="P116" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="Q116">
         <v>4.33</v>
@@ -25003,7 +25006,7 @@
         <v>1.7</v>
       </c>
       <c r="AQ116">
-        <v>1.89</v>
+        <v>1.7</v>
       </c>
       <c r="AR116">
         <v>1.34</v>
@@ -25334,7 +25337,7 @@
         <v>88</v>
       </c>
       <c r="P118" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="Q118">
         <v>15</v>
@@ -25746,7 +25749,7 @@
         <v>168</v>
       </c>
       <c r="P120" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="Q120">
         <v>3</v>
@@ -25824,7 +25827,7 @@
         <v>1.17</v>
       </c>
       <c r="AP120">
-        <v>1.56</v>
+        <v>1.7</v>
       </c>
       <c r="AQ120">
         <v>1.1</v>
@@ -26030,7 +26033,7 @@
         <v>1.17</v>
       </c>
       <c r="AP121">
-        <v>1.56</v>
+        <v>1.7</v>
       </c>
       <c r="AQ121">
         <v>1.1</v>
@@ -26158,7 +26161,7 @@
         <v>170</v>
       </c>
       <c r="P122" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="Q122">
         <v>3.25</v>
@@ -26364,7 +26367,7 @@
         <v>171</v>
       </c>
       <c r="P123" t="s">
-        <v>197</v>
+        <v>199</v>
       </c>
       <c r="Q123">
         <v>1.83</v>
@@ -26776,7 +26779,7 @@
         <v>172</v>
       </c>
       <c r="P125" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="Q125">
         <v>6.3</v>
@@ -27600,7 +27603,7 @@
         <v>174</v>
       </c>
       <c r="P129" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="Q129">
         <v>2.1</v>
@@ -27806,7 +27809,7 @@
         <v>175</v>
       </c>
       <c r="P130" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="Q130">
         <v>1.5</v>
@@ -28090,7 +28093,7 @@
         <v>0.14</v>
       </c>
       <c r="AP131">
-        <v>2.11</v>
+        <v>1.9</v>
       </c>
       <c r="AQ131">
         <v>0.11</v>
@@ -28218,7 +28221,7 @@
         <v>177</v>
       </c>
       <c r="P132" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="Q132">
         <v>4.04</v>
@@ -28424,7 +28427,7 @@
         <v>178</v>
       </c>
       <c r="P133" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="Q133">
         <v>3.5</v>
@@ -28630,7 +28633,7 @@
         <v>88</v>
       </c>
       <c r="P134" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="Q134">
         <v>2.75</v>
@@ -29042,7 +29045,7 @@
         <v>88</v>
       </c>
       <c r="P136" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="Q136">
         <v>4.5</v>
@@ -29454,7 +29457,7 @@
         <v>91</v>
       </c>
       <c r="P138" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="Q138">
         <v>2.25</v>
@@ -29660,7 +29663,7 @@
         <v>179</v>
       </c>
       <c r="P139" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="Q139">
         <v>1.9</v>
@@ -29738,7 +29741,7 @@
         <v>0.25</v>
       </c>
       <c r="AP139">
-        <v>2.11</v>
+        <v>1.9</v>
       </c>
       <c r="AQ139">
         <v>0.3</v>
@@ -29947,7 +29950,7 @@
         <v>2</v>
       </c>
       <c r="AQ140">
-        <v>1.33</v>
+        <v>1.5</v>
       </c>
       <c r="AR140">
         <v>2.06</v>
@@ -30072,7 +30075,7 @@
         <v>117</v>
       </c>
       <c r="P141" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="Q141">
         <v>4</v>
@@ -30153,7 +30156,7 @@
         <v>1.45</v>
       </c>
       <c r="AQ141">
-        <v>1.89</v>
+        <v>1.7</v>
       </c>
       <c r="AR141">
         <v>1.59</v>
@@ -30278,7 +30281,7 @@
         <v>88</v>
       </c>
       <c r="P142" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="Q142">
         <v>4</v>
@@ -30359,7 +30362,7 @@
         <v>0.27</v>
       </c>
       <c r="AQ142">
-        <v>1.33</v>
+        <v>1.2</v>
       </c>
       <c r="AR142">
         <v>1.34</v>
@@ -30690,7 +30693,7 @@
         <v>182</v>
       </c>
       <c r="P144" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="Q144">
         <v>6</v>
@@ -30768,7 +30771,7 @@
         <v>2.5</v>
       </c>
       <c r="AP144">
-        <v>1.56</v>
+        <v>1.7</v>
       </c>
       <c r="AQ144">
         <v>2.3</v>
@@ -30896,7 +30899,7 @@
         <v>88</v>
       </c>
       <c r="P145" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="Q145">
         <v>3.5</v>
@@ -31102,7 +31105,7 @@
         <v>183</v>
       </c>
       <c r="P146" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="Q146">
         <v>4.33</v>
@@ -31308,7 +31311,7 @@
         <v>184</v>
       </c>
       <c r="P147" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="Q147">
         <v>3.8</v>
@@ -31514,7 +31517,7 @@
         <v>185</v>
       </c>
       <c r="P148" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="Q148">
         <v>2.5</v>
@@ -31720,7 +31723,7 @@
         <v>186</v>
       </c>
       <c r="P149" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="Q149">
         <v>2.05</v>
@@ -31926,7 +31929,7 @@
         <v>187</v>
       </c>
       <c r="P150" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="Q150">
         <v>1.95</v>
@@ -32132,7 +32135,7 @@
         <v>188</v>
       </c>
       <c r="P151" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="Q151">
         <v>2.48</v>
@@ -32544,7 +32547,7 @@
         <v>190</v>
       </c>
       <c r="P153" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="Q153">
         <v>1.4</v>
@@ -33162,7 +33165,7 @@
         <v>88</v>
       </c>
       <c r="P156" t="s">
-        <v>201</v>
+        <v>203</v>
       </c>
       <c r="Q156">
         <v>3.2</v>
@@ -33574,7 +33577,7 @@
         <v>88</v>
       </c>
       <c r="P158" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="Q158">
         <v>5</v>
@@ -33731,6 +33734,624 @@
       </c>
       <c r="BP158">
         <v>1.24</v>
+      </c>
+    </row>
+    <row r="159" spans="1:68">
+      <c r="A159" s="1">
+        <v>158</v>
+      </c>
+      <c r="B159">
+        <v>7468238</v>
+      </c>
+      <c r="C159" t="s">
+        <v>68</v>
+      </c>
+      <c r="D159" t="s">
+        <v>69</v>
+      </c>
+      <c r="E159" s="2">
+        <v>45690.47916666666</v>
+      </c>
+      <c r="F159">
+        <v>20</v>
+      </c>
+      <c r="G159" t="s">
+        <v>71</v>
+      </c>
+      <c r="H159" t="s">
+        <v>73</v>
+      </c>
+      <c r="I159">
+        <v>0</v>
+      </c>
+      <c r="J159">
+        <v>0</v>
+      </c>
+      <c r="K159">
+        <v>0</v>
+      </c>
+      <c r="L159">
+        <v>0</v>
+      </c>
+      <c r="M159">
+        <v>1</v>
+      </c>
+      <c r="N159">
+        <v>1</v>
+      </c>
+      <c r="O159" t="s">
+        <v>88</v>
+      </c>
+      <c r="P159" t="s">
+        <v>225</v>
+      </c>
+      <c r="Q159">
+        <v>2.38</v>
+      </c>
+      <c r="R159">
+        <v>2.25</v>
+      </c>
+      <c r="S159">
+        <v>4.75</v>
+      </c>
+      <c r="T159">
+        <v>1.36</v>
+      </c>
+      <c r="U159">
+        <v>3</v>
+      </c>
+      <c r="V159">
+        <v>2.75</v>
+      </c>
+      <c r="W159">
+        <v>1.4</v>
+      </c>
+      <c r="X159">
+        <v>7</v>
+      </c>
+      <c r="Y159">
+        <v>1.1</v>
+      </c>
+      <c r="Z159">
+        <v>1.67</v>
+      </c>
+      <c r="AA159">
+        <v>3.56</v>
+      </c>
+      <c r="AB159">
+        <v>4.16</v>
+      </c>
+      <c r="AC159">
+        <v>1.04</v>
+      </c>
+      <c r="AD159">
+        <v>9</v>
+      </c>
+      <c r="AE159">
+        <v>1.25</v>
+      </c>
+      <c r="AF159">
+        <v>3.75</v>
+      </c>
+      <c r="AG159">
+        <v>1.75</v>
+      </c>
+      <c r="AH159">
+        <v>1.86</v>
+      </c>
+      <c r="AI159">
+        <v>1.8</v>
+      </c>
+      <c r="AJ159">
+        <v>1.95</v>
+      </c>
+      <c r="AK159">
+        <v>1.2</v>
+      </c>
+      <c r="AL159">
+        <v>1.26</v>
+      </c>
+      <c r="AM159">
+        <v>2</v>
+      </c>
+      <c r="AN159">
+        <v>2.11</v>
+      </c>
+      <c r="AO159">
+        <v>1.33</v>
+      </c>
+      <c r="AP159">
+        <v>1.9</v>
+      </c>
+      <c r="AQ159">
+        <v>1.5</v>
+      </c>
+      <c r="AR159">
+        <v>1.67</v>
+      </c>
+      <c r="AS159">
+        <v>1.35</v>
+      </c>
+      <c r="AT159">
+        <v>3.02</v>
+      </c>
+      <c r="AU159">
+        <v>5</v>
+      </c>
+      <c r="AV159">
+        <v>3</v>
+      </c>
+      <c r="AW159">
+        <v>8</v>
+      </c>
+      <c r="AX159">
+        <v>8</v>
+      </c>
+      <c r="AY159">
+        <v>13</v>
+      </c>
+      <c r="AZ159">
+        <v>11</v>
+      </c>
+      <c r="BA159">
+        <v>5</v>
+      </c>
+      <c r="BB159">
+        <v>12</v>
+      </c>
+      <c r="BC159">
+        <v>17</v>
+      </c>
+      <c r="BD159">
+        <v>0</v>
+      </c>
+      <c r="BE159">
+        <v>0</v>
+      </c>
+      <c r="BF159">
+        <v>0</v>
+      </c>
+      <c r="BG159">
+        <v>0</v>
+      </c>
+      <c r="BH159">
+        <v>0</v>
+      </c>
+      <c r="BI159">
+        <v>0</v>
+      </c>
+      <c r="BJ159">
+        <v>0</v>
+      </c>
+      <c r="BK159">
+        <v>0</v>
+      </c>
+      <c r="BL159">
+        <v>0</v>
+      </c>
+      <c r="BM159">
+        <v>1.88</v>
+      </c>
+      <c r="BN159">
+        <v>1.92</v>
+      </c>
+      <c r="BO159">
+        <v>0</v>
+      </c>
+      <c r="BP159">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="160" spans="1:68">
+      <c r="A160" s="1">
+        <v>159</v>
+      </c>
+      <c r="B160">
+        <v>7468233</v>
+      </c>
+      <c r="C160" t="s">
+        <v>68</v>
+      </c>
+      <c r="D160" t="s">
+        <v>69</v>
+      </c>
+      <c r="E160" s="2">
+        <v>45690.60416666666</v>
+      </c>
+      <c r="F160">
+        <v>20</v>
+      </c>
+      <c r="G160" t="s">
+        <v>80</v>
+      </c>
+      <c r="H160" t="s">
+        <v>82</v>
+      </c>
+      <c r="I160">
+        <v>0</v>
+      </c>
+      <c r="J160">
+        <v>0</v>
+      </c>
+      <c r="K160">
+        <v>0</v>
+      </c>
+      <c r="L160">
+        <v>1</v>
+      </c>
+      <c r="M160">
+        <v>0</v>
+      </c>
+      <c r="N160">
+        <v>1</v>
+      </c>
+      <c r="O160" t="s">
+        <v>192</v>
+      </c>
+      <c r="P160" t="s">
+        <v>88</v>
+      </c>
+      <c r="Q160">
+        <v>1.62</v>
+      </c>
+      <c r="R160">
+        <v>2.75</v>
+      </c>
+      <c r="S160">
+        <v>10</v>
+      </c>
+      <c r="T160">
+        <v>1.25</v>
+      </c>
+      <c r="U160">
+        <v>3.75</v>
+      </c>
+      <c r="V160">
+        <v>2.25</v>
+      </c>
+      <c r="W160">
+        <v>1.57</v>
+      </c>
+      <c r="X160">
+        <v>5.5</v>
+      </c>
+      <c r="Y160">
+        <v>1.14</v>
+      </c>
+      <c r="Z160">
+        <v>1.18</v>
+      </c>
+      <c r="AA160">
+        <v>5.75</v>
+      </c>
+      <c r="AB160">
+        <v>11</v>
+      </c>
+      <c r="AC160">
+        <v>1.01</v>
+      </c>
+      <c r="AD160">
+        <v>17</v>
+      </c>
+      <c r="AE160">
+        <v>1.15</v>
+      </c>
+      <c r="AF160">
+        <v>5</v>
+      </c>
+      <c r="AG160">
+        <v>1.53</v>
+      </c>
+      <c r="AH160">
+        <v>2.4</v>
+      </c>
+      <c r="AI160">
+        <v>2.2</v>
+      </c>
+      <c r="AJ160">
+        <v>1.62</v>
+      </c>
+      <c r="AK160">
+        <v>1.03</v>
+      </c>
+      <c r="AL160">
+        <v>1.11</v>
+      </c>
+      <c r="AM160">
+        <v>4.33</v>
+      </c>
+      <c r="AN160">
+        <v>3</v>
+      </c>
+      <c r="AO160">
+        <v>1.33</v>
+      </c>
+      <c r="AP160">
+        <v>3</v>
+      </c>
+      <c r="AQ160">
+        <v>1.2</v>
+      </c>
+      <c r="AR160">
+        <v>2.39</v>
+      </c>
+      <c r="AS160">
+        <v>1.34</v>
+      </c>
+      <c r="AT160">
+        <v>3.73</v>
+      </c>
+      <c r="AU160">
+        <v>4</v>
+      </c>
+      <c r="AV160">
+        <v>2</v>
+      </c>
+      <c r="AW160">
+        <v>10</v>
+      </c>
+      <c r="AX160">
+        <v>3</v>
+      </c>
+      <c r="AY160">
+        <v>14</v>
+      </c>
+      <c r="AZ160">
+        <v>5</v>
+      </c>
+      <c r="BA160">
+        <v>5</v>
+      </c>
+      <c r="BB160">
+        <v>5</v>
+      </c>
+      <c r="BC160">
+        <v>10</v>
+      </c>
+      <c r="BD160">
+        <v>1.25</v>
+      </c>
+      <c r="BE160">
+        <v>7.5</v>
+      </c>
+      <c r="BF160">
+        <v>4.3</v>
+      </c>
+      <c r="BG160">
+        <v>1.33</v>
+      </c>
+      <c r="BH160">
+        <v>2.95</v>
+      </c>
+      <c r="BI160">
+        <v>1.56</v>
+      </c>
+      <c r="BJ160">
+        <v>2.23</v>
+      </c>
+      <c r="BK160">
+        <v>1.91</v>
+      </c>
+      <c r="BL160">
+        <v>1.79</v>
+      </c>
+      <c r="BM160">
+        <v>2.4</v>
+      </c>
+      <c r="BN160">
+        <v>1.49</v>
+      </c>
+      <c r="BO160">
+        <v>3.05</v>
+      </c>
+      <c r="BP160">
+        <v>1.3</v>
+      </c>
+    </row>
+    <row r="161" spans="1:68">
+      <c r="A161" s="1">
+        <v>160</v>
+      </c>
+      <c r="B161">
+        <v>7468235</v>
+      </c>
+      <c r="C161" t="s">
+        <v>68</v>
+      </c>
+      <c r="D161" t="s">
+        <v>69</v>
+      </c>
+      <c r="E161" s="2">
+        <v>45691.58333333334</v>
+      </c>
+      <c r="F161">
+        <v>20</v>
+      </c>
+      <c r="G161" t="s">
+        <v>85</v>
+      </c>
+      <c r="H161" t="s">
+        <v>84</v>
+      </c>
+      <c r="I161">
+        <v>2</v>
+      </c>
+      <c r="J161">
+        <v>1</v>
+      </c>
+      <c r="K161">
+        <v>3</v>
+      </c>
+      <c r="L161">
+        <v>2</v>
+      </c>
+      <c r="M161">
+        <v>1</v>
+      </c>
+      <c r="N161">
+        <v>3</v>
+      </c>
+      <c r="O161" t="s">
+        <v>193</v>
+      </c>
+      <c r="P161" t="s">
+        <v>252</v>
+      </c>
+      <c r="Q161">
+        <v>4.75</v>
+      </c>
+      <c r="R161">
+        <v>2.3</v>
+      </c>
+      <c r="S161">
+        <v>2.3</v>
+      </c>
+      <c r="T161">
+        <v>1.33</v>
+      </c>
+      <c r="U161">
+        <v>3.25</v>
+      </c>
+      <c r="V161">
+        <v>2.63</v>
+      </c>
+      <c r="W161">
+        <v>1.44</v>
+      </c>
+      <c r="X161">
+        <v>6.5</v>
+      </c>
+      <c r="Y161">
+        <v>1.11</v>
+      </c>
+      <c r="Z161">
+        <v>4.23</v>
+      </c>
+      <c r="AA161">
+        <v>3.81</v>
+      </c>
+      <c r="AB161">
+        <v>1.71</v>
+      </c>
+      <c r="AC161">
+        <v>1.04</v>
+      </c>
+      <c r="AD161">
+        <v>11</v>
+      </c>
+      <c r="AE161">
+        <v>1.23</v>
+      </c>
+      <c r="AF161">
+        <v>3.8</v>
+      </c>
+      <c r="AG161">
+        <v>1.73</v>
+      </c>
+      <c r="AH161">
+        <v>2.08</v>
+      </c>
+      <c r="AI161">
+        <v>1.75</v>
+      </c>
+      <c r="AJ161">
+        <v>2</v>
+      </c>
+      <c r="AK161">
+        <v>2.07</v>
+      </c>
+      <c r="AL161">
+        <v>1.22</v>
+      </c>
+      <c r="AM161">
+        <v>1.21</v>
+      </c>
+      <c r="AN161">
+        <v>1.56</v>
+      </c>
+      <c r="AO161">
+        <v>1.89</v>
+      </c>
+      <c r="AP161">
+        <v>1.7</v>
+      </c>
+      <c r="AQ161">
+        <v>1.7</v>
+      </c>
+      <c r="AR161">
+        <v>1.6</v>
+      </c>
+      <c r="AS161">
+        <v>1.32</v>
+      </c>
+      <c r="AT161">
+        <v>2.92</v>
+      </c>
+      <c r="AU161">
+        <v>5</v>
+      </c>
+      <c r="AV161">
+        <v>4</v>
+      </c>
+      <c r="AW161">
+        <v>1</v>
+      </c>
+      <c r="AX161">
+        <v>13</v>
+      </c>
+      <c r="AY161">
+        <v>6</v>
+      </c>
+      <c r="AZ161">
+        <v>17</v>
+      </c>
+      <c r="BA161">
+        <v>4</v>
+      </c>
+      <c r="BB161">
+        <v>10</v>
+      </c>
+      <c r="BC161">
+        <v>14</v>
+      </c>
+      <c r="BD161">
+        <v>2.66</v>
+      </c>
+      <c r="BE161">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="BF161">
+        <v>1.61</v>
+      </c>
+      <c r="BG161">
+        <v>1.12</v>
+      </c>
+      <c r="BH161">
+        <v>5.6</v>
+      </c>
+      <c r="BI161">
+        <v>1.24</v>
+      </c>
+      <c r="BJ161">
+        <v>3.8</v>
+      </c>
+      <c r="BK161">
+        <v>1.37</v>
+      </c>
+      <c r="BL161">
+        <v>2.66</v>
+      </c>
+      <c r="BM161">
+        <v>1.65</v>
+      </c>
+      <c r="BN161">
+        <v>2.05</v>
+      </c>
+      <c r="BO161">
+        <v>2.05</v>
+      </c>
+      <c r="BP161">
+        <v>1.7</v>
       </c>
     </row>
   </sheetData>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Czech Republic First League_20242025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Czech Republic First League_20242025.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1028" uniqueCount="270">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1034" uniqueCount="272">
   <si>
     <t>Id_Jogo</t>
   </si>
@@ -598,6 +598,9 @@
     <t>['17', '35']</t>
   </si>
   <si>
+    <t>['4', '73']</t>
+  </si>
+  <si>
     <t>['25']</t>
   </si>
   <si>
@@ -824,6 +827,9 @@
   </si>
   <si>
     <t>['4', '30']</t>
+  </si>
+  <si>
+    <t>['90+1']</t>
   </si>
 </sst>
 </file>
@@ -1185,7 +1191,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:BP161"/>
+  <dimension ref="A1:BP162"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:68">
@@ -1441,7 +1447,7 @@
         <v>86</v>
       </c>
       <c r="P2" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="Q2">
         <v>1.53</v>
@@ -1853,7 +1859,7 @@
         <v>88</v>
       </c>
       <c r="P4" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="Q4">
         <v>2.88</v>
@@ -2265,7 +2271,7 @@
         <v>90</v>
       </c>
       <c r="P6" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="Q6">
         <v>5.5</v>
@@ -2471,7 +2477,7 @@
         <v>91</v>
       </c>
       <c r="P7" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="Q7">
         <v>3.2</v>
@@ -2964,7 +2970,7 @@
         <v>1.7</v>
       </c>
       <c r="AQ9">
-        <v>0.9</v>
+        <v>0.82</v>
       </c>
       <c r="AR9">
         <v>0</v>
@@ -3295,7 +3301,7 @@
         <v>94</v>
       </c>
       <c r="P11" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="Q11">
         <v>6.5</v>
@@ -3501,7 +3507,7 @@
         <v>88</v>
       </c>
       <c r="P12" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="Q12">
         <v>2.85</v>
@@ -3913,7 +3919,7 @@
         <v>96</v>
       </c>
       <c r="P14" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="Q14">
         <v>2.45</v>
@@ -4197,7 +4203,7 @@
         <v>0</v>
       </c>
       <c r="AP15">
-        <v>1.6</v>
+        <v>1.73</v>
       </c>
       <c r="AQ15">
         <v>1.1</v>
@@ -4737,7 +4743,7 @@
         <v>88</v>
       </c>
       <c r="P18" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="Q18">
         <v>5.4</v>
@@ -5642,7 +5648,7 @@
         <v>1.7</v>
       </c>
       <c r="AQ22">
-        <v>0.9</v>
+        <v>0.82</v>
       </c>
       <c r="AR22">
         <v>0</v>
@@ -5767,7 +5773,7 @@
         <v>102</v>
       </c>
       <c r="P23" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="Q23">
         <v>2.6</v>
@@ -5973,7 +5979,7 @@
         <v>103</v>
       </c>
       <c r="P24" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="Q24">
         <v>2.75</v>
@@ -6179,7 +6185,7 @@
         <v>88</v>
       </c>
       <c r="P25" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="Q25">
         <v>1.06</v>
@@ -6385,7 +6391,7 @@
         <v>104</v>
       </c>
       <c r="P26" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="Q26">
         <v>6.23</v>
@@ -7493,7 +7499,7 @@
         <v>0</v>
       </c>
       <c r="AP31">
-        <v>1.6</v>
+        <v>1.73</v>
       </c>
       <c r="AQ31">
         <v>0.11</v>
@@ -8033,7 +8039,7 @@
         <v>111</v>
       </c>
       <c r="P34" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="Q34">
         <v>1.45</v>
@@ -8114,7 +8120,7 @@
         <v>3</v>
       </c>
       <c r="AQ34">
-        <v>0.9</v>
+        <v>0.82</v>
       </c>
       <c r="AR34">
         <v>2.27</v>
@@ -8239,7 +8245,7 @@
         <v>112</v>
       </c>
       <c r="P35" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="Q35">
         <v>2.84</v>
@@ -8445,7 +8451,7 @@
         <v>113</v>
       </c>
       <c r="P36" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="Q36">
         <v>5.63</v>
@@ -8651,7 +8657,7 @@
         <v>114</v>
       </c>
       <c r="P37" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="Q37">
         <v>2.58</v>
@@ -9063,7 +9069,7 @@
         <v>88</v>
       </c>
       <c r="P39" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="Q39">
         <v>4.75</v>
@@ -9475,7 +9481,7 @@
         <v>117</v>
       </c>
       <c r="P41" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="Q41">
         <v>2.4</v>
@@ -9681,7 +9687,7 @@
         <v>107</v>
       </c>
       <c r="P42" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="Q42">
         <v>2.61</v>
@@ -9887,7 +9893,7 @@
         <v>118</v>
       </c>
       <c r="P43" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="Q43">
         <v>1.69</v>
@@ -11329,7 +11335,7 @@
         <v>88</v>
       </c>
       <c r="P50" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="Q50">
         <v>5.1</v>
@@ -11741,7 +11747,7 @@
         <v>122</v>
       </c>
       <c r="P52" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="Q52">
         <v>3</v>
@@ -12153,7 +12159,7 @@
         <v>124</v>
       </c>
       <c r="P54" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="Q54">
         <v>3</v>
@@ -12565,7 +12571,7 @@
         <v>125</v>
       </c>
       <c r="P56" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="Q56">
         <v>1.85</v>
@@ -12771,7 +12777,7 @@
         <v>88</v>
       </c>
       <c r="P57" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="Q57">
         <v>5.88</v>
@@ -12849,7 +12855,7 @@
         <v>2</v>
       </c>
       <c r="AP57">
-        <v>1.6</v>
+        <v>1.73</v>
       </c>
       <c r="AQ57">
         <v>2.3</v>
@@ -13183,7 +13189,7 @@
         <v>127</v>
       </c>
       <c r="P59" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="Q59">
         <v>3.86</v>
@@ -13801,7 +13807,7 @@
         <v>130</v>
       </c>
       <c r="P62" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="Q62">
         <v>1.83</v>
@@ -13879,7 +13885,7 @@
         <v>0.75</v>
       </c>
       <c r="AP62">
-        <v>1.6</v>
+        <v>1.73</v>
       </c>
       <c r="AQ62">
         <v>0.55</v>
@@ -14007,7 +14013,7 @@
         <v>88</v>
       </c>
       <c r="P63" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="Q63">
         <v>8.77</v>
@@ -14419,7 +14425,7 @@
         <v>132</v>
       </c>
       <c r="P65" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="Q65">
         <v>2.4</v>
@@ -14625,7 +14631,7 @@
         <v>133</v>
       </c>
       <c r="P66" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="Q66">
         <v>1.55</v>
@@ -14831,7 +14837,7 @@
         <v>134</v>
       </c>
       <c r="P67" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="Q67">
         <v>4</v>
@@ -15037,7 +15043,7 @@
         <v>88</v>
       </c>
       <c r="P68" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="Q68">
         <v>3.1</v>
@@ -15118,7 +15124,7 @@
         <v>1</v>
       </c>
       <c r="AQ68">
-        <v>0.9</v>
+        <v>0.82</v>
       </c>
       <c r="AR68">
         <v>1.23</v>
@@ -15861,7 +15867,7 @@
         <v>124</v>
       </c>
       <c r="P72" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="Q72">
         <v>1.88</v>
@@ -16067,7 +16073,7 @@
         <v>88</v>
       </c>
       <c r="P73" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="Q73">
         <v>7</v>
@@ -16479,7 +16485,7 @@
         <v>138</v>
       </c>
       <c r="P75" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="Q75">
         <v>2.3</v>
@@ -16685,7 +16691,7 @@
         <v>88</v>
       </c>
       <c r="P76" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="Q76">
         <v>3.7</v>
@@ -16891,7 +16897,7 @@
         <v>88</v>
       </c>
       <c r="P77" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="Q77">
         <v>2.47</v>
@@ -17381,7 +17387,7 @@
         <v>1</v>
       </c>
       <c r="AP79">
-        <v>1.6</v>
+        <v>1.73</v>
       </c>
       <c r="AQ79">
         <v>1.64</v>
@@ -17509,7 +17515,7 @@
         <v>140</v>
       </c>
       <c r="P80" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="Q80">
         <v>2.5</v>
@@ -17715,7 +17721,7 @@
         <v>141</v>
       </c>
       <c r="P81" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="Q81">
         <v>2.38</v>
@@ -17921,7 +17927,7 @@
         <v>142</v>
       </c>
       <c r="P82" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="Q82">
         <v>2.8</v>
@@ -18127,7 +18133,7 @@
         <v>143</v>
       </c>
       <c r="P83" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="Q83">
         <v>2.6</v>
@@ -18333,7 +18339,7 @@
         <v>144</v>
       </c>
       <c r="P84" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="Q84">
         <v>3.4</v>
@@ -18745,7 +18751,7 @@
         <v>146</v>
       </c>
       <c r="P86" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="Q86">
         <v>2.88</v>
@@ -19157,7 +19163,7 @@
         <v>88</v>
       </c>
       <c r="P88" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="Q88">
         <v>2.6</v>
@@ -19238,7 +19244,7 @@
         <v>1.4</v>
       </c>
       <c r="AQ88">
-        <v>0.9</v>
+        <v>0.82</v>
       </c>
       <c r="AR88">
         <v>1.12</v>
@@ -19363,7 +19369,7 @@
         <v>93</v>
       </c>
       <c r="P89" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="Q89">
         <v>6.5</v>
@@ -19775,7 +19781,7 @@
         <v>149</v>
       </c>
       <c r="P91" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="Q91">
         <v>4.7</v>
@@ -19981,7 +19987,7 @@
         <v>88</v>
       </c>
       <c r="P92" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="Q92">
         <v>3.8</v>
@@ -20393,7 +20399,7 @@
         <v>150</v>
       </c>
       <c r="P94" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="Q94">
         <v>3</v>
@@ -20677,7 +20683,7 @@
         <v>1.5</v>
       </c>
       <c r="AP95">
-        <v>1.6</v>
+        <v>1.73</v>
       </c>
       <c r="AQ95">
         <v>0.89</v>
@@ -21504,7 +21510,7 @@
         <v>1.9</v>
       </c>
       <c r="AQ99">
-        <v>0.9</v>
+        <v>0.82</v>
       </c>
       <c r="AR99">
         <v>1.65</v>
@@ -21835,7 +21841,7 @@
         <v>156</v>
       </c>
       <c r="P101" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="Q101">
         <v>1.83</v>
@@ -23483,7 +23489,7 @@
         <v>161</v>
       </c>
       <c r="P109" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="Q109">
         <v>2.24</v>
@@ -23689,7 +23695,7 @@
         <v>162</v>
       </c>
       <c r="P110" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="Q110">
         <v>4.6</v>
@@ -23767,7 +23773,7 @@
         <v>2.14</v>
       </c>
       <c r="AP110">
-        <v>1.6</v>
+        <v>1.73</v>
       </c>
       <c r="AQ110">
         <v>2</v>
@@ -24101,7 +24107,7 @@
         <v>164</v>
       </c>
       <c r="P112" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="Q112">
         <v>1.44</v>
@@ -24307,7 +24313,7 @@
         <v>165</v>
       </c>
       <c r="P113" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="Q113">
         <v>3.25</v>
@@ -24513,7 +24519,7 @@
         <v>99</v>
       </c>
       <c r="P114" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="Q114">
         <v>1.73</v>
@@ -24594,7 +24600,7 @@
         <v>2</v>
       </c>
       <c r="AQ114">
-        <v>0.9</v>
+        <v>0.82</v>
       </c>
       <c r="AR114">
         <v>1.87</v>
@@ -24719,7 +24725,7 @@
         <v>151</v>
       </c>
       <c r="P115" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="Q115">
         <v>2.88</v>
@@ -24925,7 +24931,7 @@
         <v>88</v>
       </c>
       <c r="P116" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="Q116">
         <v>4.33</v>
@@ -25337,7 +25343,7 @@
         <v>88</v>
       </c>
       <c r="P118" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="Q118">
         <v>15</v>
@@ -25749,7 +25755,7 @@
         <v>168</v>
       </c>
       <c r="P120" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="Q120">
         <v>3</v>
@@ -26161,7 +26167,7 @@
         <v>170</v>
       </c>
       <c r="P122" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="Q122">
         <v>3.25</v>
@@ -26367,7 +26373,7 @@
         <v>171</v>
       </c>
       <c r="P123" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="Q123">
         <v>1.83</v>
@@ -26779,7 +26785,7 @@
         <v>172</v>
       </c>
       <c r="P125" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="Q125">
         <v>6.3</v>
@@ -27269,7 +27275,7 @@
         <v>0.71</v>
       </c>
       <c r="AP127">
-        <v>1.6</v>
+        <v>1.73</v>
       </c>
       <c r="AQ127">
         <v>1.1</v>
@@ -27603,7 +27609,7 @@
         <v>174</v>
       </c>
       <c r="P129" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="Q129">
         <v>2.1</v>
@@ -27809,7 +27815,7 @@
         <v>175</v>
       </c>
       <c r="P130" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="Q130">
         <v>1.5</v>
@@ -28221,7 +28227,7 @@
         <v>177</v>
       </c>
       <c r="P132" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="Q132">
         <v>4.04</v>
@@ -28427,7 +28433,7 @@
         <v>178</v>
       </c>
       <c r="P133" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="Q133">
         <v>3.5</v>
@@ -28633,7 +28639,7 @@
         <v>88</v>
       </c>
       <c r="P134" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="Q134">
         <v>2.75</v>
@@ -28917,7 +28923,7 @@
         <v>1.25</v>
       </c>
       <c r="AP135">
-        <v>1.6</v>
+        <v>1.73</v>
       </c>
       <c r="AQ135">
         <v>1.1</v>
@@ -29045,7 +29051,7 @@
         <v>88</v>
       </c>
       <c r="P136" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="Q136">
         <v>4.5</v>
@@ -29332,7 +29338,7 @@
         <v>2.6</v>
       </c>
       <c r="AQ137">
-        <v>0.9</v>
+        <v>0.82</v>
       </c>
       <c r="AR137">
         <v>1.7</v>
@@ -29457,7 +29463,7 @@
         <v>91</v>
       </c>
       <c r="P138" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="Q138">
         <v>2.25</v>
@@ -29663,7 +29669,7 @@
         <v>179</v>
       </c>
       <c r="P139" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="Q139">
         <v>1.9</v>
@@ -30075,7 +30081,7 @@
         <v>117</v>
       </c>
       <c r="P141" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="Q141">
         <v>4</v>
@@ -30281,7 +30287,7 @@
         <v>88</v>
       </c>
       <c r="P142" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="Q142">
         <v>4</v>
@@ -30568,7 +30574,7 @@
         <v>1.3</v>
       </c>
       <c r="AQ143">
-        <v>0.9</v>
+        <v>0.82</v>
       </c>
       <c r="AR143">
         <v>1.52</v>
@@ -30693,7 +30699,7 @@
         <v>182</v>
       </c>
       <c r="P144" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="Q144">
         <v>6</v>
@@ -30899,7 +30905,7 @@
         <v>88</v>
       </c>
       <c r="P145" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="Q145">
         <v>3.5</v>
@@ -31105,7 +31111,7 @@
         <v>183</v>
       </c>
       <c r="P146" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="Q146">
         <v>4.33</v>
@@ -31311,7 +31317,7 @@
         <v>184</v>
       </c>
       <c r="P147" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="Q147">
         <v>3.8</v>
@@ -31517,7 +31523,7 @@
         <v>185</v>
       </c>
       <c r="P148" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="Q148">
         <v>2.5</v>
@@ -31723,7 +31729,7 @@
         <v>186</v>
       </c>
       <c r="P149" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="Q149">
         <v>2.05</v>
@@ -31929,7 +31935,7 @@
         <v>187</v>
       </c>
       <c r="P150" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="Q150">
         <v>1.95</v>
@@ -32135,7 +32141,7 @@
         <v>188</v>
       </c>
       <c r="P151" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="Q151">
         <v>2.48</v>
@@ -32213,7 +32219,7 @@
         <v>1</v>
       </c>
       <c r="AP151">
-        <v>1.6</v>
+        <v>1.73</v>
       </c>
       <c r="AQ151">
         <v>1.2</v>
@@ -32547,7 +32553,7 @@
         <v>190</v>
       </c>
       <c r="P153" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="Q153">
         <v>1.4</v>
@@ -32834,7 +32840,7 @@
         <v>1.45</v>
       </c>
       <c r="AQ154">
-        <v>0.9</v>
+        <v>0.82</v>
       </c>
       <c r="AR154">
         <v>1.58</v>
@@ -33165,7 +33171,7 @@
         <v>88</v>
       </c>
       <c r="P156" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="Q156">
         <v>3.2</v>
@@ -33577,7 +33583,7 @@
         <v>88</v>
       </c>
       <c r="P158" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="Q158">
         <v>5</v>
@@ -33783,7 +33789,7 @@
         <v>88</v>
       </c>
       <c r="P159" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="Q159">
         <v>2.38</v>
@@ -34195,7 +34201,7 @@
         <v>193</v>
       </c>
       <c r="P161" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="Q161">
         <v>4.75</v>
@@ -34352,6 +34358,212 @@
       </c>
       <c r="BP161">
         <v>1.7</v>
+      </c>
+    </row>
+    <row r="162" spans="1:68">
+      <c r="A162" s="1">
+        <v>161</v>
+      </c>
+      <c r="B162">
+        <v>7468243</v>
+      </c>
+      <c r="C162" t="s">
+        <v>68</v>
+      </c>
+      <c r="D162" t="s">
+        <v>69</v>
+      </c>
+      <c r="E162" s="2">
+        <v>45696.39583333334</v>
+      </c>
+      <c r="F162">
+        <v>21</v>
+      </c>
+      <c r="G162" t="s">
+        <v>82</v>
+      </c>
+      <c r="H162" t="s">
+        <v>78</v>
+      </c>
+      <c r="I162">
+        <v>1</v>
+      </c>
+      <c r="J162">
+        <v>0</v>
+      </c>
+      <c r="K162">
+        <v>1</v>
+      </c>
+      <c r="L162">
+        <v>2</v>
+      </c>
+      <c r="M162">
+        <v>1</v>
+      </c>
+      <c r="N162">
+        <v>3</v>
+      </c>
+      <c r="O162" t="s">
+        <v>194</v>
+      </c>
+      <c r="P162" t="s">
+        <v>271</v>
+      </c>
+      <c r="Q162">
+        <v>2.63</v>
+      </c>
+      <c r="R162">
+        <v>2.2</v>
+      </c>
+      <c r="S162">
+        <v>4.33</v>
+      </c>
+      <c r="T162">
+        <v>1.4</v>
+      </c>
+      <c r="U162">
+        <v>2.75</v>
+      </c>
+      <c r="V162">
+        <v>2.75</v>
+      </c>
+      <c r="W162">
+        <v>1.4</v>
+      </c>
+      <c r="X162">
+        <v>8</v>
+      </c>
+      <c r="Y162">
+        <v>1.08</v>
+      </c>
+      <c r="Z162">
+        <v>1.71</v>
+      </c>
+      <c r="AA162">
+        <v>3.12</v>
+      </c>
+      <c r="AB162">
+        <v>3.94</v>
+      </c>
+      <c r="AC162">
+        <v>1.05</v>
+      </c>
+      <c r="AD162">
+        <v>8.5</v>
+      </c>
+      <c r="AE162">
+        <v>1.27</v>
+      </c>
+      <c r="AF162">
+        <v>3.4</v>
+      </c>
+      <c r="AG162">
+        <v>1.85</v>
+      </c>
+      <c r="AH162">
+        <v>1.85</v>
+      </c>
+      <c r="AI162">
+        <v>1.75</v>
+      </c>
+      <c r="AJ162">
+        <v>2</v>
+      </c>
+      <c r="AK162">
+        <v>1.29</v>
+      </c>
+      <c r="AL162">
+        <v>1.29</v>
+      </c>
+      <c r="AM162">
+        <v>1.75</v>
+      </c>
+      <c r="AN162">
+        <v>1.6</v>
+      </c>
+      <c r="AO162">
+        <v>0.9</v>
+      </c>
+      <c r="AP162">
+        <v>1.73</v>
+      </c>
+      <c r="AQ162">
+        <v>0.82</v>
+      </c>
+      <c r="AR162">
+        <v>1.6</v>
+      </c>
+      <c r="AS162">
+        <v>1.33</v>
+      </c>
+      <c r="AT162">
+        <v>2.93</v>
+      </c>
+      <c r="AU162">
+        <v>6</v>
+      </c>
+      <c r="AV162">
+        <v>7</v>
+      </c>
+      <c r="AW162">
+        <v>2</v>
+      </c>
+      <c r="AX162">
+        <v>8</v>
+      </c>
+      <c r="AY162">
+        <v>8</v>
+      </c>
+      <c r="AZ162">
+        <v>15</v>
+      </c>
+      <c r="BA162">
+        <v>2</v>
+      </c>
+      <c r="BB162">
+        <v>11</v>
+      </c>
+      <c r="BC162">
+        <v>13</v>
+      </c>
+      <c r="BD162">
+        <v>1.58</v>
+      </c>
+      <c r="BE162">
+        <v>7</v>
+      </c>
+      <c r="BF162">
+        <v>2.55</v>
+      </c>
+      <c r="BG162">
+        <v>1.2</v>
+      </c>
+      <c r="BH162">
+        <v>3.95</v>
+      </c>
+      <c r="BI162">
+        <v>1.34</v>
+      </c>
+      <c r="BJ162">
+        <v>2.9</v>
+      </c>
+      <c r="BK162">
+        <v>1.56</v>
+      </c>
+      <c r="BL162">
+        <v>2.23</v>
+      </c>
+      <c r="BM162">
+        <v>1.95</v>
+      </c>
+      <c r="BN162">
+        <v>1.77</v>
+      </c>
+      <c r="BO162">
+        <v>2.33</v>
+      </c>
+      <c r="BP162">
+        <v>1.52</v>
       </c>
     </row>
   </sheetData>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Czech Republic First League_20242025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Czech Republic First League_20242025.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1046" uniqueCount="275">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1070" uniqueCount="280">
   <si>
     <t>Id_Jogo</t>
   </si>
@@ -604,6 +604,18 @@
     <t>['8', '11', '85']</t>
   </si>
   <si>
+    <t>['11', '52', '66', '73']</t>
+  </si>
+  <si>
+    <t>['31']</t>
+  </si>
+  <si>
+    <t>['6']</t>
+  </si>
+  <si>
+    <t>['36', '64', '69']</t>
+  </si>
+  <si>
     <t>['25']</t>
   </si>
   <si>
@@ -839,6 +851,9 @@
   </si>
   <si>
     <t>['13', '67']</t>
+  </si>
+  <si>
+    <t>['57', '90+5']</t>
   </si>
 </sst>
 </file>
@@ -1200,7 +1215,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:BP164"/>
+  <dimension ref="A1:BP168"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:68">
@@ -1456,7 +1471,7 @@
         <v>86</v>
       </c>
       <c r="P2" t="s">
-        <v>196</v>
+        <v>200</v>
       </c>
       <c r="Q2">
         <v>1.53</v>
@@ -1534,7 +1549,7 @@
         <v>0</v>
       </c>
       <c r="AP2">
-        <v>2</v>
+        <v>2.05</v>
       </c>
       <c r="AQ2">
         <v>0.71</v>
@@ -1740,7 +1755,7 @@
         <v>0</v>
       </c>
       <c r="AP3">
-        <v>1.5</v>
+        <v>1.57</v>
       </c>
       <c r="AQ3">
         <v>1.48</v>
@@ -1868,7 +1883,7 @@
         <v>88</v>
       </c>
       <c r="P4" t="s">
-        <v>197</v>
+        <v>201</v>
       </c>
       <c r="Q4">
         <v>2.88</v>
@@ -1946,10 +1961,10 @@
         <v>0</v>
       </c>
       <c r="AP4">
-        <v>0.2</v>
+        <v>0.19</v>
       </c>
       <c r="AQ4">
-        <v>1.45</v>
+        <v>1.38</v>
       </c>
       <c r="AR4">
         <v>0</v>
@@ -2152,10 +2167,10 @@
         <v>0</v>
       </c>
       <c r="AP5">
-        <v>1.25</v>
+        <v>1.33</v>
       </c>
       <c r="AQ5">
-        <v>1.95</v>
+        <v>2</v>
       </c>
       <c r="AR5">
         <v>0</v>
@@ -2280,7 +2295,7 @@
         <v>90</v>
       </c>
       <c r="P6" t="s">
-        <v>198</v>
+        <v>202</v>
       </c>
       <c r="Q6">
         <v>5.5</v>
@@ -2486,7 +2501,7 @@
         <v>91</v>
       </c>
       <c r="P7" t="s">
-        <v>199</v>
+        <v>203</v>
       </c>
       <c r="Q7">
         <v>3.2</v>
@@ -2770,7 +2785,7 @@
         <v>0</v>
       </c>
       <c r="AP8">
-        <v>1.25</v>
+        <v>1.19</v>
       </c>
       <c r="AQ8">
         <v>2.67</v>
@@ -2976,7 +2991,7 @@
         <v>0</v>
       </c>
       <c r="AP9">
-        <v>1.4</v>
+        <v>1.33</v>
       </c>
       <c r="AQ9">
         <v>1.05</v>
@@ -3185,7 +3200,7 @@
         <v>0.65</v>
       </c>
       <c r="AQ10">
-        <v>1.25</v>
+        <v>1.33</v>
       </c>
       <c r="AR10">
         <v>0.98</v>
@@ -3310,7 +3325,7 @@
         <v>94</v>
       </c>
       <c r="P11" t="s">
-        <v>200</v>
+        <v>204</v>
       </c>
       <c r="Q11">
         <v>6.5</v>
@@ -3391,7 +3406,7 @@
         <v>1.05</v>
       </c>
       <c r="AQ11">
-        <v>2</v>
+        <v>2.05</v>
       </c>
       <c r="AR11">
         <v>1.21</v>
@@ -3516,7 +3531,7 @@
         <v>88</v>
       </c>
       <c r="P12" t="s">
-        <v>201</v>
+        <v>205</v>
       </c>
       <c r="Q12">
         <v>2.85</v>
@@ -3803,7 +3818,7 @@
         <v>2.67</v>
       </c>
       <c r="AQ13">
-        <v>0.2</v>
+        <v>0.19</v>
       </c>
       <c r="AR13">
         <v>1.65</v>
@@ -3928,7 +3943,7 @@
         <v>96</v>
       </c>
       <c r="P14" t="s">
-        <v>202</v>
+        <v>206</v>
       </c>
       <c r="Q14">
         <v>2.45</v>
@@ -4009,7 +4024,7 @@
         <v>1.14</v>
       </c>
       <c r="AQ14">
-        <v>1.45</v>
+        <v>1.38</v>
       </c>
       <c r="AR14">
         <v>1.97</v>
@@ -4215,7 +4230,7 @@
         <v>1.48</v>
       </c>
       <c r="AQ15">
-        <v>1.25</v>
+        <v>1.19</v>
       </c>
       <c r="AR15">
         <v>0.9399999999999999</v>
@@ -4418,10 +4433,10 @@
         <v>3</v>
       </c>
       <c r="AP16">
-        <v>1.95</v>
+        <v>2</v>
       </c>
       <c r="AQ16">
-        <v>1.5</v>
+        <v>1.57</v>
       </c>
       <c r="AR16">
         <v>1.71</v>
@@ -4627,7 +4642,7 @@
         <v>2.19</v>
       </c>
       <c r="AQ17">
-        <v>1.4</v>
+        <v>1.33</v>
       </c>
       <c r="AR17">
         <v>1.43</v>
@@ -4752,7 +4767,7 @@
         <v>88</v>
       </c>
       <c r="P18" t="s">
-        <v>203</v>
+        <v>207</v>
       </c>
       <c r="Q18">
         <v>5.4</v>
@@ -5036,7 +5051,7 @@
         <v>1.5</v>
       </c>
       <c r="AP19">
-        <v>2</v>
+        <v>2.05</v>
       </c>
       <c r="AQ19">
         <v>0.65</v>
@@ -5242,10 +5257,10 @@
         <v>1.5</v>
       </c>
       <c r="AP20">
-        <v>1.25</v>
+        <v>1.19</v>
       </c>
       <c r="AQ20">
-        <v>1.25</v>
+        <v>1.33</v>
       </c>
       <c r="AR20">
         <v>1.25</v>
@@ -5448,7 +5463,7 @@
         <v>3</v>
       </c>
       <c r="AP21">
-        <v>1.5</v>
+        <v>1.57</v>
       </c>
       <c r="AQ21">
         <v>2.19</v>
@@ -5654,7 +5669,7 @@
         <v>0</v>
       </c>
       <c r="AP22">
-        <v>1.45</v>
+        <v>1.38</v>
       </c>
       <c r="AQ22">
         <v>1.05</v>
@@ -5782,7 +5797,7 @@
         <v>102</v>
       </c>
       <c r="P23" t="s">
-        <v>204</v>
+        <v>208</v>
       </c>
       <c r="Q23">
         <v>2.6</v>
@@ -5860,7 +5875,7 @@
         <v>0</v>
       </c>
       <c r="AP23">
-        <v>0.2</v>
+        <v>0.19</v>
       </c>
       <c r="AQ23">
         <v>0.71</v>
@@ -5988,7 +6003,7 @@
         <v>103</v>
       </c>
       <c r="P24" t="s">
-        <v>205</v>
+        <v>209</v>
       </c>
       <c r="Q24">
         <v>2.75</v>
@@ -6066,7 +6081,7 @@
         <v>1.5</v>
       </c>
       <c r="AP24">
-        <v>1.4</v>
+        <v>1.33</v>
       </c>
       <c r="AQ24">
         <v>1.48</v>
@@ -6194,7 +6209,7 @@
         <v>88</v>
       </c>
       <c r="P25" t="s">
-        <v>206</v>
+        <v>210</v>
       </c>
       <c r="Q25">
         <v>1.06</v>
@@ -6275,7 +6290,7 @@
         <v>0.65</v>
       </c>
       <c r="AQ25">
-        <v>1.5</v>
+        <v>1.57</v>
       </c>
       <c r="AR25">
         <v>0.82</v>
@@ -6400,7 +6415,7 @@
         <v>104</v>
       </c>
       <c r="P26" t="s">
-        <v>207</v>
+        <v>211</v>
       </c>
       <c r="Q26">
         <v>6.23</v>
@@ -6478,10 +6493,10 @@
         <v>3</v>
       </c>
       <c r="AP26">
-        <v>1.25</v>
+        <v>1.33</v>
       </c>
       <c r="AQ26">
-        <v>2</v>
+        <v>2.05</v>
       </c>
       <c r="AR26">
         <v>1.45</v>
@@ -6893,7 +6908,7 @@
         <v>2.67</v>
       </c>
       <c r="AQ28">
-        <v>1.45</v>
+        <v>1.38</v>
       </c>
       <c r="AR28">
         <v>1.7</v>
@@ -7099,7 +7114,7 @@
         <v>0.71</v>
       </c>
       <c r="AQ29">
-        <v>1.25</v>
+        <v>1.19</v>
       </c>
       <c r="AR29">
         <v>1.07</v>
@@ -7302,10 +7317,10 @@
         <v>2</v>
       </c>
       <c r="AP30">
-        <v>1.95</v>
+        <v>2</v>
       </c>
       <c r="AQ30">
-        <v>1.4</v>
+        <v>1.33</v>
       </c>
       <c r="AR30">
         <v>1.47</v>
@@ -7511,7 +7526,7 @@
         <v>1.48</v>
       </c>
       <c r="AQ31">
-        <v>0.2</v>
+        <v>0.19</v>
       </c>
       <c r="AR31">
         <v>1.63</v>
@@ -7920,7 +7935,7 @@
         <v>0.75</v>
       </c>
       <c r="AP33">
-        <v>1.4</v>
+        <v>1.33</v>
       </c>
       <c r="AQ33">
         <v>0.65</v>
@@ -8048,7 +8063,7 @@
         <v>111</v>
       </c>
       <c r="P34" t="s">
-        <v>208</v>
+        <v>212</v>
       </c>
       <c r="Q34">
         <v>1.45</v>
@@ -8254,7 +8269,7 @@
         <v>112</v>
       </c>
       <c r="P35" t="s">
-        <v>209</v>
+        <v>213</v>
       </c>
       <c r="Q35">
         <v>2.84</v>
@@ -8335,7 +8350,7 @@
         <v>1.2</v>
       </c>
       <c r="AQ35">
-        <v>1.25</v>
+        <v>1.33</v>
       </c>
       <c r="AR35">
         <v>1.78</v>
@@ -8460,7 +8475,7 @@
         <v>113</v>
       </c>
       <c r="P36" t="s">
-        <v>210</v>
+        <v>214</v>
       </c>
       <c r="Q36">
         <v>5.63</v>
@@ -8538,10 +8553,10 @@
         <v>3</v>
       </c>
       <c r="AP36">
-        <v>1.5</v>
+        <v>1.57</v>
       </c>
       <c r="AQ36">
-        <v>2</v>
+        <v>2.05</v>
       </c>
       <c r="AR36">
         <v>1.38</v>
@@ -8666,7 +8681,7 @@
         <v>114</v>
       </c>
       <c r="P37" t="s">
-        <v>211</v>
+        <v>215</v>
       </c>
       <c r="Q37">
         <v>2.58</v>
@@ -8744,7 +8759,7 @@
         <v>1.5</v>
       </c>
       <c r="AP37">
-        <v>1.45</v>
+        <v>1.38</v>
       </c>
       <c r="AQ37">
         <v>1.48</v>
@@ -9078,7 +9093,7 @@
         <v>88</v>
       </c>
       <c r="P39" t="s">
-        <v>212</v>
+        <v>216</v>
       </c>
       <c r="Q39">
         <v>4.75</v>
@@ -9156,7 +9171,7 @@
         <v>2.5</v>
       </c>
       <c r="AP39">
-        <v>0.2</v>
+        <v>0.19</v>
       </c>
       <c r="AQ39">
         <v>2.19</v>
@@ -9362,10 +9377,10 @@
         <v>2</v>
       </c>
       <c r="AP40">
-        <v>1.25</v>
+        <v>1.19</v>
       </c>
       <c r="AQ40">
-        <v>1.95</v>
+        <v>2</v>
       </c>
       <c r="AR40">
         <v>1.19</v>
@@ -9490,7 +9505,7 @@
         <v>117</v>
       </c>
       <c r="P41" t="s">
-        <v>213</v>
+        <v>217</v>
       </c>
       <c r="Q41">
         <v>2.4</v>
@@ -9568,10 +9583,10 @@
         <v>1.4</v>
       </c>
       <c r="AP41">
-        <v>1.25</v>
+        <v>1.33</v>
       </c>
       <c r="AQ41">
-        <v>1.5</v>
+        <v>1.57</v>
       </c>
       <c r="AR41">
         <v>1.45</v>
@@ -9696,7 +9711,7 @@
         <v>107</v>
       </c>
       <c r="P42" t="s">
-        <v>214</v>
+        <v>218</v>
       </c>
       <c r="Q42">
         <v>2.61</v>
@@ -9902,7 +9917,7 @@
         <v>118</v>
       </c>
       <c r="P43" t="s">
-        <v>215</v>
+        <v>219</v>
       </c>
       <c r="Q43">
         <v>1.69</v>
@@ -9980,10 +9995,10 @@
         <v>1.6</v>
       </c>
       <c r="AP43">
-        <v>2</v>
+        <v>2.05</v>
       </c>
       <c r="AQ43">
-        <v>1.25</v>
+        <v>1.19</v>
       </c>
       <c r="AR43">
         <v>2.07</v>
@@ -10189,7 +10204,7 @@
         <v>0.71</v>
       </c>
       <c r="AQ44">
-        <v>1.4</v>
+        <v>1.33</v>
       </c>
       <c r="AR44">
         <v>1.04</v>
@@ -10392,7 +10407,7 @@
         <v>1.4</v>
       </c>
       <c r="AP45">
-        <v>1.95</v>
+        <v>2</v>
       </c>
       <c r="AQ45">
         <v>1.14</v>
@@ -10601,7 +10616,7 @@
         <v>0.65</v>
       </c>
       <c r="AQ46">
-        <v>0.2</v>
+        <v>0.19</v>
       </c>
       <c r="AR46">
         <v>0.97</v>
@@ -10807,7 +10822,7 @@
         <v>1.2</v>
       </c>
       <c r="AQ47">
-        <v>1.95</v>
+        <v>2</v>
       </c>
       <c r="AR47">
         <v>1.67</v>
@@ -11010,10 +11025,10 @@
         <v>1.17</v>
       </c>
       <c r="AP48">
-        <v>0.2</v>
+        <v>0.19</v>
       </c>
       <c r="AQ48">
-        <v>1.25</v>
+        <v>1.33</v>
       </c>
       <c r="AR48">
         <v>1.17</v>
@@ -11216,10 +11231,10 @@
         <v>1.67</v>
       </c>
       <c r="AP49">
-        <v>1.25</v>
+        <v>1.19</v>
       </c>
       <c r="AQ49">
-        <v>1.5</v>
+        <v>1.57</v>
       </c>
       <c r="AR49">
         <v>1.18</v>
@@ -11344,7 +11359,7 @@
         <v>88</v>
       </c>
       <c r="P50" t="s">
-        <v>216</v>
+        <v>220</v>
       </c>
       <c r="Q50">
         <v>5.1</v>
@@ -11422,10 +11437,10 @@
         <v>2.67</v>
       </c>
       <c r="AP50">
-        <v>1.4</v>
+        <v>1.33</v>
       </c>
       <c r="AQ50">
-        <v>2</v>
+        <v>2.05</v>
       </c>
       <c r="AR50">
         <v>1.07</v>
@@ -11756,7 +11771,7 @@
         <v>122</v>
       </c>
       <c r="P52" t="s">
-        <v>217</v>
+        <v>221</v>
       </c>
       <c r="Q52">
         <v>3</v>
@@ -11834,10 +11849,10 @@
         <v>1.67</v>
       </c>
       <c r="AP52">
-        <v>1.45</v>
+        <v>1.38</v>
       </c>
       <c r="AQ52">
-        <v>1.95</v>
+        <v>2</v>
       </c>
       <c r="AR52">
         <v>1.38</v>
@@ -12168,7 +12183,7 @@
         <v>124</v>
       </c>
       <c r="P54" t="s">
-        <v>218</v>
+        <v>222</v>
       </c>
       <c r="Q54">
         <v>3</v>
@@ -12580,7 +12595,7 @@
         <v>125</v>
       </c>
       <c r="P56" t="s">
-        <v>219</v>
+        <v>223</v>
       </c>
       <c r="Q56">
         <v>1.85</v>
@@ -12661,7 +12676,7 @@
         <v>2.19</v>
       </c>
       <c r="AQ56">
-        <v>1.45</v>
+        <v>1.38</v>
       </c>
       <c r="AR56">
         <v>1.52</v>
@@ -12786,7 +12801,7 @@
         <v>88</v>
       </c>
       <c r="P57" t="s">
-        <v>220</v>
+        <v>224</v>
       </c>
       <c r="Q57">
         <v>5.88</v>
@@ -13070,10 +13085,10 @@
         <v>1.43</v>
       </c>
       <c r="AP58">
-        <v>1.4</v>
+        <v>1.33</v>
       </c>
       <c r="AQ58">
-        <v>1.25</v>
+        <v>1.19</v>
       </c>
       <c r="AR58">
         <v>1.14</v>
@@ -13198,7 +13213,7 @@
         <v>127</v>
       </c>
       <c r="P59" t="s">
-        <v>221</v>
+        <v>225</v>
       </c>
       <c r="Q59">
         <v>3.86</v>
@@ -13279,7 +13294,7 @@
         <v>1.05</v>
       </c>
       <c r="AQ59">
-        <v>1.95</v>
+        <v>2</v>
       </c>
       <c r="AR59">
         <v>1.35</v>
@@ -13485,7 +13500,7 @@
         <v>1.2</v>
       </c>
       <c r="AQ60">
-        <v>1.5</v>
+        <v>1.57</v>
       </c>
       <c r="AR60">
         <v>1.73</v>
@@ -13816,7 +13831,7 @@
         <v>130</v>
       </c>
       <c r="P62" t="s">
-        <v>222</v>
+        <v>226</v>
       </c>
       <c r="Q62">
         <v>1.83</v>
@@ -14022,7 +14037,7 @@
         <v>88</v>
       </c>
       <c r="P63" t="s">
-        <v>223</v>
+        <v>227</v>
       </c>
       <c r="Q63">
         <v>8.77</v>
@@ -14100,10 +14115,10 @@
         <v>2.71</v>
       </c>
       <c r="AP63">
-        <v>0.2</v>
+        <v>0.19</v>
       </c>
       <c r="AQ63">
-        <v>2</v>
+        <v>2.05</v>
       </c>
       <c r="AR63">
         <v>1.21</v>
@@ -14306,7 +14321,7 @@
         <v>1</v>
       </c>
       <c r="AP64">
-        <v>1.45</v>
+        <v>1.38</v>
       </c>
       <c r="AQ64">
         <v>0.65</v>
@@ -14434,7 +14449,7 @@
         <v>132</v>
       </c>
       <c r="P65" t="s">
-        <v>224</v>
+        <v>228</v>
       </c>
       <c r="Q65">
         <v>2.4</v>
@@ -14515,7 +14530,7 @@
         <v>1.14</v>
       </c>
       <c r="AQ65">
-        <v>1.25</v>
+        <v>1.33</v>
       </c>
       <c r="AR65">
         <v>1.47</v>
@@ -14640,7 +14655,7 @@
         <v>133</v>
       </c>
       <c r="P66" t="s">
-        <v>225</v>
+        <v>229</v>
       </c>
       <c r="Q66">
         <v>1.55</v>
@@ -14718,10 +14733,10 @@
         <v>1.75</v>
       </c>
       <c r="AP66">
-        <v>2</v>
+        <v>2.05</v>
       </c>
       <c r="AQ66">
-        <v>1.45</v>
+        <v>1.38</v>
       </c>
       <c r="AR66">
         <v>2</v>
@@ -14846,7 +14861,7 @@
         <v>134</v>
       </c>
       <c r="P67" t="s">
-        <v>226</v>
+        <v>230</v>
       </c>
       <c r="Q67">
         <v>4</v>
@@ -15052,7 +15067,7 @@
         <v>88</v>
       </c>
       <c r="P68" t="s">
-        <v>227</v>
+        <v>231</v>
       </c>
       <c r="Q68">
         <v>3.1</v>
@@ -15336,7 +15351,7 @@
         <v>1.38</v>
       </c>
       <c r="AP69">
-        <v>1.25</v>
+        <v>1.19</v>
       </c>
       <c r="AQ69">
         <v>1.2</v>
@@ -15542,10 +15557,10 @@
         <v>1.5</v>
       </c>
       <c r="AP70">
-        <v>1.5</v>
+        <v>1.57</v>
       </c>
       <c r="AQ70">
-        <v>1.4</v>
+        <v>1.33</v>
       </c>
       <c r="AR70">
         <v>1.47</v>
@@ -15748,10 +15763,10 @@
         <v>0.13</v>
       </c>
       <c r="AP71">
-        <v>1.95</v>
+        <v>2</v>
       </c>
       <c r="AQ71">
-        <v>0.2</v>
+        <v>0.19</v>
       </c>
       <c r="AR71">
         <v>1.6</v>
@@ -15876,7 +15891,7 @@
         <v>124</v>
       </c>
       <c r="P72" t="s">
-        <v>228</v>
+        <v>232</v>
       </c>
       <c r="Q72">
         <v>1.88</v>
@@ -16082,7 +16097,7 @@
         <v>88</v>
       </c>
       <c r="P73" t="s">
-        <v>229</v>
+        <v>233</v>
       </c>
       <c r="Q73">
         <v>7</v>
@@ -16160,7 +16175,7 @@
         <v>2.75</v>
       </c>
       <c r="AP73">
-        <v>1.25</v>
+        <v>1.33</v>
       </c>
       <c r="AQ73">
         <v>2.67</v>
@@ -16369,7 +16384,7 @@
         <v>1.2</v>
       </c>
       <c r="AQ74">
-        <v>1.4</v>
+        <v>1.33</v>
       </c>
       <c r="AR74">
         <v>1.76</v>
@@ -16494,7 +16509,7 @@
         <v>138</v>
       </c>
       <c r="P75" t="s">
-        <v>230</v>
+        <v>234</v>
       </c>
       <c r="Q75">
         <v>2.3</v>
@@ -16700,7 +16715,7 @@
         <v>88</v>
       </c>
       <c r="P76" t="s">
-        <v>231</v>
+        <v>235</v>
       </c>
       <c r="Q76">
         <v>3.7</v>
@@ -16778,10 +16793,10 @@
         <v>1.44</v>
       </c>
       <c r="AP76">
-        <v>0.2</v>
+        <v>0.19</v>
       </c>
       <c r="AQ76">
-        <v>1.25</v>
+        <v>1.19</v>
       </c>
       <c r="AR76">
         <v>1.18</v>
@@ -16906,7 +16921,7 @@
         <v>88</v>
       </c>
       <c r="P77" t="s">
-        <v>232</v>
+        <v>236</v>
       </c>
       <c r="Q77">
         <v>2.47</v>
@@ -16987,7 +17002,7 @@
         <v>1.14</v>
       </c>
       <c r="AQ77">
-        <v>1.5</v>
+        <v>1.57</v>
       </c>
       <c r="AR77">
         <v>1.59</v>
@@ -17399,7 +17414,7 @@
         <v>1.48</v>
       </c>
       <c r="AQ79">
-        <v>1.95</v>
+        <v>2</v>
       </c>
       <c r="AR79">
         <v>1.37</v>
@@ -17524,7 +17539,7 @@
         <v>140</v>
       </c>
       <c r="P80" t="s">
-        <v>233</v>
+        <v>237</v>
       </c>
       <c r="Q80">
         <v>2.5</v>
@@ -17602,10 +17617,10 @@
         <v>1</v>
       </c>
       <c r="AP80">
-        <v>1.45</v>
+        <v>1.38</v>
       </c>
       <c r="AQ80">
-        <v>1.25</v>
+        <v>1.33</v>
       </c>
       <c r="AR80">
         <v>1.41</v>
@@ -17730,7 +17745,7 @@
         <v>141</v>
       </c>
       <c r="P81" t="s">
-        <v>234</v>
+        <v>238</v>
       </c>
       <c r="Q81">
         <v>2.38</v>
@@ -17811,7 +17826,7 @@
         <v>2.67</v>
       </c>
       <c r="AQ81">
-        <v>2</v>
+        <v>2.05</v>
       </c>
       <c r="AR81">
         <v>2.1</v>
@@ -17936,7 +17951,7 @@
         <v>142</v>
       </c>
       <c r="P82" t="s">
-        <v>235</v>
+        <v>239</v>
       </c>
       <c r="Q82">
         <v>2.8</v>
@@ -18014,10 +18029,10 @@
         <v>1.7</v>
       </c>
       <c r="AP82">
-        <v>1.4</v>
+        <v>1.33</v>
       </c>
       <c r="AQ82">
-        <v>1.45</v>
+        <v>1.38</v>
       </c>
       <c r="AR82">
         <v>1.21</v>
@@ -18142,7 +18157,7 @@
         <v>143</v>
       </c>
       <c r="P83" t="s">
-        <v>236</v>
+        <v>240</v>
       </c>
       <c r="Q83">
         <v>2.6</v>
@@ -18348,7 +18363,7 @@
         <v>144</v>
       </c>
       <c r="P84" t="s">
-        <v>237</v>
+        <v>241</v>
       </c>
       <c r="Q84">
         <v>3.4</v>
@@ -18426,7 +18441,7 @@
         <v>2.1</v>
       </c>
       <c r="AP84">
-        <v>1.95</v>
+        <v>2</v>
       </c>
       <c r="AQ84">
         <v>2.19</v>
@@ -18632,7 +18647,7 @@
         <v>1.2</v>
       </c>
       <c r="AP85">
-        <v>2</v>
+        <v>2.05</v>
       </c>
       <c r="AQ85">
         <v>1.14</v>
@@ -18760,7 +18775,7 @@
         <v>146</v>
       </c>
       <c r="P86" t="s">
-        <v>238</v>
+        <v>242</v>
       </c>
       <c r="Q86">
         <v>2.88</v>
@@ -18838,7 +18853,7 @@
         <v>1.2</v>
       </c>
       <c r="AP86">
-        <v>1.25</v>
+        <v>1.33</v>
       </c>
       <c r="AQ86">
         <v>1.48</v>
@@ -19047,7 +19062,7 @@
         <v>1.2</v>
       </c>
       <c r="AQ87">
-        <v>0.2</v>
+        <v>0.19</v>
       </c>
       <c r="AR87">
         <v>1.72</v>
@@ -19172,7 +19187,7 @@
         <v>88</v>
       </c>
       <c r="P88" t="s">
-        <v>239</v>
+        <v>243</v>
       </c>
       <c r="Q88">
         <v>2.6</v>
@@ -19250,7 +19265,7 @@
         <v>0.7</v>
       </c>
       <c r="AP88">
-        <v>1.25</v>
+        <v>1.19</v>
       </c>
       <c r="AQ88">
         <v>1.05</v>
@@ -19378,7 +19393,7 @@
         <v>93</v>
       </c>
       <c r="P89" t="s">
-        <v>240</v>
+        <v>244</v>
       </c>
       <c r="Q89">
         <v>6.5</v>
@@ -19456,7 +19471,7 @@
         <v>2.8</v>
       </c>
       <c r="AP89">
-        <v>1.5</v>
+        <v>1.57</v>
       </c>
       <c r="AQ89">
         <v>2.67</v>
@@ -19665,7 +19680,7 @@
         <v>1.14</v>
       </c>
       <c r="AQ90">
-        <v>1.25</v>
+        <v>1.19</v>
       </c>
       <c r="AR90">
         <v>1.48</v>
@@ -19790,7 +19805,7 @@
         <v>149</v>
       </c>
       <c r="P91" t="s">
-        <v>241</v>
+        <v>245</v>
       </c>
       <c r="Q91">
         <v>4.7</v>
@@ -19871,7 +19886,7 @@
         <v>0.71</v>
       </c>
       <c r="AQ91">
-        <v>1.95</v>
+        <v>2</v>
       </c>
       <c r="AR91">
         <v>1.07</v>
@@ -19996,7 +20011,7 @@
         <v>88</v>
       </c>
       <c r="P92" t="s">
-        <v>242</v>
+        <v>246</v>
       </c>
       <c r="Q92">
         <v>3.8</v>
@@ -20074,10 +20089,10 @@
         <v>1.27</v>
       </c>
       <c r="AP92">
-        <v>0.2</v>
+        <v>0.19</v>
       </c>
       <c r="AQ92">
-        <v>1.4</v>
+        <v>1.33</v>
       </c>
       <c r="AR92">
         <v>1.18</v>
@@ -20280,10 +20295,10 @@
         <v>1.55</v>
       </c>
       <c r="AP93">
-        <v>1.45</v>
+        <v>1.38</v>
       </c>
       <c r="AQ93">
-        <v>1.5</v>
+        <v>1.57</v>
       </c>
       <c r="AR93">
         <v>1.34</v>
@@ -20408,7 +20423,7 @@
         <v>150</v>
       </c>
       <c r="P94" t="s">
-        <v>243</v>
+        <v>247</v>
       </c>
       <c r="Q94">
         <v>3</v>
@@ -20489,7 +20504,7 @@
         <v>1.05</v>
       </c>
       <c r="AQ94">
-        <v>1.25</v>
+        <v>1.33</v>
       </c>
       <c r="AR94">
         <v>1.4</v>
@@ -21107,7 +21122,7 @@
         <v>2.19</v>
       </c>
       <c r="AQ97">
-        <v>2</v>
+        <v>2.05</v>
       </c>
       <c r="AR97">
         <v>1.52</v>
@@ -21516,7 +21531,7 @@
         <v>0.83</v>
       </c>
       <c r="AP99">
-        <v>1.5</v>
+        <v>1.57</v>
       </c>
       <c r="AQ99">
         <v>1.05</v>
@@ -21725,7 +21740,7 @@
         <v>1.2</v>
       </c>
       <c r="AQ100">
-        <v>1.45</v>
+        <v>1.38</v>
       </c>
       <c r="AR100">
         <v>1.72</v>
@@ -21850,7 +21865,7 @@
         <v>156</v>
       </c>
       <c r="P101" t="s">
-        <v>244</v>
+        <v>248</v>
       </c>
       <c r="Q101">
         <v>1.83</v>
@@ -21928,10 +21943,10 @@
         <v>1.75</v>
       </c>
       <c r="AP101">
-        <v>2</v>
+        <v>2.05</v>
       </c>
       <c r="AQ101">
-        <v>1.95</v>
+        <v>2</v>
       </c>
       <c r="AR101">
         <v>1.79</v>
@@ -22134,7 +22149,7 @@
         <v>1.25</v>
       </c>
       <c r="AP102">
-        <v>0.2</v>
+        <v>0.19</v>
       </c>
       <c r="AQ102">
         <v>1.14</v>
@@ -22340,7 +22355,7 @@
         <v>0.58</v>
       </c>
       <c r="AP103">
-        <v>1.25</v>
+        <v>1.33</v>
       </c>
       <c r="AQ103">
         <v>0.71</v>
@@ -22546,7 +22561,7 @@
         <v>2.25</v>
       </c>
       <c r="AP104">
-        <v>1.25</v>
+        <v>1.19</v>
       </c>
       <c r="AQ104">
         <v>2.19</v>
@@ -22752,7 +22767,7 @@
         <v>2.83</v>
       </c>
       <c r="AP105">
-        <v>1.4</v>
+        <v>1.33</v>
       </c>
       <c r="AQ105">
         <v>2.67</v>
@@ -22958,7 +22973,7 @@
         <v>0.85</v>
       </c>
       <c r="AP106">
-        <v>1.95</v>
+        <v>2</v>
       </c>
       <c r="AQ106">
         <v>0.65</v>
@@ -23167,7 +23182,7 @@
         <v>0.71</v>
       </c>
       <c r="AQ107">
-        <v>1.5</v>
+        <v>1.57</v>
       </c>
       <c r="AR107">
         <v>1.06</v>
@@ -23373,7 +23388,7 @@
         <v>1.14</v>
       </c>
       <c r="AQ108">
-        <v>1.4</v>
+        <v>1.33</v>
       </c>
       <c r="AR108">
         <v>1.51</v>
@@ -23498,7 +23513,7 @@
         <v>161</v>
       </c>
       <c r="P109" t="s">
-        <v>245</v>
+        <v>249</v>
       </c>
       <c r="Q109">
         <v>2.24</v>
@@ -23579,7 +23594,7 @@
         <v>1.05</v>
       </c>
       <c r="AQ109">
-        <v>0.2</v>
+        <v>0.19</v>
       </c>
       <c r="AR109">
         <v>1.4</v>
@@ -23704,7 +23719,7 @@
         <v>162</v>
       </c>
       <c r="P110" t="s">
-        <v>246</v>
+        <v>250</v>
       </c>
       <c r="Q110">
         <v>4.6</v>
@@ -23785,7 +23800,7 @@
         <v>1.48</v>
       </c>
       <c r="AQ110">
-        <v>2</v>
+        <v>2.05</v>
       </c>
       <c r="AR110">
         <v>1.39</v>
@@ -23991,7 +24006,7 @@
         <v>2.19</v>
       </c>
       <c r="AQ111">
-        <v>1.25</v>
+        <v>1.33</v>
       </c>
       <c r="AR111">
         <v>1.44</v>
@@ -24116,7 +24131,7 @@
         <v>164</v>
       </c>
       <c r="P112" t="s">
-        <v>202</v>
+        <v>206</v>
       </c>
       <c r="Q112">
         <v>1.44</v>
@@ -24322,7 +24337,7 @@
         <v>165</v>
       </c>
       <c r="P113" t="s">
-        <v>247</v>
+        <v>251</v>
       </c>
       <c r="Q113">
         <v>3.25</v>
@@ -24400,10 +24415,10 @@
         <v>1.93</v>
       </c>
       <c r="AP113">
-        <v>1.5</v>
+        <v>1.57</v>
       </c>
       <c r="AQ113">
-        <v>1.95</v>
+        <v>2</v>
       </c>
       <c r="AR113">
         <v>1.5</v>
@@ -24528,7 +24543,7 @@
         <v>99</v>
       </c>
       <c r="P114" t="s">
-        <v>248</v>
+        <v>252</v>
       </c>
       <c r="Q114">
         <v>1.73</v>
@@ -24606,7 +24621,7 @@
         <v>0.93</v>
       </c>
       <c r="AP114">
-        <v>2</v>
+        <v>2.05</v>
       </c>
       <c r="AQ114">
         <v>1.05</v>
@@ -24734,7 +24749,7 @@
         <v>151</v>
       </c>
       <c r="P115" t="s">
-        <v>249</v>
+        <v>253</v>
       </c>
       <c r="Q115">
         <v>2.88</v>
@@ -24812,7 +24827,7 @@
         <v>1.29</v>
       </c>
       <c r="AP115">
-        <v>1.25</v>
+        <v>1.19</v>
       </c>
       <c r="AQ115">
         <v>1.48</v>
@@ -24940,7 +24955,7 @@
         <v>88</v>
       </c>
       <c r="P116" t="s">
-        <v>250</v>
+        <v>254</v>
       </c>
       <c r="Q116">
         <v>4.33</v>
@@ -25018,7 +25033,7 @@
         <v>2.14</v>
       </c>
       <c r="AP116">
-        <v>1.4</v>
+        <v>1.33</v>
       </c>
       <c r="AQ116">
         <v>2.19</v>
@@ -25224,7 +25239,7 @@
         <v>0.79</v>
       </c>
       <c r="AP117">
-        <v>1.25</v>
+        <v>1.33</v>
       </c>
       <c r="AQ117">
         <v>0.65</v>
@@ -25352,7 +25367,7 @@
         <v>88</v>
       </c>
       <c r="P118" t="s">
-        <v>251</v>
+        <v>255</v>
       </c>
       <c r="Q118">
         <v>15</v>
@@ -25430,7 +25445,7 @@
         <v>2.71</v>
       </c>
       <c r="AP118">
-        <v>0.2</v>
+        <v>0.19</v>
       </c>
       <c r="AQ118">
         <v>2.67</v>
@@ -25764,7 +25779,7 @@
         <v>168</v>
       </c>
       <c r="P120" t="s">
-        <v>252</v>
+        <v>256</v>
       </c>
       <c r="Q120">
         <v>3</v>
@@ -25842,7 +25857,7 @@
         <v>1.21</v>
       </c>
       <c r="AP120">
-        <v>1.45</v>
+        <v>1.38</v>
       </c>
       <c r="AQ120">
         <v>1.14</v>
@@ -26048,10 +26063,10 @@
         <v>1.43</v>
       </c>
       <c r="AP121">
-        <v>1.45</v>
+        <v>1.38</v>
       </c>
       <c r="AQ121">
-        <v>1.25</v>
+        <v>1.19</v>
       </c>
       <c r="AR121">
         <v>1.39</v>
@@ -26176,7 +26191,7 @@
         <v>170</v>
       </c>
       <c r="P122" t="s">
-        <v>253</v>
+        <v>257</v>
       </c>
       <c r="Q122">
         <v>3.25</v>
@@ -26254,10 +26269,10 @@
         <v>1.33</v>
       </c>
       <c r="AP122">
-        <v>1.25</v>
+        <v>1.33</v>
       </c>
       <c r="AQ122">
-        <v>1.25</v>
+        <v>1.19</v>
       </c>
       <c r="AR122">
         <v>1.41</v>
@@ -26382,7 +26397,7 @@
         <v>171</v>
       </c>
       <c r="P123" t="s">
-        <v>201</v>
+        <v>205</v>
       </c>
       <c r="Q123">
         <v>1.83</v>
@@ -26460,7 +26475,7 @@
         <v>1.47</v>
       </c>
       <c r="AP123">
-        <v>1.95</v>
+        <v>2</v>
       </c>
       <c r="AQ123">
         <v>1.2</v>
@@ -26669,7 +26684,7 @@
         <v>1.05</v>
       </c>
       <c r="AQ124">
-        <v>1.45</v>
+        <v>1.38</v>
       </c>
       <c r="AR124">
         <v>1.41</v>
@@ -26794,7 +26809,7 @@
         <v>172</v>
       </c>
       <c r="P125" t="s">
-        <v>254</v>
+        <v>258</v>
       </c>
       <c r="Q125">
         <v>6.3</v>
@@ -26875,7 +26890,7 @@
         <v>0.65</v>
       </c>
       <c r="AQ125">
-        <v>2</v>
+        <v>2.05</v>
       </c>
       <c r="AR125">
         <v>1.02</v>
@@ -27287,7 +27302,7 @@
         <v>1.48</v>
       </c>
       <c r="AQ127">
-        <v>1.4</v>
+        <v>1.33</v>
       </c>
       <c r="AR127">
         <v>1.4</v>
@@ -27493,7 +27508,7 @@
         <v>0.71</v>
       </c>
       <c r="AQ128">
-        <v>0.2</v>
+        <v>0.19</v>
       </c>
       <c r="AR128">
         <v>1.06</v>
@@ -27618,7 +27633,7 @@
         <v>174</v>
       </c>
       <c r="P129" t="s">
-        <v>255</v>
+        <v>259</v>
       </c>
       <c r="Q129">
         <v>2.1</v>
@@ -27699,7 +27714,7 @@
         <v>2.19</v>
       </c>
       <c r="AQ129">
-        <v>1.5</v>
+        <v>1.57</v>
       </c>
       <c r="AR129">
         <v>1.44</v>
@@ -27824,7 +27839,7 @@
         <v>175</v>
       </c>
       <c r="P130" t="s">
-        <v>256</v>
+        <v>260</v>
       </c>
       <c r="Q130">
         <v>1.5</v>
@@ -27902,7 +27917,7 @@
         <v>1.38</v>
       </c>
       <c r="AP130">
-        <v>2</v>
+        <v>2.05</v>
       </c>
       <c r="AQ130">
         <v>1.2</v>
@@ -28108,10 +28123,10 @@
         <v>0.19</v>
       </c>
       <c r="AP131">
-        <v>1.5</v>
+        <v>1.57</v>
       </c>
       <c r="AQ131">
-        <v>0.2</v>
+        <v>0.19</v>
       </c>
       <c r="AR131">
         <v>1.48</v>
@@ -28236,7 +28251,7 @@
         <v>177</v>
       </c>
       <c r="P132" t="s">
-        <v>257</v>
+        <v>261</v>
       </c>
       <c r="Q132">
         <v>4.04</v>
@@ -28317,7 +28332,7 @@
         <v>0.65</v>
       </c>
       <c r="AQ132">
-        <v>1.25</v>
+        <v>1.19</v>
       </c>
       <c r="AR132">
         <v>1.05</v>
@@ -28442,7 +28457,7 @@
         <v>178</v>
       </c>
       <c r="P133" t="s">
-        <v>258</v>
+        <v>262</v>
       </c>
       <c r="Q133">
         <v>3.5</v>
@@ -28523,7 +28538,7 @@
         <v>0.71</v>
       </c>
       <c r="AQ133">
-        <v>1.45</v>
+        <v>1.38</v>
       </c>
       <c r="AR133">
         <v>1.11</v>
@@ -28648,7 +28663,7 @@
         <v>88</v>
       </c>
       <c r="P134" t="s">
-        <v>259</v>
+        <v>263</v>
       </c>
       <c r="Q134">
         <v>2.75</v>
@@ -28726,10 +28741,10 @@
         <v>1.19</v>
       </c>
       <c r="AP134">
-        <v>1.25</v>
+        <v>1.33</v>
       </c>
       <c r="AQ134">
-        <v>1.4</v>
+        <v>1.33</v>
       </c>
       <c r="AR134">
         <v>1.4</v>
@@ -29060,7 +29075,7 @@
         <v>88</v>
       </c>
       <c r="P136" t="s">
-        <v>260</v>
+        <v>264</v>
       </c>
       <c r="Q136">
         <v>4.5</v>
@@ -29138,7 +29153,7 @@
         <v>2.75</v>
       </c>
       <c r="AP136">
-        <v>1.95</v>
+        <v>2</v>
       </c>
       <c r="AQ136">
         <v>2.67</v>
@@ -29472,7 +29487,7 @@
         <v>91</v>
       </c>
       <c r="P138" t="s">
-        <v>247</v>
+        <v>251</v>
       </c>
       <c r="Q138">
         <v>2.25</v>
@@ -29550,7 +29565,7 @@
         <v>0.76</v>
       </c>
       <c r="AP138">
-        <v>1.25</v>
+        <v>1.19</v>
       </c>
       <c r="AQ138">
         <v>0.71</v>
@@ -29678,7 +29693,7 @@
         <v>179</v>
       </c>
       <c r="P139" t="s">
-        <v>256</v>
+        <v>260</v>
       </c>
       <c r="Q139">
         <v>1.9</v>
@@ -29756,7 +29771,7 @@
         <v>0.71</v>
       </c>
       <c r="AP139">
-        <v>1.5</v>
+        <v>1.57</v>
       </c>
       <c r="AQ139">
         <v>0.65</v>
@@ -29962,10 +29977,10 @@
         <v>1.24</v>
       </c>
       <c r="AP140">
-        <v>2</v>
+        <v>2.05</v>
       </c>
       <c r="AQ140">
-        <v>1.25</v>
+        <v>1.33</v>
       </c>
       <c r="AR140">
         <v>1.86</v>
@@ -30090,7 +30105,7 @@
         <v>117</v>
       </c>
       <c r="P141" t="s">
-        <v>261</v>
+        <v>265</v>
       </c>
       <c r="Q141">
         <v>4</v>
@@ -30296,7 +30311,7 @@
         <v>88</v>
       </c>
       <c r="P142" t="s">
-        <v>262</v>
+        <v>266</v>
       </c>
       <c r="Q142">
         <v>4</v>
@@ -30374,7 +30389,7 @@
         <v>1.47</v>
       </c>
       <c r="AP142">
-        <v>0.2</v>
+        <v>0.19</v>
       </c>
       <c r="AQ142">
         <v>1.48</v>
@@ -30708,7 +30723,7 @@
         <v>182</v>
       </c>
       <c r="P144" t="s">
-        <v>263</v>
+        <v>267</v>
       </c>
       <c r="Q144">
         <v>6</v>
@@ -30786,7 +30801,7 @@
         <v>2.76</v>
       </c>
       <c r="AP144">
-        <v>1.45</v>
+        <v>1.38</v>
       </c>
       <c r="AQ144">
         <v>2.67</v>
@@ -30914,7 +30929,7 @@
         <v>88</v>
       </c>
       <c r="P145" t="s">
-        <v>264</v>
+        <v>268</v>
       </c>
       <c r="Q145">
         <v>3.5</v>
@@ -30992,10 +31007,10 @@
         <v>1.76</v>
       </c>
       <c r="AP145">
-        <v>1.4</v>
+        <v>1.33</v>
       </c>
       <c r="AQ145">
-        <v>1.95</v>
+        <v>2</v>
       </c>
       <c r="AR145">
         <v>1.28</v>
@@ -31120,7 +31135,7 @@
         <v>183</v>
       </c>
       <c r="P146" t="s">
-        <v>265</v>
+        <v>269</v>
       </c>
       <c r="Q146">
         <v>4.33</v>
@@ -31201,7 +31216,7 @@
         <v>0.65</v>
       </c>
       <c r="AQ146">
-        <v>1.4</v>
+        <v>1.33</v>
       </c>
       <c r="AR146">
         <v>1.07</v>
@@ -31326,7 +31341,7 @@
         <v>184</v>
       </c>
       <c r="P147" t="s">
-        <v>266</v>
+        <v>270</v>
       </c>
       <c r="Q147">
         <v>3.8</v>
@@ -31532,7 +31547,7 @@
         <v>185</v>
       </c>
       <c r="P148" t="s">
-        <v>267</v>
+        <v>271</v>
       </c>
       <c r="Q148">
         <v>2.5</v>
@@ -31610,7 +31625,7 @@
         <v>1.22</v>
       </c>
       <c r="AP148">
-        <v>1.25</v>
+        <v>1.33</v>
       </c>
       <c r="AQ148">
         <v>1.2</v>
@@ -31738,7 +31753,7 @@
         <v>186</v>
       </c>
       <c r="P149" t="s">
-        <v>264</v>
+        <v>268</v>
       </c>
       <c r="Q149">
         <v>2.05</v>
@@ -31816,10 +31831,10 @@
         <v>1.39</v>
       </c>
       <c r="AP149">
-        <v>1.95</v>
+        <v>2</v>
       </c>
       <c r="AQ149">
-        <v>1.25</v>
+        <v>1.19</v>
       </c>
       <c r="AR149">
         <v>1.76</v>
@@ -31944,7 +31959,7 @@
         <v>187</v>
       </c>
       <c r="P150" t="s">
-        <v>268</v>
+        <v>272</v>
       </c>
       <c r="Q150">
         <v>1.95</v>
@@ -32022,10 +32037,10 @@
         <v>1.67</v>
       </c>
       <c r="AP150">
-        <v>2</v>
+        <v>2.05</v>
       </c>
       <c r="AQ150">
-        <v>1.5</v>
+        <v>1.57</v>
       </c>
       <c r="AR150">
         <v>1.83</v>
@@ -32150,7 +32165,7 @@
         <v>188</v>
       </c>
       <c r="P151" t="s">
-        <v>269</v>
+        <v>273</v>
       </c>
       <c r="Q151">
         <v>2.48</v>
@@ -32231,7 +32246,7 @@
         <v>1.48</v>
       </c>
       <c r="AQ151">
-        <v>1.45</v>
+        <v>1.38</v>
       </c>
       <c r="AR151">
         <v>1.45</v>
@@ -32562,7 +32577,7 @@
         <v>190</v>
       </c>
       <c r="P153" t="s">
-        <v>270</v>
+        <v>274</v>
       </c>
       <c r="Q153">
         <v>1.4</v>
@@ -32643,7 +32658,7 @@
         <v>2.19</v>
       </c>
       <c r="AQ153">
-        <v>0.2</v>
+        <v>0.19</v>
       </c>
       <c r="AR153">
         <v>1.53</v>
@@ -33052,7 +33067,7 @@
         <v>0.63</v>
       </c>
       <c r="AP155">
-        <v>0.2</v>
+        <v>0.19</v>
       </c>
       <c r="AQ155">
         <v>0.65</v>
@@ -33180,7 +33195,7 @@
         <v>88</v>
       </c>
       <c r="P156" t="s">
-        <v>205</v>
+        <v>209</v>
       </c>
       <c r="Q156">
         <v>3.2</v>
@@ -33261,7 +33276,7 @@
         <v>1.14</v>
       </c>
       <c r="AQ156">
-        <v>1.95</v>
+        <v>2</v>
       </c>
       <c r="AR156">
         <v>1.49</v>
@@ -33464,7 +33479,7 @@
         <v>0.79</v>
       </c>
       <c r="AP157">
-        <v>1.4</v>
+        <v>1.33</v>
       </c>
       <c r="AQ157">
         <v>0.71</v>
@@ -33592,7 +33607,7 @@
         <v>88</v>
       </c>
       <c r="P158" t="s">
-        <v>271</v>
+        <v>275</v>
       </c>
       <c r="Q158">
         <v>5</v>
@@ -33670,10 +33685,10 @@
         <v>1.95</v>
       </c>
       <c r="AP158">
-        <v>1.25</v>
+        <v>1.19</v>
       </c>
       <c r="AQ158">
-        <v>2</v>
+        <v>2.05</v>
       </c>
       <c r="AR158">
         <v>1.23</v>
@@ -33798,7 +33813,7 @@
         <v>88</v>
       </c>
       <c r="P159" t="s">
-        <v>227</v>
+        <v>231</v>
       </c>
       <c r="Q159">
         <v>2.38</v>
@@ -33876,10 +33891,10 @@
         <v>1.16</v>
       </c>
       <c r="AP159">
-        <v>1.5</v>
+        <v>1.57</v>
       </c>
       <c r="AQ159">
-        <v>1.25</v>
+        <v>1.33</v>
       </c>
       <c r="AR159">
         <v>1.5</v>
@@ -34210,7 +34225,7 @@
         <v>193</v>
       </c>
       <c r="P161" t="s">
-        <v>254</v>
+        <v>258</v>
       </c>
       <c r="Q161">
         <v>4.75</v>
@@ -34288,7 +34303,7 @@
         <v>2.26</v>
       </c>
       <c r="AP161">
-        <v>1.45</v>
+        <v>1.38</v>
       </c>
       <c r="AQ161">
         <v>2.19</v>
@@ -34416,7 +34431,7 @@
         <v>194</v>
       </c>
       <c r="P162" t="s">
-        <v>272</v>
+        <v>276</v>
       </c>
       <c r="Q162">
         <v>2.63</v>
@@ -34622,7 +34637,7 @@
         <v>88</v>
       </c>
       <c r="P163" t="s">
-        <v>273</v>
+        <v>277</v>
       </c>
       <c r="Q163">
         <v>11</v>
@@ -34828,7 +34843,7 @@
         <v>195</v>
       </c>
       <c r="P164" t="s">
-        <v>274</v>
+        <v>278</v>
       </c>
       <c r="Q164">
         <v>2</v>
@@ -34985,6 +35000,830 @@
       </c>
       <c r="BP164">
         <v>1.44</v>
+      </c>
+    </row>
+    <row r="165" spans="1:68">
+      <c r="A165" s="1">
+        <v>164</v>
+      </c>
+      <c r="B165">
+        <v>7468244</v>
+      </c>
+      <c r="C165" t="s">
+        <v>68</v>
+      </c>
+      <c r="D165" t="s">
+        <v>69</v>
+      </c>
+      <c r="E165" s="2">
+        <v>45697.375</v>
+      </c>
+      <c r="F165">
+        <v>21</v>
+      </c>
+      <c r="G165" t="s">
+        <v>71</v>
+      </c>
+      <c r="H165" t="s">
+        <v>76</v>
+      </c>
+      <c r="I165">
+        <v>1</v>
+      </c>
+      <c r="J165">
+        <v>0</v>
+      </c>
+      <c r="K165">
+        <v>1</v>
+      </c>
+      <c r="L165">
+        <v>4</v>
+      </c>
+      <c r="M165">
+        <v>2</v>
+      </c>
+      <c r="N165">
+        <v>6</v>
+      </c>
+      <c r="O165" t="s">
+        <v>196</v>
+      </c>
+      <c r="P165" t="s">
+        <v>279</v>
+      </c>
+      <c r="Q165">
+        <v>2.5</v>
+      </c>
+      <c r="R165">
+        <v>2.2</v>
+      </c>
+      <c r="S165">
+        <v>4.75</v>
+      </c>
+      <c r="T165">
+        <v>1.4</v>
+      </c>
+      <c r="U165">
+        <v>2.75</v>
+      </c>
+      <c r="V165">
+        <v>3</v>
+      </c>
+      <c r="W165">
+        <v>1.36</v>
+      </c>
+      <c r="X165">
+        <v>8</v>
+      </c>
+      <c r="Y165">
+        <v>1.08</v>
+      </c>
+      <c r="Z165">
+        <v>1.81</v>
+      </c>
+      <c r="AA165">
+        <v>3.29</v>
+      </c>
+      <c r="AB165">
+        <v>4.47</v>
+      </c>
+      <c r="AC165">
+        <v>1.05</v>
+      </c>
+      <c r="AD165">
+        <v>8.5</v>
+      </c>
+      <c r="AE165">
+        <v>1.26</v>
+      </c>
+      <c r="AF165">
+        <v>3.5</v>
+      </c>
+      <c r="AG165">
+        <v>1.98</v>
+      </c>
+      <c r="AH165">
+        <v>1.77</v>
+      </c>
+      <c r="AI165">
+        <v>1.91</v>
+      </c>
+      <c r="AJ165">
+        <v>1.91</v>
+      </c>
+      <c r="AK165">
+        <v>1.22</v>
+      </c>
+      <c r="AL165">
+        <v>1.28</v>
+      </c>
+      <c r="AM165">
+        <v>1.93</v>
+      </c>
+      <c r="AN165">
+        <v>1.5</v>
+      </c>
+      <c r="AO165">
+        <v>1.25</v>
+      </c>
+      <c r="AP165">
+        <v>1.57</v>
+      </c>
+      <c r="AQ165">
+        <v>1.19</v>
+      </c>
+      <c r="AR165">
+        <v>1.5</v>
+      </c>
+      <c r="AS165">
+        <v>1.23</v>
+      </c>
+      <c r="AT165">
+        <v>2.73</v>
+      </c>
+      <c r="AU165">
+        <v>8</v>
+      </c>
+      <c r="AV165">
+        <v>7</v>
+      </c>
+      <c r="AW165">
+        <v>3</v>
+      </c>
+      <c r="AX165">
+        <v>0</v>
+      </c>
+      <c r="AY165">
+        <v>11</v>
+      </c>
+      <c r="AZ165">
+        <v>7</v>
+      </c>
+      <c r="BA165">
+        <v>5</v>
+      </c>
+      <c r="BB165">
+        <v>2</v>
+      </c>
+      <c r="BC165">
+        <v>7</v>
+      </c>
+      <c r="BD165">
+        <v>1.6</v>
+      </c>
+      <c r="BE165">
+        <v>7</v>
+      </c>
+      <c r="BF165">
+        <v>2.55</v>
+      </c>
+      <c r="BG165">
+        <v>1.24</v>
+      </c>
+      <c r="BH165">
+        <v>3.55</v>
+      </c>
+      <c r="BI165">
+        <v>1.43</v>
+      </c>
+      <c r="BJ165">
+        <v>2.55</v>
+      </c>
+      <c r="BK165">
+        <v>1.72</v>
+      </c>
+      <c r="BL165">
+        <v>1.98</v>
+      </c>
+      <c r="BM165">
+        <v>1.95</v>
+      </c>
+      <c r="BN165">
+        <v>1.77</v>
+      </c>
+      <c r="BO165">
+        <v>2.63</v>
+      </c>
+      <c r="BP165">
+        <v>1.43</v>
+      </c>
+    </row>
+    <row r="166" spans="1:68">
+      <c r="A166" s="1">
+        <v>165</v>
+      </c>
+      <c r="B166">
+        <v>7468241</v>
+      </c>
+      <c r="C166" t="s">
+        <v>68</v>
+      </c>
+      <c r="D166" t="s">
+        <v>69</v>
+      </c>
+      <c r="E166" s="2">
+        <v>45697.47916666666</v>
+      </c>
+      <c r="F166">
+        <v>21</v>
+      </c>
+      <c r="G166" t="s">
+        <v>83</v>
+      </c>
+      <c r="H166" t="s">
+        <v>85</v>
+      </c>
+      <c r="I166">
+        <v>1</v>
+      </c>
+      <c r="J166">
+        <v>0</v>
+      </c>
+      <c r="K166">
+        <v>1</v>
+      </c>
+      <c r="L166">
+        <v>1</v>
+      </c>
+      <c r="M166">
+        <v>0</v>
+      </c>
+      <c r="N166">
+        <v>1</v>
+      </c>
+      <c r="O166" t="s">
+        <v>197</v>
+      </c>
+      <c r="P166" t="s">
+        <v>88</v>
+      </c>
+      <c r="Q166">
+        <v>2.1</v>
+      </c>
+      <c r="R166">
+        <v>2.38</v>
+      </c>
+      <c r="S166">
+        <v>5.5</v>
+      </c>
+      <c r="T166">
+        <v>1.33</v>
+      </c>
+      <c r="U166">
+        <v>3.25</v>
+      </c>
+      <c r="V166">
+        <v>2.63</v>
+      </c>
+      <c r="W166">
+        <v>1.44</v>
+      </c>
+      <c r="X166">
+        <v>6.5</v>
+      </c>
+      <c r="Y166">
+        <v>1.11</v>
+      </c>
+      <c r="Z166">
+        <v>1.53</v>
+      </c>
+      <c r="AA166">
+        <v>4.09</v>
+      </c>
+      <c r="AB166">
+        <v>5.35</v>
+      </c>
+      <c r="AC166">
+        <v>1.04</v>
+      </c>
+      <c r="AD166">
+        <v>9</v>
+      </c>
+      <c r="AE166">
+        <v>1.23</v>
+      </c>
+      <c r="AF166">
+        <v>3.85</v>
+      </c>
+      <c r="AG166">
+        <v>1.7</v>
+      </c>
+      <c r="AH166">
+        <v>2.1</v>
+      </c>
+      <c r="AI166">
+        <v>1.8</v>
+      </c>
+      <c r="AJ166">
+        <v>1.95</v>
+      </c>
+      <c r="AK166">
+        <v>1.18</v>
+      </c>
+      <c r="AL166">
+        <v>1.22</v>
+      </c>
+      <c r="AM166">
+        <v>2.2</v>
+      </c>
+      <c r="AN166">
+        <v>1.95</v>
+      </c>
+      <c r="AO166">
+        <v>1.45</v>
+      </c>
+      <c r="AP166">
+        <v>2</v>
+      </c>
+      <c r="AQ166">
+        <v>1.38</v>
+      </c>
+      <c r="AR166">
+        <v>1.79</v>
+      </c>
+      <c r="AS166">
+        <v>1.38</v>
+      </c>
+      <c r="AT166">
+        <v>3.17</v>
+      </c>
+      <c r="AU166">
+        <v>4</v>
+      </c>
+      <c r="AV166">
+        <v>3</v>
+      </c>
+      <c r="AW166">
+        <v>5</v>
+      </c>
+      <c r="AX166">
+        <v>4</v>
+      </c>
+      <c r="AY166">
+        <v>9</v>
+      </c>
+      <c r="AZ166">
+        <v>7</v>
+      </c>
+      <c r="BA166">
+        <v>6</v>
+      </c>
+      <c r="BB166">
+        <v>2</v>
+      </c>
+      <c r="BC166">
+        <v>8</v>
+      </c>
+      <c r="BD166">
+        <v>1.43</v>
+      </c>
+      <c r="BE166">
+        <v>7</v>
+      </c>
+      <c r="BF166">
+        <v>3.15</v>
+      </c>
+      <c r="BG166">
+        <v>1.17</v>
+      </c>
+      <c r="BH166">
+        <v>4.35</v>
+      </c>
+      <c r="BI166">
+        <v>1.3</v>
+      </c>
+      <c r="BJ166">
+        <v>3.15</v>
+      </c>
+      <c r="BK166">
+        <v>1.5</v>
+      </c>
+      <c r="BL166">
+        <v>2.35</v>
+      </c>
+      <c r="BM166">
+        <v>1.77</v>
+      </c>
+      <c r="BN166">
+        <v>1.95</v>
+      </c>
+      <c r="BO166">
+        <v>2.18</v>
+      </c>
+      <c r="BP166">
+        <v>1.58</v>
+      </c>
+    </row>
+    <row r="167" spans="1:68">
+      <c r="A167" s="1">
+        <v>166</v>
+      </c>
+      <c r="B167">
+        <v>7468247</v>
+      </c>
+      <c r="C167" t="s">
+        <v>68</v>
+      </c>
+      <c r="D167" t="s">
+        <v>69</v>
+      </c>
+      <c r="E167" s="2">
+        <v>45697.47916666666</v>
+      </c>
+      <c r="F167">
+        <v>21</v>
+      </c>
+      <c r="G167" t="s">
+        <v>73</v>
+      </c>
+      <c r="H167" t="s">
+        <v>72</v>
+      </c>
+      <c r="I167">
+        <v>1</v>
+      </c>
+      <c r="J167">
+        <v>0</v>
+      </c>
+      <c r="K167">
+        <v>1</v>
+      </c>
+      <c r="L167">
+        <v>1</v>
+      </c>
+      <c r="M167">
+        <v>0</v>
+      </c>
+      <c r="N167">
+        <v>1</v>
+      </c>
+      <c r="O167" t="s">
+        <v>198</v>
+      </c>
+      <c r="P167" t="s">
+        <v>88</v>
+      </c>
+      <c r="Q167">
+        <v>1.95</v>
+      </c>
+      <c r="R167">
+        <v>2.5</v>
+      </c>
+      <c r="S167">
+        <v>6</v>
+      </c>
+      <c r="T167">
+        <v>1.3</v>
+      </c>
+      <c r="U167">
+        <v>3.4</v>
+      </c>
+      <c r="V167">
+        <v>2.5</v>
+      </c>
+      <c r="W167">
+        <v>1.5</v>
+      </c>
+      <c r="X167">
+        <v>6</v>
+      </c>
+      <c r="Y167">
+        <v>1.13</v>
+      </c>
+      <c r="Z167">
+        <v>1.44</v>
+      </c>
+      <c r="AA167">
+        <v>4.2</v>
+      </c>
+      <c r="AB167">
+        <v>6</v>
+      </c>
+      <c r="AC167">
+        <v>1.04</v>
+      </c>
+      <c r="AD167">
+        <v>9</v>
+      </c>
+      <c r="AE167">
+        <v>1.21</v>
+      </c>
+      <c r="AF167">
+        <v>4</v>
+      </c>
+      <c r="AG167">
+        <v>1.65</v>
+      </c>
+      <c r="AH167">
+        <v>2.08</v>
+      </c>
+      <c r="AI167">
+        <v>1.8</v>
+      </c>
+      <c r="AJ167">
+        <v>1.95</v>
+      </c>
+      <c r="AK167">
+        <v>1.1</v>
+      </c>
+      <c r="AL167">
+        <v>1.19</v>
+      </c>
+      <c r="AM167">
+        <v>2.75</v>
+      </c>
+      <c r="AN167">
+        <v>1.25</v>
+      </c>
+      <c r="AO167">
+        <v>0.2</v>
+      </c>
+      <c r="AP167">
+        <v>1.33</v>
+      </c>
+      <c r="AQ167">
+        <v>0.19</v>
+      </c>
+      <c r="AR167">
+        <v>1.47</v>
+      </c>
+      <c r="AS167">
+        <v>1.14</v>
+      </c>
+      <c r="AT167">
+        <v>2.61</v>
+      </c>
+      <c r="AU167">
+        <v>5</v>
+      </c>
+      <c r="AV167">
+        <v>4</v>
+      </c>
+      <c r="AW167">
+        <v>9</v>
+      </c>
+      <c r="AX167">
+        <v>6</v>
+      </c>
+      <c r="AY167">
+        <v>14</v>
+      </c>
+      <c r="AZ167">
+        <v>10</v>
+      </c>
+      <c r="BA167">
+        <v>7</v>
+      </c>
+      <c r="BB167">
+        <v>6</v>
+      </c>
+      <c r="BC167">
+        <v>13</v>
+      </c>
+      <c r="BD167">
+        <v>1.12</v>
+      </c>
+      <c r="BE167">
+        <v>11</v>
+      </c>
+      <c r="BF167">
+        <v>6.6</v>
+      </c>
+      <c r="BG167">
+        <v>1.14</v>
+      </c>
+      <c r="BH167">
+        <v>4.8</v>
+      </c>
+      <c r="BI167">
+        <v>1.19</v>
+      </c>
+      <c r="BJ167">
+        <v>4.1</v>
+      </c>
+      <c r="BK167">
+        <v>1.39</v>
+      </c>
+      <c r="BL167">
+        <v>2.75</v>
+      </c>
+      <c r="BM167">
+        <v>1.68</v>
+      </c>
+      <c r="BN167">
+        <v>2.05</v>
+      </c>
+      <c r="BO167">
+        <v>2.12</v>
+      </c>
+      <c r="BP167">
+        <v>1.62</v>
+      </c>
+    </row>
+    <row r="168" spans="1:68">
+      <c r="A168" s="1">
+        <v>167</v>
+      </c>
+      <c r="B168">
+        <v>7468245</v>
+      </c>
+      <c r="C168" t="s">
+        <v>68</v>
+      </c>
+      <c r="D168" t="s">
+        <v>69</v>
+      </c>
+      <c r="E168" s="2">
+        <v>45697.60416666666</v>
+      </c>
+      <c r="F168">
+        <v>21</v>
+      </c>
+      <c r="G168" t="s">
+        <v>70</v>
+      </c>
+      <c r="H168" t="s">
+        <v>77</v>
+      </c>
+      <c r="I168">
+        <v>1</v>
+      </c>
+      <c r="J168">
+        <v>0</v>
+      </c>
+      <c r="K168">
+        <v>1</v>
+      </c>
+      <c r="L168">
+        <v>3</v>
+      </c>
+      <c r="M168">
+        <v>0</v>
+      </c>
+      <c r="N168">
+        <v>3</v>
+      </c>
+      <c r="O168" t="s">
+        <v>199</v>
+      </c>
+      <c r="P168" t="s">
+        <v>88</v>
+      </c>
+      <c r="Q168">
+        <v>2</v>
+      </c>
+      <c r="R168">
+        <v>2.3</v>
+      </c>
+      <c r="S168">
+        <v>6.5</v>
+      </c>
+      <c r="T168">
+        <v>1.36</v>
+      </c>
+      <c r="U168">
+        <v>3</v>
+      </c>
+      <c r="V168">
+        <v>2.63</v>
+      </c>
+      <c r="W168">
+        <v>1.44</v>
+      </c>
+      <c r="X168">
+        <v>7</v>
+      </c>
+      <c r="Y168">
+        <v>1.1</v>
+      </c>
+      <c r="Z168">
+        <v>1.44</v>
+      </c>
+      <c r="AA168">
+        <v>4.2</v>
+      </c>
+      <c r="AB168">
+        <v>7</v>
+      </c>
+      <c r="AC168">
+        <v>1.04</v>
+      </c>
+      <c r="AD168">
+        <v>9</v>
+      </c>
+      <c r="AE168">
+        <v>1.25</v>
+      </c>
+      <c r="AF168">
+        <v>3.65</v>
+      </c>
+      <c r="AG168">
+        <v>1.82</v>
+      </c>
+      <c r="AH168">
+        <v>2.01</v>
+      </c>
+      <c r="AI168">
+        <v>1.95</v>
+      </c>
+      <c r="AJ168">
+        <v>1.8</v>
+      </c>
+      <c r="AK168">
+        <v>1.11</v>
+      </c>
+      <c r="AL168">
+        <v>1.19</v>
+      </c>
+      <c r="AM168">
+        <v>2.65</v>
+      </c>
+      <c r="AN168">
+        <v>2</v>
+      </c>
+      <c r="AO168">
+        <v>1.4</v>
+      </c>
+      <c r="AP168">
+        <v>2.05</v>
+      </c>
+      <c r="AQ168">
+        <v>1.33</v>
+      </c>
+      <c r="AR168">
+        <v>1.82</v>
+      </c>
+      <c r="AS168">
+        <v>1.38</v>
+      </c>
+      <c r="AT168">
+        <v>3.2</v>
+      </c>
+      <c r="AU168">
+        <v>13</v>
+      </c>
+      <c r="AV168">
+        <v>3</v>
+      </c>
+      <c r="AW168">
+        <v>11</v>
+      </c>
+      <c r="AX168">
+        <v>3</v>
+      </c>
+      <c r="AY168">
+        <v>24</v>
+      </c>
+      <c r="AZ168">
+        <v>6</v>
+      </c>
+      <c r="BA168">
+        <v>6</v>
+      </c>
+      <c r="BB168">
+        <v>1</v>
+      </c>
+      <c r="BC168">
+        <v>7</v>
+      </c>
+      <c r="BD168">
+        <v>1.53</v>
+      </c>
+      <c r="BE168">
+        <v>6.75</v>
+      </c>
+      <c r="BF168">
+        <v>2.7</v>
+      </c>
+      <c r="BG168">
+        <v>1.25</v>
+      </c>
+      <c r="BH168">
+        <v>3.45</v>
+      </c>
+      <c r="BI168">
+        <v>1.45</v>
+      </c>
+      <c r="BJ168">
+        <v>2.55</v>
+      </c>
+      <c r="BK168">
+        <v>1.7</v>
+      </c>
+      <c r="BL168">
+        <v>2.05</v>
+      </c>
+      <c r="BM168">
+        <v>2.12</v>
+      </c>
+      <c r="BN168">
+        <v>1.63</v>
+      </c>
+      <c r="BO168">
+        <v>2.7</v>
+      </c>
+      <c r="BP168">
+        <v>1.4</v>
       </c>
     </row>
   </sheetData>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Czech Republic First League_20242025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Czech Republic First League_20242025.xlsx
@@ -1549,10 +1549,10 @@
         <v>0</v>
       </c>
       <c r="AP2">
-        <v>2.05</v>
+        <v>2.09</v>
       </c>
       <c r="AQ2">
-        <v>0.71</v>
+        <v>0.55</v>
       </c>
       <c r="AR2">
         <v>0</v>
@@ -1755,10 +1755,10 @@
         <v>0</v>
       </c>
       <c r="AP3">
-        <v>1.57</v>
+        <v>2</v>
       </c>
       <c r="AQ3">
-        <v>1.48</v>
+        <v>1.2</v>
       </c>
       <c r="AR3">
         <v>0</v>
@@ -1961,10 +1961,10 @@
         <v>0</v>
       </c>
       <c r="AP4">
-        <v>0.19</v>
+        <v>0.27</v>
       </c>
       <c r="AQ4">
-        <v>1.38</v>
+        <v>1.09</v>
       </c>
       <c r="AR4">
         <v>0</v>
@@ -2167,10 +2167,10 @@
         <v>0</v>
       </c>
       <c r="AP5">
-        <v>1.33</v>
+        <v>1.18</v>
       </c>
       <c r="AQ5">
-        <v>2</v>
+        <v>1.64</v>
       </c>
       <c r="AR5">
         <v>0</v>
@@ -2373,10 +2373,10 @@
         <v>0</v>
       </c>
       <c r="AP6">
-        <v>0.65</v>
+        <v>1</v>
       </c>
       <c r="AQ6">
-        <v>2.19</v>
+        <v>1.7</v>
       </c>
       <c r="AR6">
         <v>0</v>
@@ -2579,10 +2579,10 @@
         <v>0</v>
       </c>
       <c r="AP7">
-        <v>1.2</v>
+        <v>1.45</v>
       </c>
       <c r="AQ7">
-        <v>1.14</v>
+        <v>1</v>
       </c>
       <c r="AR7">
         <v>0</v>
@@ -2785,10 +2785,10 @@
         <v>0</v>
       </c>
       <c r="AP8">
-        <v>1.19</v>
+        <v>1.4</v>
       </c>
       <c r="AQ8">
-        <v>2.67</v>
+        <v>2.36</v>
       </c>
       <c r="AR8">
         <v>0</v>
@@ -2991,10 +2991,10 @@
         <v>0</v>
       </c>
       <c r="AP9">
-        <v>1.33</v>
+        <v>1.7</v>
       </c>
       <c r="AQ9">
-        <v>1.05</v>
+        <v>0.82</v>
       </c>
       <c r="AR9">
         <v>0</v>
@@ -3194,22 +3194,22 @@
         <v>0</v>
       </c>
       <c r="AO10">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="AP10">
-        <v>0.65</v>
+        <v>1</v>
       </c>
       <c r="AQ10">
-        <v>1.33</v>
+        <v>1.5</v>
       </c>
       <c r="AR10">
         <v>0.98</v>
       </c>
       <c r="AS10">
-        <v>1.73</v>
+        <v>0</v>
       </c>
       <c r="AT10">
-        <v>2.71</v>
+        <v>0.98</v>
       </c>
       <c r="AU10">
         <v>3</v>
@@ -3400,22 +3400,22 @@
         <v>0</v>
       </c>
       <c r="AO11">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="AP11">
-        <v>1.05</v>
+        <v>1.3</v>
       </c>
       <c r="AQ11">
-        <v>2.05</v>
+        <v>2</v>
       </c>
       <c r="AR11">
-        <v>1.21</v>
+        <v>0</v>
       </c>
       <c r="AS11">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AT11">
-        <v>3.11</v>
+        <v>0</v>
       </c>
       <c r="AU11">
         <v>4</v>
@@ -3609,19 +3609,19 @@
         <v>0</v>
       </c>
       <c r="AP12">
-        <v>0.71</v>
+        <v>0.9</v>
       </c>
       <c r="AQ12">
-        <v>1.2</v>
+        <v>0.89</v>
       </c>
       <c r="AR12">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="AS12">
-        <v>1.93</v>
+        <v>0</v>
       </c>
       <c r="AT12">
-        <v>2.96</v>
+        <v>0</v>
       </c>
       <c r="AU12">
         <v>3</v>
@@ -3809,25 +3809,25 @@
         <v>5.85</v>
       </c>
       <c r="AN13">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AO13">
         <v>0</v>
       </c>
       <c r="AP13">
-        <v>2.67</v>
+        <v>3</v>
       </c>
       <c r="AQ13">
-        <v>0.19</v>
+        <v>0.1</v>
       </c>
       <c r="AR13">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="AS13">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="AT13">
-        <v>2.98</v>
+        <v>0</v>
       </c>
       <c r="AU13">
         <v>9</v>
@@ -4015,25 +4015,25 @@
         <v>1.78</v>
       </c>
       <c r="AN14">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="AO14">
         <v>3</v>
       </c>
       <c r="AP14">
-        <v>1.14</v>
+        <v>1.3</v>
       </c>
       <c r="AQ14">
-        <v>1.38</v>
+        <v>1.09</v>
       </c>
       <c r="AR14">
-        <v>1.97</v>
+        <v>0</v>
       </c>
       <c r="AS14">
         <v>2.08</v>
       </c>
       <c r="AT14">
-        <v>4.05</v>
+        <v>2.08</v>
       </c>
       <c r="AU14">
         <v>4</v>
@@ -4224,22 +4224,22 @@
         <v>0</v>
       </c>
       <c r="AO15">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AP15">
-        <v>1.48</v>
+        <v>1.73</v>
       </c>
       <c r="AQ15">
-        <v>1.19</v>
+        <v>1</v>
       </c>
       <c r="AR15">
-        <v>0.9399999999999999</v>
+        <v>0</v>
       </c>
       <c r="AS15">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AT15">
-        <v>1.94</v>
+        <v>0</v>
       </c>
       <c r="AU15">
         <v>7</v>
@@ -4430,22 +4430,22 @@
         <v>0</v>
       </c>
       <c r="AO16">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="AP16">
-        <v>2</v>
+        <v>2.4</v>
       </c>
       <c r="AQ16">
-        <v>1.57</v>
+        <v>1.1</v>
       </c>
       <c r="AR16">
-        <v>1.71</v>
+        <v>0</v>
       </c>
       <c r="AS16">
-        <v>1.81</v>
+        <v>0</v>
       </c>
       <c r="AT16">
-        <v>3.52</v>
+        <v>0</v>
       </c>
       <c r="AU16">
         <v>5</v>
@@ -4633,25 +4633,25 @@
         <v>2.7</v>
       </c>
       <c r="AN17">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="AO17">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="AP17">
-        <v>2.19</v>
+        <v>2.64</v>
       </c>
       <c r="AQ17">
-        <v>1.33</v>
+        <v>1</v>
       </c>
       <c r="AR17">
-        <v>1.43</v>
+        <v>0</v>
       </c>
       <c r="AS17">
-        <v>1.19</v>
+        <v>0</v>
       </c>
       <c r="AT17">
-        <v>2.62</v>
+        <v>0</v>
       </c>
       <c r="AU17">
         <v>8</v>
@@ -4839,25 +4839,25 @@
         <v>1.12</v>
       </c>
       <c r="AN18">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AO18">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AP18">
-        <v>1.14</v>
+        <v>1.3</v>
       </c>
       <c r="AQ18">
-        <v>2.67</v>
+        <v>2.36</v>
       </c>
       <c r="AR18">
-        <v>1.61</v>
+        <v>1.26</v>
       </c>
       <c r="AS18">
-        <v>2.02</v>
+        <v>1.65</v>
       </c>
       <c r="AT18">
-        <v>3.63</v>
+        <v>2.91</v>
       </c>
       <c r="AU18">
         <v>4</v>
@@ -5048,22 +5048,22 @@
         <v>3</v>
       </c>
       <c r="AO19">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="AP19">
-        <v>2.05</v>
+        <v>2.09</v>
       </c>
       <c r="AQ19">
-        <v>0.65</v>
+        <v>0.3</v>
       </c>
       <c r="AR19">
-        <v>1.96</v>
+        <v>1.9</v>
       </c>
       <c r="AS19">
-        <v>0.93</v>
+        <v>0</v>
       </c>
       <c r="AT19">
-        <v>2.89</v>
+        <v>1.9</v>
       </c>
       <c r="AU19">
         <v>9</v>
@@ -5251,25 +5251,25 @@
         <v>1.8</v>
       </c>
       <c r="AN20">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="AO20">
+        <v>0</v>
+      </c>
+      <c r="AP20">
+        <v>1.4</v>
+      </c>
+      <c r="AQ20">
         <v>1.5</v>
       </c>
-      <c r="AP20">
-        <v>1.19</v>
-      </c>
-      <c r="AQ20">
-        <v>1.33</v>
-      </c>
       <c r="AR20">
-        <v>1.25</v>
+        <v>1</v>
       </c>
       <c r="AS20">
-        <v>1.81</v>
+        <v>1.88</v>
       </c>
       <c r="AT20">
-        <v>3.06</v>
+        <v>2.88</v>
       </c>
       <c r="AU20">
         <v>4</v>
@@ -5457,25 +5457,25 @@
         <v>1.17</v>
       </c>
       <c r="AN21">
-        <v>1.5</v>
+        <v>3</v>
       </c>
       <c r="AO21">
         <v>3</v>
       </c>
       <c r="AP21">
-        <v>1.57</v>
+        <v>2</v>
       </c>
       <c r="AQ21">
-        <v>2.19</v>
+        <v>1.7</v>
       </c>
       <c r="AR21">
-        <v>1.38</v>
+        <v>1.81</v>
       </c>
       <c r="AS21">
-        <v>1.53</v>
+        <v>1.43</v>
       </c>
       <c r="AT21">
-        <v>2.91</v>
+        <v>3.24</v>
       </c>
       <c r="AU21">
         <v>5</v>
@@ -5663,25 +5663,25 @@
         <v>1.71</v>
       </c>
       <c r="AN22">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AO22">
         <v>0</v>
       </c>
       <c r="AP22">
-        <v>1.38</v>
+        <v>1.7</v>
       </c>
       <c r="AQ22">
-        <v>1.05</v>
+        <v>0.82</v>
       </c>
       <c r="AR22">
-        <v>1.48</v>
+        <v>0</v>
       </c>
       <c r="AS22">
-        <v>1.13</v>
+        <v>1.21</v>
       </c>
       <c r="AT22">
-        <v>2.61</v>
+        <v>1.21</v>
       </c>
       <c r="AU22">
         <v>5</v>
@@ -5875,19 +5875,19 @@
         <v>0</v>
       </c>
       <c r="AP23">
-        <v>0.19</v>
+        <v>0.27</v>
       </c>
       <c r="AQ23">
-        <v>0.71</v>
+        <v>0.55</v>
       </c>
       <c r="AR23">
-        <v>0.92</v>
+        <v>1.33</v>
       </c>
       <c r="AS23">
-        <v>1.12</v>
+        <v>1.03</v>
       </c>
       <c r="AT23">
-        <v>2.04</v>
+        <v>2.36</v>
       </c>
       <c r="AU23">
         <v>5</v>
@@ -6075,25 +6075,25 @@
         <v>1.78</v>
       </c>
       <c r="AN24">
-        <v>1.5</v>
+        <v>3</v>
       </c>
       <c r="AO24">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="AP24">
-        <v>1.33</v>
+        <v>1.7</v>
       </c>
       <c r="AQ24">
-        <v>1.48</v>
+        <v>1.2</v>
       </c>
       <c r="AR24">
-        <v>0.95</v>
+        <v>1.19</v>
       </c>
       <c r="AS24">
-        <v>1.35</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="AT24">
-        <v>2.3</v>
+        <v>2.13</v>
       </c>
       <c r="AU24">
         <v>4</v>
@@ -6281,25 +6281,25 @@
         <v>1.29</v>
       </c>
       <c r="AN25">
-        <v>1</v>
+        <v>1.5</v>
       </c>
       <c r="AO25">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="AP25">
-        <v>0.65</v>
+        <v>1</v>
       </c>
       <c r="AQ25">
-        <v>1.57</v>
+        <v>1.1</v>
       </c>
       <c r="AR25">
-        <v>0.82</v>
+        <v>0.93</v>
       </c>
       <c r="AS25">
-        <v>1.35</v>
+        <v>0.95</v>
       </c>
       <c r="AT25">
-        <v>2.17</v>
+        <v>1.88</v>
       </c>
       <c r="AU25">
         <v>3</v>
@@ -6487,25 +6487,25 @@
         <v>1.1</v>
       </c>
       <c r="AN26">
-        <v>1.33</v>
+        <v>3</v>
       </c>
       <c r="AO26">
         <v>3</v>
       </c>
       <c r="AP26">
-        <v>1.33</v>
+        <v>1.18</v>
       </c>
       <c r="AQ26">
-        <v>2.05</v>
+        <v>2</v>
       </c>
       <c r="AR26">
-        <v>1.45</v>
+        <v>1.73</v>
       </c>
       <c r="AS26">
-        <v>2.06</v>
+        <v>2.02</v>
       </c>
       <c r="AT26">
-        <v>3.51</v>
+        <v>3.75</v>
       </c>
       <c r="AU26">
         <v>6</v>
@@ -6696,22 +6696,22 @@
         <v>0</v>
       </c>
       <c r="AO27">
-        <v>1.33</v>
+        <v>3</v>
       </c>
       <c r="AP27">
-        <v>1.05</v>
+        <v>1.3</v>
       </c>
       <c r="AQ27">
-        <v>1.14</v>
+        <v>1</v>
       </c>
       <c r="AR27">
-        <v>1.28</v>
+        <v>1.06</v>
       </c>
       <c r="AS27">
-        <v>1.55</v>
+        <v>1.97</v>
       </c>
       <c r="AT27">
-        <v>2.83</v>
+        <v>3.03</v>
       </c>
       <c r="AU27">
         <v>6</v>
@@ -6899,25 +6899,25 @@
         <v>4.33</v>
       </c>
       <c r="AN28">
-        <v>2.33</v>
+        <v>3</v>
       </c>
       <c r="AO28">
-        <v>2.33</v>
+        <v>2</v>
       </c>
       <c r="AP28">
-        <v>2.67</v>
+        <v>3</v>
       </c>
       <c r="AQ28">
-        <v>1.38</v>
+        <v>1.09</v>
       </c>
       <c r="AR28">
-        <v>1.7</v>
+        <v>2.4</v>
       </c>
       <c r="AS28">
-        <v>1.4</v>
+        <v>1.48</v>
       </c>
       <c r="AT28">
-        <v>3.1</v>
+        <v>3.88</v>
       </c>
       <c r="AU28">
         <v>9</v>
@@ -7105,25 +7105,25 @@
         <v>1.36</v>
       </c>
       <c r="AN29">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AO29">
-        <v>0.67</v>
+        <v>0</v>
       </c>
       <c r="AP29">
-        <v>0.71</v>
+        <v>0.9</v>
       </c>
       <c r="AQ29">
-        <v>1.19</v>
+        <v>1</v>
       </c>
       <c r="AR29">
-        <v>1.07</v>
+        <v>1.22</v>
       </c>
       <c r="AS29">
-        <v>1.29</v>
+        <v>1.5</v>
       </c>
       <c r="AT29">
-        <v>2.36</v>
+        <v>2.72</v>
       </c>
       <c r="AU29">
         <v>4</v>
@@ -7311,25 +7311,25 @@
         <v>2.2</v>
       </c>
       <c r="AN30">
-        <v>1.5</v>
+        <v>3</v>
       </c>
       <c r="AO30">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AP30">
-        <v>2</v>
+        <v>2.4</v>
       </c>
       <c r="AQ30">
-        <v>1.33</v>
+        <v>1</v>
       </c>
       <c r="AR30">
-        <v>1.47</v>
+        <v>1.24</v>
       </c>
       <c r="AS30">
-        <v>0.96</v>
+        <v>0.71</v>
       </c>
       <c r="AT30">
-        <v>2.43</v>
+        <v>1.95</v>
       </c>
       <c r="AU30">
         <v>6</v>
@@ -7517,25 +7517,25 @@
         <v>2.38</v>
       </c>
       <c r="AN31">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="AO31">
         <v>0</v>
       </c>
       <c r="AP31">
-        <v>1.48</v>
+        <v>1.73</v>
       </c>
       <c r="AQ31">
-        <v>0.19</v>
+        <v>0.1</v>
       </c>
       <c r="AR31">
-        <v>1.63</v>
+        <v>1.76</v>
       </c>
       <c r="AS31">
-        <v>1.14</v>
+        <v>0.5</v>
       </c>
       <c r="AT31">
-        <v>2.77</v>
+        <v>2.26</v>
       </c>
       <c r="AU31">
         <v>7</v>
@@ -7723,25 +7723,25 @@
         <v>3.1</v>
       </c>
       <c r="AN32">
-        <v>2.33</v>
+        <v>3</v>
       </c>
       <c r="AO32">
-        <v>1.5</v>
+        <v>3</v>
       </c>
       <c r="AP32">
-        <v>2.19</v>
+        <v>2.64</v>
       </c>
       <c r="AQ32">
-        <v>1.2</v>
+        <v>0.89</v>
       </c>
       <c r="AR32">
-        <v>1.38</v>
+        <v>1.64</v>
       </c>
       <c r="AS32">
-        <v>2.15</v>
+        <v>2.37</v>
       </c>
       <c r="AT32">
-        <v>3.53</v>
+        <v>4.01</v>
       </c>
       <c r="AU32">
         <v>8</v>
@@ -7929,25 +7929,25 @@
         <v>2.35</v>
       </c>
       <c r="AN33">
-        <v>1.5</v>
+        <v>3</v>
       </c>
       <c r="AO33">
-        <v>0.75</v>
+        <v>0</v>
       </c>
       <c r="AP33">
-        <v>1.33</v>
+        <v>1.7</v>
       </c>
       <c r="AQ33">
-        <v>0.65</v>
+        <v>0.3</v>
       </c>
       <c r="AR33">
-        <v>0.84</v>
+        <v>1.08</v>
       </c>
       <c r="AS33">
-        <v>0.88</v>
+        <v>0.61</v>
       </c>
       <c r="AT33">
-        <v>1.72</v>
+        <v>1.69</v>
       </c>
       <c r="AU33">
         <v>6</v>
@@ -8135,25 +8135,25 @@
         <v>5.5</v>
       </c>
       <c r="AN34">
-        <v>2.5</v>
+        <v>3</v>
       </c>
       <c r="AO34">
-        <v>0.75</v>
+        <v>0</v>
       </c>
       <c r="AP34">
-        <v>2.67</v>
+        <v>3</v>
       </c>
       <c r="AQ34">
-        <v>1.05</v>
+        <v>0.82</v>
       </c>
       <c r="AR34">
-        <v>1.82</v>
+        <v>2.27</v>
       </c>
       <c r="AS34">
-        <v>1.4</v>
+        <v>1.39</v>
       </c>
       <c r="AT34">
-        <v>3.22</v>
+        <v>3.66</v>
       </c>
       <c r="AU34">
         <v>7</v>
@@ -8341,25 +8341,25 @@
         <v>1.62</v>
       </c>
       <c r="AN35">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AO35">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="AP35">
-        <v>1.2</v>
+        <v>1.45</v>
       </c>
       <c r="AQ35">
-        <v>1.33</v>
+        <v>1.5</v>
       </c>
       <c r="AR35">
-        <v>1.78</v>
+        <v>1.93</v>
       </c>
       <c r="AS35">
-        <v>1.4</v>
+        <v>1.32</v>
       </c>
       <c r="AT35">
-        <v>3.18</v>
+        <v>3.25</v>
       </c>
       <c r="AU35">
         <v>4</v>
@@ -8547,25 +8547,25 @@
         <v>1.15</v>
       </c>
       <c r="AN36">
-        <v>1.75</v>
+        <v>2</v>
       </c>
       <c r="AO36">
         <v>3</v>
       </c>
       <c r="AP36">
-        <v>1.57</v>
+        <v>2</v>
       </c>
       <c r="AQ36">
-        <v>2.05</v>
+        <v>2</v>
       </c>
       <c r="AR36">
-        <v>1.38</v>
+        <v>1.54</v>
       </c>
       <c r="AS36">
         <v>2.07</v>
       </c>
       <c r="AT36">
-        <v>3.45</v>
+        <v>3.61</v>
       </c>
       <c r="AU36">
         <v>5</v>
@@ -8753,25 +8753,25 @@
         <v>1.71</v>
       </c>
       <c r="AN37">
-        <v>1.75</v>
+        <v>3</v>
       </c>
       <c r="AO37">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="AP37">
-        <v>1.38</v>
+        <v>1.7</v>
       </c>
       <c r="AQ37">
-        <v>1.48</v>
+        <v>1.2</v>
       </c>
       <c r="AR37">
-        <v>1.23</v>
+        <v>1.25</v>
       </c>
       <c r="AS37">
-        <v>1.63</v>
+        <v>1.56</v>
       </c>
       <c r="AT37">
-        <v>2.86</v>
+        <v>2.81</v>
       </c>
       <c r="AU37">
         <v>5</v>
@@ -8959,25 +8959,25 @@
         <v>2.88</v>
       </c>
       <c r="AN38">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="AO38">
-        <v>0.75</v>
+        <v>1.5</v>
       </c>
       <c r="AP38">
-        <v>1.14</v>
+        <v>1.3</v>
       </c>
       <c r="AQ38">
-        <v>0.71</v>
+        <v>0.55</v>
       </c>
       <c r="AR38">
-        <v>1.51</v>
+        <v>1.34</v>
       </c>
       <c r="AS38">
-        <v>1.08</v>
+        <v>1</v>
       </c>
       <c r="AT38">
-        <v>2.59</v>
+        <v>2.34</v>
       </c>
       <c r="AU38">
         <v>6</v>
@@ -9168,19 +9168,19 @@
         <v>0</v>
       </c>
       <c r="AO39">
-        <v>2.5</v>
+        <v>2</v>
       </c>
       <c r="AP39">
-        <v>0.19</v>
+        <v>0.27</v>
       </c>
       <c r="AQ39">
-        <v>2.19</v>
+        <v>1.7</v>
       </c>
       <c r="AR39">
-        <v>1.16</v>
+        <v>1.46</v>
       </c>
       <c r="AS39">
-        <v>1.55</v>
+        <v>1.25</v>
       </c>
       <c r="AT39">
         <v>2.71</v>
@@ -9371,25 +9371,25 @@
         <v>1.53</v>
       </c>
       <c r="AN40">
-        <v>1.25</v>
+        <v>1</v>
       </c>
       <c r="AO40">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AP40">
-        <v>1.19</v>
+        <v>1.4</v>
       </c>
       <c r="AQ40">
-        <v>2</v>
+        <v>1.64</v>
       </c>
       <c r="AR40">
         <v>1.19</v>
       </c>
       <c r="AS40">
-        <v>1.82</v>
+        <v>1.71</v>
       </c>
       <c r="AT40">
-        <v>3.01</v>
+        <v>2.9</v>
       </c>
       <c r="AU40">
         <v>6</v>
@@ -9577,25 +9577,25 @@
         <v>1.88</v>
       </c>
       <c r="AN41">
-        <v>1.4</v>
+        <v>1.5</v>
       </c>
       <c r="AO41">
-        <v>1.4</v>
+        <v>1.5</v>
       </c>
       <c r="AP41">
-        <v>1.33</v>
+        <v>1.18</v>
       </c>
       <c r="AQ41">
-        <v>1.57</v>
+        <v>1.1</v>
       </c>
       <c r="AR41">
-        <v>1.45</v>
+        <v>1.49</v>
       </c>
       <c r="AS41">
-        <v>1.4</v>
+        <v>1.21</v>
       </c>
       <c r="AT41">
-        <v>2.85</v>
+        <v>2.7</v>
       </c>
       <c r="AU41">
         <v>6</v>
@@ -9783,25 +9783,25 @@
         <v>1.75</v>
       </c>
       <c r="AN42">
-        <v>0.6</v>
+        <v>1.5</v>
       </c>
       <c r="AO42">
-        <v>0.75</v>
+        <v>1.5</v>
       </c>
       <c r="AP42">
-        <v>1.05</v>
+        <v>1.3</v>
       </c>
       <c r="AQ42">
-        <v>1.2</v>
+        <v>0.89</v>
       </c>
       <c r="AR42">
-        <v>1.3</v>
+        <v>1.41</v>
       </c>
       <c r="AS42">
-        <v>1.74</v>
+        <v>1.7</v>
       </c>
       <c r="AT42">
-        <v>3.04</v>
+        <v>3.11</v>
       </c>
       <c r="AU42">
         <v>3</v>
@@ -9992,22 +9992,22 @@
         <v>3</v>
       </c>
       <c r="AO43">
-        <v>1.6</v>
+        <v>1.5</v>
       </c>
       <c r="AP43">
-        <v>2.05</v>
+        <v>2.09</v>
       </c>
       <c r="AQ43">
-        <v>1.19</v>
+        <v>1</v>
       </c>
       <c r="AR43">
         <v>2.07</v>
       </c>
       <c r="AS43">
-        <v>1.22</v>
+        <v>1.2</v>
       </c>
       <c r="AT43">
-        <v>3.29</v>
+        <v>3.27</v>
       </c>
       <c r="AU43">
         <v>8</v>
@@ -10195,25 +10195,25 @@
         <v>1.35</v>
       </c>
       <c r="AN44">
+        <v>0</v>
+      </c>
+      <c r="AO44">
+        <v>0</v>
+      </c>
+      <c r="AP44">
+        <v>0.9</v>
+      </c>
+      <c r="AQ44">
+        <v>1</v>
+      </c>
+      <c r="AR44">
+        <v>1.16</v>
+      </c>
+      <c r="AS44">
         <v>0.6</v>
       </c>
-      <c r="AO44">
-        <v>1.8</v>
-      </c>
-      <c r="AP44">
-        <v>0.71</v>
-      </c>
-      <c r="AQ44">
-        <v>1.33</v>
-      </c>
-      <c r="AR44">
-        <v>1.04</v>
-      </c>
-      <c r="AS44">
-        <v>0.98</v>
-      </c>
       <c r="AT44">
-        <v>2.02</v>
+        <v>1.76</v>
       </c>
       <c r="AU44">
         <v>6</v>
@@ -10401,25 +10401,25 @@
         <v>1.84</v>
       </c>
       <c r="AN45">
+        <v>3</v>
+      </c>
+      <c r="AO45">
         <v>1.5</v>
       </c>
-      <c r="AO45">
-        <v>1.4</v>
-      </c>
       <c r="AP45">
-        <v>2</v>
+        <v>2.4</v>
       </c>
       <c r="AQ45">
-        <v>1.14</v>
+        <v>1</v>
       </c>
       <c r="AR45">
-        <v>1.75</v>
+        <v>1.87</v>
       </c>
       <c r="AS45">
-        <v>1.47</v>
+        <v>1.68</v>
       </c>
       <c r="AT45">
-        <v>3.22</v>
+        <v>3.55</v>
       </c>
       <c r="AU45">
         <v>8</v>
@@ -10607,25 +10607,25 @@
         <v>1.67</v>
       </c>
       <c r="AN46">
-        <v>0.6</v>
+        <v>1</v>
       </c>
       <c r="AO46">
         <v>0</v>
       </c>
       <c r="AP46">
-        <v>0.65</v>
+        <v>1</v>
       </c>
       <c r="AQ46">
-        <v>0.19</v>
+        <v>0.1</v>
       </c>
       <c r="AR46">
         <v>0.97</v>
       </c>
       <c r="AS46">
-        <v>1.15</v>
+        <v>0.86</v>
       </c>
       <c r="AT46">
-        <v>2.12</v>
+        <v>1.83</v>
       </c>
       <c r="AU46">
         <v>6</v>
@@ -10813,25 +10813,25 @@
         <v>1.3</v>
       </c>
       <c r="AN47">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="AO47">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AP47">
-        <v>1.2</v>
+        <v>1.45</v>
       </c>
       <c r="AQ47">
-        <v>2</v>
+        <v>1.64</v>
       </c>
       <c r="AR47">
-        <v>1.67</v>
+        <v>1.77</v>
       </c>
       <c r="AS47">
-        <v>1.74</v>
+        <v>1.63</v>
       </c>
       <c r="AT47">
-        <v>3.41</v>
+        <v>3.4</v>
       </c>
       <c r="AU47">
         <v>3</v>
@@ -11022,22 +11022,22 @@
         <v>0</v>
       </c>
       <c r="AO48">
-        <v>1.17</v>
+        <v>1.33</v>
       </c>
       <c r="AP48">
-        <v>0.19</v>
+        <v>0.27</v>
       </c>
       <c r="AQ48">
-        <v>1.33</v>
+        <v>1.5</v>
       </c>
       <c r="AR48">
-        <v>1.17</v>
+        <v>1.34</v>
       </c>
       <c r="AS48">
-        <v>1.55</v>
+        <v>1.42</v>
       </c>
       <c r="AT48">
-        <v>2.72</v>
+        <v>2.76</v>
       </c>
       <c r="AU48">
         <v>6</v>
@@ -11225,25 +11225,25 @@
         <v>1.73</v>
       </c>
       <c r="AN49">
-        <v>1.5</v>
+        <v>1.67</v>
       </c>
       <c r="AO49">
-        <v>1.67</v>
+        <v>2</v>
       </c>
       <c r="AP49">
-        <v>1.19</v>
+        <v>1.4</v>
       </c>
       <c r="AQ49">
-        <v>1.57</v>
+        <v>1.1</v>
       </c>
       <c r="AR49">
-        <v>1.18</v>
+        <v>1.24</v>
       </c>
       <c r="AS49">
-        <v>1.37</v>
+        <v>1.21</v>
       </c>
       <c r="AT49">
-        <v>2.55</v>
+        <v>2.45</v>
       </c>
       <c r="AU49">
         <v>0</v>
@@ -11431,25 +11431,25 @@
         <v>1.15</v>
       </c>
       <c r="AN50">
-        <v>1.5</v>
+        <v>3</v>
       </c>
       <c r="AO50">
-        <v>2.67</v>
+        <v>3</v>
       </c>
       <c r="AP50">
-        <v>1.33</v>
+        <v>1.7</v>
       </c>
       <c r="AQ50">
-        <v>2.05</v>
+        <v>2</v>
       </c>
       <c r="AR50">
-        <v>1.07</v>
+        <v>1.24</v>
       </c>
       <c r="AS50">
-        <v>2.06</v>
+        <v>2.07</v>
       </c>
       <c r="AT50">
-        <v>3.13</v>
+        <v>3.31</v>
       </c>
       <c r="AU50">
         <v>3</v>
@@ -11637,25 +11637,25 @@
         <v>1.82</v>
       </c>
       <c r="AN51">
-        <v>1.17</v>
+        <v>0.33</v>
       </c>
       <c r="AO51">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AP51">
-        <v>1.2</v>
+        <v>1.45</v>
       </c>
       <c r="AQ51">
-        <v>0.65</v>
+        <v>0.3</v>
       </c>
       <c r="AR51">
-        <v>1.68</v>
+        <v>1.76</v>
       </c>
       <c r="AS51">
-        <v>1.04</v>
+        <v>0.97</v>
       </c>
       <c r="AT51">
-        <v>2.72</v>
+        <v>2.73</v>
       </c>
       <c r="AU51">
         <v>7</v>
@@ -11843,25 +11843,25 @@
         <v>1.52</v>
       </c>
       <c r="AN52">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AO52">
-        <v>1.67</v>
+        <v>0.33</v>
       </c>
       <c r="AP52">
-        <v>1.38</v>
+        <v>1.7</v>
       </c>
       <c r="AQ52">
-        <v>2</v>
+        <v>1.64</v>
       </c>
       <c r="AR52">
-        <v>1.38</v>
+        <v>1.61</v>
       </c>
       <c r="AS52">
-        <v>1.58</v>
+        <v>1.34</v>
       </c>
       <c r="AT52">
-        <v>2.96</v>
+        <v>2.95</v>
       </c>
       <c r="AU52">
         <v>7</v>
@@ -12049,25 +12049,25 @@
         <v>7.5</v>
       </c>
       <c r="AN53">
-        <v>2.6</v>
+        <v>3</v>
       </c>
       <c r="AO53">
         <v>1</v>
       </c>
       <c r="AP53">
-        <v>2.67</v>
+        <v>3</v>
       </c>
       <c r="AQ53">
-        <v>0.71</v>
+        <v>0.55</v>
       </c>
       <c r="AR53">
-        <v>1.95</v>
+        <v>2.35</v>
       </c>
       <c r="AS53">
-        <v>1.1</v>
+        <v>0.96</v>
       </c>
       <c r="AT53">
-        <v>3.05</v>
+        <v>3.31</v>
       </c>
       <c r="AU53">
         <v>10</v>
@@ -12255,25 +12255,25 @@
         <v>1.56</v>
       </c>
       <c r="AN54">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="AO54">
+        <v>0</v>
+      </c>
+      <c r="AP54">
+        <v>1.3</v>
+      </c>
+      <c r="AQ54">
         <v>1.2</v>
       </c>
-      <c r="AP54">
-        <v>1.05</v>
-      </c>
-      <c r="AQ54">
-        <v>1.48</v>
-      </c>
       <c r="AR54">
-        <v>1.32</v>
+        <v>1.4</v>
       </c>
       <c r="AS54">
-        <v>1.55</v>
+        <v>1.44</v>
       </c>
       <c r="AT54">
-        <v>2.87</v>
+        <v>2.84</v>
       </c>
       <c r="AU54">
         <v>3</v>
@@ -12461,25 +12461,25 @@
         <v>1.28</v>
       </c>
       <c r="AN55">
-        <v>1.17</v>
+        <v>1.33</v>
       </c>
       <c r="AO55">
-        <v>2.6</v>
+        <v>2.33</v>
       </c>
       <c r="AP55">
-        <v>1.14</v>
+        <v>1.3</v>
       </c>
       <c r="AQ55">
-        <v>2.19</v>
+        <v>1.7</v>
       </c>
       <c r="AR55">
-        <v>1.44</v>
+        <v>1.32</v>
       </c>
       <c r="AS55">
-        <v>1.53</v>
+        <v>1.32</v>
       </c>
       <c r="AT55">
-        <v>2.97</v>
+        <v>2.64</v>
       </c>
       <c r="AU55">
         <v>7</v>
@@ -12667,25 +12667,25 @@
         <v>2.75</v>
       </c>
       <c r="AN56">
-        <v>2.33</v>
+        <v>3</v>
       </c>
       <c r="AO56">
-        <v>1.83</v>
+        <v>1.33</v>
       </c>
       <c r="AP56">
-        <v>2.19</v>
+        <v>2.64</v>
       </c>
       <c r="AQ56">
-        <v>1.38</v>
+        <v>1.09</v>
       </c>
       <c r="AR56">
-        <v>1.52</v>
+        <v>1.85</v>
       </c>
       <c r="AS56">
-        <v>1.48</v>
+        <v>1.22</v>
       </c>
       <c r="AT56">
-        <v>3</v>
+        <v>3.07</v>
       </c>
       <c r="AU56">
         <v>7</v>
@@ -12873,25 +12873,25 @@
         <v>1.14</v>
       </c>
       <c r="AN57">
-        <v>1.5</v>
+        <v>3</v>
       </c>
       <c r="AO57">
-        <v>2.67</v>
+        <v>2</v>
       </c>
       <c r="AP57">
-        <v>1.48</v>
+        <v>1.73</v>
       </c>
       <c r="AQ57">
-        <v>2.67</v>
+        <v>2.36</v>
       </c>
       <c r="AR57">
-        <v>1.57</v>
+        <v>1.7</v>
       </c>
       <c r="AS57">
-        <v>2.01</v>
+        <v>1.36</v>
       </c>
       <c r="AT57">
-        <v>3.58</v>
+        <v>3.06</v>
       </c>
       <c r="AU57">
         <v>4</v>
@@ -13079,25 +13079,25 @@
         <v>1.57</v>
       </c>
       <c r="AN58">
-        <v>1.29</v>
+        <v>2.25</v>
       </c>
       <c r="AO58">
-        <v>1.43</v>
+        <v>1.33</v>
       </c>
       <c r="AP58">
-        <v>1.33</v>
+        <v>1.7</v>
       </c>
       <c r="AQ58">
-        <v>1.19</v>
+        <v>1</v>
       </c>
       <c r="AR58">
-        <v>1.14</v>
+        <v>1.32</v>
       </c>
       <c r="AS58">
-        <v>1.14</v>
+        <v>1.12</v>
       </c>
       <c r="AT58">
-        <v>2.28</v>
+        <v>2.44</v>
       </c>
       <c r="AU58">
         <v>4</v>
@@ -13285,25 +13285,25 @@
         <v>1.32</v>
       </c>
       <c r="AN59">
-        <v>0.43</v>
+        <v>0.75</v>
       </c>
       <c r="AO59">
-        <v>1.57</v>
+        <v>0.5</v>
       </c>
       <c r="AP59">
-        <v>1.05</v>
+        <v>1.3</v>
       </c>
       <c r="AQ59">
-        <v>2</v>
+        <v>1.64</v>
       </c>
       <c r="AR59">
-        <v>1.35</v>
+        <v>1.44</v>
       </c>
       <c r="AS59">
-        <v>1.62</v>
+        <v>1.47</v>
       </c>
       <c r="AT59">
-        <v>2.97</v>
+        <v>2.91</v>
       </c>
       <c r="AU59">
         <v>8</v>
@@ -13491,22 +13491,22 @@
         <v>1.49</v>
       </c>
       <c r="AN60">
-        <v>1.14</v>
+        <v>0.5</v>
       </c>
       <c r="AO60">
-        <v>1.57</v>
+        <v>1.75</v>
       </c>
       <c r="AP60">
-        <v>1.2</v>
+        <v>1.45</v>
       </c>
       <c r="AQ60">
-        <v>1.57</v>
+        <v>1.1</v>
       </c>
       <c r="AR60">
-        <v>1.73</v>
+        <v>1.83</v>
       </c>
       <c r="AS60">
-        <v>1.39</v>
+        <v>1.29</v>
       </c>
       <c r="AT60">
         <v>3.12</v>
@@ -13697,25 +13697,25 @@
         <v>2.55</v>
       </c>
       <c r="AN61">
-        <v>2.71</v>
+        <v>3</v>
       </c>
       <c r="AO61">
-        <v>2.43</v>
+        <v>2</v>
       </c>
       <c r="AP61">
-        <v>2.67</v>
+        <v>3</v>
       </c>
       <c r="AQ61">
-        <v>2.19</v>
+        <v>1.7</v>
       </c>
       <c r="AR61">
-        <v>1.98</v>
+        <v>2.33</v>
       </c>
       <c r="AS61">
-        <v>1.56</v>
+        <v>1.35</v>
       </c>
       <c r="AT61">
-        <v>3.54</v>
+        <v>3.68</v>
       </c>
       <c r="AU61">
         <v>12</v>
@@ -13903,25 +13903,25 @@
         <v>2.85</v>
       </c>
       <c r="AN62">
-        <v>1.29</v>
+        <v>2</v>
       </c>
       <c r="AO62">
-        <v>0.86</v>
+        <v>0.75</v>
       </c>
       <c r="AP62">
-        <v>1.48</v>
+        <v>1.73</v>
       </c>
       <c r="AQ62">
-        <v>0.71</v>
+        <v>0.55</v>
       </c>
       <c r="AR62">
-        <v>1.47</v>
+        <v>1.42</v>
       </c>
       <c r="AS62">
-        <v>1.13</v>
+        <v>1.06</v>
       </c>
       <c r="AT62">
-        <v>2.6</v>
+        <v>2.48</v>
       </c>
       <c r="AU62">
         <v>7</v>
@@ -14109,25 +14109,25 @@
         <v>1.04</v>
       </c>
       <c r="AN63">
-        <v>0.14</v>
+        <v>0.25</v>
       </c>
       <c r="AO63">
-        <v>2.71</v>
+        <v>3</v>
       </c>
       <c r="AP63">
-        <v>0.19</v>
+        <v>0.27</v>
       </c>
       <c r="AQ63">
-        <v>2.05</v>
+        <v>2</v>
       </c>
       <c r="AR63">
-        <v>1.21</v>
+        <v>1.37</v>
       </c>
       <c r="AS63">
-        <v>1.95</v>
+        <v>1.88</v>
       </c>
       <c r="AT63">
-        <v>3.16</v>
+        <v>3.25</v>
       </c>
       <c r="AU63">
         <v>4</v>
@@ -14315,25 +14315,25 @@
         <v>2.3</v>
       </c>
       <c r="AN64">
-        <v>1.57</v>
+        <v>2.33</v>
       </c>
       <c r="AO64">
-        <v>1</v>
+        <v>0.33</v>
       </c>
       <c r="AP64">
-        <v>1.38</v>
+        <v>1.7</v>
       </c>
       <c r="AQ64">
-        <v>0.65</v>
+        <v>0.3</v>
       </c>
       <c r="AR64">
-        <v>1.48</v>
+        <v>1.75</v>
       </c>
       <c r="AS64">
-        <v>0.99</v>
+        <v>0.87</v>
       </c>
       <c r="AT64">
-        <v>2.47</v>
+        <v>2.62</v>
       </c>
       <c r="AU64">
         <v>6</v>
@@ -14521,25 +14521,25 @@
         <v>2.02</v>
       </c>
       <c r="AN65">
-        <v>1.14</v>
+        <v>1.25</v>
       </c>
       <c r="AO65">
-        <v>1.14</v>
+        <v>1.25</v>
       </c>
       <c r="AP65">
-        <v>1.14</v>
+        <v>1.3</v>
       </c>
       <c r="AQ65">
-        <v>1.33</v>
+        <v>1.5</v>
       </c>
       <c r="AR65">
-        <v>1.47</v>
+        <v>1.42</v>
       </c>
       <c r="AS65">
-        <v>1.58</v>
+        <v>1.5</v>
       </c>
       <c r="AT65">
-        <v>3.05</v>
+        <v>2.92</v>
       </c>
       <c r="AU65">
         <v>7</v>
@@ -14727,25 +14727,25 @@
         <v>4.4</v>
       </c>
       <c r="AN66">
-        <v>2.75</v>
+        <v>2.33</v>
       </c>
       <c r="AO66">
-        <v>1.75</v>
+        <v>1</v>
       </c>
       <c r="AP66">
+        <v>2.09</v>
+      </c>
+      <c r="AQ66">
+        <v>1.09</v>
+      </c>
+      <c r="AR66">
         <v>2.05</v>
       </c>
-      <c r="AQ66">
-        <v>1.38</v>
-      </c>
-      <c r="AR66">
-        <v>2</v>
-      </c>
       <c r="AS66">
-        <v>1.47</v>
+        <v>1.28</v>
       </c>
       <c r="AT66">
-        <v>3.47</v>
+        <v>3.33</v>
       </c>
       <c r="AU66">
         <v>6</v>
@@ -14933,25 +14933,25 @@
         <v>1.27</v>
       </c>
       <c r="AN67">
-        <v>0.88</v>
+        <v>1.5</v>
       </c>
       <c r="AO67">
-        <v>1.13</v>
+        <v>1</v>
       </c>
       <c r="AP67">
-        <v>0.65</v>
+        <v>1</v>
       </c>
       <c r="AQ67">
-        <v>1.14</v>
+        <v>1</v>
       </c>
       <c r="AR67">
-        <v>0.99</v>
+        <v>1.08</v>
       </c>
       <c r="AS67">
-        <v>1.49</v>
+        <v>1.55</v>
       </c>
       <c r="AT67">
-        <v>2.48</v>
+        <v>2.63</v>
       </c>
       <c r="AU67">
         <v>4</v>
@@ -15139,25 +15139,25 @@
         <v>1.48</v>
       </c>
       <c r="AN68">
-        <v>0.88</v>
+        <v>1</v>
       </c>
       <c r="AO68">
-        <v>0.38</v>
+        <v>0</v>
       </c>
       <c r="AP68">
-        <v>0.71</v>
+        <v>0.9</v>
       </c>
       <c r="AQ68">
-        <v>1.05</v>
+        <v>0.82</v>
       </c>
       <c r="AR68">
-        <v>1.11</v>
+        <v>1.23</v>
       </c>
       <c r="AS68">
-        <v>1.39</v>
+        <v>1.24</v>
       </c>
       <c r="AT68">
-        <v>2.5</v>
+        <v>2.47</v>
       </c>
       <c r="AU68">
         <v>3</v>
@@ -15345,25 +15345,25 @@
         <v>1.95</v>
       </c>
       <c r="AN69">
-        <v>1.25</v>
+        <v>1.5</v>
       </c>
       <c r="AO69">
-        <v>1.38</v>
+        <v>2</v>
       </c>
       <c r="AP69">
-        <v>1.19</v>
+        <v>1.4</v>
       </c>
       <c r="AQ69">
-        <v>1.2</v>
+        <v>0.89</v>
       </c>
       <c r="AR69">
-        <v>1.07</v>
+        <v>1.16</v>
       </c>
       <c r="AS69">
-        <v>1.74</v>
+        <v>1.61</v>
       </c>
       <c r="AT69">
-        <v>2.81</v>
+        <v>2.77</v>
       </c>
       <c r="AU69">
         <v>3</v>
@@ -15551,25 +15551,25 @@
         <v>1.55</v>
       </c>
       <c r="AN70">
-        <v>1.38</v>
+        <v>1.33</v>
       </c>
       <c r="AO70">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="AP70">
-        <v>1.57</v>
+        <v>2</v>
       </c>
       <c r="AQ70">
-        <v>1.33</v>
+        <v>1</v>
       </c>
       <c r="AR70">
-        <v>1.47</v>
+        <v>1.53</v>
       </c>
       <c r="AS70">
-        <v>1.15</v>
+        <v>0.89</v>
       </c>
       <c r="AT70">
-        <v>2.62</v>
+        <v>2.42</v>
       </c>
       <c r="AU70">
         <v>8</v>
@@ -15757,25 +15757,25 @@
         <v>3.3</v>
       </c>
       <c r="AN71">
-        <v>1.75</v>
+        <v>3</v>
       </c>
       <c r="AO71">
-        <v>0.13</v>
+        <v>0</v>
       </c>
       <c r="AP71">
-        <v>2</v>
+        <v>2.4</v>
       </c>
       <c r="AQ71">
-        <v>0.19</v>
+        <v>0.1</v>
       </c>
       <c r="AR71">
-        <v>1.6</v>
+        <v>1.82</v>
       </c>
       <c r="AS71">
-        <v>1.18</v>
+        <v>1</v>
       </c>
       <c r="AT71">
-        <v>2.78</v>
+        <v>2.82</v>
       </c>
       <c r="AU71">
         <v>7</v>
@@ -15963,25 +15963,25 @@
         <v>2.7</v>
       </c>
       <c r="AN72">
-        <v>2.13</v>
+        <v>3</v>
       </c>
       <c r="AO72">
-        <v>1.25</v>
+        <v>0.75</v>
       </c>
       <c r="AP72">
-        <v>2.19</v>
+        <v>2.64</v>
       </c>
       <c r="AQ72">
-        <v>1.48</v>
+        <v>1.2</v>
       </c>
       <c r="AR72">
+        <v>1.84</v>
+      </c>
+      <c r="AS72">
         <v>1.5</v>
       </c>
-      <c r="AS72">
-        <v>1.49</v>
-      </c>
       <c r="AT72">
-        <v>2.99</v>
+        <v>3.34</v>
       </c>
       <c r="AU72">
         <v>7</v>
@@ -16169,25 +16169,25 @@
         <v>1.03</v>
       </c>
       <c r="AN73">
-        <v>1.13</v>
+        <v>1</v>
       </c>
       <c r="AO73">
-        <v>2.75</v>
+        <v>2.33</v>
       </c>
       <c r="AP73">
-        <v>1.33</v>
+        <v>1.18</v>
       </c>
       <c r="AQ73">
-        <v>2.67</v>
+        <v>2.36</v>
       </c>
       <c r="AR73">
-        <v>1.53</v>
+        <v>1.68</v>
       </c>
       <c r="AS73">
-        <v>2.08</v>
+        <v>1.51</v>
       </c>
       <c r="AT73">
-        <v>3.61</v>
+        <v>3.19</v>
       </c>
       <c r="AU73">
         <v>0</v>
@@ -16375,25 +16375,25 @@
         <v>1.51</v>
       </c>
       <c r="AN74">
-        <v>1.22</v>
+        <v>1</v>
       </c>
       <c r="AO74">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="AP74">
-        <v>1.2</v>
+        <v>1.45</v>
       </c>
       <c r="AQ74">
-        <v>1.33</v>
+        <v>1</v>
       </c>
       <c r="AR74">
-        <v>1.76</v>
+        <v>1.81</v>
       </c>
       <c r="AS74">
-        <v>1.17</v>
+        <v>1</v>
       </c>
       <c r="AT74">
-        <v>2.93</v>
+        <v>2.81</v>
       </c>
       <c r="AU74">
         <v>6</v>
@@ -16581,25 +16581,25 @@
         <v>1.98</v>
       </c>
       <c r="AN75">
-        <v>0.67</v>
+        <v>0.6</v>
       </c>
       <c r="AO75">
-        <v>0.78</v>
+        <v>0.25</v>
       </c>
       <c r="AP75">
-        <v>1.05</v>
+        <v>1.3</v>
       </c>
       <c r="AQ75">
-        <v>0.65</v>
+        <v>0.3</v>
       </c>
       <c r="AR75">
-        <v>1.43</v>
+        <v>1.49</v>
       </c>
       <c r="AS75">
-        <v>1.03</v>
+        <v>0.9</v>
       </c>
       <c r="AT75">
-        <v>2.46</v>
+        <v>2.39</v>
       </c>
       <c r="AU75">
         <v>5</v>
@@ -16787,25 +16787,25 @@
         <v>1.34</v>
       </c>
       <c r="AN76">
-        <v>0.11</v>
+        <v>0.2</v>
       </c>
       <c r="AO76">
-        <v>1.44</v>
+        <v>1</v>
       </c>
       <c r="AP76">
-        <v>0.19</v>
+        <v>0.27</v>
       </c>
       <c r="AQ76">
-        <v>1.19</v>
+        <v>1</v>
       </c>
       <c r="AR76">
-        <v>1.18</v>
+        <v>1.29</v>
       </c>
       <c r="AS76">
-        <v>1.06</v>
+        <v>0.99</v>
       </c>
       <c r="AT76">
-        <v>2.24</v>
+        <v>2.28</v>
       </c>
       <c r="AU76">
         <v>3</v>
@@ -16993,25 +16993,25 @@
         <v>1.85</v>
       </c>
       <c r="AN77">
-        <v>1.33</v>
+        <v>1.2</v>
       </c>
       <c r="AO77">
-        <v>1.56</v>
+        <v>1.4</v>
       </c>
       <c r="AP77">
-        <v>1.14</v>
+        <v>1.3</v>
       </c>
       <c r="AQ77">
-        <v>1.57</v>
+        <v>1.1</v>
       </c>
       <c r="AR77">
-        <v>1.59</v>
+        <v>1.45</v>
       </c>
       <c r="AS77">
-        <v>1.57</v>
+        <v>1.44</v>
       </c>
       <c r="AT77">
-        <v>3.16</v>
+        <v>2.89</v>
       </c>
       <c r="AU77">
         <v>3</v>
@@ -17199,25 +17199,25 @@
         <v>4.5</v>
       </c>
       <c r="AN78">
-        <v>2</v>
+        <v>2.5</v>
       </c>
       <c r="AO78">
-        <v>0.78</v>
+        <v>0.8</v>
       </c>
       <c r="AP78">
-        <v>2.19</v>
+        <v>2.64</v>
       </c>
       <c r="AQ78">
-        <v>0.71</v>
+        <v>0.55</v>
       </c>
       <c r="AR78">
-        <v>1.52</v>
+        <v>1.78</v>
       </c>
       <c r="AS78">
-        <v>1.07</v>
+        <v>1.03</v>
       </c>
       <c r="AT78">
-        <v>2.59</v>
+        <v>2.81</v>
       </c>
       <c r="AU78">
         <v>8</v>
@@ -17405,25 +17405,25 @@
         <v>1.48</v>
       </c>
       <c r="AN79">
-        <v>1.22</v>
+        <v>1.75</v>
       </c>
       <c r="AO79">
-        <v>1.89</v>
+        <v>1</v>
       </c>
       <c r="AP79">
-        <v>1.48</v>
+        <v>1.73</v>
       </c>
       <c r="AQ79">
-        <v>2</v>
+        <v>1.64</v>
       </c>
       <c r="AR79">
-        <v>1.37</v>
+        <v>1.49</v>
       </c>
       <c r="AS79">
-        <v>1.62</v>
+        <v>1.47</v>
       </c>
       <c r="AT79">
-        <v>2.99</v>
+        <v>2.96</v>
       </c>
       <c r="AU79">
         <v>4</v>
@@ -17611,25 +17611,25 @@
         <v>1.9</v>
       </c>
       <c r="AN80">
-        <v>1.89</v>
+        <v>2.5</v>
       </c>
       <c r="AO80">
-        <v>1</v>
+        <v>1.2</v>
       </c>
       <c r="AP80">
-        <v>1.38</v>
+        <v>1.7</v>
       </c>
       <c r="AQ80">
-        <v>1.33</v>
+        <v>1.5</v>
       </c>
       <c r="AR80">
-        <v>1.41</v>
+        <v>1.66</v>
       </c>
       <c r="AS80">
-        <v>1.43</v>
+        <v>1.44</v>
       </c>
       <c r="AT80">
-        <v>2.84</v>
+        <v>3.1</v>
       </c>
       <c r="AU80">
         <v>5</v>
@@ -17817,25 +17817,25 @@
         <v>1.89</v>
       </c>
       <c r="AN81">
-        <v>2.78</v>
+        <v>3</v>
       </c>
       <c r="AO81">
-        <v>2.44</v>
+        <v>3</v>
       </c>
       <c r="AP81">
-        <v>2.67</v>
+        <v>3</v>
       </c>
       <c r="AQ81">
-        <v>2.05</v>
+        <v>2</v>
       </c>
       <c r="AR81">
-        <v>2.1</v>
+        <v>2.43</v>
       </c>
       <c r="AS81">
-        <v>1.99</v>
+        <v>1.97</v>
       </c>
       <c r="AT81">
-        <v>4.09</v>
+        <v>4.4</v>
       </c>
       <c r="AU81">
         <v>6</v>
@@ -18023,25 +18023,25 @@
         <v>1.66</v>
       </c>
       <c r="AN82">
-        <v>1.3</v>
+        <v>2.4</v>
       </c>
       <c r="AO82">
+        <v>1.4</v>
+      </c>
+      <c r="AP82">
         <v>1.7</v>
       </c>
-      <c r="AP82">
-        <v>1.33</v>
-      </c>
       <c r="AQ82">
-        <v>1.38</v>
+        <v>1.09</v>
       </c>
       <c r="AR82">
+        <v>1.31</v>
+      </c>
+      <c r="AS82">
         <v>1.21</v>
       </c>
-      <c r="AS82">
-        <v>1.41</v>
-      </c>
       <c r="AT82">
-        <v>2.62</v>
+        <v>2.52</v>
       </c>
       <c r="AU82">
         <v>5</v>
@@ -18229,25 +18229,25 @@
         <v>1.78</v>
       </c>
       <c r="AN83">
-        <v>0.8</v>
+        <v>1.2</v>
       </c>
       <c r="AO83">
-        <v>0.7</v>
+        <v>0.67</v>
       </c>
       <c r="AP83">
-        <v>0.65</v>
+        <v>1</v>
       </c>
       <c r="AQ83">
-        <v>0.71</v>
+        <v>0.55</v>
       </c>
       <c r="AR83">
-        <v>1.01</v>
+        <v>1.14</v>
       </c>
       <c r="AS83">
-        <v>1.08</v>
+        <v>1.06</v>
       </c>
       <c r="AT83">
-        <v>2.09</v>
+        <v>2.2</v>
       </c>
       <c r="AU83">
         <v>7</v>
@@ -18435,25 +18435,25 @@
         <v>1.4</v>
       </c>
       <c r="AN84">
-        <v>1.8</v>
+        <v>3</v>
       </c>
       <c r="AO84">
-        <v>2.1</v>
+        <v>1.6</v>
       </c>
       <c r="AP84">
-        <v>2</v>
+        <v>2.4</v>
       </c>
       <c r="AQ84">
-        <v>2.19</v>
+        <v>1.7</v>
       </c>
       <c r="AR84">
-        <v>1.66</v>
+        <v>1.81</v>
       </c>
       <c r="AS84">
-        <v>1.56</v>
+        <v>1.3</v>
       </c>
       <c r="AT84">
-        <v>3.22</v>
+        <v>3.11</v>
       </c>
       <c r="AU84">
         <v>7</v>
@@ -18641,25 +18641,25 @@
         <v>3.75</v>
       </c>
       <c r="AN85">
-        <v>2.2</v>
+        <v>1.75</v>
       </c>
       <c r="AO85">
-        <v>1.2</v>
+        <v>1.5</v>
       </c>
       <c r="AP85">
-        <v>2.05</v>
+        <v>2.09</v>
       </c>
       <c r="AQ85">
-        <v>1.14</v>
+        <v>1</v>
       </c>
       <c r="AR85">
-        <v>1.91</v>
+        <v>2.02</v>
       </c>
       <c r="AS85">
-        <v>1.54</v>
+        <v>1.77</v>
       </c>
       <c r="AT85">
-        <v>3.45</v>
+        <v>3.79</v>
       </c>
       <c r="AU85">
         <v>5</v>
@@ -18847,25 +18847,25 @@
         <v>1.57</v>
       </c>
       <c r="AN86">
+        <v>0.75</v>
+      </c>
+      <c r="AO86">
+        <v>0.8</v>
+      </c>
+      <c r="AP86">
+        <v>1.18</v>
+      </c>
+      <c r="AQ86">
         <v>1.2</v>
       </c>
-      <c r="AO86">
-        <v>1.2</v>
-      </c>
-      <c r="AP86">
-        <v>1.33</v>
-      </c>
-      <c r="AQ86">
-        <v>1.48</v>
-      </c>
       <c r="AR86">
-        <v>1.44</v>
+        <v>1.41</v>
       </c>
       <c r="AS86">
-        <v>1.35</v>
+        <v>1.28</v>
       </c>
       <c r="AT86">
-        <v>2.79</v>
+        <v>2.69</v>
       </c>
       <c r="AU86">
         <v>8</v>
@@ -19053,25 +19053,25 @@
         <v>2.3</v>
       </c>
       <c r="AN87">
-        <v>1.2</v>
+        <v>1</v>
       </c>
       <c r="AO87">
+        <v>0</v>
+      </c>
+      <c r="AP87">
+        <v>1.45</v>
+      </c>
+      <c r="AQ87">
         <v>0.1</v>
       </c>
-      <c r="AP87">
-        <v>1.2</v>
-      </c>
-      <c r="AQ87">
-        <v>0.19</v>
-      </c>
       <c r="AR87">
-        <v>1.72</v>
+        <v>1.73</v>
       </c>
       <c r="AS87">
-        <v>1.21</v>
+        <v>1.04</v>
       </c>
       <c r="AT87">
-        <v>2.93</v>
+        <v>2.77</v>
       </c>
       <c r="AU87">
         <v>4</v>
@@ -19259,25 +19259,25 @@
         <v>1.85</v>
       </c>
       <c r="AN88">
-        <v>1.6</v>
+        <v>1.8</v>
       </c>
       <c r="AO88">
-        <v>0.7</v>
+        <v>0.75</v>
       </c>
       <c r="AP88">
-        <v>1.19</v>
+        <v>1.4</v>
       </c>
       <c r="AQ88">
-        <v>1.05</v>
+        <v>0.82</v>
       </c>
       <c r="AR88">
-        <v>1.1</v>
+        <v>1.12</v>
       </c>
       <c r="AS88">
-        <v>1.45</v>
+        <v>1.36</v>
       </c>
       <c r="AT88">
-        <v>2.55</v>
+        <v>2.48</v>
       </c>
       <c r="AU88">
         <v>3</v>
@@ -19465,25 +19465,25 @@
         <v>1.06</v>
       </c>
       <c r="AN89">
-        <v>1.7</v>
+        <v>1.75</v>
       </c>
       <c r="AO89">
-        <v>2.8</v>
+        <v>2.5</v>
       </c>
       <c r="AP89">
-        <v>1.57</v>
+        <v>2</v>
       </c>
       <c r="AQ89">
-        <v>2.67</v>
+        <v>2.36</v>
       </c>
       <c r="AR89">
-        <v>1.61</v>
+        <v>1.74</v>
       </c>
       <c r="AS89">
-        <v>2.06</v>
+        <v>1.69</v>
       </c>
       <c r="AT89">
-        <v>3.67</v>
+        <v>3.43</v>
       </c>
       <c r="AU89">
         <v>5</v>
@@ -19671,25 +19671,25 @@
         <v>1.96</v>
       </c>
       <c r="AN90">
-        <v>1.09</v>
+        <v>1</v>
       </c>
       <c r="AO90">
-        <v>1.45</v>
+        <v>1.4</v>
       </c>
       <c r="AP90">
-        <v>1.14</v>
+        <v>1.3</v>
       </c>
       <c r="AQ90">
-        <v>1.19</v>
+        <v>1</v>
       </c>
       <c r="AR90">
-        <v>1.48</v>
+        <v>1.39</v>
       </c>
       <c r="AS90">
-        <v>1.12</v>
+        <v>1.08</v>
       </c>
       <c r="AT90">
-        <v>2.6</v>
+        <v>2.47</v>
       </c>
       <c r="AU90">
         <v>8</v>
@@ -19877,25 +19877,25 @@
         <v>1.2</v>
       </c>
       <c r="AN91">
-        <v>0.64</v>
+        <v>0.75</v>
       </c>
       <c r="AO91">
+        <v>1</v>
+      </c>
+      <c r="AP91">
+        <v>0.9</v>
+      </c>
+      <c r="AQ91">
         <v>1.64</v>
       </c>
-      <c r="AP91">
-        <v>0.71</v>
-      </c>
-      <c r="AQ91">
-        <v>2</v>
-      </c>
       <c r="AR91">
-        <v>1.07</v>
+        <v>1.11</v>
       </c>
       <c r="AS91">
-        <v>1.7</v>
+        <v>1.55</v>
       </c>
       <c r="AT91">
-        <v>2.77</v>
+        <v>2.66</v>
       </c>
       <c r="AU91">
         <v>4</v>
@@ -20083,25 +20083,25 @@
         <v>1.32</v>
       </c>
       <c r="AN92">
-        <v>0.09</v>
+        <v>0.17</v>
       </c>
       <c r="AO92">
-        <v>1.27</v>
+        <v>0.2</v>
       </c>
       <c r="AP92">
-        <v>0.19</v>
+        <v>0.27</v>
       </c>
       <c r="AQ92">
+        <v>1</v>
+      </c>
+      <c r="AR92">
         <v>1.33</v>
       </c>
-      <c r="AR92">
-        <v>1.18</v>
-      </c>
       <c r="AS92">
-        <v>1.28</v>
+        <v>1.11</v>
       </c>
       <c r="AT92">
-        <v>2.46</v>
+        <v>2.44</v>
       </c>
       <c r="AU92">
         <v>7</v>
@@ -20289,25 +20289,25 @@
         <v>1.6</v>
       </c>
       <c r="AN93">
-        <v>1.64</v>
+        <v>2</v>
       </c>
       <c r="AO93">
-        <v>1.55</v>
+        <v>1.67</v>
       </c>
       <c r="AP93">
-        <v>1.38</v>
+        <v>1.7</v>
       </c>
       <c r="AQ93">
-        <v>1.57</v>
+        <v>1.1</v>
       </c>
       <c r="AR93">
-        <v>1.34</v>
+        <v>1.61</v>
       </c>
       <c r="AS93">
-        <v>1.59</v>
+        <v>1.53</v>
       </c>
       <c r="AT93">
-        <v>2.93</v>
+        <v>3.14</v>
       </c>
       <c r="AU93">
         <v>5</v>
@@ -20495,25 +20495,25 @@
         <v>1.55</v>
       </c>
       <c r="AN94">
-        <v>0.91</v>
+        <v>0.67</v>
       </c>
       <c r="AO94">
-        <v>1.18</v>
+        <v>1.5</v>
       </c>
       <c r="AP94">
-        <v>1.05</v>
+        <v>1.3</v>
       </c>
       <c r="AQ94">
-        <v>1.33</v>
+        <v>1.5</v>
       </c>
       <c r="AR94">
-        <v>1.4</v>
+        <v>1.52</v>
       </c>
       <c r="AS94">
-        <v>1.44</v>
+        <v>1.47</v>
       </c>
       <c r="AT94">
-        <v>2.84</v>
+        <v>2.99</v>
       </c>
       <c r="AU94">
         <v>6</v>
@@ -20701,25 +20701,25 @@
         <v>2.05</v>
       </c>
       <c r="AN95">
-        <v>1.18</v>
+        <v>1.6</v>
       </c>
       <c r="AO95">
-        <v>1.36</v>
+        <v>1.5</v>
       </c>
       <c r="AP95">
-        <v>1.48</v>
+        <v>1.73</v>
       </c>
       <c r="AQ95">
-        <v>1.2</v>
+        <v>0.89</v>
       </c>
       <c r="AR95">
-        <v>1.35</v>
+        <v>1.43</v>
       </c>
       <c r="AS95">
-        <v>1.68</v>
+        <v>1.69</v>
       </c>
       <c r="AT95">
-        <v>3.03</v>
+        <v>3.12</v>
       </c>
       <c r="AU95">
         <v>8</v>
@@ -20907,25 +20907,25 @@
         <v>7.5</v>
       </c>
       <c r="AN96">
-        <v>2.82</v>
+        <v>3</v>
       </c>
       <c r="AO96">
-        <v>1</v>
+        <v>0.4</v>
       </c>
       <c r="AP96">
-        <v>2.67</v>
+        <v>3</v>
       </c>
       <c r="AQ96">
-        <v>0.65</v>
+        <v>0.3</v>
       </c>
       <c r="AR96">
-        <v>2</v>
+        <v>2.31</v>
       </c>
       <c r="AS96">
-        <v>1.03</v>
+        <v>0.89</v>
       </c>
       <c r="AT96">
-        <v>3.03</v>
+        <v>3.2</v>
       </c>
       <c r="AU96">
         <v>7</v>
@@ -21113,25 +21113,25 @@
         <v>1.55</v>
       </c>
       <c r="AN97">
-        <v>2.18</v>
+        <v>2.6</v>
       </c>
       <c r="AO97">
-        <v>2.27</v>
+        <v>2.5</v>
       </c>
       <c r="AP97">
-        <v>2.19</v>
+        <v>2.64</v>
       </c>
       <c r="AQ97">
-        <v>2.05</v>
+        <v>2</v>
       </c>
       <c r="AR97">
-        <v>1.52</v>
+        <v>1.81</v>
       </c>
       <c r="AS97">
-        <v>1.87</v>
+        <v>1.84</v>
       </c>
       <c r="AT97">
-        <v>3.39</v>
+        <v>3.65</v>
       </c>
       <c r="AU97">
         <v>6</v>
@@ -21319,25 +21319,25 @@
         <v>1.33</v>
       </c>
       <c r="AN98">
-        <v>0.92</v>
+        <v>1.5</v>
       </c>
       <c r="AO98">
-        <v>1.17</v>
+        <v>0.83</v>
       </c>
       <c r="AP98">
-        <v>0.65</v>
+        <v>1</v>
       </c>
       <c r="AQ98">
-        <v>1.48</v>
+        <v>1.2</v>
       </c>
       <c r="AR98">
-        <v>1</v>
+        <v>1.15</v>
       </c>
       <c r="AS98">
-        <v>1.4</v>
+        <v>1.28</v>
       </c>
       <c r="AT98">
-        <v>2.4</v>
+        <v>2.43</v>
       </c>
       <c r="AU98">
         <v>4</v>
@@ -21525,25 +21525,25 @@
         <v>1.86</v>
       </c>
       <c r="AN99">
-        <v>1.5</v>
+        <v>1.4</v>
       </c>
       <c r="AO99">
-        <v>0.83</v>
+        <v>1.2</v>
       </c>
       <c r="AP99">
-        <v>1.57</v>
+        <v>2</v>
       </c>
       <c r="AQ99">
-        <v>1.05</v>
+        <v>0.82</v>
       </c>
       <c r="AR99">
-        <v>1.54</v>
+        <v>1.65</v>
       </c>
       <c r="AS99">
-        <v>1.4</v>
+        <v>1.25</v>
       </c>
       <c r="AT99">
-        <v>2.94</v>
+        <v>2.9</v>
       </c>
       <c r="AU99">
         <v>8</v>
@@ -21731,25 +21731,25 @@
         <v>1.67</v>
       </c>
       <c r="AN100">
+        <v>1.29</v>
+      </c>
+      <c r="AO100">
         <v>1.33</v>
       </c>
-      <c r="AO100">
-        <v>1.58</v>
-      </c>
       <c r="AP100">
-        <v>1.2</v>
+        <v>1.45</v>
       </c>
       <c r="AQ100">
-        <v>1.38</v>
+        <v>1.09</v>
       </c>
       <c r="AR100">
-        <v>1.72</v>
+        <v>1.67</v>
       </c>
       <c r="AS100">
-        <v>1.35</v>
+        <v>1.11</v>
       </c>
       <c r="AT100">
-        <v>3.07</v>
+        <v>2.78</v>
       </c>
       <c r="AU100">
         <v>5</v>
@@ -21937,25 +21937,25 @@
         <v>3</v>
       </c>
       <c r="AN101">
-        <v>2.08</v>
+        <v>2</v>
       </c>
       <c r="AO101">
-        <v>1.75</v>
+        <v>1.29</v>
       </c>
       <c r="AP101">
-        <v>2.05</v>
+        <v>2.09</v>
       </c>
       <c r="AQ101">
-        <v>2</v>
+        <v>1.64</v>
       </c>
       <c r="AR101">
-        <v>1.79</v>
+        <v>1.9</v>
       </c>
       <c r="AS101">
-        <v>1.73</v>
+        <v>1.63</v>
       </c>
       <c r="AT101">
-        <v>3.52</v>
+        <v>3.53</v>
       </c>
       <c r="AU101">
         <v>5</v>
@@ -22143,25 +22143,25 @@
         <v>1.24</v>
       </c>
       <c r="AN102">
-        <v>0.08</v>
+        <v>0.14</v>
       </c>
       <c r="AO102">
-        <v>1.25</v>
+        <v>1.2</v>
       </c>
       <c r="AP102">
-        <v>0.19</v>
+        <v>0.27</v>
       </c>
       <c r="AQ102">
-        <v>1.14</v>
+        <v>1</v>
       </c>
       <c r="AR102">
-        <v>1.24</v>
+        <v>1.41</v>
       </c>
       <c r="AS102">
-        <v>1.54</v>
+        <v>1.6</v>
       </c>
       <c r="AT102">
-        <v>2.78</v>
+        <v>3.01</v>
       </c>
       <c r="AU102">
         <v>5</v>
@@ -22349,25 +22349,25 @@
         <v>2.45</v>
       </c>
       <c r="AN103">
-        <v>1.33</v>
+        <v>0.8</v>
       </c>
       <c r="AO103">
-        <v>0.58</v>
+        <v>0.57</v>
       </c>
       <c r="AP103">
-        <v>1.33</v>
+        <v>1.18</v>
       </c>
       <c r="AQ103">
-        <v>0.71</v>
+        <v>0.55</v>
       </c>
       <c r="AR103">
-        <v>1.4</v>
+        <v>1.41</v>
       </c>
       <c r="AS103">
-        <v>1.08</v>
+        <v>1.04</v>
       </c>
       <c r="AT103">
-        <v>2.48</v>
+        <v>2.45</v>
       </c>
       <c r="AU103">
         <v>5</v>
@@ -22555,25 +22555,25 @@
         <v>1.2</v>
       </c>
       <c r="AN104">
-        <v>1.33</v>
+        <v>1.5</v>
       </c>
       <c r="AO104">
-        <v>2.25</v>
+        <v>1.83</v>
       </c>
       <c r="AP104">
-        <v>1.19</v>
+        <v>1.4</v>
       </c>
       <c r="AQ104">
-        <v>2.19</v>
+        <v>1.7</v>
       </c>
       <c r="AR104">
-        <v>1.09</v>
+        <v>1.15</v>
       </c>
       <c r="AS104">
-        <v>1.51</v>
+        <v>1.29</v>
       </c>
       <c r="AT104">
-        <v>2.6</v>
+        <v>2.44</v>
       </c>
       <c r="AU104">
         <v>3</v>
@@ -22761,25 +22761,25 @@
         <v>1.05</v>
       </c>
       <c r="AN105">
-        <v>1.42</v>
+        <v>2.17</v>
       </c>
       <c r="AO105">
-        <v>2.83</v>
+        <v>2.6</v>
       </c>
       <c r="AP105">
-        <v>1.33</v>
+        <v>1.7</v>
       </c>
       <c r="AQ105">
-        <v>2.67</v>
+        <v>2.36</v>
       </c>
       <c r="AR105">
-        <v>1.29</v>
+        <v>1.41</v>
       </c>
       <c r="AS105">
-        <v>1.97</v>
+        <v>1.63</v>
       </c>
       <c r="AT105">
-        <v>3.26</v>
+        <v>3.04</v>
       </c>
       <c r="AU105">
         <v>2</v>
@@ -22967,25 +22967,25 @@
         <v>3.72</v>
       </c>
       <c r="AN106">
-        <v>1.85</v>
+        <v>2.4</v>
       </c>
       <c r="AO106">
-        <v>0.85</v>
+        <v>0.33</v>
       </c>
       <c r="AP106">
-        <v>2</v>
+        <v>2.4</v>
       </c>
       <c r="AQ106">
-        <v>0.65</v>
+        <v>0.3</v>
       </c>
       <c r="AR106">
-        <v>1.72</v>
+        <v>1.87</v>
       </c>
       <c r="AS106">
-        <v>1.04</v>
+        <v>0.84</v>
       </c>
       <c r="AT106">
-        <v>2.76</v>
+        <v>2.71</v>
       </c>
       <c r="AU106">
         <v>8</v>
@@ -23173,22 +23173,22 @@
         <v>1.24</v>
       </c>
       <c r="AN107">
-        <v>0.62</v>
+        <v>0.6</v>
       </c>
       <c r="AO107">
-        <v>1.62</v>
+        <v>1.57</v>
       </c>
       <c r="AP107">
-        <v>0.71</v>
+        <v>0.9</v>
       </c>
       <c r="AQ107">
-        <v>1.57</v>
+        <v>1.1</v>
       </c>
       <c r="AR107">
-        <v>1.06</v>
+        <v>1.14</v>
       </c>
       <c r="AS107">
-        <v>1.54</v>
+        <v>1.46</v>
       </c>
       <c r="AT107">
         <v>2.6</v>
@@ -23379,25 +23379,25 @@
         <v>1.91</v>
       </c>
       <c r="AN108">
-        <v>1.23</v>
+        <v>1.29</v>
       </c>
       <c r="AO108">
-        <v>1.38</v>
+        <v>0.67</v>
       </c>
       <c r="AP108">
-        <v>1.14</v>
+        <v>1.3</v>
       </c>
       <c r="AQ108">
-        <v>1.33</v>
+        <v>1</v>
       </c>
       <c r="AR108">
-        <v>1.51</v>
+        <v>1.5</v>
       </c>
       <c r="AS108">
-        <v>1.25</v>
+        <v>1.16</v>
       </c>
       <c r="AT108">
-        <v>2.76</v>
+        <v>2.66</v>
       </c>
       <c r="AU108">
         <v>7</v>
@@ -23585,25 +23585,25 @@
         <v>2.08</v>
       </c>
       <c r="AN109">
-        <v>0.77</v>
+        <v>0.57</v>
       </c>
       <c r="AO109">
-        <v>0.15</v>
+        <v>0</v>
       </c>
       <c r="AP109">
-        <v>1.05</v>
+        <v>1.3</v>
       </c>
       <c r="AQ109">
-        <v>0.19</v>
+        <v>0.1</v>
       </c>
       <c r="AR109">
-        <v>1.4</v>
+        <v>1.51</v>
       </c>
       <c r="AS109">
-        <v>1.24</v>
+        <v>1.01</v>
       </c>
       <c r="AT109">
-        <v>2.64</v>
+        <v>2.52</v>
       </c>
       <c r="AU109">
         <v>10</v>
@@ -23791,25 +23791,25 @@
         <v>1.14</v>
       </c>
       <c r="AN110">
-        <v>1.31</v>
+        <v>1.5</v>
       </c>
       <c r="AO110">
-        <v>1.92</v>
+        <v>2.14</v>
       </c>
       <c r="AP110">
-        <v>1.48</v>
+        <v>1.73</v>
       </c>
       <c r="AQ110">
-        <v>2.05</v>
+        <v>2</v>
       </c>
       <c r="AR110">
-        <v>1.39</v>
+        <v>1.51</v>
       </c>
       <c r="AS110">
-        <v>1.79</v>
+        <v>1.71</v>
       </c>
       <c r="AT110">
-        <v>3.18</v>
+        <v>3.22</v>
       </c>
       <c r="AU110">
         <v>4</v>
@@ -23997,25 +23997,25 @@
         <v>0</v>
       </c>
       <c r="AN111">
-        <v>2.08</v>
+        <v>2.67</v>
       </c>
       <c r="AO111">
-        <v>1.31</v>
+        <v>1.71</v>
       </c>
       <c r="AP111">
-        <v>2.19</v>
+        <v>2.64</v>
       </c>
       <c r="AQ111">
-        <v>1.33</v>
+        <v>1.5</v>
       </c>
       <c r="AR111">
-        <v>1.44</v>
+        <v>1.73</v>
       </c>
       <c r="AS111">
-        <v>1.42</v>
+        <v>1.4</v>
       </c>
       <c r="AT111">
-        <v>2.86</v>
+        <v>3.13</v>
       </c>
       <c r="AU111">
         <v>6</v>
@@ -24203,25 +24203,25 @@
         <v>4.8</v>
       </c>
       <c r="AN112">
-        <v>2.69</v>
+        <v>3</v>
       </c>
       <c r="AO112">
-        <v>1.46</v>
+        <v>1.4</v>
       </c>
       <c r="AP112">
-        <v>2.67</v>
+        <v>3</v>
       </c>
       <c r="AQ112">
-        <v>1.2</v>
+        <v>0.89</v>
       </c>
       <c r="AR112">
-        <v>1.93</v>
+        <v>2.21</v>
       </c>
       <c r="AS112">
-        <v>1.7</v>
+        <v>1.8</v>
       </c>
       <c r="AT112">
-        <v>3.63</v>
+        <v>4.01</v>
       </c>
       <c r="AU112">
         <v>16</v>
@@ -24409,25 +24409,25 @@
         <v>1.47</v>
       </c>
       <c r="AN113">
+        <v>1.67</v>
+      </c>
+      <c r="AO113">
         <v>1.5</v>
       </c>
-      <c r="AO113">
-        <v>1.93</v>
-      </c>
       <c r="AP113">
-        <v>1.57</v>
+        <v>2</v>
       </c>
       <c r="AQ113">
-        <v>2</v>
+        <v>1.64</v>
       </c>
       <c r="AR113">
-        <v>1.5</v>
+        <v>1.63</v>
       </c>
       <c r="AS113">
-        <v>1.74</v>
+        <v>1.63</v>
       </c>
       <c r="AT113">
-        <v>3.24</v>
+        <v>3.26</v>
       </c>
       <c r="AU113">
         <v>5</v>
@@ -24615,25 +24615,25 @@
         <v>3.5</v>
       </c>
       <c r="AN114">
-        <v>1.86</v>
+        <v>1.67</v>
       </c>
       <c r="AO114">
-        <v>0.93</v>
+        <v>1</v>
       </c>
       <c r="AP114">
-        <v>2.05</v>
+        <v>2.09</v>
       </c>
       <c r="AQ114">
-        <v>1.05</v>
+        <v>0.82</v>
       </c>
       <c r="AR114">
-        <v>1.8</v>
+        <v>1.87</v>
       </c>
       <c r="AS114">
-        <v>1.44</v>
+        <v>1.26</v>
       </c>
       <c r="AT114">
-        <v>3.24</v>
+        <v>3.13</v>
       </c>
       <c r="AU114">
         <v>9</v>
@@ -24821,25 +24821,25 @@
         <v>1.63</v>
       </c>
       <c r="AN115">
-        <v>1.46</v>
+        <v>1.71</v>
       </c>
       <c r="AO115">
-        <v>1.29</v>
+        <v>1.14</v>
       </c>
       <c r="AP115">
-        <v>1.19</v>
+        <v>1.4</v>
       </c>
       <c r="AQ115">
-        <v>1.48</v>
+        <v>1.2</v>
       </c>
       <c r="AR115">
-        <v>1.08</v>
+        <v>1.11</v>
       </c>
       <c r="AS115">
-        <v>1.4</v>
+        <v>1.28</v>
       </c>
       <c r="AT115">
-        <v>2.48</v>
+        <v>2.39</v>
       </c>
       <c r="AU115">
         <v>-1</v>
@@ -25027,25 +25027,25 @@
         <v>1.25</v>
       </c>
       <c r="AN116">
-        <v>1.36</v>
+        <v>2</v>
       </c>
       <c r="AO116">
-        <v>2.14</v>
+        <v>1.57</v>
       </c>
       <c r="AP116">
-        <v>1.33</v>
+        <v>1.7</v>
       </c>
       <c r="AQ116">
-        <v>2.19</v>
+        <v>1.7</v>
       </c>
       <c r="AR116">
-        <v>1.24</v>
+        <v>1.34</v>
       </c>
       <c r="AS116">
-        <v>1.45</v>
+        <v>1.2</v>
       </c>
       <c r="AT116">
-        <v>2.69</v>
+        <v>2.54</v>
       </c>
       <c r="AU116">
         <v>3</v>
@@ -25233,25 +25233,25 @@
         <v>0</v>
       </c>
       <c r="AN117">
-        <v>1.21</v>
+        <v>0.83</v>
       </c>
       <c r="AO117">
-        <v>0.79</v>
+        <v>0.29</v>
       </c>
       <c r="AP117">
-        <v>1.33</v>
+        <v>1.18</v>
       </c>
       <c r="AQ117">
-        <v>0.65</v>
+        <v>0.3</v>
       </c>
       <c r="AR117">
-        <v>1.36</v>
+        <v>1.44</v>
       </c>
       <c r="AS117">
-        <v>1.03</v>
+        <v>0.84</v>
       </c>
       <c r="AT117">
-        <v>2.39</v>
+        <v>2.28</v>
       </c>
       <c r="AU117">
         <v>6</v>
@@ -25439,25 +25439,25 @@
         <v>0</v>
       </c>
       <c r="AN118">
-        <v>0.14</v>
+        <v>0.25</v>
       </c>
       <c r="AO118">
-        <v>2.71</v>
+        <v>2.33</v>
       </c>
       <c r="AP118">
-        <v>0.19</v>
+        <v>0.27</v>
       </c>
       <c r="AQ118">
-        <v>2.67</v>
+        <v>2.36</v>
       </c>
       <c r="AR118">
-        <v>1.22</v>
+        <v>1.38</v>
       </c>
       <c r="AS118">
-        <v>2.04</v>
+        <v>1.61</v>
       </c>
       <c r="AT118">
-        <v>3.26</v>
+        <v>2.99</v>
       </c>
       <c r="AU118">
         <v>2</v>
@@ -25645,25 +25645,25 @@
         <v>0</v>
       </c>
       <c r="AN119">
-        <v>1.36</v>
+        <v>1.5</v>
       </c>
       <c r="AO119">
-        <v>0.79</v>
+        <v>0.63</v>
       </c>
       <c r="AP119">
-        <v>1.2</v>
+        <v>1.45</v>
       </c>
       <c r="AQ119">
-        <v>0.71</v>
+        <v>0.55</v>
       </c>
       <c r="AR119">
-        <v>1.63</v>
+        <v>1.64</v>
       </c>
       <c r="AS119">
-        <v>1.05</v>
+        <v>1.02</v>
       </c>
       <c r="AT119">
-        <v>2.68</v>
+        <v>2.66</v>
       </c>
       <c r="AU119">
         <v>3</v>
@@ -25851,25 +25851,25 @@
         <v>1.63</v>
       </c>
       <c r="AN120">
-        <v>1.46</v>
+        <v>1.83</v>
       </c>
       <c r="AO120">
-        <v>1.21</v>
+        <v>1.17</v>
       </c>
       <c r="AP120">
-        <v>1.38</v>
+        <v>1.7</v>
       </c>
       <c r="AQ120">
-        <v>1.14</v>
+        <v>1</v>
       </c>
       <c r="AR120">
-        <v>1.38</v>
+        <v>1.59</v>
       </c>
       <c r="AS120">
         <v>1.52</v>
       </c>
       <c r="AT120">
-        <v>2.9</v>
+        <v>3.11</v>
       </c>
       <c r="AU120">
         <v>4</v>
@@ -26057,25 +26057,25 @@
         <v>1.63</v>
       </c>
       <c r="AN121">
-        <v>1.36</v>
+        <v>1.57</v>
       </c>
       <c r="AO121">
-        <v>1.43</v>
+        <v>1.17</v>
       </c>
       <c r="AP121">
-        <v>1.38</v>
+        <v>1.7</v>
       </c>
       <c r="AQ121">
-        <v>1.19</v>
+        <v>1</v>
       </c>
       <c r="AR121">
-        <v>1.39</v>
+        <v>1.57</v>
       </c>
       <c r="AS121">
-        <v>1.08</v>
+        <v>1.04</v>
       </c>
       <c r="AT121">
-        <v>2.47</v>
+        <v>2.61</v>
       </c>
       <c r="AU121">
         <v>13</v>
@@ -26263,25 +26263,25 @@
         <v>0</v>
       </c>
       <c r="AN122">
-        <v>1.33</v>
+        <v>1.14</v>
       </c>
       <c r="AO122">
-        <v>1.33</v>
+        <v>1</v>
       </c>
       <c r="AP122">
-        <v>1.33</v>
+        <v>1.18</v>
       </c>
       <c r="AQ122">
-        <v>1.19</v>
+        <v>1</v>
       </c>
       <c r="AR122">
-        <v>1.41</v>
+        <v>1.54</v>
       </c>
       <c r="AS122">
-        <v>1.07</v>
+        <v>1.03</v>
       </c>
       <c r="AT122">
-        <v>2.48</v>
+        <v>2.57</v>
       </c>
       <c r="AU122">
         <v>6</v>
@@ -26469,25 +26469,25 @@
         <v>2.82</v>
       </c>
       <c r="AN123">
-        <v>1.8</v>
+        <v>2.5</v>
       </c>
       <c r="AO123">
-        <v>1.47</v>
+        <v>1.17</v>
       </c>
       <c r="AP123">
-        <v>2</v>
+        <v>2.4</v>
       </c>
       <c r="AQ123">
-        <v>1.2</v>
+        <v>0.89</v>
       </c>
       <c r="AR123">
-        <v>1.74</v>
+        <v>1.87</v>
       </c>
       <c r="AS123">
-        <v>1.6</v>
+        <v>1.62</v>
       </c>
       <c r="AT123">
-        <v>3.34</v>
+        <v>3.49</v>
       </c>
       <c r="AU123">
         <v>12</v>
@@ -26675,25 +26675,25 @@
         <v>1.52</v>
       </c>
       <c r="AN124">
-        <v>0.93</v>
+        <v>0.88</v>
       </c>
       <c r="AO124">
-        <v>1.47</v>
+        <v>1.14</v>
       </c>
       <c r="AP124">
-        <v>1.05</v>
+        <v>1.3</v>
       </c>
       <c r="AQ124">
-        <v>1.38</v>
+        <v>1.09</v>
       </c>
       <c r="AR124">
-        <v>1.41</v>
+        <v>1.58</v>
       </c>
       <c r="AS124">
-        <v>1.46</v>
+        <v>1.2</v>
       </c>
       <c r="AT124">
-        <v>2.87</v>
+        <v>2.78</v>
       </c>
       <c r="AU124">
         <v>2</v>
@@ -26881,25 +26881,25 @@
         <v>1.08</v>
       </c>
       <c r="AN125">
-        <v>0.73</v>
+        <v>1.29</v>
       </c>
       <c r="AO125">
-        <v>1.8</v>
+        <v>2</v>
       </c>
       <c r="AP125">
-        <v>0.65</v>
+        <v>1</v>
       </c>
       <c r="AQ125">
-        <v>2.05</v>
+        <v>2</v>
       </c>
       <c r="AR125">
-        <v>1.02</v>
+        <v>1.21</v>
       </c>
       <c r="AS125">
-        <v>1.83</v>
+        <v>1.74</v>
       </c>
       <c r="AT125">
-        <v>2.85</v>
+        <v>2.95</v>
       </c>
       <c r="AU125">
         <v>5</v>
@@ -27087,25 +27087,25 @@
         <v>4.2</v>
       </c>
       <c r="AN126">
-        <v>2.73</v>
+        <v>3</v>
       </c>
       <c r="AO126">
-        <v>1.33</v>
+        <v>1.43</v>
       </c>
       <c r="AP126">
-        <v>2.67</v>
+        <v>3</v>
       </c>
       <c r="AQ126">
-        <v>1.14</v>
+        <v>1</v>
       </c>
       <c r="AR126">
-        <v>2.03</v>
+        <v>2.37</v>
       </c>
       <c r="AS126">
-        <v>1.54</v>
+        <v>1.57</v>
       </c>
       <c r="AT126">
-        <v>3.57</v>
+        <v>3.94</v>
       </c>
       <c r="AU126">
         <v>9</v>
@@ -27293,25 +27293,25 @@
         <v>1.62</v>
       </c>
       <c r="AN127">
-        <v>1.27</v>
+        <v>1.43</v>
       </c>
       <c r="AO127">
-        <v>1.27</v>
+        <v>0.71</v>
       </c>
       <c r="AP127">
-        <v>1.48</v>
+        <v>1.73</v>
       </c>
       <c r="AQ127">
-        <v>1.33</v>
+        <v>1</v>
       </c>
       <c r="AR127">
-        <v>1.4</v>
+        <v>1.5</v>
       </c>
       <c r="AS127">
-        <v>1.24</v>
+        <v>1.15</v>
       </c>
       <c r="AT127">
-        <v>2.64</v>
+        <v>2.65</v>
       </c>
       <c r="AU127">
         <v>9</v>
@@ -27499,25 +27499,25 @@
         <v>2</v>
       </c>
       <c r="AN128">
-        <v>0.73</v>
+        <v>1</v>
       </c>
       <c r="AO128">
-        <v>0.13</v>
+        <v>0</v>
       </c>
       <c r="AP128">
-        <v>0.71</v>
+        <v>0.9</v>
       </c>
       <c r="AQ128">
-        <v>0.19</v>
+        <v>0.1</v>
       </c>
       <c r="AR128">
-        <v>1.06</v>
+        <v>1.1</v>
       </c>
       <c r="AS128">
-        <v>1.2</v>
+        <v>1</v>
       </c>
       <c r="AT128">
-        <v>2.26</v>
+        <v>2.1</v>
       </c>
       <c r="AU128">
         <v>6</v>
@@ -27705,25 +27705,25 @@
         <v>2.45</v>
       </c>
       <c r="AN129">
-        <v>2.2</v>
+        <v>2.71</v>
       </c>
       <c r="AO129">
-        <v>1.6</v>
+        <v>1.38</v>
       </c>
       <c r="AP129">
-        <v>2.19</v>
+        <v>2.64</v>
       </c>
       <c r="AQ129">
-        <v>1.57</v>
+        <v>1.1</v>
       </c>
       <c r="AR129">
-        <v>1.44</v>
+        <v>1.69</v>
       </c>
       <c r="AS129">
-        <v>1.5</v>
+        <v>1.4</v>
       </c>
       <c r="AT129">
-        <v>2.94</v>
+        <v>3.09</v>
       </c>
       <c r="AU129">
         <v>6</v>
@@ -27911,25 +27911,25 @@
         <v>4.33</v>
       </c>
       <c r="AN130">
-        <v>1.75</v>
+        <v>1.57</v>
       </c>
       <c r="AO130">
-        <v>1.38</v>
+        <v>1</v>
       </c>
       <c r="AP130">
-        <v>2.05</v>
+        <v>2.09</v>
       </c>
       <c r="AQ130">
-        <v>1.2</v>
+        <v>0.89</v>
       </c>
       <c r="AR130">
-        <v>1.78</v>
+        <v>1.93</v>
       </c>
       <c r="AS130">
-        <v>1.57</v>
+        <v>1.54</v>
       </c>
       <c r="AT130">
-        <v>3.35</v>
+        <v>3.47</v>
       </c>
       <c r="AU130">
         <v>13</v>
@@ -28117,25 +28117,25 @@
         <v>2.65</v>
       </c>
       <c r="AN131">
-        <v>1.5</v>
+        <v>1.86</v>
       </c>
       <c r="AO131">
-        <v>0.19</v>
+        <v>0.14</v>
       </c>
       <c r="AP131">
-        <v>1.57</v>
+        <v>2</v>
       </c>
       <c r="AQ131">
-        <v>0.19</v>
+        <v>0.1</v>
       </c>
       <c r="AR131">
-        <v>1.48</v>
+        <v>1.63</v>
       </c>
       <c r="AS131">
-        <v>1.14</v>
+        <v>0.9</v>
       </c>
       <c r="AT131">
-        <v>2.62</v>
+        <v>2.53</v>
       </c>
       <c r="AU131">
         <v>10</v>
@@ -28323,25 +28323,25 @@
         <v>1.32</v>
       </c>
       <c r="AN132">
-        <v>0.75</v>
+        <v>1.25</v>
       </c>
       <c r="AO132">
-        <v>1.31</v>
+        <v>1</v>
       </c>
       <c r="AP132">
-        <v>0.65</v>
+        <v>1</v>
       </c>
       <c r="AQ132">
-        <v>1.19</v>
+        <v>1</v>
       </c>
       <c r="AR132">
-        <v>1.05</v>
+        <v>1.24</v>
       </c>
       <c r="AS132">
-        <v>1.13</v>
+        <v>1.14</v>
       </c>
       <c r="AT132">
-        <v>2.18</v>
+        <v>2.38</v>
       </c>
       <c r="AU132">
         <v>4</v>
@@ -28529,25 +28529,25 @@
         <v>1.36</v>
       </c>
       <c r="AN133">
-        <v>0.75</v>
+        <v>1</v>
       </c>
       <c r="AO133">
-        <v>1.38</v>
+        <v>1</v>
       </c>
       <c r="AP133">
-        <v>0.71</v>
+        <v>0.9</v>
       </c>
       <c r="AQ133">
-        <v>1.38</v>
+        <v>1.09</v>
       </c>
       <c r="AR133">
-        <v>1.11</v>
+        <v>1.21</v>
       </c>
       <c r="AS133">
-        <v>1.44</v>
+        <v>1.18</v>
       </c>
       <c r="AT133">
-        <v>2.55</v>
+        <v>2.39</v>
       </c>
       <c r="AU133">
         <v>6</v>
@@ -28735,25 +28735,25 @@
         <v>1.75</v>
       </c>
       <c r="AN134">
-        <v>1.31</v>
+        <v>1.13</v>
       </c>
       <c r="AO134">
-        <v>1.19</v>
+        <v>0.63</v>
       </c>
       <c r="AP134">
-        <v>1.33</v>
+        <v>1.18</v>
       </c>
       <c r="AQ134">
-        <v>1.33</v>
+        <v>1</v>
       </c>
       <c r="AR134">
-        <v>1.4</v>
+        <v>1.51</v>
       </c>
       <c r="AS134">
-        <v>1.27</v>
+        <v>1.23</v>
       </c>
       <c r="AT134">
-        <v>2.67</v>
+        <v>2.74</v>
       </c>
       <c r="AU134">
         <v>4</v>
@@ -28941,25 +28941,25 @@
         <v>1.69</v>
       </c>
       <c r="AN135">
-        <v>1.38</v>
+        <v>1.63</v>
       </c>
       <c r="AO135">
         <v>1.25</v>
       </c>
       <c r="AP135">
-        <v>1.48</v>
+        <v>1.73</v>
       </c>
       <c r="AQ135">
-        <v>1.14</v>
+        <v>1</v>
       </c>
       <c r="AR135">
-        <v>1.44</v>
+        <v>1.56</v>
       </c>
       <c r="AS135">
-        <v>1.5</v>
+        <v>1.49</v>
       </c>
       <c r="AT135">
-        <v>2.94</v>
+        <v>3.05</v>
       </c>
       <c r="AU135">
         <v>5</v>
@@ -29147,25 +29147,25 @@
         <v>1.15</v>
       </c>
       <c r="AN136">
-        <v>1.88</v>
+        <v>2.57</v>
       </c>
       <c r="AO136">
-        <v>2.75</v>
+        <v>2.43</v>
       </c>
       <c r="AP136">
-        <v>2</v>
+        <v>2.4</v>
       </c>
       <c r="AQ136">
-        <v>2.67</v>
+        <v>2.36</v>
       </c>
       <c r="AR136">
-        <v>1.81</v>
+        <v>2.02</v>
       </c>
       <c r="AS136">
-        <v>2.06</v>
+        <v>1.63</v>
       </c>
       <c r="AT136">
-        <v>3.87</v>
+        <v>3.65</v>
       </c>
       <c r="AU136">
         <v>4</v>
@@ -29353,25 +29353,25 @@
         <v>3.6</v>
       </c>
       <c r="AN137">
-        <v>2.25</v>
+        <v>2.75</v>
       </c>
       <c r="AO137">
-        <v>1.06</v>
+        <v>1</v>
       </c>
       <c r="AP137">
-        <v>2.19</v>
+        <v>2.64</v>
       </c>
       <c r="AQ137">
-        <v>1.05</v>
+        <v>0.82</v>
       </c>
       <c r="AR137">
-        <v>1.46</v>
+        <v>1.7</v>
       </c>
       <c r="AS137">
-        <v>1.41</v>
+        <v>1.22</v>
       </c>
       <c r="AT137">
-        <v>2.87</v>
+        <v>2.92</v>
       </c>
       <c r="AU137">
         <v>9</v>
@@ -29559,25 +29559,25 @@
         <v>2.2</v>
       </c>
       <c r="AN138">
-        <v>1.41</v>
+        <v>1.63</v>
       </c>
       <c r="AO138">
-        <v>0.76</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="AP138">
-        <v>1.19</v>
+        <v>1.4</v>
       </c>
       <c r="AQ138">
-        <v>0.71</v>
+        <v>0.55</v>
       </c>
       <c r="AR138">
-        <v>1.15</v>
+        <v>1.11</v>
       </c>
       <c r="AS138">
-        <v>1.14</v>
+        <v>1.03</v>
       </c>
       <c r="AT138">
-        <v>2.29</v>
+        <v>2.14</v>
       </c>
       <c r="AU138">
         <v>8</v>
@@ -29765,22 +29765,22 @@
         <v>2.7</v>
       </c>
       <c r="AN139">
-        <v>1.59</v>
+        <v>2</v>
       </c>
       <c r="AO139">
-        <v>0.71</v>
+        <v>0.25</v>
       </c>
       <c r="AP139">
-        <v>1.57</v>
+        <v>2</v>
       </c>
       <c r="AQ139">
-        <v>0.65</v>
+        <v>0.3</v>
       </c>
       <c r="AR139">
-        <v>1.52</v>
+        <v>1.71</v>
       </c>
       <c r="AS139">
-        <v>1.05</v>
+        <v>0.86</v>
       </c>
       <c r="AT139">
         <v>2.57</v>
@@ -29971,25 +29971,25 @@
         <v>3.75</v>
       </c>
       <c r="AN140">
-        <v>1.82</v>
+        <v>1.75</v>
       </c>
       <c r="AO140">
-        <v>1.24</v>
+        <v>1.5</v>
       </c>
       <c r="AP140">
-        <v>2.05</v>
+        <v>2.09</v>
       </c>
       <c r="AQ140">
-        <v>1.33</v>
+        <v>1.5</v>
       </c>
       <c r="AR140">
-        <v>1.86</v>
+        <v>2.06</v>
       </c>
       <c r="AS140">
-        <v>1.39</v>
+        <v>1.31</v>
       </c>
       <c r="AT140">
-        <v>3.25</v>
+        <v>3.37</v>
       </c>
       <c r="AU140">
         <v>2</v>
@@ -30177,25 +30177,25 @@
         <v>1.2</v>
       </c>
       <c r="AN141">
-        <v>1.29</v>
+        <v>1.67</v>
       </c>
       <c r="AO141">
-        <v>2.18</v>
+        <v>1.75</v>
       </c>
       <c r="AP141">
-        <v>1.2</v>
+        <v>1.45</v>
       </c>
       <c r="AQ141">
-        <v>2.19</v>
+        <v>1.7</v>
       </c>
       <c r="AR141">
-        <v>1.55</v>
+        <v>1.59</v>
       </c>
       <c r="AS141">
-        <v>1.51</v>
+        <v>1.23</v>
       </c>
       <c r="AT141">
-        <v>3.06</v>
+        <v>2.82</v>
       </c>
       <c r="AU141">
         <v>4</v>
@@ -30383,25 +30383,25 @@
         <v>1.2</v>
       </c>
       <c r="AN142">
-        <v>0.18</v>
+        <v>0.22</v>
       </c>
       <c r="AO142">
-        <v>1.47</v>
+        <v>1.13</v>
       </c>
       <c r="AP142">
-        <v>0.19</v>
+        <v>0.27</v>
       </c>
       <c r="AQ142">
-        <v>1.48</v>
+        <v>1.2</v>
       </c>
       <c r="AR142">
-        <v>1.14</v>
+        <v>1.34</v>
       </c>
       <c r="AS142">
-        <v>1.43</v>
+        <v>1.28</v>
       </c>
       <c r="AT142">
-        <v>2.57</v>
+        <v>2.62</v>
       </c>
       <c r="AU142">
         <v>5</v>
@@ -30589,25 +30589,25 @@
         <v>1.9</v>
       </c>
       <c r="AN143">
-        <v>1.18</v>
+        <v>1.25</v>
       </c>
       <c r="AO143">
-        <v>1.06</v>
+        <v>1</v>
       </c>
       <c r="AP143">
-        <v>1.14</v>
+        <v>1.3</v>
       </c>
       <c r="AQ143">
-        <v>1.05</v>
+        <v>0.82</v>
       </c>
       <c r="AR143">
-        <v>1.49</v>
+        <v>1.52</v>
       </c>
       <c r="AS143">
-        <v>1.41</v>
+        <v>1.26</v>
       </c>
       <c r="AT143">
-        <v>2.9</v>
+        <v>2.78</v>
       </c>
       <c r="AU143">
         <v>6</v>
@@ -30795,25 +30795,25 @@
         <v>1.04</v>
       </c>
       <c r="AN144">
-        <v>1.35</v>
+        <v>1.75</v>
       </c>
       <c r="AO144">
-        <v>2.76</v>
+        <v>2.5</v>
       </c>
       <c r="AP144">
-        <v>1.38</v>
+        <v>1.7</v>
       </c>
       <c r="AQ144">
-        <v>2.67</v>
+        <v>2.36</v>
       </c>
       <c r="AR144">
-        <v>1.43</v>
+        <v>1.69</v>
       </c>
       <c r="AS144">
-        <v>2.05</v>
+        <v>1.67</v>
       </c>
       <c r="AT144">
-        <v>3.48</v>
+        <v>3.36</v>
       </c>
       <c r="AU144">
         <v>4</v>
@@ -31001,25 +31001,25 @@
         <v>1.4</v>
       </c>
       <c r="AN145">
-        <v>1.29</v>
+        <v>1.75</v>
       </c>
       <c r="AO145">
-        <v>1.76</v>
+        <v>1.33</v>
       </c>
       <c r="AP145">
-        <v>1.33</v>
+        <v>1.7</v>
       </c>
       <c r="AQ145">
-        <v>2</v>
+        <v>1.64</v>
       </c>
       <c r="AR145">
-        <v>1.28</v>
+        <v>1.32</v>
       </c>
       <c r="AS145">
-        <v>1.77</v>
+        <v>1.63</v>
       </c>
       <c r="AT145">
-        <v>3.05</v>
+        <v>2.95</v>
       </c>
       <c r="AU145">
         <v>9</v>
@@ -31207,25 +31207,25 @@
         <v>1.25</v>
       </c>
       <c r="AN146">
-        <v>0.67</v>
+        <v>1.11</v>
       </c>
       <c r="AO146">
+        <v>0.89</v>
+      </c>
+      <c r="AP146">
+        <v>1</v>
+      </c>
+      <c r="AQ146">
+        <v>1</v>
+      </c>
+      <c r="AR146">
         <v>1.22</v>
       </c>
-      <c r="AP146">
-        <v>0.65</v>
-      </c>
-      <c r="AQ146">
-        <v>1.33</v>
-      </c>
-      <c r="AR146">
-        <v>1.07</v>
-      </c>
       <c r="AS146">
-        <v>1.34</v>
+        <v>1.25</v>
       </c>
       <c r="AT146">
-        <v>2.41</v>
+        <v>2.47</v>
       </c>
       <c r="AU146">
         <v>6</v>
@@ -31413,25 +31413,25 @@
         <v>1.33</v>
       </c>
       <c r="AN147">
-        <v>0.78</v>
+        <v>1</v>
       </c>
       <c r="AO147">
-        <v>1.28</v>
+        <v>1.11</v>
       </c>
       <c r="AP147">
-        <v>0.71</v>
+        <v>0.9</v>
       </c>
       <c r="AQ147">
-        <v>1.14</v>
+        <v>1</v>
       </c>
       <c r="AR147">
-        <v>1.15</v>
+        <v>1.26</v>
       </c>
       <c r="AS147">
-        <v>1.49</v>
+        <v>1.47</v>
       </c>
       <c r="AT147">
-        <v>2.64</v>
+        <v>2.73</v>
       </c>
       <c r="AU147">
         <v>4</v>
@@ -31619,25 +31619,25 @@
         <v>1.85</v>
       </c>
       <c r="AN148">
-        <v>1.17</v>
+        <v>1</v>
       </c>
       <c r="AO148">
-        <v>1.22</v>
+        <v>0.88</v>
       </c>
       <c r="AP148">
-        <v>1.33</v>
+        <v>1.18</v>
       </c>
       <c r="AQ148">
-        <v>1.2</v>
+        <v>0.89</v>
       </c>
       <c r="AR148">
-        <v>1.4</v>
+        <v>1.47</v>
       </c>
       <c r="AS148">
-        <v>1.54</v>
+        <v>1.5</v>
       </c>
       <c r="AT148">
-        <v>2.94</v>
+        <v>2.97</v>
       </c>
       <c r="AU148">
         <v>10</v>
@@ -31825,25 +31825,25 @@
         <v>2.55</v>
       </c>
       <c r="AN149">
-        <v>1.83</v>
+        <v>2.25</v>
       </c>
       <c r="AO149">
-        <v>1.39</v>
+        <v>1.22</v>
       </c>
       <c r="AP149">
-        <v>2</v>
+        <v>2.4</v>
       </c>
       <c r="AQ149">
-        <v>1.19</v>
+        <v>1</v>
       </c>
       <c r="AR149">
-        <v>1.76</v>
+        <v>1.91</v>
       </c>
       <c r="AS149">
-        <v>1.19</v>
+        <v>1.17</v>
       </c>
       <c r="AT149">
-        <v>2.95</v>
+        <v>3.08</v>
       </c>
       <c r="AU149">
         <v>7</v>
@@ -32034,22 +32034,22 @@
         <v>1.89</v>
       </c>
       <c r="AO150">
-        <v>1.67</v>
+        <v>1.22</v>
       </c>
       <c r="AP150">
-        <v>2.05</v>
+        <v>2.09</v>
       </c>
       <c r="AQ150">
-        <v>1.57</v>
+        <v>1.1</v>
       </c>
       <c r="AR150">
-        <v>1.83</v>
+        <v>1.98</v>
       </c>
       <c r="AS150">
-        <v>1.52</v>
+        <v>1.38</v>
       </c>
       <c r="AT150">
-        <v>3.35</v>
+        <v>3.36</v>
       </c>
       <c r="AU150">
         <v>6</v>
@@ -32237,25 +32237,25 @@
         <v>1.8</v>
       </c>
       <c r="AN151">
-        <v>1.56</v>
+        <v>1.78</v>
       </c>
       <c r="AO151">
-        <v>1.28</v>
+        <v>1</v>
       </c>
       <c r="AP151">
-        <v>1.48</v>
+        <v>1.73</v>
       </c>
       <c r="AQ151">
-        <v>1.38</v>
+        <v>1.09</v>
       </c>
       <c r="AR151">
-        <v>1.45</v>
+        <v>1.53</v>
       </c>
       <c r="AS151">
-        <v>1.4</v>
+        <v>1.2</v>
       </c>
       <c r="AT151">
-        <v>2.85</v>
+        <v>2.73</v>
       </c>
       <c r="AU151">
         <v>8</v>
@@ -32443,25 +32443,25 @@
         <v>1.05</v>
       </c>
       <c r="AN152">
-        <v>1</v>
+        <v>1.11</v>
       </c>
       <c r="AO152">
-        <v>2.78</v>
+        <v>2.56</v>
       </c>
       <c r="AP152">
-        <v>1.05</v>
+        <v>1.3</v>
       </c>
       <c r="AQ152">
-        <v>2.67</v>
+        <v>2.36</v>
       </c>
       <c r="AR152">
-        <v>1.43</v>
+        <v>1.55</v>
       </c>
       <c r="AS152">
-        <v>2.03</v>
+        <v>1.68</v>
       </c>
       <c r="AT152">
-        <v>3.46</v>
+        <v>3.23</v>
       </c>
       <c r="AU152">
         <v>4</v>
@@ -32649,25 +32649,25 @@
         <v>7</v>
       </c>
       <c r="AN153">
-        <v>2.22</v>
+        <v>2.56</v>
       </c>
       <c r="AO153">
-        <v>0.17</v>
+        <v>0.13</v>
       </c>
       <c r="AP153">
-        <v>2.19</v>
+        <v>2.64</v>
       </c>
       <c r="AQ153">
-        <v>0.19</v>
+        <v>0.1</v>
       </c>
       <c r="AR153">
-        <v>1.53</v>
+        <v>1.75</v>
       </c>
       <c r="AS153">
-        <v>1.16</v>
+        <v>0.93</v>
       </c>
       <c r="AT153">
-        <v>2.69</v>
+        <v>2.68</v>
       </c>
       <c r="AU153">
         <v>11</v>
@@ -32855,25 +32855,25 @@
         <v>0</v>
       </c>
       <c r="AN154">
-        <v>1.21</v>
+        <v>1.5</v>
       </c>
       <c r="AO154">
-        <v>1.11</v>
+        <v>0.89</v>
       </c>
       <c r="AP154">
-        <v>1.2</v>
+        <v>1.45</v>
       </c>
       <c r="AQ154">
-        <v>1.05</v>
+        <v>0.82</v>
       </c>
       <c r="AR154">
-        <v>1.53</v>
+        <v>1.58</v>
       </c>
       <c r="AS154">
-        <v>1.39</v>
+        <v>1.31</v>
       </c>
       <c r="AT154">
-        <v>2.92</v>
+        <v>2.89</v>
       </c>
       <c r="AU154">
         <v>2</v>
@@ -33061,25 +33061,25 @@
         <v>1.44</v>
       </c>
       <c r="AN155">
-        <v>0.16</v>
+        <v>0.2</v>
       </c>
       <c r="AO155">
-        <v>0.63</v>
+        <v>0.22</v>
       </c>
       <c r="AP155">
-        <v>0.19</v>
+        <v>0.27</v>
       </c>
       <c r="AQ155">
-        <v>0.65</v>
+        <v>0.3</v>
       </c>
       <c r="AR155">
-        <v>1.15</v>
+        <v>1.34</v>
       </c>
       <c r="AS155">
-        <v>1.11</v>
+        <v>0.93</v>
       </c>
       <c r="AT155">
-        <v>2.26</v>
+        <v>2.27</v>
       </c>
       <c r="AU155">
         <v>3</v>
@@ -33267,25 +33267,25 @@
         <v>1.45</v>
       </c>
       <c r="AN156">
-        <v>1.26</v>
+        <v>1.44</v>
       </c>
       <c r="AO156">
-        <v>1.89</v>
+        <v>1.5</v>
       </c>
       <c r="AP156">
-        <v>1.14</v>
+        <v>1.3</v>
       </c>
       <c r="AQ156">
-        <v>2</v>
+        <v>1.64</v>
       </c>
       <c r="AR156">
-        <v>1.49</v>
+        <v>1.51</v>
       </c>
       <c r="AS156">
-        <v>1.76</v>
+        <v>1.63</v>
       </c>
       <c r="AT156">
-        <v>3.25</v>
+        <v>3.14</v>
       </c>
       <c r="AU156">
         <v>2</v>
@@ -33473,25 +33473,25 @@
         <v>2.26</v>
       </c>
       <c r="AN157">
-        <v>1.32</v>
+        <v>1.56</v>
       </c>
       <c r="AO157">
-        <v>0.79</v>
+        <v>0.6</v>
       </c>
       <c r="AP157">
-        <v>1.33</v>
+        <v>1.7</v>
       </c>
       <c r="AQ157">
-        <v>0.71</v>
+        <v>0.55</v>
       </c>
       <c r="AR157">
-        <v>1.35</v>
+        <v>1.43</v>
       </c>
       <c r="AS157">
-        <v>1.17</v>
+        <v>1.06</v>
       </c>
       <c r="AT157">
-        <v>2.52</v>
+        <v>2.49</v>
       </c>
       <c r="AU157">
         <v>8</v>
@@ -33679,25 +33679,25 @@
         <v>1.2</v>
       </c>
       <c r="AN158">
-        <v>1.32</v>
+        <v>1.56</v>
       </c>
       <c r="AO158">
-        <v>1.95</v>
+        <v>1.89</v>
       </c>
       <c r="AP158">
-        <v>1.19</v>
+        <v>1.4</v>
       </c>
       <c r="AQ158">
-        <v>2.05</v>
+        <v>2</v>
       </c>
       <c r="AR158">
-        <v>1.23</v>
+        <v>1.21</v>
       </c>
       <c r="AS158">
-        <v>1.82</v>
+        <v>1.67</v>
       </c>
       <c r="AT158">
-        <v>3.05</v>
+        <v>2.88</v>
       </c>
       <c r="AU158">
         <v>0</v>
@@ -33885,25 +33885,25 @@
         <v>2</v>
       </c>
       <c r="AN159">
-        <v>1.58</v>
+        <v>2.11</v>
       </c>
       <c r="AO159">
-        <v>1.16</v>
+        <v>1.33</v>
       </c>
       <c r="AP159">
-        <v>1.57</v>
+        <v>2</v>
       </c>
       <c r="AQ159">
-        <v>1.33</v>
+        <v>1.5</v>
       </c>
       <c r="AR159">
-        <v>1.5</v>
+        <v>1.67</v>
       </c>
       <c r="AS159">
-        <v>1.47</v>
+        <v>1.35</v>
       </c>
       <c r="AT159">
-        <v>2.97</v>
+        <v>3.02</v>
       </c>
       <c r="AU159">
         <v>5</v>
@@ -34091,25 +34091,25 @@
         <v>4.33</v>
       </c>
       <c r="AN160">
-        <v>2.63</v>
+        <v>3</v>
       </c>
       <c r="AO160">
-        <v>1.47</v>
+        <v>1.33</v>
       </c>
       <c r="AP160">
-        <v>2.67</v>
+        <v>3</v>
       </c>
       <c r="AQ160">
-        <v>1.48</v>
+        <v>1.2</v>
       </c>
       <c r="AR160">
-        <v>2.05</v>
+        <v>2.39</v>
       </c>
       <c r="AS160">
-        <v>1.49</v>
+        <v>1.34</v>
       </c>
       <c r="AT160">
-        <v>3.54</v>
+        <v>3.73</v>
       </c>
       <c r="AU160">
         <v>4</v>
@@ -34297,25 +34297,25 @@
         <v>1.21</v>
       </c>
       <c r="AN161">
-        <v>1.37</v>
+        <v>1.56</v>
       </c>
       <c r="AO161">
-        <v>2.26</v>
+        <v>1.89</v>
       </c>
       <c r="AP161">
-        <v>1.38</v>
+        <v>1.7</v>
       </c>
       <c r="AQ161">
-        <v>2.19</v>
+        <v>1.7</v>
       </c>
       <c r="AR161">
-        <v>1.4</v>
+        <v>1.6</v>
       </c>
       <c r="AS161">
-        <v>1.58</v>
+        <v>1.32</v>
       </c>
       <c r="AT161">
-        <v>2.98</v>
+        <v>2.92</v>
       </c>
       <c r="AU161">
         <v>5</v>
@@ -34503,25 +34503,25 @@
         <v>1.75</v>
       </c>
       <c r="AN162">
-        <v>1.4</v>
+        <v>1.6</v>
       </c>
       <c r="AO162">
-        <v>1.1</v>
+        <v>0.9</v>
       </c>
       <c r="AP162">
-        <v>1.48</v>
+        <v>1.73</v>
       </c>
       <c r="AQ162">
-        <v>1.05</v>
+        <v>0.82</v>
       </c>
       <c r="AR162">
-        <v>1.45</v>
+        <v>1.6</v>
       </c>
       <c r="AS162">
-        <v>1.4</v>
+        <v>1.33</v>
       </c>
       <c r="AT162">
-        <v>2.85</v>
+        <v>2.93</v>
       </c>
       <c r="AU162">
         <v>6</v>
@@ -34709,25 +34709,25 @@
         <v>1.03</v>
       </c>
       <c r="AN163">
-        <v>0.75</v>
+        <v>1</v>
       </c>
       <c r="AO163">
-        <v>2.65</v>
+        <v>2.3</v>
       </c>
       <c r="AP163">
-        <v>0.71</v>
+        <v>0.9</v>
       </c>
       <c r="AQ163">
-        <v>2.67</v>
+        <v>2.36</v>
       </c>
       <c r="AR163">
-        <v>1.16</v>
+        <v>1.29</v>
       </c>
       <c r="AS163">
-        <v>2.03</v>
+        <v>1.74</v>
       </c>
       <c r="AT163">
-        <v>3.19</v>
+        <v>3.03</v>
       </c>
       <c r="AU163">
         <v>2</v>
@@ -34915,25 +34915,25 @@
         <v>2.5</v>
       </c>
       <c r="AN164">
-        <v>2.15</v>
+        <v>2.6</v>
       </c>
       <c r="AO164">
-        <v>1.2</v>
+        <v>1.1</v>
       </c>
       <c r="AP164">
-        <v>2.19</v>
+        <v>2.64</v>
       </c>
       <c r="AQ164">
-        <v>1.14</v>
+        <v>1</v>
       </c>
       <c r="AR164">
-        <v>1.59</v>
+        <v>1.81</v>
       </c>
       <c r="AS164">
-        <v>1.45</v>
+        <v>1.47</v>
       </c>
       <c r="AT164">
-        <v>3.04</v>
+        <v>3.28</v>
       </c>
       <c r="AU164">
         <v>8</v>
@@ -35121,25 +35121,25 @@
         <v>1.93</v>
       </c>
       <c r="AN165">
-        <v>1.5</v>
+        <v>1.9</v>
       </c>
       <c r="AO165">
-        <v>1.25</v>
+        <v>1.1</v>
       </c>
       <c r="AP165">
-        <v>1.57</v>
+        <v>2</v>
       </c>
       <c r="AQ165">
-        <v>1.19</v>
+        <v>1</v>
       </c>
       <c r="AR165">
-        <v>1.5</v>
+        <v>1.66</v>
       </c>
       <c r="AS165">
-        <v>1.23</v>
+        <v>1.24</v>
       </c>
       <c r="AT165">
-        <v>2.73</v>
+        <v>2.9</v>
       </c>
       <c r="AU165">
         <v>8</v>
@@ -35327,25 +35327,25 @@
         <v>2.2</v>
       </c>
       <c r="AN166">
-        <v>1.95</v>
+        <v>2.33</v>
       </c>
       <c r="AO166">
-        <v>1.45</v>
+        <v>1.2</v>
       </c>
       <c r="AP166">
-        <v>2</v>
+        <v>2.4</v>
       </c>
       <c r="AQ166">
-        <v>1.38</v>
+        <v>1.09</v>
       </c>
       <c r="AR166">
-        <v>1.79</v>
+        <v>1.9</v>
       </c>
       <c r="AS166">
-        <v>1.38</v>
+        <v>1.22</v>
       </c>
       <c r="AT166">
-        <v>3.17</v>
+        <v>3.12</v>
       </c>
       <c r="AU166">
         <v>4</v>
@@ -35533,25 +35533,25 @@
         <v>2.75</v>
       </c>
       <c r="AN167">
-        <v>1.25</v>
+        <v>1</v>
       </c>
       <c r="AO167">
-        <v>0.2</v>
+        <v>0.11</v>
       </c>
       <c r="AP167">
-        <v>1.33</v>
+        <v>1.18</v>
       </c>
       <c r="AQ167">
-        <v>0.19</v>
+        <v>0.1</v>
       </c>
       <c r="AR167">
-        <v>1.47</v>
+        <v>1.6</v>
       </c>
       <c r="AS167">
-        <v>1.14</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="AT167">
-        <v>2.61</v>
+        <v>2.54</v>
       </c>
       <c r="AU167">
         <v>5</v>
@@ -35742,22 +35742,22 @@
         <v>2</v>
       </c>
       <c r="AO168">
-        <v>1.4</v>
+        <v>1.1</v>
       </c>
       <c r="AP168">
-        <v>2.05</v>
+        <v>2.09</v>
       </c>
       <c r="AQ168">
-        <v>1.33</v>
+        <v>1</v>
       </c>
       <c r="AR168">
-        <v>1.82</v>
+        <v>1.96</v>
       </c>
       <c r="AS168">
-        <v>1.38</v>
+        <v>1.29</v>
       </c>
       <c r="AT168">
-        <v>3.2</v>
+        <v>3.25</v>
       </c>
       <c r="AU168">
         <v>13</v>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Czech Republic First League_20242025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Czech Republic First League_20242025.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1070" uniqueCount="280">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1094" uniqueCount="285">
   <si>
     <t>Id_Jogo</t>
   </si>
@@ -616,6 +616,15 @@
     <t>['36', '64', '69']</t>
   </si>
   <si>
+    <t>['9', '65', '74', '90']</t>
+  </si>
+  <si>
+    <t>['67', '88']</t>
+  </si>
+  <si>
+    <t>['5', '10']</t>
+  </si>
+  <si>
     <t>['25']</t>
   </si>
   <si>
@@ -854,6 +863,12 @@
   </si>
   <si>
     <t>['57', '90+5']</t>
+  </si>
+  <si>
+    <t>['30', '48', '73']</t>
+  </si>
+  <si>
+    <t>['20', '45+11', '53']</t>
   </si>
 </sst>
 </file>
@@ -1215,7 +1230,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:BP168"/>
+  <dimension ref="A1:BP172"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:68">
@@ -1471,7 +1486,7 @@
         <v>86</v>
       </c>
       <c r="P2" t="s">
-        <v>200</v>
+        <v>203</v>
       </c>
       <c r="Q2">
         <v>1.53</v>
@@ -1552,7 +1567,7 @@
         <v>2.09</v>
       </c>
       <c r="AQ2">
-        <v>0.55</v>
+        <v>0.5</v>
       </c>
       <c r="AR2">
         <v>0</v>
@@ -1883,7 +1898,7 @@
         <v>88</v>
       </c>
       <c r="P4" t="s">
-        <v>201</v>
+        <v>204</v>
       </c>
       <c r="Q4">
         <v>2.88</v>
@@ -1961,7 +1976,7 @@
         <v>0</v>
       </c>
       <c r="AP4">
-        <v>0.27</v>
+        <v>0.25</v>
       </c>
       <c r="AQ4">
         <v>1.09</v>
@@ -2295,7 +2310,7 @@
         <v>90</v>
       </c>
       <c r="P6" t="s">
-        <v>202</v>
+        <v>205</v>
       </c>
       <c r="Q6">
         <v>5.5</v>
@@ -2501,7 +2516,7 @@
         <v>91</v>
       </c>
       <c r="P7" t="s">
-        <v>203</v>
+        <v>206</v>
       </c>
       <c r="Q7">
         <v>3.2</v>
@@ -2579,7 +2594,7 @@
         <v>0</v>
       </c>
       <c r="AP7">
-        <v>1.45</v>
+        <v>1.33</v>
       </c>
       <c r="AQ7">
         <v>1</v>
@@ -2785,7 +2800,7 @@
         <v>0</v>
       </c>
       <c r="AP8">
-        <v>1.4</v>
+        <v>1.36</v>
       </c>
       <c r="AQ8">
         <v>2.36</v>
@@ -3325,7 +3340,7 @@
         <v>94</v>
       </c>
       <c r="P11" t="s">
-        <v>204</v>
+        <v>207</v>
       </c>
       <c r="Q11">
         <v>6.5</v>
@@ -3406,7 +3421,7 @@
         <v>1.3</v>
       </c>
       <c r="AQ11">
-        <v>2</v>
+        <v>2.09</v>
       </c>
       <c r="AR11">
         <v>0</v>
@@ -3531,7 +3546,7 @@
         <v>88</v>
       </c>
       <c r="P12" t="s">
-        <v>205</v>
+        <v>208</v>
       </c>
       <c r="Q12">
         <v>2.85</v>
@@ -3943,7 +3958,7 @@
         <v>96</v>
       </c>
       <c r="P14" t="s">
-        <v>206</v>
+        <v>209</v>
       </c>
       <c r="Q14">
         <v>2.45</v>
@@ -4436,7 +4451,7 @@
         <v>2.4</v>
       </c>
       <c r="AQ16">
-        <v>1.1</v>
+        <v>1.27</v>
       </c>
       <c r="AR16">
         <v>0</v>
@@ -4767,7 +4782,7 @@
         <v>88</v>
       </c>
       <c r="P18" t="s">
-        <v>207</v>
+        <v>210</v>
       </c>
       <c r="Q18">
         <v>5.4</v>
@@ -5054,7 +5069,7 @@
         <v>2.09</v>
       </c>
       <c r="AQ19">
-        <v>0.3</v>
+        <v>0.36</v>
       </c>
       <c r="AR19">
         <v>1.9</v>
@@ -5257,7 +5272,7 @@
         <v>0</v>
       </c>
       <c r="AP20">
-        <v>1.4</v>
+        <v>1.36</v>
       </c>
       <c r="AQ20">
         <v>1.5</v>
@@ -5669,7 +5684,7 @@
         <v>0</v>
       </c>
       <c r="AP22">
-        <v>1.7</v>
+        <v>1.82</v>
       </c>
       <c r="AQ22">
         <v>0.82</v>
@@ -5797,7 +5812,7 @@
         <v>102</v>
       </c>
       <c r="P23" t="s">
-        <v>208</v>
+        <v>211</v>
       </c>
       <c r="Q23">
         <v>2.6</v>
@@ -5875,10 +5890,10 @@
         <v>0</v>
       </c>
       <c r="AP23">
-        <v>0.27</v>
+        <v>0.25</v>
       </c>
       <c r="AQ23">
-        <v>0.55</v>
+        <v>0.5</v>
       </c>
       <c r="AR23">
         <v>1.33</v>
@@ -6003,7 +6018,7 @@
         <v>103</v>
       </c>
       <c r="P24" t="s">
-        <v>209</v>
+        <v>212</v>
       </c>
       <c r="Q24">
         <v>2.75</v>
@@ -6209,7 +6224,7 @@
         <v>88</v>
       </c>
       <c r="P25" t="s">
-        <v>210</v>
+        <v>213</v>
       </c>
       <c r="Q25">
         <v>1.06</v>
@@ -6290,7 +6305,7 @@
         <v>1</v>
       </c>
       <c r="AQ25">
-        <v>1.1</v>
+        <v>1.27</v>
       </c>
       <c r="AR25">
         <v>0.93</v>
@@ -6415,7 +6430,7 @@
         <v>104</v>
       </c>
       <c r="P26" t="s">
-        <v>211</v>
+        <v>214</v>
       </c>
       <c r="Q26">
         <v>6.23</v>
@@ -6496,7 +6511,7 @@
         <v>1.18</v>
       </c>
       <c r="AQ26">
-        <v>2</v>
+        <v>2.09</v>
       </c>
       <c r="AR26">
         <v>1.73</v>
@@ -7938,7 +7953,7 @@
         <v>1.7</v>
       </c>
       <c r="AQ33">
-        <v>0.3</v>
+        <v>0.36</v>
       </c>
       <c r="AR33">
         <v>1.08</v>
@@ -8063,7 +8078,7 @@
         <v>111</v>
       </c>
       <c r="P34" t="s">
-        <v>212</v>
+        <v>215</v>
       </c>
       <c r="Q34">
         <v>1.45</v>
@@ -8269,7 +8284,7 @@
         <v>112</v>
       </c>
       <c r="P35" t="s">
-        <v>213</v>
+        <v>216</v>
       </c>
       <c r="Q35">
         <v>2.84</v>
@@ -8347,7 +8362,7 @@
         <v>0.5</v>
       </c>
       <c r="AP35">
-        <v>1.45</v>
+        <v>1.33</v>
       </c>
       <c r="AQ35">
         <v>1.5</v>
@@ -8475,7 +8490,7 @@
         <v>113</v>
       </c>
       <c r="P36" t="s">
-        <v>214</v>
+        <v>217</v>
       </c>
       <c r="Q36">
         <v>5.63</v>
@@ -8556,7 +8571,7 @@
         <v>2</v>
       </c>
       <c r="AQ36">
-        <v>2</v>
+        <v>2.09</v>
       </c>
       <c r="AR36">
         <v>1.54</v>
@@ -8681,7 +8696,7 @@
         <v>114</v>
       </c>
       <c r="P37" t="s">
-        <v>215</v>
+        <v>218</v>
       </c>
       <c r="Q37">
         <v>2.58</v>
@@ -8759,7 +8774,7 @@
         <v>0</v>
       </c>
       <c r="AP37">
-        <v>1.7</v>
+        <v>1.82</v>
       </c>
       <c r="AQ37">
         <v>1.2</v>
@@ -8968,7 +8983,7 @@
         <v>1.3</v>
       </c>
       <c r="AQ38">
-        <v>0.55</v>
+        <v>0.5</v>
       </c>
       <c r="AR38">
         <v>1.34</v>
@@ -9093,7 +9108,7 @@
         <v>88</v>
       </c>
       <c r="P39" t="s">
-        <v>216</v>
+        <v>219</v>
       </c>
       <c r="Q39">
         <v>4.75</v>
@@ -9171,7 +9186,7 @@
         <v>2</v>
       </c>
       <c r="AP39">
-        <v>0.27</v>
+        <v>0.25</v>
       </c>
       <c r="AQ39">
         <v>1.7</v>
@@ -9377,7 +9392,7 @@
         <v>0</v>
       </c>
       <c r="AP40">
-        <v>1.4</v>
+        <v>1.36</v>
       </c>
       <c r="AQ40">
         <v>1.64</v>
@@ -9505,7 +9520,7 @@
         <v>117</v>
       </c>
       <c r="P41" t="s">
-        <v>217</v>
+        <v>220</v>
       </c>
       <c r="Q41">
         <v>2.4</v>
@@ -9586,7 +9601,7 @@
         <v>1.18</v>
       </c>
       <c r="AQ41">
-        <v>1.1</v>
+        <v>1.27</v>
       </c>
       <c r="AR41">
         <v>1.49</v>
@@ -9711,7 +9726,7 @@
         <v>107</v>
       </c>
       <c r="P42" t="s">
-        <v>218</v>
+        <v>221</v>
       </c>
       <c r="Q42">
         <v>2.61</v>
@@ -9917,7 +9932,7 @@
         <v>118</v>
       </c>
       <c r="P43" t="s">
-        <v>219</v>
+        <v>222</v>
       </c>
       <c r="Q43">
         <v>1.69</v>
@@ -10819,7 +10834,7 @@
         <v>0</v>
       </c>
       <c r="AP47">
-        <v>1.45</v>
+        <v>1.33</v>
       </c>
       <c r="AQ47">
         <v>1.64</v>
@@ -11025,7 +11040,7 @@
         <v>1.33</v>
       </c>
       <c r="AP48">
-        <v>0.27</v>
+        <v>0.25</v>
       </c>
       <c r="AQ48">
         <v>1.5</v>
@@ -11231,10 +11246,10 @@
         <v>2</v>
       </c>
       <c r="AP49">
-        <v>1.4</v>
+        <v>1.36</v>
       </c>
       <c r="AQ49">
-        <v>1.1</v>
+        <v>1.27</v>
       </c>
       <c r="AR49">
         <v>1.24</v>
@@ -11359,7 +11374,7 @@
         <v>88</v>
       </c>
       <c r="P50" t="s">
-        <v>220</v>
+        <v>223</v>
       </c>
       <c r="Q50">
         <v>5.1</v>
@@ -11440,7 +11455,7 @@
         <v>1.7</v>
       </c>
       <c r="AQ50">
-        <v>2</v>
+        <v>2.09</v>
       </c>
       <c r="AR50">
         <v>1.24</v>
@@ -11643,10 +11658,10 @@
         <v>0</v>
       </c>
       <c r="AP51">
-        <v>1.45</v>
+        <v>1.33</v>
       </c>
       <c r="AQ51">
-        <v>0.3</v>
+        <v>0.36</v>
       </c>
       <c r="AR51">
         <v>1.76</v>
@@ -11771,7 +11786,7 @@
         <v>122</v>
       </c>
       <c r="P52" t="s">
-        <v>221</v>
+        <v>224</v>
       </c>
       <c r="Q52">
         <v>3</v>
@@ -11849,7 +11864,7 @@
         <v>0.33</v>
       </c>
       <c r="AP52">
-        <v>1.7</v>
+        <v>1.82</v>
       </c>
       <c r="AQ52">
         <v>1.64</v>
@@ -12058,7 +12073,7 @@
         <v>3</v>
       </c>
       <c r="AQ53">
-        <v>0.55</v>
+        <v>0.5</v>
       </c>
       <c r="AR53">
         <v>2.35</v>
@@ -12183,7 +12198,7 @@
         <v>124</v>
       </c>
       <c r="P54" t="s">
-        <v>222</v>
+        <v>225</v>
       </c>
       <c r="Q54">
         <v>3</v>
@@ -12595,7 +12610,7 @@
         <v>125</v>
       </c>
       <c r="P56" t="s">
-        <v>223</v>
+        <v>226</v>
       </c>
       <c r="Q56">
         <v>1.85</v>
@@ -12801,7 +12816,7 @@
         <v>88</v>
       </c>
       <c r="P57" t="s">
-        <v>224</v>
+        <v>227</v>
       </c>
       <c r="Q57">
         <v>5.88</v>
@@ -13213,7 +13228,7 @@
         <v>127</v>
       </c>
       <c r="P59" t="s">
-        <v>225</v>
+        <v>228</v>
       </c>
       <c r="Q59">
         <v>3.86</v>
@@ -13497,10 +13512,10 @@
         <v>1.75</v>
       </c>
       <c r="AP60">
-        <v>1.45</v>
+        <v>1.33</v>
       </c>
       <c r="AQ60">
-        <v>1.1</v>
+        <v>1.27</v>
       </c>
       <c r="AR60">
         <v>1.83</v>
@@ -13831,7 +13846,7 @@
         <v>130</v>
       </c>
       <c r="P62" t="s">
-        <v>226</v>
+        <v>229</v>
       </c>
       <c r="Q62">
         <v>1.83</v>
@@ -13912,7 +13927,7 @@
         <v>1.73</v>
       </c>
       <c r="AQ62">
-        <v>0.55</v>
+        <v>0.5</v>
       </c>
       <c r="AR62">
         <v>1.42</v>
@@ -14037,7 +14052,7 @@
         <v>88</v>
       </c>
       <c r="P63" t="s">
-        <v>227</v>
+        <v>230</v>
       </c>
       <c r="Q63">
         <v>8.77</v>
@@ -14115,10 +14130,10 @@
         <v>3</v>
       </c>
       <c r="AP63">
-        <v>0.27</v>
+        <v>0.25</v>
       </c>
       <c r="AQ63">
-        <v>2</v>
+        <v>2.09</v>
       </c>
       <c r="AR63">
         <v>1.37</v>
@@ -14321,10 +14336,10 @@
         <v>0.33</v>
       </c>
       <c r="AP64">
-        <v>1.7</v>
+        <v>1.82</v>
       </c>
       <c r="AQ64">
-        <v>0.3</v>
+        <v>0.36</v>
       </c>
       <c r="AR64">
         <v>1.75</v>
@@ -14449,7 +14464,7 @@
         <v>132</v>
       </c>
       <c r="P65" t="s">
-        <v>228</v>
+        <v>231</v>
       </c>
       <c r="Q65">
         <v>2.4</v>
@@ -14655,7 +14670,7 @@
         <v>133</v>
       </c>
       <c r="P66" t="s">
-        <v>229</v>
+        <v>232</v>
       </c>
       <c r="Q66">
         <v>1.55</v>
@@ -14861,7 +14876,7 @@
         <v>134</v>
       </c>
       <c r="P67" t="s">
-        <v>230</v>
+        <v>233</v>
       </c>
       <c r="Q67">
         <v>4</v>
@@ -15067,7 +15082,7 @@
         <v>88</v>
       </c>
       <c r="P68" t="s">
-        <v>231</v>
+        <v>234</v>
       </c>
       <c r="Q68">
         <v>3.1</v>
@@ -15351,7 +15366,7 @@
         <v>2</v>
       </c>
       <c r="AP69">
-        <v>1.4</v>
+        <v>1.36</v>
       </c>
       <c r="AQ69">
         <v>0.89</v>
@@ -15891,7 +15906,7 @@
         <v>124</v>
       </c>
       <c r="P72" t="s">
-        <v>232</v>
+        <v>235</v>
       </c>
       <c r="Q72">
         <v>1.88</v>
@@ -16097,7 +16112,7 @@
         <v>88</v>
       </c>
       <c r="P73" t="s">
-        <v>233</v>
+        <v>236</v>
       </c>
       <c r="Q73">
         <v>7</v>
@@ -16381,7 +16396,7 @@
         <v>0</v>
       </c>
       <c r="AP74">
-        <v>1.45</v>
+        <v>1.33</v>
       </c>
       <c r="AQ74">
         <v>1</v>
@@ -16509,7 +16524,7 @@
         <v>138</v>
       </c>
       <c r="P75" t="s">
-        <v>234</v>
+        <v>237</v>
       </c>
       <c r="Q75">
         <v>2.3</v>
@@ -16590,7 +16605,7 @@
         <v>1.3</v>
       </c>
       <c r="AQ75">
-        <v>0.3</v>
+        <v>0.36</v>
       </c>
       <c r="AR75">
         <v>1.49</v>
@@ -16715,7 +16730,7 @@
         <v>88</v>
       </c>
       <c r="P76" t="s">
-        <v>235</v>
+        <v>238</v>
       </c>
       <c r="Q76">
         <v>3.7</v>
@@ -16793,7 +16808,7 @@
         <v>1</v>
       </c>
       <c r="AP76">
-        <v>0.27</v>
+        <v>0.25</v>
       </c>
       <c r="AQ76">
         <v>1</v>
@@ -16921,7 +16936,7 @@
         <v>88</v>
       </c>
       <c r="P77" t="s">
-        <v>236</v>
+        <v>239</v>
       </c>
       <c r="Q77">
         <v>2.47</v>
@@ -17002,7 +17017,7 @@
         <v>1.3</v>
       </c>
       <c r="AQ77">
-        <v>1.1</v>
+        <v>1.27</v>
       </c>
       <c r="AR77">
         <v>1.45</v>
@@ -17208,7 +17223,7 @@
         <v>2.64</v>
       </c>
       <c r="AQ78">
-        <v>0.55</v>
+        <v>0.5</v>
       </c>
       <c r="AR78">
         <v>1.78</v>
@@ -17539,7 +17554,7 @@
         <v>140</v>
       </c>
       <c r="P80" t="s">
-        <v>237</v>
+        <v>240</v>
       </c>
       <c r="Q80">
         <v>2.5</v>
@@ -17617,7 +17632,7 @@
         <v>1.2</v>
       </c>
       <c r="AP80">
-        <v>1.7</v>
+        <v>1.82</v>
       </c>
       <c r="AQ80">
         <v>1.5</v>
@@ -17745,7 +17760,7 @@
         <v>141</v>
       </c>
       <c r="P81" t="s">
-        <v>238</v>
+        <v>241</v>
       </c>
       <c r="Q81">
         <v>2.38</v>
@@ -17826,7 +17841,7 @@
         <v>3</v>
       </c>
       <c r="AQ81">
-        <v>2</v>
+        <v>2.09</v>
       </c>
       <c r="AR81">
         <v>2.43</v>
@@ -17951,7 +17966,7 @@
         <v>142</v>
       </c>
       <c r="P82" t="s">
-        <v>239</v>
+        <v>242</v>
       </c>
       <c r="Q82">
         <v>2.8</v>
@@ -18157,7 +18172,7 @@
         <v>143</v>
       </c>
       <c r="P83" t="s">
-        <v>240</v>
+        <v>243</v>
       </c>
       <c r="Q83">
         <v>2.6</v>
@@ -18238,7 +18253,7 @@
         <v>1</v>
       </c>
       <c r="AQ83">
-        <v>0.55</v>
+        <v>0.5</v>
       </c>
       <c r="AR83">
         <v>1.14</v>
@@ -18363,7 +18378,7 @@
         <v>144</v>
       </c>
       <c r="P84" t="s">
-        <v>241</v>
+        <v>244</v>
       </c>
       <c r="Q84">
         <v>3.4</v>
@@ -18775,7 +18790,7 @@
         <v>146</v>
       </c>
       <c r="P86" t="s">
-        <v>242</v>
+        <v>245</v>
       </c>
       <c r="Q86">
         <v>2.88</v>
@@ -19059,7 +19074,7 @@
         <v>0</v>
       </c>
       <c r="AP87">
-        <v>1.45</v>
+        <v>1.33</v>
       </c>
       <c r="AQ87">
         <v>0.1</v>
@@ -19187,7 +19202,7 @@
         <v>88</v>
       </c>
       <c r="P88" t="s">
-        <v>243</v>
+        <v>246</v>
       </c>
       <c r="Q88">
         <v>2.6</v>
@@ -19265,7 +19280,7 @@
         <v>0.75</v>
       </c>
       <c r="AP88">
-        <v>1.4</v>
+        <v>1.36</v>
       </c>
       <c r="AQ88">
         <v>0.82</v>
@@ -19393,7 +19408,7 @@
         <v>93</v>
       </c>
       <c r="P89" t="s">
-        <v>244</v>
+        <v>247</v>
       </c>
       <c r="Q89">
         <v>6.5</v>
@@ -19805,7 +19820,7 @@
         <v>149</v>
       </c>
       <c r="P91" t="s">
-        <v>245</v>
+        <v>248</v>
       </c>
       <c r="Q91">
         <v>4.7</v>
@@ -20011,7 +20026,7 @@
         <v>88</v>
       </c>
       <c r="P92" t="s">
-        <v>246</v>
+        <v>249</v>
       </c>
       <c r="Q92">
         <v>3.8</v>
@@ -20089,7 +20104,7 @@
         <v>0.2</v>
       </c>
       <c r="AP92">
-        <v>0.27</v>
+        <v>0.25</v>
       </c>
       <c r="AQ92">
         <v>1</v>
@@ -20295,10 +20310,10 @@
         <v>1.67</v>
       </c>
       <c r="AP93">
-        <v>1.7</v>
+        <v>1.82</v>
       </c>
       <c r="AQ93">
-        <v>1.1</v>
+        <v>1.27</v>
       </c>
       <c r="AR93">
         <v>1.61</v>
@@ -20423,7 +20438,7 @@
         <v>150</v>
       </c>
       <c r="P94" t="s">
-        <v>247</v>
+        <v>250</v>
       </c>
       <c r="Q94">
         <v>3</v>
@@ -20916,7 +20931,7 @@
         <v>3</v>
       </c>
       <c r="AQ96">
-        <v>0.3</v>
+        <v>0.36</v>
       </c>
       <c r="AR96">
         <v>2.31</v>
@@ -21122,7 +21137,7 @@
         <v>2.64</v>
       </c>
       <c r="AQ97">
-        <v>2</v>
+        <v>2.09</v>
       </c>
       <c r="AR97">
         <v>1.81</v>
@@ -21737,7 +21752,7 @@
         <v>1.33</v>
       </c>
       <c r="AP100">
-        <v>1.45</v>
+        <v>1.33</v>
       </c>
       <c r="AQ100">
         <v>1.09</v>
@@ -21865,7 +21880,7 @@
         <v>156</v>
       </c>
       <c r="P101" t="s">
-        <v>248</v>
+        <v>251</v>
       </c>
       <c r="Q101">
         <v>1.83</v>
@@ -22149,7 +22164,7 @@
         <v>1.2</v>
       </c>
       <c r="AP102">
-        <v>0.27</v>
+        <v>0.25</v>
       </c>
       <c r="AQ102">
         <v>1</v>
@@ -22358,7 +22373,7 @@
         <v>1.18</v>
       </c>
       <c r="AQ103">
-        <v>0.55</v>
+        <v>0.5</v>
       </c>
       <c r="AR103">
         <v>1.41</v>
@@ -22561,7 +22576,7 @@
         <v>1.83</v>
       </c>
       <c r="AP104">
-        <v>1.4</v>
+        <v>1.36</v>
       </c>
       <c r="AQ104">
         <v>1.7</v>
@@ -22976,7 +22991,7 @@
         <v>2.4</v>
       </c>
       <c r="AQ106">
-        <v>0.3</v>
+        <v>0.36</v>
       </c>
       <c r="AR106">
         <v>1.87</v>
@@ -23182,7 +23197,7 @@
         <v>0.9</v>
       </c>
       <c r="AQ107">
-        <v>1.1</v>
+        <v>1.27</v>
       </c>
       <c r="AR107">
         <v>1.14</v>
@@ -23513,7 +23528,7 @@
         <v>161</v>
       </c>
       <c r="P109" t="s">
-        <v>249</v>
+        <v>252</v>
       </c>
       <c r="Q109">
         <v>2.24</v>
@@ -23719,7 +23734,7 @@
         <v>162</v>
       </c>
       <c r="P110" t="s">
-        <v>250</v>
+        <v>253</v>
       </c>
       <c r="Q110">
         <v>4.6</v>
@@ -23800,7 +23815,7 @@
         <v>1.73</v>
       </c>
       <c r="AQ110">
-        <v>2</v>
+        <v>2.09</v>
       </c>
       <c r="AR110">
         <v>1.51</v>
@@ -24131,7 +24146,7 @@
         <v>164</v>
       </c>
       <c r="P112" t="s">
-        <v>206</v>
+        <v>209</v>
       </c>
       <c r="Q112">
         <v>1.44</v>
@@ -24337,7 +24352,7 @@
         <v>165</v>
       </c>
       <c r="P113" t="s">
-        <v>251</v>
+        <v>254</v>
       </c>
       <c r="Q113">
         <v>3.25</v>
@@ -24543,7 +24558,7 @@
         <v>99</v>
       </c>
       <c r="P114" t="s">
-        <v>252</v>
+        <v>255</v>
       </c>
       <c r="Q114">
         <v>1.73</v>
@@ -24749,7 +24764,7 @@
         <v>151</v>
       </c>
       <c r="P115" t="s">
-        <v>253</v>
+        <v>256</v>
       </c>
       <c r="Q115">
         <v>2.88</v>
@@ -24827,7 +24842,7 @@
         <v>1.14</v>
       </c>
       <c r="AP115">
-        <v>1.4</v>
+        <v>1.36</v>
       </c>
       <c r="AQ115">
         <v>1.2</v>
@@ -24955,7 +24970,7 @@
         <v>88</v>
       </c>
       <c r="P116" t="s">
-        <v>254</v>
+        <v>257</v>
       </c>
       <c r="Q116">
         <v>4.33</v>
@@ -25242,7 +25257,7 @@
         <v>1.18</v>
       </c>
       <c r="AQ117">
-        <v>0.3</v>
+        <v>0.36</v>
       </c>
       <c r="AR117">
         <v>1.44</v>
@@ -25367,7 +25382,7 @@
         <v>88</v>
       </c>
       <c r="P118" t="s">
-        <v>255</v>
+        <v>258</v>
       </c>
       <c r="Q118">
         <v>15</v>
@@ -25445,7 +25460,7 @@
         <v>2.33</v>
       </c>
       <c r="AP118">
-        <v>0.27</v>
+        <v>0.25</v>
       </c>
       <c r="AQ118">
         <v>2.36</v>
@@ -25651,10 +25666,10 @@
         <v>0.63</v>
       </c>
       <c r="AP119">
-        <v>1.45</v>
+        <v>1.33</v>
       </c>
       <c r="AQ119">
-        <v>0.55</v>
+        <v>0.5</v>
       </c>
       <c r="AR119">
         <v>1.64</v>
@@ -25779,7 +25794,7 @@
         <v>168</v>
       </c>
       <c r="P120" t="s">
-        <v>256</v>
+        <v>259</v>
       </c>
       <c r="Q120">
         <v>3</v>
@@ -25857,7 +25872,7 @@
         <v>1.17</v>
       </c>
       <c r="AP120">
-        <v>1.7</v>
+        <v>1.82</v>
       </c>
       <c r="AQ120">
         <v>1</v>
@@ -26063,7 +26078,7 @@
         <v>1.17</v>
       </c>
       <c r="AP121">
-        <v>1.7</v>
+        <v>1.82</v>
       </c>
       <c r="AQ121">
         <v>1</v>
@@ -26191,7 +26206,7 @@
         <v>170</v>
       </c>
       <c r="P122" t="s">
-        <v>257</v>
+        <v>260</v>
       </c>
       <c r="Q122">
         <v>3.25</v>
@@ -26397,7 +26412,7 @@
         <v>171</v>
       </c>
       <c r="P123" t="s">
-        <v>205</v>
+        <v>208</v>
       </c>
       <c r="Q123">
         <v>1.83</v>
@@ -26809,7 +26824,7 @@
         <v>172</v>
       </c>
       <c r="P125" t="s">
-        <v>258</v>
+        <v>261</v>
       </c>
       <c r="Q125">
         <v>6.3</v>
@@ -26890,7 +26905,7 @@
         <v>1</v>
       </c>
       <c r="AQ125">
-        <v>2</v>
+        <v>2.09</v>
       </c>
       <c r="AR125">
         <v>1.21</v>
@@ -27633,7 +27648,7 @@
         <v>174</v>
       </c>
       <c r="P129" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="Q129">
         <v>2.1</v>
@@ -27714,7 +27729,7 @@
         <v>2.64</v>
       </c>
       <c r="AQ129">
-        <v>1.1</v>
+        <v>1.27</v>
       </c>
       <c r="AR129">
         <v>1.69</v>
@@ -27839,7 +27854,7 @@
         <v>175</v>
       </c>
       <c r="P130" t="s">
-        <v>260</v>
+        <v>263</v>
       </c>
       <c r="Q130">
         <v>1.5</v>
@@ -28251,7 +28266,7 @@
         <v>177</v>
       </c>
       <c r="P132" t="s">
-        <v>261</v>
+        <v>264</v>
       </c>
       <c r="Q132">
         <v>4.04</v>
@@ -28457,7 +28472,7 @@
         <v>178</v>
       </c>
       <c r="P133" t="s">
-        <v>262</v>
+        <v>265</v>
       </c>
       <c r="Q133">
         <v>3.5</v>
@@ -28663,7 +28678,7 @@
         <v>88</v>
       </c>
       <c r="P134" t="s">
-        <v>263</v>
+        <v>266</v>
       </c>
       <c r="Q134">
         <v>2.75</v>
@@ -29075,7 +29090,7 @@
         <v>88</v>
       </c>
       <c r="P136" t="s">
-        <v>264</v>
+        <v>267</v>
       </c>
       <c r="Q136">
         <v>4.5</v>
@@ -29487,7 +29502,7 @@
         <v>91</v>
       </c>
       <c r="P138" t="s">
-        <v>251</v>
+        <v>254</v>
       </c>
       <c r="Q138">
         <v>2.25</v>
@@ -29565,10 +29580,10 @@
         <v>0.5600000000000001</v>
       </c>
       <c r="AP138">
-        <v>1.4</v>
+        <v>1.36</v>
       </c>
       <c r="AQ138">
-        <v>0.55</v>
+        <v>0.5</v>
       </c>
       <c r="AR138">
         <v>1.11</v>
@@ -29693,7 +29708,7 @@
         <v>179</v>
       </c>
       <c r="P139" t="s">
-        <v>260</v>
+        <v>263</v>
       </c>
       <c r="Q139">
         <v>1.9</v>
@@ -29774,7 +29789,7 @@
         <v>2</v>
       </c>
       <c r="AQ139">
-        <v>0.3</v>
+        <v>0.36</v>
       </c>
       <c r="AR139">
         <v>1.71</v>
@@ -30105,7 +30120,7 @@
         <v>117</v>
       </c>
       <c r="P141" t="s">
-        <v>265</v>
+        <v>268</v>
       </c>
       <c r="Q141">
         <v>4</v>
@@ -30183,7 +30198,7 @@
         <v>1.75</v>
       </c>
       <c r="AP141">
-        <v>1.45</v>
+        <v>1.33</v>
       </c>
       <c r="AQ141">
         <v>1.7</v>
@@ -30311,7 +30326,7 @@
         <v>88</v>
       </c>
       <c r="P142" t="s">
-        <v>266</v>
+        <v>269</v>
       </c>
       <c r="Q142">
         <v>4</v>
@@ -30389,7 +30404,7 @@
         <v>1.13</v>
       </c>
       <c r="AP142">
-        <v>0.27</v>
+        <v>0.25</v>
       </c>
       <c r="AQ142">
         <v>1.2</v>
@@ -30723,7 +30738,7 @@
         <v>182</v>
       </c>
       <c r="P144" t="s">
-        <v>267</v>
+        <v>270</v>
       </c>
       <c r="Q144">
         <v>6</v>
@@ -30801,7 +30816,7 @@
         <v>2.5</v>
       </c>
       <c r="AP144">
-        <v>1.7</v>
+        <v>1.82</v>
       </c>
       <c r="AQ144">
         <v>2.36</v>
@@ -30929,7 +30944,7 @@
         <v>88</v>
       </c>
       <c r="P145" t="s">
-        <v>268</v>
+        <v>271</v>
       </c>
       <c r="Q145">
         <v>3.5</v>
@@ -31135,7 +31150,7 @@
         <v>183</v>
       </c>
       <c r="P146" t="s">
-        <v>269</v>
+        <v>272</v>
       </c>
       <c r="Q146">
         <v>4.33</v>
@@ -31341,7 +31356,7 @@
         <v>184</v>
       </c>
       <c r="P147" t="s">
-        <v>270</v>
+        <v>273</v>
       </c>
       <c r="Q147">
         <v>3.8</v>
@@ -31547,7 +31562,7 @@
         <v>185</v>
       </c>
       <c r="P148" t="s">
-        <v>271</v>
+        <v>274</v>
       </c>
       <c r="Q148">
         <v>2.5</v>
@@ -31753,7 +31768,7 @@
         <v>186</v>
       </c>
       <c r="P149" t="s">
-        <v>268</v>
+        <v>271</v>
       </c>
       <c r="Q149">
         <v>2.05</v>
@@ -31959,7 +31974,7 @@
         <v>187</v>
       </c>
       <c r="P150" t="s">
-        <v>272</v>
+        <v>275</v>
       </c>
       <c r="Q150">
         <v>1.95</v>
@@ -32040,7 +32055,7 @@
         <v>2.09</v>
       </c>
       <c r="AQ150">
-        <v>1.1</v>
+        <v>1.27</v>
       </c>
       <c r="AR150">
         <v>1.98</v>
@@ -32165,7 +32180,7 @@
         <v>188</v>
       </c>
       <c r="P151" t="s">
-        <v>273</v>
+        <v>276</v>
       </c>
       <c r="Q151">
         <v>2.48</v>
@@ -32577,7 +32592,7 @@
         <v>190</v>
       </c>
       <c r="P153" t="s">
-        <v>274</v>
+        <v>277</v>
       </c>
       <c r="Q153">
         <v>1.4</v>
@@ -32861,7 +32876,7 @@
         <v>0.89</v>
       </c>
       <c r="AP154">
-        <v>1.45</v>
+        <v>1.33</v>
       </c>
       <c r="AQ154">
         <v>0.82</v>
@@ -33067,10 +33082,10 @@
         <v>0.22</v>
       </c>
       <c r="AP155">
-        <v>0.27</v>
+        <v>0.25</v>
       </c>
       <c r="AQ155">
-        <v>0.3</v>
+        <v>0.36</v>
       </c>
       <c r="AR155">
         <v>1.34</v>
@@ -33195,7 +33210,7 @@
         <v>88</v>
       </c>
       <c r="P156" t="s">
-        <v>209</v>
+        <v>212</v>
       </c>
       <c r="Q156">
         <v>3.2</v>
@@ -33482,7 +33497,7 @@
         <v>1.7</v>
       </c>
       <c r="AQ157">
-        <v>0.55</v>
+        <v>0.5</v>
       </c>
       <c r="AR157">
         <v>1.43</v>
@@ -33607,7 +33622,7 @@
         <v>88</v>
       </c>
       <c r="P158" t="s">
-        <v>275</v>
+        <v>278</v>
       </c>
       <c r="Q158">
         <v>5</v>
@@ -33685,10 +33700,10 @@
         <v>1.89</v>
       </c>
       <c r="AP158">
-        <v>1.4</v>
+        <v>1.36</v>
       </c>
       <c r="AQ158">
-        <v>2</v>
+        <v>2.09</v>
       </c>
       <c r="AR158">
         <v>1.21</v>
@@ -33813,7 +33828,7 @@
         <v>88</v>
       </c>
       <c r="P159" t="s">
-        <v>231</v>
+        <v>234</v>
       </c>
       <c r="Q159">
         <v>2.38</v>
@@ -34225,7 +34240,7 @@
         <v>193</v>
       </c>
       <c r="P161" t="s">
-        <v>258</v>
+        <v>261</v>
       </c>
       <c r="Q161">
         <v>4.75</v>
@@ -34303,7 +34318,7 @@
         <v>1.89</v>
       </c>
       <c r="AP161">
-        <v>1.7</v>
+        <v>1.82</v>
       </c>
       <c r="AQ161">
         <v>1.7</v>
@@ -34431,7 +34446,7 @@
         <v>194</v>
       </c>
       <c r="P162" t="s">
-        <v>276</v>
+        <v>279</v>
       </c>
       <c r="Q162">
         <v>2.63</v>
@@ -34637,7 +34652,7 @@
         <v>88</v>
       </c>
       <c r="P163" t="s">
-        <v>277</v>
+        <v>280</v>
       </c>
       <c r="Q163">
         <v>11</v>
@@ -34843,7 +34858,7 @@
         <v>195</v>
       </c>
       <c r="P164" t="s">
-        <v>278</v>
+        <v>281</v>
       </c>
       <c r="Q164">
         <v>2</v>
@@ -35049,7 +35064,7 @@
         <v>196</v>
       </c>
       <c r="P165" t="s">
-        <v>279</v>
+        <v>282</v>
       </c>
       <c r="Q165">
         <v>2.5</v>
@@ -35824,6 +35839,830 @@
       </c>
       <c r="BP168">
         <v>1.4</v>
+      </c>
+    </row>
+    <row r="169" spans="1:68">
+      <c r="A169" s="1">
+        <v>168</v>
+      </c>
+      <c r="B169">
+        <v>7468249</v>
+      </c>
+      <c r="C169" t="s">
+        <v>68</v>
+      </c>
+      <c r="D169" t="s">
+        <v>69</v>
+      </c>
+      <c r="E169" s="2">
+        <v>45703.39583333334</v>
+      </c>
+      <c r="F169">
+        <v>22</v>
+      </c>
+      <c r="G169" t="s">
+        <v>85</v>
+      </c>
+      <c r="H169" t="s">
+        <v>79</v>
+      </c>
+      <c r="I169">
+        <v>1</v>
+      </c>
+      <c r="J169">
+        <v>0</v>
+      </c>
+      <c r="K169">
+        <v>1</v>
+      </c>
+      <c r="L169">
+        <v>4</v>
+      </c>
+      <c r="M169">
+        <v>0</v>
+      </c>
+      <c r="N169">
+        <v>4</v>
+      </c>
+      <c r="O169" t="s">
+        <v>200</v>
+      </c>
+      <c r="P169" t="s">
+        <v>88</v>
+      </c>
+      <c r="Q169">
+        <v>2.27</v>
+      </c>
+      <c r="R169">
+        <v>2.24</v>
+      </c>
+      <c r="S169">
+        <v>5</v>
+      </c>
+      <c r="T169">
+        <v>1.39</v>
+      </c>
+      <c r="U169">
+        <v>2.8</v>
+      </c>
+      <c r="V169">
+        <v>2.7</v>
+      </c>
+      <c r="W169">
+        <v>1.41</v>
+      </c>
+      <c r="X169">
+        <v>6.45</v>
+      </c>
+      <c r="Y169">
+        <v>1.06</v>
+      </c>
+      <c r="Z169">
+        <v>1.64</v>
+      </c>
+      <c r="AA169">
+        <v>3.97</v>
+      </c>
+      <c r="AB169">
+        <v>5.05</v>
+      </c>
+      <c r="AC169">
+        <v>1.01</v>
+      </c>
+      <c r="AD169">
+        <v>9</v>
+      </c>
+      <c r="AE169">
+        <v>1.29</v>
+      </c>
+      <c r="AF169">
+        <v>3.25</v>
+      </c>
+      <c r="AG169">
+        <v>1.89</v>
+      </c>
+      <c r="AH169">
+        <v>1.93</v>
+      </c>
+      <c r="AI169">
+        <v>1.84</v>
+      </c>
+      <c r="AJ169">
+        <v>1.86</v>
+      </c>
+      <c r="AK169">
+        <v>1.19</v>
+      </c>
+      <c r="AL169">
+        <v>1.24</v>
+      </c>
+      <c r="AM169">
+        <v>2.03</v>
+      </c>
+      <c r="AN169">
+        <v>1.7</v>
+      </c>
+      <c r="AO169">
+        <v>0.55</v>
+      </c>
+      <c r="AP169">
+        <v>1.82</v>
+      </c>
+      <c r="AQ169">
+        <v>0.5</v>
+      </c>
+      <c r="AR169">
+        <v>1.54</v>
+      </c>
+      <c r="AS169">
+        <v>1.05</v>
+      </c>
+      <c r="AT169">
+        <v>2.59</v>
+      </c>
+      <c r="AU169">
+        <v>9</v>
+      </c>
+      <c r="AV169">
+        <v>2</v>
+      </c>
+      <c r="AW169">
+        <v>6</v>
+      </c>
+      <c r="AX169">
+        <v>4</v>
+      </c>
+      <c r="AY169">
+        <v>15</v>
+      </c>
+      <c r="AZ169">
+        <v>6</v>
+      </c>
+      <c r="BA169">
+        <v>3</v>
+      </c>
+      <c r="BB169">
+        <v>1</v>
+      </c>
+      <c r="BC169">
+        <v>4</v>
+      </c>
+      <c r="BD169">
+        <v>1.58</v>
+      </c>
+      <c r="BE169">
+        <v>6.4</v>
+      </c>
+      <c r="BF169">
+        <v>2.65</v>
+      </c>
+      <c r="BG169">
+        <v>1.43</v>
+      </c>
+      <c r="BH169">
+        <v>2.63</v>
+      </c>
+      <c r="BI169">
+        <v>1.72</v>
+      </c>
+      <c r="BJ169">
+        <v>1.98</v>
+      </c>
+      <c r="BK169">
+        <v>2.15</v>
+      </c>
+      <c r="BL169">
+        <v>1.61</v>
+      </c>
+      <c r="BM169">
+        <v>2.8</v>
+      </c>
+      <c r="BN169">
+        <v>1.38</v>
+      </c>
+      <c r="BO169">
+        <v>3.65</v>
+      </c>
+      <c r="BP169">
+        <v>1.23</v>
+      </c>
+    </row>
+    <row r="170" spans="1:68">
+      <c r="A170" s="1">
+        <v>169</v>
+      </c>
+      <c r="B170">
+        <v>7468252</v>
+      </c>
+      <c r="C170" t="s">
+        <v>68</v>
+      </c>
+      <c r="D170" t="s">
+        <v>69</v>
+      </c>
+      <c r="E170" s="2">
+        <v>45703.5</v>
+      </c>
+      <c r="F170">
+        <v>22</v>
+      </c>
+      <c r="G170" t="s">
+        <v>76</v>
+      </c>
+      <c r="H170" t="s">
+        <v>74</v>
+      </c>
+      <c r="I170">
+        <v>0</v>
+      </c>
+      <c r="J170">
+        <v>0</v>
+      </c>
+      <c r="K170">
+        <v>0</v>
+      </c>
+      <c r="L170">
+        <v>0</v>
+      </c>
+      <c r="M170">
+        <v>0</v>
+      </c>
+      <c r="N170">
+        <v>0</v>
+      </c>
+      <c r="O170" t="s">
+        <v>88</v>
+      </c>
+      <c r="P170" t="s">
+        <v>88</v>
+      </c>
+      <c r="Q170">
+        <v>2.39</v>
+      </c>
+      <c r="R170">
+        <v>2.1</v>
+      </c>
+      <c r="S170">
+        <v>5.2</v>
+      </c>
+      <c r="T170">
+        <v>1.47</v>
+      </c>
+      <c r="U170">
+        <v>2.5</v>
+      </c>
+      <c r="V170">
+        <v>3.1</v>
+      </c>
+      <c r="W170">
+        <v>1.33</v>
+      </c>
+      <c r="X170">
+        <v>9.4</v>
+      </c>
+      <c r="Y170">
+        <v>1.01</v>
+      </c>
+      <c r="Z170">
+        <v>1.76</v>
+      </c>
+      <c r="AA170">
+        <v>3.25</v>
+      </c>
+      <c r="AB170">
+        <v>4.4</v>
+      </c>
+      <c r="AC170">
+        <v>1.01</v>
+      </c>
+      <c r="AD170">
+        <v>9</v>
+      </c>
+      <c r="AE170">
+        <v>1.39</v>
+      </c>
+      <c r="AF170">
+        <v>2.75</v>
+      </c>
+      <c r="AG170">
+        <v>2.18</v>
+      </c>
+      <c r="AH170">
+        <v>1.64</v>
+      </c>
+      <c r="AI170">
+        <v>2.04</v>
+      </c>
+      <c r="AJ170">
+        <v>1.7</v>
+      </c>
+      <c r="AK170">
+        <v>1.19</v>
+      </c>
+      <c r="AL170">
+        <v>1.27</v>
+      </c>
+      <c r="AM170">
+        <v>1.96</v>
+      </c>
+      <c r="AN170">
+        <v>1.4</v>
+      </c>
+      <c r="AO170">
+        <v>0.3</v>
+      </c>
+      <c r="AP170">
+        <v>1.36</v>
+      </c>
+      <c r="AQ170">
+        <v>0.36</v>
+      </c>
+      <c r="AR170">
+        <v>1.21</v>
+      </c>
+      <c r="AS170">
+        <v>0.9</v>
+      </c>
+      <c r="AT170">
+        <v>2.11</v>
+      </c>
+      <c r="AU170">
+        <v>3</v>
+      </c>
+      <c r="AV170">
+        <v>5</v>
+      </c>
+      <c r="AW170">
+        <v>7</v>
+      </c>
+      <c r="AX170">
+        <v>2</v>
+      </c>
+      <c r="AY170">
+        <v>11</v>
+      </c>
+      <c r="AZ170">
+        <v>7</v>
+      </c>
+      <c r="BA170">
+        <v>2</v>
+      </c>
+      <c r="BB170">
+        <v>2</v>
+      </c>
+      <c r="BC170">
+        <v>4</v>
+      </c>
+      <c r="BD170">
+        <v>1.55</v>
+      </c>
+      <c r="BE170">
+        <v>6.4</v>
+      </c>
+      <c r="BF170">
+        <v>2.7</v>
+      </c>
+      <c r="BG170">
+        <v>1.49</v>
+      </c>
+      <c r="BH170">
+        <v>2.4</v>
+      </c>
+      <c r="BI170">
+        <v>1.81</v>
+      </c>
+      <c r="BJ170">
+        <v>1.88</v>
+      </c>
+      <c r="BK170">
+        <v>2.32</v>
+      </c>
+      <c r="BL170">
+        <v>1.53</v>
+      </c>
+      <c r="BM170">
+        <v>3.05</v>
+      </c>
+      <c r="BN170">
+        <v>1.32</v>
+      </c>
+      <c r="BO170">
+        <v>4.1</v>
+      </c>
+      <c r="BP170">
+        <v>1.19</v>
+      </c>
+    </row>
+    <row r="171" spans="1:68">
+      <c r="A171" s="1">
+        <v>170</v>
+      </c>
+      <c r="B171">
+        <v>7468255</v>
+      </c>
+      <c r="C171" t="s">
+        <v>68</v>
+      </c>
+      <c r="D171" t="s">
+        <v>69</v>
+      </c>
+      <c r="E171" s="2">
+        <v>45703.5</v>
+      </c>
+      <c r="F171">
+        <v>22</v>
+      </c>
+      <c r="G171" t="s">
+        <v>72</v>
+      </c>
+      <c r="H171" t="s">
+        <v>71</v>
+      </c>
+      <c r="I171">
+        <v>0</v>
+      </c>
+      <c r="J171">
+        <v>1</v>
+      </c>
+      <c r="K171">
+        <v>1</v>
+      </c>
+      <c r="L171">
+        <v>2</v>
+      </c>
+      <c r="M171">
+        <v>3</v>
+      </c>
+      <c r="N171">
+        <v>5</v>
+      </c>
+      <c r="O171" t="s">
+        <v>201</v>
+      </c>
+      <c r="P171" t="s">
+        <v>283</v>
+      </c>
+      <c r="Q171">
+        <v>5.2</v>
+      </c>
+      <c r="R171">
+        <v>2.41</v>
+      </c>
+      <c r="S171">
+        <v>2.09</v>
+      </c>
+      <c r="T171">
+        <v>1.31</v>
+      </c>
+      <c r="U171">
+        <v>3.2</v>
+      </c>
+      <c r="V171">
+        <v>2.4</v>
+      </c>
+      <c r="W171">
+        <v>1.51</v>
+      </c>
+      <c r="X171">
+        <v>5.5</v>
+      </c>
+      <c r="Y171">
+        <v>1.12</v>
+      </c>
+      <c r="Z171">
+        <v>4.7</v>
+      </c>
+      <c r="AA171">
+        <v>3.75</v>
+      </c>
+      <c r="AB171">
+        <v>1.61</v>
+      </c>
+      <c r="AC171">
+        <v>1.01</v>
+      </c>
+      <c r="AD171">
+        <v>11</v>
+      </c>
+      <c r="AE171">
+        <v>1.22</v>
+      </c>
+      <c r="AF171">
+        <v>3.95</v>
+      </c>
+      <c r="AG171">
+        <v>1.69</v>
+      </c>
+      <c r="AH171">
+        <v>2.1</v>
+      </c>
+      <c r="AI171">
+        <v>1.71</v>
+      </c>
+      <c r="AJ171">
+        <v>2.02</v>
+      </c>
+      <c r="AK171">
+        <v>2.19</v>
+      </c>
+      <c r="AL171">
+        <v>1.22</v>
+      </c>
+      <c r="AM171">
+        <v>1.17</v>
+      </c>
+      <c r="AN171">
+        <v>0.27</v>
+      </c>
+      <c r="AO171">
+        <v>1.1</v>
+      </c>
+      <c r="AP171">
+        <v>0.25</v>
+      </c>
+      <c r="AQ171">
+        <v>1.27</v>
+      </c>
+      <c r="AR171">
+        <v>1.3</v>
+      </c>
+      <c r="AS171">
+        <v>1.36</v>
+      </c>
+      <c r="AT171">
+        <v>2.66</v>
+      </c>
+      <c r="AU171">
+        <v>3</v>
+      </c>
+      <c r="AV171">
+        <v>7</v>
+      </c>
+      <c r="AW171">
+        <v>0</v>
+      </c>
+      <c r="AX171">
+        <v>3</v>
+      </c>
+      <c r="AY171">
+        <v>3</v>
+      </c>
+      <c r="AZ171">
+        <v>10</v>
+      </c>
+      <c r="BA171">
+        <v>1</v>
+      </c>
+      <c r="BB171">
+        <v>9</v>
+      </c>
+      <c r="BC171">
+        <v>10</v>
+      </c>
+      <c r="BD171">
+        <v>2.95</v>
+      </c>
+      <c r="BE171">
+        <v>6.75</v>
+      </c>
+      <c r="BF171">
+        <v>1.48</v>
+      </c>
+      <c r="BG171">
+        <v>1.36</v>
+      </c>
+      <c r="BH171">
+        <v>2.8</v>
+      </c>
+      <c r="BI171">
+        <v>1.61</v>
+      </c>
+      <c r="BJ171">
+        <v>2.15</v>
+      </c>
+      <c r="BK171">
+        <v>1.98</v>
+      </c>
+      <c r="BL171">
+        <v>1.72</v>
+      </c>
+      <c r="BM171">
+        <v>2.55</v>
+      </c>
+      <c r="BN171">
+        <v>1.45</v>
+      </c>
+      <c r="BO171">
+        <v>3.3</v>
+      </c>
+      <c r="BP171">
+        <v>1.27</v>
+      </c>
+    </row>
+    <row r="172" spans="1:68">
+      <c r="A172" s="1">
+        <v>171</v>
+      </c>
+      <c r="B172">
+        <v>7468253</v>
+      </c>
+      <c r="C172" t="s">
+        <v>68</v>
+      </c>
+      <c r="D172" t="s">
+        <v>69</v>
+      </c>
+      <c r="E172" s="2">
+        <v>45703.625</v>
+      </c>
+      <c r="F172">
+        <v>22</v>
+      </c>
+      <c r="G172" t="s">
+        <v>75</v>
+      </c>
+      <c r="H172" t="s">
+        <v>70</v>
+      </c>
+      <c r="I172">
+        <v>2</v>
+      </c>
+      <c r="J172">
+        <v>2</v>
+      </c>
+      <c r="K172">
+        <v>4</v>
+      </c>
+      <c r="L172">
+        <v>2</v>
+      </c>
+      <c r="M172">
+        <v>3</v>
+      </c>
+      <c r="N172">
+        <v>5</v>
+      </c>
+      <c r="O172" t="s">
+        <v>202</v>
+      </c>
+      <c r="P172" t="s">
+        <v>284</v>
+      </c>
+      <c r="Q172">
+        <v>6.35</v>
+      </c>
+      <c r="R172">
+        <v>2.66</v>
+      </c>
+      <c r="S172">
+        <v>1.88</v>
+      </c>
+      <c r="T172">
+        <v>1.29</v>
+      </c>
+      <c r="U172">
+        <v>3.4</v>
+      </c>
+      <c r="V172">
+        <v>2.33</v>
+      </c>
+      <c r="W172">
+        <v>1.59</v>
+      </c>
+      <c r="X172">
+        <v>5</v>
+      </c>
+      <c r="Y172">
+        <v>1.13</v>
+      </c>
+      <c r="Z172">
+        <v>5.5</v>
+      </c>
+      <c r="AA172">
+        <v>4.33</v>
+      </c>
+      <c r="AB172">
+        <v>1.45</v>
+      </c>
+      <c r="AC172">
+        <v>1</v>
+      </c>
+      <c r="AD172">
+        <v>12</v>
+      </c>
+      <c r="AE172">
+        <v>1.18</v>
+      </c>
+      <c r="AF172">
+        <v>4.33</v>
+      </c>
+      <c r="AG172">
+        <v>1.57</v>
+      </c>
+      <c r="AH172">
+        <v>2.25</v>
+      </c>
+      <c r="AI172">
+        <v>1.73</v>
+      </c>
+      <c r="AJ172">
+        <v>2</v>
+      </c>
+      <c r="AK172">
+        <v>2.7</v>
+      </c>
+      <c r="AL172">
+        <v>1.18</v>
+      </c>
+      <c r="AM172">
+        <v>1.13</v>
+      </c>
+      <c r="AN172">
+        <v>1.45</v>
+      </c>
+      <c r="AO172">
+        <v>2</v>
+      </c>
+      <c r="AP172">
+        <v>1.33</v>
+      </c>
+      <c r="AQ172">
+        <v>2.09</v>
+      </c>
+      <c r="AR172">
+        <v>1.5</v>
+      </c>
+      <c r="AS172">
+        <v>1.67</v>
+      </c>
+      <c r="AT172">
+        <v>3.17</v>
+      </c>
+      <c r="AU172">
+        <v>7</v>
+      </c>
+      <c r="AV172">
+        <v>5</v>
+      </c>
+      <c r="AW172">
+        <v>7</v>
+      </c>
+      <c r="AX172">
+        <v>10</v>
+      </c>
+      <c r="AY172">
+        <v>14</v>
+      </c>
+      <c r="AZ172">
+        <v>15</v>
+      </c>
+      <c r="BA172">
+        <v>4</v>
+      </c>
+      <c r="BB172">
+        <v>3</v>
+      </c>
+      <c r="BC172">
+        <v>7</v>
+      </c>
+      <c r="BD172">
+        <v>3.4</v>
+      </c>
+      <c r="BE172">
+        <v>7.5</v>
+      </c>
+      <c r="BF172">
+        <v>1.35</v>
+      </c>
+      <c r="BG172">
+        <v>1.25</v>
+      </c>
+      <c r="BH172">
+        <v>3.45</v>
+      </c>
+      <c r="BI172">
+        <v>1.44</v>
+      </c>
+      <c r="BJ172">
+        <v>2.55</v>
+      </c>
+      <c r="BK172">
+        <v>1.71</v>
+      </c>
+      <c r="BL172">
+        <v>2</v>
+      </c>
+      <c r="BM172">
+        <v>2.08</v>
+      </c>
+      <c r="BN172">
+        <v>1.65</v>
+      </c>
+      <c r="BO172">
+        <v>2.6</v>
+      </c>
+      <c r="BP172">
+        <v>1.43</v>
       </c>
     </row>
   </sheetData>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Czech Republic First League_20242025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Czech Republic First League_20242025.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1094" uniqueCount="285">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1118" uniqueCount="289">
   <si>
     <t>Id_Jogo</t>
   </si>
@@ -625,6 +625,12 @@
     <t>['5', '10']</t>
   </si>
   <si>
+    <t>['40', '45+1']</t>
+  </si>
+  <si>
+    <t>['37', '43', '47']</t>
+  </si>
+  <si>
     <t>['25']</t>
   </si>
   <si>
@@ -869,6 +875,12 @@
   </si>
   <si>
     <t>['20', '45+11', '53']</t>
+  </si>
+  <si>
+    <t>['12', '25']</t>
+  </si>
+  <si>
+    <t>['42', '45']</t>
   </si>
 </sst>
 </file>
@@ -1230,7 +1242,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:BP172"/>
+  <dimension ref="A1:BP176"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:68">
@@ -1486,7 +1498,7 @@
         <v>86</v>
       </c>
       <c r="P2" t="s">
-        <v>203</v>
+        <v>205</v>
       </c>
       <c r="Q2">
         <v>1.53</v>
@@ -1773,7 +1785,7 @@
         <v>2</v>
       </c>
       <c r="AQ3">
-        <v>1.2</v>
+        <v>1.09</v>
       </c>
       <c r="AR3">
         <v>0</v>
@@ -1898,7 +1910,7 @@
         <v>88</v>
       </c>
       <c r="P4" t="s">
-        <v>204</v>
+        <v>206</v>
       </c>
       <c r="Q4">
         <v>2.88</v>
@@ -2185,7 +2197,7 @@
         <v>1.18</v>
       </c>
       <c r="AQ5">
-        <v>1.64</v>
+        <v>1.5</v>
       </c>
       <c r="AR5">
         <v>0</v>
@@ -2310,7 +2322,7 @@
         <v>90</v>
       </c>
       <c r="P6" t="s">
-        <v>205</v>
+        <v>207</v>
       </c>
       <c r="Q6">
         <v>5.5</v>
@@ -2391,7 +2403,7 @@
         <v>1</v>
       </c>
       <c r="AQ6">
-        <v>1.7</v>
+        <v>1.82</v>
       </c>
       <c r="AR6">
         <v>0</v>
@@ -2516,7 +2528,7 @@
         <v>91</v>
       </c>
       <c r="P7" t="s">
-        <v>206</v>
+        <v>208</v>
       </c>
       <c r="Q7">
         <v>3.2</v>
@@ -3006,7 +3018,7 @@
         <v>0</v>
       </c>
       <c r="AP9">
-        <v>1.7</v>
+        <v>1.64</v>
       </c>
       <c r="AQ9">
         <v>0.82</v>
@@ -3215,7 +3227,7 @@
         <v>1</v>
       </c>
       <c r="AQ10">
-        <v>1.5</v>
+        <v>1.45</v>
       </c>
       <c r="AR10">
         <v>0.98</v>
@@ -3340,7 +3352,7 @@
         <v>94</v>
       </c>
       <c r="P11" t="s">
-        <v>207</v>
+        <v>209</v>
       </c>
       <c r="Q11">
         <v>6.5</v>
@@ -3418,7 +3430,7 @@
         <v>0</v>
       </c>
       <c r="AP11">
-        <v>1.3</v>
+        <v>1.18</v>
       </c>
       <c r="AQ11">
         <v>2.09</v>
@@ -3546,7 +3558,7 @@
         <v>88</v>
       </c>
       <c r="P12" t="s">
-        <v>208</v>
+        <v>210</v>
       </c>
       <c r="Q12">
         <v>2.85</v>
@@ -3958,7 +3970,7 @@
         <v>96</v>
       </c>
       <c r="P14" t="s">
-        <v>209</v>
+        <v>211</v>
       </c>
       <c r="Q14">
         <v>2.45</v>
@@ -4036,7 +4048,7 @@
         <v>3</v>
       </c>
       <c r="AP14">
-        <v>1.3</v>
+        <v>1.45</v>
       </c>
       <c r="AQ14">
         <v>1.09</v>
@@ -4782,7 +4794,7 @@
         <v>88</v>
       </c>
       <c r="P18" t="s">
-        <v>210</v>
+        <v>212</v>
       </c>
       <c r="Q18">
         <v>5.4</v>
@@ -4860,7 +4872,7 @@
         <v>1</v>
       </c>
       <c r="AP18">
-        <v>1.3</v>
+        <v>1.45</v>
       </c>
       <c r="AQ18">
         <v>2.36</v>
@@ -5275,7 +5287,7 @@
         <v>1.36</v>
       </c>
       <c r="AQ20">
-        <v>1.5</v>
+        <v>1.45</v>
       </c>
       <c r="AR20">
         <v>1</v>
@@ -5481,7 +5493,7 @@
         <v>2</v>
       </c>
       <c r="AQ21">
-        <v>1.7</v>
+        <v>1.82</v>
       </c>
       <c r="AR21">
         <v>1.81</v>
@@ -5812,7 +5824,7 @@
         <v>102</v>
       </c>
       <c r="P23" t="s">
-        <v>211</v>
+        <v>213</v>
       </c>
       <c r="Q23">
         <v>2.6</v>
@@ -6018,7 +6030,7 @@
         <v>103</v>
       </c>
       <c r="P24" t="s">
-        <v>212</v>
+        <v>214</v>
       </c>
       <c r="Q24">
         <v>2.75</v>
@@ -6096,10 +6108,10 @@
         <v>0</v>
       </c>
       <c r="AP24">
-        <v>1.7</v>
+        <v>1.64</v>
       </c>
       <c r="AQ24">
-        <v>1.2</v>
+        <v>1.09</v>
       </c>
       <c r="AR24">
         <v>1.19</v>
@@ -6224,7 +6236,7 @@
         <v>88</v>
       </c>
       <c r="P25" t="s">
-        <v>213</v>
+        <v>215</v>
       </c>
       <c r="Q25">
         <v>1.06</v>
@@ -6430,7 +6442,7 @@
         <v>104</v>
       </c>
       <c r="P26" t="s">
-        <v>214</v>
+        <v>216</v>
       </c>
       <c r="Q26">
         <v>6.23</v>
@@ -6714,7 +6726,7 @@
         <v>3</v>
       </c>
       <c r="AP27">
-        <v>1.3</v>
+        <v>1.18</v>
       </c>
       <c r="AQ27">
         <v>1</v>
@@ -7950,7 +7962,7 @@
         <v>0</v>
       </c>
       <c r="AP33">
-        <v>1.7</v>
+        <v>1.64</v>
       </c>
       <c r="AQ33">
         <v>0.36</v>
@@ -8078,7 +8090,7 @@
         <v>111</v>
       </c>
       <c r="P34" t="s">
-        <v>215</v>
+        <v>217</v>
       </c>
       <c r="Q34">
         <v>1.45</v>
@@ -8284,7 +8296,7 @@
         <v>112</v>
       </c>
       <c r="P35" t="s">
-        <v>216</v>
+        <v>218</v>
       </c>
       <c r="Q35">
         <v>2.84</v>
@@ -8365,7 +8377,7 @@
         <v>1.33</v>
       </c>
       <c r="AQ35">
-        <v>1.5</v>
+        <v>1.45</v>
       </c>
       <c r="AR35">
         <v>1.93</v>
@@ -8490,7 +8502,7 @@
         <v>113</v>
       </c>
       <c r="P36" t="s">
-        <v>217</v>
+        <v>219</v>
       </c>
       <c r="Q36">
         <v>5.63</v>
@@ -8696,7 +8708,7 @@
         <v>114</v>
       </c>
       <c r="P37" t="s">
-        <v>218</v>
+        <v>220</v>
       </c>
       <c r="Q37">
         <v>2.58</v>
@@ -8777,7 +8789,7 @@
         <v>1.82</v>
       </c>
       <c r="AQ37">
-        <v>1.2</v>
+        <v>1.09</v>
       </c>
       <c r="AR37">
         <v>1.25</v>
@@ -8980,7 +8992,7 @@
         <v>1.5</v>
       </c>
       <c r="AP38">
-        <v>1.3</v>
+        <v>1.45</v>
       </c>
       <c r="AQ38">
         <v>0.5</v>
@@ -9108,7 +9120,7 @@
         <v>88</v>
       </c>
       <c r="P39" t="s">
-        <v>219</v>
+        <v>221</v>
       </c>
       <c r="Q39">
         <v>4.75</v>
@@ -9189,7 +9201,7 @@
         <v>0.25</v>
       </c>
       <c r="AQ39">
-        <v>1.7</v>
+        <v>1.82</v>
       </c>
       <c r="AR39">
         <v>1.46</v>
@@ -9395,7 +9407,7 @@
         <v>1.36</v>
       </c>
       <c r="AQ40">
-        <v>1.64</v>
+        <v>1.5</v>
       </c>
       <c r="AR40">
         <v>1.19</v>
@@ -9520,7 +9532,7 @@
         <v>117</v>
       </c>
       <c r="P41" t="s">
-        <v>220</v>
+        <v>222</v>
       </c>
       <c r="Q41">
         <v>2.4</v>
@@ -9726,7 +9738,7 @@
         <v>107</v>
       </c>
       <c r="P42" t="s">
-        <v>221</v>
+        <v>223</v>
       </c>
       <c r="Q42">
         <v>2.61</v>
@@ -9804,7 +9816,7 @@
         <v>1.5</v>
       </c>
       <c r="AP42">
-        <v>1.3</v>
+        <v>1.18</v>
       </c>
       <c r="AQ42">
         <v>0.89</v>
@@ -9932,7 +9944,7 @@
         <v>118</v>
       </c>
       <c r="P43" t="s">
-        <v>222</v>
+        <v>224</v>
       </c>
       <c r="Q43">
         <v>1.69</v>
@@ -10837,7 +10849,7 @@
         <v>1.33</v>
       </c>
       <c r="AQ47">
-        <v>1.64</v>
+        <v>1.5</v>
       </c>
       <c r="AR47">
         <v>1.77</v>
@@ -11043,7 +11055,7 @@
         <v>0.25</v>
       </c>
       <c r="AQ48">
-        <v>1.5</v>
+        <v>1.45</v>
       </c>
       <c r="AR48">
         <v>1.34</v>
@@ -11374,7 +11386,7 @@
         <v>88</v>
       </c>
       <c r="P50" t="s">
-        <v>223</v>
+        <v>225</v>
       </c>
       <c r="Q50">
         <v>5.1</v>
@@ -11452,7 +11464,7 @@
         <v>3</v>
       </c>
       <c r="AP50">
-        <v>1.7</v>
+        <v>1.64</v>
       </c>
       <c r="AQ50">
         <v>2.09</v>
@@ -11786,7 +11798,7 @@
         <v>122</v>
       </c>
       <c r="P52" t="s">
-        <v>224</v>
+        <v>226</v>
       </c>
       <c r="Q52">
         <v>3</v>
@@ -11867,7 +11879,7 @@
         <v>1.82</v>
       </c>
       <c r="AQ52">
-        <v>1.64</v>
+        <v>1.5</v>
       </c>
       <c r="AR52">
         <v>1.61</v>
@@ -12198,7 +12210,7 @@
         <v>124</v>
       </c>
       <c r="P54" t="s">
-        <v>225</v>
+        <v>227</v>
       </c>
       <c r="Q54">
         <v>3</v>
@@ -12276,10 +12288,10 @@
         <v>0</v>
       </c>
       <c r="AP54">
-        <v>1.3</v>
+        <v>1.18</v>
       </c>
       <c r="AQ54">
-        <v>1.2</v>
+        <v>1.09</v>
       </c>
       <c r="AR54">
         <v>1.4</v>
@@ -12482,10 +12494,10 @@
         <v>2.33</v>
       </c>
       <c r="AP55">
-        <v>1.3</v>
+        <v>1.45</v>
       </c>
       <c r="AQ55">
-        <v>1.7</v>
+        <v>1.82</v>
       </c>
       <c r="AR55">
         <v>1.32</v>
@@ -12610,7 +12622,7 @@
         <v>125</v>
       </c>
       <c r="P56" t="s">
-        <v>226</v>
+        <v>228</v>
       </c>
       <c r="Q56">
         <v>1.85</v>
@@ -12816,7 +12828,7 @@
         <v>88</v>
       </c>
       <c r="P57" t="s">
-        <v>227</v>
+        <v>229</v>
       </c>
       <c r="Q57">
         <v>5.88</v>
@@ -13100,7 +13112,7 @@
         <v>1.33</v>
       </c>
       <c r="AP58">
-        <v>1.7</v>
+        <v>1.64</v>
       </c>
       <c r="AQ58">
         <v>1</v>
@@ -13228,7 +13240,7 @@
         <v>127</v>
       </c>
       <c r="P59" t="s">
-        <v>228</v>
+        <v>230</v>
       </c>
       <c r="Q59">
         <v>3.86</v>
@@ -13306,10 +13318,10 @@
         <v>0.5</v>
       </c>
       <c r="AP59">
-        <v>1.3</v>
+        <v>1.18</v>
       </c>
       <c r="AQ59">
-        <v>1.64</v>
+        <v>1.5</v>
       </c>
       <c r="AR59">
         <v>1.44</v>
@@ -13721,7 +13733,7 @@
         <v>3</v>
       </c>
       <c r="AQ61">
-        <v>1.7</v>
+        <v>1.82</v>
       </c>
       <c r="AR61">
         <v>2.33</v>
@@ -13846,7 +13858,7 @@
         <v>130</v>
       </c>
       <c r="P62" t="s">
-        <v>229</v>
+        <v>231</v>
       </c>
       <c r="Q62">
         <v>1.83</v>
@@ -14052,7 +14064,7 @@
         <v>88</v>
       </c>
       <c r="P63" t="s">
-        <v>230</v>
+        <v>232</v>
       </c>
       <c r="Q63">
         <v>8.77</v>
@@ -14464,7 +14476,7 @@
         <v>132</v>
       </c>
       <c r="P65" t="s">
-        <v>231</v>
+        <v>233</v>
       </c>
       <c r="Q65">
         <v>2.4</v>
@@ -14542,10 +14554,10 @@
         <v>1.25</v>
       </c>
       <c r="AP65">
-        <v>1.3</v>
+        <v>1.45</v>
       </c>
       <c r="AQ65">
-        <v>1.5</v>
+        <v>1.45</v>
       </c>
       <c r="AR65">
         <v>1.42</v>
@@ -14670,7 +14682,7 @@
         <v>133</v>
       </c>
       <c r="P66" t="s">
-        <v>232</v>
+        <v>234</v>
       </c>
       <c r="Q66">
         <v>1.55</v>
@@ -14876,7 +14888,7 @@
         <v>134</v>
       </c>
       <c r="P67" t="s">
-        <v>233</v>
+        <v>235</v>
       </c>
       <c r="Q67">
         <v>4</v>
@@ -15082,7 +15094,7 @@
         <v>88</v>
       </c>
       <c r="P68" t="s">
-        <v>234</v>
+        <v>236</v>
       </c>
       <c r="Q68">
         <v>3.1</v>
@@ -15906,7 +15918,7 @@
         <v>124</v>
       </c>
       <c r="P72" t="s">
-        <v>235</v>
+        <v>237</v>
       </c>
       <c r="Q72">
         <v>1.88</v>
@@ -15987,7 +15999,7 @@
         <v>2.64</v>
       </c>
       <c r="AQ72">
-        <v>1.2</v>
+        <v>1.09</v>
       </c>
       <c r="AR72">
         <v>1.84</v>
@@ -16112,7 +16124,7 @@
         <v>88</v>
       </c>
       <c r="P73" t="s">
-        <v>236</v>
+        <v>238</v>
       </c>
       <c r="Q73">
         <v>7</v>
@@ -16524,7 +16536,7 @@
         <v>138</v>
       </c>
       <c r="P75" t="s">
-        <v>237</v>
+        <v>239</v>
       </c>
       <c r="Q75">
         <v>2.3</v>
@@ -16602,7 +16614,7 @@
         <v>0.25</v>
       </c>
       <c r="AP75">
-        <v>1.3</v>
+        <v>1.18</v>
       </c>
       <c r="AQ75">
         <v>0.36</v>
@@ -16730,7 +16742,7 @@
         <v>88</v>
       </c>
       <c r="P76" t="s">
-        <v>238</v>
+        <v>240</v>
       </c>
       <c r="Q76">
         <v>3.7</v>
@@ -16936,7 +16948,7 @@
         <v>88</v>
       </c>
       <c r="P77" t="s">
-        <v>239</v>
+        <v>241</v>
       </c>
       <c r="Q77">
         <v>2.47</v>
@@ -17014,7 +17026,7 @@
         <v>1.4</v>
       </c>
       <c r="AP77">
-        <v>1.3</v>
+        <v>1.45</v>
       </c>
       <c r="AQ77">
         <v>1.27</v>
@@ -17429,7 +17441,7 @@
         <v>1.73</v>
       </c>
       <c r="AQ79">
-        <v>1.64</v>
+        <v>1.5</v>
       </c>
       <c r="AR79">
         <v>1.49</v>
@@ -17554,7 +17566,7 @@
         <v>140</v>
       </c>
       <c r="P80" t="s">
-        <v>240</v>
+        <v>242</v>
       </c>
       <c r="Q80">
         <v>2.5</v>
@@ -17635,7 +17647,7 @@
         <v>1.82</v>
       </c>
       <c r="AQ80">
-        <v>1.5</v>
+        <v>1.45</v>
       </c>
       <c r="AR80">
         <v>1.66</v>
@@ -17760,7 +17772,7 @@
         <v>141</v>
       </c>
       <c r="P81" t="s">
-        <v>241</v>
+        <v>243</v>
       </c>
       <c r="Q81">
         <v>2.38</v>
@@ -17966,7 +17978,7 @@
         <v>142</v>
       </c>
       <c r="P82" t="s">
-        <v>242</v>
+        <v>244</v>
       </c>
       <c r="Q82">
         <v>2.8</v>
@@ -18044,7 +18056,7 @@
         <v>1.4</v>
       </c>
       <c r="AP82">
-        <v>1.7</v>
+        <v>1.64</v>
       </c>
       <c r="AQ82">
         <v>1.09</v>
@@ -18172,7 +18184,7 @@
         <v>143</v>
       </c>
       <c r="P83" t="s">
-        <v>243</v>
+        <v>245</v>
       </c>
       <c r="Q83">
         <v>2.6</v>
@@ -18378,7 +18390,7 @@
         <v>144</v>
       </c>
       <c r="P84" t="s">
-        <v>244</v>
+        <v>246</v>
       </c>
       <c r="Q84">
         <v>3.4</v>
@@ -18459,7 +18471,7 @@
         <v>2.4</v>
       </c>
       <c r="AQ84">
-        <v>1.7</v>
+        <v>1.82</v>
       </c>
       <c r="AR84">
         <v>1.81</v>
@@ -18790,7 +18802,7 @@
         <v>146</v>
       </c>
       <c r="P86" t="s">
-        <v>245</v>
+        <v>247</v>
       </c>
       <c r="Q86">
         <v>2.88</v>
@@ -18871,7 +18883,7 @@
         <v>1.18</v>
       </c>
       <c r="AQ86">
-        <v>1.2</v>
+        <v>1.09</v>
       </c>
       <c r="AR86">
         <v>1.41</v>
@@ -19202,7 +19214,7 @@
         <v>88</v>
       </c>
       <c r="P88" t="s">
-        <v>246</v>
+        <v>248</v>
       </c>
       <c r="Q88">
         <v>2.6</v>
@@ -19408,7 +19420,7 @@
         <v>93</v>
       </c>
       <c r="P89" t="s">
-        <v>247</v>
+        <v>249</v>
       </c>
       <c r="Q89">
         <v>6.5</v>
@@ -19692,7 +19704,7 @@
         <v>1.4</v>
       </c>
       <c r="AP90">
-        <v>1.3</v>
+        <v>1.45</v>
       </c>
       <c r="AQ90">
         <v>1</v>
@@ -19820,7 +19832,7 @@
         <v>149</v>
       </c>
       <c r="P91" t="s">
-        <v>248</v>
+        <v>250</v>
       </c>
       <c r="Q91">
         <v>4.7</v>
@@ -19901,7 +19913,7 @@
         <v>0.9</v>
       </c>
       <c r="AQ91">
-        <v>1.64</v>
+        <v>1.5</v>
       </c>
       <c r="AR91">
         <v>1.11</v>
@@ -20026,7 +20038,7 @@
         <v>88</v>
       </c>
       <c r="P92" t="s">
-        <v>249</v>
+        <v>251</v>
       </c>
       <c r="Q92">
         <v>3.8</v>
@@ -20438,7 +20450,7 @@
         <v>150</v>
       </c>
       <c r="P94" t="s">
-        <v>250</v>
+        <v>252</v>
       </c>
       <c r="Q94">
         <v>3</v>
@@ -20516,10 +20528,10 @@
         <v>1.5</v>
       </c>
       <c r="AP94">
-        <v>1.3</v>
+        <v>1.18</v>
       </c>
       <c r="AQ94">
-        <v>1.5</v>
+        <v>1.45</v>
       </c>
       <c r="AR94">
         <v>1.52</v>
@@ -21343,7 +21355,7 @@
         <v>1</v>
       </c>
       <c r="AQ98">
-        <v>1.2</v>
+        <v>1.09</v>
       </c>
       <c r="AR98">
         <v>1.15</v>
@@ -21880,7 +21892,7 @@
         <v>156</v>
       </c>
       <c r="P101" t="s">
-        <v>251</v>
+        <v>253</v>
       </c>
       <c r="Q101">
         <v>1.83</v>
@@ -21961,7 +21973,7 @@
         <v>2.09</v>
       </c>
       <c r="AQ101">
-        <v>1.64</v>
+        <v>1.5</v>
       </c>
       <c r="AR101">
         <v>1.9</v>
@@ -22579,7 +22591,7 @@
         <v>1.36</v>
       </c>
       <c r="AQ104">
-        <v>1.7</v>
+        <v>1.82</v>
       </c>
       <c r="AR104">
         <v>1.15</v>
@@ -22782,7 +22794,7 @@
         <v>2.6</v>
       </c>
       <c r="AP105">
-        <v>1.7</v>
+        <v>1.64</v>
       </c>
       <c r="AQ105">
         <v>2.36</v>
@@ -23400,7 +23412,7 @@
         <v>0.67</v>
       </c>
       <c r="AP108">
-        <v>1.3</v>
+        <v>1.45</v>
       </c>
       <c r="AQ108">
         <v>1</v>
@@ -23528,7 +23540,7 @@
         <v>161</v>
       </c>
       <c r="P109" t="s">
-        <v>252</v>
+        <v>254</v>
       </c>
       <c r="Q109">
         <v>2.24</v>
@@ -23606,7 +23618,7 @@
         <v>0</v>
       </c>
       <c r="AP109">
-        <v>1.3</v>
+        <v>1.18</v>
       </c>
       <c r="AQ109">
         <v>0.1</v>
@@ -23734,7 +23746,7 @@
         <v>162</v>
       </c>
       <c r="P110" t="s">
-        <v>253</v>
+        <v>255</v>
       </c>
       <c r="Q110">
         <v>4.6</v>
@@ -24021,7 +24033,7 @@
         <v>2.64</v>
       </c>
       <c r="AQ111">
-        <v>1.5</v>
+        <v>1.45</v>
       </c>
       <c r="AR111">
         <v>1.73</v>
@@ -24146,7 +24158,7 @@
         <v>164</v>
       </c>
       <c r="P112" t="s">
-        <v>209</v>
+        <v>211</v>
       </c>
       <c r="Q112">
         <v>1.44</v>
@@ -24352,7 +24364,7 @@
         <v>165</v>
       </c>
       <c r="P113" t="s">
-        <v>254</v>
+        <v>256</v>
       </c>
       <c r="Q113">
         <v>3.25</v>
@@ -24433,7 +24445,7 @@
         <v>2</v>
       </c>
       <c r="AQ113">
-        <v>1.64</v>
+        <v>1.5</v>
       </c>
       <c r="AR113">
         <v>1.63</v>
@@ -24558,7 +24570,7 @@
         <v>99</v>
       </c>
       <c r="P114" t="s">
-        <v>255</v>
+        <v>257</v>
       </c>
       <c r="Q114">
         <v>1.73</v>
@@ -24764,7 +24776,7 @@
         <v>151</v>
       </c>
       <c r="P115" t="s">
-        <v>256</v>
+        <v>258</v>
       </c>
       <c r="Q115">
         <v>2.88</v>
@@ -24845,7 +24857,7 @@
         <v>1.36</v>
       </c>
       <c r="AQ115">
-        <v>1.2</v>
+        <v>1.09</v>
       </c>
       <c r="AR115">
         <v>1.11</v>
@@ -24970,7 +24982,7 @@
         <v>88</v>
       </c>
       <c r="P116" t="s">
-        <v>257</v>
+        <v>259</v>
       </c>
       <c r="Q116">
         <v>4.33</v>
@@ -25048,10 +25060,10 @@
         <v>1.57</v>
       </c>
       <c r="AP116">
-        <v>1.7</v>
+        <v>1.64</v>
       </c>
       <c r="AQ116">
-        <v>1.7</v>
+        <v>1.82</v>
       </c>
       <c r="AR116">
         <v>1.34</v>
@@ -25382,7 +25394,7 @@
         <v>88</v>
       </c>
       <c r="P118" t="s">
-        <v>258</v>
+        <v>260</v>
       </c>
       <c r="Q118">
         <v>15</v>
@@ -25794,7 +25806,7 @@
         <v>168</v>
       </c>
       <c r="P120" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="Q120">
         <v>3</v>
@@ -26206,7 +26218,7 @@
         <v>170</v>
       </c>
       <c r="P122" t="s">
-        <v>260</v>
+        <v>262</v>
       </c>
       <c r="Q122">
         <v>3.25</v>
@@ -26412,7 +26424,7 @@
         <v>171</v>
       </c>
       <c r="P123" t="s">
-        <v>208</v>
+        <v>210</v>
       </c>
       <c r="Q123">
         <v>1.83</v>
@@ -26696,7 +26708,7 @@
         <v>1.14</v>
       </c>
       <c r="AP124">
-        <v>1.3</v>
+        <v>1.18</v>
       </c>
       <c r="AQ124">
         <v>1.09</v>
@@ -26824,7 +26836,7 @@
         <v>172</v>
       </c>
       <c r="P125" t="s">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="Q125">
         <v>6.3</v>
@@ -27648,7 +27660,7 @@
         <v>174</v>
       </c>
       <c r="P129" t="s">
-        <v>262</v>
+        <v>264</v>
       </c>
       <c r="Q129">
         <v>2.1</v>
@@ -27854,7 +27866,7 @@
         <v>175</v>
       </c>
       <c r="P130" t="s">
-        <v>263</v>
+        <v>265</v>
       </c>
       <c r="Q130">
         <v>1.5</v>
@@ -28266,7 +28278,7 @@
         <v>177</v>
       </c>
       <c r="P132" t="s">
-        <v>264</v>
+        <v>266</v>
       </c>
       <c r="Q132">
         <v>4.04</v>
@@ -28472,7 +28484,7 @@
         <v>178</v>
       </c>
       <c r="P133" t="s">
-        <v>265</v>
+        <v>267</v>
       </c>
       <c r="Q133">
         <v>3.5</v>
@@ -28678,7 +28690,7 @@
         <v>88</v>
       </c>
       <c r="P134" t="s">
-        <v>266</v>
+        <v>268</v>
       </c>
       <c r="Q134">
         <v>2.75</v>
@@ -29090,7 +29102,7 @@
         <v>88</v>
       </c>
       <c r="P136" t="s">
-        <v>267</v>
+        <v>269</v>
       </c>
       <c r="Q136">
         <v>4.5</v>
@@ -29502,7 +29514,7 @@
         <v>91</v>
       </c>
       <c r="P138" t="s">
-        <v>254</v>
+        <v>256</v>
       </c>
       <c r="Q138">
         <v>2.25</v>
@@ -29708,7 +29720,7 @@
         <v>179</v>
       </c>
       <c r="P139" t="s">
-        <v>263</v>
+        <v>265</v>
       </c>
       <c r="Q139">
         <v>1.9</v>
@@ -29995,7 +30007,7 @@
         <v>2.09</v>
       </c>
       <c r="AQ140">
-        <v>1.5</v>
+        <v>1.45</v>
       </c>
       <c r="AR140">
         <v>2.06</v>
@@ -30120,7 +30132,7 @@
         <v>117</v>
       </c>
       <c r="P141" t="s">
-        <v>268</v>
+        <v>270</v>
       </c>
       <c r="Q141">
         <v>4</v>
@@ -30201,7 +30213,7 @@
         <v>1.33</v>
       </c>
       <c r="AQ141">
-        <v>1.7</v>
+        <v>1.82</v>
       </c>
       <c r="AR141">
         <v>1.59</v>
@@ -30326,7 +30338,7 @@
         <v>88</v>
       </c>
       <c r="P142" t="s">
-        <v>269</v>
+        <v>271</v>
       </c>
       <c r="Q142">
         <v>4</v>
@@ -30407,7 +30419,7 @@
         <v>0.25</v>
       </c>
       <c r="AQ142">
-        <v>1.2</v>
+        <v>1.09</v>
       </c>
       <c r="AR142">
         <v>1.34</v>
@@ -30610,7 +30622,7 @@
         <v>1</v>
       </c>
       <c r="AP143">
-        <v>1.3</v>
+        <v>1.45</v>
       </c>
       <c r="AQ143">
         <v>0.82</v>
@@ -30738,7 +30750,7 @@
         <v>182</v>
       </c>
       <c r="P144" t="s">
-        <v>270</v>
+        <v>272</v>
       </c>
       <c r="Q144">
         <v>6</v>
@@ -30944,7 +30956,7 @@
         <v>88</v>
       </c>
       <c r="P145" t="s">
-        <v>271</v>
+        <v>273</v>
       </c>
       <c r="Q145">
         <v>3.5</v>
@@ -31022,10 +31034,10 @@
         <v>1.33</v>
       </c>
       <c r="AP145">
-        <v>1.7</v>
+        <v>1.64</v>
       </c>
       <c r="AQ145">
-        <v>1.64</v>
+        <v>1.5</v>
       </c>
       <c r="AR145">
         <v>1.32</v>
@@ -31150,7 +31162,7 @@
         <v>183</v>
       </c>
       <c r="P146" t="s">
-        <v>272</v>
+        <v>274</v>
       </c>
       <c r="Q146">
         <v>4.33</v>
@@ -31356,7 +31368,7 @@
         <v>184</v>
       </c>
       <c r="P147" t="s">
-        <v>273</v>
+        <v>275</v>
       </c>
       <c r="Q147">
         <v>3.8</v>
@@ -31562,7 +31574,7 @@
         <v>185</v>
       </c>
       <c r="P148" t="s">
-        <v>274</v>
+        <v>276</v>
       </c>
       <c r="Q148">
         <v>2.5</v>
@@ -31768,7 +31780,7 @@
         <v>186</v>
       </c>
       <c r="P149" t="s">
-        <v>271</v>
+        <v>273</v>
       </c>
       <c r="Q149">
         <v>2.05</v>
@@ -31974,7 +31986,7 @@
         <v>187</v>
       </c>
       <c r="P150" t="s">
-        <v>275</v>
+        <v>277</v>
       </c>
       <c r="Q150">
         <v>1.95</v>
@@ -32180,7 +32192,7 @@
         <v>188</v>
       </c>
       <c r="P151" t="s">
-        <v>276</v>
+        <v>278</v>
       </c>
       <c r="Q151">
         <v>2.48</v>
@@ -32464,7 +32476,7 @@
         <v>2.56</v>
       </c>
       <c r="AP152">
-        <v>1.3</v>
+        <v>1.18</v>
       </c>
       <c r="AQ152">
         <v>2.36</v>
@@ -32592,7 +32604,7 @@
         <v>190</v>
       </c>
       <c r="P153" t="s">
-        <v>277</v>
+        <v>279</v>
       </c>
       <c r="Q153">
         <v>1.4</v>
@@ -33210,7 +33222,7 @@
         <v>88</v>
       </c>
       <c r="P156" t="s">
-        <v>212</v>
+        <v>214</v>
       </c>
       <c r="Q156">
         <v>3.2</v>
@@ -33288,10 +33300,10 @@
         <v>1.5</v>
       </c>
       <c r="AP156">
-        <v>1.3</v>
+        <v>1.45</v>
       </c>
       <c r="AQ156">
-        <v>1.64</v>
+        <v>1.5</v>
       </c>
       <c r="AR156">
         <v>1.51</v>
@@ -33494,7 +33506,7 @@
         <v>0.6</v>
       </c>
       <c r="AP157">
-        <v>1.7</v>
+        <v>1.64</v>
       </c>
       <c r="AQ157">
         <v>0.5</v>
@@ -33622,7 +33634,7 @@
         <v>88</v>
       </c>
       <c r="P158" t="s">
-        <v>278</v>
+        <v>280</v>
       </c>
       <c r="Q158">
         <v>5</v>
@@ -33828,7 +33840,7 @@
         <v>88</v>
       </c>
       <c r="P159" t="s">
-        <v>234</v>
+        <v>236</v>
       </c>
       <c r="Q159">
         <v>2.38</v>
@@ -33909,7 +33921,7 @@
         <v>2</v>
       </c>
       <c r="AQ159">
-        <v>1.5</v>
+        <v>1.45</v>
       </c>
       <c r="AR159">
         <v>1.67</v>
@@ -34115,7 +34127,7 @@
         <v>3</v>
       </c>
       <c r="AQ160">
-        <v>1.2</v>
+        <v>1.09</v>
       </c>
       <c r="AR160">
         <v>2.39</v>
@@ -34240,7 +34252,7 @@
         <v>193</v>
       </c>
       <c r="P161" t="s">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="Q161">
         <v>4.75</v>
@@ -34321,7 +34333,7 @@
         <v>1.82</v>
       </c>
       <c r="AQ161">
-        <v>1.7</v>
+        <v>1.82</v>
       </c>
       <c r="AR161">
         <v>1.6</v>
@@ -34446,7 +34458,7 @@
         <v>194</v>
       </c>
       <c r="P162" t="s">
-        <v>279</v>
+        <v>281</v>
       </c>
       <c r="Q162">
         <v>2.63</v>
@@ -34652,7 +34664,7 @@
         <v>88</v>
       </c>
       <c r="P163" t="s">
-        <v>280</v>
+        <v>282</v>
       </c>
       <c r="Q163">
         <v>11</v>
@@ -34858,7 +34870,7 @@
         <v>195</v>
       </c>
       <c r="P164" t="s">
-        <v>281</v>
+        <v>283</v>
       </c>
       <c r="Q164">
         <v>2</v>
@@ -35064,7 +35076,7 @@
         <v>196</v>
       </c>
       <c r="P165" t="s">
-        <v>282</v>
+        <v>284</v>
       </c>
       <c r="Q165">
         <v>2.5</v>
@@ -36300,7 +36312,7 @@
         <v>201</v>
       </c>
       <c r="P171" t="s">
-        <v>283</v>
+        <v>285</v>
       </c>
       <c r="Q171">
         <v>5.2</v>
@@ -36506,7 +36518,7 @@
         <v>202</v>
       </c>
       <c r="P172" t="s">
-        <v>284</v>
+        <v>286</v>
       </c>
       <c r="Q172">
         <v>6.35</v>
@@ -36663,6 +36675,830 @@
       </c>
       <c r="BP172">
         <v>1.43</v>
+      </c>
+    </row>
+    <row r="173" spans="1:68">
+      <c r="A173" s="1">
+        <v>172</v>
+      </c>
+      <c r="B173">
+        <v>7468254</v>
+      </c>
+      <c r="C173" t="s">
+        <v>68</v>
+      </c>
+      <c r="D173" t="s">
+        <v>69</v>
+      </c>
+      <c r="E173" s="2">
+        <v>45704.375</v>
+      </c>
+      <c r="F173">
+        <v>22</v>
+      </c>
+      <c r="G173" t="s">
+        <v>77</v>
+      </c>
+      <c r="H173" t="s">
+        <v>73</v>
+      </c>
+      <c r="I173">
+        <v>2</v>
+      </c>
+      <c r="J173">
+        <v>2</v>
+      </c>
+      <c r="K173">
+        <v>4</v>
+      </c>
+      <c r="L173">
+        <v>2</v>
+      </c>
+      <c r="M173">
+        <v>2</v>
+      </c>
+      <c r="N173">
+        <v>4</v>
+      </c>
+      <c r="O173" t="s">
+        <v>203</v>
+      </c>
+      <c r="P173" t="s">
+        <v>287</v>
+      </c>
+      <c r="Q173">
+        <v>2.6</v>
+      </c>
+      <c r="R173">
+        <v>2.1</v>
+      </c>
+      <c r="S173">
+        <v>4.5</v>
+      </c>
+      <c r="T173">
+        <v>1.44</v>
+      </c>
+      <c r="U173">
+        <v>2.63</v>
+      </c>
+      <c r="V173">
+        <v>3</v>
+      </c>
+      <c r="W173">
+        <v>1.36</v>
+      </c>
+      <c r="X173">
+        <v>9</v>
+      </c>
+      <c r="Y173">
+        <v>1.07</v>
+      </c>
+      <c r="Z173">
+        <v>1.91</v>
+      </c>
+      <c r="AA173">
+        <v>3.25</v>
+      </c>
+      <c r="AB173">
+        <v>4.33</v>
+      </c>
+      <c r="AC173">
+        <v>1.06</v>
+      </c>
+      <c r="AD173">
+        <v>8</v>
+      </c>
+      <c r="AE173">
+        <v>1.31</v>
+      </c>
+      <c r="AF173">
+        <v>3.1</v>
+      </c>
+      <c r="AG173">
+        <v>2.05</v>
+      </c>
+      <c r="AH173">
+        <v>1.75</v>
+      </c>
+      <c r="AI173">
+        <v>1.8</v>
+      </c>
+      <c r="AJ173">
+        <v>1.95</v>
+      </c>
+      <c r="AK173">
+        <v>1.26</v>
+      </c>
+      <c r="AL173">
+        <v>1.3</v>
+      </c>
+      <c r="AM173">
+        <v>1.78</v>
+      </c>
+      <c r="AN173">
+        <v>1.7</v>
+      </c>
+      <c r="AO173">
+        <v>1.5</v>
+      </c>
+      <c r="AP173">
+        <v>1.64</v>
+      </c>
+      <c r="AQ173">
+        <v>1.45</v>
+      </c>
+      <c r="AR173">
+        <v>1.47</v>
+      </c>
+      <c r="AS173">
+        <v>1.35</v>
+      </c>
+      <c r="AT173">
+        <v>2.82</v>
+      </c>
+      <c r="AU173">
+        <v>4</v>
+      </c>
+      <c r="AV173">
+        <v>5</v>
+      </c>
+      <c r="AW173">
+        <v>4</v>
+      </c>
+      <c r="AX173">
+        <v>3</v>
+      </c>
+      <c r="AY173">
+        <v>8</v>
+      </c>
+      <c r="AZ173">
+        <v>8</v>
+      </c>
+      <c r="BA173">
+        <v>8</v>
+      </c>
+      <c r="BB173">
+        <v>4</v>
+      </c>
+      <c r="BC173">
+        <v>12</v>
+      </c>
+      <c r="BD173">
+        <v>1.78</v>
+      </c>
+      <c r="BE173">
+        <v>6.1</v>
+      </c>
+      <c r="BF173">
+        <v>2.45</v>
+      </c>
+      <c r="BG173">
+        <v>1.16</v>
+      </c>
+      <c r="BH173">
+        <v>4.4</v>
+      </c>
+      <c r="BI173">
+        <v>1.25</v>
+      </c>
+      <c r="BJ173">
+        <v>3.5</v>
+      </c>
+      <c r="BK173">
+        <v>1.48</v>
+      </c>
+      <c r="BL173">
+        <v>2.42</v>
+      </c>
+      <c r="BM173">
+        <v>1.82</v>
+      </c>
+      <c r="BN173">
+        <v>1.82</v>
+      </c>
+      <c r="BO173">
+        <v>2.42</v>
+      </c>
+      <c r="BP173">
+        <v>1.49</v>
+      </c>
+    </row>
+    <row r="174" spans="1:68">
+      <c r="A174" s="1">
+        <v>173</v>
+      </c>
+      <c r="B174">
+        <v>7468248</v>
+      </c>
+      <c r="C174" t="s">
+        <v>68</v>
+      </c>
+      <c r="D174" t="s">
+        <v>69</v>
+      </c>
+      <c r="E174" s="2">
+        <v>45704.47916666666</v>
+      </c>
+      <c r="F174">
+        <v>22</v>
+      </c>
+      <c r="G174" t="s">
+        <v>81</v>
+      </c>
+      <c r="H174" t="s">
+        <v>82</v>
+      </c>
+      <c r="I174">
+        <v>2</v>
+      </c>
+      <c r="J174">
+        <v>0</v>
+      </c>
+      <c r="K174">
+        <v>2</v>
+      </c>
+      <c r="L174">
+        <v>3</v>
+      </c>
+      <c r="M174">
+        <v>1</v>
+      </c>
+      <c r="N174">
+        <v>4</v>
+      </c>
+      <c r="O174" t="s">
+        <v>204</v>
+      </c>
+      <c r="P174" t="s">
+        <v>273</v>
+      </c>
+      <c r="Q174">
+        <v>2.66</v>
+      </c>
+      <c r="R174">
+        <v>2.28</v>
+      </c>
+      <c r="S174">
+        <v>4.06</v>
+      </c>
+      <c r="T174">
+        <v>1.35</v>
+      </c>
+      <c r="U174">
+        <v>3.16</v>
+      </c>
+      <c r="V174">
+        <v>2.71</v>
+      </c>
+      <c r="W174">
+        <v>1.45</v>
+      </c>
+      <c r="X174">
+        <v>6</v>
+      </c>
+      <c r="Y174">
+        <v>1.09</v>
+      </c>
+      <c r="Z174">
+        <v>2</v>
+      </c>
+      <c r="AA174">
+        <v>3.25</v>
+      </c>
+      <c r="AB174">
+        <v>3.25</v>
+      </c>
+      <c r="AC174">
+        <v>1.02</v>
+      </c>
+      <c r="AD174">
+        <v>10</v>
+      </c>
+      <c r="AE174">
+        <v>1.25</v>
+      </c>
+      <c r="AF174">
+        <v>3.6</v>
+      </c>
+      <c r="AG174">
+        <v>1.8</v>
+      </c>
+      <c r="AH174">
+        <v>1.91</v>
+      </c>
+      <c r="AI174">
+        <v>1.67</v>
+      </c>
+      <c r="AJ174">
+        <v>2.1</v>
+      </c>
+      <c r="AK174">
+        <v>1.3</v>
+      </c>
+      <c r="AL174">
+        <v>1.3</v>
+      </c>
+      <c r="AM174">
+        <v>1.78</v>
+      </c>
+      <c r="AN174">
+        <v>1.3</v>
+      </c>
+      <c r="AO174">
+        <v>1.2</v>
+      </c>
+      <c r="AP174">
+        <v>1.45</v>
+      </c>
+      <c r="AQ174">
+        <v>1.09</v>
+      </c>
+      <c r="AR174">
+        <v>1.42</v>
+      </c>
+      <c r="AS174">
+        <v>1.27</v>
+      </c>
+      <c r="AT174">
+        <v>2.69</v>
+      </c>
+      <c r="AU174">
+        <v>10</v>
+      </c>
+      <c r="AV174">
+        <v>4</v>
+      </c>
+      <c r="AW174">
+        <v>7</v>
+      </c>
+      <c r="AX174">
+        <v>5</v>
+      </c>
+      <c r="AY174">
+        <v>17</v>
+      </c>
+      <c r="AZ174">
+        <v>9</v>
+      </c>
+      <c r="BA174">
+        <v>7</v>
+      </c>
+      <c r="BB174">
+        <v>11</v>
+      </c>
+      <c r="BC174">
+        <v>18</v>
+      </c>
+      <c r="BD174">
+        <v>1.68</v>
+      </c>
+      <c r="BE174">
+        <v>7</v>
+      </c>
+      <c r="BF174">
+        <v>2.4</v>
+      </c>
+      <c r="BG174">
+        <v>1.2</v>
+      </c>
+      <c r="BH174">
+        <v>3.95</v>
+      </c>
+      <c r="BI174">
+        <v>1.35</v>
+      </c>
+      <c r="BJ174">
+        <v>2.9</v>
+      </c>
+      <c r="BK174">
+        <v>1.58</v>
+      </c>
+      <c r="BL174">
+        <v>2.2</v>
+      </c>
+      <c r="BM174">
+        <v>1.91</v>
+      </c>
+      <c r="BN174">
+        <v>1.78</v>
+      </c>
+      <c r="BO174">
+        <v>2.35</v>
+      </c>
+      <c r="BP174">
+        <v>1.5</v>
+      </c>
+    </row>
+    <row r="175" spans="1:68">
+      <c r="A175" s="1">
+        <v>174</v>
+      </c>
+      <c r="B175">
+        <v>7468250</v>
+      </c>
+      <c r="C175" t="s">
+        <v>68</v>
+      </c>
+      <c r="D175" t="s">
+        <v>69</v>
+      </c>
+      <c r="E175" s="2">
+        <v>45704.47916666666</v>
+      </c>
+      <c r="F175">
+        <v>22</v>
+      </c>
+      <c r="G175" t="s">
+        <v>78</v>
+      </c>
+      <c r="H175" t="s">
+        <v>84</v>
+      </c>
+      <c r="I175">
+        <v>0</v>
+      </c>
+      <c r="J175">
+        <v>2</v>
+      </c>
+      <c r="K175">
+        <v>2</v>
+      </c>
+      <c r="L175">
+        <v>0</v>
+      </c>
+      <c r="M175">
+        <v>2</v>
+      </c>
+      <c r="N175">
+        <v>2</v>
+      </c>
+      <c r="O175" t="s">
+        <v>88</v>
+      </c>
+      <c r="P175" t="s">
+        <v>288</v>
+      </c>
+      <c r="Q175">
+        <v>4.86</v>
+      </c>
+      <c r="R175">
+        <v>2.22</v>
+      </c>
+      <c r="S175">
+        <v>2.47</v>
+      </c>
+      <c r="T175">
+        <v>1.4</v>
+      </c>
+      <c r="U175">
+        <v>2.88</v>
+      </c>
+      <c r="V175">
+        <v>3.04</v>
+      </c>
+      <c r="W175">
+        <v>1.37</v>
+      </c>
+      <c r="X175">
+        <v>6.5</v>
+      </c>
+      <c r="Y175">
+        <v>1.08</v>
+      </c>
+      <c r="Z175">
+        <v>3.75</v>
+      </c>
+      <c r="AA175">
+        <v>3.3</v>
+      </c>
+      <c r="AB175">
+        <v>1.83</v>
+      </c>
+      <c r="AC175">
+        <v>1.03</v>
+      </c>
+      <c r="AD175">
+        <v>9</v>
+      </c>
+      <c r="AE175">
+        <v>1.29</v>
+      </c>
+      <c r="AF175">
+        <v>3.3</v>
+      </c>
+      <c r="AG175">
+        <v>1.91</v>
+      </c>
+      <c r="AH175">
+        <v>1.8</v>
+      </c>
+      <c r="AI175">
+        <v>1.8</v>
+      </c>
+      <c r="AJ175">
+        <v>1.91</v>
+      </c>
+      <c r="AK175">
+        <v>1.88</v>
+      </c>
+      <c r="AL175">
+        <v>1.3</v>
+      </c>
+      <c r="AM175">
+        <v>1.25</v>
+      </c>
+      <c r="AN175">
+        <v>1.3</v>
+      </c>
+      <c r="AO175">
+        <v>1.7</v>
+      </c>
+      <c r="AP175">
+        <v>1.18</v>
+      </c>
+      <c r="AQ175">
+        <v>1.82</v>
+      </c>
+      <c r="AR175">
+        <v>1.47</v>
+      </c>
+      <c r="AS175">
+        <v>1.37</v>
+      </c>
+      <c r="AT175">
+        <v>2.84</v>
+      </c>
+      <c r="AU175">
+        <v>4</v>
+      </c>
+      <c r="AV175">
+        <v>7</v>
+      </c>
+      <c r="AW175">
+        <v>7</v>
+      </c>
+      <c r="AX175">
+        <v>6</v>
+      </c>
+      <c r="AY175">
+        <v>11</v>
+      </c>
+      <c r="AZ175">
+        <v>13</v>
+      </c>
+      <c r="BA175">
+        <v>1</v>
+      </c>
+      <c r="BB175">
+        <v>4</v>
+      </c>
+      <c r="BC175">
+        <v>5</v>
+      </c>
+      <c r="BD175">
+        <v>2.7</v>
+      </c>
+      <c r="BE175">
+        <v>6.75</v>
+      </c>
+      <c r="BF175">
+        <v>1.56</v>
+      </c>
+      <c r="BG175">
+        <v>1.29</v>
+      </c>
+      <c r="BH175">
+        <v>3.15</v>
+      </c>
+      <c r="BI175">
+        <v>1.5</v>
+      </c>
+      <c r="BJ175">
+        <v>2.4</v>
+      </c>
+      <c r="BK175">
+        <v>1.81</v>
+      </c>
+      <c r="BL175">
+        <v>1.88</v>
+      </c>
+      <c r="BM175">
+        <v>2.28</v>
+      </c>
+      <c r="BN175">
+        <v>1.55</v>
+      </c>
+      <c r="BO175">
+        <v>2.88</v>
+      </c>
+      <c r="BP175">
+        <v>1.35</v>
+      </c>
+    </row>
+    <row r="176" spans="1:68">
+      <c r="A176" s="1">
+        <v>175</v>
+      </c>
+      <c r="B176">
+        <v>7468251</v>
+      </c>
+      <c r="C176" t="s">
+        <v>68</v>
+      </c>
+      <c r="D176" t="s">
+        <v>69</v>
+      </c>
+      <c r="E176" s="2">
+        <v>45704.60416666666</v>
+      </c>
+      <c r="F176">
+        <v>22</v>
+      </c>
+      <c r="G176" t="s">
+        <v>80</v>
+      </c>
+      <c r="H176" t="s">
+        <v>83</v>
+      </c>
+      <c r="I176">
+        <v>1</v>
+      </c>
+      <c r="J176">
+        <v>0</v>
+      </c>
+      <c r="K176">
+        <v>1</v>
+      </c>
+      <c r="L176">
+        <v>1</v>
+      </c>
+      <c r="M176">
+        <v>0</v>
+      </c>
+      <c r="N176">
+        <v>1</v>
+      </c>
+      <c r="O176" t="s">
+        <v>177</v>
+      </c>
+      <c r="P176" t="s">
+        <v>88</v>
+      </c>
+      <c r="Q176">
+        <v>1.64</v>
+      </c>
+      <c r="R176">
+        <v>2.87</v>
+      </c>
+      <c r="S176">
+        <v>8.779999999999999</v>
+      </c>
+      <c r="T176">
+        <v>1.25</v>
+      </c>
+      <c r="U176">
+        <v>3.6</v>
+      </c>
+      <c r="V176">
+        <v>2.29</v>
+      </c>
+      <c r="W176">
+        <v>1.61</v>
+      </c>
+      <c r="X176">
+        <v>4.75</v>
+      </c>
+      <c r="Y176">
+        <v>1.15</v>
+      </c>
+      <c r="Z176">
+        <v>1.25</v>
+      </c>
+      <c r="AA176">
+        <v>5.25</v>
+      </c>
+      <c r="AB176">
+        <v>8.5</v>
+      </c>
+      <c r="AC176">
+        <v>1</v>
+      </c>
+      <c r="AD176">
+        <v>12</v>
+      </c>
+      <c r="AE176">
+        <v>1.17</v>
+      </c>
+      <c r="AF176">
+        <v>4.5</v>
+      </c>
+      <c r="AG176">
+        <v>1.55</v>
+      </c>
+      <c r="AH176">
+        <v>2.3</v>
+      </c>
+      <c r="AI176">
+        <v>2</v>
+      </c>
+      <c r="AJ176">
+        <v>1.73</v>
+      </c>
+      <c r="AK176">
+        <v>1.05</v>
+      </c>
+      <c r="AL176">
+        <v>1.13</v>
+      </c>
+      <c r="AM176">
+        <v>3.75</v>
+      </c>
+      <c r="AN176">
+        <v>3</v>
+      </c>
+      <c r="AO176">
+        <v>1.64</v>
+      </c>
+      <c r="AP176">
+        <v>3</v>
+      </c>
+      <c r="AQ176">
+        <v>1.5</v>
+      </c>
+      <c r="AR176">
+        <v>2.32</v>
+      </c>
+      <c r="AS176">
+        <v>1.69</v>
+      </c>
+      <c r="AT176">
+        <v>4.01</v>
+      </c>
+      <c r="AU176">
+        <v>9</v>
+      </c>
+      <c r="AV176">
+        <v>4</v>
+      </c>
+      <c r="AW176">
+        <v>6</v>
+      </c>
+      <c r="AX176">
+        <v>7</v>
+      </c>
+      <c r="AY176">
+        <v>15</v>
+      </c>
+      <c r="AZ176">
+        <v>11</v>
+      </c>
+      <c r="BA176">
+        <v>5</v>
+      </c>
+      <c r="BB176">
+        <v>8</v>
+      </c>
+      <c r="BC176">
+        <v>13</v>
+      </c>
+      <c r="BD176">
+        <v>1.22</v>
+      </c>
+      <c r="BE176">
+        <v>8.5</v>
+      </c>
+      <c r="BF176">
+        <v>4.6</v>
+      </c>
+      <c r="BG176">
+        <v>1.14</v>
+      </c>
+      <c r="BH176">
+        <v>4.8</v>
+      </c>
+      <c r="BI176">
+        <v>1.25</v>
+      </c>
+      <c r="BJ176">
+        <v>3.45</v>
+      </c>
+      <c r="BK176">
+        <v>1.42</v>
+      </c>
+      <c r="BL176">
+        <v>2.65</v>
+      </c>
+      <c r="BM176">
+        <v>1.66</v>
+      </c>
+      <c r="BN176">
+        <v>2.08</v>
+      </c>
+      <c r="BO176">
+        <v>2</v>
+      </c>
+      <c r="BP176">
+        <v>1.71</v>
       </c>
     </row>
   </sheetData>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Czech Republic First League_20242025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Czech Republic First League_20242025.xlsx
@@ -529,10 +529,10 @@
     <t>['31', '42', '58']</t>
   </si>
   <si>
-    <t>['64', '89']</t>
+    <t>['90+4']</t>
   </si>
   <si>
-    <t>['90+4']</t>
+    <t>['64', '89']</t>
   </si>
   <si>
     <t>['38', '46', '77']</t>
@@ -544,13 +544,13 @@
     <t>['2', '39', '45', '88']</t>
   </si>
   <si>
-    <t>['1', '17', '20', '30', '88']</t>
+    <t>['69', '90']</t>
   </si>
   <si>
     <t>['8']</t>
   </si>
   <si>
-    <t>['69', '90']</t>
+    <t>['1', '17', '20', '30', '88']</t>
   </si>
   <si>
     <t>['16', '33']</t>
@@ -787,10 +787,10 @@
     <t>['35']</t>
   </si>
   <si>
-    <t>['61']</t>
+    <t>['23']</t>
   </si>
   <si>
-    <t>['23']</t>
+    <t>['61']</t>
   </si>
   <si>
     <t>['83']</t>
@@ -814,10 +814,10 @@
     <t>['36']</t>
   </si>
   <si>
-    <t>['51', '56']</t>
+    <t>['38', '78']</t>
   </si>
   <si>
-    <t>['38', '78']</t>
+    <t>['51', '56']</t>
   </si>
   <si>
     <t>['12', '16', '51']</t>
@@ -826,10 +826,10 @@
     <t>['29']</t>
   </si>
   <si>
-    <t>['76', '86']</t>
+    <t>['60', '65', '68', '90+3']</t>
   </si>
   <si>
-    <t>['60', '65', '68', '90+3']</t>
+    <t>['76', '86']</t>
   </si>
   <si>
     <t>['79', '81']</t>
@@ -24528,7 +24528,7 @@
         <v>113</v>
       </c>
       <c r="B114">
-        <v>7468206</v>
+        <v>7468203</v>
       </c>
       <c r="C114" t="s">
         <v>68</v>
@@ -24543,19 +24543,19 @@
         <v>16</v>
       </c>
       <c r="G114" t="s">
-        <v>70</v>
+        <v>76</v>
       </c>
       <c r="H114" t="s">
-        <v>78</v>
+        <v>82</v>
       </c>
       <c r="I114">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J114">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K114">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L114">
         <v>1</v>
@@ -24567,127 +24567,127 @@
         <v>2</v>
       </c>
       <c r="O114" t="s">
-        <v>99</v>
+        <v>151</v>
       </c>
       <c r="P114" t="s">
         <v>257</v>
       </c>
       <c r="Q114">
-        <v>1.73</v>
+        <v>2.88</v>
       </c>
       <c r="R114">
+        <v>2.1</v>
+      </c>
+      <c r="S114">
+        <v>3.75</v>
+      </c>
+      <c r="T114">
+        <v>1.44</v>
+      </c>
+      <c r="U114">
         <v>2.63</v>
       </c>
-      <c r="S114">
-        <v>8.5</v>
-      </c>
-      <c r="T114">
-        <v>1.29</v>
-      </c>
-      <c r="U114">
-        <v>3.5</v>
-      </c>
       <c r="V114">
-        <v>2.38</v>
+        <v>3.25</v>
       </c>
       <c r="W114">
-        <v>1.53</v>
+        <v>1.33</v>
       </c>
       <c r="X114">
-        <v>5.5</v>
+        <v>9</v>
       </c>
       <c r="Y114">
+        <v>1.07</v>
+      </c>
+      <c r="Z114">
+        <v>3.09</v>
+      </c>
+      <c r="AA114">
+        <v>4.51</v>
+      </c>
+      <c r="AB114">
+        <v>1.77</v>
+      </c>
+      <c r="AC114">
+        <v>1.03</v>
+      </c>
+      <c r="AD114">
+        <v>6.8</v>
+      </c>
+      <c r="AE114">
+        <v>1.33</v>
+      </c>
+      <c r="AF114">
+        <v>3.1</v>
+      </c>
+      <c r="AG114">
+        <v>2.04</v>
+      </c>
+      <c r="AH114">
+        <v>1.78</v>
+      </c>
+      <c r="AI114">
+        <v>1.8</v>
+      </c>
+      <c r="AJ114">
+        <v>1.95</v>
+      </c>
+      <c r="AK114">
+        <v>1.35</v>
+      </c>
+      <c r="AL114">
+        <v>1.25</v>
+      </c>
+      <c r="AM114">
+        <v>1.63</v>
+      </c>
+      <c r="AN114">
+        <v>1.71</v>
+      </c>
+      <c r="AO114">
         <v>1.14</v>
       </c>
-      <c r="Z114">
-        <v>1.24</v>
-      </c>
-      <c r="AA114">
-        <v>4.84</v>
-      </c>
-      <c r="AB114">
-        <v>7.43</v>
-      </c>
-      <c r="AC114">
-        <v>1.01</v>
-      </c>
-      <c r="AD114">
-        <v>13</v>
-      </c>
-      <c r="AE114">
-        <v>1.16</v>
-      </c>
-      <c r="AF114">
-        <v>4.75</v>
-      </c>
-      <c r="AG114">
-        <v>1.57</v>
-      </c>
-      <c r="AH114">
-        <v>2.25</v>
-      </c>
-      <c r="AI114">
-        <v>2</v>
-      </c>
-      <c r="AJ114">
-        <v>1.75</v>
-      </c>
-      <c r="AK114">
-        <v>1.02</v>
-      </c>
-      <c r="AL114">
-        <v>1.1</v>
-      </c>
-      <c r="AM114">
-        <v>3.5</v>
-      </c>
-      <c r="AN114">
-        <v>1.67</v>
-      </c>
-      <c r="AO114">
-        <v>1</v>
-      </c>
       <c r="AP114">
-        <v>2.09</v>
+        <v>1.36</v>
       </c>
       <c r="AQ114">
-        <v>0.82</v>
+        <v>1.09</v>
       </c>
       <c r="AR114">
-        <v>1.87</v>
+        <v>1.11</v>
       </c>
       <c r="AS114">
-        <v>1.26</v>
+        <v>1.28</v>
       </c>
       <c r="AT114">
-        <v>3.13</v>
+        <v>2.39</v>
       </c>
       <c r="AU114">
+        <v>-1</v>
+      </c>
+      <c r="AV114">
+        <v>-1</v>
+      </c>
+      <c r="AW114">
+        <v>-1</v>
+      </c>
+      <c r="AX114">
+        <v>-1</v>
+      </c>
+      <c r="AY114">
+        <v>-1</v>
+      </c>
+      <c r="AZ114">
+        <v>-1</v>
+      </c>
+      <c r="BA114">
+        <v>3</v>
+      </c>
+      <c r="BB114">
         <v>9</v>
       </c>
-      <c r="AV114">
-        <v>4</v>
-      </c>
-      <c r="AW114">
-        <v>6</v>
-      </c>
-      <c r="AX114">
-        <v>2</v>
-      </c>
-      <c r="AY114">
-        <v>15</v>
-      </c>
-      <c r="AZ114">
-        <v>6</v>
-      </c>
-      <c r="BA114">
-        <v>5</v>
-      </c>
-      <c r="BB114">
-        <v>1</v>
-      </c>
       <c r="BC114">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="BD114">
         <v>0</v>
@@ -24734,7 +24734,7 @@
         <v>114</v>
       </c>
       <c r="B115">
-        <v>7468203</v>
+        <v>7468206</v>
       </c>
       <c r="C115" t="s">
         <v>68</v>
@@ -24749,19 +24749,19 @@
         <v>16</v>
       </c>
       <c r="G115" t="s">
-        <v>76</v>
+        <v>70</v>
       </c>
       <c r="H115" t="s">
-        <v>82</v>
+        <v>78</v>
       </c>
       <c r="I115">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J115">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K115">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L115">
         <v>1</v>
@@ -24773,127 +24773,127 @@
         <v>2</v>
       </c>
       <c r="O115" t="s">
-        <v>151</v>
+        <v>99</v>
       </c>
       <c r="P115" t="s">
         <v>258</v>
       </c>
       <c r="Q115">
-        <v>2.88</v>
+        <v>1.73</v>
       </c>
       <c r="R115">
-        <v>2.1</v>
+        <v>2.63</v>
       </c>
       <c r="S115">
-        <v>3.75</v>
+        <v>8.5</v>
       </c>
       <c r="T115">
-        <v>1.44</v>
+        <v>1.29</v>
       </c>
       <c r="U115">
-        <v>2.63</v>
+        <v>3.5</v>
       </c>
       <c r="V115">
-        <v>3.25</v>
+        <v>2.38</v>
       </c>
       <c r="W115">
-        <v>1.33</v>
+        <v>1.53</v>
       </c>
       <c r="X115">
+        <v>5.5</v>
+      </c>
+      <c r="Y115">
+        <v>1.14</v>
+      </c>
+      <c r="Z115">
+        <v>1.24</v>
+      </c>
+      <c r="AA115">
+        <v>4.84</v>
+      </c>
+      <c r="AB115">
+        <v>7.43</v>
+      </c>
+      <c r="AC115">
+        <v>1.01</v>
+      </c>
+      <c r="AD115">
+        <v>13</v>
+      </c>
+      <c r="AE115">
+        <v>1.16</v>
+      </c>
+      <c r="AF115">
+        <v>4.75</v>
+      </c>
+      <c r="AG115">
+        <v>1.57</v>
+      </c>
+      <c r="AH115">
+        <v>2.25</v>
+      </c>
+      <c r="AI115">
+        <v>2</v>
+      </c>
+      <c r="AJ115">
+        <v>1.75</v>
+      </c>
+      <c r="AK115">
+        <v>1.02</v>
+      </c>
+      <c r="AL115">
+        <v>1.1</v>
+      </c>
+      <c r="AM115">
+        <v>3.5</v>
+      </c>
+      <c r="AN115">
+        <v>1.67</v>
+      </c>
+      <c r="AO115">
+        <v>1</v>
+      </c>
+      <c r="AP115">
+        <v>2.09</v>
+      </c>
+      <c r="AQ115">
+        <v>0.82</v>
+      </c>
+      <c r="AR115">
+        <v>1.87</v>
+      </c>
+      <c r="AS115">
+        <v>1.26</v>
+      </c>
+      <c r="AT115">
+        <v>3.13</v>
+      </c>
+      <c r="AU115">
         <v>9</v>
       </c>
-      <c r="Y115">
-        <v>1.07</v>
-      </c>
-      <c r="Z115">
-        <v>3.09</v>
-      </c>
-      <c r="AA115">
-        <v>4.51</v>
-      </c>
-      <c r="AB115">
-        <v>1.77</v>
-      </c>
-      <c r="AC115">
-        <v>1.03</v>
-      </c>
-      <c r="AD115">
-        <v>6.8</v>
-      </c>
-      <c r="AE115">
-        <v>1.33</v>
-      </c>
-      <c r="AF115">
-        <v>3.1</v>
-      </c>
-      <c r="AG115">
-        <v>2.04</v>
-      </c>
-      <c r="AH115">
-        <v>1.78</v>
-      </c>
-      <c r="AI115">
-        <v>1.8</v>
-      </c>
-      <c r="AJ115">
-        <v>1.95</v>
-      </c>
-      <c r="AK115">
-        <v>1.35</v>
-      </c>
-      <c r="AL115">
-        <v>1.25</v>
-      </c>
-      <c r="AM115">
-        <v>1.63</v>
-      </c>
-      <c r="AN115">
-        <v>1.71</v>
-      </c>
-      <c r="AO115">
-        <v>1.14</v>
-      </c>
-      <c r="AP115">
-        <v>1.36</v>
-      </c>
-      <c r="AQ115">
-        <v>1.09</v>
-      </c>
-      <c r="AR115">
-        <v>1.11</v>
-      </c>
-      <c r="AS115">
-        <v>1.28</v>
-      </c>
-      <c r="AT115">
-        <v>2.39</v>
-      </c>
-      <c r="AU115">
-        <v>-1</v>
-      </c>
       <c r="AV115">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="AW115">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="AX115">
-        <v>-1</v>
+        <v>2</v>
       </c>
       <c r="AY115">
-        <v>-1</v>
+        <v>15</v>
       </c>
       <c r="AZ115">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="BA115">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="BB115">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="BC115">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="BD115">
         <v>0</v>
@@ -25352,7 +25352,7 @@
         <v>117</v>
       </c>
       <c r="B118">
-        <v>7468202</v>
+        <v>7468201</v>
       </c>
       <c r="C118" t="s">
         <v>68</v>
@@ -25364,151 +25364,151 @@
         <v>45620.47916666666</v>
       </c>
       <c r="F118">
-        <v>16</v>
+        <v>0</v>
       </c>
       <c r="G118" t="s">
-        <v>72</v>
+        <v>75</v>
       </c>
       <c r="H118" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="I118">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J118">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="K118">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="L118">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M118">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="N118">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="O118" t="s">
+        <v>167</v>
+      </c>
+      <c r="P118" t="s">
         <v>88</v>
       </c>
-      <c r="P118" t="s">
-        <v>260</v>
-      </c>
       <c r="Q118">
-        <v>15</v>
+        <v>2.2</v>
       </c>
       <c r="R118">
+        <v>2.3</v>
+      </c>
+      <c r="S118">
+        <v>5.5</v>
+      </c>
+      <c r="T118">
+        <v>1.33</v>
+      </c>
+      <c r="U118">
+        <v>3.25</v>
+      </c>
+      <c r="V118">
+        <v>2.63</v>
+      </c>
+      <c r="W118">
+        <v>1.44</v>
+      </c>
+      <c r="X118">
+        <v>6.5</v>
+      </c>
+      <c r="Y118">
+        <v>1.11</v>
+      </c>
+      <c r="Z118">
+        <v>1.55</v>
+      </c>
+      <c r="AA118">
+        <v>3.8</v>
+      </c>
+      <c r="AB118">
+        <v>4.7</v>
+      </c>
+      <c r="AC118">
+        <v>0</v>
+      </c>
+      <c r="AD118">
+        <v>0</v>
+      </c>
+      <c r="AE118">
+        <v>4.5</v>
+      </c>
+      <c r="AF118">
+        <v>1.14</v>
+      </c>
+      <c r="AG118">
+        <v>1.73</v>
+      </c>
+      <c r="AH118">
+        <v>2</v>
+      </c>
+      <c r="AI118">
+        <v>1.75</v>
+      </c>
+      <c r="AJ118">
+        <v>2</v>
+      </c>
+      <c r="AK118">
+        <v>0</v>
+      </c>
+      <c r="AL118">
+        <v>0</v>
+      </c>
+      <c r="AM118">
+        <v>0</v>
+      </c>
+      <c r="AN118">
+        <v>1.5</v>
+      </c>
+      <c r="AO118">
+        <v>0.63</v>
+      </c>
+      <c r="AP118">
+        <v>1.33</v>
+      </c>
+      <c r="AQ118">
+        <v>0.5</v>
+      </c>
+      <c r="AR118">
+        <v>1.64</v>
+      </c>
+      <c r="AS118">
+        <v>1.02</v>
+      </c>
+      <c r="AT118">
+        <v>2.66</v>
+      </c>
+      <c r="AU118">
         <v>3</v>
       </c>
-      <c r="S118">
-        <v>1.44</v>
-      </c>
-      <c r="T118">
-        <v>1.25</v>
-      </c>
-      <c r="U118">
-        <v>3.75</v>
-      </c>
-      <c r="V118">
-        <v>2.1</v>
-      </c>
-      <c r="W118">
-        <v>1.67</v>
-      </c>
-      <c r="X118">
-        <v>5</v>
-      </c>
-      <c r="Y118">
-        <v>1.17</v>
-      </c>
-      <c r="Z118">
+      <c r="AV118">
+        <v>6</v>
+      </c>
+      <c r="AW118">
+        <v>7</v>
+      </c>
+      <c r="AX118">
+        <v>0</v>
+      </c>
+      <c r="AY118">
+        <v>10</v>
+      </c>
+      <c r="AZ118">
         <v>11</v>
       </c>
-      <c r="AA118">
-        <v>7.5</v>
-      </c>
-      <c r="AB118">
-        <v>1.12</v>
-      </c>
-      <c r="AC118">
-        <v>0</v>
-      </c>
-      <c r="AD118">
-        <v>0</v>
-      </c>
-      <c r="AE118">
-        <v>0</v>
-      </c>
-      <c r="AF118">
-        <v>0</v>
-      </c>
-      <c r="AG118">
-        <v>1.46</v>
-      </c>
-      <c r="AH118">
-        <v>2.6</v>
-      </c>
-      <c r="AI118">
-        <v>2.5</v>
-      </c>
-      <c r="AJ118">
-        <v>1.5</v>
-      </c>
-      <c r="AK118">
-        <v>0</v>
-      </c>
-      <c r="AL118">
-        <v>0</v>
-      </c>
-      <c r="AM118">
-        <v>0</v>
-      </c>
-      <c r="AN118">
-        <v>0.25</v>
-      </c>
-      <c r="AO118">
-        <v>2.33</v>
-      </c>
-      <c r="AP118">
-        <v>0.25</v>
-      </c>
-      <c r="AQ118">
-        <v>2.36</v>
-      </c>
-      <c r="AR118">
-        <v>1.38</v>
-      </c>
-      <c r="AS118">
-        <v>1.61</v>
-      </c>
-      <c r="AT118">
-        <v>2.99</v>
-      </c>
-      <c r="AU118">
-        <v>2</v>
-      </c>
-      <c r="AV118">
-        <v>7</v>
-      </c>
-      <c r="AW118">
-        <v>4</v>
-      </c>
-      <c r="AX118">
-        <v>4</v>
-      </c>
-      <c r="AY118">
-        <v>8</v>
-      </c>
-      <c r="AZ118">
-        <v>16</v>
-      </c>
       <c r="BA118">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="BB118">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="BC118">
         <v>9</v>
@@ -25558,7 +25558,7 @@
         <v>118</v>
       </c>
       <c r="B119">
-        <v>7468201</v>
+        <v>7468202</v>
       </c>
       <c r="C119" t="s">
         <v>68</v>
@@ -25570,73 +25570,73 @@
         <v>45620.47916666666</v>
       </c>
       <c r="F119">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="G119" t="s">
-        <v>75</v>
+        <v>72</v>
       </c>
       <c r="H119" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="I119">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J119">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K119">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L119">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M119">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="N119">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="O119" t="s">
-        <v>167</v>
+        <v>88</v>
       </c>
       <c r="P119" t="s">
-        <v>88</v>
+        <v>260</v>
       </c>
       <c r="Q119">
-        <v>2.2</v>
+        <v>15</v>
       </c>
       <c r="R119">
-        <v>2.3</v>
+        <v>3</v>
       </c>
       <c r="S119">
-        <v>5.5</v>
+        <v>1.44</v>
       </c>
       <c r="T119">
-        <v>1.33</v>
+        <v>1.25</v>
       </c>
       <c r="U119">
-        <v>3.25</v>
+        <v>3.75</v>
       </c>
       <c r="V119">
-        <v>2.63</v>
+        <v>2.1</v>
       </c>
       <c r="W119">
-        <v>1.44</v>
+        <v>1.67</v>
       </c>
       <c r="X119">
-        <v>6.5</v>
+        <v>5</v>
       </c>
       <c r="Y119">
-        <v>1.11</v>
+        <v>1.17</v>
       </c>
       <c r="Z119">
-        <v>1.55</v>
+        <v>11</v>
       </c>
       <c r="AA119">
-        <v>3.8</v>
+        <v>7.5</v>
       </c>
       <c r="AB119">
-        <v>4.7</v>
+        <v>1.12</v>
       </c>
       <c r="AC119">
         <v>0</v>
@@ -25645,22 +25645,22 @@
         <v>0</v>
       </c>
       <c r="AE119">
-        <v>4.5</v>
+        <v>0</v>
       </c>
       <c r="AF119">
-        <v>1.14</v>
+        <v>0</v>
       </c>
       <c r="AG119">
-        <v>1.73</v>
+        <v>1.46</v>
       </c>
       <c r="AH119">
-        <v>2</v>
+        <v>2.6</v>
       </c>
       <c r="AI119">
-        <v>1.75</v>
+        <v>2.5</v>
       </c>
       <c r="AJ119">
-        <v>2</v>
+        <v>1.5</v>
       </c>
       <c r="AK119">
         <v>0</v>
@@ -25672,49 +25672,49 @@
         <v>0</v>
       </c>
       <c r="AN119">
-        <v>1.5</v>
+        <v>0.25</v>
       </c>
       <c r="AO119">
-        <v>0.63</v>
+        <v>2.33</v>
       </c>
       <c r="AP119">
-        <v>1.33</v>
+        <v>0.25</v>
       </c>
       <c r="AQ119">
-        <v>0.5</v>
+        <v>2.36</v>
       </c>
       <c r="AR119">
-        <v>1.64</v>
+        <v>1.38</v>
       </c>
       <c r="AS119">
-        <v>1.02</v>
+        <v>1.61</v>
       </c>
       <c r="AT119">
-        <v>2.66</v>
+        <v>2.99</v>
       </c>
       <c r="AU119">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AV119">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AW119">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="AX119">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="AY119">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="AZ119">
-        <v>11</v>
+        <v>16</v>
       </c>
       <c r="BA119">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="BB119">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="BC119">
         <v>9</v>
@@ -26382,7 +26382,7 @@
         <v>122</v>
       </c>
       <c r="B123">
-        <v>7468214</v>
+        <v>7468209</v>
       </c>
       <c r="C123" t="s">
         <v>68</v>
@@ -26397,127 +26397,127 @@
         <v>17</v>
       </c>
       <c r="G123" t="s">
-        <v>83</v>
+        <v>78</v>
       </c>
       <c r="H123" t="s">
-        <v>75</v>
+        <v>85</v>
       </c>
       <c r="I123">
         <v>0</v>
       </c>
       <c r="J123">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K123">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L123">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="M123">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N123">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="O123" t="s">
         <v>171</v>
       </c>
       <c r="P123" t="s">
-        <v>210</v>
+        <v>88</v>
       </c>
       <c r="Q123">
-        <v>1.83</v>
+        <v>3.1</v>
       </c>
       <c r="R123">
-        <v>2.55</v>
+        <v>2.2</v>
       </c>
       <c r="S123">
-        <v>5.95</v>
+        <v>3.4</v>
       </c>
       <c r="T123">
+        <v>1.4</v>
+      </c>
+      <c r="U123">
+        <v>2.75</v>
+      </c>
+      <c r="V123">
+        <v>2.75</v>
+      </c>
+      <c r="W123">
+        <v>1.4</v>
+      </c>
+      <c r="X123">
+        <v>8</v>
+      </c>
+      <c r="Y123">
+        <v>1.08</v>
+      </c>
+      <c r="Z123">
+        <v>2.21</v>
+      </c>
+      <c r="AA123">
+        <v>3.25</v>
+      </c>
+      <c r="AB123">
+        <v>2.95</v>
+      </c>
+      <c r="AC123">
+        <v>1.02</v>
+      </c>
+      <c r="AD123">
+        <v>7.2</v>
+      </c>
+      <c r="AE123">
         <v>1.25</v>
       </c>
-      <c r="U123">
-        <v>3.72</v>
-      </c>
-      <c r="V123">
-        <v>2.23</v>
-      </c>
-      <c r="W123">
-        <v>1.61</v>
-      </c>
-      <c r="X123">
-        <v>5.05</v>
-      </c>
-      <c r="Y123">
-        <v>1.15</v>
-      </c>
-      <c r="Z123">
-        <v>1.41</v>
-      </c>
-      <c r="AA123">
-        <v>4.7</v>
-      </c>
-      <c r="AB123">
-        <v>5.6</v>
-      </c>
-      <c r="AC123">
-        <v>1.01</v>
-      </c>
-      <c r="AD123">
-        <v>17</v>
-      </c>
-      <c r="AE123">
-        <v>1.1</v>
-      </c>
       <c r="AF123">
-        <v>4.8</v>
+        <v>3.14</v>
       </c>
       <c r="AG123">
-        <v>1.46</v>
+        <v>2.09</v>
       </c>
       <c r="AH123">
-        <v>2.52</v>
+        <v>1.73</v>
       </c>
       <c r="AI123">
-        <v>1.68</v>
+        <v>1.7</v>
       </c>
       <c r="AJ123">
-        <v>2.06</v>
+        <v>2.05</v>
       </c>
       <c r="AK123">
+        <v>1.42</v>
+      </c>
+      <c r="AL123">
+        <v>1.25</v>
+      </c>
+      <c r="AM123">
+        <v>1.52</v>
+      </c>
+      <c r="AN123">
+        <v>0.88</v>
+      </c>
+      <c r="AO123">
+        <v>1.14</v>
+      </c>
+      <c r="AP123">
+        <v>1.18</v>
+      </c>
+      <c r="AQ123">
         <v>1.09</v>
       </c>
-      <c r="AL123">
-        <v>1.16</v>
-      </c>
-      <c r="AM123">
-        <v>2.82</v>
-      </c>
-      <c r="AN123">
-        <v>2.5</v>
-      </c>
-      <c r="AO123">
-        <v>1.17</v>
-      </c>
-      <c r="AP123">
-        <v>2.4</v>
-      </c>
-      <c r="AQ123">
-        <v>0.89</v>
-      </c>
       <c r="AR123">
-        <v>1.87</v>
+        <v>1.58</v>
       </c>
       <c r="AS123">
-        <v>1.62</v>
+        <v>1.2</v>
       </c>
       <c r="AT123">
-        <v>3.49</v>
+        <v>2.78</v>
       </c>
       <c r="AU123">
-        <v>12</v>
+        <v>2</v>
       </c>
       <c r="AV123">
         <v>4</v>
@@ -26526,31 +26526,31 @@
         <v>9</v>
       </c>
       <c r="AX123">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AY123">
-        <v>37</v>
+        <v>13</v>
       </c>
       <c r="AZ123">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="BA123">
-        <v>16</v>
+        <v>6</v>
       </c>
       <c r="BB123">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BC123">
-        <v>17</v>
+        <v>6</v>
       </c>
       <c r="BD123">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="BE123">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="BF123">
-        <v>4.42</v>
+        <v>0</v>
       </c>
       <c r="BG123">
         <v>0</v>
@@ -26571,10 +26571,10 @@
         <v>0</v>
       </c>
       <c r="BM123">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="BN123">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="BO123">
         <v>0</v>
@@ -26588,7 +26588,7 @@
         <v>123</v>
       </c>
       <c r="B124">
-        <v>7468209</v>
+        <v>7468214</v>
       </c>
       <c r="C124" t="s">
         <v>68</v>
@@ -26603,127 +26603,127 @@
         <v>17</v>
       </c>
       <c r="G124" t="s">
-        <v>78</v>
+        <v>83</v>
       </c>
       <c r="H124" t="s">
-        <v>85</v>
+        <v>75</v>
       </c>
       <c r="I124">
         <v>0</v>
       </c>
       <c r="J124">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K124">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L124">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M124">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N124">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="O124" t="s">
         <v>172</v>
       </c>
       <c r="P124" t="s">
-        <v>88</v>
+        <v>210</v>
       </c>
       <c r="Q124">
-        <v>3.1</v>
+        <v>1.83</v>
       </c>
       <c r="R124">
-        <v>2.2</v>
+        <v>2.55</v>
       </c>
       <c r="S124">
-        <v>3.4</v>
+        <v>5.95</v>
       </c>
       <c r="T124">
-        <v>1.4</v>
+        <v>1.25</v>
       </c>
       <c r="U124">
-        <v>2.75</v>
+        <v>3.72</v>
       </c>
       <c r="V124">
-        <v>2.75</v>
+        <v>2.23</v>
       </c>
       <c r="W124">
-        <v>1.4</v>
+        <v>1.61</v>
       </c>
       <c r="X124">
-        <v>8</v>
+        <v>5.05</v>
       </c>
       <c r="Y124">
-        <v>1.08</v>
+        <v>1.15</v>
       </c>
       <c r="Z124">
-        <v>2.21</v>
+        <v>1.41</v>
       </c>
       <c r="AA124">
-        <v>3.25</v>
+        <v>4.7</v>
       </c>
       <c r="AB124">
-        <v>2.95</v>
+        <v>5.6</v>
       </c>
       <c r="AC124">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="AD124">
-        <v>7.2</v>
+        <v>17</v>
       </c>
       <c r="AE124">
-        <v>1.25</v>
+        <v>1.1</v>
       </c>
       <c r="AF124">
-        <v>3.14</v>
+        <v>4.8</v>
       </c>
       <c r="AG124">
-        <v>2.09</v>
+        <v>1.46</v>
       </c>
       <c r="AH124">
-        <v>1.73</v>
+        <v>2.52</v>
       </c>
       <c r="AI124">
-        <v>1.7</v>
+        <v>1.68</v>
       </c>
       <c r="AJ124">
-        <v>2.05</v>
+        <v>2.06</v>
       </c>
       <c r="AK124">
-        <v>1.42</v>
+        <v>1.09</v>
       </c>
       <c r="AL124">
-        <v>1.25</v>
+        <v>1.16</v>
       </c>
       <c r="AM124">
-        <v>1.52</v>
+        <v>2.82</v>
       </c>
       <c r="AN124">
-        <v>0.88</v>
+        <v>2.5</v>
       </c>
       <c r="AO124">
-        <v>1.14</v>
+        <v>1.17</v>
       </c>
       <c r="AP124">
-        <v>1.18</v>
+        <v>2.4</v>
       </c>
       <c r="AQ124">
-        <v>1.09</v>
+        <v>0.89</v>
       </c>
       <c r="AR124">
-        <v>1.58</v>
+        <v>1.87</v>
       </c>
       <c r="AS124">
-        <v>1.2</v>
+        <v>1.62</v>
       </c>
       <c r="AT124">
-        <v>2.78</v>
+        <v>3.49</v>
       </c>
       <c r="AU124">
-        <v>2</v>
+        <v>12</v>
       </c>
       <c r="AV124">
         <v>4</v>
@@ -26732,31 +26732,31 @@
         <v>9</v>
       </c>
       <c r="AX124">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AY124">
-        <v>13</v>
+        <v>37</v>
       </c>
       <c r="AZ124">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="BA124">
-        <v>6</v>
+        <v>16</v>
       </c>
       <c r="BB124">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BC124">
-        <v>6</v>
+        <v>17</v>
       </c>
       <c r="BD124">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="BE124">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="BF124">
-        <v>0</v>
+        <v>4.42</v>
       </c>
       <c r="BG124">
         <v>0</v>
@@ -26777,10 +26777,10 @@
         <v>0</v>
       </c>
       <c r="BM124">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="BN124">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="BO124">
         <v>0</v>
@@ -26833,7 +26833,7 @@
         <v>2</v>
       </c>
       <c r="O125" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="P125" t="s">
         <v>263</v>
@@ -28030,7 +28030,7 @@
         <v>130</v>
       </c>
       <c r="B131">
-        <v>7468143</v>
+        <v>7468137</v>
       </c>
       <c r="C131" t="s">
         <v>68</v>
@@ -28045,160 +28045,160 @@
         <v>8</v>
       </c>
       <c r="G131" t="s">
-        <v>71</v>
+        <v>79</v>
       </c>
       <c r="H131" t="s">
-        <v>72</v>
+        <v>85</v>
       </c>
       <c r="I131">
+        <v>0</v>
+      </c>
+      <c r="J131">
+        <v>1</v>
+      </c>
+      <c r="K131">
+        <v>1</v>
+      </c>
+      <c r="L131">
+        <v>2</v>
+      </c>
+      <c r="M131">
+        <v>2</v>
+      </c>
+      <c r="N131">
         <v>4</v>
-      </c>
-      <c r="J131">
-        <v>0</v>
-      </c>
-      <c r="K131">
-        <v>4</v>
-      </c>
-      <c r="L131">
-        <v>5</v>
-      </c>
-      <c r="M131">
-        <v>0</v>
-      </c>
-      <c r="N131">
-        <v>5</v>
       </c>
       <c r="O131" t="s">
         <v>176</v>
       </c>
       <c r="P131" t="s">
-        <v>88</v>
+        <v>266</v>
       </c>
       <c r="Q131">
+        <v>3.5</v>
+      </c>
+      <c r="R131">
+        <v>2.1</v>
+      </c>
+      <c r="S131">
+        <v>2.8</v>
+      </c>
+      <c r="T131">
+        <v>1.37</v>
+      </c>
+      <c r="U131">
+        <v>2.85</v>
+      </c>
+      <c r="V131">
+        <v>2.7</v>
+      </c>
+      <c r="W131">
+        <v>1.41</v>
+      </c>
+      <c r="X131">
+        <v>6.45</v>
+      </c>
+      <c r="Y131">
+        <v>1.09</v>
+      </c>
+      <c r="Z131">
+        <v>3.42</v>
+      </c>
+      <c r="AA131">
+        <v>3.42</v>
+      </c>
+      <c r="AB131">
+        <v>2.13</v>
+      </c>
+      <c r="AC131">
+        <v>1.05</v>
+      </c>
+      <c r="AD131">
+        <v>12.75</v>
+      </c>
+      <c r="AE131">
+        <v>1.28</v>
+      </c>
+      <c r="AF131">
+        <v>3.5</v>
+      </c>
+      <c r="AG131">
         <v>1.92</v>
       </c>
-      <c r="R131">
-        <v>2.5</v>
-      </c>
-      <c r="S131">
-        <v>5.6</v>
-      </c>
-      <c r="T131">
-        <v>1.31</v>
-      </c>
-      <c r="U131">
-        <v>3.28</v>
-      </c>
-      <c r="V131">
-        <v>2.46</v>
-      </c>
-      <c r="W131">
-        <v>1.51</v>
-      </c>
-      <c r="X131">
-        <v>5.75</v>
-      </c>
-      <c r="Y131">
-        <v>1.12</v>
-      </c>
-      <c r="Z131">
+      <c r="AH131">
+        <v>1.88</v>
+      </c>
+      <c r="AI131">
+        <v>1.7</v>
+      </c>
+      <c r="AJ131">
+        <v>2.1</v>
+      </c>
+      <c r="AK131">
+        <v>1.63</v>
+      </c>
+      <c r="AL131">
+        <v>1.25</v>
+      </c>
+      <c r="AM131">
         <v>1.36</v>
       </c>
-      <c r="AA131">
-        <v>5.2</v>
-      </c>
-      <c r="AB131">
-        <v>7.85</v>
-      </c>
-      <c r="AC131">
-        <v>1.02</v>
-      </c>
-      <c r="AD131">
-        <v>10</v>
-      </c>
-      <c r="AE131">
-        <v>1.17</v>
-      </c>
-      <c r="AF131">
-        <v>4.2</v>
-      </c>
-      <c r="AG131">
-        <v>1.57</v>
-      </c>
-      <c r="AH131">
-        <v>2.33</v>
-      </c>
-      <c r="AI131">
-        <v>1.8</v>
-      </c>
-      <c r="AJ131">
-        <v>1.93</v>
-      </c>
-      <c r="AK131">
+      <c r="AN131">
+        <v>1</v>
+      </c>
+      <c r="AO131">
+        <v>1</v>
+      </c>
+      <c r="AP131">
+        <v>0.9</v>
+      </c>
+      <c r="AQ131">
         <v>1.09</v>
       </c>
-      <c r="AL131">
-        <v>1.17</v>
-      </c>
-      <c r="AM131">
-        <v>2.65</v>
-      </c>
-      <c r="AN131">
-        <v>1.86</v>
-      </c>
-      <c r="AO131">
-        <v>0.14</v>
-      </c>
-      <c r="AP131">
-        <v>2</v>
-      </c>
-      <c r="AQ131">
-        <v>0.1</v>
-      </c>
       <c r="AR131">
-        <v>1.63</v>
+        <v>1.21</v>
       </c>
       <c r="AS131">
-        <v>0.9</v>
+        <v>1.18</v>
       </c>
       <c r="AT131">
-        <v>2.53</v>
+        <v>2.39</v>
       </c>
       <c r="AU131">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="AV131">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="AW131">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AX131">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AY131">
-        <v>19</v>
+        <v>14</v>
       </c>
       <c r="AZ131">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="BA131">
+        <v>6</v>
+      </c>
+      <c r="BB131">
+        <v>2</v>
+      </c>
+      <c r="BC131">
         <v>8</v>
       </c>
-      <c r="BB131">
-        <v>2</v>
-      </c>
-      <c r="BC131">
-        <v>10</v>
-      </c>
       <c r="BD131">
-        <v>1.26</v>
+        <v>2.12</v>
       </c>
       <c r="BE131">
-        <v>8.5</v>
+        <v>6.65</v>
       </c>
       <c r="BF131">
-        <v>5.15</v>
+        <v>2.07</v>
       </c>
       <c r="BG131">
         <v>0</v>
@@ -28207,25 +28207,25 @@
         <v>0</v>
       </c>
       <c r="BI131">
-        <v>1.27</v>
+        <v>1.25</v>
       </c>
       <c r="BJ131">
-        <v>3.28</v>
+        <v>3.42</v>
       </c>
       <c r="BK131">
-        <v>1.49</v>
+        <v>1.46</v>
       </c>
       <c r="BL131">
-        <v>2.38</v>
+        <v>2.45</v>
       </c>
       <c r="BM131">
-        <v>1.95</v>
+        <v>1.77</v>
       </c>
       <c r="BN131">
-        <v>1.85</v>
+        <v>2.02</v>
       </c>
       <c r="BO131">
-        <v>2.19</v>
+        <v>2.2</v>
       </c>
       <c r="BP131">
         <v>1.64</v>
@@ -28278,7 +28278,7 @@
         <v>177</v>
       </c>
       <c r="P132" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="Q132">
         <v>4.04</v>
@@ -28442,7 +28442,7 @@
         <v>132</v>
       </c>
       <c r="B133">
-        <v>7468137</v>
+        <v>7468143</v>
       </c>
       <c r="C133" t="s">
         <v>68</v>
@@ -28457,160 +28457,160 @@
         <v>8</v>
       </c>
       <c r="G133" t="s">
-        <v>79</v>
+        <v>71</v>
       </c>
       <c r="H133" t="s">
-        <v>85</v>
+        <v>72</v>
       </c>
       <c r="I133">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="J133">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K133">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="L133">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="M133">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="N133">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="O133" t="s">
         <v>178</v>
       </c>
       <c r="P133" t="s">
-        <v>267</v>
+        <v>88</v>
       </c>
       <c r="Q133">
-        <v>3.5</v>
+        <v>1.92</v>
       </c>
       <c r="R133">
-        <v>2.1</v>
+        <v>2.5</v>
       </c>
       <c r="S133">
-        <v>2.8</v>
+        <v>5.6</v>
       </c>
       <c r="T133">
-        <v>1.37</v>
+        <v>1.31</v>
       </c>
       <c r="U133">
-        <v>2.85</v>
+        <v>3.28</v>
       </c>
       <c r="V133">
-        <v>2.7</v>
+        <v>2.46</v>
       </c>
       <c r="W133">
-        <v>1.41</v>
+        <v>1.51</v>
       </c>
       <c r="X133">
-        <v>6.45</v>
+        <v>5.75</v>
       </c>
       <c r="Y133">
+        <v>1.12</v>
+      </c>
+      <c r="Z133">
+        <v>1.36</v>
+      </c>
+      <c r="AA133">
+        <v>5.2</v>
+      </c>
+      <c r="AB133">
+        <v>7.85</v>
+      </c>
+      <c r="AC133">
+        <v>1.02</v>
+      </c>
+      <c r="AD133">
+        <v>10</v>
+      </c>
+      <c r="AE133">
+        <v>1.17</v>
+      </c>
+      <c r="AF133">
+        <v>4.2</v>
+      </c>
+      <c r="AG133">
+        <v>1.57</v>
+      </c>
+      <c r="AH133">
+        <v>2.33</v>
+      </c>
+      <c r="AI133">
+        <v>1.8</v>
+      </c>
+      <c r="AJ133">
+        <v>1.93</v>
+      </c>
+      <c r="AK133">
         <v>1.09</v>
       </c>
-      <c r="Z133">
-        <v>3.42</v>
-      </c>
-      <c r="AA133">
-        <v>3.42</v>
-      </c>
-      <c r="AB133">
-        <v>2.13</v>
-      </c>
-      <c r="AC133">
-        <v>1.05</v>
-      </c>
-      <c r="AD133">
-        <v>12.75</v>
-      </c>
-      <c r="AE133">
-        <v>1.28</v>
-      </c>
-      <c r="AF133">
-        <v>3.5</v>
-      </c>
-      <c r="AG133">
-        <v>1.92</v>
-      </c>
-      <c r="AH133">
-        <v>1.88</v>
-      </c>
-      <c r="AI133">
-        <v>1.7</v>
-      </c>
-      <c r="AJ133">
-        <v>2.1</v>
-      </c>
-      <c r="AK133">
+      <c r="AL133">
+        <v>1.17</v>
+      </c>
+      <c r="AM133">
+        <v>2.65</v>
+      </c>
+      <c r="AN133">
+        <v>1.86</v>
+      </c>
+      <c r="AO133">
+        <v>0.14</v>
+      </c>
+      <c r="AP133">
+        <v>2</v>
+      </c>
+      <c r="AQ133">
+        <v>0.1</v>
+      </c>
+      <c r="AR133">
         <v>1.63</v>
       </c>
-      <c r="AL133">
-        <v>1.25</v>
-      </c>
-      <c r="AM133">
-        <v>1.36</v>
-      </c>
-      <c r="AN133">
-        <v>1</v>
-      </c>
-      <c r="AO133">
-        <v>1</v>
-      </c>
-      <c r="AP133">
+      <c r="AS133">
         <v>0.9</v>
       </c>
-      <c r="AQ133">
-        <v>1.09</v>
-      </c>
-      <c r="AR133">
-        <v>1.21</v>
-      </c>
-      <c r="AS133">
-        <v>1.18</v>
-      </c>
       <c r="AT133">
-        <v>2.39</v>
+        <v>2.53</v>
       </c>
       <c r="AU133">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="AV133">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="AW133">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AX133">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AY133">
-        <v>14</v>
+        <v>19</v>
       </c>
       <c r="AZ133">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="BA133">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="BB133">
         <v>2</v>
       </c>
       <c r="BC133">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="BD133">
-        <v>2.12</v>
+        <v>1.26</v>
       </c>
       <c r="BE133">
-        <v>6.65</v>
+        <v>8.5</v>
       </c>
       <c r="BF133">
-        <v>2.07</v>
+        <v>5.15</v>
       </c>
       <c r="BG133">
         <v>0</v>
@@ -28619,25 +28619,25 @@
         <v>0</v>
       </c>
       <c r="BI133">
-        <v>1.25</v>
+        <v>1.27</v>
       </c>
       <c r="BJ133">
-        <v>3.42</v>
+        <v>3.28</v>
       </c>
       <c r="BK133">
-        <v>1.46</v>
+        <v>1.49</v>
       </c>
       <c r="BL133">
-        <v>2.45</v>
+        <v>2.38</v>
       </c>
       <c r="BM133">
-        <v>1.77</v>
+        <v>1.95</v>
       </c>
       <c r="BN133">
-        <v>2.02</v>
+        <v>1.85</v>
       </c>
       <c r="BO133">
-        <v>2.2</v>
+        <v>2.19</v>
       </c>
       <c r="BP133">
         <v>1.64</v>
@@ -29308,7 +29308,7 @@
         <v>150</v>
       </c>
       <c r="P137" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="Q137">
         <v>1.7</v>
@@ -30090,7 +30090,7 @@
         <v>140</v>
       </c>
       <c r="B141">
-        <v>7468220</v>
+        <v>7468218</v>
       </c>
       <c r="C141" t="s">
         <v>68</v>
@@ -30105,31 +30105,31 @@
         <v>18</v>
       </c>
       <c r="G141" t="s">
-        <v>75</v>
+        <v>72</v>
       </c>
       <c r="H141" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="I141">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J141">
         <v>0</v>
       </c>
       <c r="K141">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L141">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M141">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="N141">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="O141" t="s">
-        <v>117</v>
+        <v>88</v>
       </c>
       <c r="P141" t="s">
         <v>270</v>
@@ -30138,64 +30138,64 @@
         <v>4</v>
       </c>
       <c r="R141">
-        <v>2.15</v>
+        <v>2.2</v>
       </c>
       <c r="S141">
-        <v>2.5</v>
+        <v>2.45</v>
       </c>
       <c r="T141">
-        <v>1.34</v>
+        <v>1.3</v>
       </c>
       <c r="U141">
-        <v>3.05</v>
+        <v>3.25</v>
       </c>
       <c r="V141">
-        <v>2.45</v>
+        <v>2.29</v>
       </c>
       <c r="W141">
-        <v>1.49</v>
+        <v>1.56</v>
       </c>
       <c r="X141">
-        <v>5.45</v>
+        <v>4.95</v>
       </c>
       <c r="Y141">
-        <v>1.12</v>
+        <v>1.14</v>
       </c>
       <c r="Z141">
-        <v>3.75</v>
+        <v>4</v>
       </c>
       <c r="AA141">
         <v>3.5</v>
       </c>
       <c r="AB141">
-        <v>1.95</v>
+        <v>1.9</v>
       </c>
       <c r="AC141">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="AD141">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="AE141">
-        <v>1.2</v>
+        <v>1.18</v>
       </c>
       <c r="AF141">
-        <v>4.2</v>
+        <v>4.5</v>
       </c>
       <c r="AG141">
-        <v>1.66</v>
+        <v>1.55</v>
       </c>
       <c r="AH141">
-        <v>2.15</v>
+        <v>2.35</v>
       </c>
       <c r="AI141">
-        <v>1.57</v>
+        <v>1.5</v>
       </c>
       <c r="AJ141">
-        <v>2.3</v>
+        <v>2.5</v>
       </c>
       <c r="AK141">
-        <v>1.83</v>
+        <v>1.87</v>
       </c>
       <c r="AL141">
         <v>1.25</v>
@@ -30204,52 +30204,52 @@
         <v>1.2</v>
       </c>
       <c r="AN141">
-        <v>1.67</v>
+        <v>0.22</v>
       </c>
       <c r="AO141">
-        <v>1.75</v>
+        <v>1.13</v>
       </c>
       <c r="AP141">
-        <v>1.33</v>
+        <v>0.25</v>
       </c>
       <c r="AQ141">
-        <v>1.82</v>
+        <v>1.09</v>
       </c>
       <c r="AR141">
-        <v>1.59</v>
+        <v>1.34</v>
       </c>
       <c r="AS141">
-        <v>1.23</v>
+        <v>1.28</v>
       </c>
       <c r="AT141">
-        <v>2.82</v>
+        <v>2.62</v>
       </c>
       <c r="AU141">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AV141">
+        <v>7</v>
+      </c>
+      <c r="AW141">
         <v>6</v>
       </c>
-      <c r="AW141">
-        <v>4</v>
-      </c>
       <c r="AX141">
+        <v>6</v>
+      </c>
+      <c r="AY141">
+        <v>15</v>
+      </c>
+      <c r="AZ141">
+        <v>21</v>
+      </c>
+      <c r="BA141">
+        <v>5</v>
+      </c>
+      <c r="BB141">
         <v>8</v>
       </c>
-      <c r="AY141">
-        <v>10</v>
-      </c>
-      <c r="AZ141">
-        <v>17</v>
-      </c>
-      <c r="BA141">
-        <v>3</v>
-      </c>
-      <c r="BB141">
-        <v>7</v>
-      </c>
       <c r="BC141">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="BD141">
         <v>0</v>
@@ -30296,7 +30296,7 @@
         <v>141</v>
       </c>
       <c r="B142">
-        <v>7468218</v>
+        <v>7468220</v>
       </c>
       <c r="C142" t="s">
         <v>68</v>
@@ -30311,31 +30311,31 @@
         <v>18</v>
       </c>
       <c r="G142" t="s">
-        <v>72</v>
+        <v>75</v>
       </c>
       <c r="H142" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="I142">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J142">
         <v>0</v>
       </c>
       <c r="K142">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L142">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M142">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="N142">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="O142" t="s">
-        <v>88</v>
+        <v>117</v>
       </c>
       <c r="P142" t="s">
         <v>271</v>
@@ -30344,64 +30344,64 @@
         <v>4</v>
       </c>
       <c r="R142">
-        <v>2.2</v>
+        <v>2.15</v>
       </c>
       <c r="S142">
+        <v>2.5</v>
+      </c>
+      <c r="T142">
+        <v>1.34</v>
+      </c>
+      <c r="U142">
+        <v>3.05</v>
+      </c>
+      <c r="V142">
         <v>2.45</v>
       </c>
-      <c r="T142">
-        <v>1.3</v>
-      </c>
-      <c r="U142">
-        <v>3.25</v>
-      </c>
-      <c r="V142">
-        <v>2.29</v>
-      </c>
       <c r="W142">
-        <v>1.56</v>
+        <v>1.49</v>
       </c>
       <c r="X142">
-        <v>4.95</v>
+        <v>5.45</v>
       </c>
       <c r="Y142">
-        <v>1.14</v>
+        <v>1.12</v>
       </c>
       <c r="Z142">
-        <v>4</v>
+        <v>3.75</v>
       </c>
       <c r="AA142">
         <v>3.5</v>
       </c>
       <c r="AB142">
-        <v>1.9</v>
+        <v>1.95</v>
       </c>
       <c r="AC142">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="AD142">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="AE142">
-        <v>1.18</v>
+        <v>1.2</v>
       </c>
       <c r="AF142">
-        <v>4.5</v>
+        <v>4.2</v>
       </c>
       <c r="AG142">
-        <v>1.55</v>
+        <v>1.66</v>
       </c>
       <c r="AH142">
-        <v>2.35</v>
+        <v>2.15</v>
       </c>
       <c r="AI142">
-        <v>1.5</v>
+        <v>1.57</v>
       </c>
       <c r="AJ142">
-        <v>2.5</v>
+        <v>2.3</v>
       </c>
       <c r="AK142">
-        <v>1.87</v>
+        <v>1.83</v>
       </c>
       <c r="AL142">
         <v>1.25</v>
@@ -30410,52 +30410,52 @@
         <v>1.2</v>
       </c>
       <c r="AN142">
-        <v>0.22</v>
+        <v>1.67</v>
       </c>
       <c r="AO142">
-        <v>1.13</v>
+        <v>1.75</v>
       </c>
       <c r="AP142">
-        <v>0.25</v>
+        <v>1.33</v>
       </c>
       <c r="AQ142">
-        <v>1.09</v>
+        <v>1.82</v>
       </c>
       <c r="AR142">
-        <v>1.34</v>
+        <v>1.59</v>
       </c>
       <c r="AS142">
-        <v>1.28</v>
+        <v>1.23</v>
       </c>
       <c r="AT142">
-        <v>2.62</v>
+        <v>2.82</v>
       </c>
       <c r="AU142">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AV142">
+        <v>6</v>
+      </c>
+      <c r="AW142">
+        <v>4</v>
+      </c>
+      <c r="AX142">
+        <v>8</v>
+      </c>
+      <c r="AY142">
+        <v>10</v>
+      </c>
+      <c r="AZ142">
+        <v>17</v>
+      </c>
+      <c r="BA142">
+        <v>3</v>
+      </c>
+      <c r="BB142">
         <v>7</v>
       </c>
-      <c r="AW142">
-        <v>6</v>
-      </c>
-      <c r="AX142">
-        <v>6</v>
-      </c>
-      <c r="AY142">
-        <v>15</v>
-      </c>
-      <c r="AZ142">
-        <v>21</v>
-      </c>
-      <c r="BA142">
-        <v>5</v>
-      </c>
-      <c r="BB142">
-        <v>8</v>
-      </c>
       <c r="BC142">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="BD142">
         <v>0</v>
@@ -32974,7 +32974,7 @@
         <v>154</v>
       </c>
       <c r="B155">
-        <v>7468237</v>
+        <v>7468236</v>
       </c>
       <c r="C155" t="s">
         <v>68</v>
@@ -32989,190 +32989,190 @@
         <v>20</v>
       </c>
       <c r="G155" t="s">
-        <v>72</v>
+        <v>81</v>
       </c>
       <c r="H155" t="s">
-        <v>74</v>
+        <v>83</v>
       </c>
       <c r="I155">
         <v>0</v>
       </c>
       <c r="J155">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K155">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L155">
         <v>0</v>
       </c>
       <c r="M155">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N155">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O155" t="s">
         <v>88</v>
       </c>
       <c r="P155" t="s">
-        <v>88</v>
+        <v>214</v>
       </c>
       <c r="Q155">
-        <v>3.3</v>
+        <v>3.2</v>
       </c>
       <c r="R155">
-        <v>2.1</v>
+        <v>2.19</v>
       </c>
       <c r="S155">
-        <v>3.08</v>
+        <v>2.97</v>
       </c>
       <c r="T155">
-        <v>1.37</v>
+        <v>1.34</v>
       </c>
       <c r="U155">
-        <v>2.95</v>
+        <v>3.1</v>
       </c>
       <c r="V155">
-        <v>2.82</v>
+        <v>2.6</v>
       </c>
       <c r="W155">
-        <v>1.4</v>
+        <v>1.46</v>
       </c>
       <c r="X155">
-        <v>7.9</v>
+        <v>6.25</v>
       </c>
       <c r="Y155">
-        <v>1.06</v>
+        <v>1.1</v>
       </c>
       <c r="Z155">
-        <v>2.9</v>
+        <v>2.69</v>
       </c>
       <c r="AA155">
-        <v>3.36</v>
+        <v>3.55</v>
       </c>
       <c r="AB155">
-        <v>2.43</v>
+        <v>2.49</v>
       </c>
       <c r="AC155">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AD155">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="AE155">
-        <v>1.23</v>
+        <v>1.21</v>
       </c>
       <c r="AF155">
-        <v>3.44</v>
+        <v>3.6</v>
       </c>
       <c r="AG155">
-        <v>1.9</v>
+        <v>1.77</v>
       </c>
       <c r="AH155">
-        <v>1.92</v>
+        <v>2.01</v>
       </c>
       <c r="AI155">
-        <v>1.69</v>
+        <v>1.61</v>
       </c>
       <c r="AJ155">
-        <v>2.04</v>
+        <v>2.17</v>
       </c>
       <c r="AK155">
         <v>1.51</v>
       </c>
       <c r="AL155">
-        <v>1.29</v>
+        <v>1.28</v>
       </c>
       <c r="AM155">
+        <v>1.45</v>
+      </c>
+      <c r="AN155">
         <v>1.44</v>
       </c>
-      <c r="AN155">
-        <v>0.2</v>
-      </c>
       <c r="AO155">
-        <v>0.22</v>
+        <v>1.5</v>
       </c>
       <c r="AP155">
-        <v>0.25</v>
+        <v>1.45</v>
       </c>
       <c r="AQ155">
-        <v>0.36</v>
+        <v>1.5</v>
       </c>
       <c r="AR155">
-        <v>1.34</v>
+        <v>1.51</v>
       </c>
       <c r="AS155">
-        <v>0.93</v>
+        <v>1.63</v>
       </c>
       <c r="AT155">
-        <v>2.27</v>
+        <v>3.14</v>
       </c>
       <c r="AU155">
+        <v>2</v>
+      </c>
+      <c r="AV155">
+        <v>9</v>
+      </c>
+      <c r="AW155">
+        <v>1</v>
+      </c>
+      <c r="AX155">
+        <v>9</v>
+      </c>
+      <c r="AY155">
         <v>3</v>
       </c>
-      <c r="AV155">
-        <v>2</v>
-      </c>
-      <c r="AW155">
-        <v>4</v>
-      </c>
-      <c r="AX155">
-        <v>2</v>
-      </c>
-      <c r="AY155">
-        <v>7</v>
-      </c>
       <c r="AZ155">
-        <v>4</v>
+        <v>18</v>
       </c>
       <c r="BA155">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="BB155">
         <v>6</v>
       </c>
       <c r="BC155">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="BD155">
-        <v>2.12</v>
+        <v>2.07</v>
       </c>
       <c r="BE155">
-        <v>6.25</v>
+        <v>6.4</v>
       </c>
       <c r="BF155">
-        <v>1.9</v>
+        <v>1.94</v>
       </c>
       <c r="BG155">
-        <v>1.38</v>
+        <v>1.36</v>
       </c>
       <c r="BH155">
-        <v>2.75</v>
+        <v>2.8</v>
       </c>
       <c r="BI155">
-        <v>1.66</v>
+        <v>1.6</v>
       </c>
       <c r="BJ155">
-        <v>2.08</v>
+        <v>2.17</v>
       </c>
       <c r="BK155">
-        <v>2.05</v>
+        <v>1.98</v>
       </c>
       <c r="BL155">
-        <v>1.68</v>
+        <v>1.72</v>
       </c>
       <c r="BM155">
-        <v>2.63</v>
+        <v>2.55</v>
       </c>
       <c r="BN155">
-        <v>1.43</v>
+        <v>1.45</v>
       </c>
       <c r="BO155">
-        <v>3.45</v>
+        <v>3.3</v>
       </c>
       <c r="BP155">
-        <v>1.25</v>
+        <v>1.27</v>
       </c>
     </row>
     <row r="156" spans="1:68">
@@ -33180,7 +33180,7 @@
         <v>155</v>
       </c>
       <c r="B156">
-        <v>7468236</v>
+        <v>7468237</v>
       </c>
       <c r="C156" t="s">
         <v>68</v>
@@ -33195,190 +33195,190 @@
         <v>20</v>
       </c>
       <c r="G156" t="s">
-        <v>81</v>
+        <v>72</v>
       </c>
       <c r="H156" t="s">
-        <v>83</v>
+        <v>74</v>
       </c>
       <c r="I156">
         <v>0</v>
       </c>
       <c r="J156">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K156">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L156">
         <v>0</v>
       </c>
       <c r="M156">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N156">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O156" t="s">
         <v>88</v>
       </c>
       <c r="P156" t="s">
-        <v>214</v>
+        <v>88</v>
       </c>
       <c r="Q156">
-        <v>3.2</v>
+        <v>3.3</v>
       </c>
       <c r="R156">
-        <v>2.19</v>
+        <v>2.1</v>
       </c>
       <c r="S156">
-        <v>2.97</v>
+        <v>3.08</v>
       </c>
       <c r="T156">
-        <v>1.34</v>
+        <v>1.37</v>
       </c>
       <c r="U156">
-        <v>3.1</v>
+        <v>2.95</v>
       </c>
       <c r="V156">
-        <v>2.6</v>
+        <v>2.82</v>
       </c>
       <c r="W156">
-        <v>1.46</v>
+        <v>1.4</v>
       </c>
       <c r="X156">
-        <v>6.25</v>
+        <v>7.9</v>
       </c>
       <c r="Y156">
-        <v>1.1</v>
+        <v>1.06</v>
       </c>
       <c r="Z156">
-        <v>2.69</v>
+        <v>2.9</v>
       </c>
       <c r="AA156">
-        <v>3.55</v>
+        <v>3.36</v>
       </c>
       <c r="AB156">
-        <v>2.49</v>
+        <v>2.43</v>
       </c>
       <c r="AC156">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AD156">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="AE156">
-        <v>1.21</v>
+        <v>1.23</v>
       </c>
       <c r="AF156">
-        <v>3.6</v>
+        <v>3.44</v>
       </c>
       <c r="AG156">
-        <v>1.77</v>
+        <v>1.9</v>
       </c>
       <c r="AH156">
-        <v>2.01</v>
+        <v>1.92</v>
       </c>
       <c r="AI156">
-        <v>1.61</v>
+        <v>1.69</v>
       </c>
       <c r="AJ156">
-        <v>2.17</v>
+        <v>2.04</v>
       </c>
       <c r="AK156">
         <v>1.51</v>
       </c>
       <c r="AL156">
-        <v>1.28</v>
+        <v>1.29</v>
       </c>
       <c r="AM156">
-        <v>1.45</v>
+        <v>1.44</v>
       </c>
       <c r="AN156">
-        <v>1.44</v>
+        <v>0.2</v>
       </c>
       <c r="AO156">
-        <v>1.5</v>
+        <v>0.22</v>
       </c>
       <c r="AP156">
-        <v>1.45</v>
+        <v>0.25</v>
       </c>
       <c r="AQ156">
-        <v>1.5</v>
+        <v>0.36</v>
       </c>
       <c r="AR156">
-        <v>1.51</v>
+        <v>1.34</v>
       </c>
       <c r="AS156">
-        <v>1.63</v>
+        <v>0.93</v>
       </c>
       <c r="AT156">
-        <v>3.14</v>
+        <v>2.27</v>
       </c>
       <c r="AU156">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AV156">
-        <v>9</v>
+        <v>2</v>
       </c>
       <c r="AW156">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="AX156">
-        <v>9</v>
+        <v>2</v>
       </c>
       <c r="AY156">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="AZ156">
-        <v>18</v>
+        <v>4</v>
       </c>
       <c r="BA156">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="BB156">
         <v>6</v>
       </c>
       <c r="BC156">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="BD156">
-        <v>2.07</v>
+        <v>2.12</v>
       </c>
       <c r="BE156">
-        <v>6.4</v>
+        <v>6.25</v>
       </c>
       <c r="BF156">
-        <v>1.94</v>
+        <v>1.9</v>
       </c>
       <c r="BG156">
-        <v>1.36</v>
+        <v>1.38</v>
       </c>
       <c r="BH156">
-        <v>2.8</v>
+        <v>2.75</v>
       </c>
       <c r="BI156">
-        <v>1.6</v>
+        <v>1.66</v>
       </c>
       <c r="BJ156">
-        <v>2.17</v>
+        <v>2.08</v>
       </c>
       <c r="BK156">
-        <v>1.98</v>
+        <v>2.05</v>
       </c>
       <c r="BL156">
-        <v>1.72</v>
+        <v>1.68</v>
       </c>
       <c r="BM156">
-        <v>2.55</v>
+        <v>2.63</v>
       </c>
       <c r="BN156">
-        <v>1.45</v>
+        <v>1.43</v>
       </c>
       <c r="BO156">
-        <v>3.3</v>
+        <v>3.45</v>
       </c>
       <c r="BP156">
-        <v>1.27</v>
+        <v>1.25</v>
       </c>
     </row>
     <row r="157" spans="1:68">
@@ -36888,7 +36888,7 @@
         <v>173</v>
       </c>
       <c r="B174">
-        <v>7468248</v>
+        <v>7468250</v>
       </c>
       <c r="C174" t="s">
         <v>68</v>
@@ -36903,190 +36903,190 @@
         <v>22</v>
       </c>
       <c r="G174" t="s">
-        <v>81</v>
+        <v>78</v>
       </c>
       <c r="H174" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="I174">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="J174">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K174">
         <v>2</v>
       </c>
       <c r="L174">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="M174">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="N174">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="O174" t="s">
-        <v>204</v>
+        <v>88</v>
       </c>
       <c r="P174" t="s">
-        <v>273</v>
+        <v>288</v>
       </c>
       <c r="Q174">
-        <v>2.66</v>
+        <v>4.86</v>
       </c>
       <c r="R174">
-        <v>2.28</v>
+        <v>2.22</v>
       </c>
       <c r="S174">
-        <v>4.06</v>
+        <v>2.47</v>
       </c>
       <c r="T174">
-        <v>1.35</v>
+        <v>1.4</v>
       </c>
       <c r="U174">
-        <v>3.16</v>
+        <v>2.88</v>
       </c>
       <c r="V174">
-        <v>2.71</v>
+        <v>3.04</v>
       </c>
       <c r="W174">
-        <v>1.45</v>
+        <v>1.37</v>
       </c>
       <c r="X174">
-        <v>6</v>
+        <v>6.5</v>
       </c>
       <c r="Y174">
-        <v>1.09</v>
+        <v>1.08</v>
       </c>
       <c r="Z174">
-        <v>2</v>
+        <v>3.75</v>
       </c>
       <c r="AA174">
-        <v>3.25</v>
+        <v>3.3</v>
       </c>
       <c r="AB174">
-        <v>3.25</v>
+        <v>1.83</v>
       </c>
       <c r="AC174">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="AD174">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AE174">
-        <v>1.25</v>
+        <v>1.29</v>
       </c>
       <c r="AF174">
-        <v>3.6</v>
+        <v>3.3</v>
       </c>
       <c r="AG174">
+        <v>1.91</v>
+      </c>
+      <c r="AH174">
         <v>1.8</v>
       </c>
-      <c r="AH174">
+      <c r="AI174">
+        <v>1.8</v>
+      </c>
+      <c r="AJ174">
         <v>1.91</v>
       </c>
-      <c r="AI174">
-        <v>1.67</v>
-      </c>
-      <c r="AJ174">
-        <v>2.1</v>
-      </c>
       <c r="AK174">
-        <v>1.3</v>
+        <v>1.88</v>
       </c>
       <c r="AL174">
         <v>1.3</v>
       </c>
       <c r="AM174">
-        <v>1.78</v>
+        <v>1.25</v>
       </c>
       <c r="AN174">
         <v>1.3</v>
       </c>
       <c r="AO174">
-        <v>1.2</v>
+        <v>1.7</v>
       </c>
       <c r="AP174">
-        <v>1.45</v>
+        <v>1.18</v>
       </c>
       <c r="AQ174">
-        <v>1.09</v>
+        <v>1.82</v>
       </c>
       <c r="AR174">
-        <v>1.42</v>
+        <v>1.47</v>
       </c>
       <c r="AS174">
-        <v>1.27</v>
+        <v>1.37</v>
       </c>
       <c r="AT174">
-        <v>2.69</v>
+        <v>2.84</v>
       </c>
       <c r="AU174">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="AV174">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="AW174">
         <v>7</v>
       </c>
       <c r="AX174">
+        <v>6</v>
+      </c>
+      <c r="AY174">
+        <v>11</v>
+      </c>
+      <c r="AZ174">
+        <v>13</v>
+      </c>
+      <c r="BA174">
+        <v>1</v>
+      </c>
+      <c r="BB174">
+        <v>4</v>
+      </c>
+      <c r="BC174">
         <v>5</v>
       </c>
-      <c r="AY174">
-        <v>17</v>
-      </c>
-      <c r="AZ174">
-        <v>9</v>
-      </c>
-      <c r="BA174">
-        <v>7</v>
-      </c>
-      <c r="BB174">
-        <v>11</v>
-      </c>
-      <c r="BC174">
-        <v>18</v>
-      </c>
       <c r="BD174">
-        <v>1.68</v>
+        <v>2.7</v>
       </c>
       <c r="BE174">
-        <v>7</v>
+        <v>6.75</v>
       </c>
       <c r="BF174">
+        <v>1.56</v>
+      </c>
+      <c r="BG174">
+        <v>1.29</v>
+      </c>
+      <c r="BH174">
+        <v>3.15</v>
+      </c>
+      <c r="BI174">
+        <v>1.5</v>
+      </c>
+      <c r="BJ174">
         <v>2.4</v>
       </c>
-      <c r="BG174">
-        <v>1.2</v>
-      </c>
-      <c r="BH174">
-        <v>3.95</v>
-      </c>
-      <c r="BI174">
+      <c r="BK174">
+        <v>1.81</v>
+      </c>
+      <c r="BL174">
+        <v>1.88</v>
+      </c>
+      <c r="BM174">
+        <v>2.28</v>
+      </c>
+      <c r="BN174">
+        <v>1.55</v>
+      </c>
+      <c r="BO174">
+        <v>2.88</v>
+      </c>
+      <c r="BP174">
         <v>1.35</v>
-      </c>
-      <c r="BJ174">
-        <v>2.9</v>
-      </c>
-      <c r="BK174">
-        <v>1.58</v>
-      </c>
-      <c r="BL174">
-        <v>2.2</v>
-      </c>
-      <c r="BM174">
-        <v>1.91</v>
-      </c>
-      <c r="BN174">
-        <v>1.78</v>
-      </c>
-      <c r="BO174">
-        <v>2.35</v>
-      </c>
-      <c r="BP174">
-        <v>1.5</v>
       </c>
     </row>
     <row r="175" spans="1:68">
@@ -37094,7 +37094,7 @@
         <v>174</v>
       </c>
       <c r="B175">
-        <v>7468250</v>
+        <v>7468248</v>
       </c>
       <c r="C175" t="s">
         <v>68</v>
@@ -37109,190 +37109,190 @@
         <v>22</v>
       </c>
       <c r="G175" t="s">
-        <v>78</v>
+        <v>81</v>
       </c>
       <c r="H175" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="I175">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J175">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="K175">
         <v>2</v>
       </c>
       <c r="L175">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="M175">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="N175">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="O175" t="s">
-        <v>88</v>
+        <v>204</v>
       </c>
       <c r="P175" t="s">
-        <v>288</v>
+        <v>273</v>
       </c>
       <c r="Q175">
-        <v>4.86</v>
+        <v>2.66</v>
       </c>
       <c r="R175">
-        <v>2.22</v>
+        <v>2.28</v>
       </c>
       <c r="S175">
-        <v>2.47</v>
+        <v>4.06</v>
       </c>
       <c r="T175">
-        <v>1.4</v>
+        <v>1.35</v>
       </c>
       <c r="U175">
-        <v>2.88</v>
+        <v>3.16</v>
       </c>
       <c r="V175">
-        <v>3.04</v>
+        <v>2.71</v>
       </c>
       <c r="W175">
-        <v>1.37</v>
+        <v>1.45</v>
       </c>
       <c r="X175">
-        <v>6.5</v>
+        <v>6</v>
       </c>
       <c r="Y175">
-        <v>1.08</v>
+        <v>1.09</v>
       </c>
       <c r="Z175">
-        <v>3.75</v>
+        <v>2</v>
       </c>
       <c r="AA175">
-        <v>3.3</v>
+        <v>3.25</v>
       </c>
       <c r="AB175">
-        <v>1.83</v>
+        <v>3.25</v>
       </c>
       <c r="AC175">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="AD175">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AE175">
-        <v>1.29</v>
+        <v>1.25</v>
       </c>
       <c r="AF175">
-        <v>3.3</v>
+        <v>3.6</v>
       </c>
       <c r="AG175">
+        <v>1.8</v>
+      </c>
+      <c r="AH175">
         <v>1.91</v>
       </c>
-      <c r="AH175">
-        <v>1.8</v>
-      </c>
       <c r="AI175">
-        <v>1.8</v>
+        <v>1.67</v>
       </c>
       <c r="AJ175">
-        <v>1.91</v>
+        <v>2.1</v>
       </c>
       <c r="AK175">
-        <v>1.88</v>
+        <v>1.3</v>
       </c>
       <c r="AL175">
         <v>1.3</v>
       </c>
       <c r="AM175">
-        <v>1.25</v>
+        <v>1.78</v>
       </c>
       <c r="AN175">
         <v>1.3</v>
       </c>
       <c r="AO175">
-        <v>1.7</v>
+        <v>1.2</v>
       </c>
       <c r="AP175">
-        <v>1.18</v>
+        <v>1.45</v>
       </c>
       <c r="AQ175">
-        <v>1.82</v>
+        <v>1.09</v>
       </c>
       <c r="AR175">
-        <v>1.47</v>
+        <v>1.42</v>
       </c>
       <c r="AS175">
-        <v>1.37</v>
+        <v>1.27</v>
       </c>
       <c r="AT175">
-        <v>2.84</v>
+        <v>2.69</v>
       </c>
       <c r="AU175">
+        <v>10</v>
+      </c>
+      <c r="AV175">
         <v>4</v>
-      </c>
-      <c r="AV175">
-        <v>7</v>
       </c>
       <c r="AW175">
         <v>7</v>
       </c>
       <c r="AX175">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AY175">
+        <v>17</v>
+      </c>
+      <c r="AZ175">
+        <v>9</v>
+      </c>
+      <c r="BA175">
+        <v>7</v>
+      </c>
+      <c r="BB175">
         <v>11</v>
       </c>
-      <c r="AZ175">
-        <v>13</v>
-      </c>
-      <c r="BA175">
-        <v>1</v>
-      </c>
-      <c r="BB175">
-        <v>4</v>
-      </c>
       <c r="BC175">
-        <v>5</v>
+        <v>18</v>
       </c>
       <c r="BD175">
-        <v>2.7</v>
+        <v>1.68</v>
       </c>
       <c r="BE175">
-        <v>6.75</v>
+        <v>7</v>
       </c>
       <c r="BF175">
-        <v>1.56</v>
+        <v>2.4</v>
       </c>
       <c r="BG175">
-        <v>1.29</v>
+        <v>1.2</v>
       </c>
       <c r="BH175">
-        <v>3.15</v>
+        <v>3.95</v>
       </c>
       <c r="BI175">
+        <v>1.35</v>
+      </c>
+      <c r="BJ175">
+        <v>2.9</v>
+      </c>
+      <c r="BK175">
+        <v>1.58</v>
+      </c>
+      <c r="BL175">
+        <v>2.2</v>
+      </c>
+      <c r="BM175">
+        <v>1.91</v>
+      </c>
+      <c r="BN175">
+        <v>1.78</v>
+      </c>
+      <c r="BO175">
+        <v>2.35</v>
+      </c>
+      <c r="BP175">
         <v>1.5</v>
-      </c>
-      <c r="BJ175">
-        <v>2.4</v>
-      </c>
-      <c r="BK175">
-        <v>1.81</v>
-      </c>
-      <c r="BL175">
-        <v>1.88</v>
-      </c>
-      <c r="BM175">
-        <v>2.28</v>
-      </c>
-      <c r="BN175">
-        <v>1.55</v>
-      </c>
-      <c r="BO175">
-        <v>2.88</v>
-      </c>
-      <c r="BP175">
-        <v>1.35</v>
       </c>
     </row>
     <row r="176" spans="1:68">

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Czech Republic First League_20242025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Czech Republic First League_20242025.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1118" uniqueCount="289">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1142" uniqueCount="294">
   <si>
     <t>Id_Jogo</t>
   </si>
@@ -631,6 +631,12 @@
     <t>['37', '43', '47']</t>
   </si>
   <si>
+    <t>['77', '85']</t>
+  </si>
+  <si>
+    <t>['64', '75']</t>
+  </si>
+  <si>
     <t>['25']</t>
   </si>
   <si>
@@ -881,6 +887,15 @@
   </si>
   <si>
     <t>['42', '45']</t>
+  </si>
+  <si>
+    <t>['23', '51', '78']</t>
+  </si>
+  <si>
+    <t>['8', '14', '52']</t>
+  </si>
+  <si>
+    <t>['90+9']</t>
   </si>
 </sst>
 </file>
@@ -1242,7 +1257,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:BP176"/>
+  <dimension ref="A1:BP180"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:68">
@@ -1498,7 +1513,7 @@
         <v>86</v>
       </c>
       <c r="P2" t="s">
-        <v>205</v>
+        <v>207</v>
       </c>
       <c r="Q2">
         <v>1.53</v>
@@ -1576,7 +1591,7 @@
         <v>0</v>
       </c>
       <c r="AP2">
-        <v>2.09</v>
+        <v>2.17</v>
       </c>
       <c r="AQ2">
         <v>0.5</v>
@@ -1785,7 +1800,7 @@
         <v>2</v>
       </c>
       <c r="AQ3">
-        <v>1.09</v>
+        <v>1.25</v>
       </c>
       <c r="AR3">
         <v>0</v>
@@ -1910,7 +1925,7 @@
         <v>88</v>
       </c>
       <c r="P4" t="s">
-        <v>206</v>
+        <v>208</v>
       </c>
       <c r="Q4">
         <v>2.88</v>
@@ -1991,7 +2006,7 @@
         <v>0.25</v>
       </c>
       <c r="AQ4">
-        <v>1.09</v>
+        <v>1.25</v>
       </c>
       <c r="AR4">
         <v>0</v>
@@ -2322,7 +2337,7 @@
         <v>90</v>
       </c>
       <c r="P6" t="s">
-        <v>207</v>
+        <v>209</v>
       </c>
       <c r="Q6">
         <v>5.5</v>
@@ -2400,7 +2415,7 @@
         <v>0</v>
       </c>
       <c r="AP6">
-        <v>1</v>
+        <v>0.91</v>
       </c>
       <c r="AQ6">
         <v>1.82</v>
@@ -2528,7 +2543,7 @@
         <v>91</v>
       </c>
       <c r="P7" t="s">
-        <v>208</v>
+        <v>210</v>
       </c>
       <c r="Q7">
         <v>3.2</v>
@@ -3021,7 +3036,7 @@
         <v>1.64</v>
       </c>
       <c r="AQ9">
-        <v>0.82</v>
+        <v>0.75</v>
       </c>
       <c r="AR9">
         <v>0</v>
@@ -3224,7 +3239,7 @@
         <v>0</v>
       </c>
       <c r="AP10">
-        <v>1</v>
+        <v>0.91</v>
       </c>
       <c r="AQ10">
         <v>1.45</v>
@@ -3352,7 +3367,7 @@
         <v>94</v>
       </c>
       <c r="P11" t="s">
-        <v>209</v>
+        <v>211</v>
       </c>
       <c r="Q11">
         <v>6.5</v>
@@ -3558,7 +3573,7 @@
         <v>88</v>
       </c>
       <c r="P12" t="s">
-        <v>210</v>
+        <v>212</v>
       </c>
       <c r="Q12">
         <v>2.85</v>
@@ -3636,7 +3651,7 @@
         <v>0</v>
       </c>
       <c r="AP12">
-        <v>0.9</v>
+        <v>0.82</v>
       </c>
       <c r="AQ12">
         <v>0.89</v>
@@ -3845,7 +3860,7 @@
         <v>3</v>
       </c>
       <c r="AQ13">
-        <v>0.1</v>
+        <v>0.09</v>
       </c>
       <c r="AR13">
         <v>0</v>
@@ -3970,7 +3985,7 @@
         <v>96</v>
       </c>
       <c r="P14" t="s">
-        <v>211</v>
+        <v>213</v>
       </c>
       <c r="Q14">
         <v>2.45</v>
@@ -4051,7 +4066,7 @@
         <v>1.45</v>
       </c>
       <c r="AQ14">
-        <v>1.09</v>
+        <v>1.25</v>
       </c>
       <c r="AR14">
         <v>0</v>
@@ -4460,7 +4475,7 @@
         <v>0</v>
       </c>
       <c r="AP16">
-        <v>2.4</v>
+        <v>2.45</v>
       </c>
       <c r="AQ16">
         <v>1.27</v>
@@ -4794,7 +4809,7 @@
         <v>88</v>
       </c>
       <c r="P18" t="s">
-        <v>212</v>
+        <v>214</v>
       </c>
       <c r="Q18">
         <v>5.4</v>
@@ -5078,7 +5093,7 @@
         <v>0</v>
       </c>
       <c r="AP19">
-        <v>2.09</v>
+        <v>2.17</v>
       </c>
       <c r="AQ19">
         <v>0.36</v>
@@ -5699,7 +5714,7 @@
         <v>1.82</v>
       </c>
       <c r="AQ22">
-        <v>0.82</v>
+        <v>0.75</v>
       </c>
       <c r="AR22">
         <v>0</v>
@@ -5824,7 +5839,7 @@
         <v>102</v>
       </c>
       <c r="P23" t="s">
-        <v>213</v>
+        <v>215</v>
       </c>
       <c r="Q23">
         <v>2.6</v>
@@ -6030,7 +6045,7 @@
         <v>103</v>
       </c>
       <c r="P24" t="s">
-        <v>214</v>
+        <v>216</v>
       </c>
       <c r="Q24">
         <v>2.75</v>
@@ -6111,7 +6126,7 @@
         <v>1.64</v>
       </c>
       <c r="AQ24">
-        <v>1.09</v>
+        <v>1.25</v>
       </c>
       <c r="AR24">
         <v>1.19</v>
@@ -6236,7 +6251,7 @@
         <v>88</v>
       </c>
       <c r="P25" t="s">
-        <v>215</v>
+        <v>217</v>
       </c>
       <c r="Q25">
         <v>1.06</v>
@@ -6314,7 +6329,7 @@
         <v>0</v>
       </c>
       <c r="AP25">
-        <v>1</v>
+        <v>0.91</v>
       </c>
       <c r="AQ25">
         <v>1.27</v>
@@ -6442,7 +6457,7 @@
         <v>104</v>
       </c>
       <c r="P26" t="s">
-        <v>216</v>
+        <v>218</v>
       </c>
       <c r="Q26">
         <v>6.23</v>
@@ -6935,7 +6950,7 @@
         <v>3</v>
       </c>
       <c r="AQ28">
-        <v>1.09</v>
+        <v>1.25</v>
       </c>
       <c r="AR28">
         <v>2.4</v>
@@ -7138,7 +7153,7 @@
         <v>0</v>
       </c>
       <c r="AP29">
-        <v>0.9</v>
+        <v>0.82</v>
       </c>
       <c r="AQ29">
         <v>1</v>
@@ -7344,7 +7359,7 @@
         <v>0</v>
       </c>
       <c r="AP30">
-        <v>2.4</v>
+        <v>2.45</v>
       </c>
       <c r="AQ30">
         <v>1</v>
@@ -7553,7 +7568,7 @@
         <v>1.73</v>
       </c>
       <c r="AQ31">
-        <v>0.1</v>
+        <v>0.09</v>
       </c>
       <c r="AR31">
         <v>1.76</v>
@@ -8090,7 +8105,7 @@
         <v>111</v>
       </c>
       <c r="P34" t="s">
-        <v>217</v>
+        <v>219</v>
       </c>
       <c r="Q34">
         <v>1.45</v>
@@ -8171,7 +8186,7 @@
         <v>3</v>
       </c>
       <c r="AQ34">
-        <v>0.82</v>
+        <v>0.75</v>
       </c>
       <c r="AR34">
         <v>2.27</v>
@@ -8296,7 +8311,7 @@
         <v>112</v>
       </c>
       <c r="P35" t="s">
-        <v>218</v>
+        <v>220</v>
       </c>
       <c r="Q35">
         <v>2.84</v>
@@ -8502,7 +8517,7 @@
         <v>113</v>
       </c>
       <c r="P36" t="s">
-        <v>219</v>
+        <v>221</v>
       </c>
       <c r="Q36">
         <v>5.63</v>
@@ -8708,7 +8723,7 @@
         <v>114</v>
       </c>
       <c r="P37" t="s">
-        <v>220</v>
+        <v>222</v>
       </c>
       <c r="Q37">
         <v>2.58</v>
@@ -8789,7 +8804,7 @@
         <v>1.82</v>
       </c>
       <c r="AQ37">
-        <v>1.09</v>
+        <v>1.25</v>
       </c>
       <c r="AR37">
         <v>1.25</v>
@@ -9120,7 +9135,7 @@
         <v>88</v>
       </c>
       <c r="P39" t="s">
-        <v>221</v>
+        <v>223</v>
       </c>
       <c r="Q39">
         <v>4.75</v>
@@ -9532,7 +9547,7 @@
         <v>117</v>
       </c>
       <c r="P41" t="s">
-        <v>222</v>
+        <v>224</v>
       </c>
       <c r="Q41">
         <v>2.4</v>
@@ -9738,7 +9753,7 @@
         <v>107</v>
       </c>
       <c r="P42" t="s">
-        <v>223</v>
+        <v>225</v>
       </c>
       <c r="Q42">
         <v>2.61</v>
@@ -9944,7 +9959,7 @@
         <v>118</v>
       </c>
       <c r="P43" t="s">
-        <v>224</v>
+        <v>226</v>
       </c>
       <c r="Q43">
         <v>1.69</v>
@@ -10022,7 +10037,7 @@
         <v>1.5</v>
       </c>
       <c r="AP43">
-        <v>2.09</v>
+        <v>2.17</v>
       </c>
       <c r="AQ43">
         <v>1</v>
@@ -10228,7 +10243,7 @@
         <v>0</v>
       </c>
       <c r="AP44">
-        <v>0.9</v>
+        <v>0.82</v>
       </c>
       <c r="AQ44">
         <v>1</v>
@@ -10434,7 +10449,7 @@
         <v>1.5</v>
       </c>
       <c r="AP45">
-        <v>2.4</v>
+        <v>2.45</v>
       </c>
       <c r="AQ45">
         <v>1</v>
@@ -10640,10 +10655,10 @@
         <v>0</v>
       </c>
       <c r="AP46">
-        <v>1</v>
+        <v>0.91</v>
       </c>
       <c r="AQ46">
-        <v>0.1</v>
+        <v>0.09</v>
       </c>
       <c r="AR46">
         <v>0.97</v>
@@ -11386,7 +11401,7 @@
         <v>88</v>
       </c>
       <c r="P50" t="s">
-        <v>225</v>
+        <v>227</v>
       </c>
       <c r="Q50">
         <v>5.1</v>
@@ -11798,7 +11813,7 @@
         <v>122</v>
       </c>
       <c r="P52" t="s">
-        <v>226</v>
+        <v>228</v>
       </c>
       <c r="Q52">
         <v>3</v>
@@ -12210,7 +12225,7 @@
         <v>124</v>
       </c>
       <c r="P54" t="s">
-        <v>227</v>
+        <v>229</v>
       </c>
       <c r="Q54">
         <v>3</v>
@@ -12291,7 +12306,7 @@
         <v>1.18</v>
       </c>
       <c r="AQ54">
-        <v>1.09</v>
+        <v>1.25</v>
       </c>
       <c r="AR54">
         <v>1.4</v>
@@ -12622,7 +12637,7 @@
         <v>125</v>
       </c>
       <c r="P56" t="s">
-        <v>228</v>
+        <v>230</v>
       </c>
       <c r="Q56">
         <v>1.85</v>
@@ -12703,7 +12718,7 @@
         <v>2.64</v>
       </c>
       <c r="AQ56">
-        <v>1.09</v>
+        <v>1.25</v>
       </c>
       <c r="AR56">
         <v>1.85</v>
@@ -12828,7 +12843,7 @@
         <v>88</v>
       </c>
       <c r="P57" t="s">
-        <v>229</v>
+        <v>231</v>
       </c>
       <c r="Q57">
         <v>5.88</v>
@@ -13240,7 +13255,7 @@
         <v>127</v>
       </c>
       <c r="P59" t="s">
-        <v>230</v>
+        <v>232</v>
       </c>
       <c r="Q59">
         <v>3.86</v>
@@ -13858,7 +13873,7 @@
         <v>130</v>
       </c>
       <c r="P62" t="s">
-        <v>231</v>
+        <v>233</v>
       </c>
       <c r="Q62">
         <v>1.83</v>
@@ -14064,7 +14079,7 @@
         <v>88</v>
       </c>
       <c r="P63" t="s">
-        <v>232</v>
+        <v>234</v>
       </c>
       <c r="Q63">
         <v>8.77</v>
@@ -14476,7 +14491,7 @@
         <v>132</v>
       </c>
       <c r="P65" t="s">
-        <v>233</v>
+        <v>235</v>
       </c>
       <c r="Q65">
         <v>2.4</v>
@@ -14682,7 +14697,7 @@
         <v>133</v>
       </c>
       <c r="P66" t="s">
-        <v>234</v>
+        <v>236</v>
       </c>
       <c r="Q66">
         <v>1.55</v>
@@ -14760,10 +14775,10 @@
         <v>1</v>
       </c>
       <c r="AP66">
-        <v>2.09</v>
+        <v>2.17</v>
       </c>
       <c r="AQ66">
-        <v>1.09</v>
+        <v>1.25</v>
       </c>
       <c r="AR66">
         <v>2.05</v>
@@ -14888,7 +14903,7 @@
         <v>134</v>
       </c>
       <c r="P67" t="s">
-        <v>235</v>
+        <v>237</v>
       </c>
       <c r="Q67">
         <v>4</v>
@@ -14966,7 +14981,7 @@
         <v>1</v>
       </c>
       <c r="AP67">
-        <v>1</v>
+        <v>0.91</v>
       </c>
       <c r="AQ67">
         <v>1</v>
@@ -15094,7 +15109,7 @@
         <v>88</v>
       </c>
       <c r="P68" t="s">
-        <v>236</v>
+        <v>238</v>
       </c>
       <c r="Q68">
         <v>3.1</v>
@@ -15172,10 +15187,10 @@
         <v>0</v>
       </c>
       <c r="AP68">
-        <v>0.9</v>
+        <v>0.82</v>
       </c>
       <c r="AQ68">
-        <v>0.82</v>
+        <v>0.75</v>
       </c>
       <c r="AR68">
         <v>1.23</v>
@@ -15790,10 +15805,10 @@
         <v>0</v>
       </c>
       <c r="AP71">
-        <v>2.4</v>
+        <v>2.45</v>
       </c>
       <c r="AQ71">
-        <v>0.1</v>
+        <v>0.09</v>
       </c>
       <c r="AR71">
         <v>1.82</v>
@@ -15918,7 +15933,7 @@
         <v>124</v>
       </c>
       <c r="P72" t="s">
-        <v>237</v>
+        <v>239</v>
       </c>
       <c r="Q72">
         <v>1.88</v>
@@ -15999,7 +16014,7 @@
         <v>2.64</v>
       </c>
       <c r="AQ72">
-        <v>1.09</v>
+        <v>1.25</v>
       </c>
       <c r="AR72">
         <v>1.84</v>
@@ -16124,7 +16139,7 @@
         <v>88</v>
       </c>
       <c r="P73" t="s">
-        <v>238</v>
+        <v>240</v>
       </c>
       <c r="Q73">
         <v>7</v>
@@ -16536,7 +16551,7 @@
         <v>138</v>
       </c>
       <c r="P75" t="s">
-        <v>239</v>
+        <v>241</v>
       </c>
       <c r="Q75">
         <v>2.3</v>
@@ -16742,7 +16757,7 @@
         <v>88</v>
       </c>
       <c r="P76" t="s">
-        <v>240</v>
+        <v>242</v>
       </c>
       <c r="Q76">
         <v>3.7</v>
@@ -16948,7 +16963,7 @@
         <v>88</v>
       </c>
       <c r="P77" t="s">
-        <v>241</v>
+        <v>243</v>
       </c>
       <c r="Q77">
         <v>2.47</v>
@@ -17566,7 +17581,7 @@
         <v>140</v>
       </c>
       <c r="P80" t="s">
-        <v>242</v>
+        <v>244</v>
       </c>
       <c r="Q80">
         <v>2.5</v>
@@ -17772,7 +17787,7 @@
         <v>141</v>
       </c>
       <c r="P81" t="s">
-        <v>243</v>
+        <v>245</v>
       </c>
       <c r="Q81">
         <v>2.38</v>
@@ -17978,7 +17993,7 @@
         <v>142</v>
       </c>
       <c r="P82" t="s">
-        <v>244</v>
+        <v>246</v>
       </c>
       <c r="Q82">
         <v>2.8</v>
@@ -18059,7 +18074,7 @@
         <v>1.64</v>
       </c>
       <c r="AQ82">
-        <v>1.09</v>
+        <v>1.25</v>
       </c>
       <c r="AR82">
         <v>1.31</v>
@@ -18184,7 +18199,7 @@
         <v>143</v>
       </c>
       <c r="P83" t="s">
-        <v>245</v>
+        <v>247</v>
       </c>
       <c r="Q83">
         <v>2.6</v>
@@ -18262,7 +18277,7 @@
         <v>0.67</v>
       </c>
       <c r="AP83">
-        <v>1</v>
+        <v>0.91</v>
       </c>
       <c r="AQ83">
         <v>0.5</v>
@@ -18390,7 +18405,7 @@
         <v>144</v>
       </c>
       <c r="P84" t="s">
-        <v>246</v>
+        <v>248</v>
       </c>
       <c r="Q84">
         <v>3.4</v>
@@ -18468,7 +18483,7 @@
         <v>1.6</v>
       </c>
       <c r="AP84">
-        <v>2.4</v>
+        <v>2.45</v>
       </c>
       <c r="AQ84">
         <v>1.82</v>
@@ -18674,7 +18689,7 @@
         <v>1.5</v>
       </c>
       <c r="AP85">
-        <v>2.09</v>
+        <v>2.17</v>
       </c>
       <c r="AQ85">
         <v>1</v>
@@ -18802,7 +18817,7 @@
         <v>146</v>
       </c>
       <c r="P86" t="s">
-        <v>247</v>
+        <v>249</v>
       </c>
       <c r="Q86">
         <v>2.88</v>
@@ -18883,7 +18898,7 @@
         <v>1.18</v>
       </c>
       <c r="AQ86">
-        <v>1.09</v>
+        <v>1.25</v>
       </c>
       <c r="AR86">
         <v>1.41</v>
@@ -19089,7 +19104,7 @@
         <v>1.33</v>
       </c>
       <c r="AQ87">
-        <v>0.1</v>
+        <v>0.09</v>
       </c>
       <c r="AR87">
         <v>1.73</v>
@@ -19214,7 +19229,7 @@
         <v>88</v>
       </c>
       <c r="P88" t="s">
-        <v>248</v>
+        <v>250</v>
       </c>
       <c r="Q88">
         <v>2.6</v>
@@ -19295,7 +19310,7 @@
         <v>1.36</v>
       </c>
       <c r="AQ88">
-        <v>0.82</v>
+        <v>0.75</v>
       </c>
       <c r="AR88">
         <v>1.12</v>
@@ -19420,7 +19435,7 @@
         <v>93</v>
       </c>
       <c r="P89" t="s">
-        <v>249</v>
+        <v>251</v>
       </c>
       <c r="Q89">
         <v>6.5</v>
@@ -19832,7 +19847,7 @@
         <v>149</v>
       </c>
       <c r="P91" t="s">
-        <v>250</v>
+        <v>252</v>
       </c>
       <c r="Q91">
         <v>4.7</v>
@@ -19910,7 +19925,7 @@
         <v>1</v>
       </c>
       <c r="AP91">
-        <v>0.9</v>
+        <v>0.82</v>
       </c>
       <c r="AQ91">
         <v>1.5</v>
@@ -20038,7 +20053,7 @@
         <v>88</v>
       </c>
       <c r="P92" t="s">
-        <v>251</v>
+        <v>253</v>
       </c>
       <c r="Q92">
         <v>3.8</v>
@@ -20450,7 +20465,7 @@
         <v>150</v>
       </c>
       <c r="P94" t="s">
-        <v>252</v>
+        <v>254</v>
       </c>
       <c r="Q94">
         <v>3</v>
@@ -21352,10 +21367,10 @@
         <v>0.83</v>
       </c>
       <c r="AP98">
-        <v>1</v>
+        <v>0.91</v>
       </c>
       <c r="AQ98">
-        <v>1.09</v>
+        <v>1.25</v>
       </c>
       <c r="AR98">
         <v>1.15</v>
@@ -21561,7 +21576,7 @@
         <v>2</v>
       </c>
       <c r="AQ99">
-        <v>0.82</v>
+        <v>0.75</v>
       </c>
       <c r="AR99">
         <v>1.65</v>
@@ -21767,7 +21782,7 @@
         <v>1.33</v>
       </c>
       <c r="AQ100">
-        <v>1.09</v>
+        <v>1.25</v>
       </c>
       <c r="AR100">
         <v>1.67</v>
@@ -21892,7 +21907,7 @@
         <v>156</v>
       </c>
       <c r="P101" t="s">
-        <v>253</v>
+        <v>255</v>
       </c>
       <c r="Q101">
         <v>1.83</v>
@@ -21970,7 +21985,7 @@
         <v>1.29</v>
       </c>
       <c r="AP101">
-        <v>2.09</v>
+        <v>2.17</v>
       </c>
       <c r="AQ101">
         <v>1.5</v>
@@ -23000,7 +23015,7 @@
         <v>0.33</v>
       </c>
       <c r="AP106">
-        <v>2.4</v>
+        <v>2.45</v>
       </c>
       <c r="AQ106">
         <v>0.36</v>
@@ -23206,7 +23221,7 @@
         <v>1.57</v>
       </c>
       <c r="AP107">
-        <v>0.9</v>
+        <v>0.82</v>
       </c>
       <c r="AQ107">
         <v>1.27</v>
@@ -23540,7 +23555,7 @@
         <v>161</v>
       </c>
       <c r="P109" t="s">
-        <v>254</v>
+        <v>256</v>
       </c>
       <c r="Q109">
         <v>2.24</v>
@@ -23621,7 +23636,7 @@
         <v>1.18</v>
       </c>
       <c r="AQ109">
-        <v>0.1</v>
+        <v>0.09</v>
       </c>
       <c r="AR109">
         <v>1.51</v>
@@ -23746,7 +23761,7 @@
         <v>162</v>
       </c>
       <c r="P110" t="s">
-        <v>255</v>
+        <v>257</v>
       </c>
       <c r="Q110">
         <v>4.6</v>
@@ -24158,7 +24173,7 @@
         <v>164</v>
       </c>
       <c r="P112" t="s">
-        <v>211</v>
+        <v>213</v>
       </c>
       <c r="Q112">
         <v>1.44</v>
@@ -24364,7 +24379,7 @@
         <v>165</v>
       </c>
       <c r="P113" t="s">
-        <v>256</v>
+        <v>258</v>
       </c>
       <c r="Q113">
         <v>3.25</v>
@@ -24570,7 +24585,7 @@
         <v>151</v>
       </c>
       <c r="P114" t="s">
-        <v>257</v>
+        <v>259</v>
       </c>
       <c r="Q114">
         <v>2.88</v>
@@ -24651,7 +24666,7 @@
         <v>1.36</v>
       </c>
       <c r="AQ114">
-        <v>1.09</v>
+        <v>1.25</v>
       </c>
       <c r="AR114">
         <v>1.11</v>
@@ -24776,7 +24791,7 @@
         <v>99</v>
       </c>
       <c r="P115" t="s">
-        <v>258</v>
+        <v>260</v>
       </c>
       <c r="Q115">
         <v>1.73</v>
@@ -24854,10 +24869,10 @@
         <v>1</v>
       </c>
       <c r="AP115">
-        <v>2.09</v>
+        <v>2.17</v>
       </c>
       <c r="AQ115">
-        <v>0.82</v>
+        <v>0.75</v>
       </c>
       <c r="AR115">
         <v>1.87</v>
@@ -24982,7 +24997,7 @@
         <v>88</v>
       </c>
       <c r="P116" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="Q116">
         <v>4.33</v>
@@ -25600,7 +25615,7 @@
         <v>88</v>
       </c>
       <c r="P119" t="s">
-        <v>260</v>
+        <v>262</v>
       </c>
       <c r="Q119">
         <v>15</v>
@@ -25806,7 +25821,7 @@
         <v>168</v>
       </c>
       <c r="P120" t="s">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="Q120">
         <v>3</v>
@@ -26218,7 +26233,7 @@
         <v>170</v>
       </c>
       <c r="P122" t="s">
-        <v>262</v>
+        <v>264</v>
       </c>
       <c r="Q122">
         <v>3.25</v>
@@ -26505,7 +26520,7 @@
         <v>1.18</v>
       </c>
       <c r="AQ123">
-        <v>1.09</v>
+        <v>1.25</v>
       </c>
       <c r="AR123">
         <v>1.58</v>
@@ -26630,7 +26645,7 @@
         <v>172</v>
       </c>
       <c r="P124" t="s">
-        <v>210</v>
+        <v>212</v>
       </c>
       <c r="Q124">
         <v>1.83</v>
@@ -26708,7 +26723,7 @@
         <v>1.17</v>
       </c>
       <c r="AP124">
-        <v>2.4</v>
+        <v>2.45</v>
       </c>
       <c r="AQ124">
         <v>0.89</v>
@@ -26836,7 +26851,7 @@
         <v>171</v>
       </c>
       <c r="P125" t="s">
-        <v>263</v>
+        <v>265</v>
       </c>
       <c r="Q125">
         <v>6.3</v>
@@ -26914,7 +26929,7 @@
         <v>2</v>
       </c>
       <c r="AP125">
-        <v>1</v>
+        <v>0.91</v>
       </c>
       <c r="AQ125">
         <v>2.09</v>
@@ -27532,10 +27547,10 @@
         <v>0</v>
       </c>
       <c r="AP128">
-        <v>0.9</v>
+        <v>0.82</v>
       </c>
       <c r="AQ128">
-        <v>0.1</v>
+        <v>0.09</v>
       </c>
       <c r="AR128">
         <v>1.1</v>
@@ -27660,7 +27675,7 @@
         <v>174</v>
       </c>
       <c r="P129" t="s">
-        <v>264</v>
+        <v>266</v>
       </c>
       <c r="Q129">
         <v>2.1</v>
@@ -27866,7 +27881,7 @@
         <v>175</v>
       </c>
       <c r="P130" t="s">
-        <v>265</v>
+        <v>267</v>
       </c>
       <c r="Q130">
         <v>1.5</v>
@@ -27944,7 +27959,7 @@
         <v>1</v>
       </c>
       <c r="AP130">
-        <v>2.09</v>
+        <v>2.17</v>
       </c>
       <c r="AQ130">
         <v>0.89</v>
@@ -28072,7 +28087,7 @@
         <v>176</v>
       </c>
       <c r="P131" t="s">
-        <v>266</v>
+        <v>268</v>
       </c>
       <c r="Q131">
         <v>3.5</v>
@@ -28150,10 +28165,10 @@
         <v>1</v>
       </c>
       <c r="AP131">
-        <v>0.9</v>
+        <v>0.82</v>
       </c>
       <c r="AQ131">
-        <v>1.09</v>
+        <v>1.25</v>
       </c>
       <c r="AR131">
         <v>1.21</v>
@@ -28278,7 +28293,7 @@
         <v>177</v>
       </c>
       <c r="P132" t="s">
-        <v>267</v>
+        <v>269</v>
       </c>
       <c r="Q132">
         <v>4.04</v>
@@ -28356,7 +28371,7 @@
         <v>1</v>
       </c>
       <c r="AP132">
-        <v>1</v>
+        <v>0.91</v>
       </c>
       <c r="AQ132">
         <v>1</v>
@@ -28565,7 +28580,7 @@
         <v>2</v>
       </c>
       <c r="AQ133">
-        <v>0.1</v>
+        <v>0.09</v>
       </c>
       <c r="AR133">
         <v>1.63</v>
@@ -28690,7 +28705,7 @@
         <v>88</v>
       </c>
       <c r="P134" t="s">
-        <v>268</v>
+        <v>270</v>
       </c>
       <c r="Q134">
         <v>2.75</v>
@@ -29102,7 +29117,7 @@
         <v>88</v>
       </c>
       <c r="P136" t="s">
-        <v>269</v>
+        <v>271</v>
       </c>
       <c r="Q136">
         <v>4.5</v>
@@ -29180,7 +29195,7 @@
         <v>2.43</v>
       </c>
       <c r="AP136">
-        <v>2.4</v>
+        <v>2.45</v>
       </c>
       <c r="AQ136">
         <v>2.36</v>
@@ -29389,7 +29404,7 @@
         <v>2.64</v>
       </c>
       <c r="AQ137">
-        <v>0.82</v>
+        <v>0.75</v>
       </c>
       <c r="AR137">
         <v>1.7</v>
@@ -29514,7 +29529,7 @@
         <v>91</v>
       </c>
       <c r="P138" t="s">
-        <v>256</v>
+        <v>258</v>
       </c>
       <c r="Q138">
         <v>2.25</v>
@@ -29720,7 +29735,7 @@
         <v>179</v>
       </c>
       <c r="P139" t="s">
-        <v>265</v>
+        <v>267</v>
       </c>
       <c r="Q139">
         <v>1.9</v>
@@ -30004,7 +30019,7 @@
         <v>1.5</v>
       </c>
       <c r="AP140">
-        <v>2.09</v>
+        <v>2.17</v>
       </c>
       <c r="AQ140">
         <v>1.45</v>
@@ -30132,7 +30147,7 @@
         <v>88</v>
       </c>
       <c r="P141" t="s">
-        <v>270</v>
+        <v>272</v>
       </c>
       <c r="Q141">
         <v>4</v>
@@ -30213,7 +30228,7 @@
         <v>0.25</v>
       </c>
       <c r="AQ141">
-        <v>1.09</v>
+        <v>1.25</v>
       </c>
       <c r="AR141">
         <v>1.34</v>
@@ -30338,7 +30353,7 @@
         <v>117</v>
       </c>
       <c r="P142" t="s">
-        <v>271</v>
+        <v>273</v>
       </c>
       <c r="Q142">
         <v>4</v>
@@ -30625,7 +30640,7 @@
         <v>1.45</v>
       </c>
       <c r="AQ143">
-        <v>0.82</v>
+        <v>0.75</v>
       </c>
       <c r="AR143">
         <v>1.52</v>
@@ -30750,7 +30765,7 @@
         <v>182</v>
       </c>
       <c r="P144" t="s">
-        <v>272</v>
+        <v>274</v>
       </c>
       <c r="Q144">
         <v>6</v>
@@ -30956,7 +30971,7 @@
         <v>88</v>
       </c>
       <c r="P145" t="s">
-        <v>273</v>
+        <v>275</v>
       </c>
       <c r="Q145">
         <v>3.5</v>
@@ -31162,7 +31177,7 @@
         <v>183</v>
       </c>
       <c r="P146" t="s">
-        <v>274</v>
+        <v>276</v>
       </c>
       <c r="Q146">
         <v>4.33</v>
@@ -31240,7 +31255,7 @@
         <v>0.89</v>
       </c>
       <c r="AP146">
-        <v>1</v>
+        <v>0.91</v>
       </c>
       <c r="AQ146">
         <v>1</v>
@@ -31368,7 +31383,7 @@
         <v>184</v>
       </c>
       <c r="P147" t="s">
-        <v>275</v>
+        <v>277</v>
       </c>
       <c r="Q147">
         <v>3.8</v>
@@ -31446,7 +31461,7 @@
         <v>1.11</v>
       </c>
       <c r="AP147">
-        <v>0.9</v>
+        <v>0.82</v>
       </c>
       <c r="AQ147">
         <v>1</v>
@@ -31574,7 +31589,7 @@
         <v>185</v>
       </c>
       <c r="P148" t="s">
-        <v>276</v>
+        <v>278</v>
       </c>
       <c r="Q148">
         <v>2.5</v>
@@ -31780,7 +31795,7 @@
         <v>186</v>
       </c>
       <c r="P149" t="s">
-        <v>273</v>
+        <v>275</v>
       </c>
       <c r="Q149">
         <v>2.05</v>
@@ -31858,7 +31873,7 @@
         <v>1.22</v>
       </c>
       <c r="AP149">
-        <v>2.4</v>
+        <v>2.45</v>
       </c>
       <c r="AQ149">
         <v>1</v>
@@ -31986,7 +32001,7 @@
         <v>187</v>
       </c>
       <c r="P150" t="s">
-        <v>277</v>
+        <v>279</v>
       </c>
       <c r="Q150">
         <v>1.95</v>
@@ -32064,7 +32079,7 @@
         <v>1.22</v>
       </c>
       <c r="AP150">
-        <v>2.09</v>
+        <v>2.17</v>
       </c>
       <c r="AQ150">
         <v>1.27</v>
@@ -32192,7 +32207,7 @@
         <v>188</v>
       </c>
       <c r="P151" t="s">
-        <v>278</v>
+        <v>280</v>
       </c>
       <c r="Q151">
         <v>2.48</v>
@@ -32273,7 +32288,7 @@
         <v>1.73</v>
       </c>
       <c r="AQ151">
-        <v>1.09</v>
+        <v>1.25</v>
       </c>
       <c r="AR151">
         <v>1.53</v>
@@ -32604,7 +32619,7 @@
         <v>190</v>
       </c>
       <c r="P153" t="s">
-        <v>279</v>
+        <v>281</v>
       </c>
       <c r="Q153">
         <v>1.4</v>
@@ -32685,7 +32700,7 @@
         <v>2.64</v>
       </c>
       <c r="AQ153">
-        <v>0.1</v>
+        <v>0.09</v>
       </c>
       <c r="AR153">
         <v>1.75</v>
@@ -32891,7 +32906,7 @@
         <v>1.33</v>
       </c>
       <c r="AQ154">
-        <v>0.82</v>
+        <v>0.75</v>
       </c>
       <c r="AR154">
         <v>1.58</v>
@@ -33016,7 +33031,7 @@
         <v>88</v>
       </c>
       <c r="P155" t="s">
-        <v>214</v>
+        <v>216</v>
       </c>
       <c r="Q155">
         <v>3.2</v>
@@ -33634,7 +33649,7 @@
         <v>88</v>
       </c>
       <c r="P158" t="s">
-        <v>280</v>
+        <v>282</v>
       </c>
       <c r="Q158">
         <v>5</v>
@@ -33840,7 +33855,7 @@
         <v>88</v>
       </c>
       <c r="P159" t="s">
-        <v>236</v>
+        <v>238</v>
       </c>
       <c r="Q159">
         <v>2.38</v>
@@ -34127,7 +34142,7 @@
         <v>3</v>
       </c>
       <c r="AQ160">
-        <v>1.09</v>
+        <v>1.25</v>
       </c>
       <c r="AR160">
         <v>2.39</v>
@@ -34252,7 +34267,7 @@
         <v>193</v>
       </c>
       <c r="P161" t="s">
-        <v>263</v>
+        <v>265</v>
       </c>
       <c r="Q161">
         <v>4.75</v>
@@ -34458,7 +34473,7 @@
         <v>194</v>
       </c>
       <c r="P162" t="s">
-        <v>281</v>
+        <v>283</v>
       </c>
       <c r="Q162">
         <v>2.63</v>
@@ -34539,7 +34554,7 @@
         <v>1.73</v>
       </c>
       <c r="AQ162">
-        <v>0.82</v>
+        <v>0.75</v>
       </c>
       <c r="AR162">
         <v>1.6</v>
@@ -34664,7 +34679,7 @@
         <v>88</v>
       </c>
       <c r="P163" t="s">
-        <v>282</v>
+        <v>284</v>
       </c>
       <c r="Q163">
         <v>11</v>
@@ -34742,7 +34757,7 @@
         <v>2.3</v>
       </c>
       <c r="AP163">
-        <v>0.9</v>
+        <v>0.82</v>
       </c>
       <c r="AQ163">
         <v>2.36</v>
@@ -34870,7 +34885,7 @@
         <v>195</v>
       </c>
       <c r="P164" t="s">
-        <v>283</v>
+        <v>285</v>
       </c>
       <c r="Q164">
         <v>2</v>
@@ -35076,7 +35091,7 @@
         <v>196</v>
       </c>
       <c r="P165" t="s">
-        <v>284</v>
+        <v>286</v>
       </c>
       <c r="Q165">
         <v>2.5</v>
@@ -35360,10 +35375,10 @@
         <v>1.2</v>
       </c>
       <c r="AP166">
-        <v>2.4</v>
+        <v>2.45</v>
       </c>
       <c r="AQ166">
-        <v>1.09</v>
+        <v>1.25</v>
       </c>
       <c r="AR166">
         <v>1.9</v>
@@ -35569,7 +35584,7 @@
         <v>1.18</v>
       </c>
       <c r="AQ167">
-        <v>0.1</v>
+        <v>0.09</v>
       </c>
       <c r="AR167">
         <v>1.6</v>
@@ -35772,7 +35787,7 @@
         <v>1.1</v>
       </c>
       <c r="AP168">
-        <v>2.09</v>
+        <v>2.17</v>
       </c>
       <c r="AQ168">
         <v>1</v>
@@ -36312,7 +36327,7 @@
         <v>201</v>
       </c>
       <c r="P171" t="s">
-        <v>285</v>
+        <v>287</v>
       </c>
       <c r="Q171">
         <v>5.2</v>
@@ -36518,7 +36533,7 @@
         <v>202</v>
       </c>
       <c r="P172" t="s">
-        <v>286</v>
+        <v>288</v>
       </c>
       <c r="Q172">
         <v>6.35</v>
@@ -36724,7 +36739,7 @@
         <v>203</v>
       </c>
       <c r="P173" t="s">
-        <v>287</v>
+        <v>289</v>
       </c>
       <c r="Q173">
         <v>2.6</v>
@@ -36930,7 +36945,7 @@
         <v>88</v>
       </c>
       <c r="P174" t="s">
-        <v>288</v>
+        <v>290</v>
       </c>
       <c r="Q174">
         <v>4.86</v>
@@ -37136,7 +37151,7 @@
         <v>204</v>
       </c>
       <c r="P175" t="s">
-        <v>273</v>
+        <v>275</v>
       </c>
       <c r="Q175">
         <v>2.66</v>
@@ -37217,7 +37232,7 @@
         <v>1.45</v>
       </c>
       <c r="AQ175">
-        <v>1.09</v>
+        <v>1.25</v>
       </c>
       <c r="AR175">
         <v>1.42</v>
@@ -37499,6 +37514,830 @@
       </c>
       <c r="BP176">
         <v>1.71</v>
+      </c>
+    </row>
+    <row r="177" spans="1:68">
+      <c r="A177" s="1">
+        <v>176</v>
+      </c>
+      <c r="B177">
+        <v>7468257</v>
+      </c>
+      <c r="C177" t="s">
+        <v>68</v>
+      </c>
+      <c r="D177" t="s">
+        <v>69</v>
+      </c>
+      <c r="E177" s="2">
+        <v>45710.39583333334</v>
+      </c>
+      <c r="F177">
+        <v>23</v>
+      </c>
+      <c r="G177" t="s">
+        <v>74</v>
+      </c>
+      <c r="H177" t="s">
+        <v>85</v>
+      </c>
+      <c r="I177">
+        <v>0</v>
+      </c>
+      <c r="J177">
+        <v>1</v>
+      </c>
+      <c r="K177">
+        <v>1</v>
+      </c>
+      <c r="L177">
+        <v>1</v>
+      </c>
+      <c r="M177">
+        <v>3</v>
+      </c>
+      <c r="N177">
+        <v>4</v>
+      </c>
+      <c r="O177" t="s">
+        <v>171</v>
+      </c>
+      <c r="P177" t="s">
+        <v>291</v>
+      </c>
+      <c r="Q177">
+        <v>3.63</v>
+      </c>
+      <c r="R177">
+        <v>2.2</v>
+      </c>
+      <c r="S177">
+        <v>3.02</v>
+      </c>
+      <c r="T177">
+        <v>1.39</v>
+      </c>
+      <c r="U177">
+        <v>2.95</v>
+      </c>
+      <c r="V177">
+        <v>2.96</v>
+      </c>
+      <c r="W177">
+        <v>1.39</v>
+      </c>
+      <c r="X177">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="Y177">
+        <v>1.02</v>
+      </c>
+      <c r="Z177">
+        <v>2.85</v>
+      </c>
+      <c r="AA177">
+        <v>3</v>
+      </c>
+      <c r="AB177">
+        <v>2.38</v>
+      </c>
+      <c r="AC177">
+        <v>1.03</v>
+      </c>
+      <c r="AD177">
+        <v>7.7</v>
+      </c>
+      <c r="AE177">
+        <v>1.31</v>
+      </c>
+      <c r="AF177">
+        <v>3.1</v>
+      </c>
+      <c r="AG177">
+        <v>1.98</v>
+      </c>
+      <c r="AH177">
+        <v>1.77</v>
+      </c>
+      <c r="AI177">
+        <v>1.74</v>
+      </c>
+      <c r="AJ177">
+        <v>1.98</v>
+      </c>
+      <c r="AK177">
+        <v>1.53</v>
+      </c>
+      <c r="AL177">
+        <v>1.31</v>
+      </c>
+      <c r="AM177">
+        <v>1.39</v>
+      </c>
+      <c r="AN177">
+        <v>1</v>
+      </c>
+      <c r="AO177">
+        <v>1.09</v>
+      </c>
+      <c r="AP177">
+        <v>0.91</v>
+      </c>
+      <c r="AQ177">
+        <v>1.25</v>
+      </c>
+      <c r="AR177">
+        <v>1.28</v>
+      </c>
+      <c r="AS177">
+        <v>1.2</v>
+      </c>
+      <c r="AT177">
+        <v>2.48</v>
+      </c>
+      <c r="AU177">
+        <v>2</v>
+      </c>
+      <c r="AV177">
+        <v>5</v>
+      </c>
+      <c r="AW177">
+        <v>3</v>
+      </c>
+      <c r="AX177">
+        <v>5</v>
+      </c>
+      <c r="AY177">
+        <v>5</v>
+      </c>
+      <c r="AZ177">
+        <v>10</v>
+      </c>
+      <c r="BA177">
+        <v>1</v>
+      </c>
+      <c r="BB177">
+        <v>10</v>
+      </c>
+      <c r="BC177">
+        <v>11</v>
+      </c>
+      <c r="BD177">
+        <v>2.08</v>
+      </c>
+      <c r="BE177">
+        <v>6.4</v>
+      </c>
+      <c r="BF177">
+        <v>1.9</v>
+      </c>
+      <c r="BG177">
+        <v>1.42</v>
+      </c>
+      <c r="BH177">
+        <v>2.65</v>
+      </c>
+      <c r="BI177">
+        <v>1.7</v>
+      </c>
+      <c r="BJ177">
+        <v>2.02</v>
+      </c>
+      <c r="BK177">
+        <v>2.12</v>
+      </c>
+      <c r="BL177">
+        <v>1.63</v>
+      </c>
+      <c r="BM177">
+        <v>2.7</v>
+      </c>
+      <c r="BN177">
+        <v>1.38</v>
+      </c>
+      <c r="BO177">
+        <v>3.65</v>
+      </c>
+      <c r="BP177">
+        <v>1.24</v>
+      </c>
+    </row>
+    <row r="178" spans="1:68">
+      <c r="A178" s="1">
+        <v>177</v>
+      </c>
+      <c r="B178">
+        <v>7468259</v>
+      </c>
+      <c r="C178" t="s">
+        <v>68</v>
+      </c>
+      <c r="D178" t="s">
+        <v>69</v>
+      </c>
+      <c r="E178" s="2">
+        <v>45710.5</v>
+      </c>
+      <c r="F178">
+        <v>23</v>
+      </c>
+      <c r="G178" t="s">
+        <v>83</v>
+      </c>
+      <c r="H178" t="s">
+        <v>78</v>
+      </c>
+      <c r="I178">
+        <v>0</v>
+      </c>
+      <c r="J178">
+        <v>0</v>
+      </c>
+      <c r="K178">
+        <v>0</v>
+      </c>
+      <c r="L178">
+        <v>2</v>
+      </c>
+      <c r="M178">
+        <v>0</v>
+      </c>
+      <c r="N178">
+        <v>2</v>
+      </c>
+      <c r="O178" t="s">
+        <v>205</v>
+      </c>
+      <c r="P178" t="s">
+        <v>88</v>
+      </c>
+      <c r="Q178">
+        <v>2.05</v>
+      </c>
+      <c r="R178">
+        <v>2.41</v>
+      </c>
+      <c r="S178">
+        <v>5.4</v>
+      </c>
+      <c r="T178">
+        <v>1.32</v>
+      </c>
+      <c r="U178">
+        <v>3.1</v>
+      </c>
+      <c r="V178">
+        <v>2.4</v>
+      </c>
+      <c r="W178">
+        <v>1.5</v>
+      </c>
+      <c r="X178">
+        <v>5.55</v>
+      </c>
+      <c r="Y178">
+        <v>1.12</v>
+      </c>
+      <c r="Z178">
+        <v>1.6</v>
+      </c>
+      <c r="AA178">
+        <v>3.55</v>
+      </c>
+      <c r="AB178">
+        <v>5.2</v>
+      </c>
+      <c r="AC178">
+        <v>1.04</v>
+      </c>
+      <c r="AD178">
+        <v>8.5</v>
+      </c>
+      <c r="AE178">
+        <v>1.23</v>
+      </c>
+      <c r="AF178">
+        <v>3.8</v>
+      </c>
+      <c r="AG178">
+        <v>1.73</v>
+      </c>
+      <c r="AH178">
+        <v>2.03</v>
+      </c>
+      <c r="AI178">
+        <v>1.75</v>
+      </c>
+      <c r="AJ178">
+        <v>1.97</v>
+      </c>
+      <c r="AK178">
+        <v>1.15</v>
+      </c>
+      <c r="AL178">
+        <v>1.23</v>
+      </c>
+      <c r="AM178">
+        <v>2.21</v>
+      </c>
+      <c r="AN178">
+        <v>2.4</v>
+      </c>
+      <c r="AO178">
+        <v>0.82</v>
+      </c>
+      <c r="AP178">
+        <v>2.45</v>
+      </c>
+      <c r="AQ178">
+        <v>0.75</v>
+      </c>
+      <c r="AR178">
+        <v>1.82</v>
+      </c>
+      <c r="AS178">
+        <v>1.38</v>
+      </c>
+      <c r="AT178">
+        <v>3.2</v>
+      </c>
+      <c r="AU178">
+        <v>4</v>
+      </c>
+      <c r="AV178">
+        <v>0</v>
+      </c>
+      <c r="AW178">
+        <v>3</v>
+      </c>
+      <c r="AX178">
+        <v>4</v>
+      </c>
+      <c r="AY178">
+        <v>7</v>
+      </c>
+      <c r="AZ178">
+        <v>4</v>
+      </c>
+      <c r="BA178">
+        <v>13</v>
+      </c>
+      <c r="BB178">
+        <v>2</v>
+      </c>
+      <c r="BC178">
+        <v>15</v>
+      </c>
+      <c r="BD178">
+        <v>1.49</v>
+      </c>
+      <c r="BE178">
+        <v>6.75</v>
+      </c>
+      <c r="BF178">
+        <v>2.9</v>
+      </c>
+      <c r="BG178">
+        <v>1.4</v>
+      </c>
+      <c r="BH178">
+        <v>2.7</v>
+      </c>
+      <c r="BI178">
+        <v>1.66</v>
+      </c>
+      <c r="BJ178">
+        <v>2.08</v>
+      </c>
+      <c r="BK178">
+        <v>2.05</v>
+      </c>
+      <c r="BL178">
+        <v>1.68</v>
+      </c>
+      <c r="BM178">
+        <v>2.6</v>
+      </c>
+      <c r="BN178">
+        <v>1.43</v>
+      </c>
+      <c r="BO178">
+        <v>3.4</v>
+      </c>
+      <c r="BP178">
+        <v>1.25</v>
+      </c>
+    </row>
+    <row r="179" spans="1:68">
+      <c r="A179" s="1">
+        <v>178</v>
+      </c>
+      <c r="B179">
+        <v>7468264</v>
+      </c>
+      <c r="C179" t="s">
+        <v>68</v>
+      </c>
+      <c r="D179" t="s">
+        <v>69</v>
+      </c>
+      <c r="E179" s="2">
+        <v>45710.5</v>
+      </c>
+      <c r="F179">
+        <v>23</v>
+      </c>
+      <c r="G179" t="s">
+        <v>79</v>
+      </c>
+      <c r="H179" t="s">
+        <v>82</v>
+      </c>
+      <c r="I179">
+        <v>0</v>
+      </c>
+      <c r="J179">
+        <v>2</v>
+      </c>
+      <c r="K179">
+        <v>2</v>
+      </c>
+      <c r="L179">
+        <v>0</v>
+      </c>
+      <c r="M179">
+        <v>3</v>
+      </c>
+      <c r="N179">
+        <v>3</v>
+      </c>
+      <c r="O179" t="s">
+        <v>88</v>
+      </c>
+      <c r="P179" t="s">
+        <v>292</v>
+      </c>
+      <c r="Q179">
+        <v>3.92</v>
+      </c>
+      <c r="R179">
+        <v>2.14</v>
+      </c>
+      <c r="S179">
+        <v>2.61</v>
+      </c>
+      <c r="T179">
+        <v>1.37</v>
+      </c>
+      <c r="U179">
+        <v>2.9</v>
+      </c>
+      <c r="V179">
+        <v>2.73</v>
+      </c>
+      <c r="W179">
+        <v>1.41</v>
+      </c>
+      <c r="X179">
+        <v>6.4</v>
+      </c>
+      <c r="Y179">
+        <v>1.06</v>
+      </c>
+      <c r="Z179">
+        <v>3.36</v>
+      </c>
+      <c r="AA179">
+        <v>3.48</v>
+      </c>
+      <c r="AB179">
+        <v>2.06</v>
+      </c>
+      <c r="AC179">
+        <v>1.01</v>
+      </c>
+      <c r="AD179">
+        <v>9</v>
+      </c>
+      <c r="AE179">
+        <v>1.25</v>
+      </c>
+      <c r="AF179">
+        <v>3.28</v>
+      </c>
+      <c r="AG179">
+        <v>1.88</v>
+      </c>
+      <c r="AH179">
+        <v>1.89</v>
+      </c>
+      <c r="AI179">
+        <v>1.71</v>
+      </c>
+      <c r="AJ179">
+        <v>2.02</v>
+      </c>
+      <c r="AK179">
+        <v>1.72</v>
+      </c>
+      <c r="AL179">
+        <v>1.28</v>
+      </c>
+      <c r="AM179">
+        <v>1.3</v>
+      </c>
+      <c r="AN179">
+        <v>0.9</v>
+      </c>
+      <c r="AO179">
+        <v>1.09</v>
+      </c>
+      <c r="AP179">
+        <v>0.82</v>
+      </c>
+      <c r="AQ179">
+        <v>1.25</v>
+      </c>
+      <c r="AR179">
+        <v>1.2</v>
+      </c>
+      <c r="AS179">
+        <v>1.3</v>
+      </c>
+      <c r="AT179">
+        <v>2.5</v>
+      </c>
+      <c r="AU179">
+        <v>5</v>
+      </c>
+      <c r="AV179">
+        <v>7</v>
+      </c>
+      <c r="AW179">
+        <v>6</v>
+      </c>
+      <c r="AX179">
+        <v>6</v>
+      </c>
+      <c r="AY179">
+        <v>11</v>
+      </c>
+      <c r="AZ179">
+        <v>13</v>
+      </c>
+      <c r="BA179">
+        <v>3</v>
+      </c>
+      <c r="BB179">
+        <v>3</v>
+      </c>
+      <c r="BC179">
+        <v>6</v>
+      </c>
+      <c r="BD179">
+        <v>2.33</v>
+      </c>
+      <c r="BE179">
+        <v>6.4</v>
+      </c>
+      <c r="BF179">
+        <v>1.74</v>
+      </c>
+      <c r="BG179">
+        <v>1.4</v>
+      </c>
+      <c r="BH179">
+        <v>2.65</v>
+      </c>
+      <c r="BI179">
+        <v>1.68</v>
+      </c>
+      <c r="BJ179">
+        <v>2.05</v>
+      </c>
+      <c r="BK179">
+        <v>2.08</v>
+      </c>
+      <c r="BL179">
+        <v>1.65</v>
+      </c>
+      <c r="BM179">
+        <v>2.65</v>
+      </c>
+      <c r="BN179">
+        <v>1.41</v>
+      </c>
+      <c r="BO179">
+        <v>3.55</v>
+      </c>
+      <c r="BP179">
+        <v>1.24</v>
+      </c>
+    </row>
+    <row r="180" spans="1:68">
+      <c r="A180" s="1">
+        <v>179</v>
+      </c>
+      <c r="B180">
+        <v>7468269</v>
+      </c>
+      <c r="C180" t="s">
+        <v>68</v>
+      </c>
+      <c r="D180" t="s">
+        <v>69</v>
+      </c>
+      <c r="E180" s="2">
+        <v>45710.625</v>
+      </c>
+      <c r="F180">
+        <v>23</v>
+      </c>
+      <c r="G180" t="s">
+        <v>70</v>
+      </c>
+      <c r="H180" t="s">
+        <v>72</v>
+      </c>
+      <c r="I180">
+        <v>0</v>
+      </c>
+      <c r="J180">
+        <v>0</v>
+      </c>
+      <c r="K180">
+        <v>0</v>
+      </c>
+      <c r="L180">
+        <v>2</v>
+      </c>
+      <c r="M180">
+        <v>1</v>
+      </c>
+      <c r="N180">
+        <v>3</v>
+      </c>
+      <c r="O180" t="s">
+        <v>206</v>
+      </c>
+      <c r="P180" t="s">
+        <v>293</v>
+      </c>
+      <c r="Q180">
+        <v>1.32</v>
+      </c>
+      <c r="R180">
+        <v>3.92</v>
+      </c>
+      <c r="S180">
+        <v>14.04</v>
+      </c>
+      <c r="T180">
+        <v>1.14</v>
+      </c>
+      <c r="U180">
+        <v>5.1</v>
+      </c>
+      <c r="V180">
+        <v>1.79</v>
+      </c>
+      <c r="W180">
+        <v>1.99</v>
+      </c>
+      <c r="X180">
+        <v>3.2</v>
+      </c>
+      <c r="Y180">
+        <v>1.3</v>
+      </c>
+      <c r="Z180">
+        <v>1.08</v>
+      </c>
+      <c r="AA180">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="AB180">
+        <v>18</v>
+      </c>
+      <c r="AC180">
+        <v>1.01</v>
+      </c>
+      <c r="AD180">
+        <v>29</v>
+      </c>
+      <c r="AE180">
+        <v>1.01</v>
+      </c>
+      <c r="AF180">
+        <v>8.699999999999999</v>
+      </c>
+      <c r="AG180">
+        <v>1.27</v>
+      </c>
+      <c r="AH180">
+        <v>3.55</v>
+      </c>
+      <c r="AI180">
+        <v>2.19</v>
+      </c>
+      <c r="AJ180">
+        <v>1.59</v>
+      </c>
+      <c r="AK180">
+        <v>1.01</v>
+      </c>
+      <c r="AL180">
+        <v>1.03</v>
+      </c>
+      <c r="AM180">
+        <v>5.8</v>
+      </c>
+      <c r="AN180">
+        <v>2.09</v>
+      </c>
+      <c r="AO180">
+        <v>0.1</v>
+      </c>
+      <c r="AP180">
+        <v>2.17</v>
+      </c>
+      <c r="AQ180">
+        <v>0.09</v>
+      </c>
+      <c r="AR180">
+        <v>2.04</v>
+      </c>
+      <c r="AS180">
+        <v>0.98</v>
+      </c>
+      <c r="AT180">
+        <v>3.02</v>
+      </c>
+      <c r="AU180">
+        <v>12</v>
+      </c>
+      <c r="AV180">
+        <v>2</v>
+      </c>
+      <c r="AW180">
+        <v>7</v>
+      </c>
+      <c r="AX180">
+        <v>4</v>
+      </c>
+      <c r="AY180">
+        <v>19</v>
+      </c>
+      <c r="AZ180">
+        <v>6</v>
+      </c>
+      <c r="BA180">
+        <v>6</v>
+      </c>
+      <c r="BB180">
+        <v>3</v>
+      </c>
+      <c r="BC180">
+        <v>9</v>
+      </c>
+      <c r="BD180">
+        <v>1.11</v>
+      </c>
+      <c r="BE180">
+        <v>10.5</v>
+      </c>
+      <c r="BF180">
+        <v>6.75</v>
+      </c>
+      <c r="BG180">
+        <v>1.25</v>
+      </c>
+      <c r="BH180">
+        <v>3.4</v>
+      </c>
+      <c r="BI180">
+        <v>1.45</v>
+      </c>
+      <c r="BJ180">
+        <v>2.55</v>
+      </c>
+      <c r="BK180">
+        <v>1.72</v>
+      </c>
+      <c r="BL180">
+        <v>1.98</v>
+      </c>
+      <c r="BM180">
+        <v>2.08</v>
+      </c>
+      <c r="BN180">
+        <v>1.65</v>
+      </c>
+      <c r="BO180">
+        <v>2.65</v>
+      </c>
+      <c r="BP180">
+        <v>1.42</v>
       </c>
     </row>
   </sheetData>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Czech Republic First League_20242025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Czech Republic First League_20242025.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1142" uniqueCount="294">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1160" uniqueCount="297">
   <si>
     <t>Id_Jogo</t>
   </si>
@@ -637,6 +637,12 @@
     <t>['64', '75']</t>
   </si>
   <si>
+    <t>['23', '31', '54', '67', '89']</t>
+  </si>
+  <si>
+    <t>['19']</t>
+  </si>
+  <si>
     <t>['25']</t>
   </si>
   <si>
@@ -896,6 +902,9 @@
   </si>
   <si>
     <t>['90+9']</t>
+  </si>
+  <si>
+    <t>['2', '42', '47']</t>
   </si>
 </sst>
 </file>
@@ -1257,7 +1266,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:BP180"/>
+  <dimension ref="A1:BP183"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:68">
@@ -1513,7 +1522,7 @@
         <v>86</v>
       </c>
       <c r="P2" t="s">
-        <v>207</v>
+        <v>209</v>
       </c>
       <c r="Q2">
         <v>1.53</v>
@@ -1797,7 +1806,7 @@
         <v>0</v>
       </c>
       <c r="AP3">
-        <v>2</v>
+        <v>2.08</v>
       </c>
       <c r="AQ3">
         <v>1.25</v>
@@ -1925,7 +1934,7 @@
         <v>88</v>
       </c>
       <c r="P4" t="s">
-        <v>208</v>
+        <v>210</v>
       </c>
       <c r="Q4">
         <v>2.88</v>
@@ -2209,7 +2218,7 @@
         <v>0</v>
       </c>
       <c r="AP5">
-        <v>1.18</v>
+        <v>1.17</v>
       </c>
       <c r="AQ5">
         <v>1.5</v>
@@ -2337,7 +2346,7 @@
         <v>90</v>
       </c>
       <c r="P6" t="s">
-        <v>209</v>
+        <v>211</v>
       </c>
       <c r="Q6">
         <v>5.5</v>
@@ -2543,7 +2552,7 @@
         <v>91</v>
       </c>
       <c r="P7" t="s">
-        <v>210</v>
+        <v>212</v>
       </c>
       <c r="Q7">
         <v>3.2</v>
@@ -2830,7 +2839,7 @@
         <v>1.36</v>
       </c>
       <c r="AQ8">
-        <v>2.36</v>
+        <v>2.42</v>
       </c>
       <c r="AR8">
         <v>0</v>
@@ -3367,7 +3376,7 @@
         <v>94</v>
       </c>
       <c r="P11" t="s">
-        <v>211</v>
+        <v>213</v>
       </c>
       <c r="Q11">
         <v>6.5</v>
@@ -3573,7 +3582,7 @@
         <v>88</v>
       </c>
       <c r="P12" t="s">
-        <v>212</v>
+        <v>214</v>
       </c>
       <c r="Q12">
         <v>2.85</v>
@@ -3654,7 +3663,7 @@
         <v>0.82</v>
       </c>
       <c r="AQ12">
-        <v>0.89</v>
+        <v>0.8</v>
       </c>
       <c r="AR12">
         <v>0</v>
@@ -3985,7 +3994,7 @@
         <v>96</v>
       </c>
       <c r="P14" t="s">
-        <v>213</v>
+        <v>215</v>
       </c>
       <c r="Q14">
         <v>2.45</v>
@@ -4681,7 +4690,7 @@
         <v>0</v>
       </c>
       <c r="AP17">
-        <v>2.64</v>
+        <v>2.42</v>
       </c>
       <c r="AQ17">
         <v>1</v>
@@ -4809,7 +4818,7 @@
         <v>88</v>
       </c>
       <c r="P18" t="s">
-        <v>214</v>
+        <v>216</v>
       </c>
       <c r="Q18">
         <v>5.4</v>
@@ -4890,7 +4899,7 @@
         <v>1.45</v>
       </c>
       <c r="AQ18">
-        <v>2.36</v>
+        <v>2.42</v>
       </c>
       <c r="AR18">
         <v>1.26</v>
@@ -5505,7 +5514,7 @@
         <v>3</v>
       </c>
       <c r="AP21">
-        <v>2</v>
+        <v>2.08</v>
       </c>
       <c r="AQ21">
         <v>1.82</v>
@@ -5839,7 +5848,7 @@
         <v>102</v>
       </c>
       <c r="P23" t="s">
-        <v>215</v>
+        <v>217</v>
       </c>
       <c r="Q23">
         <v>2.6</v>
@@ -6045,7 +6054,7 @@
         <v>103</v>
       </c>
       <c r="P24" t="s">
-        <v>216</v>
+        <v>218</v>
       </c>
       <c r="Q24">
         <v>2.75</v>
@@ -6251,7 +6260,7 @@
         <v>88</v>
       </c>
       <c r="P25" t="s">
-        <v>217</v>
+        <v>219</v>
       </c>
       <c r="Q25">
         <v>1.06</v>
@@ -6457,7 +6466,7 @@
         <v>104</v>
       </c>
       <c r="P26" t="s">
-        <v>218</v>
+        <v>220</v>
       </c>
       <c r="Q26">
         <v>6.23</v>
@@ -6535,7 +6544,7 @@
         <v>3</v>
       </c>
       <c r="AP26">
-        <v>1.18</v>
+        <v>1.17</v>
       </c>
       <c r="AQ26">
         <v>2.09</v>
@@ -7771,10 +7780,10 @@
         <v>3</v>
       </c>
       <c r="AP32">
-        <v>2.64</v>
+        <v>2.42</v>
       </c>
       <c r="AQ32">
-        <v>0.89</v>
+        <v>0.8</v>
       </c>
       <c r="AR32">
         <v>1.64</v>
@@ -8105,7 +8114,7 @@
         <v>111</v>
       </c>
       <c r="P34" t="s">
-        <v>219</v>
+        <v>221</v>
       </c>
       <c r="Q34">
         <v>1.45</v>
@@ -8311,7 +8320,7 @@
         <v>112</v>
       </c>
       <c r="P35" t="s">
-        <v>220</v>
+        <v>222</v>
       </c>
       <c r="Q35">
         <v>2.84</v>
@@ -8517,7 +8526,7 @@
         <v>113</v>
       </c>
       <c r="P36" t="s">
-        <v>221</v>
+        <v>223</v>
       </c>
       <c r="Q36">
         <v>5.63</v>
@@ -8595,7 +8604,7 @@
         <v>3</v>
       </c>
       <c r="AP36">
-        <v>2</v>
+        <v>2.08</v>
       </c>
       <c r="AQ36">
         <v>2.09</v>
@@ -8723,7 +8732,7 @@
         <v>114</v>
       </c>
       <c r="P37" t="s">
-        <v>222</v>
+        <v>224</v>
       </c>
       <c r="Q37">
         <v>2.58</v>
@@ -9135,7 +9144,7 @@
         <v>88</v>
       </c>
       <c r="P39" t="s">
-        <v>223</v>
+        <v>225</v>
       </c>
       <c r="Q39">
         <v>4.75</v>
@@ -9547,7 +9556,7 @@
         <v>117</v>
       </c>
       <c r="P41" t="s">
-        <v>224</v>
+        <v>226</v>
       </c>
       <c r="Q41">
         <v>2.4</v>
@@ -9625,7 +9634,7 @@
         <v>1.5</v>
       </c>
       <c r="AP41">
-        <v>1.18</v>
+        <v>1.17</v>
       </c>
       <c r="AQ41">
         <v>1.27</v>
@@ -9753,7 +9762,7 @@
         <v>107</v>
       </c>
       <c r="P42" t="s">
-        <v>225</v>
+        <v>227</v>
       </c>
       <c r="Q42">
         <v>2.61</v>
@@ -9834,7 +9843,7 @@
         <v>1.18</v>
       </c>
       <c r="AQ42">
-        <v>0.89</v>
+        <v>0.8</v>
       </c>
       <c r="AR42">
         <v>1.41</v>
@@ -9959,7 +9968,7 @@
         <v>118</v>
       </c>
       <c r="P43" t="s">
-        <v>226</v>
+        <v>228</v>
       </c>
       <c r="Q43">
         <v>1.69</v>
@@ -11401,7 +11410,7 @@
         <v>88</v>
       </c>
       <c r="P50" t="s">
-        <v>227</v>
+        <v>229</v>
       </c>
       <c r="Q50">
         <v>5.1</v>
@@ -11813,7 +11822,7 @@
         <v>122</v>
       </c>
       <c r="P52" t="s">
-        <v>228</v>
+        <v>230</v>
       </c>
       <c r="Q52">
         <v>3</v>
@@ -12225,7 +12234,7 @@
         <v>124</v>
       </c>
       <c r="P54" t="s">
-        <v>229</v>
+        <v>231</v>
       </c>
       <c r="Q54">
         <v>3</v>
@@ -12637,7 +12646,7 @@
         <v>125</v>
       </c>
       <c r="P56" t="s">
-        <v>230</v>
+        <v>232</v>
       </c>
       <c r="Q56">
         <v>1.85</v>
@@ -12715,7 +12724,7 @@
         <v>1.33</v>
       </c>
       <c r="AP56">
-        <v>2.64</v>
+        <v>2.42</v>
       </c>
       <c r="AQ56">
         <v>1.25</v>
@@ -12843,7 +12852,7 @@
         <v>88</v>
       </c>
       <c r="P57" t="s">
-        <v>231</v>
+        <v>233</v>
       </c>
       <c r="Q57">
         <v>5.88</v>
@@ -12924,7 +12933,7 @@
         <v>1.73</v>
       </c>
       <c r="AQ57">
-        <v>2.36</v>
+        <v>2.42</v>
       </c>
       <c r="AR57">
         <v>1.7</v>
@@ -13255,7 +13264,7 @@
         <v>127</v>
       </c>
       <c r="P59" t="s">
-        <v>232</v>
+        <v>234</v>
       </c>
       <c r="Q59">
         <v>3.86</v>
@@ -13873,7 +13882,7 @@
         <v>130</v>
       </c>
       <c r="P62" t="s">
-        <v>233</v>
+        <v>235</v>
       </c>
       <c r="Q62">
         <v>1.83</v>
@@ -14079,7 +14088,7 @@
         <v>88</v>
       </c>
       <c r="P63" t="s">
-        <v>234</v>
+        <v>236</v>
       </c>
       <c r="Q63">
         <v>8.77</v>
@@ -14491,7 +14500,7 @@
         <v>132</v>
       </c>
       <c r="P65" t="s">
-        <v>235</v>
+        <v>237</v>
       </c>
       <c r="Q65">
         <v>2.4</v>
@@ -14697,7 +14706,7 @@
         <v>133</v>
       </c>
       <c r="P66" t="s">
-        <v>236</v>
+        <v>238</v>
       </c>
       <c r="Q66">
         <v>1.55</v>
@@ -14903,7 +14912,7 @@
         <v>134</v>
       </c>
       <c r="P67" t="s">
-        <v>237</v>
+        <v>239</v>
       </c>
       <c r="Q67">
         <v>4</v>
@@ -15109,7 +15118,7 @@
         <v>88</v>
       </c>
       <c r="P68" t="s">
-        <v>238</v>
+        <v>240</v>
       </c>
       <c r="Q68">
         <v>3.1</v>
@@ -15396,7 +15405,7 @@
         <v>1.36</v>
       </c>
       <c r="AQ69">
-        <v>0.89</v>
+        <v>0.8</v>
       </c>
       <c r="AR69">
         <v>1.16</v>
@@ -15599,7 +15608,7 @@
         <v>0</v>
       </c>
       <c r="AP70">
-        <v>2</v>
+        <v>2.08</v>
       </c>
       <c r="AQ70">
         <v>1</v>
@@ -15933,7 +15942,7 @@
         <v>124</v>
       </c>
       <c r="P72" t="s">
-        <v>239</v>
+        <v>241</v>
       </c>
       <c r="Q72">
         <v>1.88</v>
@@ -16011,7 +16020,7 @@
         <v>0.75</v>
       </c>
       <c r="AP72">
-        <v>2.64</v>
+        <v>2.42</v>
       </c>
       <c r="AQ72">
         <v>1.25</v>
@@ -16139,7 +16148,7 @@
         <v>88</v>
       </c>
       <c r="P73" t="s">
-        <v>240</v>
+        <v>242</v>
       </c>
       <c r="Q73">
         <v>7</v>
@@ -16217,10 +16226,10 @@
         <v>2.33</v>
       </c>
       <c r="AP73">
-        <v>1.18</v>
+        <v>1.17</v>
       </c>
       <c r="AQ73">
-        <v>2.36</v>
+        <v>2.42</v>
       </c>
       <c r="AR73">
         <v>1.68</v>
@@ -16551,7 +16560,7 @@
         <v>138</v>
       </c>
       <c r="P75" t="s">
-        <v>241</v>
+        <v>243</v>
       </c>
       <c r="Q75">
         <v>2.3</v>
@@ -16757,7 +16766,7 @@
         <v>88</v>
       </c>
       <c r="P76" t="s">
-        <v>242</v>
+        <v>244</v>
       </c>
       <c r="Q76">
         <v>3.7</v>
@@ -16963,7 +16972,7 @@
         <v>88</v>
       </c>
       <c r="P77" t="s">
-        <v>243</v>
+        <v>245</v>
       </c>
       <c r="Q77">
         <v>2.47</v>
@@ -17247,7 +17256,7 @@
         <v>0.8</v>
       </c>
       <c r="AP78">
-        <v>2.64</v>
+        <v>2.42</v>
       </c>
       <c r="AQ78">
         <v>0.5</v>
@@ -17581,7 +17590,7 @@
         <v>140</v>
       </c>
       <c r="P80" t="s">
-        <v>244</v>
+        <v>246</v>
       </c>
       <c r="Q80">
         <v>2.5</v>
@@ -17787,7 +17796,7 @@
         <v>141</v>
       </c>
       <c r="P81" t="s">
-        <v>245</v>
+        <v>247</v>
       </c>
       <c r="Q81">
         <v>2.38</v>
@@ -17993,7 +18002,7 @@
         <v>142</v>
       </c>
       <c r="P82" t="s">
-        <v>246</v>
+        <v>248</v>
       </c>
       <c r="Q82">
         <v>2.8</v>
@@ -18199,7 +18208,7 @@
         <v>143</v>
       </c>
       <c r="P83" t="s">
-        <v>247</v>
+        <v>249</v>
       </c>
       <c r="Q83">
         <v>2.6</v>
@@ -18405,7 +18414,7 @@
         <v>144</v>
       </c>
       <c r="P84" t="s">
-        <v>248</v>
+        <v>250</v>
       </c>
       <c r="Q84">
         <v>3.4</v>
@@ -18817,7 +18826,7 @@
         <v>146</v>
       </c>
       <c r="P86" t="s">
-        <v>249</v>
+        <v>251</v>
       </c>
       <c r="Q86">
         <v>2.88</v>
@@ -18895,7 +18904,7 @@
         <v>0.8</v>
       </c>
       <c r="AP86">
-        <v>1.18</v>
+        <v>1.17</v>
       </c>
       <c r="AQ86">
         <v>1.25</v>
@@ -19229,7 +19238,7 @@
         <v>88</v>
       </c>
       <c r="P88" t="s">
-        <v>250</v>
+        <v>252</v>
       </c>
       <c r="Q88">
         <v>2.6</v>
@@ -19435,7 +19444,7 @@
         <v>93</v>
       </c>
       <c r="P89" t="s">
-        <v>251</v>
+        <v>253</v>
       </c>
       <c r="Q89">
         <v>6.5</v>
@@ -19513,10 +19522,10 @@
         <v>2.5</v>
       </c>
       <c r="AP89">
-        <v>2</v>
+        <v>2.08</v>
       </c>
       <c r="AQ89">
-        <v>2.36</v>
+        <v>2.42</v>
       </c>
       <c r="AR89">
         <v>1.74</v>
@@ -19847,7 +19856,7 @@
         <v>149</v>
       </c>
       <c r="P91" t="s">
-        <v>252</v>
+        <v>254</v>
       </c>
       <c r="Q91">
         <v>4.7</v>
@@ -20053,7 +20062,7 @@
         <v>88</v>
       </c>
       <c r="P92" t="s">
-        <v>253</v>
+        <v>255</v>
       </c>
       <c r="Q92">
         <v>3.8</v>
@@ -20465,7 +20474,7 @@
         <v>150</v>
       </c>
       <c r="P94" t="s">
-        <v>254</v>
+        <v>256</v>
       </c>
       <c r="Q94">
         <v>3</v>
@@ -20752,7 +20761,7 @@
         <v>1.73</v>
       </c>
       <c r="AQ95">
-        <v>0.89</v>
+        <v>0.8</v>
       </c>
       <c r="AR95">
         <v>1.43</v>
@@ -21161,7 +21170,7 @@
         <v>2.5</v>
       </c>
       <c r="AP97">
-        <v>2.64</v>
+        <v>2.42</v>
       </c>
       <c r="AQ97">
         <v>2.09</v>
@@ -21573,7 +21582,7 @@
         <v>1.2</v>
       </c>
       <c r="AP99">
-        <v>2</v>
+        <v>2.08</v>
       </c>
       <c r="AQ99">
         <v>0.75</v>
@@ -21907,7 +21916,7 @@
         <v>156</v>
       </c>
       <c r="P101" t="s">
-        <v>255</v>
+        <v>257</v>
       </c>
       <c r="Q101">
         <v>1.83</v>
@@ -22397,7 +22406,7 @@
         <v>0.57</v>
       </c>
       <c r="AP103">
-        <v>1.18</v>
+        <v>1.17</v>
       </c>
       <c r="AQ103">
         <v>0.5</v>
@@ -22812,7 +22821,7 @@
         <v>1.64</v>
       </c>
       <c r="AQ105">
-        <v>2.36</v>
+        <v>2.42</v>
       </c>
       <c r="AR105">
         <v>1.41</v>
@@ -23555,7 +23564,7 @@
         <v>161</v>
       </c>
       <c r="P109" t="s">
-        <v>256</v>
+        <v>258</v>
       </c>
       <c r="Q109">
         <v>2.24</v>
@@ -23761,7 +23770,7 @@
         <v>162</v>
       </c>
       <c r="P110" t="s">
-        <v>257</v>
+        <v>259</v>
       </c>
       <c r="Q110">
         <v>4.6</v>
@@ -24045,7 +24054,7 @@
         <v>1.71</v>
       </c>
       <c r="AP111">
-        <v>2.64</v>
+        <v>2.42</v>
       </c>
       <c r="AQ111">
         <v>1.45</v>
@@ -24173,7 +24182,7 @@
         <v>164</v>
       </c>
       <c r="P112" t="s">
-        <v>213</v>
+        <v>215</v>
       </c>
       <c r="Q112">
         <v>1.44</v>
@@ -24254,7 +24263,7 @@
         <v>3</v>
       </c>
       <c r="AQ112">
-        <v>0.89</v>
+        <v>0.8</v>
       </c>
       <c r="AR112">
         <v>2.21</v>
@@ -24379,7 +24388,7 @@
         <v>165</v>
       </c>
       <c r="P113" t="s">
-        <v>258</v>
+        <v>260</v>
       </c>
       <c r="Q113">
         <v>3.25</v>
@@ -24457,7 +24466,7 @@
         <v>1.5</v>
       </c>
       <c r="AP113">
-        <v>2</v>
+        <v>2.08</v>
       </c>
       <c r="AQ113">
         <v>1.5</v>
@@ -24585,7 +24594,7 @@
         <v>151</v>
       </c>
       <c r="P114" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="Q114">
         <v>2.88</v>
@@ -24791,7 +24800,7 @@
         <v>99</v>
       </c>
       <c r="P115" t="s">
-        <v>260</v>
+        <v>262</v>
       </c>
       <c r="Q115">
         <v>1.73</v>
@@ -24997,7 +25006,7 @@
         <v>88</v>
       </c>
       <c r="P116" t="s">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="Q116">
         <v>4.33</v>
@@ -25281,7 +25290,7 @@
         <v>0.29</v>
       </c>
       <c r="AP117">
-        <v>1.18</v>
+        <v>1.17</v>
       </c>
       <c r="AQ117">
         <v>0.36</v>
@@ -25615,7 +25624,7 @@
         <v>88</v>
       </c>
       <c r="P119" t="s">
-        <v>262</v>
+        <v>264</v>
       </c>
       <c r="Q119">
         <v>15</v>
@@ -25696,7 +25705,7 @@
         <v>0.25</v>
       </c>
       <c r="AQ119">
-        <v>2.36</v>
+        <v>2.42</v>
       </c>
       <c r="AR119">
         <v>1.38</v>
@@ -25821,7 +25830,7 @@
         <v>168</v>
       </c>
       <c r="P120" t="s">
-        <v>263</v>
+        <v>265</v>
       </c>
       <c r="Q120">
         <v>3</v>
@@ -26233,7 +26242,7 @@
         <v>170</v>
       </c>
       <c r="P122" t="s">
-        <v>264</v>
+        <v>266</v>
       </c>
       <c r="Q122">
         <v>3.25</v>
@@ -26311,7 +26320,7 @@
         <v>1</v>
       </c>
       <c r="AP122">
-        <v>1.18</v>
+        <v>1.17</v>
       </c>
       <c r="AQ122">
         <v>1</v>
@@ -26645,7 +26654,7 @@
         <v>172</v>
       </c>
       <c r="P124" t="s">
-        <v>212</v>
+        <v>214</v>
       </c>
       <c r="Q124">
         <v>1.83</v>
@@ -26726,7 +26735,7 @@
         <v>2.45</v>
       </c>
       <c r="AQ124">
-        <v>0.89</v>
+        <v>0.8</v>
       </c>
       <c r="AR124">
         <v>1.87</v>
@@ -26851,7 +26860,7 @@
         <v>171</v>
       </c>
       <c r="P125" t="s">
-        <v>265</v>
+        <v>267</v>
       </c>
       <c r="Q125">
         <v>6.3</v>
@@ -27675,7 +27684,7 @@
         <v>174</v>
       </c>
       <c r="P129" t="s">
-        <v>266</v>
+        <v>268</v>
       </c>
       <c r="Q129">
         <v>2.1</v>
@@ -27753,7 +27762,7 @@
         <v>1.38</v>
       </c>
       <c r="AP129">
-        <v>2.64</v>
+        <v>2.42</v>
       </c>
       <c r="AQ129">
         <v>1.27</v>
@@ -27881,7 +27890,7 @@
         <v>175</v>
       </c>
       <c r="P130" t="s">
-        <v>267</v>
+        <v>269</v>
       </c>
       <c r="Q130">
         <v>1.5</v>
@@ -27962,7 +27971,7 @@
         <v>2.17</v>
       </c>
       <c r="AQ130">
-        <v>0.89</v>
+        <v>0.8</v>
       </c>
       <c r="AR130">
         <v>1.93</v>
@@ -28087,7 +28096,7 @@
         <v>176</v>
       </c>
       <c r="P131" t="s">
-        <v>268</v>
+        <v>270</v>
       </c>
       <c r="Q131">
         <v>3.5</v>
@@ -28293,7 +28302,7 @@
         <v>177</v>
       </c>
       <c r="P132" t="s">
-        <v>269</v>
+        <v>271</v>
       </c>
       <c r="Q132">
         <v>4.04</v>
@@ -28577,7 +28586,7 @@
         <v>0.14</v>
       </c>
       <c r="AP133">
-        <v>2</v>
+        <v>2.08</v>
       </c>
       <c r="AQ133">
         <v>0.09</v>
@@ -28705,7 +28714,7 @@
         <v>88</v>
       </c>
       <c r="P134" t="s">
-        <v>270</v>
+        <v>272</v>
       </c>
       <c r="Q134">
         <v>2.75</v>
@@ -28783,7 +28792,7 @@
         <v>0.63</v>
       </c>
       <c r="AP134">
-        <v>1.18</v>
+        <v>1.17</v>
       </c>
       <c r="AQ134">
         <v>1</v>
@@ -29117,7 +29126,7 @@
         <v>88</v>
       </c>
       <c r="P136" t="s">
-        <v>271</v>
+        <v>273</v>
       </c>
       <c r="Q136">
         <v>4.5</v>
@@ -29198,7 +29207,7 @@
         <v>2.45</v>
       </c>
       <c r="AQ136">
-        <v>2.36</v>
+        <v>2.42</v>
       </c>
       <c r="AR136">
         <v>2.02</v>
@@ -29401,7 +29410,7 @@
         <v>1</v>
       </c>
       <c r="AP137">
-        <v>2.64</v>
+        <v>2.42</v>
       </c>
       <c r="AQ137">
         <v>0.75</v>
@@ -29529,7 +29538,7 @@
         <v>91</v>
       </c>
       <c r="P138" t="s">
-        <v>258</v>
+        <v>260</v>
       </c>
       <c r="Q138">
         <v>2.25</v>
@@ -29735,7 +29744,7 @@
         <v>179</v>
       </c>
       <c r="P139" t="s">
-        <v>267</v>
+        <v>269</v>
       </c>
       <c r="Q139">
         <v>1.9</v>
@@ -29813,7 +29822,7 @@
         <v>0.25</v>
       </c>
       <c r="AP139">
-        <v>2</v>
+        <v>2.08</v>
       </c>
       <c r="AQ139">
         <v>0.36</v>
@@ -30147,7 +30156,7 @@
         <v>88</v>
       </c>
       <c r="P141" t="s">
-        <v>272</v>
+        <v>274</v>
       </c>
       <c r="Q141">
         <v>4</v>
@@ -30353,7 +30362,7 @@
         <v>117</v>
       </c>
       <c r="P142" t="s">
-        <v>273</v>
+        <v>275</v>
       </c>
       <c r="Q142">
         <v>4</v>
@@ -30765,7 +30774,7 @@
         <v>182</v>
       </c>
       <c r="P144" t="s">
-        <v>274</v>
+        <v>276</v>
       </c>
       <c r="Q144">
         <v>6</v>
@@ -30846,7 +30855,7 @@
         <v>1.82</v>
       </c>
       <c r="AQ144">
-        <v>2.36</v>
+        <v>2.42</v>
       </c>
       <c r="AR144">
         <v>1.69</v>
@@ -30971,7 +30980,7 @@
         <v>88</v>
       </c>
       <c r="P145" t="s">
-        <v>275</v>
+        <v>277</v>
       </c>
       <c r="Q145">
         <v>3.5</v>
@@ -31177,7 +31186,7 @@
         <v>183</v>
       </c>
       <c r="P146" t="s">
-        <v>276</v>
+        <v>278</v>
       </c>
       <c r="Q146">
         <v>4.33</v>
@@ -31383,7 +31392,7 @@
         <v>184</v>
       </c>
       <c r="P147" t="s">
-        <v>277</v>
+        <v>279</v>
       </c>
       <c r="Q147">
         <v>3.8</v>
@@ -31589,7 +31598,7 @@
         <v>185</v>
       </c>
       <c r="P148" t="s">
-        <v>278</v>
+        <v>280</v>
       </c>
       <c r="Q148">
         <v>2.5</v>
@@ -31667,10 +31676,10 @@
         <v>0.88</v>
       </c>
       <c r="AP148">
-        <v>1.18</v>
+        <v>1.17</v>
       </c>
       <c r="AQ148">
-        <v>0.89</v>
+        <v>0.8</v>
       </c>
       <c r="AR148">
         <v>1.47</v>
@@ -31795,7 +31804,7 @@
         <v>186</v>
       </c>
       <c r="P149" t="s">
-        <v>275</v>
+        <v>277</v>
       </c>
       <c r="Q149">
         <v>2.05</v>
@@ -32001,7 +32010,7 @@
         <v>187</v>
       </c>
       <c r="P150" t="s">
-        <v>279</v>
+        <v>281</v>
       </c>
       <c r="Q150">
         <v>1.95</v>
@@ -32207,7 +32216,7 @@
         <v>188</v>
       </c>
       <c r="P151" t="s">
-        <v>280</v>
+        <v>282</v>
       </c>
       <c r="Q151">
         <v>2.48</v>
@@ -32494,7 +32503,7 @@
         <v>1.18</v>
       </c>
       <c r="AQ152">
-        <v>2.36</v>
+        <v>2.42</v>
       </c>
       <c r="AR152">
         <v>1.55</v>
@@ -32619,7 +32628,7 @@
         <v>190</v>
       </c>
       <c r="P153" t="s">
-        <v>281</v>
+        <v>283</v>
       </c>
       <c r="Q153">
         <v>1.4</v>
@@ -32697,7 +32706,7 @@
         <v>0.13</v>
       </c>
       <c r="AP153">
-        <v>2.64</v>
+        <v>2.42</v>
       </c>
       <c r="AQ153">
         <v>0.09</v>
@@ -33031,7 +33040,7 @@
         <v>88</v>
       </c>
       <c r="P155" t="s">
-        <v>216</v>
+        <v>218</v>
       </c>
       <c r="Q155">
         <v>3.2</v>
@@ -33649,7 +33658,7 @@
         <v>88</v>
       </c>
       <c r="P158" t="s">
-        <v>282</v>
+        <v>284</v>
       </c>
       <c r="Q158">
         <v>5</v>
@@ -33855,7 +33864,7 @@
         <v>88</v>
       </c>
       <c r="P159" t="s">
-        <v>238</v>
+        <v>240</v>
       </c>
       <c r="Q159">
         <v>2.38</v>
@@ -33933,7 +33942,7 @@
         <v>1.33</v>
       </c>
       <c r="AP159">
-        <v>2</v>
+        <v>2.08</v>
       </c>
       <c r="AQ159">
         <v>1.45</v>
@@ -34267,7 +34276,7 @@
         <v>193</v>
       </c>
       <c r="P161" t="s">
-        <v>265</v>
+        <v>267</v>
       </c>
       <c r="Q161">
         <v>4.75</v>
@@ -34473,7 +34482,7 @@
         <v>194</v>
       </c>
       <c r="P162" t="s">
-        <v>283</v>
+        <v>285</v>
       </c>
       <c r="Q162">
         <v>2.63</v>
@@ -34679,7 +34688,7 @@
         <v>88</v>
       </c>
       <c r="P163" t="s">
-        <v>284</v>
+        <v>286</v>
       </c>
       <c r="Q163">
         <v>11</v>
@@ -34760,7 +34769,7 @@
         <v>0.82</v>
       </c>
       <c r="AQ163">
-        <v>2.36</v>
+        <v>2.42</v>
       </c>
       <c r="AR163">
         <v>1.29</v>
@@ -34885,7 +34894,7 @@
         <v>195</v>
       </c>
       <c r="P164" t="s">
-        <v>285</v>
+        <v>287</v>
       </c>
       <c r="Q164">
         <v>2</v>
@@ -34963,7 +34972,7 @@
         <v>1.1</v>
       </c>
       <c r="AP164">
-        <v>2.64</v>
+        <v>2.42</v>
       </c>
       <c r="AQ164">
         <v>1</v>
@@ -35091,7 +35100,7 @@
         <v>196</v>
       </c>
       <c r="P165" t="s">
-        <v>286</v>
+        <v>288</v>
       </c>
       <c r="Q165">
         <v>2.5</v>
@@ -35169,7 +35178,7 @@
         <v>1.1</v>
       </c>
       <c r="AP165">
-        <v>2</v>
+        <v>2.08</v>
       </c>
       <c r="AQ165">
         <v>1</v>
@@ -35581,7 +35590,7 @@
         <v>0.11</v>
       </c>
       <c r="AP167">
-        <v>1.18</v>
+        <v>1.17</v>
       </c>
       <c r="AQ167">
         <v>0.09</v>
@@ -36327,7 +36336,7 @@
         <v>201</v>
       </c>
       <c r="P171" t="s">
-        <v>287</v>
+        <v>289</v>
       </c>
       <c r="Q171">
         <v>5.2</v>
@@ -36533,7 +36542,7 @@
         <v>202</v>
       </c>
       <c r="P172" t="s">
-        <v>288</v>
+        <v>290</v>
       </c>
       <c r="Q172">
         <v>6.35</v>
@@ -36739,7 +36748,7 @@
         <v>203</v>
       </c>
       <c r="P173" t="s">
-        <v>289</v>
+        <v>291</v>
       </c>
       <c r="Q173">
         <v>2.6</v>
@@ -36945,7 +36954,7 @@
         <v>88</v>
       </c>
       <c r="P174" t="s">
-        <v>290</v>
+        <v>292</v>
       </c>
       <c r="Q174">
         <v>4.86</v>
@@ -37151,7 +37160,7 @@
         <v>204</v>
       </c>
       <c r="P175" t="s">
-        <v>275</v>
+        <v>277</v>
       </c>
       <c r="Q175">
         <v>2.66</v>
@@ -37563,7 +37572,7 @@
         <v>171</v>
       </c>
       <c r="P177" t="s">
-        <v>291</v>
+        <v>293</v>
       </c>
       <c r="Q177">
         <v>3.63</v>
@@ -37975,7 +37984,7 @@
         <v>88</v>
       </c>
       <c r="P179" t="s">
-        <v>292</v>
+        <v>294</v>
       </c>
       <c r="Q179">
         <v>3.92</v>
@@ -38181,7 +38190,7 @@
         <v>206</v>
       </c>
       <c r="P180" t="s">
-        <v>293</v>
+        <v>295</v>
       </c>
       <c r="Q180">
         <v>1.32</v>
@@ -38338,6 +38347,624 @@
       </c>
       <c r="BP180">
         <v>1.42</v>
+      </c>
+    </row>
+    <row r="181" spans="1:68">
+      <c r="A181" s="1">
+        <v>180</v>
+      </c>
+      <c r="B181">
+        <v>7468256</v>
+      </c>
+      <c r="C181" t="s">
+        <v>68</v>
+      </c>
+      <c r="D181" t="s">
+        <v>69</v>
+      </c>
+      <c r="E181" s="2">
+        <v>45711.375</v>
+      </c>
+      <c r="F181">
+        <v>23</v>
+      </c>
+      <c r="G181" t="s">
+        <v>73</v>
+      </c>
+      <c r="H181" t="s">
+        <v>81</v>
+      </c>
+      <c r="I181">
+        <v>0</v>
+      </c>
+      <c r="J181">
+        <v>0</v>
+      </c>
+      <c r="K181">
+        <v>0</v>
+      </c>
+      <c r="L181">
+        <v>0</v>
+      </c>
+      <c r="M181">
+        <v>0</v>
+      </c>
+      <c r="N181">
+        <v>0</v>
+      </c>
+      <c r="O181" t="s">
+        <v>88</v>
+      </c>
+      <c r="P181" t="s">
+        <v>88</v>
+      </c>
+      <c r="Q181">
+        <v>2.88</v>
+      </c>
+      <c r="R181">
+        <v>2.2</v>
+      </c>
+      <c r="S181">
+        <v>3.6</v>
+      </c>
+      <c r="T181">
+        <v>1.4</v>
+      </c>
+      <c r="U181">
+        <v>2.75</v>
+      </c>
+      <c r="V181">
+        <v>2.75</v>
+      </c>
+      <c r="W181">
+        <v>1.4</v>
+      </c>
+      <c r="X181">
+        <v>8</v>
+      </c>
+      <c r="Y181">
+        <v>1.08</v>
+      </c>
+      <c r="Z181">
+        <v>2.2</v>
+      </c>
+      <c r="AA181">
+        <v>3.3</v>
+      </c>
+      <c r="AB181">
+        <v>3</v>
+      </c>
+      <c r="AC181">
+        <v>1.05</v>
+      </c>
+      <c r="AD181">
+        <v>8.5</v>
+      </c>
+      <c r="AE181">
+        <v>1.28</v>
+      </c>
+      <c r="AF181">
+        <v>3.35</v>
+      </c>
+      <c r="AG181">
+        <v>1.96</v>
+      </c>
+      <c r="AH181">
+        <v>1.86</v>
+      </c>
+      <c r="AI181">
+        <v>1.7</v>
+      </c>
+      <c r="AJ181">
+        <v>2.05</v>
+      </c>
+      <c r="AK181">
+        <v>1.34</v>
+      </c>
+      <c r="AL181">
+        <v>1.29</v>
+      </c>
+      <c r="AM181">
+        <v>1.65</v>
+      </c>
+      <c r="AN181">
+        <v>1.18</v>
+      </c>
+      <c r="AO181">
+        <v>1</v>
+      </c>
+      <c r="AP181">
+        <v>1.17</v>
+      </c>
+      <c r="AQ181">
+        <v>1</v>
+      </c>
+      <c r="AR181">
+        <v>1.62</v>
+      </c>
+      <c r="AS181">
+        <v>1.49</v>
+      </c>
+      <c r="AT181">
+        <v>3.11</v>
+      </c>
+      <c r="AU181">
+        <v>4</v>
+      </c>
+      <c r="AV181">
+        <v>3</v>
+      </c>
+      <c r="AW181">
+        <v>5</v>
+      </c>
+      <c r="AX181">
+        <v>2</v>
+      </c>
+      <c r="AY181">
+        <v>9</v>
+      </c>
+      <c r="AZ181">
+        <v>5</v>
+      </c>
+      <c r="BA181">
+        <v>4</v>
+      </c>
+      <c r="BB181">
+        <v>1</v>
+      </c>
+      <c r="BC181">
+        <v>5</v>
+      </c>
+      <c r="BD181">
+        <v>1.55</v>
+      </c>
+      <c r="BE181">
+        <v>7.6</v>
+      </c>
+      <c r="BF181">
+        <v>2.82</v>
+      </c>
+      <c r="BG181">
+        <v>1.19</v>
+      </c>
+      <c r="BH181">
+        <v>4.1</v>
+      </c>
+      <c r="BI181">
+        <v>1.24</v>
+      </c>
+      <c r="BJ181">
+        <v>3.55</v>
+      </c>
+      <c r="BK181">
+        <v>1.45</v>
+      </c>
+      <c r="BL181">
+        <v>2.52</v>
+      </c>
+      <c r="BM181">
+        <v>1.78</v>
+      </c>
+      <c r="BN181">
+        <v>1.92</v>
+      </c>
+      <c r="BO181">
+        <v>2.28</v>
+      </c>
+      <c r="BP181">
+        <v>1.52</v>
+      </c>
+    </row>
+    <row r="182" spans="1:68">
+      <c r="A182" s="1">
+        <v>181</v>
+      </c>
+      <c r="B182">
+        <v>7468270</v>
+      </c>
+      <c r="C182" t="s">
+        <v>68</v>
+      </c>
+      <c r="D182" t="s">
+        <v>69</v>
+      </c>
+      <c r="E182" s="2">
+        <v>45711.47916666666</v>
+      </c>
+      <c r="F182">
+        <v>23</v>
+      </c>
+      <c r="G182" t="s">
+        <v>71</v>
+      </c>
+      <c r="H182" t="s">
+        <v>75</v>
+      </c>
+      <c r="I182">
+        <v>2</v>
+      </c>
+      <c r="J182">
+        <v>0</v>
+      </c>
+      <c r="K182">
+        <v>2</v>
+      </c>
+      <c r="L182">
+        <v>5</v>
+      </c>
+      <c r="M182">
+        <v>0</v>
+      </c>
+      <c r="N182">
+        <v>5</v>
+      </c>
+      <c r="O182" t="s">
+        <v>207</v>
+      </c>
+      <c r="P182" t="s">
+        <v>88</v>
+      </c>
+      <c r="Q182">
+        <v>2.04</v>
+      </c>
+      <c r="R182">
+        <v>2.48</v>
+      </c>
+      <c r="S182">
+        <v>5.2</v>
+      </c>
+      <c r="T182">
+        <v>1.29</v>
+      </c>
+      <c r="U182">
+        <v>3.3</v>
+      </c>
+      <c r="V182">
+        <v>2.32</v>
+      </c>
+      <c r="W182">
+        <v>1.55</v>
+      </c>
+      <c r="X182">
+        <v>5.15</v>
+      </c>
+      <c r="Y182">
+        <v>1.13</v>
+      </c>
+      <c r="Z182">
+        <v>1.58</v>
+      </c>
+      <c r="AA182">
+        <v>3.8</v>
+      </c>
+      <c r="AB182">
+        <v>4.9</v>
+      </c>
+      <c r="AC182">
+        <v>1.01</v>
+      </c>
+      <c r="AD182">
+        <v>11</v>
+      </c>
+      <c r="AE182">
+        <v>1.2</v>
+      </c>
+      <c r="AF182">
+        <v>4.2</v>
+      </c>
+      <c r="AG182">
+        <v>1.63</v>
+      </c>
+      <c r="AH182">
+        <v>2.19</v>
+      </c>
+      <c r="AI182">
+        <v>1.68</v>
+      </c>
+      <c r="AJ182">
+        <v>2.07</v>
+      </c>
+      <c r="AK182">
+        <v>1.16</v>
+      </c>
+      <c r="AL182">
+        <v>1.21</v>
+      </c>
+      <c r="AM182">
+        <v>2.24</v>
+      </c>
+      <c r="AN182">
+        <v>2</v>
+      </c>
+      <c r="AO182">
+        <v>0.89</v>
+      </c>
+      <c r="AP182">
+        <v>2.08</v>
+      </c>
+      <c r="AQ182">
+        <v>0.8</v>
+      </c>
+      <c r="AR182">
+        <v>1.67</v>
+      </c>
+      <c r="AS182">
+        <v>1.48</v>
+      </c>
+      <c r="AT182">
+        <v>3.15</v>
+      </c>
+      <c r="AU182">
+        <v>10</v>
+      </c>
+      <c r="AV182">
+        <v>3</v>
+      </c>
+      <c r="AW182">
+        <v>5</v>
+      </c>
+      <c r="AX182">
+        <v>4</v>
+      </c>
+      <c r="AY182">
+        <v>15</v>
+      </c>
+      <c r="AZ182">
+        <v>7</v>
+      </c>
+      <c r="BA182">
+        <v>4</v>
+      </c>
+      <c r="BB182">
+        <v>2</v>
+      </c>
+      <c r="BC182">
+        <v>6</v>
+      </c>
+      <c r="BD182">
+        <v>1.5</v>
+      </c>
+      <c r="BE182">
+        <v>6.75</v>
+      </c>
+      <c r="BF182">
+        <v>2.8</v>
+      </c>
+      <c r="BG182">
+        <v>1.34</v>
+      </c>
+      <c r="BH182">
+        <v>2.9</v>
+      </c>
+      <c r="BI182">
+        <v>1.58</v>
+      </c>
+      <c r="BJ182">
+        <v>2.18</v>
+      </c>
+      <c r="BK182">
+        <v>1.95</v>
+      </c>
+      <c r="BL182">
+        <v>1.75</v>
+      </c>
+      <c r="BM182">
+        <v>2.48</v>
+      </c>
+      <c r="BN182">
+        <v>1.47</v>
+      </c>
+      <c r="BO182">
+        <v>3.2</v>
+      </c>
+      <c r="BP182">
+        <v>1.29</v>
+      </c>
+    </row>
+    <row r="183" spans="1:68">
+      <c r="A183" s="1">
+        <v>182</v>
+      </c>
+      <c r="B183">
+        <v>7468258</v>
+      </c>
+      <c r="C183" t="s">
+        <v>68</v>
+      </c>
+      <c r="D183" t="s">
+        <v>69</v>
+      </c>
+      <c r="E183" s="2">
+        <v>45711.60416666666</v>
+      </c>
+      <c r="F183">
+        <v>23</v>
+      </c>
+      <c r="G183" t="s">
+        <v>84</v>
+      </c>
+      <c r="H183" t="s">
+        <v>80</v>
+      </c>
+      <c r="I183">
+        <v>1</v>
+      </c>
+      <c r="J183">
+        <v>2</v>
+      </c>
+      <c r="K183">
+        <v>3</v>
+      </c>
+      <c r="L183">
+        <v>1</v>
+      </c>
+      <c r="M183">
+        <v>3</v>
+      </c>
+      <c r="N183">
+        <v>4</v>
+      </c>
+      <c r="O183" t="s">
+        <v>208</v>
+      </c>
+      <c r="P183" t="s">
+        <v>296</v>
+      </c>
+      <c r="Q183">
+        <v>4.3</v>
+      </c>
+      <c r="R183">
+        <v>2.08</v>
+      </c>
+      <c r="S183">
+        <v>2.7</v>
+      </c>
+      <c r="T183">
+        <v>1.46</v>
+      </c>
+      <c r="U183">
+        <v>2.55</v>
+      </c>
+      <c r="V183">
+        <v>3.05</v>
+      </c>
+      <c r="W183">
+        <v>1.34</v>
+      </c>
+      <c r="X183">
+        <v>8</v>
+      </c>
+      <c r="Y183">
+        <v>1.08</v>
+      </c>
+      <c r="Z183">
+        <v>3.45</v>
+      </c>
+      <c r="AA183">
+        <v>3.1</v>
+      </c>
+      <c r="AB183">
+        <v>2.04</v>
+      </c>
+      <c r="AC183">
+        <v>1.02</v>
+      </c>
+      <c r="AD183">
+        <v>7.9</v>
+      </c>
+      <c r="AE183">
+        <v>1.37</v>
+      </c>
+      <c r="AF183">
+        <v>2.85</v>
+      </c>
+      <c r="AG183">
+        <v>2.12</v>
+      </c>
+      <c r="AH183">
+        <v>1.67</v>
+      </c>
+      <c r="AI183">
+        <v>1.89</v>
+      </c>
+      <c r="AJ183">
+        <v>1.82</v>
+      </c>
+      <c r="AK183">
+        <v>1.71</v>
+      </c>
+      <c r="AL183">
+        <v>1.29</v>
+      </c>
+      <c r="AM183">
+        <v>1.28</v>
+      </c>
+      <c r="AN183">
+        <v>2.64</v>
+      </c>
+      <c r="AO183">
+        <v>2.36</v>
+      </c>
+      <c r="AP183">
+        <v>2.42</v>
+      </c>
+      <c r="AQ183">
+        <v>2.42</v>
+      </c>
+      <c r="AR183">
+        <v>1.82</v>
+      </c>
+      <c r="AS183">
+        <v>1.91</v>
+      </c>
+      <c r="AT183">
+        <v>3.73</v>
+      </c>
+      <c r="AU183">
+        <v>5</v>
+      </c>
+      <c r="AV183">
+        <v>7</v>
+      </c>
+      <c r="AW183">
+        <v>4</v>
+      </c>
+      <c r="AX183">
+        <v>4</v>
+      </c>
+      <c r="AY183">
+        <v>9</v>
+      </c>
+      <c r="AZ183">
+        <v>11</v>
+      </c>
+      <c r="BA183">
+        <v>4</v>
+      </c>
+      <c r="BB183">
+        <v>6</v>
+      </c>
+      <c r="BC183">
+        <v>10</v>
+      </c>
+      <c r="BD183">
+        <v>2.4</v>
+      </c>
+      <c r="BE183">
+        <v>6.75</v>
+      </c>
+      <c r="BF183">
+        <v>1.68</v>
+      </c>
+      <c r="BG183">
+        <v>1.3</v>
+      </c>
+      <c r="BH183">
+        <v>3.05</v>
+      </c>
+      <c r="BI183">
+        <v>1.52</v>
+      </c>
+      <c r="BJ183">
+        <v>2.32</v>
+      </c>
+      <c r="BK183">
+        <v>1.84</v>
+      </c>
+      <c r="BL183">
+        <v>1.84</v>
+      </c>
+      <c r="BM183">
+        <v>2.32</v>
+      </c>
+      <c r="BN183">
+        <v>1.53</v>
+      </c>
+      <c r="BO183">
+        <v>2.95</v>
+      </c>
+      <c r="BP183">
+        <v>1.33</v>
       </c>
     </row>
   </sheetData>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Czech Republic First League_20242025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Czech Republic First League_20242025.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1160" uniqueCount="297">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1184" uniqueCount="300">
   <si>
     <t>Id_Jogo</t>
   </si>
@@ -643,6 +643,9 @@
     <t>['19']</t>
   </si>
   <si>
+    <t>['37', '57']</t>
+  </si>
+  <si>
     <t>['25']</t>
   </si>
   <si>
@@ -905,6 +908,12 @@
   </si>
   <si>
     <t>['2', '42', '47']</t>
+  </si>
+  <si>
+    <t>['13', '45', '68', '81']</t>
+  </si>
+  <si>
+    <t>['25', '87']</t>
   </si>
 </sst>
 </file>
@@ -1266,7 +1275,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:BP183"/>
+  <dimension ref="A1:BP187"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:68">
@@ -1522,7 +1531,7 @@
         <v>86</v>
       </c>
       <c r="P2" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="Q2">
         <v>1.53</v>
@@ -1603,7 +1612,7 @@
         <v>2.17</v>
       </c>
       <c r="AQ2">
-        <v>0.5</v>
+        <v>0.46</v>
       </c>
       <c r="AR2">
         <v>0</v>
@@ -1934,7 +1943,7 @@
         <v>88</v>
       </c>
       <c r="P4" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="Q4">
         <v>2.88</v>
@@ -2012,7 +2021,7 @@
         <v>0</v>
       </c>
       <c r="AP4">
-        <v>0.25</v>
+        <v>0.23</v>
       </c>
       <c r="AQ4">
         <v>1.25</v>
@@ -2221,7 +2230,7 @@
         <v>1.17</v>
       </c>
       <c r="AQ5">
-        <v>1.5</v>
+        <v>1.62</v>
       </c>
       <c r="AR5">
         <v>0</v>
@@ -2346,7 +2355,7 @@
         <v>90</v>
       </c>
       <c r="P6" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="Q6">
         <v>5.5</v>
@@ -2552,7 +2561,7 @@
         <v>91</v>
       </c>
       <c r="P7" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="Q7">
         <v>3.2</v>
@@ -3042,7 +3051,7 @@
         <v>0</v>
       </c>
       <c r="AP9">
-        <v>1.64</v>
+        <v>1.58</v>
       </c>
       <c r="AQ9">
         <v>0.75</v>
@@ -3376,7 +3385,7 @@
         <v>94</v>
       </c>
       <c r="P11" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="Q11">
         <v>6.5</v>
@@ -3454,10 +3463,10 @@
         <v>0</v>
       </c>
       <c r="AP11">
-        <v>1.18</v>
+        <v>1.33</v>
       </c>
       <c r="AQ11">
-        <v>2.09</v>
+        <v>2.17</v>
       </c>
       <c r="AR11">
         <v>0</v>
@@ -3582,7 +3591,7 @@
         <v>88</v>
       </c>
       <c r="P12" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="Q12">
         <v>2.85</v>
@@ -3994,7 +4003,7 @@
         <v>96</v>
       </c>
       <c r="P14" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="Q14">
         <v>2.45</v>
@@ -4487,7 +4496,7 @@
         <v>2.45</v>
       </c>
       <c r="AQ16">
-        <v>1.27</v>
+        <v>1.25</v>
       </c>
       <c r="AR16">
         <v>0</v>
@@ -4818,7 +4827,7 @@
         <v>88</v>
       </c>
       <c r="P18" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="Q18">
         <v>5.4</v>
@@ -5720,7 +5729,7 @@
         <v>0</v>
       </c>
       <c r="AP22">
-        <v>1.82</v>
+        <v>1.67</v>
       </c>
       <c r="AQ22">
         <v>0.75</v>
@@ -5848,7 +5857,7 @@
         <v>102</v>
       </c>
       <c r="P23" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="Q23">
         <v>2.6</v>
@@ -5926,10 +5935,10 @@
         <v>0</v>
       </c>
       <c r="AP23">
-        <v>0.25</v>
+        <v>0.23</v>
       </c>
       <c r="AQ23">
-        <v>0.5</v>
+        <v>0.46</v>
       </c>
       <c r="AR23">
         <v>1.33</v>
@@ -6054,7 +6063,7 @@
         <v>103</v>
       </c>
       <c r="P24" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="Q24">
         <v>2.75</v>
@@ -6132,7 +6141,7 @@
         <v>0</v>
       </c>
       <c r="AP24">
-        <v>1.64</v>
+        <v>1.58</v>
       </c>
       <c r="AQ24">
         <v>1.25</v>
@@ -6260,7 +6269,7 @@
         <v>88</v>
       </c>
       <c r="P25" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="Q25">
         <v>1.06</v>
@@ -6341,7 +6350,7 @@
         <v>0.91</v>
       </c>
       <c r="AQ25">
-        <v>1.27</v>
+        <v>1.25</v>
       </c>
       <c r="AR25">
         <v>0.93</v>
@@ -6466,7 +6475,7 @@
         <v>104</v>
       </c>
       <c r="P26" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="Q26">
         <v>6.23</v>
@@ -6547,7 +6556,7 @@
         <v>1.17</v>
       </c>
       <c r="AQ26">
-        <v>2.09</v>
+        <v>2.17</v>
       </c>
       <c r="AR26">
         <v>1.73</v>
@@ -6750,7 +6759,7 @@
         <v>3</v>
       </c>
       <c r="AP27">
-        <v>1.18</v>
+        <v>1.33</v>
       </c>
       <c r="AQ27">
         <v>1</v>
@@ -7986,7 +7995,7 @@
         <v>0</v>
       </c>
       <c r="AP33">
-        <v>1.64</v>
+        <v>1.58</v>
       </c>
       <c r="AQ33">
         <v>0.36</v>
@@ -8114,7 +8123,7 @@
         <v>111</v>
       </c>
       <c r="P34" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="Q34">
         <v>1.45</v>
@@ -8320,7 +8329,7 @@
         <v>112</v>
       </c>
       <c r="P35" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="Q35">
         <v>2.84</v>
@@ -8526,7 +8535,7 @@
         <v>113</v>
       </c>
       <c r="P36" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="Q36">
         <v>5.63</v>
@@ -8607,7 +8616,7 @@
         <v>2.08</v>
       </c>
       <c r="AQ36">
-        <v>2.09</v>
+        <v>2.17</v>
       </c>
       <c r="AR36">
         <v>1.54</v>
@@ -8732,7 +8741,7 @@
         <v>114</v>
       </c>
       <c r="P37" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="Q37">
         <v>2.58</v>
@@ -8810,7 +8819,7 @@
         <v>0</v>
       </c>
       <c r="AP37">
-        <v>1.82</v>
+        <v>1.67</v>
       </c>
       <c r="AQ37">
         <v>1.25</v>
@@ -9019,7 +9028,7 @@
         <v>1.45</v>
       </c>
       <c r="AQ38">
-        <v>0.5</v>
+        <v>0.46</v>
       </c>
       <c r="AR38">
         <v>1.34</v>
@@ -9144,7 +9153,7 @@
         <v>88</v>
       </c>
       <c r="P39" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="Q39">
         <v>4.75</v>
@@ -9222,7 +9231,7 @@
         <v>2</v>
       </c>
       <c r="AP39">
-        <v>0.25</v>
+        <v>0.23</v>
       </c>
       <c r="AQ39">
         <v>1.82</v>
@@ -9431,7 +9440,7 @@
         <v>1.36</v>
       </c>
       <c r="AQ40">
-        <v>1.5</v>
+        <v>1.62</v>
       </c>
       <c r="AR40">
         <v>1.19</v>
@@ -9556,7 +9565,7 @@
         <v>117</v>
       </c>
       <c r="P41" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="Q41">
         <v>2.4</v>
@@ -9637,7 +9646,7 @@
         <v>1.17</v>
       </c>
       <c r="AQ41">
-        <v>1.27</v>
+        <v>1.25</v>
       </c>
       <c r="AR41">
         <v>1.49</v>
@@ -9762,7 +9771,7 @@
         <v>107</v>
       </c>
       <c r="P42" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="Q42">
         <v>2.61</v>
@@ -9840,7 +9849,7 @@
         <v>1.5</v>
       </c>
       <c r="AP42">
-        <v>1.18</v>
+        <v>1.33</v>
       </c>
       <c r="AQ42">
         <v>0.8</v>
@@ -9968,7 +9977,7 @@
         <v>118</v>
       </c>
       <c r="P43" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="Q43">
         <v>1.69</v>
@@ -10873,7 +10882,7 @@
         <v>1.33</v>
       </c>
       <c r="AQ47">
-        <v>1.5</v>
+        <v>1.62</v>
       </c>
       <c r="AR47">
         <v>1.77</v>
@@ -11076,7 +11085,7 @@
         <v>1.33</v>
       </c>
       <c r="AP48">
-        <v>0.25</v>
+        <v>0.23</v>
       </c>
       <c r="AQ48">
         <v>1.45</v>
@@ -11285,7 +11294,7 @@
         <v>1.36</v>
       </c>
       <c r="AQ49">
-        <v>1.27</v>
+        <v>1.25</v>
       </c>
       <c r="AR49">
         <v>1.24</v>
@@ -11410,7 +11419,7 @@
         <v>88</v>
       </c>
       <c r="P50" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="Q50">
         <v>5.1</v>
@@ -11488,10 +11497,10 @@
         <v>3</v>
       </c>
       <c r="AP50">
-        <v>1.64</v>
+        <v>1.58</v>
       </c>
       <c r="AQ50">
-        <v>2.09</v>
+        <v>2.17</v>
       </c>
       <c r="AR50">
         <v>1.24</v>
@@ -11822,7 +11831,7 @@
         <v>122</v>
       </c>
       <c r="P52" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="Q52">
         <v>3</v>
@@ -11900,10 +11909,10 @@
         <v>0.33</v>
       </c>
       <c r="AP52">
-        <v>1.82</v>
+        <v>1.67</v>
       </c>
       <c r="AQ52">
-        <v>1.5</v>
+        <v>1.62</v>
       </c>
       <c r="AR52">
         <v>1.61</v>
@@ -12109,7 +12118,7 @@
         <v>3</v>
       </c>
       <c r="AQ53">
-        <v>0.5</v>
+        <v>0.46</v>
       </c>
       <c r="AR53">
         <v>2.35</v>
@@ -12234,7 +12243,7 @@
         <v>124</v>
       </c>
       <c r="P54" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="Q54">
         <v>3</v>
@@ -12312,7 +12321,7 @@
         <v>0</v>
       </c>
       <c r="AP54">
-        <v>1.18</v>
+        <v>1.33</v>
       </c>
       <c r="AQ54">
         <v>1.25</v>
@@ -12646,7 +12655,7 @@
         <v>125</v>
       </c>
       <c r="P56" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="Q56">
         <v>1.85</v>
@@ -12852,7 +12861,7 @@
         <v>88</v>
       </c>
       <c r="P57" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="Q57">
         <v>5.88</v>
@@ -13136,7 +13145,7 @@
         <v>1.33</v>
       </c>
       <c r="AP58">
-        <v>1.64</v>
+        <v>1.58</v>
       </c>
       <c r="AQ58">
         <v>1</v>
@@ -13264,7 +13273,7 @@
         <v>127</v>
       </c>
       <c r="P59" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="Q59">
         <v>3.86</v>
@@ -13342,10 +13351,10 @@
         <v>0.5</v>
       </c>
       <c r="AP59">
-        <v>1.18</v>
+        <v>1.33</v>
       </c>
       <c r="AQ59">
-        <v>1.5</v>
+        <v>1.62</v>
       </c>
       <c r="AR59">
         <v>1.44</v>
@@ -13551,7 +13560,7 @@
         <v>1.33</v>
       </c>
       <c r="AQ60">
-        <v>1.27</v>
+        <v>1.25</v>
       </c>
       <c r="AR60">
         <v>1.83</v>
@@ -13882,7 +13891,7 @@
         <v>130</v>
       </c>
       <c r="P62" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="Q62">
         <v>1.83</v>
@@ -13963,7 +13972,7 @@
         <v>1.73</v>
       </c>
       <c r="AQ62">
-        <v>0.5</v>
+        <v>0.46</v>
       </c>
       <c r="AR62">
         <v>1.42</v>
@@ -14088,7 +14097,7 @@
         <v>88</v>
       </c>
       <c r="P63" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="Q63">
         <v>8.77</v>
@@ -14166,10 +14175,10 @@
         <v>3</v>
       </c>
       <c r="AP63">
-        <v>0.25</v>
+        <v>0.23</v>
       </c>
       <c r="AQ63">
-        <v>2.09</v>
+        <v>2.17</v>
       </c>
       <c r="AR63">
         <v>1.37</v>
@@ -14372,7 +14381,7 @@
         <v>0.33</v>
       </c>
       <c r="AP64">
-        <v>1.82</v>
+        <v>1.67</v>
       </c>
       <c r="AQ64">
         <v>0.36</v>
@@ -14500,7 +14509,7 @@
         <v>132</v>
       </c>
       <c r="P65" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="Q65">
         <v>2.4</v>
@@ -14706,7 +14715,7 @@
         <v>133</v>
       </c>
       <c r="P66" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="Q66">
         <v>1.55</v>
@@ -14912,7 +14921,7 @@
         <v>134</v>
       </c>
       <c r="P67" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="Q67">
         <v>4</v>
@@ -15118,7 +15127,7 @@
         <v>88</v>
       </c>
       <c r="P68" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="Q68">
         <v>3.1</v>
@@ -15942,7 +15951,7 @@
         <v>124</v>
       </c>
       <c r="P72" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="Q72">
         <v>1.88</v>
@@ -16148,7 +16157,7 @@
         <v>88</v>
       </c>
       <c r="P73" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="Q73">
         <v>7</v>
@@ -16560,7 +16569,7 @@
         <v>138</v>
       </c>
       <c r="P75" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="Q75">
         <v>2.3</v>
@@ -16638,7 +16647,7 @@
         <v>0.25</v>
       </c>
       <c r="AP75">
-        <v>1.18</v>
+        <v>1.33</v>
       </c>
       <c r="AQ75">
         <v>0.36</v>
@@ -16766,7 +16775,7 @@
         <v>88</v>
       </c>
       <c r="P76" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="Q76">
         <v>3.7</v>
@@ -16844,7 +16853,7 @@
         <v>1</v>
       </c>
       <c r="AP76">
-        <v>0.25</v>
+        <v>0.23</v>
       </c>
       <c r="AQ76">
         <v>1</v>
@@ -16972,7 +16981,7 @@
         <v>88</v>
       </c>
       <c r="P77" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="Q77">
         <v>2.47</v>
@@ -17053,7 +17062,7 @@
         <v>1.45</v>
       </c>
       <c r="AQ77">
-        <v>1.27</v>
+        <v>1.25</v>
       </c>
       <c r="AR77">
         <v>1.45</v>
@@ -17259,7 +17268,7 @@
         <v>2.42</v>
       </c>
       <c r="AQ78">
-        <v>0.5</v>
+        <v>0.46</v>
       </c>
       <c r="AR78">
         <v>1.78</v>
@@ -17465,7 +17474,7 @@
         <v>1.73</v>
       </c>
       <c r="AQ79">
-        <v>1.5</v>
+        <v>1.62</v>
       </c>
       <c r="AR79">
         <v>1.49</v>
@@ -17590,7 +17599,7 @@
         <v>140</v>
       </c>
       <c r="P80" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="Q80">
         <v>2.5</v>
@@ -17668,7 +17677,7 @@
         <v>1.2</v>
       </c>
       <c r="AP80">
-        <v>1.82</v>
+        <v>1.67</v>
       </c>
       <c r="AQ80">
         <v>1.45</v>
@@ -17796,7 +17805,7 @@
         <v>141</v>
       </c>
       <c r="P81" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="Q81">
         <v>2.38</v>
@@ -17877,7 +17886,7 @@
         <v>3</v>
       </c>
       <c r="AQ81">
-        <v>2.09</v>
+        <v>2.17</v>
       </c>
       <c r="AR81">
         <v>2.43</v>
@@ -18002,7 +18011,7 @@
         <v>142</v>
       </c>
       <c r="P82" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="Q82">
         <v>2.8</v>
@@ -18080,7 +18089,7 @@
         <v>1.4</v>
       </c>
       <c r="AP82">
-        <v>1.64</v>
+        <v>1.58</v>
       </c>
       <c r="AQ82">
         <v>1.25</v>
@@ -18208,7 +18217,7 @@
         <v>143</v>
       </c>
       <c r="P83" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="Q83">
         <v>2.6</v>
@@ -18289,7 +18298,7 @@
         <v>0.91</v>
       </c>
       <c r="AQ83">
-        <v>0.5</v>
+        <v>0.46</v>
       </c>
       <c r="AR83">
         <v>1.14</v>
@@ -18414,7 +18423,7 @@
         <v>144</v>
       </c>
       <c r="P84" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="Q84">
         <v>3.4</v>
@@ -18826,7 +18835,7 @@
         <v>146</v>
       </c>
       <c r="P86" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="Q86">
         <v>2.88</v>
@@ -19238,7 +19247,7 @@
         <v>88</v>
       </c>
       <c r="P88" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="Q88">
         <v>2.6</v>
@@ -19444,7 +19453,7 @@
         <v>93</v>
       </c>
       <c r="P89" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="Q89">
         <v>6.5</v>
@@ -19856,7 +19865,7 @@
         <v>149</v>
       </c>
       <c r="P91" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="Q91">
         <v>4.7</v>
@@ -19937,7 +19946,7 @@
         <v>0.82</v>
       </c>
       <c r="AQ91">
-        <v>1.5</v>
+        <v>1.62</v>
       </c>
       <c r="AR91">
         <v>1.11</v>
@@ -20062,7 +20071,7 @@
         <v>88</v>
       </c>
       <c r="P92" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="Q92">
         <v>3.8</v>
@@ -20140,7 +20149,7 @@
         <v>0.2</v>
       </c>
       <c r="AP92">
-        <v>0.25</v>
+        <v>0.23</v>
       </c>
       <c r="AQ92">
         <v>1</v>
@@ -20346,10 +20355,10 @@
         <v>1.67</v>
       </c>
       <c r="AP93">
-        <v>1.82</v>
+        <v>1.67</v>
       </c>
       <c r="AQ93">
-        <v>1.27</v>
+        <v>1.25</v>
       </c>
       <c r="AR93">
         <v>1.61</v>
@@ -20474,7 +20483,7 @@
         <v>150</v>
       </c>
       <c r="P94" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="Q94">
         <v>3</v>
@@ -20552,7 +20561,7 @@
         <v>1.5</v>
       </c>
       <c r="AP94">
-        <v>1.18</v>
+        <v>1.33</v>
       </c>
       <c r="AQ94">
         <v>1.45</v>
@@ -21173,7 +21182,7 @@
         <v>2.42</v>
       </c>
       <c r="AQ97">
-        <v>2.09</v>
+        <v>2.17</v>
       </c>
       <c r="AR97">
         <v>1.81</v>
@@ -21916,7 +21925,7 @@
         <v>156</v>
       </c>
       <c r="P101" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="Q101">
         <v>1.83</v>
@@ -21997,7 +22006,7 @@
         <v>2.17</v>
       </c>
       <c r="AQ101">
-        <v>1.5</v>
+        <v>1.62</v>
       </c>
       <c r="AR101">
         <v>1.9</v>
@@ -22200,7 +22209,7 @@
         <v>1.2</v>
       </c>
       <c r="AP102">
-        <v>0.25</v>
+        <v>0.23</v>
       </c>
       <c r="AQ102">
         <v>1</v>
@@ -22409,7 +22418,7 @@
         <v>1.17</v>
       </c>
       <c r="AQ103">
-        <v>0.5</v>
+        <v>0.46</v>
       </c>
       <c r="AR103">
         <v>1.41</v>
@@ -22818,7 +22827,7 @@
         <v>2.6</v>
       </c>
       <c r="AP105">
-        <v>1.64</v>
+        <v>1.58</v>
       </c>
       <c r="AQ105">
         <v>2.42</v>
@@ -23233,7 +23242,7 @@
         <v>0.82</v>
       </c>
       <c r="AQ107">
-        <v>1.27</v>
+        <v>1.25</v>
       </c>
       <c r="AR107">
         <v>1.14</v>
@@ -23564,7 +23573,7 @@
         <v>161</v>
       </c>
       <c r="P109" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="Q109">
         <v>2.24</v>
@@ -23642,7 +23651,7 @@
         <v>0</v>
       </c>
       <c r="AP109">
-        <v>1.18</v>
+        <v>1.33</v>
       </c>
       <c r="AQ109">
         <v>0.09</v>
@@ -23770,7 +23779,7 @@
         <v>162</v>
       </c>
       <c r="P110" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="Q110">
         <v>4.6</v>
@@ -23851,7 +23860,7 @@
         <v>1.73</v>
       </c>
       <c r="AQ110">
-        <v>2.09</v>
+        <v>2.17</v>
       </c>
       <c r="AR110">
         <v>1.51</v>
@@ -24182,7 +24191,7 @@
         <v>164</v>
       </c>
       <c r="P112" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="Q112">
         <v>1.44</v>
@@ -24388,7 +24397,7 @@
         <v>165</v>
       </c>
       <c r="P113" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="Q113">
         <v>3.25</v>
@@ -24469,7 +24478,7 @@
         <v>2.08</v>
       </c>
       <c r="AQ113">
-        <v>1.5</v>
+        <v>1.62</v>
       </c>
       <c r="AR113">
         <v>1.63</v>
@@ -24594,7 +24603,7 @@
         <v>151</v>
       </c>
       <c r="P114" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="Q114">
         <v>2.88</v>
@@ -24800,7 +24809,7 @@
         <v>99</v>
       </c>
       <c r="P115" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="Q115">
         <v>1.73</v>
@@ -25006,7 +25015,7 @@
         <v>88</v>
       </c>
       <c r="P116" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="Q116">
         <v>4.33</v>
@@ -25084,7 +25093,7 @@
         <v>1.57</v>
       </c>
       <c r="AP116">
-        <v>1.64</v>
+        <v>1.58</v>
       </c>
       <c r="AQ116">
         <v>1.82</v>
@@ -25499,7 +25508,7 @@
         <v>1.33</v>
       </c>
       <c r="AQ118">
-        <v>0.5</v>
+        <v>0.46</v>
       </c>
       <c r="AR118">
         <v>1.64</v>
@@ -25624,7 +25633,7 @@
         <v>88</v>
       </c>
       <c r="P119" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="Q119">
         <v>15</v>
@@ -25702,7 +25711,7 @@
         <v>2.33</v>
       </c>
       <c r="AP119">
-        <v>0.25</v>
+        <v>0.23</v>
       </c>
       <c r="AQ119">
         <v>2.42</v>
@@ -25830,7 +25839,7 @@
         <v>168</v>
       </c>
       <c r="P120" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="Q120">
         <v>3</v>
@@ -25908,7 +25917,7 @@
         <v>1.17</v>
       </c>
       <c r="AP120">
-        <v>1.82</v>
+        <v>1.67</v>
       </c>
       <c r="AQ120">
         <v>1</v>
@@ -26114,7 +26123,7 @@
         <v>1.17</v>
       </c>
       <c r="AP121">
-        <v>1.82</v>
+        <v>1.67</v>
       </c>
       <c r="AQ121">
         <v>1</v>
@@ -26242,7 +26251,7 @@
         <v>170</v>
       </c>
       <c r="P122" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="Q122">
         <v>3.25</v>
@@ -26526,7 +26535,7 @@
         <v>1.14</v>
       </c>
       <c r="AP123">
-        <v>1.18</v>
+        <v>1.33</v>
       </c>
       <c r="AQ123">
         <v>1.25</v>
@@ -26654,7 +26663,7 @@
         <v>172</v>
       </c>
       <c r="P124" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="Q124">
         <v>1.83</v>
@@ -26860,7 +26869,7 @@
         <v>171</v>
       </c>
       <c r="P125" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="Q125">
         <v>6.3</v>
@@ -26941,7 +26950,7 @@
         <v>0.91</v>
       </c>
       <c r="AQ125">
-        <v>2.09</v>
+        <v>2.17</v>
       </c>
       <c r="AR125">
         <v>1.21</v>
@@ -27684,7 +27693,7 @@
         <v>174</v>
       </c>
       <c r="P129" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="Q129">
         <v>2.1</v>
@@ -27765,7 +27774,7 @@
         <v>2.42</v>
       </c>
       <c r="AQ129">
-        <v>1.27</v>
+        <v>1.25</v>
       </c>
       <c r="AR129">
         <v>1.69</v>
@@ -27890,7 +27899,7 @@
         <v>175</v>
       </c>
       <c r="P130" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="Q130">
         <v>1.5</v>
@@ -28096,7 +28105,7 @@
         <v>176</v>
       </c>
       <c r="P131" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="Q131">
         <v>3.5</v>
@@ -28302,7 +28311,7 @@
         <v>177</v>
       </c>
       <c r="P132" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="Q132">
         <v>4.04</v>
@@ -28714,7 +28723,7 @@
         <v>88</v>
       </c>
       <c r="P134" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="Q134">
         <v>2.75</v>
@@ -29126,7 +29135,7 @@
         <v>88</v>
       </c>
       <c r="P136" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="Q136">
         <v>4.5</v>
@@ -29538,7 +29547,7 @@
         <v>91</v>
       </c>
       <c r="P138" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="Q138">
         <v>2.25</v>
@@ -29619,7 +29628,7 @@
         <v>1.36</v>
       </c>
       <c r="AQ138">
-        <v>0.5</v>
+        <v>0.46</v>
       </c>
       <c r="AR138">
         <v>1.11</v>
@@ -29744,7 +29753,7 @@
         <v>179</v>
       </c>
       <c r="P139" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="Q139">
         <v>1.9</v>
@@ -30156,7 +30165,7 @@
         <v>88</v>
       </c>
       <c r="P141" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="Q141">
         <v>4</v>
@@ -30234,7 +30243,7 @@
         <v>1.13</v>
       </c>
       <c r="AP141">
-        <v>0.25</v>
+        <v>0.23</v>
       </c>
       <c r="AQ141">
         <v>1.25</v>
@@ -30362,7 +30371,7 @@
         <v>117</v>
       </c>
       <c r="P142" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="Q142">
         <v>4</v>
@@ -30774,7 +30783,7 @@
         <v>182</v>
       </c>
       <c r="P144" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="Q144">
         <v>6</v>
@@ -30852,7 +30861,7 @@
         <v>2.5</v>
       </c>
       <c r="AP144">
-        <v>1.82</v>
+        <v>1.67</v>
       </c>
       <c r="AQ144">
         <v>2.42</v>
@@ -30980,7 +30989,7 @@
         <v>88</v>
       </c>
       <c r="P145" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="Q145">
         <v>3.5</v>
@@ -31058,10 +31067,10 @@
         <v>1.33</v>
       </c>
       <c r="AP145">
-        <v>1.64</v>
+        <v>1.58</v>
       </c>
       <c r="AQ145">
-        <v>1.5</v>
+        <v>1.62</v>
       </c>
       <c r="AR145">
         <v>1.32</v>
@@ -31186,7 +31195,7 @@
         <v>183</v>
       </c>
       <c r="P146" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="Q146">
         <v>4.33</v>
@@ -31392,7 +31401,7 @@
         <v>184</v>
       </c>
       <c r="P147" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="Q147">
         <v>3.8</v>
@@ -31598,7 +31607,7 @@
         <v>185</v>
       </c>
       <c r="P148" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="Q148">
         <v>2.5</v>
@@ -31804,7 +31813,7 @@
         <v>186</v>
       </c>
       <c r="P149" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="Q149">
         <v>2.05</v>
@@ -32010,7 +32019,7 @@
         <v>187</v>
       </c>
       <c r="P150" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="Q150">
         <v>1.95</v>
@@ -32091,7 +32100,7 @@
         <v>2.17</v>
       </c>
       <c r="AQ150">
-        <v>1.27</v>
+        <v>1.25</v>
       </c>
       <c r="AR150">
         <v>1.98</v>
@@ -32216,7 +32225,7 @@
         <v>188</v>
       </c>
       <c r="P151" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="Q151">
         <v>2.48</v>
@@ -32500,7 +32509,7 @@
         <v>2.56</v>
       </c>
       <c r="AP152">
-        <v>1.18</v>
+        <v>1.33</v>
       </c>
       <c r="AQ152">
         <v>2.42</v>
@@ -32628,7 +32637,7 @@
         <v>190</v>
       </c>
       <c r="P153" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="Q153">
         <v>1.4</v>
@@ -33040,7 +33049,7 @@
         <v>88</v>
       </c>
       <c r="P155" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="Q155">
         <v>3.2</v>
@@ -33121,7 +33130,7 @@
         <v>1.45</v>
       </c>
       <c r="AQ155">
-        <v>1.5</v>
+        <v>1.62</v>
       </c>
       <c r="AR155">
         <v>1.51</v>
@@ -33324,7 +33333,7 @@
         <v>0.22</v>
       </c>
       <c r="AP156">
-        <v>0.25</v>
+        <v>0.23</v>
       </c>
       <c r="AQ156">
         <v>0.36</v>
@@ -33530,10 +33539,10 @@
         <v>0.6</v>
       </c>
       <c r="AP157">
-        <v>1.64</v>
+        <v>1.58</v>
       </c>
       <c r="AQ157">
-        <v>0.5</v>
+        <v>0.46</v>
       </c>
       <c r="AR157">
         <v>1.43</v>
@@ -33658,7 +33667,7 @@
         <v>88</v>
       </c>
       <c r="P158" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="Q158">
         <v>5</v>
@@ -33739,7 +33748,7 @@
         <v>1.36</v>
       </c>
       <c r="AQ158">
-        <v>2.09</v>
+        <v>2.17</v>
       </c>
       <c r="AR158">
         <v>1.21</v>
@@ -33864,7 +33873,7 @@
         <v>88</v>
       </c>
       <c r="P159" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="Q159">
         <v>2.38</v>
@@ -34276,7 +34285,7 @@
         <v>193</v>
       </c>
       <c r="P161" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="Q161">
         <v>4.75</v>
@@ -34354,7 +34363,7 @@
         <v>1.89</v>
       </c>
       <c r="AP161">
-        <v>1.82</v>
+        <v>1.67</v>
       </c>
       <c r="AQ161">
         <v>1.82</v>
@@ -34482,7 +34491,7 @@
         <v>194</v>
       </c>
       <c r="P162" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="Q162">
         <v>2.63</v>
@@ -34688,7 +34697,7 @@
         <v>88</v>
       </c>
       <c r="P163" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="Q163">
         <v>11</v>
@@ -34894,7 +34903,7 @@
         <v>195</v>
       </c>
       <c r="P164" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="Q164">
         <v>2</v>
@@ -35100,7 +35109,7 @@
         <v>196</v>
       </c>
       <c r="P165" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="Q165">
         <v>2.5</v>
@@ -36002,10 +36011,10 @@
         <v>0.55</v>
       </c>
       <c r="AP169">
-        <v>1.82</v>
+        <v>1.67</v>
       </c>
       <c r="AQ169">
-        <v>0.5</v>
+        <v>0.46</v>
       </c>
       <c r="AR169">
         <v>1.54</v>
@@ -36336,7 +36345,7 @@
         <v>201</v>
       </c>
       <c r="P171" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="Q171">
         <v>5.2</v>
@@ -36414,10 +36423,10 @@
         <v>1.1</v>
       </c>
       <c r="AP171">
-        <v>0.25</v>
+        <v>0.23</v>
       </c>
       <c r="AQ171">
-        <v>1.27</v>
+        <v>1.25</v>
       </c>
       <c r="AR171">
         <v>1.3</v>
@@ -36542,7 +36551,7 @@
         <v>202</v>
       </c>
       <c r="P172" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="Q172">
         <v>6.35</v>
@@ -36623,7 +36632,7 @@
         <v>1.33</v>
       </c>
       <c r="AQ172">
-        <v>2.09</v>
+        <v>2.17</v>
       </c>
       <c r="AR172">
         <v>1.5</v>
@@ -36748,7 +36757,7 @@
         <v>203</v>
       </c>
       <c r="P173" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="Q173">
         <v>2.6</v>
@@ -36826,7 +36835,7 @@
         <v>1.5</v>
       </c>
       <c r="AP173">
-        <v>1.64</v>
+        <v>1.58</v>
       </c>
       <c r="AQ173">
         <v>1.45</v>
@@ -36954,7 +36963,7 @@
         <v>88</v>
       </c>
       <c r="P174" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="Q174">
         <v>4.86</v>
@@ -37032,7 +37041,7 @@
         <v>1.7</v>
       </c>
       <c r="AP174">
-        <v>1.18</v>
+        <v>1.33</v>
       </c>
       <c r="AQ174">
         <v>1.82</v>
@@ -37160,7 +37169,7 @@
         <v>204</v>
       </c>
       <c r="P175" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="Q175">
         <v>2.66</v>
@@ -37447,7 +37456,7 @@
         <v>3</v>
       </c>
       <c r="AQ176">
-        <v>1.5</v>
+        <v>1.62</v>
       </c>
       <c r="AR176">
         <v>2.32</v>
@@ -37572,7 +37581,7 @@
         <v>171</v>
       </c>
       <c r="P177" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="Q177">
         <v>3.63</v>
@@ -37984,7 +37993,7 @@
         <v>88</v>
       </c>
       <c r="P179" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="Q179">
         <v>3.92</v>
@@ -38190,7 +38199,7 @@
         <v>206</v>
       </c>
       <c r="P180" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="Q180">
         <v>1.32</v>
@@ -38808,7 +38817,7 @@
         <v>208</v>
       </c>
       <c r="P183" t="s">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="Q183">
         <v>4.3</v>
@@ -38965,6 +38974,830 @@
       </c>
       <c r="BP183">
         <v>1.33</v>
+      </c>
+    </row>
+    <row r="184" spans="1:68">
+      <c r="A184" s="1">
+        <v>183</v>
+      </c>
+      <c r="B184">
+        <v>7468274</v>
+      </c>
+      <c r="C184" t="s">
+        <v>68</v>
+      </c>
+      <c r="D184" t="s">
+        <v>69</v>
+      </c>
+      <c r="E184" s="2">
+        <v>45717.39583333334</v>
+      </c>
+      <c r="F184">
+        <v>24</v>
+      </c>
+      <c r="G184" t="s">
+        <v>72</v>
+      </c>
+      <c r="H184" t="s">
+        <v>83</v>
+      </c>
+      <c r="I184">
+        <v>0</v>
+      </c>
+      <c r="J184">
+        <v>2</v>
+      </c>
+      <c r="K184">
+        <v>2</v>
+      </c>
+      <c r="L184">
+        <v>0</v>
+      </c>
+      <c r="M184">
+        <v>4</v>
+      </c>
+      <c r="N184">
+        <v>4</v>
+      </c>
+      <c r="O184" t="s">
+        <v>88</v>
+      </c>
+      <c r="P184" t="s">
+        <v>298</v>
+      </c>
+      <c r="Q184">
+        <v>5.8</v>
+      </c>
+      <c r="R184">
+        <v>2.6</v>
+      </c>
+      <c r="S184">
+        <v>1.89</v>
+      </c>
+      <c r="T184">
+        <v>1.26</v>
+      </c>
+      <c r="U184">
+        <v>3.55</v>
+      </c>
+      <c r="V184">
+        <v>2.19</v>
+      </c>
+      <c r="W184">
+        <v>1.61</v>
+      </c>
+      <c r="X184">
+        <v>4.75</v>
+      </c>
+      <c r="Y184">
+        <v>1.15</v>
+      </c>
+      <c r="Z184">
+        <v>5.6</v>
+      </c>
+      <c r="AA184">
+        <v>4.3</v>
+      </c>
+      <c r="AB184">
+        <v>1.45</v>
+      </c>
+      <c r="AC184">
+        <v>1.01</v>
+      </c>
+      <c r="AD184">
+        <v>13</v>
+      </c>
+      <c r="AE184">
+        <v>1.17</v>
+      </c>
+      <c r="AF184">
+        <v>4.6</v>
+      </c>
+      <c r="AG184">
+        <v>1.54</v>
+      </c>
+      <c r="AH184">
+        <v>2.38</v>
+      </c>
+      <c r="AI184">
+        <v>1.68</v>
+      </c>
+      <c r="AJ184">
+        <v>2.06</v>
+      </c>
+      <c r="AK184">
+        <v>2.55</v>
+      </c>
+      <c r="AL184">
+        <v>1.17</v>
+      </c>
+      <c r="AM184">
+        <v>1.13</v>
+      </c>
+      <c r="AN184">
+        <v>0.25</v>
+      </c>
+      <c r="AO184">
+        <v>1.5</v>
+      </c>
+      <c r="AP184">
+        <v>0.23</v>
+      </c>
+      <c r="AQ184">
+        <v>1.62</v>
+      </c>
+      <c r="AR184">
+        <v>1.24</v>
+      </c>
+      <c r="AS184">
+        <v>1.65</v>
+      </c>
+      <c r="AT184">
+        <v>2.89</v>
+      </c>
+      <c r="AU184">
+        <v>2</v>
+      </c>
+      <c r="AV184">
+        <v>12</v>
+      </c>
+      <c r="AW184">
+        <v>5</v>
+      </c>
+      <c r="AX184">
+        <v>10</v>
+      </c>
+      <c r="AY184">
+        <v>7</v>
+      </c>
+      <c r="AZ184">
+        <v>22</v>
+      </c>
+      <c r="BA184">
+        <v>2</v>
+      </c>
+      <c r="BB184">
+        <v>16</v>
+      </c>
+      <c r="BC184">
+        <v>18</v>
+      </c>
+      <c r="BD184">
+        <v>3.3</v>
+      </c>
+      <c r="BE184">
+        <v>7.5</v>
+      </c>
+      <c r="BF184">
+        <v>1.38</v>
+      </c>
+      <c r="BG184">
+        <v>1.17</v>
+      </c>
+      <c r="BH184">
+        <v>4.35</v>
+      </c>
+      <c r="BI184">
+        <v>1.3</v>
+      </c>
+      <c r="BJ184">
+        <v>3.15</v>
+      </c>
+      <c r="BK184">
+        <v>1.49</v>
+      </c>
+      <c r="BL184">
+        <v>2.4</v>
+      </c>
+      <c r="BM184">
+        <v>1.78</v>
+      </c>
+      <c r="BN184">
+        <v>1.92</v>
+      </c>
+      <c r="BO184">
+        <v>2.17</v>
+      </c>
+      <c r="BP184">
+        <v>1.6</v>
+      </c>
+    </row>
+    <row r="185" spans="1:68">
+      <c r="A185" s="1">
+        <v>184</v>
+      </c>
+      <c r="B185">
+        <v>7468276</v>
+      </c>
+      <c r="C185" t="s">
+        <v>68</v>
+      </c>
+      <c r="D185" t="s">
+        <v>69</v>
+      </c>
+      <c r="E185" s="2">
+        <v>45717.5</v>
+      </c>
+      <c r="F185">
+        <v>24</v>
+      </c>
+      <c r="G185" t="s">
+        <v>77</v>
+      </c>
+      <c r="H185" t="s">
+        <v>71</v>
+      </c>
+      <c r="I185">
+        <v>0</v>
+      </c>
+      <c r="J185">
+        <v>1</v>
+      </c>
+      <c r="K185">
+        <v>1</v>
+      </c>
+      <c r="L185">
+        <v>1</v>
+      </c>
+      <c r="M185">
+        <v>1</v>
+      </c>
+      <c r="N185">
+        <v>2</v>
+      </c>
+      <c r="O185" t="s">
+        <v>150</v>
+      </c>
+      <c r="P185" t="s">
+        <v>182</v>
+      </c>
+      <c r="Q185">
+        <v>3.14</v>
+      </c>
+      <c r="R185">
+        <v>2.19</v>
+      </c>
+      <c r="S185">
+        <v>3.49</v>
+      </c>
+      <c r="T185">
+        <v>1.4</v>
+      </c>
+      <c r="U185">
+        <v>2.92</v>
+      </c>
+      <c r="V185">
+        <v>2.99</v>
+      </c>
+      <c r="W185">
+        <v>1.38</v>
+      </c>
+      <c r="X185">
+        <v>7.8</v>
+      </c>
+      <c r="Y185">
+        <v>1.03</v>
+      </c>
+      <c r="Z185">
+        <v>2.44</v>
+      </c>
+      <c r="AA185">
+        <v>2.95</v>
+      </c>
+      <c r="AB185">
+        <v>2.8</v>
+      </c>
+      <c r="AC185">
+        <v>1</v>
+      </c>
+      <c r="AD185">
+        <v>9.300000000000001</v>
+      </c>
+      <c r="AE185">
+        <v>1.31</v>
+      </c>
+      <c r="AF185">
+        <v>3.1</v>
+      </c>
+      <c r="AG185">
+        <v>1.99</v>
+      </c>
+      <c r="AH185">
+        <v>1.76</v>
+      </c>
+      <c r="AI185">
+        <v>1.74</v>
+      </c>
+      <c r="AJ185">
+        <v>1.99</v>
+      </c>
+      <c r="AK185">
+        <v>1.4</v>
+      </c>
+      <c r="AL185">
+        <v>1.32</v>
+      </c>
+      <c r="AM185">
+        <v>1.5</v>
+      </c>
+      <c r="AN185">
+        <v>1.64</v>
+      </c>
+      <c r="AO185">
+        <v>1.27</v>
+      </c>
+      <c r="AP185">
+        <v>1.58</v>
+      </c>
+      <c r="AQ185">
+        <v>1.25</v>
+      </c>
+      <c r="AR185">
+        <v>1.46</v>
+      </c>
+      <c r="AS185">
+        <v>1.36</v>
+      </c>
+      <c r="AT185">
+        <v>2.82</v>
+      </c>
+      <c r="AU185">
+        <v>4</v>
+      </c>
+      <c r="AV185">
+        <v>6</v>
+      </c>
+      <c r="AW185">
+        <v>7</v>
+      </c>
+      <c r="AX185">
+        <v>14</v>
+      </c>
+      <c r="AY185">
+        <v>11</v>
+      </c>
+      <c r="AZ185">
+        <v>20</v>
+      </c>
+      <c r="BA185">
+        <v>3</v>
+      </c>
+      <c r="BB185">
+        <v>3</v>
+      </c>
+      <c r="BC185">
+        <v>6</v>
+      </c>
+      <c r="BD185">
+        <v>1.9</v>
+      </c>
+      <c r="BE185">
+        <v>6.5</v>
+      </c>
+      <c r="BF185">
+        <v>2.07</v>
+      </c>
+      <c r="BG185">
+        <v>1.26</v>
+      </c>
+      <c r="BH185">
+        <v>3.4</v>
+      </c>
+      <c r="BI185">
+        <v>1.46</v>
+      </c>
+      <c r="BJ185">
+        <v>2.48</v>
+      </c>
+      <c r="BK185">
+        <v>1.74</v>
+      </c>
+      <c r="BL185">
+        <v>1.98</v>
+      </c>
+      <c r="BM185">
+        <v>2.15</v>
+      </c>
+      <c r="BN185">
+        <v>1.61</v>
+      </c>
+      <c r="BO185">
+        <v>2.7</v>
+      </c>
+      <c r="BP185">
+        <v>1.4</v>
+      </c>
+    </row>
+    <row r="186" spans="1:68">
+      <c r="A186" s="1">
+        <v>185</v>
+      </c>
+      <c r="B186">
+        <v>7468275</v>
+      </c>
+      <c r="C186" t="s">
+        <v>68</v>
+      </c>
+      <c r="D186" t="s">
+        <v>69</v>
+      </c>
+      <c r="E186" s="2">
+        <v>45717.5</v>
+      </c>
+      <c r="F186">
+        <v>24</v>
+      </c>
+      <c r="G186" t="s">
+        <v>85</v>
+      </c>
+      <c r="H186" t="s">
+        <v>70</v>
+      </c>
+      <c r="I186">
+        <v>1</v>
+      </c>
+      <c r="J186">
+        <v>1</v>
+      </c>
+      <c r="K186">
+        <v>2</v>
+      </c>
+      <c r="L186">
+        <v>1</v>
+      </c>
+      <c r="M186">
+        <v>2</v>
+      </c>
+      <c r="N186">
+        <v>3</v>
+      </c>
+      <c r="O186" t="s">
+        <v>96</v>
+      </c>
+      <c r="P186" t="s">
+        <v>299</v>
+      </c>
+      <c r="Q186">
+        <v>4.7</v>
+      </c>
+      <c r="R186">
+        <v>2.44</v>
+      </c>
+      <c r="S186">
+        <v>2.17</v>
+      </c>
+      <c r="T186">
+        <v>1.29</v>
+      </c>
+      <c r="U186">
+        <v>3.3</v>
+      </c>
+      <c r="V186">
+        <v>2.31</v>
+      </c>
+      <c r="W186">
+        <v>1.56</v>
+      </c>
+      <c r="X186">
+        <v>5.15</v>
+      </c>
+      <c r="Y186">
+        <v>1.13</v>
+      </c>
+      <c r="Z186">
+        <v>4.2</v>
+      </c>
+      <c r="AA186">
+        <v>3.7</v>
+      </c>
+      <c r="AB186">
+        <v>1.69</v>
+      </c>
+      <c r="AC186">
+        <v>1.01</v>
+      </c>
+      <c r="AD186">
+        <v>11</v>
+      </c>
+      <c r="AE186">
+        <v>1.19</v>
+      </c>
+      <c r="AF186">
+        <v>4.3</v>
+      </c>
+      <c r="AG186">
+        <v>1.62</v>
+      </c>
+      <c r="AH186">
+        <v>2.22</v>
+      </c>
+      <c r="AI186">
+        <v>1.61</v>
+      </c>
+      <c r="AJ186">
+        <v>2.18</v>
+      </c>
+      <c r="AK186">
+        <v>2.06</v>
+      </c>
+      <c r="AL186">
+        <v>1.23</v>
+      </c>
+      <c r="AM186">
+        <v>1.2</v>
+      </c>
+      <c r="AN186">
+        <v>1.82</v>
+      </c>
+      <c r="AO186">
+        <v>2.09</v>
+      </c>
+      <c r="AP186">
+        <v>1.67</v>
+      </c>
+      <c r="AQ186">
+        <v>2.17</v>
+      </c>
+      <c r="AR186">
+        <v>1.58</v>
+      </c>
+      <c r="AS186">
+        <v>1.69</v>
+      </c>
+      <c r="AT186">
+        <v>3.27</v>
+      </c>
+      <c r="AU186">
+        <v>3</v>
+      </c>
+      <c r="AV186">
+        <v>6</v>
+      </c>
+      <c r="AW186">
+        <v>7</v>
+      </c>
+      <c r="AX186">
+        <v>6</v>
+      </c>
+      <c r="AY186">
+        <v>10</v>
+      </c>
+      <c r="AZ186">
+        <v>12</v>
+      </c>
+      <c r="BA186">
+        <v>7</v>
+      </c>
+      <c r="BB186">
+        <v>5</v>
+      </c>
+      <c r="BC186">
+        <v>12</v>
+      </c>
+      <c r="BD186">
+        <v>2.8</v>
+      </c>
+      <c r="BE186">
+        <v>7</v>
+      </c>
+      <c r="BF186">
+        <v>1.5</v>
+      </c>
+      <c r="BG186">
+        <v>1.24</v>
+      </c>
+      <c r="BH186">
+        <v>3.55</v>
+      </c>
+      <c r="BI186">
+        <v>1.42</v>
+      </c>
+      <c r="BJ186">
+        <v>2.63</v>
+      </c>
+      <c r="BK186">
+        <v>1.68</v>
+      </c>
+      <c r="BL186">
+        <v>2.05</v>
+      </c>
+      <c r="BM186">
+        <v>2.05</v>
+      </c>
+      <c r="BN186">
+        <v>1.68</v>
+      </c>
+      <c r="BO186">
+        <v>2.55</v>
+      </c>
+      <c r="BP186">
+        <v>1.44</v>
+      </c>
+    </row>
+    <row r="187" spans="1:68">
+      <c r="A187" s="1">
+        <v>186</v>
+      </c>
+      <c r="B187">
+        <v>7468271</v>
+      </c>
+      <c r="C187" t="s">
+        <v>68</v>
+      </c>
+      <c r="D187" t="s">
+        <v>69</v>
+      </c>
+      <c r="E187" s="2">
+        <v>45717.625</v>
+      </c>
+      <c r="F187">
+        <v>24</v>
+      </c>
+      <c r="G187" t="s">
+        <v>78</v>
+      </c>
+      <c r="H187" t="s">
+        <v>79</v>
+      </c>
+      <c r="I187">
+        <v>1</v>
+      </c>
+      <c r="J187">
+        <v>0</v>
+      </c>
+      <c r="K187">
+        <v>1</v>
+      </c>
+      <c r="L187">
+        <v>2</v>
+      </c>
+      <c r="M187">
+        <v>0</v>
+      </c>
+      <c r="N187">
+        <v>2</v>
+      </c>
+      <c r="O187" t="s">
+        <v>209</v>
+      </c>
+      <c r="P187" t="s">
+        <v>88</v>
+      </c>
+      <c r="Q187">
+        <v>2.12</v>
+      </c>
+      <c r="R187">
+        <v>2.29</v>
+      </c>
+      <c r="S187">
+        <v>5.8</v>
+      </c>
+      <c r="T187">
+        <v>1.38</v>
+      </c>
+      <c r="U187">
+        <v>2.85</v>
+      </c>
+      <c r="V187">
+        <v>2.7</v>
+      </c>
+      <c r="W187">
+        <v>1.41</v>
+      </c>
+      <c r="X187">
+        <v>6.3</v>
+      </c>
+      <c r="Y187">
+        <v>1.09</v>
+      </c>
+      <c r="Z187">
+        <v>1.63</v>
+      </c>
+      <c r="AA187">
+        <v>3.35</v>
+      </c>
+      <c r="AB187">
+        <v>5.2</v>
+      </c>
+      <c r="AC187">
+        <v>1.03</v>
+      </c>
+      <c r="AD187">
+        <v>9</v>
+      </c>
+      <c r="AE187">
+        <v>1.3</v>
+      </c>
+      <c r="AF187">
+        <v>3.25</v>
+      </c>
+      <c r="AG187">
+        <v>1.93</v>
+      </c>
+      <c r="AH187">
+        <v>1.81</v>
+      </c>
+      <c r="AI187">
+        <v>1.9</v>
+      </c>
+      <c r="AJ187">
+        <v>1.81</v>
+      </c>
+      <c r="AK187">
+        <v>1.15</v>
+      </c>
+      <c r="AL187">
+        <v>1.25</v>
+      </c>
+      <c r="AM187">
+        <v>2.14</v>
+      </c>
+      <c r="AN187">
+        <v>1.18</v>
+      </c>
+      <c r="AO187">
+        <v>0.5</v>
+      </c>
+      <c r="AP187">
+        <v>1.33</v>
+      </c>
+      <c r="AQ187">
+        <v>0.46</v>
+      </c>
+      <c r="AR187">
+        <v>1.45</v>
+      </c>
+      <c r="AS187">
+        <v>1.03</v>
+      </c>
+      <c r="AT187">
+        <v>2.48</v>
+      </c>
+      <c r="AU187">
+        <v>7</v>
+      </c>
+      <c r="AV187">
+        <v>2</v>
+      </c>
+      <c r="AW187">
+        <v>5</v>
+      </c>
+      <c r="AX187">
+        <v>4</v>
+      </c>
+      <c r="AY187">
+        <v>12</v>
+      </c>
+      <c r="AZ187">
+        <v>6</v>
+      </c>
+      <c r="BA187">
+        <v>4</v>
+      </c>
+      <c r="BB187">
+        <v>1</v>
+      </c>
+      <c r="BC187">
+        <v>5</v>
+      </c>
+      <c r="BD187">
+        <v>1.47</v>
+      </c>
+      <c r="BE187">
+        <v>6.75</v>
+      </c>
+      <c r="BF187">
+        <v>3.05</v>
+      </c>
+      <c r="BG187">
+        <v>1.29</v>
+      </c>
+      <c r="BH187">
+        <v>3.15</v>
+      </c>
+      <c r="BI187">
+        <v>1.5</v>
+      </c>
+      <c r="BJ187">
+        <v>2.38</v>
+      </c>
+      <c r="BK187">
+        <v>1.81</v>
+      </c>
+      <c r="BL187">
+        <v>1.88</v>
+      </c>
+      <c r="BM187">
+        <v>2.28</v>
+      </c>
+      <c r="BN187">
+        <v>1.55</v>
+      </c>
+      <c r="BO187">
+        <v>2.9</v>
+      </c>
+      <c r="BP187">
+        <v>1.34</v>
       </c>
     </row>
   </sheetData>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Czech Republic First League_20242025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Czech Republic First League_20242025.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1184" uniqueCount="300">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1190" uniqueCount="300">
   <si>
     <t>Id_Jogo</t>
   </si>
@@ -646,6 +646,9 @@
     <t>['37', '57']</t>
   </si>
   <si>
+    <t>['29']</t>
+  </si>
+  <si>
     <t>['25']</t>
   </si>
   <si>
@@ -836,9 +839,6 @@
   </si>
   <si>
     <t>['12', '16', '51']</t>
-  </si>
-  <si>
-    <t>['29']</t>
   </si>
   <si>
     <t>['60', '65', '68', '90+3']</t>
@@ -1275,7 +1275,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:BP187"/>
+  <dimension ref="A1:BP188"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:68">
@@ -1531,7 +1531,7 @@
         <v>86</v>
       </c>
       <c r="P2" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="Q2">
         <v>1.53</v>
@@ -1943,7 +1943,7 @@
         <v>88</v>
       </c>
       <c r="P4" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="Q4">
         <v>2.88</v>
@@ -2355,7 +2355,7 @@
         <v>90</v>
       </c>
       <c r="P6" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="Q6">
         <v>5.5</v>
@@ -2561,7 +2561,7 @@
         <v>91</v>
       </c>
       <c r="P7" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="Q7">
         <v>3.2</v>
@@ -3385,7 +3385,7 @@
         <v>94</v>
       </c>
       <c r="P11" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="Q11">
         <v>6.5</v>
@@ -3591,7 +3591,7 @@
         <v>88</v>
       </c>
       <c r="P12" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="Q12">
         <v>2.85</v>
@@ -4003,7 +4003,7 @@
         <v>96</v>
       </c>
       <c r="P14" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="Q14">
         <v>2.45</v>
@@ -4081,7 +4081,7 @@
         <v>3</v>
       </c>
       <c r="AP14">
-        <v>1.45</v>
+        <v>1.42</v>
       </c>
       <c r="AQ14">
         <v>1.25</v>
@@ -4827,7 +4827,7 @@
         <v>88</v>
       </c>
       <c r="P18" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="Q18">
         <v>5.4</v>
@@ -4905,7 +4905,7 @@
         <v>1</v>
       </c>
       <c r="AP18">
-        <v>1.45</v>
+        <v>1.42</v>
       </c>
       <c r="AQ18">
         <v>2.42</v>
@@ -5114,7 +5114,7 @@
         <v>2.17</v>
       </c>
       <c r="AQ19">
-        <v>0.36</v>
+        <v>0.42</v>
       </c>
       <c r="AR19">
         <v>1.9</v>
@@ -5857,7 +5857,7 @@
         <v>102</v>
       </c>
       <c r="P23" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="Q23">
         <v>2.6</v>
@@ -6063,7 +6063,7 @@
         <v>103</v>
       </c>
       <c r="P24" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="Q24">
         <v>2.75</v>
@@ -6269,7 +6269,7 @@
         <v>88</v>
       </c>
       <c r="P25" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="Q25">
         <v>1.06</v>
@@ -6475,7 +6475,7 @@
         <v>104</v>
       </c>
       <c r="P26" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="Q26">
         <v>6.23</v>
@@ -7998,7 +7998,7 @@
         <v>1.58</v>
       </c>
       <c r="AQ33">
-        <v>0.36</v>
+        <v>0.42</v>
       </c>
       <c r="AR33">
         <v>1.08</v>
@@ -8123,7 +8123,7 @@
         <v>111</v>
       </c>
       <c r="P34" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="Q34">
         <v>1.45</v>
@@ -8329,7 +8329,7 @@
         <v>112</v>
       </c>
       <c r="P35" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="Q35">
         <v>2.84</v>
@@ -8535,7 +8535,7 @@
         <v>113</v>
       </c>
       <c r="P36" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="Q36">
         <v>5.63</v>
@@ -8741,7 +8741,7 @@
         <v>114</v>
       </c>
       <c r="P37" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="Q37">
         <v>2.58</v>
@@ -9025,7 +9025,7 @@
         <v>1.5</v>
       </c>
       <c r="AP38">
-        <v>1.45</v>
+        <v>1.42</v>
       </c>
       <c r="AQ38">
         <v>0.46</v>
@@ -9153,7 +9153,7 @@
         <v>88</v>
       </c>
       <c r="P39" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="Q39">
         <v>4.75</v>
@@ -9565,7 +9565,7 @@
         <v>117</v>
       </c>
       <c r="P41" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="Q41">
         <v>2.4</v>
@@ -9771,7 +9771,7 @@
         <v>107</v>
       </c>
       <c r="P42" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="Q42">
         <v>2.61</v>
@@ -9977,7 +9977,7 @@
         <v>118</v>
       </c>
       <c r="P43" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="Q43">
         <v>1.69</v>
@@ -11419,7 +11419,7 @@
         <v>88</v>
       </c>
       <c r="P50" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="Q50">
         <v>5.1</v>
@@ -11706,7 +11706,7 @@
         <v>1.33</v>
       </c>
       <c r="AQ51">
-        <v>0.36</v>
+        <v>0.42</v>
       </c>
       <c r="AR51">
         <v>1.76</v>
@@ -11831,7 +11831,7 @@
         <v>122</v>
       </c>
       <c r="P52" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="Q52">
         <v>3</v>
@@ -12243,7 +12243,7 @@
         <v>124</v>
       </c>
       <c r="P54" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="Q54">
         <v>3</v>
@@ -12527,7 +12527,7 @@
         <v>2.33</v>
       </c>
       <c r="AP55">
-        <v>1.45</v>
+        <v>1.42</v>
       </c>
       <c r="AQ55">
         <v>1.82</v>
@@ -12655,7 +12655,7 @@
         <v>125</v>
       </c>
       <c r="P56" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="Q56">
         <v>1.85</v>
@@ -12861,7 +12861,7 @@
         <v>88</v>
       </c>
       <c r="P57" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="Q57">
         <v>5.88</v>
@@ -13273,7 +13273,7 @@
         <v>127</v>
       </c>
       <c r="P59" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="Q59">
         <v>3.86</v>
@@ -13891,7 +13891,7 @@
         <v>130</v>
       </c>
       <c r="P62" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="Q62">
         <v>1.83</v>
@@ -14097,7 +14097,7 @@
         <v>88</v>
       </c>
       <c r="P63" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="Q63">
         <v>8.77</v>
@@ -14384,7 +14384,7 @@
         <v>1.67</v>
       </c>
       <c r="AQ64">
-        <v>0.36</v>
+        <v>0.42</v>
       </c>
       <c r="AR64">
         <v>1.75</v>
@@ -14509,7 +14509,7 @@
         <v>132</v>
       </c>
       <c r="P65" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="Q65">
         <v>2.4</v>
@@ -14587,7 +14587,7 @@
         <v>1.25</v>
       </c>
       <c r="AP65">
-        <v>1.45</v>
+        <v>1.42</v>
       </c>
       <c r="AQ65">
         <v>1.45</v>
@@ -14715,7 +14715,7 @@
         <v>133</v>
       </c>
       <c r="P66" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="Q66">
         <v>1.55</v>
@@ -14921,7 +14921,7 @@
         <v>134</v>
       </c>
       <c r="P67" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="Q67">
         <v>4</v>
@@ -15127,7 +15127,7 @@
         <v>88</v>
       </c>
       <c r="P68" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="Q68">
         <v>3.1</v>
@@ -15951,7 +15951,7 @@
         <v>124</v>
       </c>
       <c r="P72" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="Q72">
         <v>1.88</v>
@@ -16157,7 +16157,7 @@
         <v>88</v>
       </c>
       <c r="P73" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="Q73">
         <v>7</v>
@@ -16569,7 +16569,7 @@
         <v>138</v>
       </c>
       <c r="P75" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="Q75">
         <v>2.3</v>
@@ -16650,7 +16650,7 @@
         <v>1.33</v>
       </c>
       <c r="AQ75">
-        <v>0.36</v>
+        <v>0.42</v>
       </c>
       <c r="AR75">
         <v>1.49</v>
@@ -16775,7 +16775,7 @@
         <v>88</v>
       </c>
       <c r="P76" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="Q76">
         <v>3.7</v>
@@ -16981,7 +16981,7 @@
         <v>88</v>
       </c>
       <c r="P77" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="Q77">
         <v>2.47</v>
@@ -17059,7 +17059,7 @@
         <v>1.4</v>
       </c>
       <c r="AP77">
-        <v>1.45</v>
+        <v>1.42</v>
       </c>
       <c r="AQ77">
         <v>1.25</v>
@@ -17599,7 +17599,7 @@
         <v>140</v>
       </c>
       <c r="P80" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="Q80">
         <v>2.5</v>
@@ -17805,7 +17805,7 @@
         <v>141</v>
       </c>
       <c r="P81" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="Q81">
         <v>2.38</v>
@@ -18011,7 +18011,7 @@
         <v>142</v>
       </c>
       <c r="P82" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="Q82">
         <v>2.8</v>
@@ -18217,7 +18217,7 @@
         <v>143</v>
       </c>
       <c r="P83" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="Q83">
         <v>2.6</v>
@@ -18423,7 +18423,7 @@
         <v>144</v>
       </c>
       <c r="P84" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="Q84">
         <v>3.4</v>
@@ -18835,7 +18835,7 @@
         <v>146</v>
       </c>
       <c r="P86" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="Q86">
         <v>2.88</v>
@@ -19247,7 +19247,7 @@
         <v>88</v>
       </c>
       <c r="P88" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="Q88">
         <v>2.6</v>
@@ -19453,7 +19453,7 @@
         <v>93</v>
       </c>
       <c r="P89" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="Q89">
         <v>6.5</v>
@@ -19737,7 +19737,7 @@
         <v>1.4</v>
       </c>
       <c r="AP90">
-        <v>1.45</v>
+        <v>1.42</v>
       </c>
       <c r="AQ90">
         <v>1</v>
@@ -19865,7 +19865,7 @@
         <v>149</v>
       </c>
       <c r="P91" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="Q91">
         <v>4.7</v>
@@ -20071,7 +20071,7 @@
         <v>88</v>
       </c>
       <c r="P92" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="Q92">
         <v>3.8</v>
@@ -20483,7 +20483,7 @@
         <v>150</v>
       </c>
       <c r="P94" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="Q94">
         <v>3</v>
@@ -20976,7 +20976,7 @@
         <v>3</v>
       </c>
       <c r="AQ96">
-        <v>0.36</v>
+        <v>0.42</v>
       </c>
       <c r="AR96">
         <v>2.31</v>
@@ -21925,7 +21925,7 @@
         <v>156</v>
       </c>
       <c r="P101" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="Q101">
         <v>1.83</v>
@@ -23036,7 +23036,7 @@
         <v>2.45</v>
       </c>
       <c r="AQ106">
-        <v>0.36</v>
+        <v>0.42</v>
       </c>
       <c r="AR106">
         <v>1.87</v>
@@ -23445,7 +23445,7 @@
         <v>0.67</v>
       </c>
       <c r="AP108">
-        <v>1.45</v>
+        <v>1.42</v>
       </c>
       <c r="AQ108">
         <v>1</v>
@@ -23573,7 +23573,7 @@
         <v>161</v>
       </c>
       <c r="P109" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="Q109">
         <v>2.24</v>
@@ -23779,7 +23779,7 @@
         <v>162</v>
       </c>
       <c r="P110" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="Q110">
         <v>4.6</v>
@@ -24191,7 +24191,7 @@
         <v>164</v>
       </c>
       <c r="P112" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="Q112">
         <v>1.44</v>
@@ -24397,7 +24397,7 @@
         <v>165</v>
       </c>
       <c r="P113" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="Q113">
         <v>3.25</v>
@@ -24603,7 +24603,7 @@
         <v>151</v>
       </c>
       <c r="P114" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="Q114">
         <v>2.88</v>
@@ -24809,7 +24809,7 @@
         <v>99</v>
       </c>
       <c r="P115" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="Q115">
         <v>1.73</v>
@@ -25015,7 +25015,7 @@
         <v>88</v>
       </c>
       <c r="P116" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="Q116">
         <v>4.33</v>
@@ -25302,7 +25302,7 @@
         <v>1.17</v>
       </c>
       <c r="AQ117">
-        <v>0.36</v>
+        <v>0.42</v>
       </c>
       <c r="AR117">
         <v>1.44</v>
@@ -25633,7 +25633,7 @@
         <v>88</v>
       </c>
       <c r="P119" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="Q119">
         <v>15</v>
@@ -25839,7 +25839,7 @@
         <v>168</v>
       </c>
       <c r="P120" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="Q120">
         <v>3</v>
@@ -26251,7 +26251,7 @@
         <v>170</v>
       </c>
       <c r="P122" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="Q122">
         <v>3.25</v>
@@ -26663,7 +26663,7 @@
         <v>172</v>
       </c>
       <c r="P124" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="Q124">
         <v>1.83</v>
@@ -26869,7 +26869,7 @@
         <v>171</v>
       </c>
       <c r="P125" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="Q125">
         <v>6.3</v>
@@ -27693,7 +27693,7 @@
         <v>174</v>
       </c>
       <c r="P129" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="Q129">
         <v>2.1</v>
@@ -27899,7 +27899,7 @@
         <v>175</v>
       </c>
       <c r="P130" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="Q130">
         <v>1.5</v>
@@ -28105,7 +28105,7 @@
         <v>176</v>
       </c>
       <c r="P131" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="Q131">
         <v>3.5</v>
@@ -28311,7 +28311,7 @@
         <v>177</v>
       </c>
       <c r="P132" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="Q132">
         <v>4.04</v>
@@ -28723,7 +28723,7 @@
         <v>88</v>
       </c>
       <c r="P134" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="Q134">
         <v>2.75</v>
@@ -29135,7 +29135,7 @@
         <v>88</v>
       </c>
       <c r="P136" t="s">
-        <v>274</v>
+        <v>210</v>
       </c>
       <c r="Q136">
         <v>4.5</v>
@@ -29547,7 +29547,7 @@
         <v>91</v>
       </c>
       <c r="P138" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="Q138">
         <v>2.25</v>
@@ -29753,7 +29753,7 @@
         <v>179</v>
       </c>
       <c r="P139" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="Q139">
         <v>1.9</v>
@@ -29834,7 +29834,7 @@
         <v>2.08</v>
       </c>
       <c r="AQ139">
-        <v>0.36</v>
+        <v>0.42</v>
       </c>
       <c r="AR139">
         <v>1.71</v>
@@ -30655,7 +30655,7 @@
         <v>1</v>
       </c>
       <c r="AP143">
-        <v>1.45</v>
+        <v>1.42</v>
       </c>
       <c r="AQ143">
         <v>0.75</v>
@@ -33049,7 +33049,7 @@
         <v>88</v>
       </c>
       <c r="P155" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="Q155">
         <v>3.2</v>
@@ -33127,7 +33127,7 @@
         <v>1.5</v>
       </c>
       <c r="AP155">
-        <v>1.45</v>
+        <v>1.42</v>
       </c>
       <c r="AQ155">
         <v>1.62</v>
@@ -33336,7 +33336,7 @@
         <v>0.23</v>
       </c>
       <c r="AQ156">
-        <v>0.36</v>
+        <v>0.42</v>
       </c>
       <c r="AR156">
         <v>1.34</v>
@@ -33873,7 +33873,7 @@
         <v>88</v>
       </c>
       <c r="P159" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="Q159">
         <v>2.38</v>
@@ -34285,7 +34285,7 @@
         <v>193</v>
       </c>
       <c r="P161" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="Q161">
         <v>4.75</v>
@@ -36220,7 +36220,7 @@
         <v>1.36</v>
       </c>
       <c r="AQ170">
-        <v>0.36</v>
+        <v>0.42</v>
       </c>
       <c r="AR170">
         <v>1.21</v>
@@ -37247,7 +37247,7 @@
         <v>1.2</v>
       </c>
       <c r="AP175">
-        <v>1.45</v>
+        <v>1.42</v>
       </c>
       <c r="AQ175">
         <v>1.25</v>
@@ -39798,6 +39798,212 @@
       </c>
       <c r="BP187">
         <v>1.34</v>
+      </c>
+    </row>
+    <row r="188" spans="1:68">
+      <c r="A188" s="1">
+        <v>187</v>
+      </c>
+      <c r="B188">
+        <v>7468663</v>
+      </c>
+      <c r="C188" t="s">
+        <v>68</v>
+      </c>
+      <c r="D188" t="s">
+        <v>69</v>
+      </c>
+      <c r="E188" s="2">
+        <v>45718.375</v>
+      </c>
+      <c r="F188">
+        <v>24</v>
+      </c>
+      <c r="G188" t="s">
+        <v>81</v>
+      </c>
+      <c r="H188" t="s">
+        <v>74</v>
+      </c>
+      <c r="I188">
+        <v>1</v>
+      </c>
+      <c r="J188">
+        <v>0</v>
+      </c>
+      <c r="K188">
+        <v>1</v>
+      </c>
+      <c r="L188">
+        <v>1</v>
+      </c>
+      <c r="M188">
+        <v>1</v>
+      </c>
+      <c r="N188">
+        <v>2</v>
+      </c>
+      <c r="O188" t="s">
+        <v>210</v>
+      </c>
+      <c r="P188" t="s">
+        <v>102</v>
+      </c>
+      <c r="Q188">
+        <v>2.05</v>
+      </c>
+      <c r="R188">
+        <v>2.3</v>
+      </c>
+      <c r="S188">
+        <v>6.5</v>
+      </c>
+      <c r="T188">
+        <v>1.36</v>
+      </c>
+      <c r="U188">
+        <v>3</v>
+      </c>
+      <c r="V188">
+        <v>2.75</v>
+      </c>
+      <c r="W188">
+        <v>1.4</v>
+      </c>
+      <c r="X188">
+        <v>7</v>
+      </c>
+      <c r="Y188">
+        <v>1.1</v>
+      </c>
+      <c r="Z188">
+        <v>1.45</v>
+      </c>
+      <c r="AA188">
+        <v>4</v>
+      </c>
+      <c r="AB188">
+        <v>8</v>
+      </c>
+      <c r="AC188">
+        <v>1.05</v>
+      </c>
+      <c r="AD188">
+        <v>8.5</v>
+      </c>
+      <c r="AE188">
+        <v>1.28</v>
+      </c>
+      <c r="AF188">
+        <v>3.35</v>
+      </c>
+      <c r="AG188">
+        <v>1.85</v>
+      </c>
+      <c r="AH188">
+        <v>1.95</v>
+      </c>
+      <c r="AI188">
+        <v>1.95</v>
+      </c>
+      <c r="AJ188">
+        <v>1.8</v>
+      </c>
+      <c r="AK188">
+        <v>1.11</v>
+      </c>
+      <c r="AL188">
+        <v>1.21</v>
+      </c>
+      <c r="AM188">
+        <v>2.55</v>
+      </c>
+      <c r="AN188">
+        <v>1.45</v>
+      </c>
+      <c r="AO188">
+        <v>0.36</v>
+      </c>
+      <c r="AP188">
+        <v>1.42</v>
+      </c>
+      <c r="AQ188">
+        <v>0.42</v>
+      </c>
+      <c r="AR188">
+        <v>1.49</v>
+      </c>
+      <c r="AS188">
+        <v>0.91</v>
+      </c>
+      <c r="AT188">
+        <v>2.4</v>
+      </c>
+      <c r="AU188">
+        <v>4</v>
+      </c>
+      <c r="AV188">
+        <v>2</v>
+      </c>
+      <c r="AW188">
+        <v>7</v>
+      </c>
+      <c r="AX188">
+        <v>5</v>
+      </c>
+      <c r="AY188">
+        <v>11</v>
+      </c>
+      <c r="AZ188">
+        <v>7</v>
+      </c>
+      <c r="BA188">
+        <v>6</v>
+      </c>
+      <c r="BB188">
+        <v>3</v>
+      </c>
+      <c r="BC188">
+        <v>9</v>
+      </c>
+      <c r="BD188">
+        <v>1.36</v>
+      </c>
+      <c r="BE188">
+        <v>7</v>
+      </c>
+      <c r="BF188">
+        <v>3.4</v>
+      </c>
+      <c r="BG188">
+        <v>1.24</v>
+      </c>
+      <c r="BH188">
+        <v>3.55</v>
+      </c>
+      <c r="BI188">
+        <v>1.42</v>
+      </c>
+      <c r="BJ188">
+        <v>2.65</v>
+      </c>
+      <c r="BK188">
+        <v>1.68</v>
+      </c>
+      <c r="BL188">
+        <v>2.05</v>
+      </c>
+      <c r="BM188">
+        <v>2.05</v>
+      </c>
+      <c r="BN188">
+        <v>1.68</v>
+      </c>
+      <c r="BO188">
+        <v>2.55</v>
+      </c>
+      <c r="BP188">
+        <v>1.45</v>
       </c>
     </row>
   </sheetData>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Czech Republic First League_20242025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Czech Republic First League_20242025.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1190" uniqueCount="300">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1202" uniqueCount="302">
   <si>
     <t>Id_Jogo</t>
   </si>
@@ -649,6 +649,9 @@
     <t>['29']</t>
   </si>
   <si>
+    <t>['65', '88']</t>
+  </si>
+  <si>
     <t>['25']</t>
   </si>
   <si>
@@ -914,6 +917,9 @@
   </si>
   <si>
     <t>['25', '87']</t>
+  </si>
+  <si>
+    <t>['13', '80']</t>
   </si>
 </sst>
 </file>
@@ -1275,7 +1281,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:BP188"/>
+  <dimension ref="A1:BP190"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:68">
@@ -1531,7 +1537,7 @@
         <v>86</v>
       </c>
       <c r="P2" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="Q2">
         <v>1.53</v>
@@ -1943,7 +1949,7 @@
         <v>88</v>
       </c>
       <c r="P4" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="Q4">
         <v>2.88</v>
@@ -2355,7 +2361,7 @@
         <v>90</v>
       </c>
       <c r="P6" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="Q6">
         <v>5.5</v>
@@ -2436,7 +2442,7 @@
         <v>0.91</v>
       </c>
       <c r="AQ6">
-        <v>1.82</v>
+        <v>1.92</v>
       </c>
       <c r="AR6">
         <v>0</v>
@@ -2561,7 +2567,7 @@
         <v>91</v>
       </c>
       <c r="P7" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="Q7">
         <v>3.2</v>
@@ -2639,7 +2645,7 @@
         <v>0</v>
       </c>
       <c r="AP7">
-        <v>1.33</v>
+        <v>1.46</v>
       </c>
       <c r="AQ7">
         <v>1</v>
@@ -3385,7 +3391,7 @@
         <v>94</v>
       </c>
       <c r="P11" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="Q11">
         <v>6.5</v>
@@ -3591,7 +3597,7 @@
         <v>88</v>
       </c>
       <c r="P12" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="Q12">
         <v>2.85</v>
@@ -4003,7 +4009,7 @@
         <v>96</v>
       </c>
       <c r="P14" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="Q14">
         <v>2.45</v>
@@ -4287,10 +4293,10 @@
         <v>0</v>
       </c>
       <c r="AP15">
-        <v>1.73</v>
+        <v>1.58</v>
       </c>
       <c r="AQ15">
-        <v>1</v>
+        <v>0.92</v>
       </c>
       <c r="AR15">
         <v>0</v>
@@ -4827,7 +4833,7 @@
         <v>88</v>
       </c>
       <c r="P18" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="Q18">
         <v>5.4</v>
@@ -5526,7 +5532,7 @@
         <v>2.08</v>
       </c>
       <c r="AQ21">
-        <v>1.82</v>
+        <v>1.92</v>
       </c>
       <c r="AR21">
         <v>1.81</v>
@@ -5857,7 +5863,7 @@
         <v>102</v>
       </c>
       <c r="P23" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="Q23">
         <v>2.6</v>
@@ -6063,7 +6069,7 @@
         <v>103</v>
       </c>
       <c r="P24" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="Q24">
         <v>2.75</v>
@@ -6269,7 +6275,7 @@
         <v>88</v>
       </c>
       <c r="P25" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="Q25">
         <v>1.06</v>
@@ -6475,7 +6481,7 @@
         <v>104</v>
       </c>
       <c r="P26" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="Q26">
         <v>6.23</v>
@@ -7174,7 +7180,7 @@
         <v>0.82</v>
       </c>
       <c r="AQ29">
-        <v>1</v>
+        <v>0.92</v>
       </c>
       <c r="AR29">
         <v>1.22</v>
@@ -7583,7 +7589,7 @@
         <v>0</v>
       </c>
       <c r="AP31">
-        <v>1.73</v>
+        <v>1.58</v>
       </c>
       <c r="AQ31">
         <v>0.09</v>
@@ -8123,7 +8129,7 @@
         <v>111</v>
       </c>
       <c r="P34" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="Q34">
         <v>1.45</v>
@@ -8329,7 +8335,7 @@
         <v>112</v>
       </c>
       <c r="P35" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="Q35">
         <v>2.84</v>
@@ -8407,7 +8413,7 @@
         <v>0.5</v>
       </c>
       <c r="AP35">
-        <v>1.33</v>
+        <v>1.46</v>
       </c>
       <c r="AQ35">
         <v>1.45</v>
@@ -8535,7 +8541,7 @@
         <v>113</v>
       </c>
       <c r="P36" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="Q36">
         <v>5.63</v>
@@ -8741,7 +8747,7 @@
         <v>114</v>
       </c>
       <c r="P37" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="Q37">
         <v>2.58</v>
@@ -9153,7 +9159,7 @@
         <v>88</v>
       </c>
       <c r="P39" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="Q39">
         <v>4.75</v>
@@ -9234,7 +9240,7 @@
         <v>0.23</v>
       </c>
       <c r="AQ39">
-        <v>1.82</v>
+        <v>1.92</v>
       </c>
       <c r="AR39">
         <v>1.46</v>
@@ -9565,7 +9571,7 @@
         <v>117</v>
       </c>
       <c r="P41" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="Q41">
         <v>2.4</v>
@@ -9771,7 +9777,7 @@
         <v>107</v>
       </c>
       <c r="P42" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="Q42">
         <v>2.61</v>
@@ -9977,7 +9983,7 @@
         <v>118</v>
       </c>
       <c r="P43" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="Q43">
         <v>1.69</v>
@@ -10058,7 +10064,7 @@
         <v>2.17</v>
       </c>
       <c r="AQ43">
-        <v>1</v>
+        <v>0.92</v>
       </c>
       <c r="AR43">
         <v>2.07</v>
@@ -10879,7 +10885,7 @@
         <v>0</v>
       </c>
       <c r="AP47">
-        <v>1.33</v>
+        <v>1.46</v>
       </c>
       <c r="AQ47">
         <v>1.62</v>
@@ -11419,7 +11425,7 @@
         <v>88</v>
       </c>
       <c r="P50" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="Q50">
         <v>5.1</v>
@@ -11703,7 +11709,7 @@
         <v>0</v>
       </c>
       <c r="AP51">
-        <v>1.33</v>
+        <v>1.46</v>
       </c>
       <c r="AQ51">
         <v>0.42</v>
@@ -11831,7 +11837,7 @@
         <v>122</v>
       </c>
       <c r="P52" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="Q52">
         <v>3</v>
@@ -12243,7 +12249,7 @@
         <v>124</v>
       </c>
       <c r="P54" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="Q54">
         <v>3</v>
@@ -12530,7 +12536,7 @@
         <v>1.42</v>
       </c>
       <c r="AQ55">
-        <v>1.82</v>
+        <v>1.92</v>
       </c>
       <c r="AR55">
         <v>1.32</v>
@@ -12655,7 +12661,7 @@
         <v>125</v>
       </c>
       <c r="P56" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="Q56">
         <v>1.85</v>
@@ -12861,7 +12867,7 @@
         <v>88</v>
       </c>
       <c r="P57" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="Q57">
         <v>5.88</v>
@@ -12939,7 +12945,7 @@
         <v>2</v>
       </c>
       <c r="AP57">
-        <v>1.73</v>
+        <v>1.58</v>
       </c>
       <c r="AQ57">
         <v>2.42</v>
@@ -13148,7 +13154,7 @@
         <v>1.58</v>
       </c>
       <c r="AQ58">
-        <v>1</v>
+        <v>0.92</v>
       </c>
       <c r="AR58">
         <v>1.32</v>
@@ -13273,7 +13279,7 @@
         <v>127</v>
       </c>
       <c r="P59" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="Q59">
         <v>3.86</v>
@@ -13557,7 +13563,7 @@
         <v>1.75</v>
       </c>
       <c r="AP60">
-        <v>1.33</v>
+        <v>1.46</v>
       </c>
       <c r="AQ60">
         <v>1.25</v>
@@ -13766,7 +13772,7 @@
         <v>3</v>
       </c>
       <c r="AQ61">
-        <v>1.82</v>
+        <v>1.92</v>
       </c>
       <c r="AR61">
         <v>2.33</v>
@@ -13891,7 +13897,7 @@
         <v>130</v>
       </c>
       <c r="P62" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="Q62">
         <v>1.83</v>
@@ -13969,7 +13975,7 @@
         <v>0.75</v>
       </c>
       <c r="AP62">
-        <v>1.73</v>
+        <v>1.58</v>
       </c>
       <c r="AQ62">
         <v>0.46</v>
@@ -14097,7 +14103,7 @@
         <v>88</v>
       </c>
       <c r="P63" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="Q63">
         <v>8.77</v>
@@ -14509,7 +14515,7 @@
         <v>132</v>
       </c>
       <c r="P65" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="Q65">
         <v>2.4</v>
@@ -14715,7 +14721,7 @@
         <v>133</v>
       </c>
       <c r="P66" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="Q66">
         <v>1.55</v>
@@ -14921,7 +14927,7 @@
         <v>134</v>
       </c>
       <c r="P67" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="Q67">
         <v>4</v>
@@ -15127,7 +15133,7 @@
         <v>88</v>
       </c>
       <c r="P68" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="Q68">
         <v>3.1</v>
@@ -15951,7 +15957,7 @@
         <v>124</v>
       </c>
       <c r="P72" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="Q72">
         <v>1.88</v>
@@ -16157,7 +16163,7 @@
         <v>88</v>
       </c>
       <c r="P73" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="Q73">
         <v>7</v>
@@ -16441,7 +16447,7 @@
         <v>0</v>
       </c>
       <c r="AP74">
-        <v>1.33</v>
+        <v>1.46</v>
       </c>
       <c r="AQ74">
         <v>1</v>
@@ -16569,7 +16575,7 @@
         <v>138</v>
       </c>
       <c r="P75" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="Q75">
         <v>2.3</v>
@@ -16775,7 +16781,7 @@
         <v>88</v>
       </c>
       <c r="P76" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="Q76">
         <v>3.7</v>
@@ -16856,7 +16862,7 @@
         <v>0.23</v>
       </c>
       <c r="AQ76">
-        <v>1</v>
+        <v>0.92</v>
       </c>
       <c r="AR76">
         <v>1.29</v>
@@ -16981,7 +16987,7 @@
         <v>88</v>
       </c>
       <c r="P77" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="Q77">
         <v>2.47</v>
@@ -17471,7 +17477,7 @@
         <v>1</v>
       </c>
       <c r="AP79">
-        <v>1.73</v>
+        <v>1.58</v>
       </c>
       <c r="AQ79">
         <v>1.62</v>
@@ -17599,7 +17605,7 @@
         <v>140</v>
       </c>
       <c r="P80" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="Q80">
         <v>2.5</v>
@@ -17805,7 +17811,7 @@
         <v>141</v>
       </c>
       <c r="P81" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="Q81">
         <v>2.38</v>
@@ -18011,7 +18017,7 @@
         <v>142</v>
       </c>
       <c r="P82" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="Q82">
         <v>2.8</v>
@@ -18217,7 +18223,7 @@
         <v>143</v>
       </c>
       <c r="P83" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="Q83">
         <v>2.6</v>
@@ -18423,7 +18429,7 @@
         <v>144</v>
       </c>
       <c r="P84" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="Q84">
         <v>3.4</v>
@@ -18504,7 +18510,7 @@
         <v>2.45</v>
       </c>
       <c r="AQ84">
-        <v>1.82</v>
+        <v>1.92</v>
       </c>
       <c r="AR84">
         <v>1.81</v>
@@ -18835,7 +18841,7 @@
         <v>146</v>
       </c>
       <c r="P86" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="Q86">
         <v>2.88</v>
@@ -19119,7 +19125,7 @@
         <v>0</v>
       </c>
       <c r="AP87">
-        <v>1.33</v>
+        <v>1.46</v>
       </c>
       <c r="AQ87">
         <v>0.09</v>
@@ -19247,7 +19253,7 @@
         <v>88</v>
       </c>
       <c r="P88" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="Q88">
         <v>2.6</v>
@@ -19453,7 +19459,7 @@
         <v>93</v>
       </c>
       <c r="P89" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="Q89">
         <v>6.5</v>
@@ -19740,7 +19746,7 @@
         <v>1.42</v>
       </c>
       <c r="AQ90">
-        <v>1</v>
+        <v>0.92</v>
       </c>
       <c r="AR90">
         <v>1.39</v>
@@ -19865,7 +19871,7 @@
         <v>149</v>
       </c>
       <c r="P91" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="Q91">
         <v>4.7</v>
@@ -20071,7 +20077,7 @@
         <v>88</v>
       </c>
       <c r="P92" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="Q92">
         <v>3.8</v>
@@ -20483,7 +20489,7 @@
         <v>150</v>
       </c>
       <c r="P94" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="Q94">
         <v>3</v>
@@ -20767,7 +20773,7 @@
         <v>1.5</v>
       </c>
       <c r="AP95">
-        <v>1.73</v>
+        <v>1.58</v>
       </c>
       <c r="AQ95">
         <v>0.8</v>
@@ -21797,7 +21803,7 @@
         <v>1.33</v>
       </c>
       <c r="AP100">
-        <v>1.33</v>
+        <v>1.46</v>
       </c>
       <c r="AQ100">
         <v>1.25</v>
@@ -21925,7 +21931,7 @@
         <v>156</v>
       </c>
       <c r="P101" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="Q101">
         <v>1.83</v>
@@ -22624,7 +22630,7 @@
         <v>1.36</v>
       </c>
       <c r="AQ104">
-        <v>1.82</v>
+        <v>1.92</v>
       </c>
       <c r="AR104">
         <v>1.15</v>
@@ -23573,7 +23579,7 @@
         <v>161</v>
       </c>
       <c r="P109" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="Q109">
         <v>2.24</v>
@@ -23779,7 +23785,7 @@
         <v>162</v>
       </c>
       <c r="P110" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="Q110">
         <v>4.6</v>
@@ -23857,7 +23863,7 @@
         <v>2.14</v>
       </c>
       <c r="AP110">
-        <v>1.73</v>
+        <v>1.58</v>
       </c>
       <c r="AQ110">
         <v>2.17</v>
@@ -24191,7 +24197,7 @@
         <v>164</v>
       </c>
       <c r="P112" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="Q112">
         <v>1.44</v>
@@ -24397,7 +24403,7 @@
         <v>165</v>
       </c>
       <c r="P113" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="Q113">
         <v>3.25</v>
@@ -24603,7 +24609,7 @@
         <v>151</v>
       </c>
       <c r="P114" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="Q114">
         <v>2.88</v>
@@ -24809,7 +24815,7 @@
         <v>99</v>
       </c>
       <c r="P115" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="Q115">
         <v>1.73</v>
@@ -25015,7 +25021,7 @@
         <v>88</v>
       </c>
       <c r="P116" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="Q116">
         <v>4.33</v>
@@ -25096,7 +25102,7 @@
         <v>1.58</v>
       </c>
       <c r="AQ116">
-        <v>1.82</v>
+        <v>1.92</v>
       </c>
       <c r="AR116">
         <v>1.34</v>
@@ -25505,7 +25511,7 @@
         <v>0.63</v>
       </c>
       <c r="AP118">
-        <v>1.33</v>
+        <v>1.46</v>
       </c>
       <c r="AQ118">
         <v>0.46</v>
@@ -25633,7 +25639,7 @@
         <v>88</v>
       </c>
       <c r="P119" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="Q119">
         <v>15</v>
@@ -25839,7 +25845,7 @@
         <v>168</v>
       </c>
       <c r="P120" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="Q120">
         <v>3</v>
@@ -26126,7 +26132,7 @@
         <v>1.67</v>
       </c>
       <c r="AQ121">
-        <v>1</v>
+        <v>0.92</v>
       </c>
       <c r="AR121">
         <v>1.57</v>
@@ -26251,7 +26257,7 @@
         <v>170</v>
       </c>
       <c r="P122" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="Q122">
         <v>3.25</v>
@@ -26332,7 +26338,7 @@
         <v>1.17</v>
       </c>
       <c r="AQ122">
-        <v>1</v>
+        <v>0.92</v>
       </c>
       <c r="AR122">
         <v>1.54</v>
@@ -26663,7 +26669,7 @@
         <v>172</v>
       </c>
       <c r="P124" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="Q124">
         <v>1.83</v>
@@ -26869,7 +26875,7 @@
         <v>171</v>
       </c>
       <c r="P125" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="Q125">
         <v>6.3</v>
@@ -27359,7 +27365,7 @@
         <v>0.71</v>
       </c>
       <c r="AP127">
-        <v>1.73</v>
+        <v>1.58</v>
       </c>
       <c r="AQ127">
         <v>1</v>
@@ -27693,7 +27699,7 @@
         <v>174</v>
       </c>
       <c r="P129" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="Q129">
         <v>2.1</v>
@@ -27899,7 +27905,7 @@
         <v>175</v>
       </c>
       <c r="P130" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="Q130">
         <v>1.5</v>
@@ -28105,7 +28111,7 @@
         <v>176</v>
       </c>
       <c r="P131" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="Q131">
         <v>3.5</v>
@@ -28311,7 +28317,7 @@
         <v>177</v>
       </c>
       <c r="P132" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="Q132">
         <v>4.04</v>
@@ -28392,7 +28398,7 @@
         <v>0.91</v>
       </c>
       <c r="AQ132">
-        <v>1</v>
+        <v>0.92</v>
       </c>
       <c r="AR132">
         <v>1.24</v>
@@ -28723,7 +28729,7 @@
         <v>88</v>
       </c>
       <c r="P134" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="Q134">
         <v>2.75</v>
@@ -29007,7 +29013,7 @@
         <v>1.25</v>
       </c>
       <c r="AP135">
-        <v>1.73</v>
+        <v>1.58</v>
       </c>
       <c r="AQ135">
         <v>1</v>
@@ -29547,7 +29553,7 @@
         <v>91</v>
       </c>
       <c r="P138" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="Q138">
         <v>2.25</v>
@@ -29753,7 +29759,7 @@
         <v>179</v>
       </c>
       <c r="P139" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="Q139">
         <v>1.9</v>
@@ -30165,7 +30171,7 @@
         <v>88</v>
       </c>
       <c r="P141" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="Q141">
         <v>4</v>
@@ -30371,7 +30377,7 @@
         <v>117</v>
       </c>
       <c r="P142" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="Q142">
         <v>4</v>
@@ -30449,10 +30455,10 @@
         <v>1.75</v>
       </c>
       <c r="AP142">
-        <v>1.33</v>
+        <v>1.46</v>
       </c>
       <c r="AQ142">
-        <v>1.82</v>
+        <v>1.92</v>
       </c>
       <c r="AR142">
         <v>1.59</v>
@@ -30783,7 +30789,7 @@
         <v>182</v>
       </c>
       <c r="P144" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="Q144">
         <v>6</v>
@@ -30989,7 +30995,7 @@
         <v>88</v>
       </c>
       <c r="P145" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="Q145">
         <v>3.5</v>
@@ -31195,7 +31201,7 @@
         <v>183</v>
       </c>
       <c r="P146" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="Q146">
         <v>4.33</v>
@@ -31401,7 +31407,7 @@
         <v>184</v>
       </c>
       <c r="P147" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="Q147">
         <v>3.8</v>
@@ -31607,7 +31613,7 @@
         <v>185</v>
       </c>
       <c r="P148" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="Q148">
         <v>2.5</v>
@@ -31813,7 +31819,7 @@
         <v>186</v>
       </c>
       <c r="P149" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="Q149">
         <v>2.05</v>
@@ -31894,7 +31900,7 @@
         <v>2.45</v>
       </c>
       <c r="AQ149">
-        <v>1</v>
+        <v>0.92</v>
       </c>
       <c r="AR149">
         <v>1.91</v>
@@ -32019,7 +32025,7 @@
         <v>187</v>
       </c>
       <c r="P150" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="Q150">
         <v>1.95</v>
@@ -32225,7 +32231,7 @@
         <v>188</v>
       </c>
       <c r="P151" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="Q151">
         <v>2.48</v>
@@ -32303,7 +32309,7 @@
         <v>1</v>
       </c>
       <c r="AP151">
-        <v>1.73</v>
+        <v>1.58</v>
       </c>
       <c r="AQ151">
         <v>1.25</v>
@@ -32637,7 +32643,7 @@
         <v>190</v>
       </c>
       <c r="P153" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="Q153">
         <v>1.4</v>
@@ -32921,7 +32927,7 @@
         <v>0.89</v>
       </c>
       <c r="AP154">
-        <v>1.33</v>
+        <v>1.46</v>
       </c>
       <c r="AQ154">
         <v>0.75</v>
@@ -33049,7 +33055,7 @@
         <v>88</v>
       </c>
       <c r="P155" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="Q155">
         <v>3.2</v>
@@ -33667,7 +33673,7 @@
         <v>88</v>
       </c>
       <c r="P158" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="Q158">
         <v>5</v>
@@ -33873,7 +33879,7 @@
         <v>88</v>
       </c>
       <c r="P159" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="Q159">
         <v>2.38</v>
@@ -34285,7 +34291,7 @@
         <v>193</v>
       </c>
       <c r="P161" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="Q161">
         <v>4.75</v>
@@ -34366,7 +34372,7 @@
         <v>1.67</v>
       </c>
       <c r="AQ161">
-        <v>1.82</v>
+        <v>1.92</v>
       </c>
       <c r="AR161">
         <v>1.6</v>
@@ -34491,7 +34497,7 @@
         <v>194</v>
       </c>
       <c r="P162" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="Q162">
         <v>2.63</v>
@@ -34569,7 +34575,7 @@
         <v>0.9</v>
       </c>
       <c r="AP162">
-        <v>1.73</v>
+        <v>1.58</v>
       </c>
       <c r="AQ162">
         <v>0.75</v>
@@ -34697,7 +34703,7 @@
         <v>88</v>
       </c>
       <c r="P163" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="Q163">
         <v>11</v>
@@ -34903,7 +34909,7 @@
         <v>195</v>
       </c>
       <c r="P164" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="Q164">
         <v>2</v>
@@ -35109,7 +35115,7 @@
         <v>196</v>
       </c>
       <c r="P165" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="Q165">
         <v>2.5</v>
@@ -35190,7 +35196,7 @@
         <v>2.08</v>
       </c>
       <c r="AQ165">
-        <v>1</v>
+        <v>0.92</v>
       </c>
       <c r="AR165">
         <v>1.66</v>
@@ -36345,7 +36351,7 @@
         <v>201</v>
       </c>
       <c r="P171" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="Q171">
         <v>5.2</v>
@@ -36551,7 +36557,7 @@
         <v>202</v>
       </c>
       <c r="P172" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="Q172">
         <v>6.35</v>
@@ -36629,7 +36635,7 @@
         <v>2</v>
       </c>
       <c r="AP172">
-        <v>1.33</v>
+        <v>1.46</v>
       </c>
       <c r="AQ172">
         <v>2.17</v>
@@ -36757,7 +36763,7 @@
         <v>203</v>
       </c>
       <c r="P173" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="Q173">
         <v>2.6</v>
@@ -36963,7 +36969,7 @@
         <v>88</v>
       </c>
       <c r="P174" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="Q174">
         <v>4.86</v>
@@ -37044,7 +37050,7 @@
         <v>1.33</v>
       </c>
       <c r="AQ174">
-        <v>1.82</v>
+        <v>1.92</v>
       </c>
       <c r="AR174">
         <v>1.47</v>
@@ -37169,7 +37175,7 @@
         <v>204</v>
       </c>
       <c r="P175" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="Q175">
         <v>2.66</v>
@@ -37581,7 +37587,7 @@
         <v>171</v>
       </c>
       <c r="P177" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="Q177">
         <v>3.63</v>
@@ -37993,7 +37999,7 @@
         <v>88</v>
       </c>
       <c r="P179" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="Q179">
         <v>3.92</v>
@@ -38199,7 +38205,7 @@
         <v>206</v>
       </c>
       <c r="P180" t="s">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="Q180">
         <v>1.32</v>
@@ -38817,7 +38823,7 @@
         <v>208</v>
       </c>
       <c r="P183" t="s">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="Q183">
         <v>4.3</v>
@@ -39023,7 +39029,7 @@
         <v>88</v>
       </c>
       <c r="P184" t="s">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="Q184">
         <v>5.8</v>
@@ -39435,7 +39441,7 @@
         <v>96</v>
       </c>
       <c r="P186" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="Q186">
         <v>4.7</v>
@@ -40003,6 +40009,418 @@
         <v>2.55</v>
       </c>
       <c r="BP188">
+        <v>1.45</v>
+      </c>
+    </row>
+    <row r="189" spans="1:68">
+      <c r="A189" s="1">
+        <v>188</v>
+      </c>
+      <c r="B189">
+        <v>7468272</v>
+      </c>
+      <c r="C189" t="s">
+        <v>68</v>
+      </c>
+      <c r="D189" t="s">
+        <v>69</v>
+      </c>
+      <c r="E189" s="2">
+        <v>45718.47916666666</v>
+      </c>
+      <c r="F189">
+        <v>24</v>
+      </c>
+      <c r="G189" t="s">
+        <v>82</v>
+      </c>
+      <c r="H189" t="s">
+        <v>84</v>
+      </c>
+      <c r="I189">
+        <v>0</v>
+      </c>
+      <c r="J189">
+        <v>1</v>
+      </c>
+      <c r="K189">
+        <v>1</v>
+      </c>
+      <c r="L189">
+        <v>0</v>
+      </c>
+      <c r="M189">
+        <v>2</v>
+      </c>
+      <c r="N189">
+        <v>2</v>
+      </c>
+      <c r="O189" t="s">
+        <v>88</v>
+      </c>
+      <c r="P189" t="s">
+        <v>301</v>
+      </c>
+      <c r="Q189">
+        <v>4.5</v>
+      </c>
+      <c r="R189">
+        <v>2.3</v>
+      </c>
+      <c r="S189">
+        <v>2.38</v>
+      </c>
+      <c r="T189">
+        <v>1.33</v>
+      </c>
+      <c r="U189">
+        <v>3.25</v>
+      </c>
+      <c r="V189">
+        <v>2.5</v>
+      </c>
+      <c r="W189">
+        <v>1.5</v>
+      </c>
+      <c r="X189">
+        <v>6.5</v>
+      </c>
+      <c r="Y189">
+        <v>1.11</v>
+      </c>
+      <c r="Z189">
+        <v>4.33</v>
+      </c>
+      <c r="AA189">
+        <v>3.8</v>
+      </c>
+      <c r="AB189">
+        <v>1.75</v>
+      </c>
+      <c r="AC189">
+        <v>1.04</v>
+      </c>
+      <c r="AD189">
+        <v>9</v>
+      </c>
+      <c r="AE189">
+        <v>1.21</v>
+      </c>
+      <c r="AF189">
+        <v>3.95</v>
+      </c>
+      <c r="AG189">
+        <v>1.7</v>
+      </c>
+      <c r="AH189">
+        <v>2.1</v>
+      </c>
+      <c r="AI189">
+        <v>1.67</v>
+      </c>
+      <c r="AJ189">
+        <v>2.1</v>
+      </c>
+      <c r="AK189">
+        <v>1.98</v>
+      </c>
+      <c r="AL189">
+        <v>1.25</v>
+      </c>
+      <c r="AM189">
+        <v>1.22</v>
+      </c>
+      <c r="AN189">
+        <v>1.73</v>
+      </c>
+      <c r="AO189">
+        <v>1.82</v>
+      </c>
+      <c r="AP189">
+        <v>1.58</v>
+      </c>
+      <c r="AQ189">
+        <v>1.92</v>
+      </c>
+      <c r="AR189">
+        <v>1.57</v>
+      </c>
+      <c r="AS189">
+        <v>1.41</v>
+      </c>
+      <c r="AT189">
+        <v>2.98</v>
+      </c>
+      <c r="AU189">
+        <v>4</v>
+      </c>
+      <c r="AV189">
+        <v>4</v>
+      </c>
+      <c r="AW189">
+        <v>4</v>
+      </c>
+      <c r="AX189">
+        <v>7</v>
+      </c>
+      <c r="AY189">
+        <v>8</v>
+      </c>
+      <c r="AZ189">
+        <v>11</v>
+      </c>
+      <c r="BA189">
+        <v>7</v>
+      </c>
+      <c r="BB189">
+        <v>3</v>
+      </c>
+      <c r="BC189">
+        <v>10</v>
+      </c>
+      <c r="BD189">
+        <v>2.8</v>
+      </c>
+      <c r="BE189">
+        <v>7</v>
+      </c>
+      <c r="BF189">
+        <v>1.49</v>
+      </c>
+      <c r="BG189">
+        <v>1.21</v>
+      </c>
+      <c r="BH189">
+        <v>3.9</v>
+      </c>
+      <c r="BI189">
+        <v>1.36</v>
+      </c>
+      <c r="BJ189">
+        <v>2.85</v>
+      </c>
+      <c r="BK189">
+        <v>1.58</v>
+      </c>
+      <c r="BL189">
+        <v>2.2</v>
+      </c>
+      <c r="BM189">
+        <v>1.91</v>
+      </c>
+      <c r="BN189">
+        <v>1.79</v>
+      </c>
+      <c r="BO189">
+        <v>2.35</v>
+      </c>
+      <c r="BP189">
+        <v>1.5</v>
+      </c>
+    </row>
+    <row r="190" spans="1:68">
+      <c r="A190" s="1">
+        <v>189</v>
+      </c>
+      <c r="B190">
+        <v>7468277</v>
+      </c>
+      <c r="C190" t="s">
+        <v>68</v>
+      </c>
+      <c r="D190" t="s">
+        <v>69</v>
+      </c>
+      <c r="E190" s="2">
+        <v>45718.47916666666</v>
+      </c>
+      <c r="F190">
+        <v>24</v>
+      </c>
+      <c r="G190" t="s">
+        <v>75</v>
+      </c>
+      <c r="H190" t="s">
+        <v>76</v>
+      </c>
+      <c r="I190">
+        <v>0</v>
+      </c>
+      <c r="J190">
+        <v>0</v>
+      </c>
+      <c r="K190">
+        <v>0</v>
+      </c>
+      <c r="L190">
+        <v>2</v>
+      </c>
+      <c r="M190">
+        <v>0</v>
+      </c>
+      <c r="N190">
+        <v>2</v>
+      </c>
+      <c r="O190" t="s">
+        <v>211</v>
+      </c>
+      <c r="P190" t="s">
+        <v>88</v>
+      </c>
+      <c r="Q190">
+        <v>2.88</v>
+      </c>
+      <c r="R190">
+        <v>2.2</v>
+      </c>
+      <c r="S190">
+        <v>3.75</v>
+      </c>
+      <c r="T190">
+        <v>1.4</v>
+      </c>
+      <c r="U190">
+        <v>2.75</v>
+      </c>
+      <c r="V190">
+        <v>2.75</v>
+      </c>
+      <c r="W190">
+        <v>1.4</v>
+      </c>
+      <c r="X190">
+        <v>8</v>
+      </c>
+      <c r="Y190">
+        <v>1.08</v>
+      </c>
+      <c r="Z190">
+        <v>2.2</v>
+      </c>
+      <c r="AA190">
+        <v>3.4</v>
+      </c>
+      <c r="AB190">
+        <v>3.25</v>
+      </c>
+      <c r="AC190">
+        <v>1.05</v>
+      </c>
+      <c r="AD190">
+        <v>8.5</v>
+      </c>
+      <c r="AE190">
+        <v>1.28</v>
+      </c>
+      <c r="AF190">
+        <v>3.3</v>
+      </c>
+      <c r="AG190">
+        <v>1.9</v>
+      </c>
+      <c r="AH190">
+        <v>1.9</v>
+      </c>
+      <c r="AI190">
+        <v>1.7</v>
+      </c>
+      <c r="AJ190">
+        <v>2.05</v>
+      </c>
+      <c r="AK190">
+        <v>1.35</v>
+      </c>
+      <c r="AL190">
+        <v>1.3</v>
+      </c>
+      <c r="AM190">
+        <v>1.63</v>
+      </c>
+      <c r="AN190">
+        <v>1.33</v>
+      </c>
+      <c r="AO190">
+        <v>1</v>
+      </c>
+      <c r="AP190">
+        <v>1.46</v>
+      </c>
+      <c r="AQ190">
+        <v>0.92</v>
+      </c>
+      <c r="AR190">
+        <v>1.53</v>
+      </c>
+      <c r="AS190">
+        <v>1.24</v>
+      </c>
+      <c r="AT190">
+        <v>2.77</v>
+      </c>
+      <c r="AU190">
+        <v>7</v>
+      </c>
+      <c r="AV190">
+        <v>0</v>
+      </c>
+      <c r="AW190">
+        <v>11</v>
+      </c>
+      <c r="AX190">
+        <v>2</v>
+      </c>
+      <c r="AY190">
+        <v>18</v>
+      </c>
+      <c r="AZ190">
+        <v>2</v>
+      </c>
+      <c r="BA190">
+        <v>5</v>
+      </c>
+      <c r="BB190">
+        <v>2</v>
+      </c>
+      <c r="BC190">
+        <v>7</v>
+      </c>
+      <c r="BD190">
+        <v>1.75</v>
+      </c>
+      <c r="BE190">
+        <v>6.75</v>
+      </c>
+      <c r="BF190">
+        <v>2.25</v>
+      </c>
+      <c r="BG190">
+        <v>1.24</v>
+      </c>
+      <c r="BH190">
+        <v>3.65</v>
+      </c>
+      <c r="BI190">
+        <v>1.41</v>
+      </c>
+      <c r="BJ190">
+        <v>2.65</v>
+      </c>
+      <c r="BK190">
+        <v>1.67</v>
+      </c>
+      <c r="BL190">
+        <v>2.07</v>
+      </c>
+      <c r="BM190">
+        <v>2.05</v>
+      </c>
+      <c r="BN190">
+        <v>1.68</v>
+      </c>
+      <c r="BO190">
+        <v>2.55</v>
+      </c>
+      <c r="BP190">
         <v>1.45</v>
       </c>
     </row>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Czech Republic First League_20242025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Czech Republic First League_20242025.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1202" uniqueCount="302">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1208" uniqueCount="303">
   <si>
     <t>Id_Jogo</t>
   </si>
@@ -652,6 +652,9 @@
     <t>['65', '88']</t>
   </si>
   <si>
+    <t>['49', '90+9']</t>
+  </si>
+  <si>
     <t>['25']</t>
   </si>
   <si>
@@ -1281,7 +1284,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:BP190"/>
+  <dimension ref="A1:BP191"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:68">
@@ -1537,7 +1540,7 @@
         <v>86</v>
       </c>
       <c r="P2" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="Q2">
         <v>1.53</v>
@@ -1618,7 +1621,7 @@
         <v>2.17</v>
       </c>
       <c r="AQ2">
-        <v>0.46</v>
+        <v>0.63</v>
       </c>
       <c r="AR2">
         <v>0</v>
@@ -1821,10 +1824,10 @@
         <v>0</v>
       </c>
       <c r="AP3">
-        <v>2.08</v>
+        <v>1.67</v>
       </c>
       <c r="AQ3">
-        <v>1.25</v>
+        <v>1.42</v>
       </c>
       <c r="AR3">
         <v>0</v>
@@ -1949,7 +1952,7 @@
         <v>88</v>
       </c>
       <c r="P4" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="Q4">
         <v>2.88</v>
@@ -2027,10 +2030,10 @@
         <v>0</v>
       </c>
       <c r="AP4">
-        <v>0.23</v>
+        <v>0.17</v>
       </c>
       <c r="AQ4">
-        <v>1.25</v>
+        <v>1.46</v>
       </c>
       <c r="AR4">
         <v>0</v>
@@ -2233,10 +2236,10 @@
         <v>0</v>
       </c>
       <c r="AP5">
-        <v>1.17</v>
+        <v>1.25</v>
       </c>
       <c r="AQ5">
-        <v>1.62</v>
+        <v>2</v>
       </c>
       <c r="AR5">
         <v>0</v>
@@ -2361,7 +2364,7 @@
         <v>90</v>
       </c>
       <c r="P6" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="Q6">
         <v>5.5</v>
@@ -2439,10 +2442,10 @@
         <v>0</v>
       </c>
       <c r="AP6">
-        <v>0.91</v>
+        <v>0.65</v>
       </c>
       <c r="AQ6">
-        <v>1.92</v>
+        <v>2.17</v>
       </c>
       <c r="AR6">
         <v>0</v>
@@ -2567,7 +2570,7 @@
         <v>91</v>
       </c>
       <c r="P7" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="Q7">
         <v>3.2</v>
@@ -2645,10 +2648,10 @@
         <v>0</v>
       </c>
       <c r="AP7">
-        <v>1.46</v>
+        <v>1.17</v>
       </c>
       <c r="AQ7">
-        <v>1</v>
+        <v>1.21</v>
       </c>
       <c r="AR7">
         <v>0</v>
@@ -2851,10 +2854,10 @@
         <v>0</v>
       </c>
       <c r="AP8">
-        <v>1.36</v>
+        <v>1.13</v>
       </c>
       <c r="AQ8">
-        <v>2.42</v>
+        <v>2.71</v>
       </c>
       <c r="AR8">
         <v>0</v>
@@ -3057,10 +3060,10 @@
         <v>0</v>
       </c>
       <c r="AP9">
-        <v>1.58</v>
+        <v>1.3</v>
       </c>
       <c r="AQ9">
-        <v>0.75</v>
+        <v>1.04</v>
       </c>
       <c r="AR9">
         <v>0</v>
@@ -3260,22 +3263,22 @@
         <v>0</v>
       </c>
       <c r="AO10">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AP10">
-        <v>0.91</v>
+        <v>0.65</v>
       </c>
       <c r="AQ10">
-        <v>1.45</v>
+        <v>1.25</v>
       </c>
       <c r="AR10">
         <v>0.98</v>
       </c>
       <c r="AS10">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AT10">
-        <v>0.98</v>
+        <v>2.71</v>
       </c>
       <c r="AU10">
         <v>3</v>
@@ -3391,7 +3394,7 @@
         <v>94</v>
       </c>
       <c r="P11" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="Q11">
         <v>6.5</v>
@@ -3466,22 +3469,22 @@
         <v>0</v>
       </c>
       <c r="AO11">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AP11">
-        <v>1.33</v>
+        <v>1.04</v>
       </c>
       <c r="AQ11">
         <v>2.17</v>
       </c>
       <c r="AR11">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="AS11">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AT11">
-        <v>0</v>
+        <v>3.11</v>
       </c>
       <c r="AU11">
         <v>4</v>
@@ -3597,7 +3600,7 @@
         <v>88</v>
       </c>
       <c r="P12" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="Q12">
         <v>2.85</v>
@@ -3675,19 +3678,19 @@
         <v>0</v>
       </c>
       <c r="AP12">
-        <v>0.82</v>
+        <v>0.63</v>
       </c>
       <c r="AQ12">
-        <v>0.8</v>
+        <v>1.17</v>
       </c>
       <c r="AR12">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AS12">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="AT12">
-        <v>0</v>
+        <v>2.96</v>
       </c>
       <c r="AU12">
         <v>3</v>
@@ -3875,25 +3878,25 @@
         <v>5.85</v>
       </c>
       <c r="AN13">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AO13">
         <v>0</v>
       </c>
       <c r="AP13">
-        <v>3</v>
+        <v>2.71</v>
       </c>
       <c r="AQ13">
-        <v>0.09</v>
+        <v>0.17</v>
       </c>
       <c r="AR13">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AS13">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AT13">
-        <v>0</v>
+        <v>2.98</v>
       </c>
       <c r="AU13">
         <v>9</v>
@@ -4009,7 +4012,7 @@
         <v>96</v>
       </c>
       <c r="P14" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="Q14">
         <v>2.45</v>
@@ -4081,25 +4084,25 @@
         <v>1.78</v>
       </c>
       <c r="AN14">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AO14">
         <v>3</v>
       </c>
       <c r="AP14">
-        <v>1.42</v>
+        <v>1.21</v>
       </c>
       <c r="AQ14">
-        <v>1.25</v>
+        <v>1.46</v>
       </c>
       <c r="AR14">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="AS14">
         <v>2.08</v>
       </c>
       <c r="AT14">
-        <v>2.08</v>
+        <v>4.05</v>
       </c>
       <c r="AU14">
         <v>4</v>
@@ -4290,22 +4293,22 @@
         <v>0</v>
       </c>
       <c r="AO15">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AP15">
-        <v>1.58</v>
+        <v>1.42</v>
       </c>
       <c r="AQ15">
-        <v>0.92</v>
+        <v>1.13</v>
       </c>
       <c r="AR15">
-        <v>0</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="AS15">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AT15">
-        <v>0</v>
+        <v>1.94</v>
       </c>
       <c r="AU15">
         <v>7</v>
@@ -4496,22 +4499,22 @@
         <v>0</v>
       </c>
       <c r="AO16">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AP16">
-        <v>2.45</v>
+        <v>2</v>
       </c>
       <c r="AQ16">
-        <v>1.25</v>
+        <v>1.67</v>
       </c>
       <c r="AR16">
-        <v>0</v>
+        <v>1.71</v>
       </c>
       <c r="AS16">
-        <v>0</v>
+        <v>1.81</v>
       </c>
       <c r="AT16">
-        <v>0</v>
+        <v>3.52</v>
       </c>
       <c r="AU16">
         <v>5</v>
@@ -4699,25 +4702,25 @@
         <v>2.7</v>
       </c>
       <c r="AN17">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AO17">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AP17">
-        <v>2.42</v>
+        <v>2.17</v>
       </c>
       <c r="AQ17">
-        <v>1</v>
+        <v>1.3</v>
       </c>
       <c r="AR17">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="AS17">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="AT17">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="AU17">
         <v>8</v>
@@ -4833,7 +4836,7 @@
         <v>88</v>
       </c>
       <c r="P18" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="Q18">
         <v>5.4</v>
@@ -4905,25 +4908,25 @@
         <v>1.12</v>
       </c>
       <c r="AN18">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AO18">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AP18">
-        <v>1.42</v>
+        <v>1.21</v>
       </c>
       <c r="AQ18">
-        <v>2.42</v>
+        <v>2.71</v>
       </c>
       <c r="AR18">
-        <v>1.26</v>
+        <v>1.61</v>
       </c>
       <c r="AS18">
-        <v>1.65</v>
+        <v>2.02</v>
       </c>
       <c r="AT18">
-        <v>2.91</v>
+        <v>3.63</v>
       </c>
       <c r="AU18">
         <v>4</v>
@@ -5114,22 +5117,22 @@
         <v>3</v>
       </c>
       <c r="AO19">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AP19">
         <v>2.17</v>
       </c>
       <c r="AQ19">
-        <v>0.42</v>
+        <v>0.65</v>
       </c>
       <c r="AR19">
-        <v>1.9</v>
+        <v>1.96</v>
       </c>
       <c r="AS19">
-        <v>0</v>
+        <v>0.93</v>
       </c>
       <c r="AT19">
-        <v>1.9</v>
+        <v>2.89</v>
       </c>
       <c r="AU19">
         <v>9</v>
@@ -5317,25 +5320,25 @@
         <v>1.8</v>
       </c>
       <c r="AN20">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="AO20">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AP20">
-        <v>1.36</v>
+        <v>1.13</v>
       </c>
       <c r="AQ20">
-        <v>1.45</v>
+        <v>1.25</v>
       </c>
       <c r="AR20">
-        <v>1</v>
+        <v>1.25</v>
       </c>
       <c r="AS20">
-        <v>1.88</v>
+        <v>1.81</v>
       </c>
       <c r="AT20">
-        <v>2.88</v>
+        <v>3.06</v>
       </c>
       <c r="AU20">
         <v>4</v>
@@ -5523,25 +5526,25 @@
         <v>1.17</v>
       </c>
       <c r="AN21">
-        <v>3</v>
+        <v>1.5</v>
       </c>
       <c r="AO21">
         <v>3</v>
       </c>
       <c r="AP21">
-        <v>2.08</v>
+        <v>1.67</v>
       </c>
       <c r="AQ21">
-        <v>1.92</v>
+        <v>2.17</v>
       </c>
       <c r="AR21">
-        <v>1.81</v>
+        <v>1.38</v>
       </c>
       <c r="AS21">
-        <v>1.43</v>
+        <v>1.53</v>
       </c>
       <c r="AT21">
-        <v>3.24</v>
+        <v>2.91</v>
       </c>
       <c r="AU21">
         <v>5</v>
@@ -5729,25 +5732,25 @@
         <v>1.71</v>
       </c>
       <c r="AN22">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AO22">
         <v>0</v>
       </c>
       <c r="AP22">
-        <v>1.67</v>
+        <v>1.46</v>
       </c>
       <c r="AQ22">
-        <v>0.75</v>
+        <v>1.04</v>
       </c>
       <c r="AR22">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="AS22">
-        <v>1.21</v>
+        <v>1.13</v>
       </c>
       <c r="AT22">
-        <v>1.21</v>
+        <v>2.61</v>
       </c>
       <c r="AU22">
         <v>5</v>
@@ -5863,7 +5866,7 @@
         <v>102</v>
       </c>
       <c r="P23" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="Q23">
         <v>2.6</v>
@@ -5941,19 +5944,19 @@
         <v>0</v>
       </c>
       <c r="AP23">
-        <v>0.23</v>
+        <v>0.17</v>
       </c>
       <c r="AQ23">
-        <v>0.46</v>
+        <v>0.63</v>
       </c>
       <c r="AR23">
-        <v>1.33</v>
+        <v>0.92</v>
       </c>
       <c r="AS23">
-        <v>1.03</v>
+        <v>1.12</v>
       </c>
       <c r="AT23">
-        <v>2.36</v>
+        <v>2.04</v>
       </c>
       <c r="AU23">
         <v>5</v>
@@ -6069,7 +6072,7 @@
         <v>103</v>
       </c>
       <c r="P24" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="Q24">
         <v>2.75</v>
@@ -6141,25 +6144,25 @@
         <v>1.78</v>
       </c>
       <c r="AN24">
-        <v>3</v>
+        <v>1.5</v>
       </c>
       <c r="AO24">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AP24">
-        <v>1.58</v>
+        <v>1.3</v>
       </c>
       <c r="AQ24">
-        <v>1.25</v>
+        <v>1.42</v>
       </c>
       <c r="AR24">
-        <v>1.19</v>
+        <v>0.95</v>
       </c>
       <c r="AS24">
-        <v>0.9399999999999999</v>
+        <v>1.35</v>
       </c>
       <c r="AT24">
-        <v>2.13</v>
+        <v>2.3</v>
       </c>
       <c r="AU24">
         <v>4</v>
@@ -6275,7 +6278,7 @@
         <v>88</v>
       </c>
       <c r="P25" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="Q25">
         <v>1.06</v>
@@ -6347,25 +6350,25 @@
         <v>1.29</v>
       </c>
       <c r="AN25">
-        <v>1.5</v>
+        <v>1</v>
       </c>
       <c r="AO25">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AP25">
-        <v>0.91</v>
+        <v>0.65</v>
       </c>
       <c r="AQ25">
-        <v>1.25</v>
+        <v>1.67</v>
       </c>
       <c r="AR25">
-        <v>0.93</v>
+        <v>0.82</v>
       </c>
       <c r="AS25">
-        <v>0.95</v>
+        <v>1.35</v>
       </c>
       <c r="AT25">
-        <v>1.88</v>
+        <v>2.17</v>
       </c>
       <c r="AU25">
         <v>3</v>
@@ -6481,7 +6484,7 @@
         <v>104</v>
       </c>
       <c r="P26" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="Q26">
         <v>6.23</v>
@@ -6553,25 +6556,25 @@
         <v>1.1</v>
       </c>
       <c r="AN26">
-        <v>3</v>
+        <v>1.33</v>
       </c>
       <c r="AO26">
         <v>3</v>
       </c>
       <c r="AP26">
-        <v>1.17</v>
+        <v>1.25</v>
       </c>
       <c r="AQ26">
         <v>2.17</v>
       </c>
       <c r="AR26">
-        <v>1.73</v>
+        <v>1.45</v>
       </c>
       <c r="AS26">
-        <v>2.02</v>
+        <v>2.06</v>
       </c>
       <c r="AT26">
-        <v>3.75</v>
+        <v>3.51</v>
       </c>
       <c r="AU26">
         <v>6</v>
@@ -6762,22 +6765,22 @@
         <v>0</v>
       </c>
       <c r="AO27">
-        <v>3</v>
+        <v>1.33</v>
       </c>
       <c r="AP27">
-        <v>1.33</v>
+        <v>1.04</v>
       </c>
       <c r="AQ27">
-        <v>1</v>
+        <v>1.21</v>
       </c>
       <c r="AR27">
-        <v>1.06</v>
+        <v>1.28</v>
       </c>
       <c r="AS27">
-        <v>1.97</v>
+        <v>1.55</v>
       </c>
       <c r="AT27">
-        <v>3.03</v>
+        <v>2.83</v>
       </c>
       <c r="AU27">
         <v>6</v>
@@ -6965,25 +6968,25 @@
         <v>4.33</v>
       </c>
       <c r="AN28">
-        <v>3</v>
+        <v>2.33</v>
       </c>
       <c r="AO28">
-        <v>2</v>
+        <v>2.33</v>
       </c>
       <c r="AP28">
-        <v>3</v>
+        <v>2.71</v>
       </c>
       <c r="AQ28">
-        <v>1.25</v>
+        <v>1.46</v>
       </c>
       <c r="AR28">
-        <v>2.4</v>
+        <v>1.7</v>
       </c>
       <c r="AS28">
-        <v>1.48</v>
+        <v>1.4</v>
       </c>
       <c r="AT28">
-        <v>3.88</v>
+        <v>3.1</v>
       </c>
       <c r="AU28">
         <v>9</v>
@@ -7171,25 +7174,25 @@
         <v>1.36</v>
       </c>
       <c r="AN29">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AO29">
-        <v>0</v>
+        <v>0.67</v>
       </c>
       <c r="AP29">
-        <v>0.82</v>
+        <v>0.63</v>
       </c>
       <c r="AQ29">
-        <v>0.92</v>
+        <v>1.13</v>
       </c>
       <c r="AR29">
-        <v>1.22</v>
+        <v>1.07</v>
       </c>
       <c r="AS29">
-        <v>1.5</v>
+        <v>1.29</v>
       </c>
       <c r="AT29">
-        <v>2.72</v>
+        <v>2.36</v>
       </c>
       <c r="AU29">
         <v>4</v>
@@ -7377,25 +7380,25 @@
         <v>2.2</v>
       </c>
       <c r="AN30">
-        <v>3</v>
+        <v>1.5</v>
       </c>
       <c r="AO30">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AP30">
-        <v>2.45</v>
+        <v>2</v>
       </c>
       <c r="AQ30">
-        <v>1</v>
+        <v>1.3</v>
       </c>
       <c r="AR30">
-        <v>1.24</v>
+        <v>1.47</v>
       </c>
       <c r="AS30">
-        <v>0.71</v>
+        <v>0.96</v>
       </c>
       <c r="AT30">
-        <v>1.95</v>
+        <v>2.43</v>
       </c>
       <c r="AU30">
         <v>6</v>
@@ -7583,25 +7586,25 @@
         <v>2.38</v>
       </c>
       <c r="AN31">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="AO31">
         <v>0</v>
       </c>
       <c r="AP31">
-        <v>1.58</v>
+        <v>1.42</v>
       </c>
       <c r="AQ31">
-        <v>0.09</v>
+        <v>0.17</v>
       </c>
       <c r="AR31">
-        <v>1.76</v>
+        <v>1.63</v>
       </c>
       <c r="AS31">
-        <v>0.5</v>
+        <v>1.14</v>
       </c>
       <c r="AT31">
-        <v>2.26</v>
+        <v>2.77</v>
       </c>
       <c r="AU31">
         <v>7</v>
@@ -7789,25 +7792,25 @@
         <v>3.1</v>
       </c>
       <c r="AN32">
-        <v>3</v>
+        <v>2.33</v>
       </c>
       <c r="AO32">
-        <v>3</v>
+        <v>1.5</v>
       </c>
       <c r="AP32">
-        <v>2.42</v>
+        <v>2.17</v>
       </c>
       <c r="AQ32">
-        <v>0.8</v>
+        <v>1.17</v>
       </c>
       <c r="AR32">
-        <v>1.64</v>
+        <v>1.38</v>
       </c>
       <c r="AS32">
-        <v>2.37</v>
+        <v>2.15</v>
       </c>
       <c r="AT32">
-        <v>4.01</v>
+        <v>3.53</v>
       </c>
       <c r="AU32">
         <v>8</v>
@@ -7995,25 +7998,25 @@
         <v>2.35</v>
       </c>
       <c r="AN33">
-        <v>3</v>
+        <v>1.5</v>
       </c>
       <c r="AO33">
-        <v>0</v>
+        <v>0.75</v>
       </c>
       <c r="AP33">
-        <v>1.58</v>
+        <v>1.3</v>
       </c>
       <c r="AQ33">
-        <v>0.42</v>
+        <v>0.65</v>
       </c>
       <c r="AR33">
-        <v>1.08</v>
+        <v>0.84</v>
       </c>
       <c r="AS33">
-        <v>0.61</v>
+        <v>0.88</v>
       </c>
       <c r="AT33">
-        <v>1.69</v>
+        <v>1.72</v>
       </c>
       <c r="AU33">
         <v>6</v>
@@ -8129,7 +8132,7 @@
         <v>111</v>
       </c>
       <c r="P34" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="Q34">
         <v>1.45</v>
@@ -8201,25 +8204,25 @@
         <v>5.5</v>
       </c>
       <c r="AN34">
-        <v>3</v>
+        <v>2.5</v>
       </c>
       <c r="AO34">
-        <v>0</v>
+        <v>0.75</v>
       </c>
       <c r="AP34">
-        <v>3</v>
+        <v>2.71</v>
       </c>
       <c r="AQ34">
-        <v>0.75</v>
+        <v>1.04</v>
       </c>
       <c r="AR34">
-        <v>2.27</v>
+        <v>1.82</v>
       </c>
       <c r="AS34">
-        <v>1.39</v>
+        <v>1.4</v>
       </c>
       <c r="AT34">
-        <v>3.66</v>
+        <v>3.22</v>
       </c>
       <c r="AU34">
         <v>7</v>
@@ -8335,7 +8338,7 @@
         <v>112</v>
       </c>
       <c r="P35" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="Q35">
         <v>2.84</v>
@@ -8407,25 +8410,25 @@
         <v>1.62</v>
       </c>
       <c r="AN35">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AO35">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="AP35">
-        <v>1.46</v>
+        <v>1.17</v>
       </c>
       <c r="AQ35">
-        <v>1.45</v>
+        <v>1.25</v>
       </c>
       <c r="AR35">
-        <v>1.93</v>
+        <v>1.78</v>
       </c>
       <c r="AS35">
-        <v>1.32</v>
+        <v>1.4</v>
       </c>
       <c r="AT35">
-        <v>3.25</v>
+        <v>3.18</v>
       </c>
       <c r="AU35">
         <v>4</v>
@@ -8541,7 +8544,7 @@
         <v>113</v>
       </c>
       <c r="P36" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="Q36">
         <v>5.63</v>
@@ -8613,25 +8616,25 @@
         <v>1.15</v>
       </c>
       <c r="AN36">
-        <v>2</v>
+        <v>1.75</v>
       </c>
       <c r="AO36">
         <v>3</v>
       </c>
       <c r="AP36">
-        <v>2.08</v>
+        <v>1.67</v>
       </c>
       <c r="AQ36">
         <v>2.17</v>
       </c>
       <c r="AR36">
-        <v>1.54</v>
+        <v>1.38</v>
       </c>
       <c r="AS36">
         <v>2.07</v>
       </c>
       <c r="AT36">
-        <v>3.61</v>
+        <v>3.45</v>
       </c>
       <c r="AU36">
         <v>5</v>
@@ -8747,7 +8750,7 @@
         <v>114</v>
       </c>
       <c r="P37" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="Q37">
         <v>2.58</v>
@@ -8819,25 +8822,25 @@
         <v>1.71</v>
       </c>
       <c r="AN37">
-        <v>3</v>
+        <v>1.75</v>
       </c>
       <c r="AO37">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AP37">
-        <v>1.67</v>
+        <v>1.46</v>
       </c>
       <c r="AQ37">
-        <v>1.25</v>
+        <v>1.42</v>
       </c>
       <c r="AR37">
-        <v>1.25</v>
+        <v>1.23</v>
       </c>
       <c r="AS37">
-        <v>1.56</v>
+        <v>1.63</v>
       </c>
       <c r="AT37">
-        <v>2.81</v>
+        <v>2.86</v>
       </c>
       <c r="AU37">
         <v>5</v>
@@ -9025,25 +9028,25 @@
         <v>2.88</v>
       </c>
       <c r="AN38">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="AO38">
-        <v>1.5</v>
+        <v>0.75</v>
       </c>
       <c r="AP38">
-        <v>1.42</v>
+        <v>1.21</v>
       </c>
       <c r="AQ38">
-        <v>0.46</v>
+        <v>0.63</v>
       </c>
       <c r="AR38">
-        <v>1.34</v>
+        <v>1.51</v>
       </c>
       <c r="AS38">
-        <v>1</v>
+        <v>1.08</v>
       </c>
       <c r="AT38">
-        <v>2.34</v>
+        <v>2.59</v>
       </c>
       <c r="AU38">
         <v>6</v>
@@ -9159,7 +9162,7 @@
         <v>88</v>
       </c>
       <c r="P39" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="Q39">
         <v>4.75</v>
@@ -9234,19 +9237,19 @@
         <v>0</v>
       </c>
       <c r="AO39">
-        <v>2</v>
+        <v>2.5</v>
       </c>
       <c r="AP39">
-        <v>0.23</v>
+        <v>0.17</v>
       </c>
       <c r="AQ39">
-        <v>1.92</v>
+        <v>2.17</v>
       </c>
       <c r="AR39">
-        <v>1.46</v>
+        <v>1.16</v>
       </c>
       <c r="AS39">
-        <v>1.25</v>
+        <v>1.55</v>
       </c>
       <c r="AT39">
         <v>2.71</v>
@@ -9437,25 +9440,25 @@
         <v>1.53</v>
       </c>
       <c r="AN40">
-        <v>1</v>
+        <v>1.25</v>
       </c>
       <c r="AO40">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AP40">
-        <v>1.36</v>
+        <v>1.13</v>
       </c>
       <c r="AQ40">
-        <v>1.62</v>
+        <v>2</v>
       </c>
       <c r="AR40">
         <v>1.19</v>
       </c>
       <c r="AS40">
-        <v>1.71</v>
+        <v>1.82</v>
       </c>
       <c r="AT40">
-        <v>2.9</v>
+        <v>3.01</v>
       </c>
       <c r="AU40">
         <v>6</v>
@@ -9571,7 +9574,7 @@
         <v>117</v>
       </c>
       <c r="P41" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="Q41">
         <v>2.4</v>
@@ -9643,25 +9646,25 @@
         <v>1.88</v>
       </c>
       <c r="AN41">
-        <v>1.5</v>
+        <v>1.4</v>
       </c>
       <c r="AO41">
-        <v>1.5</v>
+        <v>1.4</v>
       </c>
       <c r="AP41">
-        <v>1.17</v>
+        <v>1.25</v>
       </c>
       <c r="AQ41">
-        <v>1.25</v>
+        <v>1.67</v>
       </c>
       <c r="AR41">
-        <v>1.49</v>
+        <v>1.45</v>
       </c>
       <c r="AS41">
-        <v>1.21</v>
+        <v>1.4</v>
       </c>
       <c r="AT41">
-        <v>2.7</v>
+        <v>2.85</v>
       </c>
       <c r="AU41">
         <v>6</v>
@@ -9777,7 +9780,7 @@
         <v>107</v>
       </c>
       <c r="P42" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="Q42">
         <v>2.61</v>
@@ -9849,25 +9852,25 @@
         <v>1.75</v>
       </c>
       <c r="AN42">
-        <v>1.5</v>
+        <v>0.6</v>
       </c>
       <c r="AO42">
-        <v>1.5</v>
+        <v>0.75</v>
       </c>
       <c r="AP42">
-        <v>1.33</v>
+        <v>1.04</v>
       </c>
       <c r="AQ42">
-        <v>0.8</v>
+        <v>1.17</v>
       </c>
       <c r="AR42">
-        <v>1.41</v>
+        <v>1.3</v>
       </c>
       <c r="AS42">
-        <v>1.7</v>
+        <v>1.74</v>
       </c>
       <c r="AT42">
-        <v>3.11</v>
+        <v>3.04</v>
       </c>
       <c r="AU42">
         <v>3</v>
@@ -9983,7 +9986,7 @@
         <v>118</v>
       </c>
       <c r="P43" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="Q43">
         <v>1.69</v>
@@ -10058,22 +10061,22 @@
         <v>3</v>
       </c>
       <c r="AO43">
-        <v>1.5</v>
+        <v>1.6</v>
       </c>
       <c r="AP43">
         <v>2.17</v>
       </c>
       <c r="AQ43">
-        <v>0.92</v>
+        <v>1.13</v>
       </c>
       <c r="AR43">
         <v>2.07</v>
       </c>
       <c r="AS43">
-        <v>1.2</v>
+        <v>1.22</v>
       </c>
       <c r="AT43">
-        <v>3.27</v>
+        <v>3.29</v>
       </c>
       <c r="AU43">
         <v>8</v>
@@ -10261,25 +10264,25 @@
         <v>1.35</v>
       </c>
       <c r="AN44">
-        <v>0</v>
+        <v>0.6</v>
       </c>
       <c r="AO44">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AP44">
-        <v>0.82</v>
+        <v>0.63</v>
       </c>
       <c r="AQ44">
-        <v>1</v>
+        <v>1.3</v>
       </c>
       <c r="AR44">
-        <v>1.16</v>
+        <v>1.04</v>
       </c>
       <c r="AS44">
-        <v>0.6</v>
+        <v>0.98</v>
       </c>
       <c r="AT44">
-        <v>1.76</v>
+        <v>2.02</v>
       </c>
       <c r="AU44">
         <v>6</v>
@@ -10467,25 +10470,25 @@
         <v>1.84</v>
       </c>
       <c r="AN45">
-        <v>3</v>
+        <v>1.5</v>
       </c>
       <c r="AO45">
-        <v>1.5</v>
+        <v>1.4</v>
       </c>
       <c r="AP45">
-        <v>2.45</v>
+        <v>2</v>
       </c>
       <c r="AQ45">
-        <v>1</v>
+        <v>1.21</v>
       </c>
       <c r="AR45">
-        <v>1.87</v>
+        <v>1.75</v>
       </c>
       <c r="AS45">
-        <v>1.68</v>
+        <v>1.47</v>
       </c>
       <c r="AT45">
-        <v>3.55</v>
+        <v>3.22</v>
       </c>
       <c r="AU45">
         <v>8</v>
@@ -10673,25 +10676,25 @@
         <v>1.67</v>
       </c>
       <c r="AN46">
-        <v>1</v>
+        <v>0.6</v>
       </c>
       <c r="AO46">
         <v>0</v>
       </c>
       <c r="AP46">
-        <v>0.91</v>
+        <v>0.65</v>
       </c>
       <c r="AQ46">
-        <v>0.09</v>
+        <v>0.17</v>
       </c>
       <c r="AR46">
         <v>0.97</v>
       </c>
       <c r="AS46">
-        <v>0.86</v>
+        <v>1.15</v>
       </c>
       <c r="AT46">
-        <v>1.83</v>
+        <v>2.12</v>
       </c>
       <c r="AU46">
         <v>6</v>
@@ -10879,25 +10882,25 @@
         <v>1.3</v>
       </c>
       <c r="AN47">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AO47">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AP47">
-        <v>1.46</v>
+        <v>1.17</v>
       </c>
       <c r="AQ47">
-        <v>1.62</v>
+        <v>2</v>
       </c>
       <c r="AR47">
-        <v>1.77</v>
+        <v>1.67</v>
       </c>
       <c r="AS47">
-        <v>1.63</v>
+        <v>1.74</v>
       </c>
       <c r="AT47">
-        <v>3.4</v>
+        <v>3.41</v>
       </c>
       <c r="AU47">
         <v>3</v>
@@ -11088,22 +11091,22 @@
         <v>0</v>
       </c>
       <c r="AO48">
-        <v>1.33</v>
+        <v>1.17</v>
       </c>
       <c r="AP48">
-        <v>0.23</v>
+        <v>0.17</v>
       </c>
       <c r="AQ48">
-        <v>1.45</v>
+        <v>1.25</v>
       </c>
       <c r="AR48">
-        <v>1.34</v>
+        <v>1.17</v>
       </c>
       <c r="AS48">
-        <v>1.42</v>
+        <v>1.55</v>
       </c>
       <c r="AT48">
-        <v>2.76</v>
+        <v>2.72</v>
       </c>
       <c r="AU48">
         <v>6</v>
@@ -11291,25 +11294,25 @@
         <v>1.73</v>
       </c>
       <c r="AN49">
+        <v>1.5</v>
+      </c>
+      <c r="AO49">
         <v>1.67</v>
       </c>
-      <c r="AO49">
-        <v>2</v>
-      </c>
       <c r="AP49">
-        <v>1.36</v>
+        <v>1.13</v>
       </c>
       <c r="AQ49">
-        <v>1.25</v>
+        <v>1.67</v>
       </c>
       <c r="AR49">
-        <v>1.24</v>
+        <v>1.18</v>
       </c>
       <c r="AS49">
-        <v>1.21</v>
+        <v>1.37</v>
       </c>
       <c r="AT49">
-        <v>2.45</v>
+        <v>2.55</v>
       </c>
       <c r="AU49">
         <v>0</v>
@@ -11425,7 +11428,7 @@
         <v>88</v>
       </c>
       <c r="P50" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="Q50">
         <v>5.1</v>
@@ -11497,25 +11500,25 @@
         <v>1.15</v>
       </c>
       <c r="AN50">
-        <v>3</v>
+        <v>1.5</v>
       </c>
       <c r="AO50">
-        <v>3</v>
+        <v>2.67</v>
       </c>
       <c r="AP50">
-        <v>1.58</v>
+        <v>1.3</v>
       </c>
       <c r="AQ50">
         <v>2.17</v>
       </c>
       <c r="AR50">
-        <v>1.24</v>
+        <v>1.07</v>
       </c>
       <c r="AS50">
-        <v>2.07</v>
+        <v>2.06</v>
       </c>
       <c r="AT50">
-        <v>3.31</v>
+        <v>3.13</v>
       </c>
       <c r="AU50">
         <v>3</v>
@@ -11703,25 +11706,25 @@
         <v>1.82</v>
       </c>
       <c r="AN51">
-        <v>0.33</v>
+        <v>1.17</v>
       </c>
       <c r="AO51">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AP51">
-        <v>1.46</v>
+        <v>1.17</v>
       </c>
       <c r="AQ51">
-        <v>0.42</v>
+        <v>0.65</v>
       </c>
       <c r="AR51">
-        <v>1.76</v>
+        <v>1.68</v>
       </c>
       <c r="AS51">
-        <v>0.97</v>
+        <v>1.04</v>
       </c>
       <c r="AT51">
-        <v>2.73</v>
+        <v>2.72</v>
       </c>
       <c r="AU51">
         <v>7</v>
@@ -11837,7 +11840,7 @@
         <v>122</v>
       </c>
       <c r="P52" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="Q52">
         <v>3</v>
@@ -11909,25 +11912,25 @@
         <v>1.52</v>
       </c>
       <c r="AN52">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AO52">
-        <v>0.33</v>
+        <v>1.67</v>
       </c>
       <c r="AP52">
-        <v>1.67</v>
+        <v>1.46</v>
       </c>
       <c r="AQ52">
-        <v>1.62</v>
+        <v>2</v>
       </c>
       <c r="AR52">
-        <v>1.61</v>
+        <v>1.38</v>
       </c>
       <c r="AS52">
-        <v>1.34</v>
+        <v>1.58</v>
       </c>
       <c r="AT52">
-        <v>2.95</v>
+        <v>2.96</v>
       </c>
       <c r="AU52">
         <v>7</v>
@@ -12115,25 +12118,25 @@
         <v>7.5</v>
       </c>
       <c r="AN53">
-        <v>3</v>
+        <v>2.6</v>
       </c>
       <c r="AO53">
         <v>1</v>
       </c>
       <c r="AP53">
-        <v>3</v>
+        <v>2.71</v>
       </c>
       <c r="AQ53">
-        <v>0.46</v>
+        <v>0.63</v>
       </c>
       <c r="AR53">
-        <v>2.35</v>
+        <v>1.95</v>
       </c>
       <c r="AS53">
-        <v>0.96</v>
+        <v>1.1</v>
       </c>
       <c r="AT53">
-        <v>3.31</v>
+        <v>3.05</v>
       </c>
       <c r="AU53">
         <v>10</v>
@@ -12249,7 +12252,7 @@
         <v>124</v>
       </c>
       <c r="P54" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="Q54">
         <v>3</v>
@@ -12321,25 +12324,25 @@
         <v>1.56</v>
       </c>
       <c r="AN54">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="AO54">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AP54">
-        <v>1.33</v>
+        <v>1.04</v>
       </c>
       <c r="AQ54">
-        <v>1.25</v>
+        <v>1.42</v>
       </c>
       <c r="AR54">
-        <v>1.4</v>
+        <v>1.32</v>
       </c>
       <c r="AS54">
-        <v>1.44</v>
+        <v>1.55</v>
       </c>
       <c r="AT54">
-        <v>2.84</v>
+        <v>2.87</v>
       </c>
       <c r="AU54">
         <v>3</v>
@@ -12527,25 +12530,25 @@
         <v>1.28</v>
       </c>
       <c r="AN55">
-        <v>1.33</v>
+        <v>1.17</v>
       </c>
       <c r="AO55">
-        <v>2.33</v>
+        <v>2.6</v>
       </c>
       <c r="AP55">
-        <v>1.42</v>
+        <v>1.21</v>
       </c>
       <c r="AQ55">
-        <v>1.92</v>
+        <v>2.17</v>
       </c>
       <c r="AR55">
-        <v>1.32</v>
+        <v>1.44</v>
       </c>
       <c r="AS55">
-        <v>1.32</v>
+        <v>1.53</v>
       </c>
       <c r="AT55">
-        <v>2.64</v>
+        <v>2.97</v>
       </c>
       <c r="AU55">
         <v>7</v>
@@ -12661,7 +12664,7 @@
         <v>125</v>
       </c>
       <c r="P56" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="Q56">
         <v>1.85</v>
@@ -12733,25 +12736,25 @@
         <v>2.75</v>
       </c>
       <c r="AN56">
+        <v>2.33</v>
+      </c>
+      <c r="AO56">
+        <v>1.83</v>
+      </c>
+      <c r="AP56">
+        <v>2.17</v>
+      </c>
+      <c r="AQ56">
+        <v>1.46</v>
+      </c>
+      <c r="AR56">
+        <v>1.52</v>
+      </c>
+      <c r="AS56">
+        <v>1.48</v>
+      </c>
+      <c r="AT56">
         <v>3</v>
-      </c>
-      <c r="AO56">
-        <v>1.33</v>
-      </c>
-      <c r="AP56">
-        <v>2.42</v>
-      </c>
-      <c r="AQ56">
-        <v>1.25</v>
-      </c>
-      <c r="AR56">
-        <v>1.85</v>
-      </c>
-      <c r="AS56">
-        <v>1.22</v>
-      </c>
-      <c r="AT56">
-        <v>3.07</v>
       </c>
       <c r="AU56">
         <v>7</v>
@@ -12867,7 +12870,7 @@
         <v>88</v>
       </c>
       <c r="P57" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="Q57">
         <v>5.88</v>
@@ -12939,25 +12942,25 @@
         <v>1.14</v>
       </c>
       <c r="AN57">
-        <v>3</v>
+        <v>1.5</v>
       </c>
       <c r="AO57">
-        <v>2</v>
+        <v>2.67</v>
       </c>
       <c r="AP57">
-        <v>1.58</v>
+        <v>1.42</v>
       </c>
       <c r="AQ57">
-        <v>2.42</v>
+        <v>2.71</v>
       </c>
       <c r="AR57">
-        <v>1.7</v>
+        <v>1.57</v>
       </c>
       <c r="AS57">
-        <v>1.36</v>
+        <v>2.01</v>
       </c>
       <c r="AT57">
-        <v>3.06</v>
+        <v>3.58</v>
       </c>
       <c r="AU57">
         <v>4</v>
@@ -13145,25 +13148,25 @@
         <v>1.57</v>
       </c>
       <c r="AN58">
-        <v>2.25</v>
+        <v>1.29</v>
       </c>
       <c r="AO58">
-        <v>1.33</v>
+        <v>1.43</v>
       </c>
       <c r="AP58">
-        <v>1.58</v>
+        <v>1.3</v>
       </c>
       <c r="AQ58">
-        <v>0.92</v>
+        <v>1.13</v>
       </c>
       <c r="AR58">
-        <v>1.32</v>
+        <v>1.14</v>
       </c>
       <c r="AS58">
-        <v>1.12</v>
+        <v>1.14</v>
       </c>
       <c r="AT58">
-        <v>2.44</v>
+        <v>2.28</v>
       </c>
       <c r="AU58">
         <v>4</v>
@@ -13279,7 +13282,7 @@
         <v>127</v>
       </c>
       <c r="P59" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="Q59">
         <v>3.86</v>
@@ -13351,25 +13354,25 @@
         <v>1.32</v>
       </c>
       <c r="AN59">
-        <v>0.75</v>
+        <v>0.43</v>
       </c>
       <c r="AO59">
-        <v>0.5</v>
+        <v>1.57</v>
       </c>
       <c r="AP59">
-        <v>1.33</v>
+        <v>1.04</v>
       </c>
       <c r="AQ59">
+        <v>2</v>
+      </c>
+      <c r="AR59">
+        <v>1.35</v>
+      </c>
+      <c r="AS59">
         <v>1.62</v>
       </c>
-      <c r="AR59">
-        <v>1.44</v>
-      </c>
-      <c r="AS59">
-        <v>1.47</v>
-      </c>
       <c r="AT59">
-        <v>2.91</v>
+        <v>2.97</v>
       </c>
       <c r="AU59">
         <v>8</v>
@@ -13557,22 +13560,22 @@
         <v>1.49</v>
       </c>
       <c r="AN60">
-        <v>0.5</v>
+        <v>1.14</v>
       </c>
       <c r="AO60">
-        <v>1.75</v>
+        <v>1.57</v>
       </c>
       <c r="AP60">
-        <v>1.46</v>
+        <v>1.17</v>
       </c>
       <c r="AQ60">
-        <v>1.25</v>
+        <v>1.67</v>
       </c>
       <c r="AR60">
-        <v>1.83</v>
+        <v>1.73</v>
       </c>
       <c r="AS60">
-        <v>1.29</v>
+        <v>1.39</v>
       </c>
       <c r="AT60">
         <v>3.12</v>
@@ -13763,25 +13766,25 @@
         <v>2.55</v>
       </c>
       <c r="AN61">
-        <v>3</v>
+        <v>2.71</v>
       </c>
       <c r="AO61">
-        <v>2</v>
+        <v>2.43</v>
       </c>
       <c r="AP61">
-        <v>3</v>
+        <v>2.71</v>
       </c>
       <c r="AQ61">
-        <v>1.92</v>
+        <v>2.17</v>
       </c>
       <c r="AR61">
-        <v>2.33</v>
+        <v>1.98</v>
       </c>
       <c r="AS61">
-        <v>1.35</v>
+        <v>1.56</v>
       </c>
       <c r="AT61">
-        <v>3.68</v>
+        <v>3.54</v>
       </c>
       <c r="AU61">
         <v>12</v>
@@ -13897,7 +13900,7 @@
         <v>130</v>
       </c>
       <c r="P62" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="Q62">
         <v>1.83</v>
@@ -13969,25 +13972,25 @@
         <v>2.85</v>
       </c>
       <c r="AN62">
-        <v>2</v>
+        <v>1.29</v>
       </c>
       <c r="AO62">
-        <v>0.75</v>
+        <v>0.86</v>
       </c>
       <c r="AP62">
-        <v>1.58</v>
+        <v>1.42</v>
       </c>
       <c r="AQ62">
-        <v>0.46</v>
+        <v>0.63</v>
       </c>
       <c r="AR62">
-        <v>1.42</v>
+        <v>1.47</v>
       </c>
       <c r="AS62">
-        <v>1.06</v>
+        <v>1.13</v>
       </c>
       <c r="AT62">
-        <v>2.48</v>
+        <v>2.6</v>
       </c>
       <c r="AU62">
         <v>7</v>
@@ -14103,7 +14106,7 @@
         <v>88</v>
       </c>
       <c r="P63" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="Q63">
         <v>8.77</v>
@@ -14175,25 +14178,25 @@
         <v>1.04</v>
       </c>
       <c r="AN63">
-        <v>0.25</v>
+        <v>0.14</v>
       </c>
       <c r="AO63">
-        <v>3</v>
+        <v>2.71</v>
       </c>
       <c r="AP63">
-        <v>0.23</v>
+        <v>0.17</v>
       </c>
       <c r="AQ63">
         <v>2.17</v>
       </c>
       <c r="AR63">
-        <v>1.37</v>
+        <v>1.21</v>
       </c>
       <c r="AS63">
-        <v>1.88</v>
+        <v>1.95</v>
       </c>
       <c r="AT63">
-        <v>3.25</v>
+        <v>3.16</v>
       </c>
       <c r="AU63">
         <v>4</v>
@@ -14381,25 +14384,25 @@
         <v>2.3</v>
       </c>
       <c r="AN64">
-        <v>2.33</v>
+        <v>1.57</v>
       </c>
       <c r="AO64">
-        <v>0.33</v>
+        <v>1</v>
       </c>
       <c r="AP64">
-        <v>1.67</v>
+        <v>1.46</v>
       </c>
       <c r="AQ64">
-        <v>0.42</v>
+        <v>0.65</v>
       </c>
       <c r="AR64">
-        <v>1.75</v>
+        <v>1.48</v>
       </c>
       <c r="AS64">
-        <v>0.87</v>
+        <v>0.99</v>
       </c>
       <c r="AT64">
-        <v>2.62</v>
+        <v>2.47</v>
       </c>
       <c r="AU64">
         <v>6</v>
@@ -14515,7 +14518,7 @@
         <v>132</v>
       </c>
       <c r="P65" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="Q65">
         <v>2.4</v>
@@ -14587,25 +14590,25 @@
         <v>2.02</v>
       </c>
       <c r="AN65">
+        <v>1.14</v>
+      </c>
+      <c r="AO65">
+        <v>1.14</v>
+      </c>
+      <c r="AP65">
+        <v>1.21</v>
+      </c>
+      <c r="AQ65">
         <v>1.25</v>
       </c>
-      <c r="AO65">
-        <v>1.25</v>
-      </c>
-      <c r="AP65">
-        <v>1.42</v>
-      </c>
-      <c r="AQ65">
-        <v>1.45</v>
-      </c>
       <c r="AR65">
-        <v>1.42</v>
+        <v>1.47</v>
       </c>
       <c r="AS65">
-        <v>1.5</v>
+        <v>1.58</v>
       </c>
       <c r="AT65">
-        <v>2.92</v>
+        <v>3.05</v>
       </c>
       <c r="AU65">
         <v>7</v>
@@ -14721,7 +14724,7 @@
         <v>133</v>
       </c>
       <c r="P66" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="Q66">
         <v>1.55</v>
@@ -14793,25 +14796,25 @@
         <v>4.4</v>
       </c>
       <c r="AN66">
-        <v>2.33</v>
+        <v>2.75</v>
       </c>
       <c r="AO66">
-        <v>1</v>
+        <v>1.75</v>
       </c>
       <c r="AP66">
         <v>2.17</v>
       </c>
       <c r="AQ66">
-        <v>1.25</v>
+        <v>1.46</v>
       </c>
       <c r="AR66">
-        <v>2.05</v>
+        <v>2</v>
       </c>
       <c r="AS66">
-        <v>1.28</v>
+        <v>1.47</v>
       </c>
       <c r="AT66">
-        <v>3.33</v>
+        <v>3.47</v>
       </c>
       <c r="AU66">
         <v>6</v>
@@ -14927,7 +14930,7 @@
         <v>134</v>
       </c>
       <c r="P67" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="Q67">
         <v>4</v>
@@ -14999,25 +15002,25 @@
         <v>1.27</v>
       </c>
       <c r="AN67">
-        <v>1.5</v>
+        <v>0.88</v>
       </c>
       <c r="AO67">
-        <v>1</v>
+        <v>1.13</v>
       </c>
       <c r="AP67">
-        <v>0.91</v>
+        <v>0.65</v>
       </c>
       <c r="AQ67">
-        <v>1</v>
+        <v>1.21</v>
       </c>
       <c r="AR67">
-        <v>1.08</v>
+        <v>0.99</v>
       </c>
       <c r="AS67">
-        <v>1.55</v>
+        <v>1.49</v>
       </c>
       <c r="AT67">
-        <v>2.63</v>
+        <v>2.48</v>
       </c>
       <c r="AU67">
         <v>4</v>
@@ -15133,7 +15136,7 @@
         <v>88</v>
       </c>
       <c r="P68" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="Q68">
         <v>3.1</v>
@@ -15205,25 +15208,25 @@
         <v>1.48</v>
       </c>
       <c r="AN68">
-        <v>1</v>
+        <v>0.88</v>
       </c>
       <c r="AO68">
-        <v>0</v>
+        <v>0.38</v>
       </c>
       <c r="AP68">
-        <v>0.82</v>
+        <v>0.63</v>
       </c>
       <c r="AQ68">
-        <v>0.75</v>
+        <v>1.04</v>
       </c>
       <c r="AR68">
-        <v>1.23</v>
+        <v>1.11</v>
       </c>
       <c r="AS68">
-        <v>1.24</v>
+        <v>1.39</v>
       </c>
       <c r="AT68">
-        <v>2.47</v>
+        <v>2.5</v>
       </c>
       <c r="AU68">
         <v>3</v>
@@ -15411,25 +15414,25 @@
         <v>1.95</v>
       </c>
       <c r="AN69">
-        <v>1.5</v>
+        <v>1.25</v>
       </c>
       <c r="AO69">
-        <v>2</v>
+        <v>1.38</v>
       </c>
       <c r="AP69">
-        <v>1.36</v>
+        <v>1.13</v>
       </c>
       <c r="AQ69">
-        <v>0.8</v>
+        <v>1.17</v>
       </c>
       <c r="AR69">
-        <v>1.16</v>
+        <v>1.07</v>
       </c>
       <c r="AS69">
-        <v>1.61</v>
+        <v>1.74</v>
       </c>
       <c r="AT69">
-        <v>2.77</v>
+        <v>2.81</v>
       </c>
       <c r="AU69">
         <v>3</v>
@@ -15617,25 +15620,25 @@
         <v>1.55</v>
       </c>
       <c r="AN70">
-        <v>1.33</v>
+        <v>1.38</v>
       </c>
       <c r="AO70">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AP70">
-        <v>2.08</v>
+        <v>1.67</v>
       </c>
       <c r="AQ70">
-        <v>1</v>
+        <v>1.3</v>
       </c>
       <c r="AR70">
-        <v>1.53</v>
+        <v>1.47</v>
       </c>
       <c r="AS70">
-        <v>0.89</v>
+        <v>1.15</v>
       </c>
       <c r="AT70">
-        <v>2.42</v>
+        <v>2.62</v>
       </c>
       <c r="AU70">
         <v>8</v>
@@ -15823,25 +15826,25 @@
         <v>3.3</v>
       </c>
       <c r="AN71">
-        <v>3</v>
+        <v>1.75</v>
       </c>
       <c r="AO71">
-        <v>0</v>
+        <v>0.13</v>
       </c>
       <c r="AP71">
-        <v>2.45</v>
+        <v>2</v>
       </c>
       <c r="AQ71">
-        <v>0.09</v>
+        <v>0.17</v>
       </c>
       <c r="AR71">
-        <v>1.82</v>
+        <v>1.6</v>
       </c>
       <c r="AS71">
-        <v>1</v>
+        <v>1.18</v>
       </c>
       <c r="AT71">
-        <v>2.82</v>
+        <v>2.78</v>
       </c>
       <c r="AU71">
         <v>7</v>
@@ -15957,7 +15960,7 @@
         <v>124</v>
       </c>
       <c r="P72" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="Q72">
         <v>1.88</v>
@@ -16029,25 +16032,25 @@
         <v>2.7</v>
       </c>
       <c r="AN72">
-        <v>3</v>
+        <v>2.13</v>
       </c>
       <c r="AO72">
-        <v>0.75</v>
+        <v>1.25</v>
       </c>
       <c r="AP72">
-        <v>2.42</v>
+        <v>2.17</v>
       </c>
       <c r="AQ72">
-        <v>1.25</v>
+        <v>1.42</v>
       </c>
       <c r="AR72">
-        <v>1.84</v>
+        <v>1.5</v>
       </c>
       <c r="AS72">
-        <v>1.5</v>
+        <v>1.49</v>
       </c>
       <c r="AT72">
-        <v>3.34</v>
+        <v>2.99</v>
       </c>
       <c r="AU72">
         <v>7</v>
@@ -16163,7 +16166,7 @@
         <v>88</v>
       </c>
       <c r="P73" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="Q73">
         <v>7</v>
@@ -16235,25 +16238,25 @@
         <v>1.03</v>
       </c>
       <c r="AN73">
-        <v>1</v>
+        <v>1.13</v>
       </c>
       <c r="AO73">
-        <v>2.33</v>
+        <v>2.75</v>
       </c>
       <c r="AP73">
-        <v>1.17</v>
+        <v>1.25</v>
       </c>
       <c r="AQ73">
-        <v>2.42</v>
+        <v>2.71</v>
       </c>
       <c r="AR73">
-        <v>1.68</v>
+        <v>1.53</v>
       </c>
       <c r="AS73">
-        <v>1.51</v>
+        <v>2.08</v>
       </c>
       <c r="AT73">
-        <v>3.19</v>
+        <v>3.61</v>
       </c>
       <c r="AU73">
         <v>0</v>
@@ -16441,25 +16444,25 @@
         <v>1.51</v>
       </c>
       <c r="AN74">
-        <v>1</v>
+        <v>1.22</v>
       </c>
       <c r="AO74">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AP74">
-        <v>1.46</v>
+        <v>1.17</v>
       </c>
       <c r="AQ74">
-        <v>1</v>
+        <v>1.3</v>
       </c>
       <c r="AR74">
-        <v>1.81</v>
+        <v>1.76</v>
       </c>
       <c r="AS74">
-        <v>1</v>
+        <v>1.17</v>
       </c>
       <c r="AT74">
-        <v>2.81</v>
+        <v>2.93</v>
       </c>
       <c r="AU74">
         <v>6</v>
@@ -16575,7 +16578,7 @@
         <v>138</v>
       </c>
       <c r="P75" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="Q75">
         <v>2.3</v>
@@ -16647,25 +16650,25 @@
         <v>1.98</v>
       </c>
       <c r="AN75">
-        <v>0.6</v>
+        <v>0.67</v>
       </c>
       <c r="AO75">
-        <v>0.25</v>
+        <v>0.78</v>
       </c>
       <c r="AP75">
-        <v>1.33</v>
+        <v>1.04</v>
       </c>
       <c r="AQ75">
-        <v>0.42</v>
+        <v>0.65</v>
       </c>
       <c r="AR75">
-        <v>1.49</v>
+        <v>1.43</v>
       </c>
       <c r="AS75">
-        <v>0.9</v>
+        <v>1.03</v>
       </c>
       <c r="AT75">
-        <v>2.39</v>
+        <v>2.46</v>
       </c>
       <c r="AU75">
         <v>5</v>
@@ -16781,7 +16784,7 @@
         <v>88</v>
       </c>
       <c r="P76" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="Q76">
         <v>3.7</v>
@@ -16853,25 +16856,25 @@
         <v>1.34</v>
       </c>
       <c r="AN76">
-        <v>0.2</v>
+        <v>0.11</v>
       </c>
       <c r="AO76">
-        <v>1</v>
+        <v>1.44</v>
       </c>
       <c r="AP76">
-        <v>0.23</v>
+        <v>0.17</v>
       </c>
       <c r="AQ76">
-        <v>0.92</v>
+        <v>1.13</v>
       </c>
       <c r="AR76">
-        <v>1.29</v>
+        <v>1.18</v>
       </c>
       <c r="AS76">
-        <v>0.99</v>
+        <v>1.06</v>
       </c>
       <c r="AT76">
-        <v>2.28</v>
+        <v>2.24</v>
       </c>
       <c r="AU76">
         <v>3</v>
@@ -16987,7 +16990,7 @@
         <v>88</v>
       </c>
       <c r="P77" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="Q77">
         <v>2.47</v>
@@ -17059,25 +17062,25 @@
         <v>1.85</v>
       </c>
       <c r="AN77">
-        <v>1.2</v>
+        <v>1.33</v>
       </c>
       <c r="AO77">
-        <v>1.4</v>
+        <v>1.56</v>
       </c>
       <c r="AP77">
-        <v>1.42</v>
+        <v>1.21</v>
       </c>
       <c r="AQ77">
-        <v>1.25</v>
+        <v>1.67</v>
       </c>
       <c r="AR77">
-        <v>1.45</v>
+        <v>1.59</v>
       </c>
       <c r="AS77">
-        <v>1.44</v>
+        <v>1.57</v>
       </c>
       <c r="AT77">
-        <v>2.89</v>
+        <v>3.16</v>
       </c>
       <c r="AU77">
         <v>3</v>
@@ -17265,25 +17268,25 @@
         <v>4.5</v>
       </c>
       <c r="AN78">
-        <v>2.5</v>
+        <v>2</v>
       </c>
       <c r="AO78">
-        <v>0.8</v>
+        <v>0.78</v>
       </c>
       <c r="AP78">
-        <v>2.42</v>
+        <v>2.17</v>
       </c>
       <c r="AQ78">
-        <v>0.46</v>
+        <v>0.63</v>
       </c>
       <c r="AR78">
-        <v>1.78</v>
+        <v>1.52</v>
       </c>
       <c r="AS78">
-        <v>1.03</v>
+        <v>1.07</v>
       </c>
       <c r="AT78">
-        <v>2.81</v>
+        <v>2.59</v>
       </c>
       <c r="AU78">
         <v>8</v>
@@ -17471,25 +17474,25 @@
         <v>1.48</v>
       </c>
       <c r="AN79">
-        <v>1.75</v>
+        <v>1.22</v>
       </c>
       <c r="AO79">
-        <v>1</v>
+        <v>1.89</v>
       </c>
       <c r="AP79">
-        <v>1.58</v>
+        <v>1.42</v>
       </c>
       <c r="AQ79">
+        <v>2</v>
+      </c>
+      <c r="AR79">
+        <v>1.37</v>
+      </c>
+      <c r="AS79">
         <v>1.62</v>
       </c>
-      <c r="AR79">
-        <v>1.49</v>
-      </c>
-      <c r="AS79">
-        <v>1.47</v>
-      </c>
       <c r="AT79">
-        <v>2.96</v>
+        <v>2.99</v>
       </c>
       <c r="AU79">
         <v>4</v>
@@ -17605,7 +17608,7 @@
         <v>140</v>
       </c>
       <c r="P80" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="Q80">
         <v>2.5</v>
@@ -17677,25 +17680,25 @@
         <v>1.9</v>
       </c>
       <c r="AN80">
-        <v>2.5</v>
+        <v>1.89</v>
       </c>
       <c r="AO80">
-        <v>1.2</v>
+        <v>1</v>
       </c>
       <c r="AP80">
-        <v>1.67</v>
+        <v>1.46</v>
       </c>
       <c r="AQ80">
-        <v>1.45</v>
+        <v>1.25</v>
       </c>
       <c r="AR80">
-        <v>1.66</v>
+        <v>1.41</v>
       </c>
       <c r="AS80">
-        <v>1.44</v>
+        <v>1.43</v>
       </c>
       <c r="AT80">
-        <v>3.1</v>
+        <v>2.84</v>
       </c>
       <c r="AU80">
         <v>5</v>
@@ -17811,7 +17814,7 @@
         <v>141</v>
       </c>
       <c r="P81" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="Q81">
         <v>2.38</v>
@@ -17883,25 +17886,25 @@
         <v>1.89</v>
       </c>
       <c r="AN81">
-        <v>3</v>
+        <v>2.78</v>
       </c>
       <c r="AO81">
-        <v>3</v>
+        <v>2.44</v>
       </c>
       <c r="AP81">
-        <v>3</v>
+        <v>2.71</v>
       </c>
       <c r="AQ81">
         <v>2.17</v>
       </c>
       <c r="AR81">
-        <v>2.43</v>
+        <v>2.1</v>
       </c>
       <c r="AS81">
-        <v>1.97</v>
+        <v>1.99</v>
       </c>
       <c r="AT81">
-        <v>4.4</v>
+        <v>4.09</v>
       </c>
       <c r="AU81">
         <v>6</v>
@@ -18017,7 +18020,7 @@
         <v>142</v>
       </c>
       <c r="P82" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="Q82">
         <v>2.8</v>
@@ -18089,25 +18092,25 @@
         <v>1.66</v>
       </c>
       <c r="AN82">
-        <v>2.4</v>
+        <v>1.3</v>
       </c>
       <c r="AO82">
-        <v>1.4</v>
+        <v>1.7</v>
       </c>
       <c r="AP82">
-        <v>1.58</v>
+        <v>1.3</v>
       </c>
       <c r="AQ82">
-        <v>1.25</v>
+        <v>1.46</v>
       </c>
       <c r="AR82">
-        <v>1.31</v>
+        <v>1.21</v>
       </c>
       <c r="AS82">
-        <v>1.21</v>
+        <v>1.41</v>
       </c>
       <c r="AT82">
-        <v>2.52</v>
+        <v>2.62</v>
       </c>
       <c r="AU82">
         <v>5</v>
@@ -18223,7 +18226,7 @@
         <v>143</v>
       </c>
       <c r="P83" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="Q83">
         <v>2.6</v>
@@ -18295,25 +18298,25 @@
         <v>1.78</v>
       </c>
       <c r="AN83">
-        <v>1.2</v>
+        <v>0.8</v>
       </c>
       <c r="AO83">
-        <v>0.67</v>
+        <v>0.7</v>
       </c>
       <c r="AP83">
-        <v>0.91</v>
+        <v>0.65</v>
       </c>
       <c r="AQ83">
-        <v>0.46</v>
+        <v>0.63</v>
       </c>
       <c r="AR83">
-        <v>1.14</v>
+        <v>1.01</v>
       </c>
       <c r="AS83">
-        <v>1.06</v>
+        <v>1.08</v>
       </c>
       <c r="AT83">
-        <v>2.2</v>
+        <v>2.09</v>
       </c>
       <c r="AU83">
         <v>7</v>
@@ -18429,7 +18432,7 @@
         <v>144</v>
       </c>
       <c r="P84" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="Q84">
         <v>3.4</v>
@@ -18501,25 +18504,25 @@
         <v>1.4</v>
       </c>
       <c r="AN84">
-        <v>3</v>
+        <v>1.8</v>
       </c>
       <c r="AO84">
-        <v>1.6</v>
+        <v>2.1</v>
       </c>
       <c r="AP84">
-        <v>2.45</v>
+        <v>2</v>
       </c>
       <c r="AQ84">
-        <v>1.92</v>
+        <v>2.17</v>
       </c>
       <c r="AR84">
-        <v>1.81</v>
+        <v>1.66</v>
       </c>
       <c r="AS84">
-        <v>1.3</v>
+        <v>1.56</v>
       </c>
       <c r="AT84">
-        <v>3.11</v>
+        <v>3.22</v>
       </c>
       <c r="AU84">
         <v>7</v>
@@ -18707,25 +18710,25 @@
         <v>3.75</v>
       </c>
       <c r="AN85">
-        <v>1.75</v>
+        <v>2.2</v>
       </c>
       <c r="AO85">
-        <v>1.5</v>
+        <v>1.2</v>
       </c>
       <c r="AP85">
         <v>2.17</v>
       </c>
       <c r="AQ85">
-        <v>1</v>
+        <v>1.21</v>
       </c>
       <c r="AR85">
-        <v>2.02</v>
+        <v>1.91</v>
       </c>
       <c r="AS85">
-        <v>1.77</v>
+        <v>1.54</v>
       </c>
       <c r="AT85">
-        <v>3.79</v>
+        <v>3.45</v>
       </c>
       <c r="AU85">
         <v>5</v>
@@ -18841,7 +18844,7 @@
         <v>146</v>
       </c>
       <c r="P86" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="Q86">
         <v>2.88</v>
@@ -18913,25 +18916,25 @@
         <v>1.57</v>
       </c>
       <c r="AN86">
-        <v>0.75</v>
+        <v>1.2</v>
       </c>
       <c r="AO86">
-        <v>0.8</v>
+        <v>1.2</v>
       </c>
       <c r="AP86">
-        <v>1.17</v>
+        <v>1.25</v>
       </c>
       <c r="AQ86">
-        <v>1.25</v>
+        <v>1.42</v>
       </c>
       <c r="AR86">
-        <v>1.41</v>
+        <v>1.44</v>
       </c>
       <c r="AS86">
-        <v>1.28</v>
+        <v>1.35</v>
       </c>
       <c r="AT86">
-        <v>2.69</v>
+        <v>2.79</v>
       </c>
       <c r="AU86">
         <v>8</v>
@@ -19119,25 +19122,25 @@
         <v>2.3</v>
       </c>
       <c r="AN87">
-        <v>1</v>
+        <v>1.2</v>
       </c>
       <c r="AO87">
-        <v>0</v>
+        <v>0.1</v>
       </c>
       <c r="AP87">
-        <v>1.46</v>
+        <v>1.17</v>
       </c>
       <c r="AQ87">
-        <v>0.09</v>
+        <v>0.17</v>
       </c>
       <c r="AR87">
-        <v>1.73</v>
+        <v>1.72</v>
       </c>
       <c r="AS87">
-        <v>1.04</v>
+        <v>1.21</v>
       </c>
       <c r="AT87">
-        <v>2.77</v>
+        <v>2.93</v>
       </c>
       <c r="AU87">
         <v>4</v>
@@ -19253,7 +19256,7 @@
         <v>88</v>
       </c>
       <c r="P88" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="Q88">
         <v>2.6</v>
@@ -19325,25 +19328,25 @@
         <v>1.85</v>
       </c>
       <c r="AN88">
-        <v>1.8</v>
+        <v>1.6</v>
       </c>
       <c r="AO88">
-        <v>0.75</v>
+        <v>0.7</v>
       </c>
       <c r="AP88">
-        <v>1.36</v>
+        <v>1.13</v>
       </c>
       <c r="AQ88">
-        <v>0.75</v>
+        <v>1.04</v>
       </c>
       <c r="AR88">
-        <v>1.12</v>
+        <v>1.1</v>
       </c>
       <c r="AS88">
-        <v>1.36</v>
+        <v>1.45</v>
       </c>
       <c r="AT88">
-        <v>2.48</v>
+        <v>2.55</v>
       </c>
       <c r="AU88">
         <v>3</v>
@@ -19459,7 +19462,7 @@
         <v>93</v>
       </c>
       <c r="P89" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="Q89">
         <v>6.5</v>
@@ -19531,25 +19534,25 @@
         <v>1.06</v>
       </c>
       <c r="AN89">
-        <v>1.75</v>
+        <v>1.7</v>
       </c>
       <c r="AO89">
-        <v>2.5</v>
+        <v>2.8</v>
       </c>
       <c r="AP89">
-        <v>2.08</v>
+        <v>1.67</v>
       </c>
       <c r="AQ89">
-        <v>2.42</v>
+        <v>2.71</v>
       </c>
       <c r="AR89">
-        <v>1.74</v>
+        <v>1.61</v>
       </c>
       <c r="AS89">
-        <v>1.69</v>
+        <v>2.06</v>
       </c>
       <c r="AT89">
-        <v>3.43</v>
+        <v>3.67</v>
       </c>
       <c r="AU89">
         <v>5</v>
@@ -19737,25 +19740,25 @@
         <v>1.96</v>
       </c>
       <c r="AN90">
-        <v>1</v>
+        <v>1.09</v>
       </c>
       <c r="AO90">
-        <v>1.4</v>
+        <v>1.45</v>
       </c>
       <c r="AP90">
-        <v>1.42</v>
+        <v>1.21</v>
       </c>
       <c r="AQ90">
-        <v>0.92</v>
+        <v>1.13</v>
       </c>
       <c r="AR90">
-        <v>1.39</v>
+        <v>1.48</v>
       </c>
       <c r="AS90">
-        <v>1.08</v>
+        <v>1.12</v>
       </c>
       <c r="AT90">
-        <v>2.47</v>
+        <v>2.6</v>
       </c>
       <c r="AU90">
         <v>8</v>
@@ -19871,7 +19874,7 @@
         <v>149</v>
       </c>
       <c r="P91" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="Q91">
         <v>4.7</v>
@@ -19943,25 +19946,25 @@
         <v>1.2</v>
       </c>
       <c r="AN91">
-        <v>0.75</v>
+        <v>0.64</v>
       </c>
       <c r="AO91">
-        <v>1</v>
+        <v>1.64</v>
       </c>
       <c r="AP91">
-        <v>0.82</v>
+        <v>0.63</v>
       </c>
       <c r="AQ91">
-        <v>1.62</v>
+        <v>2</v>
       </c>
       <c r="AR91">
-        <v>1.11</v>
+        <v>1.07</v>
       </c>
       <c r="AS91">
-        <v>1.55</v>
+        <v>1.7</v>
       </c>
       <c r="AT91">
-        <v>2.66</v>
+        <v>2.77</v>
       </c>
       <c r="AU91">
         <v>4</v>
@@ -20077,7 +20080,7 @@
         <v>88</v>
       </c>
       <c r="P92" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="Q92">
         <v>3.8</v>
@@ -20149,25 +20152,25 @@
         <v>1.32</v>
       </c>
       <c r="AN92">
+        <v>0.09</v>
+      </c>
+      <c r="AO92">
+        <v>1.27</v>
+      </c>
+      <c r="AP92">
         <v>0.17</v>
       </c>
-      <c r="AO92">
-        <v>0.2</v>
-      </c>
-      <c r="AP92">
-        <v>0.23</v>
-      </c>
       <c r="AQ92">
-        <v>1</v>
+        <v>1.3</v>
       </c>
       <c r="AR92">
-        <v>1.33</v>
+        <v>1.18</v>
       </c>
       <c r="AS92">
-        <v>1.11</v>
+        <v>1.28</v>
       </c>
       <c r="AT92">
-        <v>2.44</v>
+        <v>2.46</v>
       </c>
       <c r="AU92">
         <v>7</v>
@@ -20355,25 +20358,25 @@
         <v>1.6</v>
       </c>
       <c r="AN93">
-        <v>2</v>
+        <v>1.64</v>
       </c>
       <c r="AO93">
+        <v>1.55</v>
+      </c>
+      <c r="AP93">
+        <v>1.46</v>
+      </c>
+      <c r="AQ93">
         <v>1.67</v>
       </c>
-      <c r="AP93">
-        <v>1.67</v>
-      </c>
-      <c r="AQ93">
-        <v>1.25</v>
-      </c>
       <c r="AR93">
-        <v>1.61</v>
+        <v>1.34</v>
       </c>
       <c r="AS93">
-        <v>1.53</v>
+        <v>1.59</v>
       </c>
       <c r="AT93">
-        <v>3.14</v>
+        <v>2.93</v>
       </c>
       <c r="AU93">
         <v>5</v>
@@ -20489,7 +20492,7 @@
         <v>150</v>
       </c>
       <c r="P94" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="Q94">
         <v>3</v>
@@ -20561,25 +20564,25 @@
         <v>1.55</v>
       </c>
       <c r="AN94">
-        <v>0.67</v>
+        <v>0.91</v>
       </c>
       <c r="AO94">
-        <v>1.5</v>
+        <v>1.18</v>
       </c>
       <c r="AP94">
-        <v>1.33</v>
+        <v>1.04</v>
       </c>
       <c r="AQ94">
-        <v>1.45</v>
+        <v>1.25</v>
       </c>
       <c r="AR94">
-        <v>1.52</v>
+        <v>1.4</v>
       </c>
       <c r="AS94">
-        <v>1.47</v>
+        <v>1.44</v>
       </c>
       <c r="AT94">
-        <v>2.99</v>
+        <v>2.84</v>
       </c>
       <c r="AU94">
         <v>6</v>
@@ -20767,25 +20770,25 @@
         <v>2.05</v>
       </c>
       <c r="AN95">
-        <v>1.6</v>
+        <v>1.18</v>
       </c>
       <c r="AO95">
-        <v>1.5</v>
+        <v>1.36</v>
       </c>
       <c r="AP95">
-        <v>1.58</v>
+        <v>1.42</v>
       </c>
       <c r="AQ95">
-        <v>0.8</v>
+        <v>1.17</v>
       </c>
       <c r="AR95">
-        <v>1.43</v>
+        <v>1.35</v>
       </c>
       <c r="AS95">
-        <v>1.69</v>
+        <v>1.68</v>
       </c>
       <c r="AT95">
-        <v>3.12</v>
+        <v>3.03</v>
       </c>
       <c r="AU95">
         <v>8</v>
@@ -20973,25 +20976,25 @@
         <v>7.5</v>
       </c>
       <c r="AN96">
-        <v>3</v>
+        <v>2.82</v>
       </c>
       <c r="AO96">
-        <v>0.4</v>
+        <v>1</v>
       </c>
       <c r="AP96">
-        <v>3</v>
+        <v>2.71</v>
       </c>
       <c r="AQ96">
-        <v>0.42</v>
+        <v>0.65</v>
       </c>
       <c r="AR96">
-        <v>2.31</v>
+        <v>2</v>
       </c>
       <c r="AS96">
-        <v>0.89</v>
+        <v>1.03</v>
       </c>
       <c r="AT96">
-        <v>3.2</v>
+        <v>3.03</v>
       </c>
       <c r="AU96">
         <v>7</v>
@@ -21179,25 +21182,25 @@
         <v>1.55</v>
       </c>
       <c r="AN97">
-        <v>2.6</v>
+        <v>2.18</v>
       </c>
       <c r="AO97">
-        <v>2.5</v>
+        <v>2.27</v>
       </c>
       <c r="AP97">
-        <v>2.42</v>
+        <v>2.17</v>
       </c>
       <c r="AQ97">
         <v>2.17</v>
       </c>
       <c r="AR97">
-        <v>1.81</v>
+        <v>1.52</v>
       </c>
       <c r="AS97">
-        <v>1.84</v>
+        <v>1.87</v>
       </c>
       <c r="AT97">
-        <v>3.65</v>
+        <v>3.39</v>
       </c>
       <c r="AU97">
         <v>6</v>
@@ -21385,25 +21388,25 @@
         <v>1.33</v>
       </c>
       <c r="AN98">
-        <v>1.5</v>
+        <v>0.92</v>
       </c>
       <c r="AO98">
-        <v>0.83</v>
+        <v>1.17</v>
       </c>
       <c r="AP98">
-        <v>0.91</v>
+        <v>0.65</v>
       </c>
       <c r="AQ98">
-        <v>1.25</v>
+        <v>1.42</v>
       </c>
       <c r="AR98">
-        <v>1.15</v>
+        <v>1</v>
       </c>
       <c r="AS98">
-        <v>1.28</v>
+        <v>1.4</v>
       </c>
       <c r="AT98">
-        <v>2.43</v>
+        <v>2.4</v>
       </c>
       <c r="AU98">
         <v>4</v>
@@ -21591,25 +21594,25 @@
         <v>1.86</v>
       </c>
       <c r="AN99">
+        <v>1.5</v>
+      </c>
+      <c r="AO99">
+        <v>0.83</v>
+      </c>
+      <c r="AP99">
+        <v>1.67</v>
+      </c>
+      <c r="AQ99">
+        <v>1.04</v>
+      </c>
+      <c r="AR99">
+        <v>1.54</v>
+      </c>
+      <c r="AS99">
         <v>1.4</v>
       </c>
-      <c r="AO99">
-        <v>1.2</v>
-      </c>
-      <c r="AP99">
-        <v>2.08</v>
-      </c>
-      <c r="AQ99">
-        <v>0.75</v>
-      </c>
-      <c r="AR99">
-        <v>1.65</v>
-      </c>
-      <c r="AS99">
-        <v>1.25</v>
-      </c>
       <c r="AT99">
-        <v>2.9</v>
+        <v>2.94</v>
       </c>
       <c r="AU99">
         <v>8</v>
@@ -21797,25 +21800,25 @@
         <v>1.67</v>
       </c>
       <c r="AN100">
-        <v>1.29</v>
+        <v>1.33</v>
       </c>
       <c r="AO100">
-        <v>1.33</v>
+        <v>1.58</v>
       </c>
       <c r="AP100">
+        <v>1.17</v>
+      </c>
+      <c r="AQ100">
         <v>1.46</v>
       </c>
-      <c r="AQ100">
-        <v>1.25</v>
-      </c>
       <c r="AR100">
-        <v>1.67</v>
+        <v>1.72</v>
       </c>
       <c r="AS100">
-        <v>1.11</v>
+        <v>1.35</v>
       </c>
       <c r="AT100">
-        <v>2.78</v>
+        <v>3.07</v>
       </c>
       <c r="AU100">
         <v>5</v>
@@ -21931,7 +21934,7 @@
         <v>156</v>
       </c>
       <c r="P101" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="Q101">
         <v>1.83</v>
@@ -22003,25 +22006,25 @@
         <v>3</v>
       </c>
       <c r="AN101">
-        <v>2</v>
+        <v>2.08</v>
       </c>
       <c r="AO101">
-        <v>1.29</v>
+        <v>1.75</v>
       </c>
       <c r="AP101">
         <v>2.17</v>
       </c>
       <c r="AQ101">
-        <v>1.62</v>
+        <v>2</v>
       </c>
       <c r="AR101">
-        <v>1.9</v>
+        <v>1.79</v>
       </c>
       <c r="AS101">
-        <v>1.63</v>
+        <v>1.73</v>
       </c>
       <c r="AT101">
-        <v>3.53</v>
+        <v>3.52</v>
       </c>
       <c r="AU101">
         <v>5</v>
@@ -22209,25 +22212,25 @@
         <v>1.24</v>
       </c>
       <c r="AN102">
-        <v>0.14</v>
+        <v>0.08</v>
       </c>
       <c r="AO102">
-        <v>1.2</v>
+        <v>1.25</v>
       </c>
       <c r="AP102">
-        <v>0.23</v>
+        <v>0.17</v>
       </c>
       <c r="AQ102">
-        <v>1</v>
+        <v>1.21</v>
       </c>
       <c r="AR102">
-        <v>1.41</v>
+        <v>1.24</v>
       </c>
       <c r="AS102">
-        <v>1.6</v>
+        <v>1.54</v>
       </c>
       <c r="AT102">
-        <v>3.01</v>
+        <v>2.78</v>
       </c>
       <c r="AU102">
         <v>5</v>
@@ -22415,25 +22418,25 @@
         <v>2.45</v>
       </c>
       <c r="AN103">
-        <v>0.8</v>
+        <v>1.33</v>
       </c>
       <c r="AO103">
-        <v>0.57</v>
+        <v>0.58</v>
       </c>
       <c r="AP103">
-        <v>1.17</v>
+        <v>1.25</v>
       </c>
       <c r="AQ103">
-        <v>0.46</v>
+        <v>0.63</v>
       </c>
       <c r="AR103">
-        <v>1.41</v>
+        <v>1.4</v>
       </c>
       <c r="AS103">
-        <v>1.04</v>
+        <v>1.08</v>
       </c>
       <c r="AT103">
-        <v>2.45</v>
+        <v>2.48</v>
       </c>
       <c r="AU103">
         <v>5</v>
@@ -22621,25 +22624,25 @@
         <v>1.2</v>
       </c>
       <c r="AN104">
-        <v>1.5</v>
+        <v>1.33</v>
       </c>
       <c r="AO104">
-        <v>1.83</v>
+        <v>2.25</v>
       </c>
       <c r="AP104">
-        <v>1.36</v>
+        <v>1.13</v>
       </c>
       <c r="AQ104">
-        <v>1.92</v>
+        <v>2.17</v>
       </c>
       <c r="AR104">
-        <v>1.15</v>
+        <v>1.09</v>
       </c>
       <c r="AS104">
-        <v>1.29</v>
+        <v>1.51</v>
       </c>
       <c r="AT104">
-        <v>2.44</v>
+        <v>2.6</v>
       </c>
       <c r="AU104">
         <v>3</v>
@@ -22827,25 +22830,25 @@
         <v>1.05</v>
       </c>
       <c r="AN105">
-        <v>2.17</v>
+        <v>1.42</v>
       </c>
       <c r="AO105">
-        <v>2.6</v>
+        <v>2.83</v>
       </c>
       <c r="AP105">
-        <v>1.58</v>
+        <v>1.3</v>
       </c>
       <c r="AQ105">
-        <v>2.42</v>
+        <v>2.71</v>
       </c>
       <c r="AR105">
-        <v>1.41</v>
+        <v>1.29</v>
       </c>
       <c r="AS105">
-        <v>1.63</v>
+        <v>1.97</v>
       </c>
       <c r="AT105">
-        <v>3.04</v>
+        <v>3.26</v>
       </c>
       <c r="AU105">
         <v>2</v>
@@ -23033,25 +23036,25 @@
         <v>3.72</v>
       </c>
       <c r="AN106">
-        <v>2.4</v>
+        <v>1.85</v>
       </c>
       <c r="AO106">
-        <v>0.33</v>
+        <v>0.85</v>
       </c>
       <c r="AP106">
-        <v>2.45</v>
+        <v>2</v>
       </c>
       <c r="AQ106">
-        <v>0.42</v>
+        <v>0.65</v>
       </c>
       <c r="AR106">
-        <v>1.87</v>
+        <v>1.72</v>
       </c>
       <c r="AS106">
-        <v>0.84</v>
+        <v>1.04</v>
       </c>
       <c r="AT106">
-        <v>2.71</v>
+        <v>2.76</v>
       </c>
       <c r="AU106">
         <v>8</v>
@@ -23239,22 +23242,22 @@
         <v>1.24</v>
       </c>
       <c r="AN107">
-        <v>0.6</v>
+        <v>0.62</v>
       </c>
       <c r="AO107">
-        <v>1.57</v>
+        <v>1.62</v>
       </c>
       <c r="AP107">
-        <v>0.82</v>
+        <v>0.63</v>
       </c>
       <c r="AQ107">
-        <v>1.25</v>
+        <v>1.67</v>
       </c>
       <c r="AR107">
-        <v>1.14</v>
+        <v>1.06</v>
       </c>
       <c r="AS107">
-        <v>1.46</v>
+        <v>1.54</v>
       </c>
       <c r="AT107">
         <v>2.6</v>
@@ -23445,25 +23448,25 @@
         <v>1.91</v>
       </c>
       <c r="AN108">
-        <v>1.29</v>
+        <v>1.23</v>
       </c>
       <c r="AO108">
-        <v>0.67</v>
+        <v>1.38</v>
       </c>
       <c r="AP108">
-        <v>1.42</v>
+        <v>1.21</v>
       </c>
       <c r="AQ108">
-        <v>1</v>
+        <v>1.3</v>
       </c>
       <c r="AR108">
-        <v>1.5</v>
+        <v>1.51</v>
       </c>
       <c r="AS108">
-        <v>1.16</v>
+        <v>1.25</v>
       </c>
       <c r="AT108">
-        <v>2.66</v>
+        <v>2.76</v>
       </c>
       <c r="AU108">
         <v>7</v>
@@ -23579,7 +23582,7 @@
         <v>161</v>
       </c>
       <c r="P109" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="Q109">
         <v>2.24</v>
@@ -23651,25 +23654,25 @@
         <v>2.08</v>
       </c>
       <c r="AN109">
-        <v>0.57</v>
+        <v>0.77</v>
       </c>
       <c r="AO109">
-        <v>0</v>
+        <v>0.15</v>
       </c>
       <c r="AP109">
-        <v>1.33</v>
+        <v>1.04</v>
       </c>
       <c r="AQ109">
-        <v>0.09</v>
+        <v>0.17</v>
       </c>
       <c r="AR109">
-        <v>1.51</v>
+        <v>1.4</v>
       </c>
       <c r="AS109">
-        <v>1.01</v>
+        <v>1.24</v>
       </c>
       <c r="AT109">
-        <v>2.52</v>
+        <v>2.64</v>
       </c>
       <c r="AU109">
         <v>10</v>
@@ -23785,7 +23788,7 @@
         <v>162</v>
       </c>
       <c r="P110" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="Q110">
         <v>4.6</v>
@@ -23857,25 +23860,25 @@
         <v>1.14</v>
       </c>
       <c r="AN110">
-        <v>1.5</v>
+        <v>1.31</v>
       </c>
       <c r="AO110">
-        <v>2.14</v>
+        <v>1.92</v>
       </c>
       <c r="AP110">
-        <v>1.58</v>
+        <v>1.42</v>
       </c>
       <c r="AQ110">
         <v>2.17</v>
       </c>
       <c r="AR110">
-        <v>1.51</v>
+        <v>1.39</v>
       </c>
       <c r="AS110">
-        <v>1.71</v>
+        <v>1.79</v>
       </c>
       <c r="AT110">
-        <v>3.22</v>
+        <v>3.18</v>
       </c>
       <c r="AU110">
         <v>4</v>
@@ -24063,25 +24066,25 @@
         <v>0</v>
       </c>
       <c r="AN111">
-        <v>2.67</v>
+        <v>2.08</v>
       </c>
       <c r="AO111">
-        <v>1.71</v>
+        <v>1.31</v>
       </c>
       <c r="AP111">
-        <v>2.42</v>
+        <v>2.17</v>
       </c>
       <c r="AQ111">
-        <v>1.45</v>
+        <v>1.25</v>
       </c>
       <c r="AR111">
-        <v>1.73</v>
+        <v>1.44</v>
       </c>
       <c r="AS111">
-        <v>1.4</v>
+        <v>1.42</v>
       </c>
       <c r="AT111">
-        <v>3.13</v>
+        <v>2.86</v>
       </c>
       <c r="AU111">
         <v>6</v>
@@ -24197,7 +24200,7 @@
         <v>164</v>
       </c>
       <c r="P112" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="Q112">
         <v>1.44</v>
@@ -24269,25 +24272,25 @@
         <v>4.8</v>
       </c>
       <c r="AN112">
-        <v>3</v>
+        <v>2.69</v>
       </c>
       <c r="AO112">
-        <v>1.4</v>
+        <v>1.46</v>
       </c>
       <c r="AP112">
-        <v>3</v>
+        <v>2.71</v>
       </c>
       <c r="AQ112">
-        <v>0.8</v>
+        <v>1.17</v>
       </c>
       <c r="AR112">
-        <v>2.21</v>
+        <v>1.93</v>
       </c>
       <c r="AS112">
-        <v>1.8</v>
+        <v>1.7</v>
       </c>
       <c r="AT112">
-        <v>4.01</v>
+        <v>3.63</v>
       </c>
       <c r="AU112">
         <v>16</v>
@@ -24403,7 +24406,7 @@
         <v>165</v>
       </c>
       <c r="P113" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="Q113">
         <v>3.25</v>
@@ -24475,25 +24478,25 @@
         <v>1.47</v>
       </c>
       <c r="AN113">
+        <v>1.5</v>
+      </c>
+      <c r="AO113">
+        <v>1.93</v>
+      </c>
+      <c r="AP113">
         <v>1.67</v>
       </c>
-      <c r="AO113">
+      <c r="AQ113">
+        <v>2</v>
+      </c>
+      <c r="AR113">
         <v>1.5</v>
       </c>
-      <c r="AP113">
-        <v>2.08</v>
-      </c>
-      <c r="AQ113">
-        <v>1.62</v>
-      </c>
-      <c r="AR113">
-        <v>1.63</v>
-      </c>
       <c r="AS113">
-        <v>1.63</v>
+        <v>1.74</v>
       </c>
       <c r="AT113">
-        <v>3.26</v>
+        <v>3.24</v>
       </c>
       <c r="AU113">
         <v>5</v>
@@ -24609,7 +24612,7 @@
         <v>151</v>
       </c>
       <c r="P114" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="Q114">
         <v>2.88</v>
@@ -24681,25 +24684,25 @@
         <v>1.63</v>
       </c>
       <c r="AN114">
-        <v>1.71</v>
+        <v>1.46</v>
       </c>
       <c r="AO114">
-        <v>1.14</v>
+        <v>1.29</v>
       </c>
       <c r="AP114">
-        <v>1.36</v>
+        <v>1.13</v>
       </c>
       <c r="AQ114">
-        <v>1.25</v>
+        <v>1.42</v>
       </c>
       <c r="AR114">
-        <v>1.11</v>
+        <v>1.08</v>
       </c>
       <c r="AS114">
-        <v>1.28</v>
+        <v>1.4</v>
       </c>
       <c r="AT114">
-        <v>2.39</v>
+        <v>2.48</v>
       </c>
       <c r="AU114">
         <v>-1</v>
@@ -24815,7 +24818,7 @@
         <v>99</v>
       </c>
       <c r="P115" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="Q115">
         <v>1.73</v>
@@ -24887,25 +24890,25 @@
         <v>3.5</v>
       </c>
       <c r="AN115">
-        <v>1.67</v>
+        <v>1.86</v>
       </c>
       <c r="AO115">
-        <v>1</v>
+        <v>0.93</v>
       </c>
       <c r="AP115">
         <v>2.17</v>
       </c>
       <c r="AQ115">
-        <v>0.75</v>
+        <v>1.04</v>
       </c>
       <c r="AR115">
-        <v>1.87</v>
+        <v>1.8</v>
       </c>
       <c r="AS115">
-        <v>1.26</v>
+        <v>1.44</v>
       </c>
       <c r="AT115">
-        <v>3.13</v>
+        <v>3.24</v>
       </c>
       <c r="AU115">
         <v>9</v>
@@ -25021,7 +25024,7 @@
         <v>88</v>
       </c>
       <c r="P116" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="Q116">
         <v>4.33</v>
@@ -25093,25 +25096,25 @@
         <v>1.25</v>
       </c>
       <c r="AN116">
-        <v>2</v>
+        <v>1.36</v>
       </c>
       <c r="AO116">
-        <v>1.57</v>
+        <v>2.14</v>
       </c>
       <c r="AP116">
-        <v>1.58</v>
+        <v>1.3</v>
       </c>
       <c r="AQ116">
-        <v>1.92</v>
+        <v>2.17</v>
       </c>
       <c r="AR116">
-        <v>1.34</v>
+        <v>1.24</v>
       </c>
       <c r="AS116">
-        <v>1.2</v>
+        <v>1.45</v>
       </c>
       <c r="AT116">
-        <v>2.54</v>
+        <v>2.69</v>
       </c>
       <c r="AU116">
         <v>3</v>
@@ -25299,25 +25302,25 @@
         <v>0</v>
       </c>
       <c r="AN117">
-        <v>0.83</v>
+        <v>1.21</v>
       </c>
       <c r="AO117">
-        <v>0.29</v>
+        <v>0.79</v>
       </c>
       <c r="AP117">
-        <v>1.17</v>
+        <v>1.25</v>
       </c>
       <c r="AQ117">
-        <v>0.42</v>
+        <v>0.65</v>
       </c>
       <c r="AR117">
-        <v>1.44</v>
+        <v>1.36</v>
       </c>
       <c r="AS117">
-        <v>0.84</v>
+        <v>1.03</v>
       </c>
       <c r="AT117">
-        <v>2.28</v>
+        <v>2.39</v>
       </c>
       <c r="AU117">
         <v>6</v>
@@ -25505,25 +25508,25 @@
         <v>0</v>
       </c>
       <c r="AN118">
-        <v>1.5</v>
+        <v>1.36</v>
       </c>
       <c r="AO118">
+        <v>0.79</v>
+      </c>
+      <c r="AP118">
+        <v>1.17</v>
+      </c>
+      <c r="AQ118">
         <v>0.63</v>
       </c>
-      <c r="AP118">
-        <v>1.46</v>
-      </c>
-      <c r="AQ118">
-        <v>0.46</v>
-      </c>
       <c r="AR118">
-        <v>1.64</v>
+        <v>1.63</v>
       </c>
       <c r="AS118">
-        <v>1.02</v>
+        <v>1.05</v>
       </c>
       <c r="AT118">
-        <v>2.66</v>
+        <v>2.68</v>
       </c>
       <c r="AU118">
         <v>3</v>
@@ -25639,7 +25642,7 @@
         <v>88</v>
       </c>
       <c r="P119" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="Q119">
         <v>15</v>
@@ -25711,25 +25714,25 @@
         <v>0</v>
       </c>
       <c r="AN119">
-        <v>0.25</v>
+        <v>0.14</v>
       </c>
       <c r="AO119">
-        <v>2.33</v>
+        <v>2.71</v>
       </c>
       <c r="AP119">
-        <v>0.23</v>
+        <v>0.17</v>
       </c>
       <c r="AQ119">
-        <v>2.42</v>
+        <v>2.71</v>
       </c>
       <c r="AR119">
-        <v>1.38</v>
+        <v>1.22</v>
       </c>
       <c r="AS119">
-        <v>1.61</v>
+        <v>2.04</v>
       </c>
       <c r="AT119">
-        <v>2.99</v>
+        <v>3.26</v>
       </c>
       <c r="AU119">
         <v>2</v>
@@ -25845,7 +25848,7 @@
         <v>168</v>
       </c>
       <c r="P120" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="Q120">
         <v>3</v>
@@ -25917,25 +25920,25 @@
         <v>1.63</v>
       </c>
       <c r="AN120">
-        <v>1.83</v>
+        <v>1.46</v>
       </c>
       <c r="AO120">
-        <v>1.17</v>
+        <v>1.21</v>
       </c>
       <c r="AP120">
-        <v>1.67</v>
+        <v>1.46</v>
       </c>
       <c r="AQ120">
-        <v>1</v>
+        <v>1.21</v>
       </c>
       <c r="AR120">
-        <v>1.59</v>
+        <v>1.38</v>
       </c>
       <c r="AS120">
         <v>1.52</v>
       </c>
       <c r="AT120">
-        <v>3.11</v>
+        <v>2.9</v>
       </c>
       <c r="AU120">
         <v>4</v>
@@ -26123,25 +26126,25 @@
         <v>1.63</v>
       </c>
       <c r="AN121">
-        <v>1.57</v>
+        <v>1.36</v>
       </c>
       <c r="AO121">
-        <v>1.17</v>
+        <v>1.43</v>
       </c>
       <c r="AP121">
-        <v>1.67</v>
+        <v>1.46</v>
       </c>
       <c r="AQ121">
-        <v>0.92</v>
+        <v>1.13</v>
       </c>
       <c r="AR121">
-        <v>1.57</v>
+        <v>1.39</v>
       </c>
       <c r="AS121">
-        <v>1.04</v>
+        <v>1.08</v>
       </c>
       <c r="AT121">
-        <v>2.61</v>
+        <v>2.47</v>
       </c>
       <c r="AU121">
         <v>13</v>
@@ -26257,7 +26260,7 @@
         <v>170</v>
       </c>
       <c r="P122" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="Q122">
         <v>3.25</v>
@@ -26329,25 +26332,25 @@
         <v>0</v>
       </c>
       <c r="AN122">
-        <v>1.14</v>
+        <v>1.33</v>
       </c>
       <c r="AO122">
-        <v>1</v>
+        <v>1.33</v>
       </c>
       <c r="AP122">
-        <v>1.17</v>
+        <v>1.25</v>
       </c>
       <c r="AQ122">
-        <v>0.92</v>
+        <v>1.13</v>
       </c>
       <c r="AR122">
-        <v>1.54</v>
+        <v>1.41</v>
       </c>
       <c r="AS122">
-        <v>1.03</v>
+        <v>1.07</v>
       </c>
       <c r="AT122">
-        <v>2.57</v>
+        <v>2.48</v>
       </c>
       <c r="AU122">
         <v>6</v>
@@ -26535,25 +26538,25 @@
         <v>1.52</v>
       </c>
       <c r="AN123">
-        <v>0.88</v>
+        <v>0.93</v>
       </c>
       <c r="AO123">
-        <v>1.14</v>
+        <v>1.47</v>
       </c>
       <c r="AP123">
-        <v>1.33</v>
+        <v>1.04</v>
       </c>
       <c r="AQ123">
-        <v>1.25</v>
+        <v>1.46</v>
       </c>
       <c r="AR123">
-        <v>1.58</v>
+        <v>1.41</v>
       </c>
       <c r="AS123">
-        <v>1.2</v>
+        <v>1.46</v>
       </c>
       <c r="AT123">
-        <v>2.78</v>
+        <v>2.87</v>
       </c>
       <c r="AU123">
         <v>2</v>
@@ -26669,7 +26672,7 @@
         <v>172</v>
       </c>
       <c r="P124" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="Q124">
         <v>1.83</v>
@@ -26741,25 +26744,25 @@
         <v>2.82</v>
       </c>
       <c r="AN124">
-        <v>2.5</v>
+        <v>1.8</v>
       </c>
       <c r="AO124">
+        <v>1.47</v>
+      </c>
+      <c r="AP124">
+        <v>2</v>
+      </c>
+      <c r="AQ124">
         <v>1.17</v>
       </c>
-      <c r="AP124">
-        <v>2.45</v>
-      </c>
-      <c r="AQ124">
-        <v>0.8</v>
-      </c>
       <c r="AR124">
-        <v>1.87</v>
+        <v>1.74</v>
       </c>
       <c r="AS124">
-        <v>1.62</v>
+        <v>1.6</v>
       </c>
       <c r="AT124">
-        <v>3.49</v>
+        <v>3.34</v>
       </c>
       <c r="AU124">
         <v>12</v>
@@ -26875,7 +26878,7 @@
         <v>171</v>
       </c>
       <c r="P125" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="Q125">
         <v>6.3</v>
@@ -26947,25 +26950,25 @@
         <v>1.08</v>
       </c>
       <c r="AN125">
-        <v>1.29</v>
+        <v>0.73</v>
       </c>
       <c r="AO125">
-        <v>2</v>
+        <v>1.8</v>
       </c>
       <c r="AP125">
-        <v>0.91</v>
+        <v>0.65</v>
       </c>
       <c r="AQ125">
         <v>2.17</v>
       </c>
       <c r="AR125">
-        <v>1.21</v>
+        <v>1.02</v>
       </c>
       <c r="AS125">
-        <v>1.74</v>
+        <v>1.83</v>
       </c>
       <c r="AT125">
-        <v>2.95</v>
+        <v>2.85</v>
       </c>
       <c r="AU125">
         <v>5</v>
@@ -27153,25 +27156,25 @@
         <v>4.2</v>
       </c>
       <c r="AN126">
-        <v>3</v>
+        <v>2.73</v>
       </c>
       <c r="AO126">
-        <v>1.43</v>
+        <v>1.33</v>
       </c>
       <c r="AP126">
-        <v>3</v>
+        <v>2.71</v>
       </c>
       <c r="AQ126">
-        <v>1</v>
+        <v>1.21</v>
       </c>
       <c r="AR126">
-        <v>2.37</v>
+        <v>2.03</v>
       </c>
       <c r="AS126">
-        <v>1.57</v>
+        <v>1.54</v>
       </c>
       <c r="AT126">
-        <v>3.94</v>
+        <v>3.57</v>
       </c>
       <c r="AU126">
         <v>9</v>
@@ -27359,25 +27362,25 @@
         <v>1.62</v>
       </c>
       <c r="AN127">
-        <v>1.43</v>
+        <v>1.27</v>
       </c>
       <c r="AO127">
-        <v>0.71</v>
+        <v>1.27</v>
       </c>
       <c r="AP127">
-        <v>1.58</v>
+        <v>1.42</v>
       </c>
       <c r="AQ127">
-        <v>1</v>
+        <v>1.3</v>
       </c>
       <c r="AR127">
-        <v>1.5</v>
+        <v>1.4</v>
       </c>
       <c r="AS127">
-        <v>1.15</v>
+        <v>1.24</v>
       </c>
       <c r="AT127">
-        <v>2.65</v>
+        <v>2.64</v>
       </c>
       <c r="AU127">
         <v>9</v>
@@ -27565,25 +27568,25 @@
         <v>2</v>
       </c>
       <c r="AN128">
-        <v>1</v>
+        <v>0.73</v>
       </c>
       <c r="AO128">
-        <v>0</v>
+        <v>0.13</v>
       </c>
       <c r="AP128">
-        <v>0.82</v>
+        <v>0.63</v>
       </c>
       <c r="AQ128">
-        <v>0.09</v>
+        <v>0.17</v>
       </c>
       <c r="AR128">
-        <v>1.1</v>
+        <v>1.06</v>
       </c>
       <c r="AS128">
-        <v>1</v>
+        <v>1.2</v>
       </c>
       <c r="AT128">
-        <v>2.1</v>
+        <v>2.26</v>
       </c>
       <c r="AU128">
         <v>6</v>
@@ -27699,7 +27702,7 @@
         <v>174</v>
       </c>
       <c r="P129" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="Q129">
         <v>2.1</v>
@@ -27771,25 +27774,25 @@
         <v>2.45</v>
       </c>
       <c r="AN129">
-        <v>2.71</v>
+        <v>2.2</v>
       </c>
       <c r="AO129">
-        <v>1.38</v>
+        <v>1.6</v>
       </c>
       <c r="AP129">
-        <v>2.42</v>
+        <v>2.17</v>
       </c>
       <c r="AQ129">
-        <v>1.25</v>
+        <v>1.67</v>
       </c>
       <c r="AR129">
-        <v>1.69</v>
+        <v>1.44</v>
       </c>
       <c r="AS129">
-        <v>1.4</v>
+        <v>1.5</v>
       </c>
       <c r="AT129">
-        <v>3.09</v>
+        <v>2.94</v>
       </c>
       <c r="AU129">
         <v>6</v>
@@ -27905,7 +27908,7 @@
         <v>175</v>
       </c>
       <c r="P130" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="Q130">
         <v>1.5</v>
@@ -27977,25 +27980,25 @@
         <v>4.33</v>
       </c>
       <c r="AN130">
-        <v>1.57</v>
+        <v>1.75</v>
       </c>
       <c r="AO130">
-        <v>1</v>
+        <v>1.38</v>
       </c>
       <c r="AP130">
         <v>2.17</v>
       </c>
       <c r="AQ130">
-        <v>0.8</v>
+        <v>1.17</v>
       </c>
       <c r="AR130">
-        <v>1.93</v>
+        <v>1.78</v>
       </c>
       <c r="AS130">
-        <v>1.54</v>
+        <v>1.57</v>
       </c>
       <c r="AT130">
-        <v>3.47</v>
+        <v>3.35</v>
       </c>
       <c r="AU130">
         <v>13</v>
@@ -28111,7 +28114,7 @@
         <v>176</v>
       </c>
       <c r="P131" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="Q131">
         <v>3.5</v>
@@ -28183,25 +28186,25 @@
         <v>1.36</v>
       </c>
       <c r="AN131">
-        <v>1</v>
+        <v>0.75</v>
       </c>
       <c r="AO131">
-        <v>1</v>
+        <v>1.38</v>
       </c>
       <c r="AP131">
-        <v>0.82</v>
+        <v>0.63</v>
       </c>
       <c r="AQ131">
-        <v>1.25</v>
+        <v>1.46</v>
       </c>
       <c r="AR131">
-        <v>1.21</v>
+        <v>1.11</v>
       </c>
       <c r="AS131">
-        <v>1.18</v>
+        <v>1.44</v>
       </c>
       <c r="AT131">
-        <v>2.39</v>
+        <v>2.55</v>
       </c>
       <c r="AU131">
         <v>6</v>
@@ -28317,7 +28320,7 @@
         <v>177</v>
       </c>
       <c r="P132" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="Q132">
         <v>4.04</v>
@@ -28389,25 +28392,25 @@
         <v>1.32</v>
       </c>
       <c r="AN132">
-        <v>1.25</v>
+        <v>0.75</v>
       </c>
       <c r="AO132">
-        <v>1</v>
+        <v>1.31</v>
       </c>
       <c r="AP132">
-        <v>0.91</v>
+        <v>0.65</v>
       </c>
       <c r="AQ132">
-        <v>0.92</v>
+        <v>1.13</v>
       </c>
       <c r="AR132">
-        <v>1.24</v>
+        <v>1.05</v>
       </c>
       <c r="AS132">
-        <v>1.14</v>
+        <v>1.13</v>
       </c>
       <c r="AT132">
-        <v>2.38</v>
+        <v>2.18</v>
       </c>
       <c r="AU132">
         <v>4</v>
@@ -28595,25 +28598,25 @@
         <v>2.65</v>
       </c>
       <c r="AN133">
-        <v>1.86</v>
+        <v>1.5</v>
       </c>
       <c r="AO133">
-        <v>0.14</v>
+        <v>0.19</v>
       </c>
       <c r="AP133">
-        <v>2.08</v>
+        <v>1.67</v>
       </c>
       <c r="AQ133">
-        <v>0.09</v>
+        <v>0.17</v>
       </c>
       <c r="AR133">
-        <v>1.63</v>
+        <v>1.48</v>
       </c>
       <c r="AS133">
-        <v>0.9</v>
+        <v>1.14</v>
       </c>
       <c r="AT133">
-        <v>2.53</v>
+        <v>2.62</v>
       </c>
       <c r="AU133">
         <v>10</v>
@@ -28729,7 +28732,7 @@
         <v>88</v>
       </c>
       <c r="P134" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="Q134">
         <v>2.75</v>
@@ -28801,25 +28804,25 @@
         <v>1.75</v>
       </c>
       <c r="AN134">
-        <v>1.13</v>
+        <v>1.31</v>
       </c>
       <c r="AO134">
-        <v>0.63</v>
+        <v>1.19</v>
       </c>
       <c r="AP134">
-        <v>1.17</v>
+        <v>1.25</v>
       </c>
       <c r="AQ134">
-        <v>1</v>
+        <v>1.3</v>
       </c>
       <c r="AR134">
-        <v>1.51</v>
+        <v>1.4</v>
       </c>
       <c r="AS134">
-        <v>1.23</v>
+        <v>1.27</v>
       </c>
       <c r="AT134">
-        <v>2.74</v>
+        <v>2.67</v>
       </c>
       <c r="AU134">
         <v>4</v>
@@ -29007,25 +29010,25 @@
         <v>1.69</v>
       </c>
       <c r="AN135">
-        <v>1.63</v>
+        <v>1.38</v>
       </c>
       <c r="AO135">
         <v>1.25</v>
       </c>
       <c r="AP135">
-        <v>1.58</v>
+        <v>1.42</v>
       </c>
       <c r="AQ135">
-        <v>1</v>
+        <v>1.21</v>
       </c>
       <c r="AR135">
-        <v>1.56</v>
+        <v>1.44</v>
       </c>
       <c r="AS135">
-        <v>1.49</v>
+        <v>1.5</v>
       </c>
       <c r="AT135">
-        <v>3.05</v>
+        <v>2.94</v>
       </c>
       <c r="AU135">
         <v>5</v>
@@ -29213,25 +29216,25 @@
         <v>1.15</v>
       </c>
       <c r="AN136">
-        <v>2.57</v>
+        <v>1.88</v>
       </c>
       <c r="AO136">
-        <v>2.43</v>
+        <v>2.75</v>
       </c>
       <c r="AP136">
-        <v>2.45</v>
+        <v>2</v>
       </c>
       <c r="AQ136">
-        <v>2.42</v>
+        <v>2.71</v>
       </c>
       <c r="AR136">
-        <v>2.02</v>
+        <v>1.81</v>
       </c>
       <c r="AS136">
-        <v>1.63</v>
+        <v>2.06</v>
       </c>
       <c r="AT136">
-        <v>3.65</v>
+        <v>3.87</v>
       </c>
       <c r="AU136">
         <v>4</v>
@@ -29419,25 +29422,25 @@
         <v>3.6</v>
       </c>
       <c r="AN137">
-        <v>2.75</v>
+        <v>2.25</v>
       </c>
       <c r="AO137">
-        <v>1</v>
+        <v>1.06</v>
       </c>
       <c r="AP137">
-        <v>2.42</v>
+        <v>2.17</v>
       </c>
       <c r="AQ137">
-        <v>0.75</v>
+        <v>1.04</v>
       </c>
       <c r="AR137">
-        <v>1.7</v>
+        <v>1.46</v>
       </c>
       <c r="AS137">
-        <v>1.22</v>
+        <v>1.41</v>
       </c>
       <c r="AT137">
-        <v>2.92</v>
+        <v>2.87</v>
       </c>
       <c r="AU137">
         <v>9</v>
@@ -29553,7 +29556,7 @@
         <v>91</v>
       </c>
       <c r="P138" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="Q138">
         <v>2.25</v>
@@ -29625,25 +29628,25 @@
         <v>2.2</v>
       </c>
       <c r="AN138">
-        <v>1.63</v>
+        <v>1.41</v>
       </c>
       <c r="AO138">
-        <v>0.5600000000000001</v>
+        <v>0.76</v>
       </c>
       <c r="AP138">
-        <v>1.36</v>
+        <v>1.13</v>
       </c>
       <c r="AQ138">
-        <v>0.46</v>
+        <v>0.63</v>
       </c>
       <c r="AR138">
-        <v>1.11</v>
+        <v>1.15</v>
       </c>
       <c r="AS138">
-        <v>1.03</v>
+        <v>1.14</v>
       </c>
       <c r="AT138">
-        <v>2.14</v>
+        <v>2.29</v>
       </c>
       <c r="AU138">
         <v>8</v>
@@ -29759,7 +29762,7 @@
         <v>179</v>
       </c>
       <c r="P139" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="Q139">
         <v>1.9</v>
@@ -29831,22 +29834,22 @@
         <v>2.7</v>
       </c>
       <c r="AN139">
-        <v>2</v>
+        <v>1.59</v>
       </c>
       <c r="AO139">
-        <v>0.25</v>
+        <v>0.71</v>
       </c>
       <c r="AP139">
-        <v>2.08</v>
+        <v>1.67</v>
       </c>
       <c r="AQ139">
-        <v>0.42</v>
+        <v>0.65</v>
       </c>
       <c r="AR139">
-        <v>1.71</v>
+        <v>1.52</v>
       </c>
       <c r="AS139">
-        <v>0.86</v>
+        <v>1.05</v>
       </c>
       <c r="AT139">
         <v>2.57</v>
@@ -30037,25 +30040,25 @@
         <v>3.75</v>
       </c>
       <c r="AN140">
-        <v>1.75</v>
+        <v>1.82</v>
       </c>
       <c r="AO140">
-        <v>1.5</v>
+        <v>1.24</v>
       </c>
       <c r="AP140">
         <v>2.17</v>
       </c>
       <c r="AQ140">
-        <v>1.45</v>
+        <v>1.25</v>
       </c>
       <c r="AR140">
-        <v>2.06</v>
+        <v>1.86</v>
       </c>
       <c r="AS140">
-        <v>1.31</v>
+        <v>1.39</v>
       </c>
       <c r="AT140">
-        <v>3.37</v>
+        <v>3.25</v>
       </c>
       <c r="AU140">
         <v>2</v>
@@ -30171,7 +30174,7 @@
         <v>88</v>
       </c>
       <c r="P141" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="Q141">
         <v>4</v>
@@ -30243,25 +30246,25 @@
         <v>1.2</v>
       </c>
       <c r="AN141">
-        <v>0.22</v>
+        <v>0.18</v>
       </c>
       <c r="AO141">
-        <v>1.13</v>
+        <v>1.47</v>
       </c>
       <c r="AP141">
-        <v>0.23</v>
+        <v>0.17</v>
       </c>
       <c r="AQ141">
-        <v>1.25</v>
+        <v>1.42</v>
       </c>
       <c r="AR141">
-        <v>1.34</v>
+        <v>1.14</v>
       </c>
       <c r="AS141">
-        <v>1.28</v>
+        <v>1.43</v>
       </c>
       <c r="AT141">
-        <v>2.62</v>
+        <v>2.57</v>
       </c>
       <c r="AU141">
         <v>5</v>
@@ -30377,7 +30380,7 @@
         <v>117</v>
       </c>
       <c r="P142" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="Q142">
         <v>4</v>
@@ -30449,25 +30452,25 @@
         <v>1.2</v>
       </c>
       <c r="AN142">
-        <v>1.67</v>
+        <v>1.29</v>
       </c>
       <c r="AO142">
-        <v>1.75</v>
+        <v>2.18</v>
       </c>
       <c r="AP142">
-        <v>1.46</v>
+        <v>1.17</v>
       </c>
       <c r="AQ142">
-        <v>1.92</v>
+        <v>2.17</v>
       </c>
       <c r="AR142">
-        <v>1.59</v>
+        <v>1.55</v>
       </c>
       <c r="AS142">
-        <v>1.23</v>
+        <v>1.51</v>
       </c>
       <c r="AT142">
-        <v>2.82</v>
+        <v>3.06</v>
       </c>
       <c r="AU142">
         <v>4</v>
@@ -30655,25 +30658,25 @@
         <v>1.9</v>
       </c>
       <c r="AN143">
-        <v>1.25</v>
+        <v>1.18</v>
       </c>
       <c r="AO143">
-        <v>1</v>
+        <v>1.06</v>
       </c>
       <c r="AP143">
-        <v>1.42</v>
+        <v>1.21</v>
       </c>
       <c r="AQ143">
-        <v>0.75</v>
+        <v>1.04</v>
       </c>
       <c r="AR143">
-        <v>1.52</v>
+        <v>1.49</v>
       </c>
       <c r="AS143">
-        <v>1.26</v>
+        <v>1.41</v>
       </c>
       <c r="AT143">
-        <v>2.78</v>
+        <v>2.9</v>
       </c>
       <c r="AU143">
         <v>6</v>
@@ -30789,7 +30792,7 @@
         <v>182</v>
       </c>
       <c r="P144" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="Q144">
         <v>6</v>
@@ -30861,25 +30864,25 @@
         <v>1.04</v>
       </c>
       <c r="AN144">
-        <v>1.75</v>
+        <v>1.35</v>
       </c>
       <c r="AO144">
-        <v>2.5</v>
+        <v>2.76</v>
       </c>
       <c r="AP144">
-        <v>1.67</v>
+        <v>1.46</v>
       </c>
       <c r="AQ144">
-        <v>2.42</v>
+        <v>2.71</v>
       </c>
       <c r="AR144">
-        <v>1.69</v>
+        <v>1.43</v>
       </c>
       <c r="AS144">
-        <v>1.67</v>
+        <v>2.05</v>
       </c>
       <c r="AT144">
-        <v>3.36</v>
+        <v>3.48</v>
       </c>
       <c r="AU144">
         <v>4</v>
@@ -30995,7 +30998,7 @@
         <v>88</v>
       </c>
       <c r="P145" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="Q145">
         <v>3.5</v>
@@ -31067,25 +31070,25 @@
         <v>1.4</v>
       </c>
       <c r="AN145">
-        <v>1.75</v>
+        <v>1.29</v>
       </c>
       <c r="AO145">
-        <v>1.33</v>
+        <v>1.76</v>
       </c>
       <c r="AP145">
-        <v>1.58</v>
+        <v>1.3</v>
       </c>
       <c r="AQ145">
-        <v>1.62</v>
+        <v>2</v>
       </c>
       <c r="AR145">
-        <v>1.32</v>
+        <v>1.28</v>
       </c>
       <c r="AS145">
-        <v>1.63</v>
+        <v>1.77</v>
       </c>
       <c r="AT145">
-        <v>2.95</v>
+        <v>3.05</v>
       </c>
       <c r="AU145">
         <v>9</v>
@@ -31201,7 +31204,7 @@
         <v>183</v>
       </c>
       <c r="P146" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="Q146">
         <v>4.33</v>
@@ -31273,25 +31276,25 @@
         <v>1.25</v>
       </c>
       <c r="AN146">
-        <v>1.11</v>
+        <v>0.67</v>
       </c>
       <c r="AO146">
-        <v>0.89</v>
+        <v>1.22</v>
       </c>
       <c r="AP146">
-        <v>0.91</v>
+        <v>0.65</v>
       </c>
       <c r="AQ146">
-        <v>1</v>
+        <v>1.3</v>
       </c>
       <c r="AR146">
-        <v>1.22</v>
+        <v>1.07</v>
       </c>
       <c r="AS146">
-        <v>1.25</v>
+        <v>1.34</v>
       </c>
       <c r="AT146">
-        <v>2.47</v>
+        <v>2.41</v>
       </c>
       <c r="AU146">
         <v>6</v>
@@ -31407,7 +31410,7 @@
         <v>184</v>
       </c>
       <c r="P147" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="Q147">
         <v>3.8</v>
@@ -31479,25 +31482,25 @@
         <v>1.33</v>
       </c>
       <c r="AN147">
-        <v>1</v>
+        <v>0.78</v>
       </c>
       <c r="AO147">
-        <v>1.11</v>
+        <v>1.28</v>
       </c>
       <c r="AP147">
-        <v>0.82</v>
+        <v>0.63</v>
       </c>
       <c r="AQ147">
-        <v>1</v>
+        <v>1.21</v>
       </c>
       <c r="AR147">
-        <v>1.26</v>
+        <v>1.15</v>
       </c>
       <c r="AS147">
-        <v>1.47</v>
+        <v>1.49</v>
       </c>
       <c r="AT147">
-        <v>2.73</v>
+        <v>2.64</v>
       </c>
       <c r="AU147">
         <v>4</v>
@@ -31613,7 +31616,7 @@
         <v>185</v>
       </c>
       <c r="P148" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="Q148">
         <v>2.5</v>
@@ -31685,25 +31688,25 @@
         <v>1.85</v>
       </c>
       <c r="AN148">
-        <v>1</v>
+        <v>1.17</v>
       </c>
       <c r="AO148">
-        <v>0.88</v>
+        <v>1.22</v>
       </c>
       <c r="AP148">
+        <v>1.25</v>
+      </c>
+      <c r="AQ148">
         <v>1.17</v>
       </c>
-      <c r="AQ148">
-        <v>0.8</v>
-      </c>
       <c r="AR148">
-        <v>1.47</v>
+        <v>1.4</v>
       </c>
       <c r="AS148">
-        <v>1.5</v>
+        <v>1.54</v>
       </c>
       <c r="AT148">
-        <v>2.97</v>
+        <v>2.94</v>
       </c>
       <c r="AU148">
         <v>10</v>
@@ -31819,7 +31822,7 @@
         <v>186</v>
       </c>
       <c r="P149" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="Q149">
         <v>2.05</v>
@@ -31891,25 +31894,25 @@
         <v>2.55</v>
       </c>
       <c r="AN149">
-        <v>2.25</v>
+        <v>1.83</v>
       </c>
       <c r="AO149">
-        <v>1.22</v>
+        <v>1.39</v>
       </c>
       <c r="AP149">
-        <v>2.45</v>
+        <v>2</v>
       </c>
       <c r="AQ149">
-        <v>0.92</v>
+        <v>1.13</v>
       </c>
       <c r="AR149">
-        <v>1.91</v>
+        <v>1.76</v>
       </c>
       <c r="AS149">
-        <v>1.17</v>
+        <v>1.19</v>
       </c>
       <c r="AT149">
-        <v>3.08</v>
+        <v>2.95</v>
       </c>
       <c r="AU149">
         <v>7</v>
@@ -32025,7 +32028,7 @@
         <v>187</v>
       </c>
       <c r="P150" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="Q150">
         <v>1.95</v>
@@ -32100,22 +32103,22 @@
         <v>1.89</v>
       </c>
       <c r="AO150">
-        <v>1.22</v>
+        <v>1.67</v>
       </c>
       <c r="AP150">
         <v>2.17</v>
       </c>
       <c r="AQ150">
-        <v>1.25</v>
+        <v>1.67</v>
       </c>
       <c r="AR150">
-        <v>1.98</v>
+        <v>1.83</v>
       </c>
       <c r="AS150">
-        <v>1.38</v>
+        <v>1.52</v>
       </c>
       <c r="AT150">
-        <v>3.36</v>
+        <v>3.35</v>
       </c>
       <c r="AU150">
         <v>6</v>
@@ -32231,7 +32234,7 @@
         <v>188</v>
       </c>
       <c r="P151" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="Q151">
         <v>2.48</v>
@@ -32303,25 +32306,25 @@
         <v>1.8</v>
       </c>
       <c r="AN151">
-        <v>1.78</v>
+        <v>1.56</v>
       </c>
       <c r="AO151">
-        <v>1</v>
+        <v>1.28</v>
       </c>
       <c r="AP151">
-        <v>1.58</v>
+        <v>1.42</v>
       </c>
       <c r="AQ151">
-        <v>1.25</v>
+        <v>1.46</v>
       </c>
       <c r="AR151">
-        <v>1.53</v>
+        <v>1.45</v>
       </c>
       <c r="AS151">
-        <v>1.2</v>
+        <v>1.4</v>
       </c>
       <c r="AT151">
-        <v>2.73</v>
+        <v>2.85</v>
       </c>
       <c r="AU151">
         <v>8</v>
@@ -32509,25 +32512,25 @@
         <v>1.05</v>
       </c>
       <c r="AN152">
-        <v>1.11</v>
+        <v>1</v>
       </c>
       <c r="AO152">
-        <v>2.56</v>
+        <v>2.78</v>
       </c>
       <c r="AP152">
-        <v>1.33</v>
+        <v>1.04</v>
       </c>
       <c r="AQ152">
-        <v>2.42</v>
+        <v>2.71</v>
       </c>
       <c r="AR152">
-        <v>1.55</v>
+        <v>1.43</v>
       </c>
       <c r="AS152">
-        <v>1.68</v>
+        <v>2.03</v>
       </c>
       <c r="AT152">
-        <v>3.23</v>
+        <v>3.46</v>
       </c>
       <c r="AU152">
         <v>4</v>
@@ -32643,7 +32646,7 @@
         <v>190</v>
       </c>
       <c r="P153" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="Q153">
         <v>1.4</v>
@@ -32715,25 +32718,25 @@
         <v>7</v>
       </c>
       <c r="AN153">
-        <v>2.56</v>
+        <v>2.22</v>
       </c>
       <c r="AO153">
-        <v>0.13</v>
+        <v>0.17</v>
       </c>
       <c r="AP153">
-        <v>2.42</v>
+        <v>2.17</v>
       </c>
       <c r="AQ153">
-        <v>0.09</v>
+        <v>0.17</v>
       </c>
       <c r="AR153">
-        <v>1.75</v>
+        <v>1.53</v>
       </c>
       <c r="AS153">
-        <v>0.93</v>
+        <v>1.16</v>
       </c>
       <c r="AT153">
-        <v>2.68</v>
+        <v>2.69</v>
       </c>
       <c r="AU153">
         <v>11</v>
@@ -32921,25 +32924,25 @@
         <v>0</v>
       </c>
       <c r="AN154">
-        <v>1.5</v>
+        <v>1.21</v>
       </c>
       <c r="AO154">
-        <v>0.89</v>
+        <v>1.11</v>
       </c>
       <c r="AP154">
-        <v>1.46</v>
+        <v>1.17</v>
       </c>
       <c r="AQ154">
-        <v>0.75</v>
+        <v>1.04</v>
       </c>
       <c r="AR154">
-        <v>1.58</v>
+        <v>1.53</v>
       </c>
       <c r="AS154">
-        <v>1.31</v>
+        <v>1.39</v>
       </c>
       <c r="AT154">
-        <v>2.89</v>
+        <v>2.92</v>
       </c>
       <c r="AU154">
         <v>2</v>
@@ -33055,7 +33058,7 @@
         <v>88</v>
       </c>
       <c r="P155" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="Q155">
         <v>3.2</v>
@@ -33127,25 +33130,25 @@
         <v>1.45</v>
       </c>
       <c r="AN155">
-        <v>1.44</v>
+        <v>1.26</v>
       </c>
       <c r="AO155">
-        <v>1.5</v>
+        <v>1.89</v>
       </c>
       <c r="AP155">
-        <v>1.42</v>
+        <v>1.21</v>
       </c>
       <c r="AQ155">
-        <v>1.62</v>
+        <v>2</v>
       </c>
       <c r="AR155">
-        <v>1.51</v>
+        <v>1.49</v>
       </c>
       <c r="AS155">
-        <v>1.63</v>
+        <v>1.76</v>
       </c>
       <c r="AT155">
-        <v>3.14</v>
+        <v>3.25</v>
       </c>
       <c r="AU155">
         <v>2</v>
@@ -33333,25 +33336,25 @@
         <v>1.44</v>
       </c>
       <c r="AN156">
-        <v>0.2</v>
+        <v>0.16</v>
       </c>
       <c r="AO156">
-        <v>0.22</v>
+        <v>0.63</v>
       </c>
       <c r="AP156">
-        <v>0.23</v>
+        <v>0.17</v>
       </c>
       <c r="AQ156">
-        <v>0.42</v>
+        <v>0.65</v>
       </c>
       <c r="AR156">
-        <v>1.34</v>
+        <v>1.15</v>
       </c>
       <c r="AS156">
-        <v>0.93</v>
+        <v>1.11</v>
       </c>
       <c r="AT156">
-        <v>2.27</v>
+        <v>2.26</v>
       </c>
       <c r="AU156">
         <v>3</v>
@@ -33539,25 +33542,25 @@
         <v>2.26</v>
       </c>
       <c r="AN157">
-        <v>1.56</v>
+        <v>1.32</v>
       </c>
       <c r="AO157">
-        <v>0.6</v>
+        <v>0.79</v>
       </c>
       <c r="AP157">
-        <v>1.58</v>
+        <v>1.3</v>
       </c>
       <c r="AQ157">
-        <v>0.46</v>
+        <v>0.63</v>
       </c>
       <c r="AR157">
-        <v>1.43</v>
+        <v>1.35</v>
       </c>
       <c r="AS157">
-        <v>1.06</v>
+        <v>1.17</v>
       </c>
       <c r="AT157">
-        <v>2.49</v>
+        <v>2.52</v>
       </c>
       <c r="AU157">
         <v>8</v>
@@ -33673,7 +33676,7 @@
         <v>88</v>
       </c>
       <c r="P158" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="Q158">
         <v>5</v>
@@ -33745,25 +33748,25 @@
         <v>1.2</v>
       </c>
       <c r="AN158">
-        <v>1.56</v>
+        <v>1.32</v>
       </c>
       <c r="AO158">
-        <v>1.89</v>
+        <v>1.95</v>
       </c>
       <c r="AP158">
-        <v>1.36</v>
+        <v>1.13</v>
       </c>
       <c r="AQ158">
         <v>2.17</v>
       </c>
       <c r="AR158">
-        <v>1.21</v>
+        <v>1.23</v>
       </c>
       <c r="AS158">
-        <v>1.67</v>
+        <v>1.82</v>
       </c>
       <c r="AT158">
-        <v>2.88</v>
+        <v>3.05</v>
       </c>
       <c r="AU158">
         <v>0</v>
@@ -33879,7 +33882,7 @@
         <v>88</v>
       </c>
       <c r="P159" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="Q159">
         <v>2.38</v>
@@ -33951,25 +33954,25 @@
         <v>2</v>
       </c>
       <c r="AN159">
-        <v>2.11</v>
+        <v>1.58</v>
       </c>
       <c r="AO159">
-        <v>1.33</v>
+        <v>1.16</v>
       </c>
       <c r="AP159">
-        <v>2.08</v>
+        <v>1.67</v>
       </c>
       <c r="AQ159">
-        <v>1.45</v>
+        <v>1.25</v>
       </c>
       <c r="AR159">
-        <v>1.67</v>
+        <v>1.5</v>
       </c>
       <c r="AS159">
-        <v>1.35</v>
+        <v>1.47</v>
       </c>
       <c r="AT159">
-        <v>3.02</v>
+        <v>2.97</v>
       </c>
       <c r="AU159">
         <v>5</v>
@@ -34157,25 +34160,25 @@
         <v>4.33</v>
       </c>
       <c r="AN160">
-        <v>3</v>
+        <v>2.63</v>
       </c>
       <c r="AO160">
-        <v>1.33</v>
+        <v>1.47</v>
       </c>
       <c r="AP160">
-        <v>3</v>
+        <v>2.71</v>
       </c>
       <c r="AQ160">
-        <v>1.25</v>
+        <v>1.42</v>
       </c>
       <c r="AR160">
-        <v>2.39</v>
+        <v>2.05</v>
       </c>
       <c r="AS160">
-        <v>1.34</v>
+        <v>1.49</v>
       </c>
       <c r="AT160">
-        <v>3.73</v>
+        <v>3.54</v>
       </c>
       <c r="AU160">
         <v>4</v>
@@ -34291,7 +34294,7 @@
         <v>193</v>
       </c>
       <c r="P161" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="Q161">
         <v>4.75</v>
@@ -34363,25 +34366,25 @@
         <v>1.21</v>
       </c>
       <c r="AN161">
-        <v>1.56</v>
+        <v>1.37</v>
       </c>
       <c r="AO161">
-        <v>1.89</v>
+        <v>2.26</v>
       </c>
       <c r="AP161">
-        <v>1.67</v>
+        <v>1.46</v>
       </c>
       <c r="AQ161">
-        <v>1.92</v>
+        <v>2.17</v>
       </c>
       <c r="AR161">
-        <v>1.6</v>
+        <v>1.4</v>
       </c>
       <c r="AS161">
-        <v>1.32</v>
+        <v>1.58</v>
       </c>
       <c r="AT161">
-        <v>2.92</v>
+        <v>2.98</v>
       </c>
       <c r="AU161">
         <v>5</v>
@@ -34497,7 +34500,7 @@
         <v>194</v>
       </c>
       <c r="P162" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="Q162">
         <v>2.63</v>
@@ -34569,25 +34572,25 @@
         <v>1.75</v>
       </c>
       <c r="AN162">
-        <v>1.6</v>
+        <v>1.4</v>
       </c>
       <c r="AO162">
-        <v>0.9</v>
+        <v>1.1</v>
       </c>
       <c r="AP162">
-        <v>1.58</v>
+        <v>1.42</v>
       </c>
       <c r="AQ162">
-        <v>0.75</v>
+        <v>1.04</v>
       </c>
       <c r="AR162">
-        <v>1.6</v>
+        <v>1.45</v>
       </c>
       <c r="AS162">
-        <v>1.33</v>
+        <v>1.4</v>
       </c>
       <c r="AT162">
-        <v>2.93</v>
+        <v>2.85</v>
       </c>
       <c r="AU162">
         <v>6</v>
@@ -34703,7 +34706,7 @@
         <v>88</v>
       </c>
       <c r="P163" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="Q163">
         <v>11</v>
@@ -34775,25 +34778,25 @@
         <v>1.03</v>
       </c>
       <c r="AN163">
-        <v>1</v>
+        <v>0.75</v>
       </c>
       <c r="AO163">
-        <v>2.3</v>
+        <v>2.65</v>
       </c>
       <c r="AP163">
-        <v>0.82</v>
+        <v>0.63</v>
       </c>
       <c r="AQ163">
-        <v>2.42</v>
+        <v>2.71</v>
       </c>
       <c r="AR163">
-        <v>1.29</v>
+        <v>1.16</v>
       </c>
       <c r="AS163">
-        <v>1.74</v>
+        <v>2.03</v>
       </c>
       <c r="AT163">
-        <v>3.03</v>
+        <v>3.19</v>
       </c>
       <c r="AU163">
         <v>2</v>
@@ -34909,7 +34912,7 @@
         <v>195</v>
       </c>
       <c r="P164" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="Q164">
         <v>2</v>
@@ -34981,25 +34984,25 @@
         <v>2.5</v>
       </c>
       <c r="AN164">
-        <v>2.6</v>
+        <v>2.15</v>
       </c>
       <c r="AO164">
-        <v>1.1</v>
+        <v>1.2</v>
       </c>
       <c r="AP164">
-        <v>2.42</v>
+        <v>2.17</v>
       </c>
       <c r="AQ164">
-        <v>1</v>
+        <v>1.21</v>
       </c>
       <c r="AR164">
-        <v>1.81</v>
+        <v>1.59</v>
       </c>
       <c r="AS164">
-        <v>1.47</v>
+        <v>1.45</v>
       </c>
       <c r="AT164">
-        <v>3.28</v>
+        <v>3.04</v>
       </c>
       <c r="AU164">
         <v>8</v>
@@ -35115,7 +35118,7 @@
         <v>196</v>
       </c>
       <c r="P165" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="Q165">
         <v>2.5</v>
@@ -35187,25 +35190,25 @@
         <v>1.93</v>
       </c>
       <c r="AN165">
-        <v>1.9</v>
+        <v>1.5</v>
       </c>
       <c r="AO165">
-        <v>1.1</v>
+        <v>1.25</v>
       </c>
       <c r="AP165">
-        <v>2.08</v>
+        <v>1.67</v>
       </c>
       <c r="AQ165">
-        <v>0.92</v>
+        <v>1.13</v>
       </c>
       <c r="AR165">
-        <v>1.66</v>
+        <v>1.5</v>
       </c>
       <c r="AS165">
-        <v>1.24</v>
+        <v>1.23</v>
       </c>
       <c r="AT165">
-        <v>2.9</v>
+        <v>2.73</v>
       </c>
       <c r="AU165">
         <v>8</v>
@@ -35393,25 +35396,25 @@
         <v>2.2</v>
       </c>
       <c r="AN166">
-        <v>2.33</v>
+        <v>1.95</v>
       </c>
       <c r="AO166">
-        <v>1.2</v>
+        <v>1.45</v>
       </c>
       <c r="AP166">
-        <v>2.45</v>
+        <v>2</v>
       </c>
       <c r="AQ166">
-        <v>1.25</v>
+        <v>1.46</v>
       </c>
       <c r="AR166">
-        <v>1.9</v>
+        <v>1.79</v>
       </c>
       <c r="AS166">
-        <v>1.22</v>
+        <v>1.38</v>
       </c>
       <c r="AT166">
-        <v>3.12</v>
+        <v>3.17</v>
       </c>
       <c r="AU166">
         <v>4</v>
@@ -35599,25 +35602,25 @@
         <v>2.75</v>
       </c>
       <c r="AN167">
-        <v>1</v>
+        <v>1.25</v>
       </c>
       <c r="AO167">
-        <v>0.11</v>
+        <v>0.2</v>
       </c>
       <c r="AP167">
-        <v>1.17</v>
+        <v>1.25</v>
       </c>
       <c r="AQ167">
-        <v>0.09</v>
+        <v>0.17</v>
       </c>
       <c r="AR167">
-        <v>1.6</v>
+        <v>1.47</v>
       </c>
       <c r="AS167">
-        <v>0.9399999999999999</v>
+        <v>1.14</v>
       </c>
       <c r="AT167">
-        <v>2.54</v>
+        <v>2.61</v>
       </c>
       <c r="AU167">
         <v>5</v>
@@ -35808,22 +35811,22 @@
         <v>2</v>
       </c>
       <c r="AO168">
-        <v>1.1</v>
+        <v>1.4</v>
       </c>
       <c r="AP168">
         <v>2.17</v>
       </c>
       <c r="AQ168">
-        <v>1</v>
+        <v>1.3</v>
       </c>
       <c r="AR168">
-        <v>1.96</v>
+        <v>1.82</v>
       </c>
       <c r="AS168">
-        <v>1.29</v>
+        <v>1.38</v>
       </c>
       <c r="AT168">
-        <v>3.25</v>
+        <v>3.2</v>
       </c>
       <c r="AU168">
         <v>13</v>
@@ -36011,25 +36014,25 @@
         <v>2.03</v>
       </c>
       <c r="AN169">
-        <v>1.7</v>
+        <v>1.38</v>
       </c>
       <c r="AO169">
-        <v>0.55</v>
+        <v>0.71</v>
       </c>
       <c r="AP169">
-        <v>1.67</v>
+        <v>1.46</v>
       </c>
       <c r="AQ169">
-        <v>0.46</v>
+        <v>0.63</v>
       </c>
       <c r="AR169">
-        <v>1.54</v>
+        <v>1.36</v>
       </c>
       <c r="AS169">
-        <v>1.05</v>
+        <v>1.12</v>
       </c>
       <c r="AT169">
-        <v>2.59</v>
+        <v>2.48</v>
       </c>
       <c r="AU169">
         <v>9</v>
@@ -36217,25 +36220,25 @@
         <v>1.96</v>
       </c>
       <c r="AN170">
-        <v>1.4</v>
+        <v>1.19</v>
       </c>
       <c r="AO170">
-        <v>0.3</v>
+        <v>0.65</v>
       </c>
       <c r="AP170">
-        <v>1.36</v>
+        <v>1.13</v>
       </c>
       <c r="AQ170">
-        <v>0.42</v>
+        <v>0.65</v>
       </c>
       <c r="AR170">
-        <v>1.21</v>
+        <v>1.23</v>
       </c>
       <c r="AS170">
-        <v>0.9</v>
+        <v>1.09</v>
       </c>
       <c r="AT170">
-        <v>2.11</v>
+        <v>2.32</v>
       </c>
       <c r="AU170">
         <v>3</v>
@@ -36351,7 +36354,7 @@
         <v>201</v>
       </c>
       <c r="P171" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="Q171">
         <v>5.2</v>
@@ -36423,22 +36426,22 @@
         <v>1.17</v>
       </c>
       <c r="AN171">
-        <v>0.27</v>
+        <v>0.19</v>
       </c>
       <c r="AO171">
-        <v>1.1</v>
+        <v>1.57</v>
       </c>
       <c r="AP171">
-        <v>0.23</v>
+        <v>0.17</v>
       </c>
       <c r="AQ171">
-        <v>1.25</v>
+        <v>1.67</v>
       </c>
       <c r="AR171">
-        <v>1.3</v>
+        <v>1.15</v>
       </c>
       <c r="AS171">
-        <v>1.36</v>
+        <v>1.51</v>
       </c>
       <c r="AT171">
         <v>2.66</v>
@@ -36557,7 +36560,7 @@
         <v>202</v>
       </c>
       <c r="P172" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="Q172">
         <v>6.35</v>
@@ -36629,25 +36632,25 @@
         <v>1.13</v>
       </c>
       <c r="AN172">
-        <v>1.45</v>
+        <v>1.2</v>
       </c>
       <c r="AO172">
-        <v>2</v>
+        <v>2.05</v>
       </c>
       <c r="AP172">
-        <v>1.46</v>
+        <v>1.17</v>
       </c>
       <c r="AQ172">
         <v>2.17</v>
       </c>
       <c r="AR172">
-        <v>1.5</v>
+        <v>1.49</v>
       </c>
       <c r="AS172">
-        <v>1.67</v>
+        <v>1.87</v>
       </c>
       <c r="AT172">
-        <v>3.17</v>
+        <v>3.36</v>
       </c>
       <c r="AU172">
         <v>7</v>
@@ -36763,7 +36766,7 @@
         <v>203</v>
       </c>
       <c r="P173" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="Q173">
         <v>2.6</v>
@@ -36835,25 +36838,25 @@
         <v>1.78</v>
       </c>
       <c r="AN173">
-        <v>1.7</v>
+        <v>1.33</v>
       </c>
       <c r="AO173">
-        <v>1.5</v>
+        <v>1.33</v>
       </c>
       <c r="AP173">
-        <v>1.58</v>
+        <v>1.3</v>
       </c>
       <c r="AQ173">
-        <v>1.45</v>
+        <v>1.25</v>
       </c>
       <c r="AR173">
-        <v>1.47</v>
+        <v>1.35</v>
       </c>
       <c r="AS173">
-        <v>1.35</v>
+        <v>1.49</v>
       </c>
       <c r="AT173">
-        <v>2.82</v>
+        <v>2.84</v>
       </c>
       <c r="AU173">
         <v>4</v>
@@ -36969,7 +36972,7 @@
         <v>88</v>
       </c>
       <c r="P174" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="Q174">
         <v>4.86</v>
@@ -37041,25 +37044,25 @@
         <v>1.25</v>
       </c>
       <c r="AN174">
-        <v>1.3</v>
+        <v>1.05</v>
       </c>
       <c r="AO174">
-        <v>1.7</v>
+        <v>2.19</v>
       </c>
       <c r="AP174">
-        <v>1.33</v>
+        <v>1.04</v>
       </c>
       <c r="AQ174">
-        <v>1.92</v>
+        <v>2.17</v>
       </c>
       <c r="AR174">
-        <v>1.47</v>
+        <v>1.43</v>
       </c>
       <c r="AS174">
-        <v>1.37</v>
+        <v>1.6</v>
       </c>
       <c r="AT174">
-        <v>2.84</v>
+        <v>3.03</v>
       </c>
       <c r="AU174">
         <v>4</v>
@@ -37175,7 +37178,7 @@
         <v>204</v>
       </c>
       <c r="P175" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="Q175">
         <v>2.66</v>
@@ -37247,25 +37250,25 @@
         <v>1.78</v>
       </c>
       <c r="AN175">
-        <v>1.3</v>
+        <v>1.14</v>
       </c>
       <c r="AO175">
-        <v>1.2</v>
+        <v>1.48</v>
       </c>
       <c r="AP175">
+        <v>1.21</v>
+      </c>
+      <c r="AQ175">
         <v>1.42</v>
       </c>
-      <c r="AQ175">
-        <v>1.25</v>
-      </c>
       <c r="AR175">
-        <v>1.42</v>
+        <v>1.46</v>
       </c>
       <c r="AS175">
-        <v>1.27</v>
+        <v>1.44</v>
       </c>
       <c r="AT175">
-        <v>2.69</v>
+        <v>2.9</v>
       </c>
       <c r="AU175">
         <v>10</v>
@@ -37453,25 +37456,25 @@
         <v>3.75</v>
       </c>
       <c r="AN176">
-        <v>3</v>
+        <v>2.67</v>
       </c>
       <c r="AO176">
-        <v>1.64</v>
+        <v>2</v>
       </c>
       <c r="AP176">
-        <v>3</v>
+        <v>2.71</v>
       </c>
       <c r="AQ176">
-        <v>1.62</v>
+        <v>2</v>
       </c>
       <c r="AR176">
-        <v>2.32</v>
+        <v>2.1</v>
       </c>
       <c r="AS176">
-        <v>1.69</v>
+        <v>1.75</v>
       </c>
       <c r="AT176">
-        <v>4.01</v>
+        <v>3.85</v>
       </c>
       <c r="AU176">
         <v>9</v>
@@ -37587,7 +37590,7 @@
         <v>171</v>
       </c>
       <c r="P177" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="Q177">
         <v>3.63</v>
@@ -37659,25 +37662,25 @@
         <v>1.39</v>
       </c>
       <c r="AN177">
-        <v>1</v>
+        <v>0.67</v>
       </c>
       <c r="AO177">
-        <v>1.09</v>
+        <v>1.45</v>
       </c>
       <c r="AP177">
-        <v>0.91</v>
+        <v>0.65</v>
       </c>
       <c r="AQ177">
-        <v>1.25</v>
+        <v>1.46</v>
       </c>
       <c r="AR177">
-        <v>1.28</v>
+        <v>1.08</v>
       </c>
       <c r="AS177">
-        <v>1.2</v>
+        <v>1.39</v>
       </c>
       <c r="AT177">
-        <v>2.48</v>
+        <v>2.47</v>
       </c>
       <c r="AU177">
         <v>2</v>
@@ -37865,25 +37868,25 @@
         <v>2.21</v>
       </c>
       <c r="AN178">
-        <v>2.4</v>
+        <v>1.91</v>
       </c>
       <c r="AO178">
-        <v>0.82</v>
+        <v>1</v>
       </c>
       <c r="AP178">
-        <v>2.45</v>
+        <v>2</v>
       </c>
       <c r="AQ178">
-        <v>0.75</v>
+        <v>1.04</v>
       </c>
       <c r="AR178">
-        <v>1.82</v>
+        <v>1.73</v>
       </c>
       <c r="AS178">
-        <v>1.38</v>
+        <v>1.42</v>
       </c>
       <c r="AT178">
-        <v>3.2</v>
+        <v>3.15</v>
       </c>
       <c r="AU178">
         <v>4</v>
@@ -37999,7 +38002,7 @@
         <v>88</v>
       </c>
       <c r="P179" t="s">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="Q179">
         <v>3.92</v>
@@ -38071,25 +38074,25 @@
         <v>1.3</v>
       </c>
       <c r="AN179">
-        <v>0.9</v>
+        <v>0.68</v>
       </c>
       <c r="AO179">
-        <v>1.09</v>
+        <v>1.41</v>
       </c>
       <c r="AP179">
-        <v>0.82</v>
+        <v>0.63</v>
       </c>
       <c r="AQ179">
-        <v>1.25</v>
+        <v>1.42</v>
       </c>
       <c r="AR179">
-        <v>1.2</v>
+        <v>1.11</v>
       </c>
       <c r="AS179">
-        <v>1.3</v>
+        <v>1.45</v>
       </c>
       <c r="AT179">
-        <v>2.5</v>
+        <v>2.56</v>
       </c>
       <c r="AU179">
         <v>5</v>
@@ -38205,7 +38208,7 @@
         <v>206</v>
       </c>
       <c r="P180" t="s">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="Q180">
         <v>1.32</v>
@@ -38280,22 +38283,22 @@
         <v>2.09</v>
       </c>
       <c r="AO180">
-        <v>0.1</v>
+        <v>0.18</v>
       </c>
       <c r="AP180">
         <v>2.17</v>
       </c>
       <c r="AQ180">
-        <v>0.09</v>
+        <v>0.17</v>
       </c>
       <c r="AR180">
-        <v>2.04</v>
+        <v>1.87</v>
       </c>
       <c r="AS180">
-        <v>0.98</v>
+        <v>1.12</v>
       </c>
       <c r="AT180">
-        <v>3.02</v>
+        <v>2.99</v>
       </c>
       <c r="AU180">
         <v>12</v>
@@ -38483,25 +38486,25 @@
         <v>1.65</v>
       </c>
       <c r="AN181">
-        <v>1.18</v>
+        <v>1.32</v>
       </c>
       <c r="AO181">
-        <v>1</v>
+        <v>1.23</v>
       </c>
       <c r="AP181">
-        <v>1.17</v>
+        <v>1.25</v>
       </c>
       <c r="AQ181">
-        <v>1</v>
+        <v>1.21</v>
       </c>
       <c r="AR181">
-        <v>1.62</v>
+        <v>1.48</v>
       </c>
       <c r="AS181">
         <v>1.49</v>
       </c>
       <c r="AT181">
-        <v>3.11</v>
+        <v>2.97</v>
       </c>
       <c r="AU181">
         <v>4</v>
@@ -38689,25 +38692,25 @@
         <v>2.24</v>
       </c>
       <c r="AN182">
-        <v>2</v>
+        <v>1.64</v>
       </c>
       <c r="AO182">
-        <v>0.89</v>
+        <v>1.14</v>
       </c>
       <c r="AP182">
-        <v>2.08</v>
+        <v>1.67</v>
       </c>
       <c r="AQ182">
-        <v>0.8</v>
+        <v>1.17</v>
       </c>
       <c r="AR182">
-        <v>1.67</v>
+        <v>1.51</v>
       </c>
       <c r="AS182">
-        <v>1.48</v>
+        <v>1.51</v>
       </c>
       <c r="AT182">
-        <v>3.15</v>
+        <v>3.02</v>
       </c>
       <c r="AU182">
         <v>10</v>
@@ -38823,7 +38826,7 @@
         <v>208</v>
       </c>
       <c r="P183" t="s">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="Q183">
         <v>4.3</v>
@@ -38895,25 +38898,25 @@
         <v>1.28</v>
       </c>
       <c r="AN183">
-        <v>2.64</v>
+        <v>2.23</v>
       </c>
       <c r="AO183">
-        <v>2.36</v>
+        <v>2.68</v>
       </c>
       <c r="AP183">
-        <v>2.42</v>
+        <v>2.17</v>
       </c>
       <c r="AQ183">
-        <v>2.42</v>
+        <v>2.71</v>
       </c>
       <c r="AR183">
-        <v>1.82</v>
+        <v>1.61</v>
       </c>
       <c r="AS183">
-        <v>1.91</v>
+        <v>2.1</v>
       </c>
       <c r="AT183">
-        <v>3.73</v>
+        <v>3.71</v>
       </c>
       <c r="AU183">
         <v>5</v>
@@ -39029,7 +39032,7 @@
         <v>88</v>
       </c>
       <c r="P184" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="Q184">
         <v>5.8</v>
@@ -39101,25 +39104,25 @@
         <v>1.13</v>
       </c>
       <c r="AN184">
-        <v>0.25</v>
+        <v>0.17</v>
       </c>
       <c r="AO184">
-        <v>1.5</v>
+        <v>1.96</v>
       </c>
       <c r="AP184">
-        <v>0.23</v>
+        <v>0.17</v>
       </c>
       <c r="AQ184">
-        <v>1.62</v>
+        <v>2</v>
       </c>
       <c r="AR184">
-        <v>1.24</v>
+        <v>1.11</v>
       </c>
       <c r="AS184">
-        <v>1.65</v>
+        <v>1.71</v>
       </c>
       <c r="AT184">
-        <v>2.89</v>
+        <v>2.82</v>
       </c>
       <c r="AU184">
         <v>2</v>
@@ -39307,25 +39310,25 @@
         <v>1.5</v>
       </c>
       <c r="AN185">
-        <v>1.64</v>
+        <v>1.32</v>
       </c>
       <c r="AO185">
-        <v>1.27</v>
+        <v>1.7</v>
       </c>
       <c r="AP185">
-        <v>1.58</v>
+        <v>1.3</v>
       </c>
       <c r="AQ185">
-        <v>1.25</v>
+        <v>1.67</v>
       </c>
       <c r="AR185">
-        <v>1.46</v>
+        <v>1.35</v>
       </c>
       <c r="AS185">
-        <v>1.36</v>
+        <v>1.53</v>
       </c>
       <c r="AT185">
-        <v>2.82</v>
+        <v>2.88</v>
       </c>
       <c r="AU185">
         <v>4</v>
@@ -39441,7 +39444,7 @@
         <v>96</v>
       </c>
       <c r="P186" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="Q186">
         <v>4.7</v>
@@ -39513,25 +39516,25 @@
         <v>1.2</v>
       </c>
       <c r="AN186">
-        <v>1.82</v>
+        <v>1.52</v>
       </c>
       <c r="AO186">
-        <v>2.09</v>
+        <v>2.13</v>
       </c>
       <c r="AP186">
-        <v>1.67</v>
+        <v>1.46</v>
       </c>
       <c r="AQ186">
         <v>2.17</v>
       </c>
       <c r="AR186">
-        <v>1.58</v>
+        <v>1.4</v>
       </c>
       <c r="AS186">
-        <v>1.69</v>
+        <v>1.91</v>
       </c>
       <c r="AT186">
-        <v>3.27</v>
+        <v>3.31</v>
       </c>
       <c r="AU186">
         <v>3</v>
@@ -39719,25 +39722,25 @@
         <v>2.14</v>
       </c>
       <c r="AN187">
-        <v>1.18</v>
+        <v>0.96</v>
       </c>
       <c r="AO187">
-        <v>0.5</v>
+        <v>0.65</v>
       </c>
       <c r="AP187">
-        <v>1.33</v>
+        <v>1.04</v>
       </c>
       <c r="AQ187">
-        <v>0.46</v>
+        <v>0.63</v>
       </c>
       <c r="AR187">
-        <v>1.45</v>
+        <v>1.38</v>
       </c>
       <c r="AS187">
-        <v>1.03</v>
+        <v>1.12</v>
       </c>
       <c r="AT187">
-        <v>2.48</v>
+        <v>2.5</v>
       </c>
       <c r="AU187">
         <v>7</v>
@@ -39925,25 +39928,25 @@
         <v>2.55</v>
       </c>
       <c r="AN188">
-        <v>1.45</v>
+        <v>1.22</v>
       </c>
       <c r="AO188">
-        <v>0.36</v>
+        <v>0.64</v>
       </c>
       <c r="AP188">
-        <v>1.42</v>
+        <v>1.21</v>
       </c>
       <c r="AQ188">
-        <v>0.42</v>
+        <v>0.65</v>
       </c>
       <c r="AR188">
-        <v>1.49</v>
+        <v>1.47</v>
       </c>
       <c r="AS188">
-        <v>0.91</v>
+        <v>1.07</v>
       </c>
       <c r="AT188">
-        <v>2.4</v>
+        <v>2.54</v>
       </c>
       <c r="AU188">
         <v>4</v>
@@ -40059,7 +40062,7 @@
         <v>88</v>
       </c>
       <c r="P189" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="Q189">
         <v>4.5</v>
@@ -40131,25 +40134,25 @@
         <v>1.22</v>
       </c>
       <c r="AN189">
-        <v>1.73</v>
+        <v>1.48</v>
       </c>
       <c r="AO189">
-        <v>1.82</v>
+        <v>2.13</v>
       </c>
       <c r="AP189">
-        <v>1.58</v>
+        <v>1.42</v>
       </c>
       <c r="AQ189">
-        <v>1.92</v>
+        <v>2.17</v>
       </c>
       <c r="AR189">
-        <v>1.57</v>
+        <v>1.46</v>
       </c>
       <c r="AS189">
-        <v>1.41</v>
+        <v>1.6</v>
       </c>
       <c r="AT189">
-        <v>2.98</v>
+        <v>3.06</v>
       </c>
       <c r="AU189">
         <v>4</v>
@@ -40337,25 +40340,25 @@
         <v>1.63</v>
       </c>
       <c r="AN190">
-        <v>1.33</v>
+        <v>1.09</v>
       </c>
       <c r="AO190">
-        <v>1</v>
+        <v>1.18</v>
       </c>
       <c r="AP190">
-        <v>1.46</v>
+        <v>1.17</v>
       </c>
       <c r="AQ190">
-        <v>0.92</v>
+        <v>1.13</v>
       </c>
       <c r="AR190">
-        <v>1.53</v>
+        <v>1.48</v>
       </c>
       <c r="AS190">
-        <v>1.24</v>
+        <v>1.22</v>
       </c>
       <c r="AT190">
-        <v>2.77</v>
+        <v>2.7</v>
       </c>
       <c r="AU190">
         <v>7</v>
@@ -40422,6 +40425,212 @@
       </c>
       <c r="BP190">
         <v>1.45</v>
+      </c>
+    </row>
+    <row r="191" spans="1:68">
+      <c r="A191" s="1">
+        <v>190</v>
+      </c>
+      <c r="B191">
+        <v>7468273</v>
+      </c>
+      <c r="C191" t="s">
+        <v>68</v>
+      </c>
+      <c r="D191" t="s">
+        <v>69</v>
+      </c>
+      <c r="E191" s="2">
+        <v>45718.60416666666</v>
+      </c>
+      <c r="F191">
+        <v>24</v>
+      </c>
+      <c r="G191" t="s">
+        <v>80</v>
+      </c>
+      <c r="H191" t="s">
+        <v>73</v>
+      </c>
+      <c r="I191">
+        <v>0</v>
+      </c>
+      <c r="J191">
+        <v>0</v>
+      </c>
+      <c r="K191">
+        <v>0</v>
+      </c>
+      <c r="L191">
+        <v>2</v>
+      </c>
+      <c r="M191">
+        <v>0</v>
+      </c>
+      <c r="N191">
+        <v>2</v>
+      </c>
+      <c r="O191" t="s">
+        <v>212</v>
+      </c>
+      <c r="P191" t="s">
+        <v>88</v>
+      </c>
+      <c r="Q191">
+        <v>1.62</v>
+      </c>
+      <c r="R191">
+        <v>2.75</v>
+      </c>
+      <c r="S191">
+        <v>9.5</v>
+      </c>
+      <c r="T191">
+        <v>1.25</v>
+      </c>
+      <c r="U191">
+        <v>3.75</v>
+      </c>
+      <c r="V191">
+        <v>2.2</v>
+      </c>
+      <c r="W191">
+        <v>1.62</v>
+      </c>
+      <c r="X191">
+        <v>5</v>
+      </c>
+      <c r="Y191">
+        <v>1.17</v>
+      </c>
+      <c r="Z191">
+        <v>1.22</v>
+      </c>
+      <c r="AA191">
+        <v>6.5</v>
+      </c>
+      <c r="AB191">
+        <v>9.5</v>
+      </c>
+      <c r="AC191">
+        <v>0</v>
+      </c>
+      <c r="AD191">
+        <v>0</v>
+      </c>
+      <c r="AE191">
+        <v>2.2</v>
+      </c>
+      <c r="AF191">
+        <v>1.64</v>
+      </c>
+      <c r="AG191">
+        <v>1.5</v>
+      </c>
+      <c r="AH191">
+        <v>2.5</v>
+      </c>
+      <c r="AI191">
+        <v>2.05</v>
+      </c>
+      <c r="AJ191">
+        <v>1.7</v>
+      </c>
+      <c r="AK191">
+        <v>0</v>
+      </c>
+      <c r="AL191">
+        <v>0</v>
+      </c>
+      <c r="AM191">
+        <v>0</v>
+      </c>
+      <c r="AN191">
+        <v>2.7</v>
+      </c>
+      <c r="AO191">
+        <v>1.3</v>
+      </c>
+      <c r="AP191">
+        <v>2.71</v>
+      </c>
+      <c r="AQ191">
+        <v>1.25</v>
+      </c>
+      <c r="AR191">
+        <v>2.08</v>
+      </c>
+      <c r="AS191">
+        <v>1.48</v>
+      </c>
+      <c r="AT191">
+        <v>3.56</v>
+      </c>
+      <c r="AU191">
+        <v>10</v>
+      </c>
+      <c r="AV191">
+        <v>3</v>
+      </c>
+      <c r="AW191">
+        <v>10</v>
+      </c>
+      <c r="AX191">
+        <v>3</v>
+      </c>
+      <c r="AY191">
+        <v>20</v>
+      </c>
+      <c r="AZ191">
+        <v>6</v>
+      </c>
+      <c r="BA191">
+        <v>13</v>
+      </c>
+      <c r="BB191">
+        <v>4</v>
+      </c>
+      <c r="BC191">
+        <v>17</v>
+      </c>
+      <c r="BD191">
+        <v>0</v>
+      </c>
+      <c r="BE191">
+        <v>0</v>
+      </c>
+      <c r="BF191">
+        <v>0</v>
+      </c>
+      <c r="BG191">
+        <v>0</v>
+      </c>
+      <c r="BH191">
+        <v>0</v>
+      </c>
+      <c r="BI191">
+        <v>0</v>
+      </c>
+      <c r="BJ191">
+        <v>0</v>
+      </c>
+      <c r="BK191">
+        <v>0</v>
+      </c>
+      <c r="BL191">
+        <v>0</v>
+      </c>
+      <c r="BM191">
+        <v>0</v>
+      </c>
+      <c r="BN191">
+        <v>0</v>
+      </c>
+      <c r="BO191">
+        <v>0</v>
+      </c>
+      <c r="BP191">
+        <v>0</v>
       </c>
     </row>
   </sheetData>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Czech Republic First League_20242025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Czech Republic First League_20242025.xlsx
@@ -1621,7 +1621,7 @@
         <v>2.17</v>
       </c>
       <c r="AQ2">
-        <v>0.63</v>
+        <v>0.46</v>
       </c>
       <c r="AR2">
         <v>0</v>
@@ -1824,10 +1824,10 @@
         <v>0</v>
       </c>
       <c r="AP3">
-        <v>1.67</v>
+        <v>2.08</v>
       </c>
       <c r="AQ3">
-        <v>1.42</v>
+        <v>1.25</v>
       </c>
       <c r="AR3">
         <v>0</v>
@@ -2030,10 +2030,10 @@
         <v>0</v>
       </c>
       <c r="AP4">
-        <v>0.17</v>
+        <v>0.23</v>
       </c>
       <c r="AQ4">
-        <v>1.46</v>
+        <v>1.25</v>
       </c>
       <c r="AR4">
         <v>0</v>
@@ -2236,10 +2236,10 @@
         <v>0</v>
       </c>
       <c r="AP5">
-        <v>1.25</v>
+        <v>1.17</v>
       </c>
       <c r="AQ5">
-        <v>2</v>
+        <v>1.62</v>
       </c>
       <c r="AR5">
         <v>0</v>
@@ -2442,10 +2442,10 @@
         <v>0</v>
       </c>
       <c r="AP6">
-        <v>0.65</v>
+        <v>0.91</v>
       </c>
       <c r="AQ6">
-        <v>2.17</v>
+        <v>1.92</v>
       </c>
       <c r="AR6">
         <v>0</v>
@@ -2648,10 +2648,10 @@
         <v>0</v>
       </c>
       <c r="AP7">
-        <v>1.17</v>
+        <v>1.46</v>
       </c>
       <c r="AQ7">
-        <v>1.21</v>
+        <v>1</v>
       </c>
       <c r="AR7">
         <v>0</v>
@@ -2854,10 +2854,10 @@
         <v>0</v>
       </c>
       <c r="AP8">
-        <v>1.13</v>
+        <v>1.36</v>
       </c>
       <c r="AQ8">
-        <v>2.71</v>
+        <v>2.42</v>
       </c>
       <c r="AR8">
         <v>0</v>
@@ -3060,10 +3060,10 @@
         <v>0</v>
       </c>
       <c r="AP9">
-        <v>1.3</v>
+        <v>1.58</v>
       </c>
       <c r="AQ9">
-        <v>1.04</v>
+        <v>0.75</v>
       </c>
       <c r="AR9">
         <v>0</v>
@@ -3263,22 +3263,22 @@
         <v>0</v>
       </c>
       <c r="AO10">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="AP10">
-        <v>0.65</v>
+        <v>0.91</v>
       </c>
       <c r="AQ10">
-        <v>1.25</v>
+        <v>1.33</v>
       </c>
       <c r="AR10">
         <v>0.98</v>
       </c>
       <c r="AS10">
-        <v>1.73</v>
+        <v>0</v>
       </c>
       <c r="AT10">
-        <v>2.71</v>
+        <v>0.98</v>
       </c>
       <c r="AU10">
         <v>3</v>
@@ -3469,22 +3469,22 @@
         <v>0</v>
       </c>
       <c r="AO11">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="AP11">
-        <v>1.04</v>
+        <v>1.33</v>
       </c>
       <c r="AQ11">
         <v>2.17</v>
       </c>
       <c r="AR11">
-        <v>1.21</v>
+        <v>0</v>
       </c>
       <c r="AS11">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AT11">
-        <v>3.11</v>
+        <v>0</v>
       </c>
       <c r="AU11">
         <v>4</v>
@@ -3678,19 +3678,19 @@
         <v>0</v>
       </c>
       <c r="AP12">
-        <v>0.63</v>
+        <v>0.82</v>
       </c>
       <c r="AQ12">
-        <v>1.17</v>
+        <v>0.8</v>
       </c>
       <c r="AR12">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="AS12">
-        <v>1.93</v>
+        <v>0</v>
       </c>
       <c r="AT12">
-        <v>2.96</v>
+        <v>0</v>
       </c>
       <c r="AU12">
         <v>3</v>
@@ -3878,25 +3878,25 @@
         <v>5.85</v>
       </c>
       <c r="AN13">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AO13">
         <v>0</v>
       </c>
       <c r="AP13">
-        <v>2.71</v>
+        <v>3</v>
       </c>
       <c r="AQ13">
-        <v>0.17</v>
+        <v>0.09</v>
       </c>
       <c r="AR13">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="AS13">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="AT13">
-        <v>2.98</v>
+        <v>0</v>
       </c>
       <c r="AU13">
         <v>9</v>
@@ -4084,25 +4084,25 @@
         <v>1.78</v>
       </c>
       <c r="AN14">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="AO14">
         <v>3</v>
       </c>
       <c r="AP14">
-        <v>1.21</v>
+        <v>1.42</v>
       </c>
       <c r="AQ14">
-        <v>1.46</v>
+        <v>1.25</v>
       </c>
       <c r="AR14">
-        <v>1.97</v>
+        <v>0</v>
       </c>
       <c r="AS14">
         <v>2.08</v>
       </c>
       <c r="AT14">
-        <v>4.05</v>
+        <v>2.08</v>
       </c>
       <c r="AU14">
         <v>4</v>
@@ -4293,22 +4293,22 @@
         <v>0</v>
       </c>
       <c r="AO15">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AP15">
-        <v>1.42</v>
+        <v>1.58</v>
       </c>
       <c r="AQ15">
-        <v>1.13</v>
+        <v>0.92</v>
       </c>
       <c r="AR15">
-        <v>0.9399999999999999</v>
+        <v>0</v>
       </c>
       <c r="AS15">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AT15">
-        <v>1.94</v>
+        <v>0</v>
       </c>
       <c r="AU15">
         <v>7</v>
@@ -4499,22 +4499,22 @@
         <v>0</v>
       </c>
       <c r="AO16">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="AP16">
-        <v>2</v>
+        <v>2.45</v>
       </c>
       <c r="AQ16">
-        <v>1.67</v>
+        <v>1.25</v>
       </c>
       <c r="AR16">
-        <v>1.71</v>
+        <v>0</v>
       </c>
       <c r="AS16">
-        <v>1.81</v>
+        <v>0</v>
       </c>
       <c r="AT16">
-        <v>3.52</v>
+        <v>0</v>
       </c>
       <c r="AU16">
         <v>5</v>
@@ -4702,25 +4702,25 @@
         <v>2.7</v>
       </c>
       <c r="AN17">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="AO17">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="AP17">
-        <v>2.17</v>
+        <v>2.42</v>
       </c>
       <c r="AQ17">
-        <v>1.3</v>
+        <v>1</v>
       </c>
       <c r="AR17">
-        <v>1.43</v>
+        <v>0</v>
       </c>
       <c r="AS17">
-        <v>1.19</v>
+        <v>0</v>
       </c>
       <c r="AT17">
-        <v>2.62</v>
+        <v>0</v>
       </c>
       <c r="AU17">
         <v>8</v>
@@ -4908,25 +4908,25 @@
         <v>1.12</v>
       </c>
       <c r="AN18">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AO18">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AP18">
-        <v>1.21</v>
+        <v>1.42</v>
       </c>
       <c r="AQ18">
-        <v>2.71</v>
+        <v>2.42</v>
       </c>
       <c r="AR18">
-        <v>1.61</v>
+        <v>1.26</v>
       </c>
       <c r="AS18">
-        <v>2.02</v>
+        <v>1.65</v>
       </c>
       <c r="AT18">
-        <v>3.63</v>
+        <v>2.91</v>
       </c>
       <c r="AU18">
         <v>4</v>
@@ -5117,22 +5117,22 @@
         <v>3</v>
       </c>
       <c r="AO19">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="AP19">
         <v>2.17</v>
       </c>
       <c r="AQ19">
-        <v>0.65</v>
+        <v>0.42</v>
       </c>
       <c r="AR19">
-        <v>1.96</v>
+        <v>1.9</v>
       </c>
       <c r="AS19">
-        <v>0.93</v>
+        <v>0</v>
       </c>
       <c r="AT19">
-        <v>2.89</v>
+        <v>1.9</v>
       </c>
       <c r="AU19">
         <v>9</v>
@@ -5320,25 +5320,25 @@
         <v>1.8</v>
       </c>
       <c r="AN20">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="AO20">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="AP20">
-        <v>1.13</v>
+        <v>1.36</v>
       </c>
       <c r="AQ20">
-        <v>1.25</v>
+        <v>1.33</v>
       </c>
       <c r="AR20">
-        <v>1.25</v>
+        <v>1</v>
       </c>
       <c r="AS20">
-        <v>1.81</v>
+        <v>1.88</v>
       </c>
       <c r="AT20">
-        <v>3.06</v>
+        <v>2.88</v>
       </c>
       <c r="AU20">
         <v>4</v>
@@ -5526,25 +5526,25 @@
         <v>1.17</v>
       </c>
       <c r="AN21">
-        <v>1.5</v>
+        <v>3</v>
       </c>
       <c r="AO21">
         <v>3</v>
       </c>
       <c r="AP21">
-        <v>1.67</v>
+        <v>2.08</v>
       </c>
       <c r="AQ21">
-        <v>2.17</v>
+        <v>1.92</v>
       </c>
       <c r="AR21">
-        <v>1.38</v>
+        <v>1.81</v>
       </c>
       <c r="AS21">
-        <v>1.53</v>
+        <v>1.43</v>
       </c>
       <c r="AT21">
-        <v>2.91</v>
+        <v>3.24</v>
       </c>
       <c r="AU21">
         <v>5</v>
@@ -5732,25 +5732,25 @@
         <v>1.71</v>
       </c>
       <c r="AN22">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AO22">
         <v>0</v>
       </c>
       <c r="AP22">
-        <v>1.46</v>
+        <v>1.67</v>
       </c>
       <c r="AQ22">
-        <v>1.04</v>
+        <v>0.75</v>
       </c>
       <c r="AR22">
-        <v>1.48</v>
+        <v>0</v>
       </c>
       <c r="AS22">
-        <v>1.13</v>
+        <v>1.21</v>
       </c>
       <c r="AT22">
-        <v>2.61</v>
+        <v>1.21</v>
       </c>
       <c r="AU22">
         <v>5</v>
@@ -5944,19 +5944,19 @@
         <v>0</v>
       </c>
       <c r="AP23">
-        <v>0.17</v>
+        <v>0.23</v>
       </c>
       <c r="AQ23">
-        <v>0.63</v>
+        <v>0.46</v>
       </c>
       <c r="AR23">
-        <v>0.92</v>
+        <v>1.33</v>
       </c>
       <c r="AS23">
-        <v>1.12</v>
+        <v>1.03</v>
       </c>
       <c r="AT23">
-        <v>2.04</v>
+        <v>2.36</v>
       </c>
       <c r="AU23">
         <v>5</v>
@@ -6144,25 +6144,25 @@
         <v>1.78</v>
       </c>
       <c r="AN24">
-        <v>1.5</v>
+        <v>3</v>
       </c>
       <c r="AO24">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="AP24">
-        <v>1.3</v>
+        <v>1.58</v>
       </c>
       <c r="AQ24">
-        <v>1.42</v>
+        <v>1.25</v>
       </c>
       <c r="AR24">
-        <v>0.95</v>
+        <v>1.19</v>
       </c>
       <c r="AS24">
-        <v>1.35</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="AT24">
-        <v>2.3</v>
+        <v>2.13</v>
       </c>
       <c r="AU24">
         <v>4</v>
@@ -6350,25 +6350,25 @@
         <v>1.29</v>
       </c>
       <c r="AN25">
-        <v>1</v>
+        <v>1.5</v>
       </c>
       <c r="AO25">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="AP25">
-        <v>0.65</v>
+        <v>0.91</v>
       </c>
       <c r="AQ25">
-        <v>1.67</v>
+        <v>1.25</v>
       </c>
       <c r="AR25">
-        <v>0.82</v>
+        <v>0.93</v>
       </c>
       <c r="AS25">
-        <v>1.35</v>
+        <v>0.95</v>
       </c>
       <c r="AT25">
-        <v>2.17</v>
+        <v>1.88</v>
       </c>
       <c r="AU25">
         <v>3</v>
@@ -6556,25 +6556,25 @@
         <v>1.1</v>
       </c>
       <c r="AN26">
-        <v>1.33</v>
+        <v>3</v>
       </c>
       <c r="AO26">
         <v>3</v>
       </c>
       <c r="AP26">
-        <v>1.25</v>
+        <v>1.17</v>
       </c>
       <c r="AQ26">
         <v>2.17</v>
       </c>
       <c r="AR26">
-        <v>1.45</v>
+        <v>1.73</v>
       </c>
       <c r="AS26">
-        <v>2.06</v>
+        <v>2.02</v>
       </c>
       <c r="AT26">
-        <v>3.51</v>
+        <v>3.75</v>
       </c>
       <c r="AU26">
         <v>6</v>
@@ -6765,22 +6765,22 @@
         <v>0</v>
       </c>
       <c r="AO27">
+        <v>3</v>
+      </c>
+      <c r="AP27">
         <v>1.33</v>
       </c>
-      <c r="AP27">
-        <v>1.04</v>
-      </c>
       <c r="AQ27">
-        <v>1.21</v>
+        <v>1</v>
       </c>
       <c r="AR27">
-        <v>1.28</v>
+        <v>1.06</v>
       </c>
       <c r="AS27">
-        <v>1.55</v>
+        <v>1.97</v>
       </c>
       <c r="AT27">
-        <v>2.83</v>
+        <v>3.03</v>
       </c>
       <c r="AU27">
         <v>6</v>
@@ -6968,25 +6968,25 @@
         <v>4.33</v>
       </c>
       <c r="AN28">
-        <v>2.33</v>
+        <v>3</v>
       </c>
       <c r="AO28">
-        <v>2.33</v>
+        <v>2</v>
       </c>
       <c r="AP28">
-        <v>2.71</v>
+        <v>3</v>
       </c>
       <c r="AQ28">
-        <v>1.46</v>
+        <v>1.25</v>
       </c>
       <c r="AR28">
-        <v>1.7</v>
+        <v>2.4</v>
       </c>
       <c r="AS28">
-        <v>1.4</v>
+        <v>1.48</v>
       </c>
       <c r="AT28">
-        <v>3.1</v>
+        <v>3.88</v>
       </c>
       <c r="AU28">
         <v>9</v>
@@ -7174,25 +7174,25 @@
         <v>1.36</v>
       </c>
       <c r="AN29">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AO29">
-        <v>0.67</v>
+        <v>0</v>
       </c>
       <c r="AP29">
-        <v>0.63</v>
+        <v>0.82</v>
       </c>
       <c r="AQ29">
-        <v>1.13</v>
+        <v>0.92</v>
       </c>
       <c r="AR29">
-        <v>1.07</v>
+        <v>1.22</v>
       </c>
       <c r="AS29">
-        <v>1.29</v>
+        <v>1.5</v>
       </c>
       <c r="AT29">
-        <v>2.36</v>
+        <v>2.72</v>
       </c>
       <c r="AU29">
         <v>4</v>
@@ -7380,25 +7380,25 @@
         <v>2.2</v>
       </c>
       <c r="AN30">
-        <v>1.5</v>
+        <v>3</v>
       </c>
       <c r="AO30">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AP30">
-        <v>2</v>
+        <v>2.45</v>
       </c>
       <c r="AQ30">
-        <v>1.3</v>
+        <v>1</v>
       </c>
       <c r="AR30">
-        <v>1.47</v>
+        <v>1.24</v>
       </c>
       <c r="AS30">
-        <v>0.96</v>
+        <v>0.71</v>
       </c>
       <c r="AT30">
-        <v>2.43</v>
+        <v>1.95</v>
       </c>
       <c r="AU30">
         <v>6</v>
@@ -7586,25 +7586,25 @@
         <v>2.38</v>
       </c>
       <c r="AN31">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="AO31">
         <v>0</v>
       </c>
       <c r="AP31">
-        <v>1.42</v>
+        <v>1.58</v>
       </c>
       <c r="AQ31">
-        <v>0.17</v>
+        <v>0.09</v>
       </c>
       <c r="AR31">
-        <v>1.63</v>
+        <v>1.76</v>
       </c>
       <c r="AS31">
-        <v>1.14</v>
+        <v>0.5</v>
       </c>
       <c r="AT31">
-        <v>2.77</v>
+        <v>2.26</v>
       </c>
       <c r="AU31">
         <v>7</v>
@@ -7792,25 +7792,25 @@
         <v>3.1</v>
       </c>
       <c r="AN32">
-        <v>2.33</v>
+        <v>3</v>
       </c>
       <c r="AO32">
-        <v>1.5</v>
+        <v>3</v>
       </c>
       <c r="AP32">
-        <v>2.17</v>
+        <v>2.42</v>
       </c>
       <c r="AQ32">
-        <v>1.17</v>
+        <v>0.8</v>
       </c>
       <c r="AR32">
-        <v>1.38</v>
+        <v>1.64</v>
       </c>
       <c r="AS32">
-        <v>2.15</v>
+        <v>2.37</v>
       </c>
       <c r="AT32">
-        <v>3.53</v>
+        <v>4.01</v>
       </c>
       <c r="AU32">
         <v>8</v>
@@ -7998,25 +7998,25 @@
         <v>2.35</v>
       </c>
       <c r="AN33">
-        <v>1.5</v>
+        <v>3</v>
       </c>
       <c r="AO33">
-        <v>0.75</v>
+        <v>0</v>
       </c>
       <c r="AP33">
-        <v>1.3</v>
+        <v>1.58</v>
       </c>
       <c r="AQ33">
-        <v>0.65</v>
+        <v>0.42</v>
       </c>
       <c r="AR33">
-        <v>0.84</v>
+        <v>1.08</v>
       </c>
       <c r="AS33">
-        <v>0.88</v>
+        <v>0.61</v>
       </c>
       <c r="AT33">
-        <v>1.72</v>
+        <v>1.69</v>
       </c>
       <c r="AU33">
         <v>6</v>
@@ -8204,25 +8204,25 @@
         <v>5.5</v>
       </c>
       <c r="AN34">
-        <v>2.5</v>
+        <v>3</v>
       </c>
       <c r="AO34">
+        <v>0</v>
+      </c>
+      <c r="AP34">
+        <v>3</v>
+      </c>
+      <c r="AQ34">
         <v>0.75</v>
       </c>
-      <c r="AP34">
-        <v>2.71</v>
-      </c>
-      <c r="AQ34">
-        <v>1.04</v>
-      </c>
       <c r="AR34">
-        <v>1.82</v>
+        <v>2.27</v>
       </c>
       <c r="AS34">
-        <v>1.4</v>
+        <v>1.39</v>
       </c>
       <c r="AT34">
-        <v>3.22</v>
+        <v>3.66</v>
       </c>
       <c r="AU34">
         <v>7</v>
@@ -8410,25 +8410,25 @@
         <v>1.62</v>
       </c>
       <c r="AN35">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AO35">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="AP35">
-        <v>1.17</v>
+        <v>1.46</v>
       </c>
       <c r="AQ35">
-        <v>1.25</v>
+        <v>1.33</v>
       </c>
       <c r="AR35">
-        <v>1.78</v>
+        <v>1.93</v>
       </c>
       <c r="AS35">
-        <v>1.4</v>
+        <v>1.32</v>
       </c>
       <c r="AT35">
-        <v>3.18</v>
+        <v>3.25</v>
       </c>
       <c r="AU35">
         <v>4</v>
@@ -8616,25 +8616,25 @@
         <v>1.15</v>
       </c>
       <c r="AN36">
-        <v>1.75</v>
+        <v>2</v>
       </c>
       <c r="AO36">
         <v>3</v>
       </c>
       <c r="AP36">
-        <v>1.67</v>
+        <v>2.08</v>
       </c>
       <c r="AQ36">
         <v>2.17</v>
       </c>
       <c r="AR36">
-        <v>1.38</v>
+        <v>1.54</v>
       </c>
       <c r="AS36">
         <v>2.07</v>
       </c>
       <c r="AT36">
-        <v>3.45</v>
+        <v>3.61</v>
       </c>
       <c r="AU36">
         <v>5</v>
@@ -8822,25 +8822,25 @@
         <v>1.71</v>
       </c>
       <c r="AN37">
-        <v>1.75</v>
+        <v>3</v>
       </c>
       <c r="AO37">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="AP37">
-        <v>1.46</v>
+        <v>1.67</v>
       </c>
       <c r="AQ37">
-        <v>1.42</v>
+        <v>1.25</v>
       </c>
       <c r="AR37">
-        <v>1.23</v>
+        <v>1.25</v>
       </c>
       <c r="AS37">
-        <v>1.63</v>
+        <v>1.56</v>
       </c>
       <c r="AT37">
-        <v>2.86</v>
+        <v>2.81</v>
       </c>
       <c r="AU37">
         <v>5</v>
@@ -9028,25 +9028,25 @@
         <v>2.88</v>
       </c>
       <c r="AN38">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="AO38">
-        <v>0.75</v>
+        <v>1.5</v>
       </c>
       <c r="AP38">
-        <v>1.21</v>
+        <v>1.42</v>
       </c>
       <c r="AQ38">
-        <v>0.63</v>
+        <v>0.46</v>
       </c>
       <c r="AR38">
-        <v>1.51</v>
+        <v>1.34</v>
       </c>
       <c r="AS38">
-        <v>1.08</v>
+        <v>1</v>
       </c>
       <c r="AT38">
-        <v>2.59</v>
+        <v>2.34</v>
       </c>
       <c r="AU38">
         <v>6</v>
@@ -9237,19 +9237,19 @@
         <v>0</v>
       </c>
       <c r="AO39">
-        <v>2.5</v>
+        <v>2</v>
       </c>
       <c r="AP39">
-        <v>0.17</v>
+        <v>0.23</v>
       </c>
       <c r="AQ39">
-        <v>2.17</v>
+        <v>1.92</v>
       </c>
       <c r="AR39">
-        <v>1.16</v>
+        <v>1.46</v>
       </c>
       <c r="AS39">
-        <v>1.55</v>
+        <v>1.25</v>
       </c>
       <c r="AT39">
         <v>2.71</v>
@@ -9440,25 +9440,25 @@
         <v>1.53</v>
       </c>
       <c r="AN40">
-        <v>1.25</v>
+        <v>1</v>
       </c>
       <c r="AO40">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AP40">
-        <v>1.13</v>
+        <v>1.36</v>
       </c>
       <c r="AQ40">
-        <v>2</v>
+        <v>1.62</v>
       </c>
       <c r="AR40">
         <v>1.19</v>
       </c>
       <c r="AS40">
-        <v>1.82</v>
+        <v>1.71</v>
       </c>
       <c r="AT40">
-        <v>3.01</v>
+        <v>2.9</v>
       </c>
       <c r="AU40">
         <v>6</v>
@@ -9646,25 +9646,25 @@
         <v>1.88</v>
       </c>
       <c r="AN41">
-        <v>1.4</v>
+        <v>1.5</v>
       </c>
       <c r="AO41">
-        <v>1.4</v>
+        <v>1.5</v>
       </c>
       <c r="AP41">
+        <v>1.17</v>
+      </c>
+      <c r="AQ41">
         <v>1.25</v>
       </c>
-      <c r="AQ41">
-        <v>1.67</v>
-      </c>
       <c r="AR41">
-        <v>1.45</v>
+        <v>1.49</v>
       </c>
       <c r="AS41">
-        <v>1.4</v>
+        <v>1.21</v>
       </c>
       <c r="AT41">
-        <v>2.85</v>
+        <v>2.7</v>
       </c>
       <c r="AU41">
         <v>6</v>
@@ -9852,25 +9852,25 @@
         <v>1.75</v>
       </c>
       <c r="AN42">
-        <v>0.6</v>
+        <v>1.5</v>
       </c>
       <c r="AO42">
-        <v>0.75</v>
+        <v>1.5</v>
       </c>
       <c r="AP42">
-        <v>1.04</v>
+        <v>1.33</v>
       </c>
       <c r="AQ42">
-        <v>1.17</v>
+        <v>0.8</v>
       </c>
       <c r="AR42">
-        <v>1.3</v>
+        <v>1.41</v>
       </c>
       <c r="AS42">
-        <v>1.74</v>
+        <v>1.7</v>
       </c>
       <c r="AT42">
-        <v>3.04</v>
+        <v>3.11</v>
       </c>
       <c r="AU42">
         <v>3</v>
@@ -10061,22 +10061,22 @@
         <v>3</v>
       </c>
       <c r="AO43">
-        <v>1.6</v>
+        <v>1.5</v>
       </c>
       <c r="AP43">
         <v>2.17</v>
       </c>
       <c r="AQ43">
-        <v>1.13</v>
+        <v>0.92</v>
       </c>
       <c r="AR43">
         <v>2.07</v>
       </c>
       <c r="AS43">
-        <v>1.22</v>
+        <v>1.2</v>
       </c>
       <c r="AT43">
-        <v>3.29</v>
+        <v>3.27</v>
       </c>
       <c r="AU43">
         <v>8</v>
@@ -10264,25 +10264,25 @@
         <v>1.35</v>
       </c>
       <c r="AN44">
+        <v>0</v>
+      </c>
+      <c r="AO44">
+        <v>0</v>
+      </c>
+      <c r="AP44">
+        <v>0.82</v>
+      </c>
+      <c r="AQ44">
+        <v>1</v>
+      </c>
+      <c r="AR44">
+        <v>1.16</v>
+      </c>
+      <c r="AS44">
         <v>0.6</v>
       </c>
-      <c r="AO44">
-        <v>1.8</v>
-      </c>
-      <c r="AP44">
-        <v>0.63</v>
-      </c>
-      <c r="AQ44">
-        <v>1.3</v>
-      </c>
-      <c r="AR44">
-        <v>1.04</v>
-      </c>
-      <c r="AS44">
-        <v>0.98</v>
-      </c>
       <c r="AT44">
-        <v>2.02</v>
+        <v>1.76</v>
       </c>
       <c r="AU44">
         <v>6</v>
@@ -10470,25 +10470,25 @@
         <v>1.84</v>
       </c>
       <c r="AN45">
+        <v>3</v>
+      </c>
+      <c r="AO45">
         <v>1.5</v>
       </c>
-      <c r="AO45">
-        <v>1.4</v>
-      </c>
       <c r="AP45">
-        <v>2</v>
+        <v>2.45</v>
       </c>
       <c r="AQ45">
-        <v>1.21</v>
+        <v>1</v>
       </c>
       <c r="AR45">
-        <v>1.75</v>
+        <v>1.87</v>
       </c>
       <c r="AS45">
-        <v>1.47</v>
+        <v>1.68</v>
       </c>
       <c r="AT45">
-        <v>3.22</v>
+        <v>3.55</v>
       </c>
       <c r="AU45">
         <v>8</v>
@@ -10676,25 +10676,25 @@
         <v>1.67</v>
       </c>
       <c r="AN46">
-        <v>0.6</v>
+        <v>1</v>
       </c>
       <c r="AO46">
         <v>0</v>
       </c>
       <c r="AP46">
-        <v>0.65</v>
+        <v>0.91</v>
       </c>
       <c r="AQ46">
-        <v>0.17</v>
+        <v>0.09</v>
       </c>
       <c r="AR46">
         <v>0.97</v>
       </c>
       <c r="AS46">
-        <v>1.15</v>
+        <v>0.86</v>
       </c>
       <c r="AT46">
-        <v>2.12</v>
+        <v>1.83</v>
       </c>
       <c r="AU46">
         <v>6</v>
@@ -10882,25 +10882,25 @@
         <v>1.3</v>
       </c>
       <c r="AN47">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="AO47">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AP47">
-        <v>1.17</v>
+        <v>1.46</v>
       </c>
       <c r="AQ47">
-        <v>2</v>
+        <v>1.62</v>
       </c>
       <c r="AR47">
-        <v>1.67</v>
+        <v>1.77</v>
       </c>
       <c r="AS47">
-        <v>1.74</v>
+        <v>1.63</v>
       </c>
       <c r="AT47">
-        <v>3.41</v>
+        <v>3.4</v>
       </c>
       <c r="AU47">
         <v>3</v>
@@ -11091,22 +11091,22 @@
         <v>0</v>
       </c>
       <c r="AO48">
-        <v>1.17</v>
+        <v>1.33</v>
       </c>
       <c r="AP48">
-        <v>0.17</v>
+        <v>0.23</v>
       </c>
       <c r="AQ48">
-        <v>1.25</v>
+        <v>1.33</v>
       </c>
       <c r="AR48">
-        <v>1.17</v>
+        <v>1.34</v>
       </c>
       <c r="AS48">
-        <v>1.55</v>
+        <v>1.42</v>
       </c>
       <c r="AT48">
-        <v>2.72</v>
+        <v>2.76</v>
       </c>
       <c r="AU48">
         <v>6</v>
@@ -11294,25 +11294,25 @@
         <v>1.73</v>
       </c>
       <c r="AN49">
-        <v>1.5</v>
+        <v>1.67</v>
       </c>
       <c r="AO49">
-        <v>1.67</v>
+        <v>2</v>
       </c>
       <c r="AP49">
-        <v>1.13</v>
+        <v>1.36</v>
       </c>
       <c r="AQ49">
-        <v>1.67</v>
+        <v>1.25</v>
       </c>
       <c r="AR49">
-        <v>1.18</v>
+        <v>1.24</v>
       </c>
       <c r="AS49">
-        <v>1.37</v>
+        <v>1.21</v>
       </c>
       <c r="AT49">
-        <v>2.55</v>
+        <v>2.45</v>
       </c>
       <c r="AU49">
         <v>0</v>
@@ -11500,25 +11500,25 @@
         <v>1.15</v>
       </c>
       <c r="AN50">
-        <v>1.5</v>
+        <v>3</v>
       </c>
       <c r="AO50">
-        <v>2.67</v>
+        <v>3</v>
       </c>
       <c r="AP50">
-        <v>1.3</v>
+        <v>1.58</v>
       </c>
       <c r="AQ50">
         <v>2.17</v>
       </c>
       <c r="AR50">
-        <v>1.07</v>
+        <v>1.24</v>
       </c>
       <c r="AS50">
-        <v>2.06</v>
+        <v>2.07</v>
       </c>
       <c r="AT50">
-        <v>3.13</v>
+        <v>3.31</v>
       </c>
       <c r="AU50">
         <v>3</v>
@@ -11706,25 +11706,25 @@
         <v>1.82</v>
       </c>
       <c r="AN51">
-        <v>1.17</v>
+        <v>0.33</v>
       </c>
       <c r="AO51">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AP51">
-        <v>1.17</v>
+        <v>1.46</v>
       </c>
       <c r="AQ51">
-        <v>0.65</v>
+        <v>0.42</v>
       </c>
       <c r="AR51">
-        <v>1.68</v>
+        <v>1.76</v>
       </c>
       <c r="AS51">
-        <v>1.04</v>
+        <v>0.97</v>
       </c>
       <c r="AT51">
-        <v>2.72</v>
+        <v>2.73</v>
       </c>
       <c r="AU51">
         <v>7</v>
@@ -11912,25 +11912,25 @@
         <v>1.52</v>
       </c>
       <c r="AN52">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AO52">
+        <v>0.33</v>
+      </c>
+      <c r="AP52">
         <v>1.67</v>
       </c>
-      <c r="AP52">
-        <v>1.46</v>
-      </c>
       <c r="AQ52">
-        <v>2</v>
+        <v>1.62</v>
       </c>
       <c r="AR52">
-        <v>1.38</v>
+        <v>1.61</v>
       </c>
       <c r="AS52">
-        <v>1.58</v>
+        <v>1.34</v>
       </c>
       <c r="AT52">
-        <v>2.96</v>
+        <v>2.95</v>
       </c>
       <c r="AU52">
         <v>7</v>
@@ -12118,25 +12118,25 @@
         <v>7.5</v>
       </c>
       <c r="AN53">
-        <v>2.6</v>
+        <v>3</v>
       </c>
       <c r="AO53">
         <v>1</v>
       </c>
       <c r="AP53">
-        <v>2.71</v>
+        <v>3</v>
       </c>
       <c r="AQ53">
-        <v>0.63</v>
+        <v>0.46</v>
       </c>
       <c r="AR53">
-        <v>1.95</v>
+        <v>2.35</v>
       </c>
       <c r="AS53">
-        <v>1.1</v>
+        <v>0.96</v>
       </c>
       <c r="AT53">
-        <v>3.05</v>
+        <v>3.31</v>
       </c>
       <c r="AU53">
         <v>10</v>
@@ -12324,25 +12324,25 @@
         <v>1.56</v>
       </c>
       <c r="AN54">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="AO54">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="AP54">
-        <v>1.04</v>
+        <v>1.33</v>
       </c>
       <c r="AQ54">
-        <v>1.42</v>
+        <v>1.25</v>
       </c>
       <c r="AR54">
-        <v>1.32</v>
+        <v>1.4</v>
       </c>
       <c r="AS54">
-        <v>1.55</v>
+        <v>1.44</v>
       </c>
       <c r="AT54">
-        <v>2.87</v>
+        <v>2.84</v>
       </c>
       <c r="AU54">
         <v>3</v>
@@ -12530,25 +12530,25 @@
         <v>1.28</v>
       </c>
       <c r="AN55">
-        <v>1.17</v>
+        <v>1.33</v>
       </c>
       <c r="AO55">
-        <v>2.6</v>
+        <v>2.33</v>
       </c>
       <c r="AP55">
-        <v>1.21</v>
+        <v>1.42</v>
       </c>
       <c r="AQ55">
-        <v>2.17</v>
+        <v>1.92</v>
       </c>
       <c r="AR55">
-        <v>1.44</v>
+        <v>1.32</v>
       </c>
       <c r="AS55">
-        <v>1.53</v>
+        <v>1.32</v>
       </c>
       <c r="AT55">
-        <v>2.97</v>
+        <v>2.64</v>
       </c>
       <c r="AU55">
         <v>7</v>
@@ -12736,25 +12736,25 @@
         <v>2.75</v>
       </c>
       <c r="AN56">
-        <v>2.33</v>
+        <v>3</v>
       </c>
       <c r="AO56">
-        <v>1.83</v>
+        <v>1.33</v>
       </c>
       <c r="AP56">
-        <v>2.17</v>
+        <v>2.42</v>
       </c>
       <c r="AQ56">
-        <v>1.46</v>
+        <v>1.25</v>
       </c>
       <c r="AR56">
-        <v>1.52</v>
+        <v>1.85</v>
       </c>
       <c r="AS56">
-        <v>1.48</v>
+        <v>1.22</v>
       </c>
       <c r="AT56">
-        <v>3</v>
+        <v>3.07</v>
       </c>
       <c r="AU56">
         <v>7</v>
@@ -12942,25 +12942,25 @@
         <v>1.14</v>
       </c>
       <c r="AN57">
-        <v>1.5</v>
+        <v>3</v>
       </c>
       <c r="AO57">
-        <v>2.67</v>
+        <v>2</v>
       </c>
       <c r="AP57">
-        <v>1.42</v>
+        <v>1.58</v>
       </c>
       <c r="AQ57">
-        <v>2.71</v>
+        <v>2.42</v>
       </c>
       <c r="AR57">
-        <v>1.57</v>
+        <v>1.7</v>
       </c>
       <c r="AS57">
-        <v>2.01</v>
+        <v>1.36</v>
       </c>
       <c r="AT57">
-        <v>3.58</v>
+        <v>3.06</v>
       </c>
       <c r="AU57">
         <v>4</v>
@@ -13148,25 +13148,25 @@
         <v>1.57</v>
       </c>
       <c r="AN58">
-        <v>1.29</v>
+        <v>2.25</v>
       </c>
       <c r="AO58">
-        <v>1.43</v>
+        <v>1.33</v>
       </c>
       <c r="AP58">
-        <v>1.3</v>
+        <v>1.58</v>
       </c>
       <c r="AQ58">
-        <v>1.13</v>
+        <v>0.92</v>
       </c>
       <c r="AR58">
-        <v>1.14</v>
+        <v>1.32</v>
       </c>
       <c r="AS58">
-        <v>1.14</v>
+        <v>1.12</v>
       </c>
       <c r="AT58">
-        <v>2.28</v>
+        <v>2.44</v>
       </c>
       <c r="AU58">
         <v>4</v>
@@ -13354,25 +13354,25 @@
         <v>1.32</v>
       </c>
       <c r="AN59">
-        <v>0.43</v>
+        <v>0.75</v>
       </c>
       <c r="AO59">
-        <v>1.57</v>
+        <v>0.5</v>
       </c>
       <c r="AP59">
-        <v>1.04</v>
+        <v>1.33</v>
       </c>
       <c r="AQ59">
-        <v>2</v>
+        <v>1.62</v>
       </c>
       <c r="AR59">
-        <v>1.35</v>
+        <v>1.44</v>
       </c>
       <c r="AS59">
-        <v>1.62</v>
+        <v>1.47</v>
       </c>
       <c r="AT59">
-        <v>2.97</v>
+        <v>2.91</v>
       </c>
       <c r="AU59">
         <v>8</v>
@@ -13560,22 +13560,22 @@
         <v>1.49</v>
       </c>
       <c r="AN60">
-        <v>1.14</v>
+        <v>0.5</v>
       </c>
       <c r="AO60">
-        <v>1.57</v>
+        <v>1.75</v>
       </c>
       <c r="AP60">
-        <v>1.17</v>
+        <v>1.46</v>
       </c>
       <c r="AQ60">
-        <v>1.67</v>
+        <v>1.25</v>
       </c>
       <c r="AR60">
-        <v>1.73</v>
+        <v>1.83</v>
       </c>
       <c r="AS60">
-        <v>1.39</v>
+        <v>1.29</v>
       </c>
       <c r="AT60">
         <v>3.12</v>
@@ -13766,25 +13766,25 @@
         <v>2.55</v>
       </c>
       <c r="AN61">
-        <v>2.71</v>
+        <v>3</v>
       </c>
       <c r="AO61">
-        <v>2.43</v>
+        <v>2</v>
       </c>
       <c r="AP61">
-        <v>2.71</v>
+        <v>3</v>
       </c>
       <c r="AQ61">
-        <v>2.17</v>
+        <v>1.92</v>
       </c>
       <c r="AR61">
-        <v>1.98</v>
+        <v>2.33</v>
       </c>
       <c r="AS61">
-        <v>1.56</v>
+        <v>1.35</v>
       </c>
       <c r="AT61">
-        <v>3.54</v>
+        <v>3.68</v>
       </c>
       <c r="AU61">
         <v>12</v>
@@ -13972,25 +13972,25 @@
         <v>2.85</v>
       </c>
       <c r="AN62">
-        <v>1.29</v>
+        <v>2</v>
       </c>
       <c r="AO62">
-        <v>0.86</v>
+        <v>0.75</v>
       </c>
       <c r="AP62">
+        <v>1.58</v>
+      </c>
+      <c r="AQ62">
+        <v>0.46</v>
+      </c>
+      <c r="AR62">
         <v>1.42</v>
       </c>
-      <c r="AQ62">
-        <v>0.63</v>
-      </c>
-      <c r="AR62">
-        <v>1.47</v>
-      </c>
       <c r="AS62">
-        <v>1.13</v>
+        <v>1.06</v>
       </c>
       <c r="AT62">
-        <v>2.6</v>
+        <v>2.48</v>
       </c>
       <c r="AU62">
         <v>7</v>
@@ -14178,25 +14178,25 @@
         <v>1.04</v>
       </c>
       <c r="AN63">
-        <v>0.14</v>
+        <v>0.25</v>
       </c>
       <c r="AO63">
-        <v>2.71</v>
+        <v>3</v>
       </c>
       <c r="AP63">
-        <v>0.17</v>
+        <v>0.23</v>
       </c>
       <c r="AQ63">
         <v>2.17</v>
       </c>
       <c r="AR63">
-        <v>1.21</v>
+        <v>1.37</v>
       </c>
       <c r="AS63">
-        <v>1.95</v>
+        <v>1.88</v>
       </c>
       <c r="AT63">
-        <v>3.16</v>
+        <v>3.25</v>
       </c>
       <c r="AU63">
         <v>4</v>
@@ -14384,25 +14384,25 @@
         <v>2.3</v>
       </c>
       <c r="AN64">
-        <v>1.57</v>
+        <v>2.33</v>
       </c>
       <c r="AO64">
-        <v>1</v>
+        <v>0.33</v>
       </c>
       <c r="AP64">
-        <v>1.46</v>
+        <v>1.67</v>
       </c>
       <c r="AQ64">
-        <v>0.65</v>
+        <v>0.42</v>
       </c>
       <c r="AR64">
-        <v>1.48</v>
+        <v>1.75</v>
       </c>
       <c r="AS64">
-        <v>0.99</v>
+        <v>0.87</v>
       </c>
       <c r="AT64">
-        <v>2.47</v>
+        <v>2.62</v>
       </c>
       <c r="AU64">
         <v>6</v>
@@ -14590,25 +14590,25 @@
         <v>2.02</v>
       </c>
       <c r="AN65">
-        <v>1.14</v>
+        <v>1.25</v>
       </c>
       <c r="AO65">
-        <v>1.14</v>
+        <v>1.25</v>
       </c>
       <c r="AP65">
-        <v>1.21</v>
+        <v>1.42</v>
       </c>
       <c r="AQ65">
-        <v>1.25</v>
+        <v>1.33</v>
       </c>
       <c r="AR65">
-        <v>1.47</v>
+        <v>1.42</v>
       </c>
       <c r="AS65">
-        <v>1.58</v>
+        <v>1.5</v>
       </c>
       <c r="AT65">
-        <v>3.05</v>
+        <v>2.92</v>
       </c>
       <c r="AU65">
         <v>7</v>
@@ -14796,25 +14796,25 @@
         <v>4.4</v>
       </c>
       <c r="AN66">
-        <v>2.75</v>
+        <v>2.33</v>
       </c>
       <c r="AO66">
-        <v>1.75</v>
+        <v>1</v>
       </c>
       <c r="AP66">
         <v>2.17</v>
       </c>
       <c r="AQ66">
-        <v>1.46</v>
+        <v>1.25</v>
       </c>
       <c r="AR66">
-        <v>2</v>
+        <v>2.05</v>
       </c>
       <c r="AS66">
-        <v>1.47</v>
+        <v>1.28</v>
       </c>
       <c r="AT66">
-        <v>3.47</v>
+        <v>3.33</v>
       </c>
       <c r="AU66">
         <v>6</v>
@@ -15002,25 +15002,25 @@
         <v>1.27</v>
       </c>
       <c r="AN67">
-        <v>0.88</v>
+        <v>1.5</v>
       </c>
       <c r="AO67">
-        <v>1.13</v>
+        <v>1</v>
       </c>
       <c r="AP67">
-        <v>0.65</v>
+        <v>0.91</v>
       </c>
       <c r="AQ67">
-        <v>1.21</v>
+        <v>1</v>
       </c>
       <c r="AR67">
-        <v>0.99</v>
+        <v>1.08</v>
       </c>
       <c r="AS67">
-        <v>1.49</v>
+        <v>1.55</v>
       </c>
       <c r="AT67">
-        <v>2.48</v>
+        <v>2.63</v>
       </c>
       <c r="AU67">
         <v>4</v>
@@ -15208,25 +15208,25 @@
         <v>1.48</v>
       </c>
       <c r="AN68">
-        <v>0.88</v>
+        <v>1</v>
       </c>
       <c r="AO68">
-        <v>0.38</v>
+        <v>0</v>
       </c>
       <c r="AP68">
-        <v>0.63</v>
+        <v>0.82</v>
       </c>
       <c r="AQ68">
-        <v>1.04</v>
+        <v>0.75</v>
       </c>
       <c r="AR68">
-        <v>1.11</v>
+        <v>1.23</v>
       </c>
       <c r="AS68">
-        <v>1.39</v>
+        <v>1.24</v>
       </c>
       <c r="AT68">
-        <v>2.5</v>
+        <v>2.47</v>
       </c>
       <c r="AU68">
         <v>3</v>
@@ -15414,25 +15414,25 @@
         <v>1.95</v>
       </c>
       <c r="AN69">
-        <v>1.25</v>
+        <v>1.5</v>
       </c>
       <c r="AO69">
-        <v>1.38</v>
+        <v>2</v>
       </c>
       <c r="AP69">
-        <v>1.13</v>
+        <v>1.36</v>
       </c>
       <c r="AQ69">
-        <v>1.17</v>
+        <v>0.8</v>
       </c>
       <c r="AR69">
-        <v>1.07</v>
+        <v>1.16</v>
       </c>
       <c r="AS69">
-        <v>1.74</v>
+        <v>1.61</v>
       </c>
       <c r="AT69">
-        <v>2.81</v>
+        <v>2.77</v>
       </c>
       <c r="AU69">
         <v>3</v>
@@ -15620,25 +15620,25 @@
         <v>1.55</v>
       </c>
       <c r="AN70">
-        <v>1.38</v>
+        <v>1.33</v>
       </c>
       <c r="AO70">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="AP70">
-        <v>1.67</v>
+        <v>2.08</v>
       </c>
       <c r="AQ70">
-        <v>1.3</v>
+        <v>1</v>
       </c>
       <c r="AR70">
-        <v>1.47</v>
+        <v>1.53</v>
       </c>
       <c r="AS70">
-        <v>1.15</v>
+        <v>0.89</v>
       </c>
       <c r="AT70">
-        <v>2.62</v>
+        <v>2.42</v>
       </c>
       <c r="AU70">
         <v>8</v>
@@ -15826,25 +15826,25 @@
         <v>3.3</v>
       </c>
       <c r="AN71">
-        <v>1.75</v>
+        <v>3</v>
       </c>
       <c r="AO71">
-        <v>0.13</v>
+        <v>0</v>
       </c>
       <c r="AP71">
-        <v>2</v>
+        <v>2.45</v>
       </c>
       <c r="AQ71">
-        <v>0.17</v>
+        <v>0.09</v>
       </c>
       <c r="AR71">
-        <v>1.6</v>
+        <v>1.82</v>
       </c>
       <c r="AS71">
-        <v>1.18</v>
+        <v>1</v>
       </c>
       <c r="AT71">
-        <v>2.78</v>
+        <v>2.82</v>
       </c>
       <c r="AU71">
         <v>7</v>
@@ -16032,25 +16032,25 @@
         <v>2.7</v>
       </c>
       <c r="AN72">
-        <v>2.13</v>
+        <v>3</v>
       </c>
       <c r="AO72">
+        <v>0.75</v>
+      </c>
+      <c r="AP72">
+        <v>2.42</v>
+      </c>
+      <c r="AQ72">
         <v>1.25</v>
       </c>
-      <c r="AP72">
-        <v>2.17</v>
-      </c>
-      <c r="AQ72">
-        <v>1.42</v>
-      </c>
       <c r="AR72">
+        <v>1.84</v>
+      </c>
+      <c r="AS72">
         <v>1.5</v>
       </c>
-      <c r="AS72">
-        <v>1.49</v>
-      </c>
       <c r="AT72">
-        <v>2.99</v>
+        <v>3.34</v>
       </c>
       <c r="AU72">
         <v>7</v>
@@ -16238,25 +16238,25 @@
         <v>1.03</v>
       </c>
       <c r="AN73">
-        <v>1.13</v>
+        <v>1</v>
       </c>
       <c r="AO73">
-        <v>2.75</v>
+        <v>2.33</v>
       </c>
       <c r="AP73">
-        <v>1.25</v>
+        <v>1.17</v>
       </c>
       <c r="AQ73">
-        <v>2.71</v>
+        <v>2.42</v>
       </c>
       <c r="AR73">
-        <v>1.53</v>
+        <v>1.68</v>
       </c>
       <c r="AS73">
-        <v>2.08</v>
+        <v>1.51</v>
       </c>
       <c r="AT73">
-        <v>3.61</v>
+        <v>3.19</v>
       </c>
       <c r="AU73">
         <v>0</v>
@@ -16444,25 +16444,25 @@
         <v>1.51</v>
       </c>
       <c r="AN74">
-        <v>1.22</v>
+        <v>1</v>
       </c>
       <c r="AO74">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="AP74">
-        <v>1.17</v>
+        <v>1.46</v>
       </c>
       <c r="AQ74">
-        <v>1.3</v>
+        <v>1</v>
       </c>
       <c r="AR74">
-        <v>1.76</v>
+        <v>1.81</v>
       </c>
       <c r="AS74">
-        <v>1.17</v>
+        <v>1</v>
       </c>
       <c r="AT74">
-        <v>2.93</v>
+        <v>2.81</v>
       </c>
       <c r="AU74">
         <v>6</v>
@@ -16650,25 +16650,25 @@
         <v>1.98</v>
       </c>
       <c r="AN75">
-        <v>0.67</v>
+        <v>0.6</v>
       </c>
       <c r="AO75">
-        <v>0.78</v>
+        <v>0.25</v>
       </c>
       <c r="AP75">
-        <v>1.04</v>
+        <v>1.33</v>
       </c>
       <c r="AQ75">
-        <v>0.65</v>
+        <v>0.42</v>
       </c>
       <c r="AR75">
-        <v>1.43</v>
+        <v>1.49</v>
       </c>
       <c r="AS75">
-        <v>1.03</v>
+        <v>0.9</v>
       </c>
       <c r="AT75">
-        <v>2.46</v>
+        <v>2.39</v>
       </c>
       <c r="AU75">
         <v>5</v>
@@ -16856,25 +16856,25 @@
         <v>1.34</v>
       </c>
       <c r="AN76">
-        <v>0.11</v>
+        <v>0.2</v>
       </c>
       <c r="AO76">
-        <v>1.44</v>
+        <v>1</v>
       </c>
       <c r="AP76">
-        <v>0.17</v>
+        <v>0.23</v>
       </c>
       <c r="AQ76">
-        <v>1.13</v>
+        <v>0.92</v>
       </c>
       <c r="AR76">
-        <v>1.18</v>
+        <v>1.29</v>
       </c>
       <c r="AS76">
-        <v>1.06</v>
+        <v>0.99</v>
       </c>
       <c r="AT76">
-        <v>2.24</v>
+        <v>2.28</v>
       </c>
       <c r="AU76">
         <v>3</v>
@@ -17062,25 +17062,25 @@
         <v>1.85</v>
       </c>
       <c r="AN77">
-        <v>1.33</v>
+        <v>1.2</v>
       </c>
       <c r="AO77">
-        <v>1.56</v>
+        <v>1.4</v>
       </c>
       <c r="AP77">
-        <v>1.21</v>
+        <v>1.42</v>
       </c>
       <c r="AQ77">
-        <v>1.67</v>
+        <v>1.25</v>
       </c>
       <c r="AR77">
-        <v>1.59</v>
+        <v>1.45</v>
       </c>
       <c r="AS77">
-        <v>1.57</v>
+        <v>1.44</v>
       </c>
       <c r="AT77">
-        <v>3.16</v>
+        <v>2.89</v>
       </c>
       <c r="AU77">
         <v>3</v>
@@ -17268,25 +17268,25 @@
         <v>4.5</v>
       </c>
       <c r="AN78">
-        <v>2</v>
+        <v>2.5</v>
       </c>
       <c r="AO78">
-        <v>0.78</v>
+        <v>0.8</v>
       </c>
       <c r="AP78">
-        <v>2.17</v>
+        <v>2.42</v>
       </c>
       <c r="AQ78">
-        <v>0.63</v>
+        <v>0.46</v>
       </c>
       <c r="AR78">
-        <v>1.52</v>
+        <v>1.78</v>
       </c>
       <c r="AS78">
-        <v>1.07</v>
+        <v>1.03</v>
       </c>
       <c r="AT78">
-        <v>2.59</v>
+        <v>2.81</v>
       </c>
       <c r="AU78">
         <v>8</v>
@@ -17474,25 +17474,25 @@
         <v>1.48</v>
       </c>
       <c r="AN79">
-        <v>1.22</v>
+        <v>1.75</v>
       </c>
       <c r="AO79">
-        <v>1.89</v>
+        <v>1</v>
       </c>
       <c r="AP79">
-        <v>1.42</v>
+        <v>1.58</v>
       </c>
       <c r="AQ79">
-        <v>2</v>
+        <v>1.62</v>
       </c>
       <c r="AR79">
-        <v>1.37</v>
+        <v>1.49</v>
       </c>
       <c r="AS79">
-        <v>1.62</v>
+        <v>1.47</v>
       </c>
       <c r="AT79">
-        <v>2.99</v>
+        <v>2.96</v>
       </c>
       <c r="AU79">
         <v>4</v>
@@ -17680,25 +17680,25 @@
         <v>1.9</v>
       </c>
       <c r="AN80">
-        <v>1.89</v>
+        <v>2.5</v>
       </c>
       <c r="AO80">
-        <v>1</v>
+        <v>1.2</v>
       </c>
       <c r="AP80">
-        <v>1.46</v>
+        <v>1.67</v>
       </c>
       <c r="AQ80">
-        <v>1.25</v>
+        <v>1.33</v>
       </c>
       <c r="AR80">
-        <v>1.41</v>
+        <v>1.66</v>
       </c>
       <c r="AS80">
-        <v>1.43</v>
+        <v>1.44</v>
       </c>
       <c r="AT80">
-        <v>2.84</v>
+        <v>3.1</v>
       </c>
       <c r="AU80">
         <v>5</v>
@@ -17886,25 +17886,25 @@
         <v>1.89</v>
       </c>
       <c r="AN81">
-        <v>2.78</v>
+        <v>3</v>
       </c>
       <c r="AO81">
-        <v>2.44</v>
+        <v>3</v>
       </c>
       <c r="AP81">
-        <v>2.71</v>
+        <v>3</v>
       </c>
       <c r="AQ81">
         <v>2.17</v>
       </c>
       <c r="AR81">
-        <v>2.1</v>
+        <v>2.43</v>
       </c>
       <c r="AS81">
-        <v>1.99</v>
+        <v>1.97</v>
       </c>
       <c r="AT81">
-        <v>4.09</v>
+        <v>4.4</v>
       </c>
       <c r="AU81">
         <v>6</v>
@@ -18092,25 +18092,25 @@
         <v>1.66</v>
       </c>
       <c r="AN82">
-        <v>1.3</v>
+        <v>2.4</v>
       </c>
       <c r="AO82">
-        <v>1.7</v>
+        <v>1.4</v>
       </c>
       <c r="AP82">
-        <v>1.3</v>
+        <v>1.58</v>
       </c>
       <c r="AQ82">
-        <v>1.46</v>
+        <v>1.25</v>
       </c>
       <c r="AR82">
+        <v>1.31</v>
+      </c>
+      <c r="AS82">
         <v>1.21</v>
       </c>
-      <c r="AS82">
-        <v>1.41</v>
-      </c>
       <c r="AT82">
-        <v>2.62</v>
+        <v>2.52</v>
       </c>
       <c r="AU82">
         <v>5</v>
@@ -18298,25 +18298,25 @@
         <v>1.78</v>
       </c>
       <c r="AN83">
-        <v>0.8</v>
+        <v>1.2</v>
       </c>
       <c r="AO83">
-        <v>0.7</v>
+        <v>0.67</v>
       </c>
       <c r="AP83">
-        <v>0.65</v>
+        <v>0.91</v>
       </c>
       <c r="AQ83">
-        <v>0.63</v>
+        <v>0.46</v>
       </c>
       <c r="AR83">
-        <v>1.01</v>
+        <v>1.14</v>
       </c>
       <c r="AS83">
-        <v>1.08</v>
+        <v>1.06</v>
       </c>
       <c r="AT83">
-        <v>2.09</v>
+        <v>2.2</v>
       </c>
       <c r="AU83">
         <v>7</v>
@@ -18504,25 +18504,25 @@
         <v>1.4</v>
       </c>
       <c r="AN84">
-        <v>1.8</v>
+        <v>3</v>
       </c>
       <c r="AO84">
-        <v>2.1</v>
+        <v>1.6</v>
       </c>
       <c r="AP84">
-        <v>2</v>
+        <v>2.45</v>
       </c>
       <c r="AQ84">
-        <v>2.17</v>
+        <v>1.92</v>
       </c>
       <c r="AR84">
-        <v>1.66</v>
+        <v>1.81</v>
       </c>
       <c r="AS84">
-        <v>1.56</v>
+        <v>1.3</v>
       </c>
       <c r="AT84">
-        <v>3.22</v>
+        <v>3.11</v>
       </c>
       <c r="AU84">
         <v>7</v>
@@ -18710,25 +18710,25 @@
         <v>3.75</v>
       </c>
       <c r="AN85">
-        <v>2.2</v>
+        <v>1.75</v>
       </c>
       <c r="AO85">
-        <v>1.2</v>
+        <v>1.5</v>
       </c>
       <c r="AP85">
         <v>2.17</v>
       </c>
       <c r="AQ85">
-        <v>1.21</v>
+        <v>1</v>
       </c>
       <c r="AR85">
-        <v>1.91</v>
+        <v>2.02</v>
       </c>
       <c r="AS85">
-        <v>1.54</v>
+        <v>1.77</v>
       </c>
       <c r="AT85">
-        <v>3.45</v>
+        <v>3.79</v>
       </c>
       <c r="AU85">
         <v>5</v>
@@ -18916,25 +18916,25 @@
         <v>1.57</v>
       </c>
       <c r="AN86">
-        <v>1.2</v>
+        <v>0.75</v>
       </c>
       <c r="AO86">
-        <v>1.2</v>
+        <v>0.8</v>
       </c>
       <c r="AP86">
+        <v>1.17</v>
+      </c>
+      <c r="AQ86">
         <v>1.25</v>
       </c>
-      <c r="AQ86">
-        <v>1.42</v>
-      </c>
       <c r="AR86">
-        <v>1.44</v>
+        <v>1.41</v>
       </c>
       <c r="AS86">
-        <v>1.35</v>
+        <v>1.28</v>
       </c>
       <c r="AT86">
-        <v>2.79</v>
+        <v>2.69</v>
       </c>
       <c r="AU86">
         <v>8</v>
@@ -19122,25 +19122,25 @@
         <v>2.3</v>
       </c>
       <c r="AN87">
-        <v>1.2</v>
+        <v>1</v>
       </c>
       <c r="AO87">
-        <v>0.1</v>
+        <v>0</v>
       </c>
       <c r="AP87">
-        <v>1.17</v>
+        <v>1.46</v>
       </c>
       <c r="AQ87">
-        <v>0.17</v>
+        <v>0.09</v>
       </c>
       <c r="AR87">
-        <v>1.72</v>
+        <v>1.73</v>
       </c>
       <c r="AS87">
-        <v>1.21</v>
+        <v>1.04</v>
       </c>
       <c r="AT87">
-        <v>2.93</v>
+        <v>2.77</v>
       </c>
       <c r="AU87">
         <v>4</v>
@@ -19328,25 +19328,25 @@
         <v>1.85</v>
       </c>
       <c r="AN88">
-        <v>1.6</v>
+        <v>1.8</v>
       </c>
       <c r="AO88">
-        <v>0.7</v>
+        <v>0.75</v>
       </c>
       <c r="AP88">
-        <v>1.13</v>
+        <v>1.36</v>
       </c>
       <c r="AQ88">
-        <v>1.04</v>
+        <v>0.75</v>
       </c>
       <c r="AR88">
-        <v>1.1</v>
+        <v>1.12</v>
       </c>
       <c r="AS88">
-        <v>1.45</v>
+        <v>1.36</v>
       </c>
       <c r="AT88">
-        <v>2.55</v>
+        <v>2.48</v>
       </c>
       <c r="AU88">
         <v>3</v>
@@ -19534,25 +19534,25 @@
         <v>1.06</v>
       </c>
       <c r="AN89">
-        <v>1.7</v>
+        <v>1.75</v>
       </c>
       <c r="AO89">
-        <v>2.8</v>
+        <v>2.5</v>
       </c>
       <c r="AP89">
-        <v>1.67</v>
+        <v>2.08</v>
       </c>
       <c r="AQ89">
-        <v>2.71</v>
+        <v>2.42</v>
       </c>
       <c r="AR89">
-        <v>1.61</v>
+        <v>1.74</v>
       </c>
       <c r="AS89">
-        <v>2.06</v>
+        <v>1.69</v>
       </c>
       <c r="AT89">
-        <v>3.67</v>
+        <v>3.43</v>
       </c>
       <c r="AU89">
         <v>5</v>
@@ -19740,25 +19740,25 @@
         <v>1.96</v>
       </c>
       <c r="AN90">
-        <v>1.09</v>
+        <v>1</v>
       </c>
       <c r="AO90">
-        <v>1.45</v>
+        <v>1.4</v>
       </c>
       <c r="AP90">
-        <v>1.21</v>
+        <v>1.42</v>
       </c>
       <c r="AQ90">
-        <v>1.13</v>
+        <v>0.92</v>
       </c>
       <c r="AR90">
-        <v>1.48</v>
+        <v>1.39</v>
       </c>
       <c r="AS90">
-        <v>1.12</v>
+        <v>1.08</v>
       </c>
       <c r="AT90">
-        <v>2.6</v>
+        <v>2.47</v>
       </c>
       <c r="AU90">
         <v>8</v>
@@ -19946,25 +19946,25 @@
         <v>1.2</v>
       </c>
       <c r="AN91">
-        <v>0.64</v>
+        <v>0.75</v>
       </c>
       <c r="AO91">
-        <v>1.64</v>
+        <v>1</v>
       </c>
       <c r="AP91">
-        <v>0.63</v>
+        <v>0.82</v>
       </c>
       <c r="AQ91">
-        <v>2</v>
+        <v>1.62</v>
       </c>
       <c r="AR91">
-        <v>1.07</v>
+        <v>1.11</v>
       </c>
       <c r="AS91">
-        <v>1.7</v>
+        <v>1.55</v>
       </c>
       <c r="AT91">
-        <v>2.77</v>
+        <v>2.66</v>
       </c>
       <c r="AU91">
         <v>4</v>
@@ -20152,25 +20152,25 @@
         <v>1.32</v>
       </c>
       <c r="AN92">
-        <v>0.09</v>
+        <v>0.17</v>
       </c>
       <c r="AO92">
-        <v>1.27</v>
+        <v>0.2</v>
       </c>
       <c r="AP92">
-        <v>0.17</v>
+        <v>0.23</v>
       </c>
       <c r="AQ92">
-        <v>1.3</v>
+        <v>1</v>
       </c>
       <c r="AR92">
-        <v>1.18</v>
+        <v>1.33</v>
       </c>
       <c r="AS92">
-        <v>1.28</v>
+        <v>1.11</v>
       </c>
       <c r="AT92">
-        <v>2.46</v>
+        <v>2.44</v>
       </c>
       <c r="AU92">
         <v>7</v>
@@ -20358,25 +20358,25 @@
         <v>1.6</v>
       </c>
       <c r="AN93">
-        <v>1.64</v>
+        <v>2</v>
       </c>
       <c r="AO93">
-        <v>1.55</v>
+        <v>1.67</v>
       </c>
       <c r="AP93">
-        <v>1.46</v>
+        <v>1.67</v>
       </c>
       <c r="AQ93">
-        <v>1.67</v>
+        <v>1.25</v>
       </c>
       <c r="AR93">
-        <v>1.34</v>
+        <v>1.61</v>
       </c>
       <c r="AS93">
-        <v>1.59</v>
+        <v>1.53</v>
       </c>
       <c r="AT93">
-        <v>2.93</v>
+        <v>3.14</v>
       </c>
       <c r="AU93">
         <v>5</v>
@@ -20564,25 +20564,25 @@
         <v>1.55</v>
       </c>
       <c r="AN94">
-        <v>0.91</v>
+        <v>0.67</v>
       </c>
       <c r="AO94">
-        <v>1.18</v>
+        <v>1.5</v>
       </c>
       <c r="AP94">
-        <v>1.04</v>
+        <v>1.33</v>
       </c>
       <c r="AQ94">
-        <v>1.25</v>
+        <v>1.33</v>
       </c>
       <c r="AR94">
-        <v>1.4</v>
+        <v>1.52</v>
       </c>
       <c r="AS94">
-        <v>1.44</v>
+        <v>1.47</v>
       </c>
       <c r="AT94">
-        <v>2.84</v>
+        <v>2.99</v>
       </c>
       <c r="AU94">
         <v>6</v>
@@ -20770,25 +20770,25 @@
         <v>2.05</v>
       </c>
       <c r="AN95">
-        <v>1.18</v>
+        <v>1.6</v>
       </c>
       <c r="AO95">
-        <v>1.36</v>
+        <v>1.5</v>
       </c>
       <c r="AP95">
-        <v>1.42</v>
+        <v>1.58</v>
       </c>
       <c r="AQ95">
-        <v>1.17</v>
+        <v>0.8</v>
       </c>
       <c r="AR95">
-        <v>1.35</v>
+        <v>1.43</v>
       </c>
       <c r="AS95">
-        <v>1.68</v>
+        <v>1.69</v>
       </c>
       <c r="AT95">
-        <v>3.03</v>
+        <v>3.12</v>
       </c>
       <c r="AU95">
         <v>8</v>
@@ -20976,25 +20976,25 @@
         <v>7.5</v>
       </c>
       <c r="AN96">
-        <v>2.82</v>
+        <v>3</v>
       </c>
       <c r="AO96">
-        <v>1</v>
+        <v>0.4</v>
       </c>
       <c r="AP96">
-        <v>2.71</v>
+        <v>3</v>
       </c>
       <c r="AQ96">
-        <v>0.65</v>
+        <v>0.42</v>
       </c>
       <c r="AR96">
-        <v>2</v>
+        <v>2.31</v>
       </c>
       <c r="AS96">
-        <v>1.03</v>
+        <v>0.89</v>
       </c>
       <c r="AT96">
-        <v>3.03</v>
+        <v>3.2</v>
       </c>
       <c r="AU96">
         <v>7</v>
@@ -21182,25 +21182,25 @@
         <v>1.55</v>
       </c>
       <c r="AN97">
-        <v>2.18</v>
+        <v>2.6</v>
       </c>
       <c r="AO97">
-        <v>2.27</v>
+        <v>2.5</v>
       </c>
       <c r="AP97">
-        <v>2.17</v>
+        <v>2.42</v>
       </c>
       <c r="AQ97">
         <v>2.17</v>
       </c>
       <c r="AR97">
-        <v>1.52</v>
+        <v>1.81</v>
       </c>
       <c r="AS97">
-        <v>1.87</v>
+        <v>1.84</v>
       </c>
       <c r="AT97">
-        <v>3.39</v>
+        <v>3.65</v>
       </c>
       <c r="AU97">
         <v>6</v>
@@ -21388,25 +21388,25 @@
         <v>1.33</v>
       </c>
       <c r="AN98">
-        <v>0.92</v>
+        <v>1.5</v>
       </c>
       <c r="AO98">
-        <v>1.17</v>
+        <v>0.83</v>
       </c>
       <c r="AP98">
-        <v>0.65</v>
+        <v>0.91</v>
       </c>
       <c r="AQ98">
-        <v>1.42</v>
+        <v>1.25</v>
       </c>
       <c r="AR98">
-        <v>1</v>
+        <v>1.15</v>
       </c>
       <c r="AS98">
-        <v>1.4</v>
+        <v>1.28</v>
       </c>
       <c r="AT98">
-        <v>2.4</v>
+        <v>2.43</v>
       </c>
       <c r="AU98">
         <v>4</v>
@@ -21594,25 +21594,25 @@
         <v>1.86</v>
       </c>
       <c r="AN99">
-        <v>1.5</v>
+        <v>1.4</v>
       </c>
       <c r="AO99">
-        <v>0.83</v>
+        <v>1.2</v>
       </c>
       <c r="AP99">
-        <v>1.67</v>
+        <v>2.08</v>
       </c>
       <c r="AQ99">
-        <v>1.04</v>
+        <v>0.75</v>
       </c>
       <c r="AR99">
-        <v>1.54</v>
+        <v>1.65</v>
       </c>
       <c r="AS99">
-        <v>1.4</v>
+        <v>1.25</v>
       </c>
       <c r="AT99">
-        <v>2.94</v>
+        <v>2.9</v>
       </c>
       <c r="AU99">
         <v>8</v>
@@ -21800,25 +21800,25 @@
         <v>1.67</v>
       </c>
       <c r="AN100">
+        <v>1.29</v>
+      </c>
+      <c r="AO100">
         <v>1.33</v>
       </c>
-      <c r="AO100">
-        <v>1.58</v>
-      </c>
       <c r="AP100">
-        <v>1.17</v>
+        <v>1.46</v>
       </c>
       <c r="AQ100">
-        <v>1.46</v>
+        <v>1.25</v>
       </c>
       <c r="AR100">
-        <v>1.72</v>
+        <v>1.67</v>
       </c>
       <c r="AS100">
-        <v>1.35</v>
+        <v>1.11</v>
       </c>
       <c r="AT100">
-        <v>3.07</v>
+        <v>2.78</v>
       </c>
       <c r="AU100">
         <v>5</v>
@@ -22006,25 +22006,25 @@
         <v>3</v>
       </c>
       <c r="AN101">
-        <v>2.08</v>
+        <v>2</v>
       </c>
       <c r="AO101">
-        <v>1.75</v>
+        <v>1.29</v>
       </c>
       <c r="AP101">
         <v>2.17</v>
       </c>
       <c r="AQ101">
-        <v>2</v>
+        <v>1.62</v>
       </c>
       <c r="AR101">
-        <v>1.79</v>
+        <v>1.9</v>
       </c>
       <c r="AS101">
-        <v>1.73</v>
+        <v>1.63</v>
       </c>
       <c r="AT101">
-        <v>3.52</v>
+        <v>3.53</v>
       </c>
       <c r="AU101">
         <v>5</v>
@@ -22212,25 +22212,25 @@
         <v>1.24</v>
       </c>
       <c r="AN102">
-        <v>0.08</v>
+        <v>0.14</v>
       </c>
       <c r="AO102">
-        <v>1.25</v>
+        <v>1.2</v>
       </c>
       <c r="AP102">
-        <v>0.17</v>
+        <v>0.23</v>
       </c>
       <c r="AQ102">
-        <v>1.21</v>
+        <v>1</v>
       </c>
       <c r="AR102">
-        <v>1.24</v>
+        <v>1.41</v>
       </c>
       <c r="AS102">
-        <v>1.54</v>
+        <v>1.6</v>
       </c>
       <c r="AT102">
-        <v>2.78</v>
+        <v>3.01</v>
       </c>
       <c r="AU102">
         <v>5</v>
@@ -22418,25 +22418,25 @@
         <v>2.45</v>
       </c>
       <c r="AN103">
-        <v>1.33</v>
+        <v>0.8</v>
       </c>
       <c r="AO103">
-        <v>0.58</v>
+        <v>0.57</v>
       </c>
       <c r="AP103">
-        <v>1.25</v>
+        <v>1.17</v>
       </c>
       <c r="AQ103">
-        <v>0.63</v>
+        <v>0.46</v>
       </c>
       <c r="AR103">
-        <v>1.4</v>
+        <v>1.41</v>
       </c>
       <c r="AS103">
-        <v>1.08</v>
+        <v>1.04</v>
       </c>
       <c r="AT103">
-        <v>2.48</v>
+        <v>2.45</v>
       </c>
       <c r="AU103">
         <v>5</v>
@@ -22624,25 +22624,25 @@
         <v>1.2</v>
       </c>
       <c r="AN104">
-        <v>1.33</v>
+        <v>1.5</v>
       </c>
       <c r="AO104">
-        <v>2.25</v>
+        <v>1.83</v>
       </c>
       <c r="AP104">
-        <v>1.13</v>
+        <v>1.36</v>
       </c>
       <c r="AQ104">
-        <v>2.17</v>
+        <v>1.92</v>
       </c>
       <c r="AR104">
-        <v>1.09</v>
+        <v>1.15</v>
       </c>
       <c r="AS104">
-        <v>1.51</v>
+        <v>1.29</v>
       </c>
       <c r="AT104">
-        <v>2.6</v>
+        <v>2.44</v>
       </c>
       <c r="AU104">
         <v>3</v>
@@ -22830,25 +22830,25 @@
         <v>1.05</v>
       </c>
       <c r="AN105">
-        <v>1.42</v>
+        <v>2.17</v>
       </c>
       <c r="AO105">
-        <v>2.83</v>
+        <v>2.6</v>
       </c>
       <c r="AP105">
-        <v>1.3</v>
+        <v>1.58</v>
       </c>
       <c r="AQ105">
-        <v>2.71</v>
+        <v>2.42</v>
       </c>
       <c r="AR105">
-        <v>1.29</v>
+        <v>1.41</v>
       </c>
       <c r="AS105">
-        <v>1.97</v>
+        <v>1.63</v>
       </c>
       <c r="AT105">
-        <v>3.26</v>
+        <v>3.04</v>
       </c>
       <c r="AU105">
         <v>2</v>
@@ -23036,25 +23036,25 @@
         <v>3.72</v>
       </c>
       <c r="AN106">
-        <v>1.85</v>
+        <v>2.4</v>
       </c>
       <c r="AO106">
-        <v>0.85</v>
+        <v>0.33</v>
       </c>
       <c r="AP106">
-        <v>2</v>
+        <v>2.45</v>
       </c>
       <c r="AQ106">
-        <v>0.65</v>
+        <v>0.42</v>
       </c>
       <c r="AR106">
-        <v>1.72</v>
+        <v>1.87</v>
       </c>
       <c r="AS106">
-        <v>1.04</v>
+        <v>0.84</v>
       </c>
       <c r="AT106">
-        <v>2.76</v>
+        <v>2.71</v>
       </c>
       <c r="AU106">
         <v>8</v>
@@ -23242,22 +23242,22 @@
         <v>1.24</v>
       </c>
       <c r="AN107">
-        <v>0.62</v>
+        <v>0.6</v>
       </c>
       <c r="AO107">
-        <v>1.62</v>
+        <v>1.57</v>
       </c>
       <c r="AP107">
-        <v>0.63</v>
+        <v>0.82</v>
       </c>
       <c r="AQ107">
-        <v>1.67</v>
+        <v>1.25</v>
       </c>
       <c r="AR107">
-        <v>1.06</v>
+        <v>1.14</v>
       </c>
       <c r="AS107">
-        <v>1.54</v>
+        <v>1.46</v>
       </c>
       <c r="AT107">
         <v>2.6</v>
@@ -23448,25 +23448,25 @@
         <v>1.91</v>
       </c>
       <c r="AN108">
-        <v>1.23</v>
+        <v>1.29</v>
       </c>
       <c r="AO108">
-        <v>1.38</v>
+        <v>0.67</v>
       </c>
       <c r="AP108">
-        <v>1.21</v>
+        <v>1.42</v>
       </c>
       <c r="AQ108">
-        <v>1.3</v>
+        <v>1</v>
       </c>
       <c r="AR108">
-        <v>1.51</v>
+        <v>1.5</v>
       </c>
       <c r="AS108">
-        <v>1.25</v>
+        <v>1.16</v>
       </c>
       <c r="AT108">
-        <v>2.76</v>
+        <v>2.66</v>
       </c>
       <c r="AU108">
         <v>7</v>
@@ -23654,25 +23654,25 @@
         <v>2.08</v>
       </c>
       <c r="AN109">
-        <v>0.77</v>
+        <v>0.57</v>
       </c>
       <c r="AO109">
-        <v>0.15</v>
+        <v>0</v>
       </c>
       <c r="AP109">
-        <v>1.04</v>
+        <v>1.33</v>
       </c>
       <c r="AQ109">
-        <v>0.17</v>
+        <v>0.09</v>
       </c>
       <c r="AR109">
-        <v>1.4</v>
+        <v>1.51</v>
       </c>
       <c r="AS109">
-        <v>1.24</v>
+        <v>1.01</v>
       </c>
       <c r="AT109">
-        <v>2.64</v>
+        <v>2.52</v>
       </c>
       <c r="AU109">
         <v>10</v>
@@ -23860,25 +23860,25 @@
         <v>1.14</v>
       </c>
       <c r="AN110">
-        <v>1.31</v>
+        <v>1.5</v>
       </c>
       <c r="AO110">
-        <v>1.92</v>
+        <v>2.14</v>
       </c>
       <c r="AP110">
-        <v>1.42</v>
+        <v>1.58</v>
       </c>
       <c r="AQ110">
         <v>2.17</v>
       </c>
       <c r="AR110">
-        <v>1.39</v>
+        <v>1.51</v>
       </c>
       <c r="AS110">
-        <v>1.79</v>
+        <v>1.71</v>
       </c>
       <c r="AT110">
-        <v>3.18</v>
+        <v>3.22</v>
       </c>
       <c r="AU110">
         <v>4</v>
@@ -24066,25 +24066,25 @@
         <v>0</v>
       </c>
       <c r="AN111">
-        <v>2.08</v>
+        <v>2.67</v>
       </c>
       <c r="AO111">
-        <v>1.31</v>
+        <v>1.71</v>
       </c>
       <c r="AP111">
-        <v>2.17</v>
+        <v>2.42</v>
       </c>
       <c r="AQ111">
-        <v>1.25</v>
+        <v>1.33</v>
       </c>
       <c r="AR111">
-        <v>1.44</v>
+        <v>1.73</v>
       </c>
       <c r="AS111">
-        <v>1.42</v>
+        <v>1.4</v>
       </c>
       <c r="AT111">
-        <v>2.86</v>
+        <v>3.13</v>
       </c>
       <c r="AU111">
         <v>6</v>
@@ -24272,25 +24272,25 @@
         <v>4.8</v>
       </c>
       <c r="AN112">
-        <v>2.69</v>
+        <v>3</v>
       </c>
       <c r="AO112">
-        <v>1.46</v>
+        <v>1.4</v>
       </c>
       <c r="AP112">
-        <v>2.71</v>
+        <v>3</v>
       </c>
       <c r="AQ112">
-        <v>1.17</v>
+        <v>0.8</v>
       </c>
       <c r="AR112">
-        <v>1.93</v>
+        <v>2.21</v>
       </c>
       <c r="AS112">
-        <v>1.7</v>
+        <v>1.8</v>
       </c>
       <c r="AT112">
-        <v>3.63</v>
+        <v>4.01</v>
       </c>
       <c r="AU112">
         <v>16</v>
@@ -24478,25 +24478,25 @@
         <v>1.47</v>
       </c>
       <c r="AN113">
+        <v>1.67</v>
+      </c>
+      <c r="AO113">
         <v>1.5</v>
       </c>
-      <c r="AO113">
-        <v>1.93</v>
-      </c>
       <c r="AP113">
-        <v>1.67</v>
+        <v>2.08</v>
       </c>
       <c r="AQ113">
-        <v>2</v>
+        <v>1.62</v>
       </c>
       <c r="AR113">
-        <v>1.5</v>
+        <v>1.63</v>
       </c>
       <c r="AS113">
-        <v>1.74</v>
+        <v>1.63</v>
       </c>
       <c r="AT113">
-        <v>3.24</v>
+        <v>3.26</v>
       </c>
       <c r="AU113">
         <v>5</v>
@@ -24684,25 +24684,25 @@
         <v>1.63</v>
       </c>
       <c r="AN114">
-        <v>1.46</v>
+        <v>1.71</v>
       </c>
       <c r="AO114">
-        <v>1.29</v>
+        <v>1.14</v>
       </c>
       <c r="AP114">
-        <v>1.13</v>
+        <v>1.36</v>
       </c>
       <c r="AQ114">
-        <v>1.42</v>
+        <v>1.25</v>
       </c>
       <c r="AR114">
-        <v>1.08</v>
+        <v>1.11</v>
       </c>
       <c r="AS114">
-        <v>1.4</v>
+        <v>1.28</v>
       </c>
       <c r="AT114">
-        <v>2.48</v>
+        <v>2.39</v>
       </c>
       <c r="AU114">
         <v>-1</v>
@@ -24890,25 +24890,25 @@
         <v>3.5</v>
       </c>
       <c r="AN115">
-        <v>1.86</v>
+        <v>1.67</v>
       </c>
       <c r="AO115">
-        <v>0.93</v>
+        <v>1</v>
       </c>
       <c r="AP115">
         <v>2.17</v>
       </c>
       <c r="AQ115">
-        <v>1.04</v>
+        <v>0.75</v>
       </c>
       <c r="AR115">
-        <v>1.8</v>
+        <v>1.87</v>
       </c>
       <c r="AS115">
-        <v>1.44</v>
+        <v>1.26</v>
       </c>
       <c r="AT115">
-        <v>3.24</v>
+        <v>3.13</v>
       </c>
       <c r="AU115">
         <v>9</v>
@@ -25096,25 +25096,25 @@
         <v>1.25</v>
       </c>
       <c r="AN116">
-        <v>1.36</v>
+        <v>2</v>
       </c>
       <c r="AO116">
-        <v>2.14</v>
+        <v>1.57</v>
       </c>
       <c r="AP116">
-        <v>1.3</v>
+        <v>1.58</v>
       </c>
       <c r="AQ116">
-        <v>2.17</v>
+        <v>1.92</v>
       </c>
       <c r="AR116">
-        <v>1.24</v>
+        <v>1.34</v>
       </c>
       <c r="AS116">
-        <v>1.45</v>
+        <v>1.2</v>
       </c>
       <c r="AT116">
-        <v>2.69</v>
+        <v>2.54</v>
       </c>
       <c r="AU116">
         <v>3</v>
@@ -25302,25 +25302,25 @@
         <v>0</v>
       </c>
       <c r="AN117">
-        <v>1.21</v>
+        <v>0.83</v>
       </c>
       <c r="AO117">
-        <v>0.79</v>
+        <v>0.29</v>
       </c>
       <c r="AP117">
-        <v>1.25</v>
+        <v>1.17</v>
       </c>
       <c r="AQ117">
-        <v>0.65</v>
+        <v>0.42</v>
       </c>
       <c r="AR117">
-        <v>1.36</v>
+        <v>1.44</v>
       </c>
       <c r="AS117">
-        <v>1.03</v>
+        <v>0.84</v>
       </c>
       <c r="AT117">
-        <v>2.39</v>
+        <v>2.28</v>
       </c>
       <c r="AU117">
         <v>6</v>
@@ -25508,25 +25508,25 @@
         <v>0</v>
       </c>
       <c r="AN118">
-        <v>1.36</v>
+        <v>1.5</v>
       </c>
       <c r="AO118">
-        <v>0.79</v>
+        <v>0.63</v>
       </c>
       <c r="AP118">
-        <v>1.17</v>
+        <v>1.46</v>
       </c>
       <c r="AQ118">
-        <v>0.63</v>
+        <v>0.46</v>
       </c>
       <c r="AR118">
-        <v>1.63</v>
+        <v>1.64</v>
       </c>
       <c r="AS118">
-        <v>1.05</v>
+        <v>1.02</v>
       </c>
       <c r="AT118">
-        <v>2.68</v>
+        <v>2.66</v>
       </c>
       <c r="AU118">
         <v>3</v>
@@ -25714,25 +25714,25 @@
         <v>0</v>
       </c>
       <c r="AN119">
-        <v>0.14</v>
+        <v>0.25</v>
       </c>
       <c r="AO119">
-        <v>2.71</v>
+        <v>2.33</v>
       </c>
       <c r="AP119">
-        <v>0.17</v>
+        <v>0.23</v>
       </c>
       <c r="AQ119">
-        <v>2.71</v>
+        <v>2.42</v>
       </c>
       <c r="AR119">
-        <v>1.22</v>
+        <v>1.38</v>
       </c>
       <c r="AS119">
-        <v>2.04</v>
+        <v>1.61</v>
       </c>
       <c r="AT119">
-        <v>3.26</v>
+        <v>2.99</v>
       </c>
       <c r="AU119">
         <v>2</v>
@@ -25920,25 +25920,25 @@
         <v>1.63</v>
       </c>
       <c r="AN120">
-        <v>1.46</v>
+        <v>1.83</v>
       </c>
       <c r="AO120">
-        <v>1.21</v>
+        <v>1.17</v>
       </c>
       <c r="AP120">
-        <v>1.46</v>
+        <v>1.67</v>
       </c>
       <c r="AQ120">
-        <v>1.21</v>
+        <v>1</v>
       </c>
       <c r="AR120">
-        <v>1.38</v>
+        <v>1.59</v>
       </c>
       <c r="AS120">
         <v>1.52</v>
       </c>
       <c r="AT120">
-        <v>2.9</v>
+        <v>3.11</v>
       </c>
       <c r="AU120">
         <v>4</v>
@@ -26126,25 +26126,25 @@
         <v>1.63</v>
       </c>
       <c r="AN121">
-        <v>1.36</v>
+        <v>1.57</v>
       </c>
       <c r="AO121">
-        <v>1.43</v>
+        <v>1.17</v>
       </c>
       <c r="AP121">
-        <v>1.46</v>
+        <v>1.67</v>
       </c>
       <c r="AQ121">
-        <v>1.13</v>
+        <v>0.92</v>
       </c>
       <c r="AR121">
-        <v>1.39</v>
+        <v>1.57</v>
       </c>
       <c r="AS121">
-        <v>1.08</v>
+        <v>1.04</v>
       </c>
       <c r="AT121">
-        <v>2.47</v>
+        <v>2.61</v>
       </c>
       <c r="AU121">
         <v>13</v>
@@ -26332,25 +26332,25 @@
         <v>0</v>
       </c>
       <c r="AN122">
-        <v>1.33</v>
+        <v>1.14</v>
       </c>
       <c r="AO122">
-        <v>1.33</v>
+        <v>1</v>
       </c>
       <c r="AP122">
-        <v>1.25</v>
+        <v>1.17</v>
       </c>
       <c r="AQ122">
-        <v>1.13</v>
+        <v>0.92</v>
       </c>
       <c r="AR122">
-        <v>1.41</v>
+        <v>1.54</v>
       </c>
       <c r="AS122">
-        <v>1.07</v>
+        <v>1.03</v>
       </c>
       <c r="AT122">
-        <v>2.48</v>
+        <v>2.57</v>
       </c>
       <c r="AU122">
         <v>6</v>
@@ -26538,25 +26538,25 @@
         <v>1.52</v>
       </c>
       <c r="AN123">
-        <v>0.93</v>
+        <v>0.88</v>
       </c>
       <c r="AO123">
-        <v>1.47</v>
+        <v>1.14</v>
       </c>
       <c r="AP123">
-        <v>1.04</v>
+        <v>1.33</v>
       </c>
       <c r="AQ123">
-        <v>1.46</v>
+        <v>1.25</v>
       </c>
       <c r="AR123">
-        <v>1.41</v>
+        <v>1.58</v>
       </c>
       <c r="AS123">
-        <v>1.46</v>
+        <v>1.2</v>
       </c>
       <c r="AT123">
-        <v>2.87</v>
+        <v>2.78</v>
       </c>
       <c r="AU123">
         <v>2</v>
@@ -26744,25 +26744,25 @@
         <v>2.82</v>
       </c>
       <c r="AN124">
-        <v>1.8</v>
+        <v>2.5</v>
       </c>
       <c r="AO124">
-        <v>1.47</v>
+        <v>1.17</v>
       </c>
       <c r="AP124">
-        <v>2</v>
+        <v>2.45</v>
       </c>
       <c r="AQ124">
-        <v>1.17</v>
+        <v>0.8</v>
       </c>
       <c r="AR124">
-        <v>1.74</v>
+        <v>1.87</v>
       </c>
       <c r="AS124">
-        <v>1.6</v>
+        <v>1.62</v>
       </c>
       <c r="AT124">
-        <v>3.34</v>
+        <v>3.49</v>
       </c>
       <c r="AU124">
         <v>12</v>
@@ -26950,25 +26950,25 @@
         <v>1.08</v>
       </c>
       <c r="AN125">
-        <v>0.73</v>
+        <v>1.29</v>
       </c>
       <c r="AO125">
-        <v>1.8</v>
+        <v>2</v>
       </c>
       <c r="AP125">
-        <v>0.65</v>
+        <v>0.91</v>
       </c>
       <c r="AQ125">
         <v>2.17</v>
       </c>
       <c r="AR125">
-        <v>1.02</v>
+        <v>1.21</v>
       </c>
       <c r="AS125">
-        <v>1.83</v>
+        <v>1.74</v>
       </c>
       <c r="AT125">
-        <v>2.85</v>
+        <v>2.95</v>
       </c>
       <c r="AU125">
         <v>5</v>
@@ -27156,25 +27156,25 @@
         <v>4.2</v>
       </c>
       <c r="AN126">
-        <v>2.73</v>
+        <v>3</v>
       </c>
       <c r="AO126">
-        <v>1.33</v>
+        <v>1.43</v>
       </c>
       <c r="AP126">
-        <v>2.71</v>
+        <v>3</v>
       </c>
       <c r="AQ126">
-        <v>1.21</v>
+        <v>1</v>
       </c>
       <c r="AR126">
-        <v>2.03</v>
+        <v>2.37</v>
       </c>
       <c r="AS126">
-        <v>1.54</v>
+        <v>1.57</v>
       </c>
       <c r="AT126">
-        <v>3.57</v>
+        <v>3.94</v>
       </c>
       <c r="AU126">
         <v>9</v>
@@ -27362,25 +27362,25 @@
         <v>1.62</v>
       </c>
       <c r="AN127">
-        <v>1.27</v>
+        <v>1.43</v>
       </c>
       <c r="AO127">
-        <v>1.27</v>
+        <v>0.71</v>
       </c>
       <c r="AP127">
-        <v>1.42</v>
+        <v>1.58</v>
       </c>
       <c r="AQ127">
-        <v>1.3</v>
+        <v>1</v>
       </c>
       <c r="AR127">
-        <v>1.4</v>
+        <v>1.5</v>
       </c>
       <c r="AS127">
-        <v>1.24</v>
+        <v>1.15</v>
       </c>
       <c r="AT127">
-        <v>2.64</v>
+        <v>2.65</v>
       </c>
       <c r="AU127">
         <v>9</v>
@@ -27568,25 +27568,25 @@
         <v>2</v>
       </c>
       <c r="AN128">
-        <v>0.73</v>
+        <v>1</v>
       </c>
       <c r="AO128">
-        <v>0.13</v>
+        <v>0</v>
       </c>
       <c r="AP128">
-        <v>0.63</v>
+        <v>0.82</v>
       </c>
       <c r="AQ128">
-        <v>0.17</v>
+        <v>0.09</v>
       </c>
       <c r="AR128">
-        <v>1.06</v>
+        <v>1.1</v>
       </c>
       <c r="AS128">
-        <v>1.2</v>
+        <v>1</v>
       </c>
       <c r="AT128">
-        <v>2.26</v>
+        <v>2.1</v>
       </c>
       <c r="AU128">
         <v>6</v>
@@ -27774,25 +27774,25 @@
         <v>2.45</v>
       </c>
       <c r="AN129">
-        <v>2.2</v>
+        <v>2.71</v>
       </c>
       <c r="AO129">
-        <v>1.6</v>
+        <v>1.38</v>
       </c>
       <c r="AP129">
-        <v>2.17</v>
+        <v>2.42</v>
       </c>
       <c r="AQ129">
-        <v>1.67</v>
+        <v>1.25</v>
       </c>
       <c r="AR129">
-        <v>1.44</v>
+        <v>1.69</v>
       </c>
       <c r="AS129">
-        <v>1.5</v>
+        <v>1.4</v>
       </c>
       <c r="AT129">
-        <v>2.94</v>
+        <v>3.09</v>
       </c>
       <c r="AU129">
         <v>6</v>
@@ -27980,25 +27980,25 @@
         <v>4.33</v>
       </c>
       <c r="AN130">
-        <v>1.75</v>
+        <v>1.57</v>
       </c>
       <c r="AO130">
-        <v>1.38</v>
+        <v>1</v>
       </c>
       <c r="AP130">
         <v>2.17</v>
       </c>
       <c r="AQ130">
-        <v>1.17</v>
+        <v>0.8</v>
       </c>
       <c r="AR130">
-        <v>1.78</v>
+        <v>1.93</v>
       </c>
       <c r="AS130">
-        <v>1.57</v>
+        <v>1.54</v>
       </c>
       <c r="AT130">
-        <v>3.35</v>
+        <v>3.47</v>
       </c>
       <c r="AU130">
         <v>13</v>
@@ -28186,25 +28186,25 @@
         <v>1.36</v>
       </c>
       <c r="AN131">
-        <v>0.75</v>
+        <v>1</v>
       </c>
       <c r="AO131">
-        <v>1.38</v>
+        <v>1</v>
       </c>
       <c r="AP131">
-        <v>0.63</v>
+        <v>0.82</v>
       </c>
       <c r="AQ131">
-        <v>1.46</v>
+        <v>1.25</v>
       </c>
       <c r="AR131">
-        <v>1.11</v>
+        <v>1.21</v>
       </c>
       <c r="AS131">
-        <v>1.44</v>
+        <v>1.18</v>
       </c>
       <c r="AT131">
-        <v>2.55</v>
+        <v>2.39</v>
       </c>
       <c r="AU131">
         <v>6</v>
@@ -28392,25 +28392,25 @@
         <v>1.32</v>
       </c>
       <c r="AN132">
-        <v>0.75</v>
+        <v>1.25</v>
       </c>
       <c r="AO132">
-        <v>1.31</v>
+        <v>1</v>
       </c>
       <c r="AP132">
-        <v>0.65</v>
+        <v>0.91</v>
       </c>
       <c r="AQ132">
-        <v>1.13</v>
+        <v>0.92</v>
       </c>
       <c r="AR132">
-        <v>1.05</v>
+        <v>1.24</v>
       </c>
       <c r="AS132">
-        <v>1.13</v>
+        <v>1.14</v>
       </c>
       <c r="AT132">
-        <v>2.18</v>
+        <v>2.38</v>
       </c>
       <c r="AU132">
         <v>4</v>
@@ -28598,25 +28598,25 @@
         <v>2.65</v>
       </c>
       <c r="AN133">
-        <v>1.5</v>
+        <v>1.86</v>
       </c>
       <c r="AO133">
-        <v>0.19</v>
+        <v>0.14</v>
       </c>
       <c r="AP133">
-        <v>1.67</v>
+        <v>2.08</v>
       </c>
       <c r="AQ133">
-        <v>0.17</v>
+        <v>0.09</v>
       </c>
       <c r="AR133">
-        <v>1.48</v>
+        <v>1.63</v>
       </c>
       <c r="AS133">
-        <v>1.14</v>
+        <v>0.9</v>
       </c>
       <c r="AT133">
-        <v>2.62</v>
+        <v>2.53</v>
       </c>
       <c r="AU133">
         <v>10</v>
@@ -28804,25 +28804,25 @@
         <v>1.75</v>
       </c>
       <c r="AN134">
-        <v>1.31</v>
+        <v>1.13</v>
       </c>
       <c r="AO134">
-        <v>1.19</v>
+        <v>0.63</v>
       </c>
       <c r="AP134">
-        <v>1.25</v>
+        <v>1.17</v>
       </c>
       <c r="AQ134">
-        <v>1.3</v>
+        <v>1</v>
       </c>
       <c r="AR134">
-        <v>1.4</v>
+        <v>1.51</v>
       </c>
       <c r="AS134">
-        <v>1.27</v>
+        <v>1.23</v>
       </c>
       <c r="AT134">
-        <v>2.67</v>
+        <v>2.74</v>
       </c>
       <c r="AU134">
         <v>4</v>
@@ -29010,25 +29010,25 @@
         <v>1.69</v>
       </c>
       <c r="AN135">
-        <v>1.38</v>
+        <v>1.63</v>
       </c>
       <c r="AO135">
         <v>1.25</v>
       </c>
       <c r="AP135">
-        <v>1.42</v>
+        <v>1.58</v>
       </c>
       <c r="AQ135">
-        <v>1.21</v>
+        <v>1</v>
       </c>
       <c r="AR135">
-        <v>1.44</v>
+        <v>1.56</v>
       </c>
       <c r="AS135">
-        <v>1.5</v>
+        <v>1.49</v>
       </c>
       <c r="AT135">
-        <v>2.94</v>
+        <v>3.05</v>
       </c>
       <c r="AU135">
         <v>5</v>
@@ -29216,25 +29216,25 @@
         <v>1.15</v>
       </c>
       <c r="AN136">
-        <v>1.88</v>
+        <v>2.57</v>
       </c>
       <c r="AO136">
-        <v>2.75</v>
+        <v>2.43</v>
       </c>
       <c r="AP136">
-        <v>2</v>
+        <v>2.45</v>
       </c>
       <c r="AQ136">
-        <v>2.71</v>
+        <v>2.42</v>
       </c>
       <c r="AR136">
-        <v>1.81</v>
+        <v>2.02</v>
       </c>
       <c r="AS136">
-        <v>2.06</v>
+        <v>1.63</v>
       </c>
       <c r="AT136">
-        <v>3.87</v>
+        <v>3.65</v>
       </c>
       <c r="AU136">
         <v>4</v>
@@ -29422,25 +29422,25 @@
         <v>3.6</v>
       </c>
       <c r="AN137">
-        <v>2.25</v>
+        <v>2.75</v>
       </c>
       <c r="AO137">
-        <v>1.06</v>
+        <v>1</v>
       </c>
       <c r="AP137">
-        <v>2.17</v>
+        <v>2.42</v>
       </c>
       <c r="AQ137">
-        <v>1.04</v>
+        <v>0.75</v>
       </c>
       <c r="AR137">
-        <v>1.46</v>
+        <v>1.7</v>
       </c>
       <c r="AS137">
-        <v>1.41</v>
+        <v>1.22</v>
       </c>
       <c r="AT137">
-        <v>2.87</v>
+        <v>2.92</v>
       </c>
       <c r="AU137">
         <v>9</v>
@@ -29628,25 +29628,25 @@
         <v>2.2</v>
       </c>
       <c r="AN138">
-        <v>1.41</v>
+        <v>1.63</v>
       </c>
       <c r="AO138">
-        <v>0.76</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="AP138">
-        <v>1.13</v>
+        <v>1.36</v>
       </c>
       <c r="AQ138">
-        <v>0.63</v>
+        <v>0.46</v>
       </c>
       <c r="AR138">
-        <v>1.15</v>
+        <v>1.11</v>
       </c>
       <c r="AS138">
-        <v>1.14</v>
+        <v>1.03</v>
       </c>
       <c r="AT138">
-        <v>2.29</v>
+        <v>2.14</v>
       </c>
       <c r="AU138">
         <v>8</v>
@@ -29834,22 +29834,22 @@
         <v>2.7</v>
       </c>
       <c r="AN139">
-        <v>1.59</v>
+        <v>2</v>
       </c>
       <c r="AO139">
-        <v>0.71</v>
+        <v>0.25</v>
       </c>
       <c r="AP139">
-        <v>1.67</v>
+        <v>2.08</v>
       </c>
       <c r="AQ139">
-        <v>0.65</v>
+        <v>0.42</v>
       </c>
       <c r="AR139">
-        <v>1.52</v>
+        <v>1.71</v>
       </c>
       <c r="AS139">
-        <v>1.05</v>
+        <v>0.86</v>
       </c>
       <c r="AT139">
         <v>2.57</v>
@@ -30040,25 +30040,25 @@
         <v>3.75</v>
       </c>
       <c r="AN140">
-        <v>1.82</v>
+        <v>1.75</v>
       </c>
       <c r="AO140">
-        <v>1.24</v>
+        <v>1.5</v>
       </c>
       <c r="AP140">
         <v>2.17</v>
       </c>
       <c r="AQ140">
-        <v>1.25</v>
+        <v>1.33</v>
       </c>
       <c r="AR140">
-        <v>1.86</v>
+        <v>2.06</v>
       </c>
       <c r="AS140">
-        <v>1.39</v>
+        <v>1.31</v>
       </c>
       <c r="AT140">
-        <v>3.25</v>
+        <v>3.37</v>
       </c>
       <c r="AU140">
         <v>2</v>
@@ -30246,25 +30246,25 @@
         <v>1.2</v>
       </c>
       <c r="AN141">
-        <v>0.18</v>
+        <v>0.22</v>
       </c>
       <c r="AO141">
-        <v>1.47</v>
+        <v>1.13</v>
       </c>
       <c r="AP141">
-        <v>0.17</v>
+        <v>0.23</v>
       </c>
       <c r="AQ141">
-        <v>1.42</v>
+        <v>1.25</v>
       </c>
       <c r="AR141">
-        <v>1.14</v>
+        <v>1.34</v>
       </c>
       <c r="AS141">
-        <v>1.43</v>
+        <v>1.28</v>
       </c>
       <c r="AT141">
-        <v>2.57</v>
+        <v>2.62</v>
       </c>
       <c r="AU141">
         <v>5</v>
@@ -30452,25 +30452,25 @@
         <v>1.2</v>
       </c>
       <c r="AN142">
-        <v>1.29</v>
+        <v>1.67</v>
       </c>
       <c r="AO142">
-        <v>2.18</v>
+        <v>1.75</v>
       </c>
       <c r="AP142">
-        <v>1.17</v>
+        <v>1.46</v>
       </c>
       <c r="AQ142">
-        <v>2.17</v>
+        <v>1.92</v>
       </c>
       <c r="AR142">
-        <v>1.55</v>
+        <v>1.59</v>
       </c>
       <c r="AS142">
-        <v>1.51</v>
+        <v>1.23</v>
       </c>
       <c r="AT142">
-        <v>3.06</v>
+        <v>2.82</v>
       </c>
       <c r="AU142">
         <v>4</v>
@@ -30658,25 +30658,25 @@
         <v>1.9</v>
       </c>
       <c r="AN143">
-        <v>1.18</v>
+        <v>1.25</v>
       </c>
       <c r="AO143">
-        <v>1.06</v>
+        <v>1</v>
       </c>
       <c r="AP143">
-        <v>1.21</v>
+        <v>1.42</v>
       </c>
       <c r="AQ143">
-        <v>1.04</v>
+        <v>0.75</v>
       </c>
       <c r="AR143">
-        <v>1.49</v>
+        <v>1.52</v>
       </c>
       <c r="AS143">
-        <v>1.41</v>
+        <v>1.26</v>
       </c>
       <c r="AT143">
-        <v>2.9</v>
+        <v>2.78</v>
       </c>
       <c r="AU143">
         <v>6</v>
@@ -30864,25 +30864,25 @@
         <v>1.04</v>
       </c>
       <c r="AN144">
-        <v>1.35</v>
+        <v>1.75</v>
       </c>
       <c r="AO144">
-        <v>2.76</v>
+        <v>2.5</v>
       </c>
       <c r="AP144">
-        <v>1.46</v>
+        <v>1.67</v>
       </c>
       <c r="AQ144">
-        <v>2.71</v>
+        <v>2.42</v>
       </c>
       <c r="AR144">
-        <v>1.43</v>
+        <v>1.69</v>
       </c>
       <c r="AS144">
-        <v>2.05</v>
+        <v>1.67</v>
       </c>
       <c r="AT144">
-        <v>3.48</v>
+        <v>3.36</v>
       </c>
       <c r="AU144">
         <v>4</v>
@@ -31070,25 +31070,25 @@
         <v>1.4</v>
       </c>
       <c r="AN145">
-        <v>1.29</v>
+        <v>1.75</v>
       </c>
       <c r="AO145">
-        <v>1.76</v>
+        <v>1.33</v>
       </c>
       <c r="AP145">
-        <v>1.3</v>
+        <v>1.58</v>
       </c>
       <c r="AQ145">
-        <v>2</v>
+        <v>1.62</v>
       </c>
       <c r="AR145">
-        <v>1.28</v>
+        <v>1.32</v>
       </c>
       <c r="AS145">
-        <v>1.77</v>
+        <v>1.63</v>
       </c>
       <c r="AT145">
-        <v>3.05</v>
+        <v>2.95</v>
       </c>
       <c r="AU145">
         <v>9</v>
@@ -31276,25 +31276,25 @@
         <v>1.25</v>
       </c>
       <c r="AN146">
-        <v>0.67</v>
+        <v>1.11</v>
       </c>
       <c r="AO146">
+        <v>0.89</v>
+      </c>
+      <c r="AP146">
+        <v>0.91</v>
+      </c>
+      <c r="AQ146">
+        <v>1</v>
+      </c>
+      <c r="AR146">
         <v>1.22</v>
       </c>
-      <c r="AP146">
-        <v>0.65</v>
-      </c>
-      <c r="AQ146">
-        <v>1.3</v>
-      </c>
-      <c r="AR146">
-        <v>1.07</v>
-      </c>
       <c r="AS146">
-        <v>1.34</v>
+        <v>1.25</v>
       </c>
       <c r="AT146">
-        <v>2.41</v>
+        <v>2.47</v>
       </c>
       <c r="AU146">
         <v>6</v>
@@ -31482,25 +31482,25 @@
         <v>1.33</v>
       </c>
       <c r="AN147">
-        <v>0.78</v>
+        <v>1</v>
       </c>
       <c r="AO147">
-        <v>1.28</v>
+        <v>1.11</v>
       </c>
       <c r="AP147">
-        <v>0.63</v>
+        <v>0.82</v>
       </c>
       <c r="AQ147">
-        <v>1.21</v>
+        <v>1</v>
       </c>
       <c r="AR147">
-        <v>1.15</v>
+        <v>1.26</v>
       </c>
       <c r="AS147">
-        <v>1.49</v>
+        <v>1.47</v>
       </c>
       <c r="AT147">
-        <v>2.64</v>
+        <v>2.73</v>
       </c>
       <c r="AU147">
         <v>4</v>
@@ -31688,25 +31688,25 @@
         <v>1.85</v>
       </c>
       <c r="AN148">
+        <v>1</v>
+      </c>
+      <c r="AO148">
+        <v>0.88</v>
+      </c>
+      <c r="AP148">
         <v>1.17</v>
       </c>
-      <c r="AO148">
-        <v>1.22</v>
-      </c>
-      <c r="AP148">
-        <v>1.25</v>
-      </c>
       <c r="AQ148">
-        <v>1.17</v>
+        <v>0.8</v>
       </c>
       <c r="AR148">
-        <v>1.4</v>
+        <v>1.47</v>
       </c>
       <c r="AS148">
-        <v>1.54</v>
+        <v>1.5</v>
       </c>
       <c r="AT148">
-        <v>2.94</v>
+        <v>2.97</v>
       </c>
       <c r="AU148">
         <v>10</v>
@@ -31894,25 +31894,25 @@
         <v>2.55</v>
       </c>
       <c r="AN149">
-        <v>1.83</v>
+        <v>2.25</v>
       </c>
       <c r="AO149">
-        <v>1.39</v>
+        <v>1.22</v>
       </c>
       <c r="AP149">
-        <v>2</v>
+        <v>2.45</v>
       </c>
       <c r="AQ149">
-        <v>1.13</v>
+        <v>0.92</v>
       </c>
       <c r="AR149">
-        <v>1.76</v>
+        <v>1.91</v>
       </c>
       <c r="AS149">
-        <v>1.19</v>
+        <v>1.17</v>
       </c>
       <c r="AT149">
-        <v>2.95</v>
+        <v>3.08</v>
       </c>
       <c r="AU149">
         <v>7</v>
@@ -32103,22 +32103,22 @@
         <v>1.89</v>
       </c>
       <c r="AO150">
-        <v>1.67</v>
+        <v>1.22</v>
       </c>
       <c r="AP150">
         <v>2.17</v>
       </c>
       <c r="AQ150">
-        <v>1.67</v>
+        <v>1.25</v>
       </c>
       <c r="AR150">
-        <v>1.83</v>
+        <v>1.98</v>
       </c>
       <c r="AS150">
-        <v>1.52</v>
+        <v>1.38</v>
       </c>
       <c r="AT150">
-        <v>3.35</v>
+        <v>3.36</v>
       </c>
       <c r="AU150">
         <v>6</v>
@@ -32306,25 +32306,25 @@
         <v>1.8</v>
       </c>
       <c r="AN151">
-        <v>1.56</v>
+        <v>1.78</v>
       </c>
       <c r="AO151">
-        <v>1.28</v>
+        <v>1</v>
       </c>
       <c r="AP151">
-        <v>1.42</v>
+        <v>1.58</v>
       </c>
       <c r="AQ151">
-        <v>1.46</v>
+        <v>1.25</v>
       </c>
       <c r="AR151">
-        <v>1.45</v>
+        <v>1.53</v>
       </c>
       <c r="AS151">
-        <v>1.4</v>
+        <v>1.2</v>
       </c>
       <c r="AT151">
-        <v>2.85</v>
+        <v>2.73</v>
       </c>
       <c r="AU151">
         <v>8</v>
@@ -32512,25 +32512,25 @@
         <v>1.05</v>
       </c>
       <c r="AN152">
-        <v>1</v>
+        <v>1.11</v>
       </c>
       <c r="AO152">
-        <v>2.78</v>
+        <v>2.56</v>
       </c>
       <c r="AP152">
-        <v>1.04</v>
+        <v>1.33</v>
       </c>
       <c r="AQ152">
-        <v>2.71</v>
+        <v>2.42</v>
       </c>
       <c r="AR152">
-        <v>1.43</v>
+        <v>1.55</v>
       </c>
       <c r="AS152">
-        <v>2.03</v>
+        <v>1.68</v>
       </c>
       <c r="AT152">
-        <v>3.46</v>
+        <v>3.23</v>
       </c>
       <c r="AU152">
         <v>4</v>
@@ -32718,25 +32718,25 @@
         <v>7</v>
       </c>
       <c r="AN153">
-        <v>2.22</v>
+        <v>2.56</v>
       </c>
       <c r="AO153">
-        <v>0.17</v>
+        <v>0.13</v>
       </c>
       <c r="AP153">
-        <v>2.17</v>
+        <v>2.42</v>
       </c>
       <c r="AQ153">
-        <v>0.17</v>
+        <v>0.09</v>
       </c>
       <c r="AR153">
-        <v>1.53</v>
+        <v>1.75</v>
       </c>
       <c r="AS153">
-        <v>1.16</v>
+        <v>0.93</v>
       </c>
       <c r="AT153">
-        <v>2.69</v>
+        <v>2.68</v>
       </c>
       <c r="AU153">
         <v>11</v>
@@ -32924,25 +32924,25 @@
         <v>0</v>
       </c>
       <c r="AN154">
-        <v>1.21</v>
+        <v>1.5</v>
       </c>
       <c r="AO154">
-        <v>1.11</v>
+        <v>0.89</v>
       </c>
       <c r="AP154">
-        <v>1.17</v>
+        <v>1.46</v>
       </c>
       <c r="AQ154">
-        <v>1.04</v>
+        <v>0.75</v>
       </c>
       <c r="AR154">
-        <v>1.53</v>
+        <v>1.58</v>
       </c>
       <c r="AS154">
-        <v>1.39</v>
+        <v>1.31</v>
       </c>
       <c r="AT154">
-        <v>2.92</v>
+        <v>2.89</v>
       </c>
       <c r="AU154">
         <v>2</v>
@@ -33130,25 +33130,25 @@
         <v>1.45</v>
       </c>
       <c r="AN155">
-        <v>1.26</v>
+        <v>1.44</v>
       </c>
       <c r="AO155">
-        <v>1.89</v>
+        <v>1.5</v>
       </c>
       <c r="AP155">
-        <v>1.21</v>
+        <v>1.42</v>
       </c>
       <c r="AQ155">
-        <v>2</v>
+        <v>1.62</v>
       </c>
       <c r="AR155">
-        <v>1.49</v>
+        <v>1.51</v>
       </c>
       <c r="AS155">
-        <v>1.76</v>
+        <v>1.63</v>
       </c>
       <c r="AT155">
-        <v>3.25</v>
+        <v>3.14</v>
       </c>
       <c r="AU155">
         <v>2</v>
@@ -33336,25 +33336,25 @@
         <v>1.44</v>
       </c>
       <c r="AN156">
-        <v>0.16</v>
+        <v>0.2</v>
       </c>
       <c r="AO156">
-        <v>0.63</v>
+        <v>0.22</v>
       </c>
       <c r="AP156">
-        <v>0.17</v>
+        <v>0.23</v>
       </c>
       <c r="AQ156">
-        <v>0.65</v>
+        <v>0.42</v>
       </c>
       <c r="AR156">
-        <v>1.15</v>
+        <v>1.34</v>
       </c>
       <c r="AS156">
-        <v>1.11</v>
+        <v>0.93</v>
       </c>
       <c r="AT156">
-        <v>2.26</v>
+        <v>2.27</v>
       </c>
       <c r="AU156">
         <v>3</v>
@@ -33542,25 +33542,25 @@
         <v>2.26</v>
       </c>
       <c r="AN157">
-        <v>1.32</v>
+        <v>1.56</v>
       </c>
       <c r="AO157">
-        <v>0.79</v>
+        <v>0.6</v>
       </c>
       <c r="AP157">
-        <v>1.3</v>
+        <v>1.58</v>
       </c>
       <c r="AQ157">
-        <v>0.63</v>
+        <v>0.46</v>
       </c>
       <c r="AR157">
-        <v>1.35</v>
+        <v>1.43</v>
       </c>
       <c r="AS157">
-        <v>1.17</v>
+        <v>1.06</v>
       </c>
       <c r="AT157">
-        <v>2.52</v>
+        <v>2.49</v>
       </c>
       <c r="AU157">
         <v>8</v>
@@ -33748,25 +33748,25 @@
         <v>1.2</v>
       </c>
       <c r="AN158">
-        <v>1.32</v>
+        <v>1.56</v>
       </c>
       <c r="AO158">
-        <v>1.95</v>
+        <v>1.89</v>
       </c>
       <c r="AP158">
-        <v>1.13</v>
+        <v>1.36</v>
       </c>
       <c r="AQ158">
         <v>2.17</v>
       </c>
       <c r="AR158">
-        <v>1.23</v>
+        <v>1.21</v>
       </c>
       <c r="AS158">
-        <v>1.82</v>
+        <v>1.67</v>
       </c>
       <c r="AT158">
-        <v>3.05</v>
+        <v>2.88</v>
       </c>
       <c r="AU158">
         <v>0</v>
@@ -33954,25 +33954,25 @@
         <v>2</v>
       </c>
       <c r="AN159">
-        <v>1.58</v>
+        <v>2.11</v>
       </c>
       <c r="AO159">
-        <v>1.16</v>
+        <v>1.33</v>
       </c>
       <c r="AP159">
+        <v>2.08</v>
+      </c>
+      <c r="AQ159">
+        <v>1.33</v>
+      </c>
+      <c r="AR159">
         <v>1.67</v>
       </c>
-      <c r="AQ159">
-        <v>1.25</v>
-      </c>
-      <c r="AR159">
-        <v>1.5</v>
-      </c>
       <c r="AS159">
-        <v>1.47</v>
+        <v>1.35</v>
       </c>
       <c r="AT159">
-        <v>2.97</v>
+        <v>3.02</v>
       </c>
       <c r="AU159">
         <v>5</v>
@@ -34160,25 +34160,25 @@
         <v>4.33</v>
       </c>
       <c r="AN160">
-        <v>2.63</v>
+        <v>3</v>
       </c>
       <c r="AO160">
-        <v>1.47</v>
+        <v>1.33</v>
       </c>
       <c r="AP160">
-        <v>2.71</v>
+        <v>3</v>
       </c>
       <c r="AQ160">
-        <v>1.42</v>
+        <v>1.25</v>
       </c>
       <c r="AR160">
-        <v>2.05</v>
+        <v>2.39</v>
       </c>
       <c r="AS160">
-        <v>1.49</v>
+        <v>1.34</v>
       </c>
       <c r="AT160">
-        <v>3.54</v>
+        <v>3.73</v>
       </c>
       <c r="AU160">
         <v>4</v>
@@ -34366,25 +34366,25 @@
         <v>1.21</v>
       </c>
       <c r="AN161">
-        <v>1.37</v>
+        <v>1.56</v>
       </c>
       <c r="AO161">
-        <v>2.26</v>
+        <v>1.89</v>
       </c>
       <c r="AP161">
-        <v>1.46</v>
+        <v>1.67</v>
       </c>
       <c r="AQ161">
-        <v>2.17</v>
+        <v>1.92</v>
       </c>
       <c r="AR161">
-        <v>1.4</v>
+        <v>1.6</v>
       </c>
       <c r="AS161">
-        <v>1.58</v>
+        <v>1.32</v>
       </c>
       <c r="AT161">
-        <v>2.98</v>
+        <v>2.92</v>
       </c>
       <c r="AU161">
         <v>5</v>
@@ -34572,25 +34572,25 @@
         <v>1.75</v>
       </c>
       <c r="AN162">
-        <v>1.4</v>
+        <v>1.6</v>
       </c>
       <c r="AO162">
-        <v>1.1</v>
+        <v>0.9</v>
       </c>
       <c r="AP162">
-        <v>1.42</v>
+        <v>1.58</v>
       </c>
       <c r="AQ162">
-        <v>1.04</v>
+        <v>0.75</v>
       </c>
       <c r="AR162">
-        <v>1.45</v>
+        <v>1.6</v>
       </c>
       <c r="AS162">
-        <v>1.4</v>
+        <v>1.33</v>
       </c>
       <c r="AT162">
-        <v>2.85</v>
+        <v>2.93</v>
       </c>
       <c r="AU162">
         <v>6</v>
@@ -34778,25 +34778,25 @@
         <v>1.03</v>
       </c>
       <c r="AN163">
-        <v>0.75</v>
+        <v>1</v>
       </c>
       <c r="AO163">
-        <v>2.65</v>
+        <v>2.3</v>
       </c>
       <c r="AP163">
-        <v>0.63</v>
+        <v>0.82</v>
       </c>
       <c r="AQ163">
-        <v>2.71</v>
+        <v>2.42</v>
       </c>
       <c r="AR163">
-        <v>1.16</v>
+        <v>1.29</v>
       </c>
       <c r="AS163">
-        <v>2.03</v>
+        <v>1.74</v>
       </c>
       <c r="AT163">
-        <v>3.19</v>
+        <v>3.03</v>
       </c>
       <c r="AU163">
         <v>2</v>
@@ -34984,25 +34984,25 @@
         <v>2.5</v>
       </c>
       <c r="AN164">
-        <v>2.15</v>
+        <v>2.6</v>
       </c>
       <c r="AO164">
-        <v>1.2</v>
+        <v>1.1</v>
       </c>
       <c r="AP164">
-        <v>2.17</v>
+        <v>2.42</v>
       </c>
       <c r="AQ164">
-        <v>1.21</v>
+        <v>1</v>
       </c>
       <c r="AR164">
-        <v>1.59</v>
+        <v>1.81</v>
       </c>
       <c r="AS164">
-        <v>1.45</v>
+        <v>1.47</v>
       </c>
       <c r="AT164">
-        <v>3.04</v>
+        <v>3.28</v>
       </c>
       <c r="AU164">
         <v>8</v>
@@ -35190,25 +35190,25 @@
         <v>1.93</v>
       </c>
       <c r="AN165">
-        <v>1.5</v>
+        <v>1.9</v>
       </c>
       <c r="AO165">
-        <v>1.25</v>
+        <v>1.1</v>
       </c>
       <c r="AP165">
-        <v>1.67</v>
+        <v>2.08</v>
       </c>
       <c r="AQ165">
-        <v>1.13</v>
+        <v>0.92</v>
       </c>
       <c r="AR165">
-        <v>1.5</v>
+        <v>1.66</v>
       </c>
       <c r="AS165">
-        <v>1.23</v>
+        <v>1.24</v>
       </c>
       <c r="AT165">
-        <v>2.73</v>
+        <v>2.9</v>
       </c>
       <c r="AU165">
         <v>8</v>
@@ -35396,25 +35396,25 @@
         <v>2.2</v>
       </c>
       <c r="AN166">
-        <v>1.95</v>
+        <v>2.33</v>
       </c>
       <c r="AO166">
-        <v>1.45</v>
+        <v>1.2</v>
       </c>
       <c r="AP166">
-        <v>2</v>
+        <v>2.45</v>
       </c>
       <c r="AQ166">
-        <v>1.46</v>
+        <v>1.25</v>
       </c>
       <c r="AR166">
-        <v>1.79</v>
+        <v>1.9</v>
       </c>
       <c r="AS166">
-        <v>1.38</v>
+        <v>1.22</v>
       </c>
       <c r="AT166">
-        <v>3.17</v>
+        <v>3.12</v>
       </c>
       <c r="AU166">
         <v>4</v>
@@ -35602,25 +35602,25 @@
         <v>2.75</v>
       </c>
       <c r="AN167">
-        <v>1.25</v>
+        <v>1</v>
       </c>
       <c r="AO167">
-        <v>0.2</v>
+        <v>0.11</v>
       </c>
       <c r="AP167">
-        <v>1.25</v>
+        <v>1.17</v>
       </c>
       <c r="AQ167">
-        <v>0.17</v>
+        <v>0.09</v>
       </c>
       <c r="AR167">
-        <v>1.47</v>
+        <v>1.6</v>
       </c>
       <c r="AS167">
-        <v>1.14</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="AT167">
-        <v>2.61</v>
+        <v>2.54</v>
       </c>
       <c r="AU167">
         <v>5</v>
@@ -35811,22 +35811,22 @@
         <v>2</v>
       </c>
       <c r="AO168">
-        <v>1.4</v>
+        <v>1.1</v>
       </c>
       <c r="AP168">
         <v>2.17</v>
       </c>
       <c r="AQ168">
-        <v>1.3</v>
+        <v>1</v>
       </c>
       <c r="AR168">
-        <v>1.82</v>
+        <v>1.96</v>
       </c>
       <c r="AS168">
-        <v>1.38</v>
+        <v>1.29</v>
       </c>
       <c r="AT168">
-        <v>3.2</v>
+        <v>3.25</v>
       </c>
       <c r="AU168">
         <v>13</v>
@@ -36014,25 +36014,25 @@
         <v>2.03</v>
       </c>
       <c r="AN169">
-        <v>1.38</v>
+        <v>1.7</v>
       </c>
       <c r="AO169">
-        <v>0.71</v>
+        <v>0.55</v>
       </c>
       <c r="AP169">
-        <v>1.46</v>
+        <v>1.67</v>
       </c>
       <c r="AQ169">
-        <v>0.63</v>
+        <v>0.46</v>
       </c>
       <c r="AR169">
-        <v>1.36</v>
+        <v>1.54</v>
       </c>
       <c r="AS169">
-        <v>1.12</v>
+        <v>1.05</v>
       </c>
       <c r="AT169">
-        <v>2.48</v>
+        <v>2.59</v>
       </c>
       <c r="AU169">
         <v>9</v>
@@ -36220,25 +36220,25 @@
         <v>1.96</v>
       </c>
       <c r="AN170">
-        <v>1.19</v>
+        <v>1.4</v>
       </c>
       <c r="AO170">
-        <v>0.65</v>
+        <v>0.3</v>
       </c>
       <c r="AP170">
-        <v>1.13</v>
+        <v>1.36</v>
       </c>
       <c r="AQ170">
-        <v>0.65</v>
+        <v>0.42</v>
       </c>
       <c r="AR170">
-        <v>1.23</v>
+        <v>1.21</v>
       </c>
       <c r="AS170">
-        <v>1.09</v>
+        <v>0.9</v>
       </c>
       <c r="AT170">
-        <v>2.32</v>
+        <v>2.11</v>
       </c>
       <c r="AU170">
         <v>3</v>
@@ -36426,22 +36426,22 @@
         <v>1.17</v>
       </c>
       <c r="AN171">
-        <v>0.19</v>
+        <v>0.27</v>
       </c>
       <c r="AO171">
-        <v>1.57</v>
+        <v>1.1</v>
       </c>
       <c r="AP171">
-        <v>0.17</v>
+        <v>0.23</v>
       </c>
       <c r="AQ171">
-        <v>1.67</v>
+        <v>1.25</v>
       </c>
       <c r="AR171">
-        <v>1.15</v>
+        <v>1.3</v>
       </c>
       <c r="AS171">
-        <v>1.51</v>
+        <v>1.36</v>
       </c>
       <c r="AT171">
         <v>2.66</v>
@@ -36632,25 +36632,25 @@
         <v>1.13</v>
       </c>
       <c r="AN172">
-        <v>1.2</v>
+        <v>1.45</v>
       </c>
       <c r="AO172">
-        <v>2.05</v>
+        <v>2</v>
       </c>
       <c r="AP172">
-        <v>1.17</v>
+        <v>1.46</v>
       </c>
       <c r="AQ172">
         <v>2.17</v>
       </c>
       <c r="AR172">
-        <v>1.49</v>
+        <v>1.5</v>
       </c>
       <c r="AS172">
-        <v>1.87</v>
+        <v>1.67</v>
       </c>
       <c r="AT172">
-        <v>3.36</v>
+        <v>3.17</v>
       </c>
       <c r="AU172">
         <v>7</v>
@@ -36838,25 +36838,25 @@
         <v>1.78</v>
       </c>
       <c r="AN173">
+        <v>1.7</v>
+      </c>
+      <c r="AO173">
+        <v>1.5</v>
+      </c>
+      <c r="AP173">
+        <v>1.58</v>
+      </c>
+      <c r="AQ173">
         <v>1.33</v>
       </c>
-      <c r="AO173">
-        <v>1.33</v>
-      </c>
-      <c r="AP173">
-        <v>1.3</v>
-      </c>
-      <c r="AQ173">
-        <v>1.25</v>
-      </c>
       <c r="AR173">
+        <v>1.47</v>
+      </c>
+      <c r="AS173">
         <v>1.35</v>
       </c>
-      <c r="AS173">
-        <v>1.49</v>
-      </c>
       <c r="AT173">
-        <v>2.84</v>
+        <v>2.82</v>
       </c>
       <c r="AU173">
         <v>4</v>
@@ -37044,25 +37044,25 @@
         <v>1.25</v>
       </c>
       <c r="AN174">
-        <v>1.05</v>
+        <v>1.3</v>
       </c>
       <c r="AO174">
-        <v>2.19</v>
+        <v>1.7</v>
       </c>
       <c r="AP174">
-        <v>1.04</v>
+        <v>1.33</v>
       </c>
       <c r="AQ174">
-        <v>2.17</v>
+        <v>1.92</v>
       </c>
       <c r="AR174">
-        <v>1.43</v>
+        <v>1.47</v>
       </c>
       <c r="AS174">
-        <v>1.6</v>
+        <v>1.37</v>
       </c>
       <c r="AT174">
-        <v>3.03</v>
+        <v>2.84</v>
       </c>
       <c r="AU174">
         <v>4</v>
@@ -37250,25 +37250,25 @@
         <v>1.78</v>
       </c>
       <c r="AN175">
-        <v>1.14</v>
+        <v>1.3</v>
       </c>
       <c r="AO175">
-        <v>1.48</v>
+        <v>1.2</v>
       </c>
       <c r="AP175">
-        <v>1.21</v>
+        <v>1.42</v>
       </c>
       <c r="AQ175">
+        <v>1.25</v>
+      </c>
+      <c r="AR175">
         <v>1.42</v>
       </c>
-      <c r="AR175">
-        <v>1.46</v>
-      </c>
       <c r="AS175">
-        <v>1.44</v>
+        <v>1.27</v>
       </c>
       <c r="AT175">
-        <v>2.9</v>
+        <v>2.69</v>
       </c>
       <c r="AU175">
         <v>10</v>
@@ -37456,25 +37456,25 @@
         <v>3.75</v>
       </c>
       <c r="AN176">
-        <v>2.67</v>
+        <v>3</v>
       </c>
       <c r="AO176">
-        <v>2</v>
+        <v>1.64</v>
       </c>
       <c r="AP176">
-        <v>2.71</v>
+        <v>3</v>
       </c>
       <c r="AQ176">
-        <v>2</v>
+        <v>1.62</v>
       </c>
       <c r="AR176">
-        <v>2.1</v>
+        <v>2.32</v>
       </c>
       <c r="AS176">
-        <v>1.75</v>
+        <v>1.69</v>
       </c>
       <c r="AT176">
-        <v>3.85</v>
+        <v>4.01</v>
       </c>
       <c r="AU176">
         <v>9</v>
@@ -37662,25 +37662,25 @@
         <v>1.39</v>
       </c>
       <c r="AN177">
-        <v>0.67</v>
+        <v>1</v>
       </c>
       <c r="AO177">
-        <v>1.45</v>
+        <v>1.09</v>
       </c>
       <c r="AP177">
-        <v>0.65</v>
+        <v>0.91</v>
       </c>
       <c r="AQ177">
-        <v>1.46</v>
+        <v>1.25</v>
       </c>
       <c r="AR177">
-        <v>1.08</v>
+        <v>1.28</v>
       </c>
       <c r="AS177">
-        <v>1.39</v>
+        <v>1.2</v>
       </c>
       <c r="AT177">
-        <v>2.47</v>
+        <v>2.48</v>
       </c>
       <c r="AU177">
         <v>2</v>
@@ -37868,25 +37868,25 @@
         <v>2.21</v>
       </c>
       <c r="AN178">
-        <v>1.91</v>
+        <v>2.4</v>
       </c>
       <c r="AO178">
-        <v>1</v>
+        <v>0.82</v>
       </c>
       <c r="AP178">
-        <v>2</v>
+        <v>2.45</v>
       </c>
       <c r="AQ178">
-        <v>1.04</v>
+        <v>0.75</v>
       </c>
       <c r="AR178">
-        <v>1.73</v>
+        <v>1.82</v>
       </c>
       <c r="AS178">
-        <v>1.42</v>
+        <v>1.38</v>
       </c>
       <c r="AT178">
-        <v>3.15</v>
+        <v>3.2</v>
       </c>
       <c r="AU178">
         <v>4</v>
@@ -38074,25 +38074,25 @@
         <v>1.3</v>
       </c>
       <c r="AN179">
-        <v>0.68</v>
+        <v>0.9</v>
       </c>
       <c r="AO179">
-        <v>1.41</v>
+        <v>1.09</v>
       </c>
       <c r="AP179">
-        <v>0.63</v>
+        <v>0.82</v>
       </c>
       <c r="AQ179">
-        <v>1.42</v>
+        <v>1.25</v>
       </c>
       <c r="AR179">
-        <v>1.11</v>
+        <v>1.2</v>
       </c>
       <c r="AS179">
-        <v>1.45</v>
+        <v>1.3</v>
       </c>
       <c r="AT179">
-        <v>2.56</v>
+        <v>2.5</v>
       </c>
       <c r="AU179">
         <v>5</v>
@@ -38283,22 +38283,22 @@
         <v>2.09</v>
       </c>
       <c r="AO180">
-        <v>0.18</v>
+        <v>0.1</v>
       </c>
       <c r="AP180">
         <v>2.17</v>
       </c>
       <c r="AQ180">
-        <v>0.17</v>
+        <v>0.09</v>
       </c>
       <c r="AR180">
-        <v>1.87</v>
+        <v>2.04</v>
       </c>
       <c r="AS180">
-        <v>1.12</v>
+        <v>0.98</v>
       </c>
       <c r="AT180">
-        <v>2.99</v>
+        <v>3.02</v>
       </c>
       <c r="AU180">
         <v>12</v>
@@ -38486,25 +38486,25 @@
         <v>1.65</v>
       </c>
       <c r="AN181">
-        <v>1.32</v>
+        <v>1.18</v>
       </c>
       <c r="AO181">
-        <v>1.23</v>
+        <v>1</v>
       </c>
       <c r="AP181">
-        <v>1.25</v>
+        <v>1.17</v>
       </c>
       <c r="AQ181">
-        <v>1.21</v>
+        <v>1</v>
       </c>
       <c r="AR181">
-        <v>1.48</v>
+        <v>1.62</v>
       </c>
       <c r="AS181">
         <v>1.49</v>
       </c>
       <c r="AT181">
-        <v>2.97</v>
+        <v>3.11</v>
       </c>
       <c r="AU181">
         <v>4</v>
@@ -38692,25 +38692,25 @@
         <v>2.24</v>
       </c>
       <c r="AN182">
-        <v>1.64</v>
+        <v>2</v>
       </c>
       <c r="AO182">
-        <v>1.14</v>
+        <v>0.89</v>
       </c>
       <c r="AP182">
+        <v>2.08</v>
+      </c>
+      <c r="AQ182">
+        <v>0.8</v>
+      </c>
+      <c r="AR182">
         <v>1.67</v>
       </c>
-      <c r="AQ182">
-        <v>1.17</v>
-      </c>
-      <c r="AR182">
-        <v>1.51</v>
-      </c>
       <c r="AS182">
-        <v>1.51</v>
+        <v>1.48</v>
       </c>
       <c r="AT182">
-        <v>3.02</v>
+        <v>3.15</v>
       </c>
       <c r="AU182">
         <v>10</v>
@@ -38898,25 +38898,25 @@
         <v>1.28</v>
       </c>
       <c r="AN183">
-        <v>2.23</v>
+        <v>2.64</v>
       </c>
       <c r="AO183">
-        <v>2.68</v>
+        <v>2.36</v>
       </c>
       <c r="AP183">
-        <v>2.17</v>
+        <v>2.42</v>
       </c>
       <c r="AQ183">
-        <v>2.71</v>
+        <v>2.42</v>
       </c>
       <c r="AR183">
-        <v>1.61</v>
+        <v>1.82</v>
       </c>
       <c r="AS183">
-        <v>2.1</v>
+        <v>1.91</v>
       </c>
       <c r="AT183">
-        <v>3.71</v>
+        <v>3.73</v>
       </c>
       <c r="AU183">
         <v>5</v>
@@ -39104,25 +39104,25 @@
         <v>1.13</v>
       </c>
       <c r="AN184">
-        <v>0.17</v>
+        <v>0.25</v>
       </c>
       <c r="AO184">
-        <v>1.96</v>
+        <v>1.5</v>
       </c>
       <c r="AP184">
-        <v>0.17</v>
+        <v>0.23</v>
       </c>
       <c r="AQ184">
-        <v>2</v>
+        <v>1.62</v>
       </c>
       <c r="AR184">
-        <v>1.11</v>
+        <v>1.24</v>
       </c>
       <c r="AS184">
-        <v>1.71</v>
+        <v>1.65</v>
       </c>
       <c r="AT184">
-        <v>2.82</v>
+        <v>2.89</v>
       </c>
       <c r="AU184">
         <v>2</v>
@@ -39310,25 +39310,25 @@
         <v>1.5</v>
       </c>
       <c r="AN185">
-        <v>1.32</v>
+        <v>1.64</v>
       </c>
       <c r="AO185">
-        <v>1.7</v>
+        <v>1.27</v>
       </c>
       <c r="AP185">
-        <v>1.3</v>
+        <v>1.58</v>
       </c>
       <c r="AQ185">
-        <v>1.67</v>
+        <v>1.25</v>
       </c>
       <c r="AR185">
-        <v>1.35</v>
+        <v>1.46</v>
       </c>
       <c r="AS185">
-        <v>1.53</v>
+        <v>1.36</v>
       </c>
       <c r="AT185">
-        <v>2.88</v>
+        <v>2.82</v>
       </c>
       <c r="AU185">
         <v>4</v>
@@ -39516,25 +39516,25 @@
         <v>1.2</v>
       </c>
       <c r="AN186">
-        <v>1.52</v>
+        <v>1.82</v>
       </c>
       <c r="AO186">
-        <v>2.13</v>
+        <v>2.09</v>
       </c>
       <c r="AP186">
-        <v>1.46</v>
+        <v>1.67</v>
       </c>
       <c r="AQ186">
         <v>2.17</v>
       </c>
       <c r="AR186">
-        <v>1.4</v>
+        <v>1.58</v>
       </c>
       <c r="AS186">
-        <v>1.91</v>
+        <v>1.69</v>
       </c>
       <c r="AT186">
-        <v>3.31</v>
+        <v>3.27</v>
       </c>
       <c r="AU186">
         <v>3</v>
@@ -39722,25 +39722,25 @@
         <v>2.14</v>
       </c>
       <c r="AN187">
-        <v>0.96</v>
+        <v>1.18</v>
       </c>
       <c r="AO187">
-        <v>0.65</v>
+        <v>0.5</v>
       </c>
       <c r="AP187">
-        <v>1.04</v>
+        <v>1.33</v>
       </c>
       <c r="AQ187">
-        <v>0.63</v>
+        <v>0.46</v>
       </c>
       <c r="AR187">
-        <v>1.38</v>
+        <v>1.45</v>
       </c>
       <c r="AS187">
-        <v>1.12</v>
+        <v>1.03</v>
       </c>
       <c r="AT187">
-        <v>2.5</v>
+        <v>2.48</v>
       </c>
       <c r="AU187">
         <v>7</v>
@@ -39928,25 +39928,25 @@
         <v>2.55</v>
       </c>
       <c r="AN188">
-        <v>1.22</v>
+        <v>1.45</v>
       </c>
       <c r="AO188">
-        <v>0.64</v>
+        <v>0.36</v>
       </c>
       <c r="AP188">
-        <v>1.21</v>
+        <v>1.42</v>
       </c>
       <c r="AQ188">
-        <v>0.65</v>
+        <v>0.42</v>
       </c>
       <c r="AR188">
-        <v>1.47</v>
+        <v>1.49</v>
       </c>
       <c r="AS188">
-        <v>1.07</v>
+        <v>0.91</v>
       </c>
       <c r="AT188">
-        <v>2.54</v>
+        <v>2.4</v>
       </c>
       <c r="AU188">
         <v>4</v>
@@ -40134,25 +40134,25 @@
         <v>1.22</v>
       </c>
       <c r="AN189">
-        <v>1.48</v>
+        <v>1.73</v>
       </c>
       <c r="AO189">
-        <v>2.13</v>
+        <v>1.82</v>
       </c>
       <c r="AP189">
-        <v>1.42</v>
+        <v>1.58</v>
       </c>
       <c r="AQ189">
-        <v>2.17</v>
+        <v>1.92</v>
       </c>
       <c r="AR189">
-        <v>1.46</v>
+        <v>1.57</v>
       </c>
       <c r="AS189">
-        <v>1.6</v>
+        <v>1.41</v>
       </c>
       <c r="AT189">
-        <v>3.06</v>
+        <v>2.98</v>
       </c>
       <c r="AU189">
         <v>4</v>
@@ -40340,25 +40340,25 @@
         <v>1.63</v>
       </c>
       <c r="AN190">
-        <v>1.09</v>
+        <v>1.33</v>
       </c>
       <c r="AO190">
-        <v>1.18</v>
+        <v>1</v>
       </c>
       <c r="AP190">
-        <v>1.17</v>
+        <v>1.46</v>
       </c>
       <c r="AQ190">
-        <v>1.13</v>
+        <v>0.92</v>
       </c>
       <c r="AR190">
-        <v>1.48</v>
+        <v>1.53</v>
       </c>
       <c r="AS190">
-        <v>1.22</v>
+        <v>1.24</v>
       </c>
       <c r="AT190">
-        <v>2.7</v>
+        <v>2.77</v>
       </c>
       <c r="AU190">
         <v>7</v>
@@ -40546,25 +40546,25 @@
         <v>0</v>
       </c>
       <c r="AN191">
-        <v>2.7</v>
+        <v>3</v>
       </c>
       <c r="AO191">
-        <v>1.3</v>
+        <v>1.45</v>
       </c>
       <c r="AP191">
-        <v>2.71</v>
+        <v>3</v>
       </c>
       <c r="AQ191">
-        <v>1.25</v>
+        <v>1.33</v>
       </c>
       <c r="AR191">
-        <v>2.08</v>
+        <v>2.28</v>
       </c>
       <c r="AS191">
-        <v>1.48</v>
+        <v>1.34</v>
       </c>
       <c r="AT191">
-        <v>3.56</v>
+        <v>3.62</v>
       </c>
       <c r="AU191">
         <v>10</v>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Czech Republic First League_20242025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Czech Republic First League_20242025.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1208" uniqueCount="303">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1232" uniqueCount="305">
   <si>
     <t>Id_Jogo</t>
   </si>
@@ -655,6 +655,12 @@
     <t>['49', '90+9']</t>
   </si>
   <si>
+    <t>['23', '50']</t>
+  </si>
+  <si>
+    <t>['51', '57']</t>
+  </si>
+  <si>
     <t>['25']</t>
   </si>
   <si>
@@ -1284,7 +1290,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:BP191"/>
+  <dimension ref="A1:BP195"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:68">
@@ -1540,7 +1546,7 @@
         <v>86</v>
       </c>
       <c r="P2" t="s">
-        <v>213</v>
+        <v>215</v>
       </c>
       <c r="Q2">
         <v>1.53</v>
@@ -1618,7 +1624,7 @@
         <v>0</v>
       </c>
       <c r="AP2">
-        <v>2.17</v>
+        <v>2.23</v>
       </c>
       <c r="AQ2">
         <v>0.46</v>
@@ -1824,7 +1830,7 @@
         <v>0</v>
       </c>
       <c r="AP3">
-        <v>2.08</v>
+        <v>2</v>
       </c>
       <c r="AQ3">
         <v>1.25</v>
@@ -1952,7 +1958,7 @@
         <v>88</v>
       </c>
       <c r="P4" t="s">
-        <v>214</v>
+        <v>216</v>
       </c>
       <c r="Q4">
         <v>2.88</v>
@@ -2364,7 +2370,7 @@
         <v>90</v>
       </c>
       <c r="P6" t="s">
-        <v>215</v>
+        <v>217</v>
       </c>
       <c r="Q6">
         <v>5.5</v>
@@ -2442,7 +2448,7 @@
         <v>0</v>
       </c>
       <c r="AP6">
-        <v>0.91</v>
+        <v>0.92</v>
       </c>
       <c r="AQ6">
         <v>1.92</v>
@@ -2570,7 +2576,7 @@
         <v>91</v>
       </c>
       <c r="P7" t="s">
-        <v>216</v>
+        <v>218</v>
       </c>
       <c r="Q7">
         <v>3.2</v>
@@ -2854,10 +2860,10 @@
         <v>0</v>
       </c>
       <c r="AP8">
-        <v>1.36</v>
+        <v>1.5</v>
       </c>
       <c r="AQ8">
-        <v>2.42</v>
+        <v>2.23</v>
       </c>
       <c r="AR8">
         <v>0</v>
@@ -3063,7 +3069,7 @@
         <v>1.58</v>
       </c>
       <c r="AQ9">
-        <v>0.75</v>
+        <v>0.77</v>
       </c>
       <c r="AR9">
         <v>0</v>
@@ -3266,7 +3272,7 @@
         <v>0</v>
       </c>
       <c r="AP10">
-        <v>0.91</v>
+        <v>0.92</v>
       </c>
       <c r="AQ10">
         <v>1.33</v>
@@ -3394,7 +3400,7 @@
         <v>94</v>
       </c>
       <c r="P11" t="s">
-        <v>217</v>
+        <v>219</v>
       </c>
       <c r="Q11">
         <v>6.5</v>
@@ -3600,7 +3606,7 @@
         <v>88</v>
       </c>
       <c r="P12" t="s">
-        <v>218</v>
+        <v>220</v>
       </c>
       <c r="Q12">
         <v>2.85</v>
@@ -3887,7 +3893,7 @@
         <v>3</v>
       </c>
       <c r="AQ13">
-        <v>0.09</v>
+        <v>0.08</v>
       </c>
       <c r="AR13">
         <v>0</v>
@@ -4012,7 +4018,7 @@
         <v>96</v>
       </c>
       <c r="P14" t="s">
-        <v>219</v>
+        <v>221</v>
       </c>
       <c r="Q14">
         <v>2.45</v>
@@ -4836,7 +4842,7 @@
         <v>88</v>
       </c>
       <c r="P18" t="s">
-        <v>220</v>
+        <v>222</v>
       </c>
       <c r="Q18">
         <v>5.4</v>
@@ -4917,7 +4923,7 @@
         <v>1.42</v>
       </c>
       <c r="AQ18">
-        <v>2.42</v>
+        <v>2.23</v>
       </c>
       <c r="AR18">
         <v>1.26</v>
@@ -5120,7 +5126,7 @@
         <v>0</v>
       </c>
       <c r="AP19">
-        <v>2.17</v>
+        <v>2.23</v>
       </c>
       <c r="AQ19">
         <v>0.42</v>
@@ -5326,7 +5332,7 @@
         <v>0</v>
       </c>
       <c r="AP20">
-        <v>1.36</v>
+        <v>1.5</v>
       </c>
       <c r="AQ20">
         <v>1.33</v>
@@ -5532,7 +5538,7 @@
         <v>3</v>
       </c>
       <c r="AP21">
-        <v>2.08</v>
+        <v>2</v>
       </c>
       <c r="AQ21">
         <v>1.92</v>
@@ -5741,7 +5747,7 @@
         <v>1.67</v>
       </c>
       <c r="AQ22">
-        <v>0.75</v>
+        <v>0.77</v>
       </c>
       <c r="AR22">
         <v>0</v>
@@ -5866,7 +5872,7 @@
         <v>102</v>
       </c>
       <c r="P23" t="s">
-        <v>221</v>
+        <v>223</v>
       </c>
       <c r="Q23">
         <v>2.6</v>
@@ -6072,7 +6078,7 @@
         <v>103</v>
       </c>
       <c r="P24" t="s">
-        <v>222</v>
+        <v>224</v>
       </c>
       <c r="Q24">
         <v>2.75</v>
@@ -6278,7 +6284,7 @@
         <v>88</v>
       </c>
       <c r="P25" t="s">
-        <v>223</v>
+        <v>225</v>
       </c>
       <c r="Q25">
         <v>1.06</v>
@@ -6356,7 +6362,7 @@
         <v>0</v>
       </c>
       <c r="AP25">
-        <v>0.91</v>
+        <v>0.92</v>
       </c>
       <c r="AQ25">
         <v>1.25</v>
@@ -6484,7 +6490,7 @@
         <v>104</v>
       </c>
       <c r="P26" t="s">
-        <v>224</v>
+        <v>226</v>
       </c>
       <c r="Q26">
         <v>6.23</v>
@@ -7595,7 +7601,7 @@
         <v>1.58</v>
       </c>
       <c r="AQ31">
-        <v>0.09</v>
+        <v>0.08</v>
       </c>
       <c r="AR31">
         <v>1.76</v>
@@ -8132,7 +8138,7 @@
         <v>111</v>
       </c>
       <c r="P34" t="s">
-        <v>225</v>
+        <v>227</v>
       </c>
       <c r="Q34">
         <v>1.45</v>
@@ -8213,7 +8219,7 @@
         <v>3</v>
       </c>
       <c r="AQ34">
-        <v>0.75</v>
+        <v>0.77</v>
       </c>
       <c r="AR34">
         <v>2.27</v>
@@ -8338,7 +8344,7 @@
         <v>112</v>
       </c>
       <c r="P35" t="s">
-        <v>226</v>
+        <v>228</v>
       </c>
       <c r="Q35">
         <v>2.84</v>
@@ -8544,7 +8550,7 @@
         <v>113</v>
       </c>
       <c r="P36" t="s">
-        <v>227</v>
+        <v>229</v>
       </c>
       <c r="Q36">
         <v>5.63</v>
@@ -8622,7 +8628,7 @@
         <v>3</v>
       </c>
       <c r="AP36">
-        <v>2.08</v>
+        <v>2</v>
       </c>
       <c r="AQ36">
         <v>2.17</v>
@@ -8750,7 +8756,7 @@
         <v>114</v>
       </c>
       <c r="P37" t="s">
-        <v>228</v>
+        <v>230</v>
       </c>
       <c r="Q37">
         <v>2.58</v>
@@ -9162,7 +9168,7 @@
         <v>88</v>
       </c>
       <c r="P39" t="s">
-        <v>229</v>
+        <v>231</v>
       </c>
       <c r="Q39">
         <v>4.75</v>
@@ -9446,7 +9452,7 @@
         <v>0</v>
       </c>
       <c r="AP40">
-        <v>1.36</v>
+        <v>1.5</v>
       </c>
       <c r="AQ40">
         <v>1.62</v>
@@ -9574,7 +9580,7 @@
         <v>117</v>
       </c>
       <c r="P41" t="s">
-        <v>230</v>
+        <v>232</v>
       </c>
       <c r="Q41">
         <v>2.4</v>
@@ -9780,7 +9786,7 @@
         <v>107</v>
       </c>
       <c r="P42" t="s">
-        <v>231</v>
+        <v>233</v>
       </c>
       <c r="Q42">
         <v>2.61</v>
@@ -9986,7 +9992,7 @@
         <v>118</v>
       </c>
       <c r="P43" t="s">
-        <v>232</v>
+        <v>234</v>
       </c>
       <c r="Q43">
         <v>1.69</v>
@@ -10064,7 +10070,7 @@
         <v>1.5</v>
       </c>
       <c r="AP43">
-        <v>2.17</v>
+        <v>2.23</v>
       </c>
       <c r="AQ43">
         <v>0.92</v>
@@ -10682,10 +10688,10 @@
         <v>0</v>
       </c>
       <c r="AP46">
-        <v>0.91</v>
+        <v>0.92</v>
       </c>
       <c r="AQ46">
-        <v>0.09</v>
+        <v>0.08</v>
       </c>
       <c r="AR46">
         <v>0.97</v>
@@ -11300,7 +11306,7 @@
         <v>2</v>
       </c>
       <c r="AP49">
-        <v>1.36</v>
+        <v>1.5</v>
       </c>
       <c r="AQ49">
         <v>1.25</v>
@@ -11428,7 +11434,7 @@
         <v>88</v>
       </c>
       <c r="P50" t="s">
-        <v>233</v>
+        <v>235</v>
       </c>
       <c r="Q50">
         <v>5.1</v>
@@ -11840,7 +11846,7 @@
         <v>122</v>
       </c>
       <c r="P52" t="s">
-        <v>234</v>
+        <v>236</v>
       </c>
       <c r="Q52">
         <v>3</v>
@@ -12252,7 +12258,7 @@
         <v>124</v>
       </c>
       <c r="P54" t="s">
-        <v>235</v>
+        <v>237</v>
       </c>
       <c r="Q54">
         <v>3</v>
@@ -12664,7 +12670,7 @@
         <v>125</v>
       </c>
       <c r="P56" t="s">
-        <v>236</v>
+        <v>238</v>
       </c>
       <c r="Q56">
         <v>1.85</v>
@@ -12870,7 +12876,7 @@
         <v>88</v>
       </c>
       <c r="P57" t="s">
-        <v>237</v>
+        <v>239</v>
       </c>
       <c r="Q57">
         <v>5.88</v>
@@ -12951,7 +12957,7 @@
         <v>1.58</v>
       </c>
       <c r="AQ57">
-        <v>2.42</v>
+        <v>2.23</v>
       </c>
       <c r="AR57">
         <v>1.7</v>
@@ -13282,7 +13288,7 @@
         <v>127</v>
       </c>
       <c r="P59" t="s">
-        <v>238</v>
+        <v>240</v>
       </c>
       <c r="Q59">
         <v>3.86</v>
@@ -13900,7 +13906,7 @@
         <v>130</v>
       </c>
       <c r="P62" t="s">
-        <v>239</v>
+        <v>241</v>
       </c>
       <c r="Q62">
         <v>1.83</v>
@@ -14106,7 +14112,7 @@
         <v>88</v>
       </c>
       <c r="P63" t="s">
-        <v>240</v>
+        <v>242</v>
       </c>
       <c r="Q63">
         <v>8.77</v>
@@ -14518,7 +14524,7 @@
         <v>132</v>
       </c>
       <c r="P65" t="s">
-        <v>241</v>
+        <v>243</v>
       </c>
       <c r="Q65">
         <v>2.4</v>
@@ -14724,7 +14730,7 @@
         <v>133</v>
       </c>
       <c r="P66" t="s">
-        <v>242</v>
+        <v>244</v>
       </c>
       <c r="Q66">
         <v>1.55</v>
@@ -14802,7 +14808,7 @@
         <v>1</v>
       </c>
       <c r="AP66">
-        <v>2.17</v>
+        <v>2.23</v>
       </c>
       <c r="AQ66">
         <v>1.25</v>
@@ -14930,7 +14936,7 @@
         <v>134</v>
       </c>
       <c r="P67" t="s">
-        <v>243</v>
+        <v>245</v>
       </c>
       <c r="Q67">
         <v>4</v>
@@ -15008,7 +15014,7 @@
         <v>1</v>
       </c>
       <c r="AP67">
-        <v>0.91</v>
+        <v>0.92</v>
       </c>
       <c r="AQ67">
         <v>1</v>
@@ -15136,7 +15142,7 @@
         <v>88</v>
       </c>
       <c r="P68" t="s">
-        <v>244</v>
+        <v>246</v>
       </c>
       <c r="Q68">
         <v>3.1</v>
@@ -15217,7 +15223,7 @@
         <v>0.82</v>
       </c>
       <c r="AQ68">
-        <v>0.75</v>
+        <v>0.77</v>
       </c>
       <c r="AR68">
         <v>1.23</v>
@@ -15420,7 +15426,7 @@
         <v>2</v>
       </c>
       <c r="AP69">
-        <v>1.36</v>
+        <v>1.5</v>
       </c>
       <c r="AQ69">
         <v>0.8</v>
@@ -15626,7 +15632,7 @@
         <v>0</v>
       </c>
       <c r="AP70">
-        <v>2.08</v>
+        <v>2</v>
       </c>
       <c r="AQ70">
         <v>1</v>
@@ -15835,7 +15841,7 @@
         <v>2.45</v>
       </c>
       <c r="AQ71">
-        <v>0.09</v>
+        <v>0.08</v>
       </c>
       <c r="AR71">
         <v>1.82</v>
@@ -15960,7 +15966,7 @@
         <v>124</v>
       </c>
       <c r="P72" t="s">
-        <v>245</v>
+        <v>247</v>
       </c>
       <c r="Q72">
         <v>1.88</v>
@@ -16166,7 +16172,7 @@
         <v>88</v>
       </c>
       <c r="P73" t="s">
-        <v>246</v>
+        <v>248</v>
       </c>
       <c r="Q73">
         <v>7</v>
@@ -16247,7 +16253,7 @@
         <v>1.17</v>
       </c>
       <c r="AQ73">
-        <v>2.42</v>
+        <v>2.23</v>
       </c>
       <c r="AR73">
         <v>1.68</v>
@@ -16578,7 +16584,7 @@
         <v>138</v>
       </c>
       <c r="P75" t="s">
-        <v>247</v>
+        <v>249</v>
       </c>
       <c r="Q75">
         <v>2.3</v>
@@ -16784,7 +16790,7 @@
         <v>88</v>
       </c>
       <c r="P76" t="s">
-        <v>248</v>
+        <v>250</v>
       </c>
       <c r="Q76">
         <v>3.7</v>
@@ -16990,7 +16996,7 @@
         <v>88</v>
       </c>
       <c r="P77" t="s">
-        <v>249</v>
+        <v>251</v>
       </c>
       <c r="Q77">
         <v>2.47</v>
@@ -17608,7 +17614,7 @@
         <v>140</v>
       </c>
       <c r="P80" t="s">
-        <v>250</v>
+        <v>252</v>
       </c>
       <c r="Q80">
         <v>2.5</v>
@@ -17814,7 +17820,7 @@
         <v>141</v>
       </c>
       <c r="P81" t="s">
-        <v>251</v>
+        <v>253</v>
       </c>
       <c r="Q81">
         <v>2.38</v>
@@ -18020,7 +18026,7 @@
         <v>142</v>
       </c>
       <c r="P82" t="s">
-        <v>252</v>
+        <v>254</v>
       </c>
       <c r="Q82">
         <v>2.8</v>
@@ -18226,7 +18232,7 @@
         <v>143</v>
       </c>
       <c r="P83" t="s">
-        <v>253</v>
+        <v>255</v>
       </c>
       <c r="Q83">
         <v>2.6</v>
@@ -18304,7 +18310,7 @@
         <v>0.67</v>
       </c>
       <c r="AP83">
-        <v>0.91</v>
+        <v>0.92</v>
       </c>
       <c r="AQ83">
         <v>0.46</v>
@@ -18432,7 +18438,7 @@
         <v>144</v>
       </c>
       <c r="P84" t="s">
-        <v>254</v>
+        <v>256</v>
       </c>
       <c r="Q84">
         <v>3.4</v>
@@ -18716,7 +18722,7 @@
         <v>1.5</v>
       </c>
       <c r="AP85">
-        <v>2.17</v>
+        <v>2.23</v>
       </c>
       <c r="AQ85">
         <v>1</v>
@@ -18844,7 +18850,7 @@
         <v>146</v>
       </c>
       <c r="P86" t="s">
-        <v>255</v>
+        <v>257</v>
       </c>
       <c r="Q86">
         <v>2.88</v>
@@ -19131,7 +19137,7 @@
         <v>1.46</v>
       </c>
       <c r="AQ87">
-        <v>0.09</v>
+        <v>0.08</v>
       </c>
       <c r="AR87">
         <v>1.73</v>
@@ -19256,7 +19262,7 @@
         <v>88</v>
       </c>
       <c r="P88" t="s">
-        <v>256</v>
+        <v>258</v>
       </c>
       <c r="Q88">
         <v>2.6</v>
@@ -19334,10 +19340,10 @@
         <v>0.75</v>
       </c>
       <c r="AP88">
-        <v>1.36</v>
+        <v>1.5</v>
       </c>
       <c r="AQ88">
-        <v>0.75</v>
+        <v>0.77</v>
       </c>
       <c r="AR88">
         <v>1.12</v>
@@ -19462,7 +19468,7 @@
         <v>93</v>
       </c>
       <c r="P89" t="s">
-        <v>257</v>
+        <v>259</v>
       </c>
       <c r="Q89">
         <v>6.5</v>
@@ -19540,10 +19546,10 @@
         <v>2.5</v>
       </c>
       <c r="AP89">
-        <v>2.08</v>
+        <v>2</v>
       </c>
       <c r="AQ89">
-        <v>2.42</v>
+        <v>2.23</v>
       </c>
       <c r="AR89">
         <v>1.74</v>
@@ -19874,7 +19880,7 @@
         <v>149</v>
       </c>
       <c r="P91" t="s">
-        <v>258</v>
+        <v>260</v>
       </c>
       <c r="Q91">
         <v>4.7</v>
@@ -20080,7 +20086,7 @@
         <v>88</v>
       </c>
       <c r="P92" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="Q92">
         <v>3.8</v>
@@ -20492,7 +20498,7 @@
         <v>150</v>
       </c>
       <c r="P94" t="s">
-        <v>260</v>
+        <v>262</v>
       </c>
       <c r="Q94">
         <v>3</v>
@@ -21394,7 +21400,7 @@
         <v>0.83</v>
       </c>
       <c r="AP98">
-        <v>0.91</v>
+        <v>0.92</v>
       </c>
       <c r="AQ98">
         <v>1.25</v>
@@ -21600,10 +21606,10 @@
         <v>1.2</v>
       </c>
       <c r="AP99">
-        <v>2.08</v>
+        <v>2</v>
       </c>
       <c r="AQ99">
-        <v>0.75</v>
+        <v>0.77</v>
       </c>
       <c r="AR99">
         <v>1.65</v>
@@ -21934,7 +21940,7 @@
         <v>156</v>
       </c>
       <c r="P101" t="s">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="Q101">
         <v>1.83</v>
@@ -22012,7 +22018,7 @@
         <v>1.29</v>
       </c>
       <c r="AP101">
-        <v>2.17</v>
+        <v>2.23</v>
       </c>
       <c r="AQ101">
         <v>1.62</v>
@@ -22630,7 +22636,7 @@
         <v>1.83</v>
       </c>
       <c r="AP104">
-        <v>1.36</v>
+        <v>1.5</v>
       </c>
       <c r="AQ104">
         <v>1.92</v>
@@ -22839,7 +22845,7 @@
         <v>1.58</v>
       </c>
       <c r="AQ105">
-        <v>2.42</v>
+        <v>2.23</v>
       </c>
       <c r="AR105">
         <v>1.41</v>
@@ -23582,7 +23588,7 @@
         <v>161</v>
       </c>
       <c r="P109" t="s">
-        <v>262</v>
+        <v>264</v>
       </c>
       <c r="Q109">
         <v>2.24</v>
@@ -23663,7 +23669,7 @@
         <v>1.33</v>
       </c>
       <c r="AQ109">
-        <v>0.09</v>
+        <v>0.08</v>
       </c>
       <c r="AR109">
         <v>1.51</v>
@@ -23788,7 +23794,7 @@
         <v>162</v>
       </c>
       <c r="P110" t="s">
-        <v>263</v>
+        <v>265</v>
       </c>
       <c r="Q110">
         <v>4.6</v>
@@ -24200,7 +24206,7 @@
         <v>164</v>
       </c>
       <c r="P112" t="s">
-        <v>219</v>
+        <v>221</v>
       </c>
       <c r="Q112">
         <v>1.44</v>
@@ -24406,7 +24412,7 @@
         <v>165</v>
       </c>
       <c r="P113" t="s">
-        <v>264</v>
+        <v>266</v>
       </c>
       <c r="Q113">
         <v>3.25</v>
@@ -24484,7 +24490,7 @@
         <v>1.5</v>
       </c>
       <c r="AP113">
-        <v>2.08</v>
+        <v>2</v>
       </c>
       <c r="AQ113">
         <v>1.62</v>
@@ -24612,7 +24618,7 @@
         <v>151</v>
       </c>
       <c r="P114" t="s">
-        <v>265</v>
+        <v>267</v>
       </c>
       <c r="Q114">
         <v>2.88</v>
@@ -24690,7 +24696,7 @@
         <v>1.14</v>
       </c>
       <c r="AP114">
-        <v>1.36</v>
+        <v>1.5</v>
       </c>
       <c r="AQ114">
         <v>1.25</v>
@@ -24818,7 +24824,7 @@
         <v>99</v>
       </c>
       <c r="P115" t="s">
-        <v>266</v>
+        <v>268</v>
       </c>
       <c r="Q115">
         <v>1.73</v>
@@ -24896,10 +24902,10 @@
         <v>1</v>
       </c>
       <c r="AP115">
-        <v>2.17</v>
+        <v>2.23</v>
       </c>
       <c r="AQ115">
-        <v>0.75</v>
+        <v>0.77</v>
       </c>
       <c r="AR115">
         <v>1.87</v>
@@ -25024,7 +25030,7 @@
         <v>88</v>
       </c>
       <c r="P116" t="s">
-        <v>267</v>
+        <v>269</v>
       </c>
       <c r="Q116">
         <v>4.33</v>
@@ -25642,7 +25648,7 @@
         <v>88</v>
       </c>
       <c r="P119" t="s">
-        <v>268</v>
+        <v>270</v>
       </c>
       <c r="Q119">
         <v>15</v>
@@ -25723,7 +25729,7 @@
         <v>0.23</v>
       </c>
       <c r="AQ119">
-        <v>2.42</v>
+        <v>2.23</v>
       </c>
       <c r="AR119">
         <v>1.38</v>
@@ -25848,7 +25854,7 @@
         <v>168</v>
       </c>
       <c r="P120" t="s">
-        <v>269</v>
+        <v>271</v>
       </c>
       <c r="Q120">
         <v>3</v>
@@ -26260,7 +26266,7 @@
         <v>170</v>
       </c>
       <c r="P122" t="s">
-        <v>270</v>
+        <v>272</v>
       </c>
       <c r="Q122">
         <v>3.25</v>
@@ -26672,7 +26678,7 @@
         <v>172</v>
       </c>
       <c r="P124" t="s">
-        <v>218</v>
+        <v>220</v>
       </c>
       <c r="Q124">
         <v>1.83</v>
@@ -26878,7 +26884,7 @@
         <v>171</v>
       </c>
       <c r="P125" t="s">
-        <v>271</v>
+        <v>273</v>
       </c>
       <c r="Q125">
         <v>6.3</v>
@@ -26956,7 +26962,7 @@
         <v>2</v>
       </c>
       <c r="AP125">
-        <v>0.91</v>
+        <v>0.92</v>
       </c>
       <c r="AQ125">
         <v>2.17</v>
@@ -27577,7 +27583,7 @@
         <v>0.82</v>
       </c>
       <c r="AQ128">
-        <v>0.09</v>
+        <v>0.08</v>
       </c>
       <c r="AR128">
         <v>1.1</v>
@@ -27702,7 +27708,7 @@
         <v>174</v>
       </c>
       <c r="P129" t="s">
-        <v>272</v>
+        <v>274</v>
       </c>
       <c r="Q129">
         <v>2.1</v>
@@ -27908,7 +27914,7 @@
         <v>175</v>
       </c>
       <c r="P130" t="s">
-        <v>273</v>
+        <v>275</v>
       </c>
       <c r="Q130">
         <v>1.5</v>
@@ -27986,7 +27992,7 @@
         <v>1</v>
       </c>
       <c r="AP130">
-        <v>2.17</v>
+        <v>2.23</v>
       </c>
       <c r="AQ130">
         <v>0.8</v>
@@ -28114,7 +28120,7 @@
         <v>176</v>
       </c>
       <c r="P131" t="s">
-        <v>274</v>
+        <v>276</v>
       </c>
       <c r="Q131">
         <v>3.5</v>
@@ -28320,7 +28326,7 @@
         <v>177</v>
       </c>
       <c r="P132" t="s">
-        <v>275</v>
+        <v>277</v>
       </c>
       <c r="Q132">
         <v>4.04</v>
@@ -28398,7 +28404,7 @@
         <v>1</v>
       </c>
       <c r="AP132">
-        <v>0.91</v>
+        <v>0.92</v>
       </c>
       <c r="AQ132">
         <v>0.92</v>
@@ -28604,10 +28610,10 @@
         <v>0.14</v>
       </c>
       <c r="AP133">
-        <v>2.08</v>
+        <v>2</v>
       </c>
       <c r="AQ133">
-        <v>0.09</v>
+        <v>0.08</v>
       </c>
       <c r="AR133">
         <v>1.63</v>
@@ -28732,7 +28738,7 @@
         <v>88</v>
       </c>
       <c r="P134" t="s">
-        <v>276</v>
+        <v>278</v>
       </c>
       <c r="Q134">
         <v>2.75</v>
@@ -29225,7 +29231,7 @@
         <v>2.45</v>
       </c>
       <c r="AQ136">
-        <v>2.42</v>
+        <v>2.23</v>
       </c>
       <c r="AR136">
         <v>2.02</v>
@@ -29431,7 +29437,7 @@
         <v>2.42</v>
       </c>
       <c r="AQ137">
-        <v>0.75</v>
+        <v>0.77</v>
       </c>
       <c r="AR137">
         <v>1.7</v>
@@ -29556,7 +29562,7 @@
         <v>91</v>
       </c>
       <c r="P138" t="s">
-        <v>264</v>
+        <v>266</v>
       </c>
       <c r="Q138">
         <v>2.25</v>
@@ -29634,7 +29640,7 @@
         <v>0.5600000000000001</v>
       </c>
       <c r="AP138">
-        <v>1.36</v>
+        <v>1.5</v>
       </c>
       <c r="AQ138">
         <v>0.46</v>
@@ -29762,7 +29768,7 @@
         <v>179</v>
       </c>
       <c r="P139" t="s">
-        <v>273</v>
+        <v>275</v>
       </c>
       <c r="Q139">
         <v>1.9</v>
@@ -29840,7 +29846,7 @@
         <v>0.25</v>
       </c>
       <c r="AP139">
-        <v>2.08</v>
+        <v>2</v>
       </c>
       <c r="AQ139">
         <v>0.42</v>
@@ -30046,7 +30052,7 @@
         <v>1.5</v>
       </c>
       <c r="AP140">
-        <v>2.17</v>
+        <v>2.23</v>
       </c>
       <c r="AQ140">
         <v>1.33</v>
@@ -30174,7 +30180,7 @@
         <v>88</v>
       </c>
       <c r="P141" t="s">
-        <v>277</v>
+        <v>279</v>
       </c>
       <c r="Q141">
         <v>4</v>
@@ -30380,7 +30386,7 @@
         <v>117</v>
       </c>
       <c r="P142" t="s">
-        <v>278</v>
+        <v>280</v>
       </c>
       <c r="Q142">
         <v>4</v>
@@ -30667,7 +30673,7 @@
         <v>1.42</v>
       </c>
       <c r="AQ143">
-        <v>0.75</v>
+        <v>0.77</v>
       </c>
       <c r="AR143">
         <v>1.52</v>
@@ -30792,7 +30798,7 @@
         <v>182</v>
       </c>
       <c r="P144" t="s">
-        <v>279</v>
+        <v>281</v>
       </c>
       <c r="Q144">
         <v>6</v>
@@ -30873,7 +30879,7 @@
         <v>1.67</v>
       </c>
       <c r="AQ144">
-        <v>2.42</v>
+        <v>2.23</v>
       </c>
       <c r="AR144">
         <v>1.69</v>
@@ -30998,7 +31004,7 @@
         <v>88</v>
       </c>
       <c r="P145" t="s">
-        <v>280</v>
+        <v>282</v>
       </c>
       <c r="Q145">
         <v>3.5</v>
@@ -31204,7 +31210,7 @@
         <v>183</v>
       </c>
       <c r="P146" t="s">
-        <v>281</v>
+        <v>283</v>
       </c>
       <c r="Q146">
         <v>4.33</v>
@@ -31282,7 +31288,7 @@
         <v>0.89</v>
       </c>
       <c r="AP146">
-        <v>0.91</v>
+        <v>0.92</v>
       </c>
       <c r="AQ146">
         <v>1</v>
@@ -31410,7 +31416,7 @@
         <v>184</v>
       </c>
       <c r="P147" t="s">
-        <v>282</v>
+        <v>284</v>
       </c>
       <c r="Q147">
         <v>3.8</v>
@@ -31616,7 +31622,7 @@
         <v>185</v>
       </c>
       <c r="P148" t="s">
-        <v>283</v>
+        <v>285</v>
       </c>
       <c r="Q148">
         <v>2.5</v>
@@ -31822,7 +31828,7 @@
         <v>186</v>
       </c>
       <c r="P149" t="s">
-        <v>280</v>
+        <v>282</v>
       </c>
       <c r="Q149">
         <v>2.05</v>
@@ -32028,7 +32034,7 @@
         <v>187</v>
       </c>
       <c r="P150" t="s">
-        <v>284</v>
+        <v>286</v>
       </c>
       <c r="Q150">
         <v>1.95</v>
@@ -32106,7 +32112,7 @@
         <v>1.22</v>
       </c>
       <c r="AP150">
-        <v>2.17</v>
+        <v>2.23</v>
       </c>
       <c r="AQ150">
         <v>1.25</v>
@@ -32234,7 +32240,7 @@
         <v>188</v>
       </c>
       <c r="P151" t="s">
-        <v>285</v>
+        <v>287</v>
       </c>
       <c r="Q151">
         <v>2.48</v>
@@ -32521,7 +32527,7 @@
         <v>1.33</v>
       </c>
       <c r="AQ152">
-        <v>2.42</v>
+        <v>2.23</v>
       </c>
       <c r="AR152">
         <v>1.55</v>
@@ -32646,7 +32652,7 @@
         <v>190</v>
       </c>
       <c r="P153" t="s">
-        <v>286</v>
+        <v>288</v>
       </c>
       <c r="Q153">
         <v>1.4</v>
@@ -32727,7 +32733,7 @@
         <v>2.42</v>
       </c>
       <c r="AQ153">
-        <v>0.09</v>
+        <v>0.08</v>
       </c>
       <c r="AR153">
         <v>1.75</v>
@@ -32933,7 +32939,7 @@
         <v>1.46</v>
       </c>
       <c r="AQ154">
-        <v>0.75</v>
+        <v>0.77</v>
       </c>
       <c r="AR154">
         <v>1.58</v>
@@ -33058,7 +33064,7 @@
         <v>88</v>
       </c>
       <c r="P155" t="s">
-        <v>222</v>
+        <v>224</v>
       </c>
       <c r="Q155">
         <v>3.2</v>
@@ -33676,7 +33682,7 @@
         <v>88</v>
       </c>
       <c r="P158" t="s">
-        <v>287</v>
+        <v>289</v>
       </c>
       <c r="Q158">
         <v>5</v>
@@ -33754,7 +33760,7 @@
         <v>1.89</v>
       </c>
       <c r="AP158">
-        <v>1.36</v>
+        <v>1.5</v>
       </c>
       <c r="AQ158">
         <v>2.17</v>
@@ -33882,7 +33888,7 @@
         <v>88</v>
       </c>
       <c r="P159" t="s">
-        <v>244</v>
+        <v>246</v>
       </c>
       <c r="Q159">
         <v>2.38</v>
@@ -33960,7 +33966,7 @@
         <v>1.33</v>
       </c>
       <c r="AP159">
-        <v>2.08</v>
+        <v>2</v>
       </c>
       <c r="AQ159">
         <v>1.33</v>
@@ -34294,7 +34300,7 @@
         <v>193</v>
       </c>
       <c r="P161" t="s">
-        <v>271</v>
+        <v>273</v>
       </c>
       <c r="Q161">
         <v>4.75</v>
@@ -34500,7 +34506,7 @@
         <v>194</v>
       </c>
       <c r="P162" t="s">
-        <v>288</v>
+        <v>290</v>
       </c>
       <c r="Q162">
         <v>2.63</v>
@@ -34581,7 +34587,7 @@
         <v>1.58</v>
       </c>
       <c r="AQ162">
-        <v>0.75</v>
+        <v>0.77</v>
       </c>
       <c r="AR162">
         <v>1.6</v>
@@ -34706,7 +34712,7 @@
         <v>88</v>
       </c>
       <c r="P163" t="s">
-        <v>289</v>
+        <v>291</v>
       </c>
       <c r="Q163">
         <v>11</v>
@@ -34787,7 +34793,7 @@
         <v>0.82</v>
       </c>
       <c r="AQ163">
-        <v>2.42</v>
+        <v>2.23</v>
       </c>
       <c r="AR163">
         <v>1.29</v>
@@ -34912,7 +34918,7 @@
         <v>195</v>
       </c>
       <c r="P164" t="s">
-        <v>290</v>
+        <v>292</v>
       </c>
       <c r="Q164">
         <v>2</v>
@@ -35118,7 +35124,7 @@
         <v>196</v>
       </c>
       <c r="P165" t="s">
-        <v>291</v>
+        <v>293</v>
       </c>
       <c r="Q165">
         <v>2.5</v>
@@ -35196,7 +35202,7 @@
         <v>1.1</v>
       </c>
       <c r="AP165">
-        <v>2.08</v>
+        <v>2</v>
       </c>
       <c r="AQ165">
         <v>0.92</v>
@@ -35611,7 +35617,7 @@
         <v>1.17</v>
       </c>
       <c r="AQ167">
-        <v>0.09</v>
+        <v>0.08</v>
       </c>
       <c r="AR167">
         <v>1.6</v>
@@ -35814,7 +35820,7 @@
         <v>1.1</v>
       </c>
       <c r="AP168">
-        <v>2.17</v>
+        <v>2.23</v>
       </c>
       <c r="AQ168">
         <v>1</v>
@@ -36226,7 +36232,7 @@
         <v>0.3</v>
       </c>
       <c r="AP170">
-        <v>1.36</v>
+        <v>1.5</v>
       </c>
       <c r="AQ170">
         <v>0.42</v>
@@ -36354,7 +36360,7 @@
         <v>201</v>
       </c>
       <c r="P171" t="s">
-        <v>292</v>
+        <v>294</v>
       </c>
       <c r="Q171">
         <v>5.2</v>
@@ -36560,7 +36566,7 @@
         <v>202</v>
       </c>
       <c r="P172" t="s">
-        <v>293</v>
+        <v>295</v>
       </c>
       <c r="Q172">
         <v>6.35</v>
@@ -36766,7 +36772,7 @@
         <v>203</v>
       </c>
       <c r="P173" t="s">
-        <v>294</v>
+        <v>296</v>
       </c>
       <c r="Q173">
         <v>2.6</v>
@@ -36972,7 +36978,7 @@
         <v>88</v>
       </c>
       <c r="P174" t="s">
-        <v>295</v>
+        <v>297</v>
       </c>
       <c r="Q174">
         <v>4.86</v>
@@ -37178,7 +37184,7 @@
         <v>204</v>
       </c>
       <c r="P175" t="s">
-        <v>280</v>
+        <v>282</v>
       </c>
       <c r="Q175">
         <v>2.66</v>
@@ -37590,7 +37596,7 @@
         <v>171</v>
       </c>
       <c r="P177" t="s">
-        <v>296</v>
+        <v>298</v>
       </c>
       <c r="Q177">
         <v>3.63</v>
@@ -37668,7 +37674,7 @@
         <v>1.09</v>
       </c>
       <c r="AP177">
-        <v>0.91</v>
+        <v>0.92</v>
       </c>
       <c r="AQ177">
         <v>1.25</v>
@@ -37877,7 +37883,7 @@
         <v>2.45</v>
       </c>
       <c r="AQ178">
-        <v>0.75</v>
+        <v>0.77</v>
       </c>
       <c r="AR178">
         <v>1.82</v>
@@ -38002,7 +38008,7 @@
         <v>88</v>
       </c>
       <c r="P179" t="s">
-        <v>297</v>
+        <v>299</v>
       </c>
       <c r="Q179">
         <v>3.92</v>
@@ -38208,7 +38214,7 @@
         <v>206</v>
       </c>
       <c r="P180" t="s">
-        <v>298</v>
+        <v>300</v>
       </c>
       <c r="Q180">
         <v>1.32</v>
@@ -38286,10 +38292,10 @@
         <v>0.1</v>
       </c>
       <c r="AP180">
-        <v>2.17</v>
+        <v>2.23</v>
       </c>
       <c r="AQ180">
-        <v>0.09</v>
+        <v>0.08</v>
       </c>
       <c r="AR180">
         <v>2.04</v>
@@ -38698,7 +38704,7 @@
         <v>0.89</v>
       </c>
       <c r="AP182">
-        <v>2.08</v>
+        <v>2</v>
       </c>
       <c r="AQ182">
         <v>0.8</v>
@@ -38826,7 +38832,7 @@
         <v>208</v>
       </c>
       <c r="P183" t="s">
-        <v>299</v>
+        <v>301</v>
       </c>
       <c r="Q183">
         <v>4.3</v>
@@ -38907,7 +38913,7 @@
         <v>2.42</v>
       </c>
       <c r="AQ183">
-        <v>2.42</v>
+        <v>2.23</v>
       </c>
       <c r="AR183">
         <v>1.82</v>
@@ -39032,7 +39038,7 @@
         <v>88</v>
       </c>
       <c r="P184" t="s">
-        <v>300</v>
+        <v>302</v>
       </c>
       <c r="Q184">
         <v>5.8</v>
@@ -39444,7 +39450,7 @@
         <v>96</v>
       </c>
       <c r="P186" t="s">
-        <v>301</v>
+        <v>303</v>
       </c>
       <c r="Q186">
         <v>4.7</v>
@@ -40062,7 +40068,7 @@
         <v>88</v>
       </c>
       <c r="P189" t="s">
-        <v>302</v>
+        <v>304</v>
       </c>
       <c r="Q189">
         <v>4.5</v>
@@ -40631,6 +40637,830 @@
       </c>
       <c r="BP191">
         <v>0</v>
+      </c>
+    </row>
+    <row r="192" spans="1:68">
+      <c r="A192" s="1">
+        <v>191</v>
+      </c>
+      <c r="B192">
+        <v>7468281</v>
+      </c>
+      <c r="C192" t="s">
+        <v>68</v>
+      </c>
+      <c r="D192" t="s">
+        <v>69</v>
+      </c>
+      <c r="E192" s="2">
+        <v>45724.39583333334</v>
+      </c>
+      <c r="F192">
+        <v>25</v>
+      </c>
+      <c r="G192" t="s">
+        <v>74</v>
+      </c>
+      <c r="H192" t="s">
+        <v>78</v>
+      </c>
+      <c r="I192">
+        <v>1</v>
+      </c>
+      <c r="J192">
+        <v>0</v>
+      </c>
+      <c r="K192">
+        <v>1</v>
+      </c>
+      <c r="L192">
+        <v>1</v>
+      </c>
+      <c r="M192">
+        <v>1</v>
+      </c>
+      <c r="N192">
+        <v>2</v>
+      </c>
+      <c r="O192" t="s">
+        <v>182</v>
+      </c>
+      <c r="P192" t="s">
+        <v>92</v>
+      </c>
+      <c r="Q192">
+        <v>3.46</v>
+      </c>
+      <c r="R192">
+        <v>2.02</v>
+      </c>
+      <c r="S192">
+        <v>3.12</v>
+      </c>
+      <c r="T192">
+        <v>1.44</v>
+      </c>
+      <c r="U192">
+        <v>2.59</v>
+      </c>
+      <c r="V192">
+        <v>3.1</v>
+      </c>
+      <c r="W192">
+        <v>1.32</v>
+      </c>
+      <c r="X192">
+        <v>7.5</v>
+      </c>
+      <c r="Y192">
+        <v>1.03</v>
+      </c>
+      <c r="Z192">
+        <v>2.77</v>
+      </c>
+      <c r="AA192">
+        <v>3.24</v>
+      </c>
+      <c r="AB192">
+        <v>2.5</v>
+      </c>
+      <c r="AC192">
+        <v>1.03</v>
+      </c>
+      <c r="AD192">
+        <v>7.5</v>
+      </c>
+      <c r="AE192">
+        <v>1.33</v>
+      </c>
+      <c r="AF192">
+        <v>2.82</v>
+      </c>
+      <c r="AG192">
+        <v>2.14</v>
+      </c>
+      <c r="AH192">
+        <v>1.68</v>
+      </c>
+      <c r="AI192">
+        <v>1.85</v>
+      </c>
+      <c r="AJ192">
+        <v>1.85</v>
+      </c>
+      <c r="AK192">
+        <v>1.5</v>
+      </c>
+      <c r="AL192">
+        <v>1.32</v>
+      </c>
+      <c r="AM192">
+        <v>1.42</v>
+      </c>
+      <c r="AN192">
+        <v>0.91</v>
+      </c>
+      <c r="AO192">
+        <v>0.75</v>
+      </c>
+      <c r="AP192">
+        <v>0.92</v>
+      </c>
+      <c r="AQ192">
+        <v>0.77</v>
+      </c>
+      <c r="AR192">
+        <v>1.24</v>
+      </c>
+      <c r="AS192">
+        <v>1.31</v>
+      </c>
+      <c r="AT192">
+        <v>2.55</v>
+      </c>
+      <c r="AU192">
+        <v>3</v>
+      </c>
+      <c r="AV192">
+        <v>4</v>
+      </c>
+      <c r="AW192">
+        <v>2</v>
+      </c>
+      <c r="AX192">
+        <v>12</v>
+      </c>
+      <c r="AY192">
+        <v>5</v>
+      </c>
+      <c r="AZ192">
+        <v>16</v>
+      </c>
+      <c r="BA192">
+        <v>7</v>
+      </c>
+      <c r="BB192">
+        <v>6</v>
+      </c>
+      <c r="BC192">
+        <v>13</v>
+      </c>
+      <c r="BD192">
+        <v>2.05</v>
+      </c>
+      <c r="BE192">
+        <v>6.5</v>
+      </c>
+      <c r="BF192">
+        <v>1.94</v>
+      </c>
+      <c r="BG192">
+        <v>1.25</v>
+      </c>
+      <c r="BH192">
+        <v>3.45</v>
+      </c>
+      <c r="BI192">
+        <v>1.45</v>
+      </c>
+      <c r="BJ192">
+        <v>2.55</v>
+      </c>
+      <c r="BK192">
+        <v>1.74</v>
+      </c>
+      <c r="BL192">
+        <v>1.98</v>
+      </c>
+      <c r="BM192">
+        <v>2.15</v>
+      </c>
+      <c r="BN192">
+        <v>1.63</v>
+      </c>
+      <c r="BO192">
+        <v>2.65</v>
+      </c>
+      <c r="BP192">
+        <v>1.4</v>
+      </c>
+    </row>
+    <row r="193" spans="1:68">
+      <c r="A193" s="1">
+        <v>192</v>
+      </c>
+      <c r="B193">
+        <v>7468278</v>
+      </c>
+      <c r="C193" t="s">
+        <v>68</v>
+      </c>
+      <c r="D193" t="s">
+        <v>69</v>
+      </c>
+      <c r="E193" s="2">
+        <v>45724.5</v>
+      </c>
+      <c r="F193">
+        <v>25</v>
+      </c>
+      <c r="G193" t="s">
+        <v>71</v>
+      </c>
+      <c r="H193" t="s">
+        <v>81</v>
+      </c>
+      <c r="I193">
+        <v>0</v>
+      </c>
+      <c r="J193">
+        <v>0</v>
+      </c>
+      <c r="K193">
+        <v>0</v>
+      </c>
+      <c r="L193">
+        <v>0</v>
+      </c>
+      <c r="M193">
+        <v>0</v>
+      </c>
+      <c r="N193">
+        <v>0</v>
+      </c>
+      <c r="O193" t="s">
+        <v>88</v>
+      </c>
+      <c r="P193" t="s">
+        <v>88</v>
+      </c>
+      <c r="Q193">
+        <v>2.32</v>
+      </c>
+      <c r="R193">
+        <v>2.19</v>
+      </c>
+      <c r="S193">
+        <v>4.6</v>
+      </c>
+      <c r="T193">
+        <v>1.34</v>
+      </c>
+      <c r="U193">
+        <v>2.99</v>
+      </c>
+      <c r="V193">
+        <v>2.65</v>
+      </c>
+      <c r="W193">
+        <v>1.42</v>
+      </c>
+      <c r="X193">
+        <v>6.35</v>
+      </c>
+      <c r="Y193">
+        <v>1.06</v>
+      </c>
+      <c r="Z193">
+        <v>1.79</v>
+      </c>
+      <c r="AA193">
+        <v>3.72</v>
+      </c>
+      <c r="AB193">
+        <v>4.15</v>
+      </c>
+      <c r="AC193">
+        <v>1.02</v>
+      </c>
+      <c r="AD193">
+        <v>10</v>
+      </c>
+      <c r="AE193">
+        <v>1.22</v>
+      </c>
+      <c r="AF193">
+        <v>3.52</v>
+      </c>
+      <c r="AG193">
+        <v>1.83</v>
+      </c>
+      <c r="AH193">
+        <v>1.94</v>
+      </c>
+      <c r="AI193">
+        <v>1.74</v>
+      </c>
+      <c r="AJ193">
+        <v>1.98</v>
+      </c>
+      <c r="AK193">
+        <v>1.21</v>
+      </c>
+      <c r="AL193">
+        <v>1.25</v>
+      </c>
+      <c r="AM193">
+        <v>1.96</v>
+      </c>
+      <c r="AN193">
+        <v>2.08</v>
+      </c>
+      <c r="AO193">
+        <v>1</v>
+      </c>
+      <c r="AP193">
+        <v>2</v>
+      </c>
+      <c r="AQ193">
+        <v>1</v>
+      </c>
+      <c r="AR193">
+        <v>1.7</v>
+      </c>
+      <c r="AS193">
+        <v>1.44</v>
+      </c>
+      <c r="AT193">
+        <v>3.14</v>
+      </c>
+      <c r="AU193">
+        <v>3</v>
+      </c>
+      <c r="AV193">
+        <v>7</v>
+      </c>
+      <c r="AW193">
+        <v>4</v>
+      </c>
+      <c r="AX193">
+        <v>1</v>
+      </c>
+      <c r="AY193">
+        <v>7</v>
+      </c>
+      <c r="AZ193">
+        <v>8</v>
+      </c>
+      <c r="BA193">
+        <v>11</v>
+      </c>
+      <c r="BB193">
+        <v>4</v>
+      </c>
+      <c r="BC193">
+        <v>15</v>
+      </c>
+      <c r="BD193">
+        <v>1.58</v>
+      </c>
+      <c r="BE193">
+        <v>6.75</v>
+      </c>
+      <c r="BF193">
+        <v>2.55</v>
+      </c>
+      <c r="BG193">
+        <v>1.28</v>
+      </c>
+      <c r="BH193">
+        <v>3.3</v>
+      </c>
+      <c r="BI193">
+        <v>1.49</v>
+      </c>
+      <c r="BJ193">
+        <v>2.4</v>
+      </c>
+      <c r="BK193">
+        <v>1.81</v>
+      </c>
+      <c r="BL193">
+        <v>1.88</v>
+      </c>
+      <c r="BM193">
+        <v>2.25</v>
+      </c>
+      <c r="BN193">
+        <v>1.56</v>
+      </c>
+      <c r="BO193">
+        <v>2.9</v>
+      </c>
+      <c r="BP193">
+        <v>1.35</v>
+      </c>
+    </row>
+    <row r="194" spans="1:68">
+      <c r="A194" s="1">
+        <v>193</v>
+      </c>
+      <c r="B194">
+        <v>7468285</v>
+      </c>
+      <c r="C194" t="s">
+        <v>68</v>
+      </c>
+      <c r="D194" t="s">
+        <v>69</v>
+      </c>
+      <c r="E194" s="2">
+        <v>45724.5</v>
+      </c>
+      <c r="F194">
+        <v>25</v>
+      </c>
+      <c r="G194" t="s">
+        <v>76</v>
+      </c>
+      <c r="H194" t="s">
+        <v>72</v>
+      </c>
+      <c r="I194">
+        <v>1</v>
+      </c>
+      <c r="J194">
+        <v>1</v>
+      </c>
+      <c r="K194">
+        <v>2</v>
+      </c>
+      <c r="L194">
+        <v>2</v>
+      </c>
+      <c r="M194">
+        <v>1</v>
+      </c>
+      <c r="N194">
+        <v>3</v>
+      </c>
+      <c r="O194" t="s">
+        <v>213</v>
+      </c>
+      <c r="P194" t="s">
+        <v>138</v>
+      </c>
+      <c r="Q194">
+        <v>1.95</v>
+      </c>
+      <c r="R194">
+        <v>2.28</v>
+      </c>
+      <c r="S194">
+        <v>6.5</v>
+      </c>
+      <c r="T194">
+        <v>1.33</v>
+      </c>
+      <c r="U194">
+        <v>3.04</v>
+      </c>
+      <c r="V194">
+        <v>2.69</v>
+      </c>
+      <c r="W194">
+        <v>1.41</v>
+      </c>
+      <c r="X194">
+        <v>6.95</v>
+      </c>
+      <c r="Y194">
+        <v>1.04</v>
+      </c>
+      <c r="Z194">
+        <v>1.44</v>
+      </c>
+      <c r="AA194">
+        <v>4.35</v>
+      </c>
+      <c r="AB194">
+        <v>6.85</v>
+      </c>
+      <c r="AC194">
+        <v>1.01</v>
+      </c>
+      <c r="AD194">
+        <v>11</v>
+      </c>
+      <c r="AE194">
+        <v>1.2</v>
+      </c>
+      <c r="AF194">
+        <v>3.7</v>
+      </c>
+      <c r="AG194">
+        <v>1.82</v>
+      </c>
+      <c r="AH194">
+        <v>1.95</v>
+      </c>
+      <c r="AI194">
+        <v>1.95</v>
+      </c>
+      <c r="AJ194">
+        <v>1.76</v>
+      </c>
+      <c r="AK194">
+        <v>1.08</v>
+      </c>
+      <c r="AL194">
+        <v>1.19</v>
+      </c>
+      <c r="AM194">
+        <v>2.67</v>
+      </c>
+      <c r="AN194">
+        <v>1.36</v>
+      </c>
+      <c r="AO194">
+        <v>0.09</v>
+      </c>
+      <c r="AP194">
+        <v>1.5</v>
+      </c>
+      <c r="AQ194">
+        <v>0.08</v>
+      </c>
+      <c r="AR194">
+        <v>1.2</v>
+      </c>
+      <c r="AS194">
+        <v>0.96</v>
+      </c>
+      <c r="AT194">
+        <v>2.16</v>
+      </c>
+      <c r="AU194">
+        <v>4</v>
+      </c>
+      <c r="AV194">
+        <v>5</v>
+      </c>
+      <c r="AW194">
+        <v>4</v>
+      </c>
+      <c r="AX194">
+        <v>5</v>
+      </c>
+      <c r="AY194">
+        <v>8</v>
+      </c>
+      <c r="AZ194">
+        <v>10</v>
+      </c>
+      <c r="BA194">
+        <v>3</v>
+      </c>
+      <c r="BB194">
+        <v>5</v>
+      </c>
+      <c r="BC194">
+        <v>8</v>
+      </c>
+      <c r="BD194">
+        <v>1.35</v>
+      </c>
+      <c r="BE194">
+        <v>7.5</v>
+      </c>
+      <c r="BF194">
+        <v>3.45</v>
+      </c>
+      <c r="BG194">
+        <v>1.29</v>
+      </c>
+      <c r="BH194">
+        <v>3.2</v>
+      </c>
+      <c r="BI194">
+        <v>1.5</v>
+      </c>
+      <c r="BJ194">
+        <v>2.38</v>
+      </c>
+      <c r="BK194">
+        <v>1.81</v>
+      </c>
+      <c r="BL194">
+        <v>1.88</v>
+      </c>
+      <c r="BM194">
+        <v>2.25</v>
+      </c>
+      <c r="BN194">
+        <v>1.55</v>
+      </c>
+      <c r="BO194">
+        <v>2.9</v>
+      </c>
+      <c r="BP194">
+        <v>1.34</v>
+      </c>
+    </row>
+    <row r="195" spans="1:68">
+      <c r="A195" s="1">
+        <v>194</v>
+      </c>
+      <c r="B195">
+        <v>7468280</v>
+      </c>
+      <c r="C195" t="s">
+        <v>68</v>
+      </c>
+      <c r="D195" t="s">
+        <v>69</v>
+      </c>
+      <c r="E195" s="2">
+        <v>45724.625</v>
+      </c>
+      <c r="F195">
+        <v>25</v>
+      </c>
+      <c r="G195" t="s">
+        <v>70</v>
+      </c>
+      <c r="H195" t="s">
+        <v>80</v>
+      </c>
+      <c r="I195">
+        <v>0</v>
+      </c>
+      <c r="J195">
+        <v>0</v>
+      </c>
+      <c r="K195">
+        <v>0</v>
+      </c>
+      <c r="L195">
+        <v>2</v>
+      </c>
+      <c r="M195">
+        <v>0</v>
+      </c>
+      <c r="N195">
+        <v>2</v>
+      </c>
+      <c r="O195" t="s">
+        <v>214</v>
+      </c>
+      <c r="P195" t="s">
+        <v>88</v>
+      </c>
+      <c r="Q195">
+        <v>4.1</v>
+      </c>
+      <c r="R195">
+        <v>2.07</v>
+      </c>
+      <c r="S195">
+        <v>2.65</v>
+      </c>
+      <c r="T195">
+        <v>1.39</v>
+      </c>
+      <c r="U195">
+        <v>2.77</v>
+      </c>
+      <c r="V195">
+        <v>2.94</v>
+      </c>
+      <c r="W195">
+        <v>1.35</v>
+      </c>
+      <c r="X195">
+        <v>7.7</v>
+      </c>
+      <c r="Y195">
+        <v>1.03</v>
+      </c>
+      <c r="Z195">
+        <v>3.46</v>
+      </c>
+      <c r="AA195">
+        <v>3.44</v>
+      </c>
+      <c r="AB195">
+        <v>2.04</v>
+      </c>
+      <c r="AC195">
+        <v>1.03</v>
+      </c>
+      <c r="AD195">
+        <v>9</v>
+      </c>
+      <c r="AE195">
+        <v>1.28</v>
+      </c>
+      <c r="AF195">
+        <v>3.1</v>
+      </c>
+      <c r="AG195">
+        <v>2.01</v>
+      </c>
+      <c r="AH195">
+        <v>1.77</v>
+      </c>
+      <c r="AI195">
+        <v>1.8</v>
+      </c>
+      <c r="AJ195">
+        <v>1.9</v>
+      </c>
+      <c r="AK195">
+        <v>1.73</v>
+      </c>
+      <c r="AL195">
+        <v>1.28</v>
+      </c>
+      <c r="AM195">
+        <v>1.28</v>
+      </c>
+      <c r="AN195">
+        <v>2.17</v>
+      </c>
+      <c r="AO195">
+        <v>2.42</v>
+      </c>
+      <c r="AP195">
+        <v>2.23</v>
+      </c>
+      <c r="AQ195">
+        <v>2.23</v>
+      </c>
+      <c r="AR195">
+        <v>2.09</v>
+      </c>
+      <c r="AS195">
+        <v>1.89</v>
+      </c>
+      <c r="AT195">
+        <v>3.98</v>
+      </c>
+      <c r="AU195">
+        <v>6</v>
+      </c>
+      <c r="AV195">
+        <v>0</v>
+      </c>
+      <c r="AW195">
+        <v>4</v>
+      </c>
+      <c r="AX195">
+        <v>4</v>
+      </c>
+      <c r="AY195">
+        <v>10</v>
+      </c>
+      <c r="AZ195">
+        <v>4</v>
+      </c>
+      <c r="BA195">
+        <v>2</v>
+      </c>
+      <c r="BB195">
+        <v>3</v>
+      </c>
+      <c r="BC195">
+        <v>5</v>
+      </c>
+      <c r="BD195">
+        <v>2.32</v>
+      </c>
+      <c r="BE195">
+        <v>6.75</v>
+      </c>
+      <c r="BF195">
+        <v>1.74</v>
+      </c>
+      <c r="BG195">
+        <v>1.28</v>
+      </c>
+      <c r="BH195">
+        <v>3.2</v>
+      </c>
+      <c r="BI195">
+        <v>1.49</v>
+      </c>
+      <c r="BJ195">
+        <v>2.4</v>
+      </c>
+      <c r="BK195">
+        <v>1.8</v>
+      </c>
+      <c r="BL195">
+        <v>1.89</v>
+      </c>
+      <c r="BM195">
+        <v>2.25</v>
+      </c>
+      <c r="BN195">
+        <v>1.55</v>
+      </c>
+      <c r="BO195">
+        <v>2.9</v>
+      </c>
+      <c r="BP195">
+        <v>1.35</v>
       </c>
     </row>
   </sheetData>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Czech Republic First League_20242025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Czech Republic First League_20242025.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1232" uniqueCount="305">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1256" uniqueCount="306">
   <si>
     <t>Id_Jogo</t>
   </si>
@@ -661,6 +661,9 @@
     <t>['51', '57']</t>
   </si>
   <si>
+    <t>['31', '35']</t>
+  </si>
+  <si>
     <t>['25']</t>
   </si>
   <si>
@@ -1290,7 +1293,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:BP195"/>
+  <dimension ref="A1:BP199"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:68">
@@ -1546,7 +1549,7 @@
         <v>86</v>
       </c>
       <c r="P2" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="Q2">
         <v>1.53</v>
@@ -1833,7 +1836,7 @@
         <v>2</v>
       </c>
       <c r="AQ3">
-        <v>1.25</v>
+        <v>1.15</v>
       </c>
       <c r="AR3">
         <v>0</v>
@@ -1958,7 +1961,7 @@
         <v>88</v>
       </c>
       <c r="P4" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="Q4">
         <v>2.88</v>
@@ -2039,7 +2042,7 @@
         <v>0.23</v>
       </c>
       <c r="AQ4">
-        <v>1.25</v>
+        <v>1.38</v>
       </c>
       <c r="AR4">
         <v>0</v>
@@ -2242,7 +2245,7 @@
         <v>0</v>
       </c>
       <c r="AP5">
-        <v>1.17</v>
+        <v>1.08</v>
       </c>
       <c r="AQ5">
         <v>1.62</v>
@@ -2370,7 +2373,7 @@
         <v>90</v>
       </c>
       <c r="P6" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="Q6">
         <v>5.5</v>
@@ -2451,7 +2454,7 @@
         <v>0.92</v>
       </c>
       <c r="AQ6">
-        <v>1.92</v>
+        <v>1.85</v>
       </c>
       <c r="AR6">
         <v>0</v>
@@ -2576,7 +2579,7 @@
         <v>91</v>
       </c>
       <c r="P7" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="Q7">
         <v>3.2</v>
@@ -3066,7 +3069,7 @@
         <v>0</v>
       </c>
       <c r="AP9">
-        <v>1.58</v>
+        <v>1.54</v>
       </c>
       <c r="AQ9">
         <v>0.77</v>
@@ -3400,7 +3403,7 @@
         <v>94</v>
       </c>
       <c r="P11" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="Q11">
         <v>6.5</v>
@@ -3606,7 +3609,7 @@
         <v>88</v>
       </c>
       <c r="P12" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="Q12">
         <v>2.85</v>
@@ -3684,10 +3687,10 @@
         <v>0</v>
       </c>
       <c r="AP12">
+        <v>0.83</v>
+      </c>
+      <c r="AQ12">
         <v>0.82</v>
-      </c>
-      <c r="AQ12">
-        <v>0.8</v>
       </c>
       <c r="AR12">
         <v>0</v>
@@ -4018,7 +4021,7 @@
         <v>96</v>
       </c>
       <c r="P14" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="Q14">
         <v>2.45</v>
@@ -4099,7 +4102,7 @@
         <v>1.42</v>
       </c>
       <c r="AQ14">
-        <v>1.25</v>
+        <v>1.38</v>
       </c>
       <c r="AR14">
         <v>0</v>
@@ -4508,7 +4511,7 @@
         <v>0</v>
       </c>
       <c r="AP16">
-        <v>2.45</v>
+        <v>2.5</v>
       </c>
       <c r="AQ16">
         <v>1.25</v>
@@ -4842,7 +4845,7 @@
         <v>88</v>
       </c>
       <c r="P18" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="Q18">
         <v>5.4</v>
@@ -5541,7 +5544,7 @@
         <v>2</v>
       </c>
       <c r="AQ21">
-        <v>1.92</v>
+        <v>1.85</v>
       </c>
       <c r="AR21">
         <v>1.81</v>
@@ -5872,7 +5875,7 @@
         <v>102</v>
       </c>
       <c r="P23" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="Q23">
         <v>2.6</v>
@@ -6078,7 +6081,7 @@
         <v>103</v>
       </c>
       <c r="P24" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="Q24">
         <v>2.75</v>
@@ -6156,10 +6159,10 @@
         <v>0</v>
       </c>
       <c r="AP24">
-        <v>1.58</v>
+        <v>1.54</v>
       </c>
       <c r="AQ24">
-        <v>1.25</v>
+        <v>1.15</v>
       </c>
       <c r="AR24">
         <v>1.19</v>
@@ -6284,7 +6287,7 @@
         <v>88</v>
       </c>
       <c r="P25" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="Q25">
         <v>1.06</v>
@@ -6490,7 +6493,7 @@
         <v>104</v>
       </c>
       <c r="P26" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="Q26">
         <v>6.23</v>
@@ -6568,7 +6571,7 @@
         <v>3</v>
       </c>
       <c r="AP26">
-        <v>1.17</v>
+        <v>1.08</v>
       </c>
       <c r="AQ26">
         <v>2.17</v>
@@ -6983,7 +6986,7 @@
         <v>3</v>
       </c>
       <c r="AQ28">
-        <v>1.25</v>
+        <v>1.38</v>
       </c>
       <c r="AR28">
         <v>2.4</v>
@@ -7186,7 +7189,7 @@
         <v>0</v>
       </c>
       <c r="AP29">
-        <v>0.82</v>
+        <v>0.83</v>
       </c>
       <c r="AQ29">
         <v>0.92</v>
@@ -7392,7 +7395,7 @@
         <v>0</v>
       </c>
       <c r="AP30">
-        <v>2.45</v>
+        <v>2.5</v>
       </c>
       <c r="AQ30">
         <v>1</v>
@@ -7807,7 +7810,7 @@
         <v>2.42</v>
       </c>
       <c r="AQ32">
-        <v>0.8</v>
+        <v>0.82</v>
       </c>
       <c r="AR32">
         <v>1.64</v>
@@ -8010,7 +8013,7 @@
         <v>0</v>
       </c>
       <c r="AP33">
-        <v>1.58</v>
+        <v>1.54</v>
       </c>
       <c r="AQ33">
         <v>0.42</v>
@@ -8138,7 +8141,7 @@
         <v>111</v>
       </c>
       <c r="P34" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="Q34">
         <v>1.45</v>
@@ -8344,7 +8347,7 @@
         <v>112</v>
       </c>
       <c r="P35" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="Q35">
         <v>2.84</v>
@@ -8550,7 +8553,7 @@
         <v>113</v>
       </c>
       <c r="P36" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="Q36">
         <v>5.63</v>
@@ -8756,7 +8759,7 @@
         <v>114</v>
       </c>
       <c r="P37" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="Q37">
         <v>2.58</v>
@@ -8837,7 +8840,7 @@
         <v>1.67</v>
       </c>
       <c r="AQ37">
-        <v>1.25</v>
+        <v>1.15</v>
       </c>
       <c r="AR37">
         <v>1.25</v>
@@ -9168,7 +9171,7 @@
         <v>88</v>
       </c>
       <c r="P39" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="Q39">
         <v>4.75</v>
@@ -9249,7 +9252,7 @@
         <v>0.23</v>
       </c>
       <c r="AQ39">
-        <v>1.92</v>
+        <v>1.85</v>
       </c>
       <c r="AR39">
         <v>1.46</v>
@@ -9580,7 +9583,7 @@
         <v>117</v>
       </c>
       <c r="P41" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="Q41">
         <v>2.4</v>
@@ -9658,7 +9661,7 @@
         <v>1.5</v>
       </c>
       <c r="AP41">
-        <v>1.17</v>
+        <v>1.08</v>
       </c>
       <c r="AQ41">
         <v>1.25</v>
@@ -9786,7 +9789,7 @@
         <v>107</v>
       </c>
       <c r="P42" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="Q42">
         <v>2.61</v>
@@ -9867,7 +9870,7 @@
         <v>1.33</v>
       </c>
       <c r="AQ42">
-        <v>0.8</v>
+        <v>0.82</v>
       </c>
       <c r="AR42">
         <v>1.41</v>
@@ -9992,7 +9995,7 @@
         <v>118</v>
       </c>
       <c r="P43" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="Q43">
         <v>1.69</v>
@@ -10276,7 +10279,7 @@
         <v>0</v>
       </c>
       <c r="AP44">
-        <v>0.82</v>
+        <v>0.83</v>
       </c>
       <c r="AQ44">
         <v>1</v>
@@ -10482,7 +10485,7 @@
         <v>1.5</v>
       </c>
       <c r="AP45">
-        <v>2.45</v>
+        <v>2.5</v>
       </c>
       <c r="AQ45">
         <v>1</v>
@@ -11434,7 +11437,7 @@
         <v>88</v>
       </c>
       <c r="P50" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="Q50">
         <v>5.1</v>
@@ -11512,7 +11515,7 @@
         <v>3</v>
       </c>
       <c r="AP50">
-        <v>1.58</v>
+        <v>1.54</v>
       </c>
       <c r="AQ50">
         <v>2.17</v>
@@ -11846,7 +11849,7 @@
         <v>122</v>
       </c>
       <c r="P52" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="Q52">
         <v>3</v>
@@ -12258,7 +12261,7 @@
         <v>124</v>
       </c>
       <c r="P54" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="Q54">
         <v>3</v>
@@ -12339,7 +12342,7 @@
         <v>1.33</v>
       </c>
       <c r="AQ54">
-        <v>1.25</v>
+        <v>1.15</v>
       </c>
       <c r="AR54">
         <v>1.4</v>
@@ -12545,7 +12548,7 @@
         <v>1.42</v>
       </c>
       <c r="AQ55">
-        <v>1.92</v>
+        <v>1.85</v>
       </c>
       <c r="AR55">
         <v>1.32</v>
@@ -12670,7 +12673,7 @@
         <v>125</v>
       </c>
       <c r="P56" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="Q56">
         <v>1.85</v>
@@ -12751,7 +12754,7 @@
         <v>2.42</v>
       </c>
       <c r="AQ56">
-        <v>1.25</v>
+        <v>1.38</v>
       </c>
       <c r="AR56">
         <v>1.85</v>
@@ -12876,7 +12879,7 @@
         <v>88</v>
       </c>
       <c r="P57" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="Q57">
         <v>5.88</v>
@@ -13160,7 +13163,7 @@
         <v>1.33</v>
       </c>
       <c r="AP58">
-        <v>1.58</v>
+        <v>1.54</v>
       </c>
       <c r="AQ58">
         <v>0.92</v>
@@ -13288,7 +13291,7 @@
         <v>127</v>
       </c>
       <c r="P59" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="Q59">
         <v>3.86</v>
@@ -13781,7 +13784,7 @@
         <v>3</v>
       </c>
       <c r="AQ61">
-        <v>1.92</v>
+        <v>1.85</v>
       </c>
       <c r="AR61">
         <v>2.33</v>
@@ -13906,7 +13909,7 @@
         <v>130</v>
       </c>
       <c r="P62" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="Q62">
         <v>1.83</v>
@@ -14112,7 +14115,7 @@
         <v>88</v>
       </c>
       <c r="P63" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="Q63">
         <v>8.77</v>
@@ -14524,7 +14527,7 @@
         <v>132</v>
       </c>
       <c r="P65" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="Q65">
         <v>2.4</v>
@@ -14730,7 +14733,7 @@
         <v>133</v>
       </c>
       <c r="P66" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="Q66">
         <v>1.55</v>
@@ -14811,7 +14814,7 @@
         <v>2.23</v>
       </c>
       <c r="AQ66">
-        <v>1.25</v>
+        <v>1.38</v>
       </c>
       <c r="AR66">
         <v>2.05</v>
@@ -14936,7 +14939,7 @@
         <v>134</v>
       </c>
       <c r="P67" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="Q67">
         <v>4</v>
@@ -15142,7 +15145,7 @@
         <v>88</v>
       </c>
       <c r="P68" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="Q68">
         <v>3.1</v>
@@ -15220,7 +15223,7 @@
         <v>0</v>
       </c>
       <c r="AP68">
-        <v>0.82</v>
+        <v>0.83</v>
       </c>
       <c r="AQ68">
         <v>0.77</v>
@@ -15429,7 +15432,7 @@
         <v>1.5</v>
       </c>
       <c r="AQ69">
-        <v>0.8</v>
+        <v>0.82</v>
       </c>
       <c r="AR69">
         <v>1.16</v>
@@ -15838,7 +15841,7 @@
         <v>0</v>
       </c>
       <c r="AP71">
-        <v>2.45</v>
+        <v>2.5</v>
       </c>
       <c r="AQ71">
         <v>0.08</v>
@@ -15966,7 +15969,7 @@
         <v>124</v>
       </c>
       <c r="P72" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="Q72">
         <v>1.88</v>
@@ -16047,7 +16050,7 @@
         <v>2.42</v>
       </c>
       <c r="AQ72">
-        <v>1.25</v>
+        <v>1.15</v>
       </c>
       <c r="AR72">
         <v>1.84</v>
@@ -16172,7 +16175,7 @@
         <v>88</v>
       </c>
       <c r="P73" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="Q73">
         <v>7</v>
@@ -16250,7 +16253,7 @@
         <v>2.33</v>
       </c>
       <c r="AP73">
-        <v>1.17</v>
+        <v>1.08</v>
       </c>
       <c r="AQ73">
         <v>2.23</v>
@@ -16584,7 +16587,7 @@
         <v>138</v>
       </c>
       <c r="P75" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="Q75">
         <v>2.3</v>
@@ -16790,7 +16793,7 @@
         <v>88</v>
       </c>
       <c r="P76" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="Q76">
         <v>3.7</v>
@@ -16996,7 +16999,7 @@
         <v>88</v>
       </c>
       <c r="P77" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="Q77">
         <v>2.47</v>
@@ -17614,7 +17617,7 @@
         <v>140</v>
       </c>
       <c r="P80" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="Q80">
         <v>2.5</v>
@@ -17820,7 +17823,7 @@
         <v>141</v>
       </c>
       <c r="P81" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="Q81">
         <v>2.38</v>
@@ -18026,7 +18029,7 @@
         <v>142</v>
       </c>
       <c r="P82" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="Q82">
         <v>2.8</v>
@@ -18104,10 +18107,10 @@
         <v>1.4</v>
       </c>
       <c r="AP82">
-        <v>1.58</v>
+        <v>1.54</v>
       </c>
       <c r="AQ82">
-        <v>1.25</v>
+        <v>1.38</v>
       </c>
       <c r="AR82">
         <v>1.31</v>
@@ -18232,7 +18235,7 @@
         <v>143</v>
       </c>
       <c r="P83" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="Q83">
         <v>2.6</v>
@@ -18438,7 +18441,7 @@
         <v>144</v>
       </c>
       <c r="P84" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="Q84">
         <v>3.4</v>
@@ -18516,10 +18519,10 @@
         <v>1.6</v>
       </c>
       <c r="AP84">
-        <v>2.45</v>
+        <v>2.5</v>
       </c>
       <c r="AQ84">
-        <v>1.92</v>
+        <v>1.85</v>
       </c>
       <c r="AR84">
         <v>1.81</v>
@@ -18850,7 +18853,7 @@
         <v>146</v>
       </c>
       <c r="P86" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="Q86">
         <v>2.88</v>
@@ -18928,10 +18931,10 @@
         <v>0.8</v>
       </c>
       <c r="AP86">
-        <v>1.17</v>
+        <v>1.08</v>
       </c>
       <c r="AQ86">
-        <v>1.25</v>
+        <v>1.15</v>
       </c>
       <c r="AR86">
         <v>1.41</v>
@@ -19262,7 +19265,7 @@
         <v>88</v>
       </c>
       <c r="P88" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="Q88">
         <v>2.6</v>
@@ -19468,7 +19471,7 @@
         <v>93</v>
       </c>
       <c r="P89" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="Q89">
         <v>6.5</v>
@@ -19880,7 +19883,7 @@
         <v>149</v>
       </c>
       <c r="P91" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="Q91">
         <v>4.7</v>
@@ -19958,7 +19961,7 @@
         <v>1</v>
       </c>
       <c r="AP91">
-        <v>0.82</v>
+        <v>0.83</v>
       </c>
       <c r="AQ91">
         <v>1.62</v>
@@ -20086,7 +20089,7 @@
         <v>88</v>
       </c>
       <c r="P92" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="Q92">
         <v>3.8</v>
@@ -20498,7 +20501,7 @@
         <v>150</v>
       </c>
       <c r="P94" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="Q94">
         <v>3</v>
@@ -20785,7 +20788,7 @@
         <v>1.58</v>
       </c>
       <c r="AQ95">
-        <v>0.8</v>
+        <v>0.82</v>
       </c>
       <c r="AR95">
         <v>1.43</v>
@@ -21403,7 +21406,7 @@
         <v>0.92</v>
       </c>
       <c r="AQ98">
-        <v>1.25</v>
+        <v>1.15</v>
       </c>
       <c r="AR98">
         <v>1.15</v>
@@ -21815,7 +21818,7 @@
         <v>1.46</v>
       </c>
       <c r="AQ100">
-        <v>1.25</v>
+        <v>1.38</v>
       </c>
       <c r="AR100">
         <v>1.67</v>
@@ -21940,7 +21943,7 @@
         <v>156</v>
       </c>
       <c r="P101" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="Q101">
         <v>1.83</v>
@@ -22430,7 +22433,7 @@
         <v>0.57</v>
       </c>
       <c r="AP103">
-        <v>1.17</v>
+        <v>1.08</v>
       </c>
       <c r="AQ103">
         <v>0.46</v>
@@ -22639,7 +22642,7 @@
         <v>1.5</v>
       </c>
       <c r="AQ104">
-        <v>1.92</v>
+        <v>1.85</v>
       </c>
       <c r="AR104">
         <v>1.15</v>
@@ -22842,7 +22845,7 @@
         <v>2.6</v>
       </c>
       <c r="AP105">
-        <v>1.58</v>
+        <v>1.54</v>
       </c>
       <c r="AQ105">
         <v>2.23</v>
@@ -23048,7 +23051,7 @@
         <v>0.33</v>
       </c>
       <c r="AP106">
-        <v>2.45</v>
+        <v>2.5</v>
       </c>
       <c r="AQ106">
         <v>0.42</v>
@@ -23254,7 +23257,7 @@
         <v>1.57</v>
       </c>
       <c r="AP107">
-        <v>0.82</v>
+        <v>0.83</v>
       </c>
       <c r="AQ107">
         <v>1.25</v>
@@ -23588,7 +23591,7 @@
         <v>161</v>
       </c>
       <c r="P109" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="Q109">
         <v>2.24</v>
@@ -23794,7 +23797,7 @@
         <v>162</v>
       </c>
       <c r="P110" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="Q110">
         <v>4.6</v>
@@ -24206,7 +24209,7 @@
         <v>164</v>
       </c>
       <c r="P112" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="Q112">
         <v>1.44</v>
@@ -24287,7 +24290,7 @@
         <v>3</v>
       </c>
       <c r="AQ112">
-        <v>0.8</v>
+        <v>0.82</v>
       </c>
       <c r="AR112">
         <v>2.21</v>
@@ -24412,7 +24415,7 @@
         <v>165</v>
       </c>
       <c r="P113" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="Q113">
         <v>3.25</v>
@@ -24618,7 +24621,7 @@
         <v>151</v>
       </c>
       <c r="P114" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="Q114">
         <v>2.88</v>
@@ -24699,7 +24702,7 @@
         <v>1.5</v>
       </c>
       <c r="AQ114">
-        <v>1.25</v>
+        <v>1.15</v>
       </c>
       <c r="AR114">
         <v>1.11</v>
@@ -24824,7 +24827,7 @@
         <v>99</v>
       </c>
       <c r="P115" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="Q115">
         <v>1.73</v>
@@ -25030,7 +25033,7 @@
         <v>88</v>
       </c>
       <c r="P116" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="Q116">
         <v>4.33</v>
@@ -25108,10 +25111,10 @@
         <v>1.57</v>
       </c>
       <c r="AP116">
-        <v>1.58</v>
+        <v>1.54</v>
       </c>
       <c r="AQ116">
-        <v>1.92</v>
+        <v>1.85</v>
       </c>
       <c r="AR116">
         <v>1.34</v>
@@ -25314,7 +25317,7 @@
         <v>0.29</v>
       </c>
       <c r="AP117">
-        <v>1.17</v>
+        <v>1.08</v>
       </c>
       <c r="AQ117">
         <v>0.42</v>
@@ -25648,7 +25651,7 @@
         <v>88</v>
       </c>
       <c r="P119" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="Q119">
         <v>15</v>
@@ -25854,7 +25857,7 @@
         <v>168</v>
       </c>
       <c r="P120" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="Q120">
         <v>3</v>
@@ -26266,7 +26269,7 @@
         <v>170</v>
       </c>
       <c r="P122" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="Q122">
         <v>3.25</v>
@@ -26344,7 +26347,7 @@
         <v>1</v>
       </c>
       <c r="AP122">
-        <v>1.17</v>
+        <v>1.08</v>
       </c>
       <c r="AQ122">
         <v>0.92</v>
@@ -26553,7 +26556,7 @@
         <v>1.33</v>
       </c>
       <c r="AQ123">
-        <v>1.25</v>
+        <v>1.38</v>
       </c>
       <c r="AR123">
         <v>1.58</v>
@@ -26678,7 +26681,7 @@
         <v>172</v>
       </c>
       <c r="P124" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="Q124">
         <v>1.83</v>
@@ -26756,10 +26759,10 @@
         <v>1.17</v>
       </c>
       <c r="AP124">
-        <v>2.45</v>
+        <v>2.5</v>
       </c>
       <c r="AQ124">
-        <v>0.8</v>
+        <v>0.82</v>
       </c>
       <c r="AR124">
         <v>1.87</v>
@@ -26884,7 +26887,7 @@
         <v>171</v>
       </c>
       <c r="P125" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="Q125">
         <v>6.3</v>
@@ -27580,7 +27583,7 @@
         <v>0</v>
       </c>
       <c r="AP128">
-        <v>0.82</v>
+        <v>0.83</v>
       </c>
       <c r="AQ128">
         <v>0.08</v>
@@ -27708,7 +27711,7 @@
         <v>174</v>
       </c>
       <c r="P129" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="Q129">
         <v>2.1</v>
@@ -27914,7 +27917,7 @@
         <v>175</v>
       </c>
       <c r="P130" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="Q130">
         <v>1.5</v>
@@ -27995,7 +27998,7 @@
         <v>2.23</v>
       </c>
       <c r="AQ130">
-        <v>0.8</v>
+        <v>0.82</v>
       </c>
       <c r="AR130">
         <v>1.93</v>
@@ -28120,7 +28123,7 @@
         <v>176</v>
       </c>
       <c r="P131" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="Q131">
         <v>3.5</v>
@@ -28198,10 +28201,10 @@
         <v>1</v>
       </c>
       <c r="AP131">
-        <v>0.82</v>
+        <v>0.83</v>
       </c>
       <c r="AQ131">
-        <v>1.25</v>
+        <v>1.38</v>
       </c>
       <c r="AR131">
         <v>1.21</v>
@@ -28326,7 +28329,7 @@
         <v>177</v>
       </c>
       <c r="P132" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="Q132">
         <v>4.04</v>
@@ -28738,7 +28741,7 @@
         <v>88</v>
       </c>
       <c r="P134" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="Q134">
         <v>2.75</v>
@@ -28816,7 +28819,7 @@
         <v>0.63</v>
       </c>
       <c r="AP134">
-        <v>1.17</v>
+        <v>1.08</v>
       </c>
       <c r="AQ134">
         <v>1</v>
@@ -29228,7 +29231,7 @@
         <v>2.43</v>
       </c>
       <c r="AP136">
-        <v>2.45</v>
+        <v>2.5</v>
       </c>
       <c r="AQ136">
         <v>2.23</v>
@@ -29562,7 +29565,7 @@
         <v>91</v>
       </c>
       <c r="P138" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="Q138">
         <v>2.25</v>
@@ -29768,7 +29771,7 @@
         <v>179</v>
       </c>
       <c r="P139" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="Q139">
         <v>1.9</v>
@@ -30180,7 +30183,7 @@
         <v>88</v>
       </c>
       <c r="P141" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="Q141">
         <v>4</v>
@@ -30261,7 +30264,7 @@
         <v>0.23</v>
       </c>
       <c r="AQ141">
-        <v>1.25</v>
+        <v>1.15</v>
       </c>
       <c r="AR141">
         <v>1.34</v>
@@ -30386,7 +30389,7 @@
         <v>117</v>
       </c>
       <c r="P142" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="Q142">
         <v>4</v>
@@ -30467,7 +30470,7 @@
         <v>1.46</v>
       </c>
       <c r="AQ142">
-        <v>1.92</v>
+        <v>1.85</v>
       </c>
       <c r="AR142">
         <v>1.59</v>
@@ -30798,7 +30801,7 @@
         <v>182</v>
       </c>
       <c r="P144" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="Q144">
         <v>6</v>
@@ -31004,7 +31007,7 @@
         <v>88</v>
       </c>
       <c r="P145" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="Q145">
         <v>3.5</v>
@@ -31082,7 +31085,7 @@
         <v>1.33</v>
       </c>
       <c r="AP145">
-        <v>1.58</v>
+        <v>1.54</v>
       </c>
       <c r="AQ145">
         <v>1.62</v>
@@ -31210,7 +31213,7 @@
         <v>183</v>
       </c>
       <c r="P146" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="Q146">
         <v>4.33</v>
@@ -31416,7 +31419,7 @@
         <v>184</v>
       </c>
       <c r="P147" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="Q147">
         <v>3.8</v>
@@ -31494,7 +31497,7 @@
         <v>1.11</v>
       </c>
       <c r="AP147">
-        <v>0.82</v>
+        <v>0.83</v>
       </c>
       <c r="AQ147">
         <v>1</v>
@@ -31622,7 +31625,7 @@
         <v>185</v>
       </c>
       <c r="P148" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="Q148">
         <v>2.5</v>
@@ -31700,10 +31703,10 @@
         <v>0.88</v>
       </c>
       <c r="AP148">
-        <v>1.17</v>
+        <v>1.08</v>
       </c>
       <c r="AQ148">
-        <v>0.8</v>
+        <v>0.82</v>
       </c>
       <c r="AR148">
         <v>1.47</v>
@@ -31828,7 +31831,7 @@
         <v>186</v>
       </c>
       <c r="P149" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="Q149">
         <v>2.05</v>
@@ -31906,7 +31909,7 @@
         <v>1.22</v>
       </c>
       <c r="AP149">
-        <v>2.45</v>
+        <v>2.5</v>
       </c>
       <c r="AQ149">
         <v>0.92</v>
@@ -32034,7 +32037,7 @@
         <v>187</v>
       </c>
       <c r="P150" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="Q150">
         <v>1.95</v>
@@ -32240,7 +32243,7 @@
         <v>188</v>
       </c>
       <c r="P151" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="Q151">
         <v>2.48</v>
@@ -32321,7 +32324,7 @@
         <v>1.58</v>
       </c>
       <c r="AQ151">
-        <v>1.25</v>
+        <v>1.38</v>
       </c>
       <c r="AR151">
         <v>1.53</v>
@@ -32652,7 +32655,7 @@
         <v>190</v>
       </c>
       <c r="P153" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="Q153">
         <v>1.4</v>
@@ -33064,7 +33067,7 @@
         <v>88</v>
       </c>
       <c r="P155" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="Q155">
         <v>3.2</v>
@@ -33554,7 +33557,7 @@
         <v>0.6</v>
       </c>
       <c r="AP157">
-        <v>1.58</v>
+        <v>1.54</v>
       </c>
       <c r="AQ157">
         <v>0.46</v>
@@ -33682,7 +33685,7 @@
         <v>88</v>
       </c>
       <c r="P158" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="Q158">
         <v>5</v>
@@ -33888,7 +33891,7 @@
         <v>88</v>
       </c>
       <c r="P159" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="Q159">
         <v>2.38</v>
@@ -34175,7 +34178,7 @@
         <v>3</v>
       </c>
       <c r="AQ160">
-        <v>1.25</v>
+        <v>1.15</v>
       </c>
       <c r="AR160">
         <v>2.39</v>
@@ -34300,7 +34303,7 @@
         <v>193</v>
       </c>
       <c r="P161" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="Q161">
         <v>4.75</v>
@@ -34381,7 +34384,7 @@
         <v>1.67</v>
       </c>
       <c r="AQ161">
-        <v>1.92</v>
+        <v>1.85</v>
       </c>
       <c r="AR161">
         <v>1.6</v>
@@ -34506,7 +34509,7 @@
         <v>194</v>
       </c>
       <c r="P162" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="Q162">
         <v>2.63</v>
@@ -34712,7 +34715,7 @@
         <v>88</v>
       </c>
       <c r="P163" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="Q163">
         <v>11</v>
@@ -34790,7 +34793,7 @@
         <v>2.3</v>
       </c>
       <c r="AP163">
-        <v>0.82</v>
+        <v>0.83</v>
       </c>
       <c r="AQ163">
         <v>2.23</v>
@@ -34918,7 +34921,7 @@
         <v>195</v>
       </c>
       <c r="P164" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="Q164">
         <v>2</v>
@@ -35124,7 +35127,7 @@
         <v>196</v>
       </c>
       <c r="P165" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="Q165">
         <v>2.5</v>
@@ -35408,10 +35411,10 @@
         <v>1.2</v>
       </c>
       <c r="AP166">
-        <v>2.45</v>
+        <v>2.5</v>
       </c>
       <c r="AQ166">
-        <v>1.25</v>
+        <v>1.38</v>
       </c>
       <c r="AR166">
         <v>1.9</v>
@@ -35614,7 +35617,7 @@
         <v>0.11</v>
       </c>
       <c r="AP167">
-        <v>1.17</v>
+        <v>1.08</v>
       </c>
       <c r="AQ167">
         <v>0.08</v>
@@ -36360,7 +36363,7 @@
         <v>201</v>
       </c>
       <c r="P171" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="Q171">
         <v>5.2</v>
@@ -36566,7 +36569,7 @@
         <v>202</v>
       </c>
       <c r="P172" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="Q172">
         <v>6.35</v>
@@ -36772,7 +36775,7 @@
         <v>203</v>
       </c>
       <c r="P173" t="s">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="Q173">
         <v>2.6</v>
@@ -36850,7 +36853,7 @@
         <v>1.5</v>
       </c>
       <c r="AP173">
-        <v>1.58</v>
+        <v>1.54</v>
       </c>
       <c r="AQ173">
         <v>1.33</v>
@@ -36978,7 +36981,7 @@
         <v>88</v>
       </c>
       <c r="P174" t="s">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="Q174">
         <v>4.86</v>
@@ -37059,7 +37062,7 @@
         <v>1.33</v>
       </c>
       <c r="AQ174">
-        <v>1.92</v>
+        <v>1.85</v>
       </c>
       <c r="AR174">
         <v>1.47</v>
@@ -37184,7 +37187,7 @@
         <v>204</v>
       </c>
       <c r="P175" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="Q175">
         <v>2.66</v>
@@ -37265,7 +37268,7 @@
         <v>1.42</v>
       </c>
       <c r="AQ175">
-        <v>1.25</v>
+        <v>1.15</v>
       </c>
       <c r="AR175">
         <v>1.42</v>
@@ -37596,7 +37599,7 @@
         <v>171</v>
       </c>
       <c r="P177" t="s">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="Q177">
         <v>3.63</v>
@@ -37677,7 +37680,7 @@
         <v>0.92</v>
       </c>
       <c r="AQ177">
-        <v>1.25</v>
+        <v>1.38</v>
       </c>
       <c r="AR177">
         <v>1.28</v>
@@ -37880,7 +37883,7 @@
         <v>0.82</v>
       </c>
       <c r="AP178">
-        <v>2.45</v>
+        <v>2.5</v>
       </c>
       <c r="AQ178">
         <v>0.77</v>
@@ -38008,7 +38011,7 @@
         <v>88</v>
       </c>
       <c r="P179" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="Q179">
         <v>3.92</v>
@@ -38086,10 +38089,10 @@
         <v>1.09</v>
       </c>
       <c r="AP179">
-        <v>0.82</v>
+        <v>0.83</v>
       </c>
       <c r="AQ179">
-        <v>1.25</v>
+        <v>1.15</v>
       </c>
       <c r="AR179">
         <v>1.2</v>
@@ -38214,7 +38217,7 @@
         <v>206</v>
       </c>
       <c r="P180" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="Q180">
         <v>1.32</v>
@@ -38498,7 +38501,7 @@
         <v>1</v>
       </c>
       <c r="AP181">
-        <v>1.17</v>
+        <v>1.08</v>
       </c>
       <c r="AQ181">
         <v>1</v>
@@ -38707,7 +38710,7 @@
         <v>2</v>
       </c>
       <c r="AQ182">
-        <v>0.8</v>
+        <v>0.82</v>
       </c>
       <c r="AR182">
         <v>1.67</v>
@@ -38832,7 +38835,7 @@
         <v>208</v>
       </c>
       <c r="P183" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="Q183">
         <v>4.3</v>
@@ -39038,7 +39041,7 @@
         <v>88</v>
       </c>
       <c r="P184" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="Q184">
         <v>5.8</v>
@@ -39322,7 +39325,7 @@
         <v>1.27</v>
       </c>
       <c r="AP185">
-        <v>1.58</v>
+        <v>1.54</v>
       </c>
       <c r="AQ185">
         <v>1.25</v>
@@ -39450,7 +39453,7 @@
         <v>96</v>
       </c>
       <c r="P186" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="Q186">
         <v>4.7</v>
@@ -40068,7 +40071,7 @@
         <v>88</v>
       </c>
       <c r="P189" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="Q189">
         <v>4.5</v>
@@ -40149,7 +40152,7 @@
         <v>1.58</v>
       </c>
       <c r="AQ189">
-        <v>1.92</v>
+        <v>1.85</v>
       </c>
       <c r="AR189">
         <v>1.57</v>
@@ -41461,6 +41464,830 @@
       </c>
       <c r="BP195">
         <v>1.35</v>
+      </c>
+    </row>
+    <row r="196" spans="1:68">
+      <c r="A196" s="1">
+        <v>195</v>
+      </c>
+      <c r="B196">
+        <v>7468282</v>
+      </c>
+      <c r="C196" t="s">
+        <v>68</v>
+      </c>
+      <c r="D196" t="s">
+        <v>69</v>
+      </c>
+      <c r="E196" s="2">
+        <v>45725.375</v>
+      </c>
+      <c r="F196">
+        <v>25</v>
+      </c>
+      <c r="G196" t="s">
+        <v>83</v>
+      </c>
+      <c r="H196" t="s">
+        <v>82</v>
+      </c>
+      <c r="I196">
+        <v>2</v>
+      </c>
+      <c r="J196">
+        <v>1</v>
+      </c>
+      <c r="K196">
+        <v>3</v>
+      </c>
+      <c r="L196">
+        <v>2</v>
+      </c>
+      <c r="M196">
+        <v>1</v>
+      </c>
+      <c r="N196">
+        <v>3</v>
+      </c>
+      <c r="O196" t="s">
+        <v>215</v>
+      </c>
+      <c r="P196" t="s">
+        <v>221</v>
+      </c>
+      <c r="Q196">
+        <v>1.95</v>
+      </c>
+      <c r="R196">
+        <v>2.5</v>
+      </c>
+      <c r="S196">
+        <v>5</v>
+      </c>
+      <c r="T196">
+        <v>1.25</v>
+      </c>
+      <c r="U196">
+        <v>3.75</v>
+      </c>
+      <c r="V196">
+        <v>2.2</v>
+      </c>
+      <c r="W196">
+        <v>1.62</v>
+      </c>
+      <c r="X196">
+        <v>4.8</v>
+      </c>
+      <c r="Y196">
+        <v>1.17</v>
+      </c>
+      <c r="Z196">
+        <v>1.51</v>
+      </c>
+      <c r="AA196">
+        <v>4.45</v>
+      </c>
+      <c r="AB196">
+        <v>5.45</v>
+      </c>
+      <c r="AC196">
+        <v>1.02</v>
+      </c>
+      <c r="AD196">
+        <v>10</v>
+      </c>
+      <c r="AE196">
+        <v>1.12</v>
+      </c>
+      <c r="AF196">
+        <v>4.75</v>
+      </c>
+      <c r="AG196">
+        <v>1.49</v>
+      </c>
+      <c r="AH196">
+        <v>2.31</v>
+      </c>
+      <c r="AI196">
+        <v>1.62</v>
+      </c>
+      <c r="AJ196">
+        <v>2.2</v>
+      </c>
+      <c r="AK196">
+        <v>1.15</v>
+      </c>
+      <c r="AL196">
+        <v>1.2</v>
+      </c>
+      <c r="AM196">
+        <v>2.5</v>
+      </c>
+      <c r="AN196">
+        <v>2.45</v>
+      </c>
+      <c r="AO196">
+        <v>1.25</v>
+      </c>
+      <c r="AP196">
+        <v>2.5</v>
+      </c>
+      <c r="AQ196">
+        <v>1.15</v>
+      </c>
+      <c r="AR196">
+        <v>1.76</v>
+      </c>
+      <c r="AS196">
+        <v>1.33</v>
+      </c>
+      <c r="AT196">
+        <v>3.09</v>
+      </c>
+      <c r="AU196">
+        <v>10</v>
+      </c>
+      <c r="AV196">
+        <v>5</v>
+      </c>
+      <c r="AW196">
+        <v>11</v>
+      </c>
+      <c r="AX196">
+        <v>8</v>
+      </c>
+      <c r="AY196">
+        <v>21</v>
+      </c>
+      <c r="AZ196">
+        <v>13</v>
+      </c>
+      <c r="BA196">
+        <v>5</v>
+      </c>
+      <c r="BB196">
+        <v>7</v>
+      </c>
+      <c r="BC196">
+        <v>12</v>
+      </c>
+      <c r="BD196">
+        <v>1.45</v>
+      </c>
+      <c r="BE196">
+        <v>7</v>
+      </c>
+      <c r="BF196">
+        <v>3.05</v>
+      </c>
+      <c r="BG196">
+        <v>1.18</v>
+      </c>
+      <c r="BH196">
+        <v>4.1</v>
+      </c>
+      <c r="BI196">
+        <v>1.32</v>
+      </c>
+      <c r="BJ196">
+        <v>3.05</v>
+      </c>
+      <c r="BK196">
+        <v>1.54</v>
+      </c>
+      <c r="BL196">
+        <v>2.3</v>
+      </c>
+      <c r="BM196">
+        <v>1.84</v>
+      </c>
+      <c r="BN196">
+        <v>1.84</v>
+      </c>
+      <c r="BO196">
+        <v>2.3</v>
+      </c>
+      <c r="BP196">
+        <v>1.54</v>
+      </c>
+    </row>
+    <row r="197" spans="1:68">
+      <c r="A197" s="1">
+        <v>196</v>
+      </c>
+      <c r="B197">
+        <v>7468279</v>
+      </c>
+      <c r="C197" t="s">
+        <v>68</v>
+      </c>
+      <c r="D197" t="s">
+        <v>69</v>
+      </c>
+      <c r="E197" s="2">
+        <v>45725.47916666666</v>
+      </c>
+      <c r="F197">
+        <v>25</v>
+      </c>
+      <c r="G197" t="s">
+        <v>73</v>
+      </c>
+      <c r="H197" t="s">
+        <v>85</v>
+      </c>
+      <c r="I197">
+        <v>0</v>
+      </c>
+      <c r="J197">
+        <v>1</v>
+      </c>
+      <c r="K197">
+        <v>1</v>
+      </c>
+      <c r="L197">
+        <v>0</v>
+      </c>
+      <c r="M197">
+        <v>1</v>
+      </c>
+      <c r="N197">
+        <v>1</v>
+      </c>
+      <c r="O197" t="s">
+        <v>88</v>
+      </c>
+      <c r="P197" t="s">
+        <v>221</v>
+      </c>
+      <c r="Q197">
+        <v>2.88</v>
+      </c>
+      <c r="R197">
+        <v>2.1</v>
+      </c>
+      <c r="S197">
+        <v>3.75</v>
+      </c>
+      <c r="T197">
+        <v>1.4</v>
+      </c>
+      <c r="U197">
+        <v>2.75</v>
+      </c>
+      <c r="V197">
+        <v>3</v>
+      </c>
+      <c r="W197">
+        <v>1.36</v>
+      </c>
+      <c r="X197">
+        <v>8</v>
+      </c>
+      <c r="Y197">
+        <v>1.08</v>
+      </c>
+      <c r="Z197">
+        <v>2.1</v>
+      </c>
+      <c r="AA197">
+        <v>3.3</v>
+      </c>
+      <c r="AB197">
+        <v>3.3</v>
+      </c>
+      <c r="AC197">
+        <v>0</v>
+      </c>
+      <c r="AD197">
+        <v>0</v>
+      </c>
+      <c r="AE197">
+        <v>2.88</v>
+      </c>
+      <c r="AF197">
+        <v>1.41</v>
+      </c>
+      <c r="AG197">
+        <v>1.97</v>
+      </c>
+      <c r="AH197">
+        <v>1.85</v>
+      </c>
+      <c r="AI197">
+        <v>1.75</v>
+      </c>
+      <c r="AJ197">
+        <v>2</v>
+      </c>
+      <c r="AK197">
+        <v>0</v>
+      </c>
+      <c r="AL197">
+        <v>0</v>
+      </c>
+      <c r="AM197">
+        <v>0</v>
+      </c>
+      <c r="AN197">
+        <v>1.17</v>
+      </c>
+      <c r="AO197">
+        <v>1.25</v>
+      </c>
+      <c r="AP197">
+        <v>1.08</v>
+      </c>
+      <c r="AQ197">
+        <v>1.38</v>
+      </c>
+      <c r="AR197">
+        <v>1.61</v>
+      </c>
+      <c r="AS197">
+        <v>1.22</v>
+      </c>
+      <c r="AT197">
+        <v>2.83</v>
+      </c>
+      <c r="AU197">
+        <v>5</v>
+      </c>
+      <c r="AV197">
+        <v>4</v>
+      </c>
+      <c r="AW197">
+        <v>3</v>
+      </c>
+      <c r="AX197">
+        <v>5</v>
+      </c>
+      <c r="AY197">
+        <v>8</v>
+      </c>
+      <c r="AZ197">
+        <v>9</v>
+      </c>
+      <c r="BA197">
+        <v>5</v>
+      </c>
+      <c r="BB197">
+        <v>4</v>
+      </c>
+      <c r="BC197">
+        <v>9</v>
+      </c>
+      <c r="BD197">
+        <v>0</v>
+      </c>
+      <c r="BE197">
+        <v>0</v>
+      </c>
+      <c r="BF197">
+        <v>0</v>
+      </c>
+      <c r="BG197">
+        <v>0</v>
+      </c>
+      <c r="BH197">
+        <v>0</v>
+      </c>
+      <c r="BI197">
+        <v>0</v>
+      </c>
+      <c r="BJ197">
+        <v>0</v>
+      </c>
+      <c r="BK197">
+        <v>0</v>
+      </c>
+      <c r="BL197">
+        <v>0</v>
+      </c>
+      <c r="BM197">
+        <v>0</v>
+      </c>
+      <c r="BN197">
+        <v>0</v>
+      </c>
+      <c r="BO197">
+        <v>0</v>
+      </c>
+      <c r="BP197">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="198" spans="1:68">
+      <c r="A198" s="1">
+        <v>197</v>
+      </c>
+      <c r="B198">
+        <v>7468284</v>
+      </c>
+      <c r="C198" t="s">
+        <v>68</v>
+      </c>
+      <c r="D198" t="s">
+        <v>69</v>
+      </c>
+      <c r="E198" s="2">
+        <v>45725.47916666666</v>
+      </c>
+      <c r="F198">
+        <v>25</v>
+      </c>
+      <c r="G198" t="s">
+        <v>77</v>
+      </c>
+      <c r="H198" t="s">
+        <v>75</v>
+      </c>
+      <c r="I198">
+        <v>1</v>
+      </c>
+      <c r="J198">
+        <v>1</v>
+      </c>
+      <c r="K198">
+        <v>2</v>
+      </c>
+      <c r="L198">
+        <v>1</v>
+      </c>
+      <c r="M198">
+        <v>1</v>
+      </c>
+      <c r="N198">
+        <v>2</v>
+      </c>
+      <c r="O198" t="s">
+        <v>182</v>
+      </c>
+      <c r="P198" t="s">
+        <v>134</v>
+      </c>
+      <c r="Q198">
+        <v>2.45</v>
+      </c>
+      <c r="R198">
+        <v>2.1</v>
+      </c>
+      <c r="S198">
+        <v>4.6</v>
+      </c>
+      <c r="T198">
+        <v>1.4</v>
+      </c>
+      <c r="U198">
+        <v>2.75</v>
+      </c>
+      <c r="V198">
+        <v>3</v>
+      </c>
+      <c r="W198">
+        <v>1.36</v>
+      </c>
+      <c r="X198">
+        <v>8.5</v>
+      </c>
+      <c r="Y198">
+        <v>1.07</v>
+      </c>
+      <c r="Z198">
+        <v>1.76</v>
+      </c>
+      <c r="AA198">
+        <v>3.64</v>
+      </c>
+      <c r="AB198">
+        <v>4.4</v>
+      </c>
+      <c r="AC198">
+        <v>1</v>
+      </c>
+      <c r="AD198">
+        <v>9.300000000000001</v>
+      </c>
+      <c r="AE198">
+        <v>1.27</v>
+      </c>
+      <c r="AF198">
+        <v>3.15</v>
+      </c>
+      <c r="AG198">
+        <v>1.98</v>
+      </c>
+      <c r="AH198">
+        <v>1.79</v>
+      </c>
+      <c r="AI198">
+        <v>1.85</v>
+      </c>
+      <c r="AJ198">
+        <v>1.85</v>
+      </c>
+      <c r="AK198">
+        <v>1.22</v>
+      </c>
+      <c r="AL198">
+        <v>1.3</v>
+      </c>
+      <c r="AM198">
+        <v>1.91</v>
+      </c>
+      <c r="AN198">
+        <v>1.58</v>
+      </c>
+      <c r="AO198">
+        <v>0.8</v>
+      </c>
+      <c r="AP198">
+        <v>1.54</v>
+      </c>
+      <c r="AQ198">
+        <v>0.82</v>
+      </c>
+      <c r="AR198">
+        <v>1.45</v>
+      </c>
+      <c r="AS198">
+        <v>1.43</v>
+      </c>
+      <c r="AT198">
+        <v>2.88</v>
+      </c>
+      <c r="AU198">
+        <v>9</v>
+      </c>
+      <c r="AV198">
+        <v>3</v>
+      </c>
+      <c r="AW198">
+        <v>6</v>
+      </c>
+      <c r="AX198">
+        <v>2</v>
+      </c>
+      <c r="AY198">
+        <v>15</v>
+      </c>
+      <c r="AZ198">
+        <v>5</v>
+      </c>
+      <c r="BA198">
+        <v>11</v>
+      </c>
+      <c r="BB198">
+        <v>3</v>
+      </c>
+      <c r="BC198">
+        <v>14</v>
+      </c>
+      <c r="BD198">
+        <v>1.47</v>
+      </c>
+      <c r="BE198">
+        <v>6.75</v>
+      </c>
+      <c r="BF198">
+        <v>3.05</v>
+      </c>
+      <c r="BG198">
+        <v>1.43</v>
+      </c>
+      <c r="BH198">
+        <v>2.63</v>
+      </c>
+      <c r="BI198">
+        <v>1.71</v>
+      </c>
+      <c r="BJ198">
+        <v>2</v>
+      </c>
+      <c r="BK198">
+        <v>2.15</v>
+      </c>
+      <c r="BL198">
+        <v>1.61</v>
+      </c>
+      <c r="BM198">
+        <v>2.75</v>
+      </c>
+      <c r="BN198">
+        <v>1.38</v>
+      </c>
+      <c r="BO198">
+        <v>3.65</v>
+      </c>
+      <c r="BP198">
+        <v>1.23</v>
+      </c>
+    </row>
+    <row r="199" spans="1:68">
+      <c r="A199" s="1">
+        <v>198</v>
+      </c>
+      <c r="B199">
+        <v>7468283</v>
+      </c>
+      <c r="C199" t="s">
+        <v>68</v>
+      </c>
+      <c r="D199" t="s">
+        <v>69</v>
+      </c>
+      <c r="E199" s="2">
+        <v>45725.60416666666</v>
+      </c>
+      <c r="F199">
+        <v>25</v>
+      </c>
+      <c r="G199" t="s">
+        <v>79</v>
+      </c>
+      <c r="H199" t="s">
+        <v>84</v>
+      </c>
+      <c r="I199">
+        <v>0</v>
+      </c>
+      <c r="J199">
+        <v>0</v>
+      </c>
+      <c r="K199">
+        <v>0</v>
+      </c>
+      <c r="L199">
+        <v>0</v>
+      </c>
+      <c r="M199">
+        <v>0</v>
+      </c>
+      <c r="N199">
+        <v>0</v>
+      </c>
+      <c r="O199" t="s">
+        <v>88</v>
+      </c>
+      <c r="P199" t="s">
+        <v>88</v>
+      </c>
+      <c r="Q199">
+        <v>7</v>
+      </c>
+      <c r="R199">
+        <v>2.4</v>
+      </c>
+      <c r="S199">
+        <v>1.85</v>
+      </c>
+      <c r="T199">
+        <v>1.3</v>
+      </c>
+      <c r="U199">
+        <v>3.25</v>
+      </c>
+      <c r="V199">
+        <v>2.5</v>
+      </c>
+      <c r="W199">
+        <v>1.5</v>
+      </c>
+      <c r="X199">
+        <v>6</v>
+      </c>
+      <c r="Y199">
+        <v>1.11</v>
+      </c>
+      <c r="Z199">
+        <v>8.699999999999999</v>
+      </c>
+      <c r="AA199">
+        <v>5.05</v>
+      </c>
+      <c r="AB199">
+        <v>1.32</v>
+      </c>
+      <c r="AC199">
+        <v>1.01</v>
+      </c>
+      <c r="AD199">
+        <v>13</v>
+      </c>
+      <c r="AE199">
+        <v>1.18</v>
+      </c>
+      <c r="AF199">
+        <v>3.94</v>
+      </c>
+      <c r="AG199">
+        <v>1.68</v>
+      </c>
+      <c r="AH199">
+        <v>2.14</v>
+      </c>
+      <c r="AI199">
+        <v>2</v>
+      </c>
+      <c r="AJ199">
+        <v>1.75</v>
+      </c>
+      <c r="AK199">
+        <v>2.8</v>
+      </c>
+      <c r="AL199">
+        <v>1.2</v>
+      </c>
+      <c r="AM199">
+        <v>1.1</v>
+      </c>
+      <c r="AN199">
+        <v>0.82</v>
+      </c>
+      <c r="AO199">
+        <v>1.92</v>
+      </c>
+      <c r="AP199">
+        <v>0.83</v>
+      </c>
+      <c r="AQ199">
+        <v>1.85</v>
+      </c>
+      <c r="AR199">
+        <v>1.23</v>
+      </c>
+      <c r="AS199">
+        <v>1.4</v>
+      </c>
+      <c r="AT199">
+        <v>2.63</v>
+      </c>
+      <c r="AU199">
+        <v>6</v>
+      </c>
+      <c r="AV199">
+        <v>5</v>
+      </c>
+      <c r="AW199">
+        <v>2</v>
+      </c>
+      <c r="AX199">
+        <v>9</v>
+      </c>
+      <c r="AY199">
+        <v>8</v>
+      </c>
+      <c r="AZ199">
+        <v>14</v>
+      </c>
+      <c r="BA199">
+        <v>6</v>
+      </c>
+      <c r="BB199">
+        <v>13</v>
+      </c>
+      <c r="BC199">
+        <v>19</v>
+      </c>
+      <c r="BD199">
+        <v>3.65</v>
+      </c>
+      <c r="BE199">
+        <v>7.5</v>
+      </c>
+      <c r="BF199">
+        <v>1.32</v>
+      </c>
+      <c r="BG199">
+        <v>1.28</v>
+      </c>
+      <c r="BH199">
+        <v>3.3</v>
+      </c>
+      <c r="BI199">
+        <v>1.48</v>
+      </c>
+      <c r="BJ199">
+        <v>2.48</v>
+      </c>
+      <c r="BK199">
+        <v>1.76</v>
+      </c>
+      <c r="BL199">
+        <v>1.94</v>
+      </c>
+      <c r="BM199">
+        <v>2.18</v>
+      </c>
+      <c r="BN199">
+        <v>1.58</v>
+      </c>
+      <c r="BO199">
+        <v>2.75</v>
+      </c>
+      <c r="BP199">
+        <v>1.38</v>
       </c>
     </row>
   </sheetData>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Czech Republic First League_20242025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Czech Republic First League_20242025.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1256" uniqueCount="306">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1262" uniqueCount="306">
   <si>
     <t>Id_Jogo</t>
   </si>
@@ -1293,7 +1293,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:BP199"/>
+  <dimension ref="A1:BP200"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:68">
@@ -3690,7 +3690,7 @@
         <v>0.83</v>
       </c>
       <c r="AQ12">
-        <v>0.82</v>
+        <v>0.83</v>
       </c>
       <c r="AR12">
         <v>0</v>
@@ -7810,7 +7810,7 @@
         <v>2.42</v>
       </c>
       <c r="AQ32">
-        <v>0.82</v>
+        <v>0.83</v>
       </c>
       <c r="AR32">
         <v>1.64</v>
@@ -9870,7 +9870,7 @@
         <v>1.33</v>
       </c>
       <c r="AQ42">
-        <v>0.82</v>
+        <v>0.83</v>
       </c>
       <c r="AR42">
         <v>1.41</v>
@@ -15432,7 +15432,7 @@
         <v>1.5</v>
       </c>
       <c r="AQ69">
-        <v>0.82</v>
+        <v>0.83</v>
       </c>
       <c r="AR69">
         <v>1.16</v>
@@ -20788,7 +20788,7 @@
         <v>1.58</v>
       </c>
       <c r="AQ95">
-        <v>0.82</v>
+        <v>0.83</v>
       </c>
       <c r="AR95">
         <v>1.43</v>
@@ -24290,7 +24290,7 @@
         <v>3</v>
       </c>
       <c r="AQ112">
-        <v>0.82</v>
+        <v>0.83</v>
       </c>
       <c r="AR112">
         <v>2.21</v>
@@ -26762,7 +26762,7 @@
         <v>2.5</v>
       </c>
       <c r="AQ124">
-        <v>0.82</v>
+        <v>0.83</v>
       </c>
       <c r="AR124">
         <v>1.87</v>
@@ -27998,7 +27998,7 @@
         <v>2.23</v>
       </c>
       <c r="AQ130">
-        <v>0.82</v>
+        <v>0.83</v>
       </c>
       <c r="AR130">
         <v>1.93</v>
@@ -31706,7 +31706,7 @@
         <v>1.08</v>
       </c>
       <c r="AQ148">
-        <v>0.82</v>
+        <v>0.83</v>
       </c>
       <c r="AR148">
         <v>1.47</v>
@@ -38710,7 +38710,7 @@
         <v>2</v>
       </c>
       <c r="AQ182">
-        <v>0.82</v>
+        <v>0.83</v>
       </c>
       <c r="AR182">
         <v>1.67</v>
@@ -42006,7 +42006,7 @@
         <v>1.54</v>
       </c>
       <c r="AQ198">
-        <v>0.82</v>
+        <v>0.83</v>
       </c>
       <c r="AR198">
         <v>1.45</v>
@@ -42288,6 +42288,212 @@
       </c>
       <c r="BP199">
         <v>1.38</v>
+      </c>
+    </row>
+    <row r="200" spans="1:68">
+      <c r="A200" s="1">
+        <v>199</v>
+      </c>
+      <c r="B200">
+        <v>7468246</v>
+      </c>
+      <c r="C200" t="s">
+        <v>68</v>
+      </c>
+      <c r="D200" t="s">
+        <v>69</v>
+      </c>
+      <c r="E200" s="2">
+        <v>45728.58333333334</v>
+      </c>
+      <c r="F200">
+        <v>21</v>
+      </c>
+      <c r="G200" t="s">
+        <v>74</v>
+      </c>
+      <c r="H200" t="s">
+        <v>75</v>
+      </c>
+      <c r="I200">
+        <v>0</v>
+      </c>
+      <c r="J200">
+        <v>0</v>
+      </c>
+      <c r="K200">
+        <v>0</v>
+      </c>
+      <c r="L200">
+        <v>0</v>
+      </c>
+      <c r="M200">
+        <v>0</v>
+      </c>
+      <c r="N200">
+        <v>0</v>
+      </c>
+      <c r="O200" t="s">
+        <v>88</v>
+      </c>
+      <c r="P200" t="s">
+        <v>88</v>
+      </c>
+      <c r="Q200">
+        <v>3.3</v>
+      </c>
+      <c r="R200">
+        <v>2.23</v>
+      </c>
+      <c r="S200">
+        <v>3.05</v>
+      </c>
+      <c r="T200">
+        <v>1.36</v>
+      </c>
+      <c r="U200">
+        <v>2.9</v>
+      </c>
+      <c r="V200">
+        <v>2.55</v>
+      </c>
+      <c r="W200">
+        <v>1.45</v>
+      </c>
+      <c r="X200">
+        <v>5.95</v>
+      </c>
+      <c r="Y200">
+        <v>1.1</v>
+      </c>
+      <c r="Z200">
+        <v>2.65</v>
+      </c>
+      <c r="AA200">
+        <v>3.25</v>
+      </c>
+      <c r="AB200">
+        <v>2.4</v>
+      </c>
+      <c r="AC200">
+        <v>1.02</v>
+      </c>
+      <c r="AD200">
+        <v>10</v>
+      </c>
+      <c r="AE200">
+        <v>1.25</v>
+      </c>
+      <c r="AF200">
+        <v>3.6</v>
+      </c>
+      <c r="AG200">
+        <v>1.78</v>
+      </c>
+      <c r="AH200">
+        <v>1.97</v>
+      </c>
+      <c r="AI200">
+        <v>1.63</v>
+      </c>
+      <c r="AJ200">
+        <v>2.15</v>
+      </c>
+      <c r="AK200">
+        <v>1.52</v>
+      </c>
+      <c r="AL200">
+        <v>1.28</v>
+      </c>
+      <c r="AM200">
+        <v>1.44</v>
+      </c>
+      <c r="AN200">
+        <v>0.92</v>
+      </c>
+      <c r="AO200">
+        <v>0.82</v>
+      </c>
+      <c r="AP200">
+        <v>0.92</v>
+      </c>
+      <c r="AQ200">
+        <v>0.83</v>
+      </c>
+      <c r="AR200">
+        <v>1.2</v>
+      </c>
+      <c r="AS200">
+        <v>1.37</v>
+      </c>
+      <c r="AT200">
+        <v>2.57</v>
+      </c>
+      <c r="AU200">
+        <v>6</v>
+      </c>
+      <c r="AV200">
+        <v>3</v>
+      </c>
+      <c r="AW200">
+        <v>11</v>
+      </c>
+      <c r="AX200">
+        <v>5</v>
+      </c>
+      <c r="AY200">
+        <v>17</v>
+      </c>
+      <c r="AZ200">
+        <v>8</v>
+      </c>
+      <c r="BA200">
+        <v>4</v>
+      </c>
+      <c r="BB200">
+        <v>2</v>
+      </c>
+      <c r="BC200">
+        <v>6</v>
+      </c>
+      <c r="BD200">
+        <v>2.07</v>
+      </c>
+      <c r="BE200">
+        <v>6.75</v>
+      </c>
+      <c r="BF200">
+        <v>1.92</v>
+      </c>
+      <c r="BG200">
+        <v>1.25</v>
+      </c>
+      <c r="BH200">
+        <v>3.45</v>
+      </c>
+      <c r="BI200">
+        <v>1.44</v>
+      </c>
+      <c r="BJ200">
+        <v>2.55</v>
+      </c>
+      <c r="BK200">
+        <v>1.71</v>
+      </c>
+      <c r="BL200">
+        <v>2</v>
+      </c>
+      <c r="BM200">
+        <v>2.08</v>
+      </c>
+      <c r="BN200">
+        <v>1.66</v>
+      </c>
+      <c r="BO200">
+        <v>2.65</v>
+      </c>
+      <c r="BP200">
+        <v>1.41</v>
       </c>
     </row>
   </sheetData>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Czech Republic First League_20242025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Czech Republic First League_20242025.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1262" uniqueCount="306">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1286" uniqueCount="308">
   <si>
     <t>Id_Jogo</t>
   </si>
@@ -664,6 +664,12 @@
     <t>['31', '35']</t>
   </si>
   <si>
+    <t>['89']</t>
+  </si>
+  <si>
+    <t>['49']</t>
+  </si>
+  <si>
     <t>['25']</t>
   </si>
   <si>
@@ -731,9 +737,6 @@
   </si>
   <si>
     <t>['26', '85']</t>
-  </si>
-  <si>
-    <t>['89']</t>
   </si>
   <si>
     <t>['23', '42']</t>
@@ -932,6 +935,9 @@
   </si>
   <si>
     <t>['13', '80']</t>
+  </si>
+  <si>
+    <t>['13', '18']</t>
   </si>
 </sst>
 </file>
@@ -1293,7 +1299,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:BP200"/>
+  <dimension ref="A1:BP204"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:68">
@@ -1549,7 +1555,7 @@
         <v>86</v>
       </c>
       <c r="P2" t="s">
-        <v>216</v>
+        <v>218</v>
       </c>
       <c r="Q2">
         <v>1.53</v>
@@ -1961,7 +1967,7 @@
         <v>88</v>
       </c>
       <c r="P4" t="s">
-        <v>217</v>
+        <v>219</v>
       </c>
       <c r="Q4">
         <v>2.88</v>
@@ -2373,7 +2379,7 @@
         <v>90</v>
       </c>
       <c r="P6" t="s">
-        <v>218</v>
+        <v>220</v>
       </c>
       <c r="Q6">
         <v>5.5</v>
@@ -2579,7 +2585,7 @@
         <v>91</v>
       </c>
       <c r="P7" t="s">
-        <v>219</v>
+        <v>221</v>
       </c>
       <c r="Q7">
         <v>3.2</v>
@@ -3278,7 +3284,7 @@
         <v>0.92</v>
       </c>
       <c r="AQ10">
-        <v>1.33</v>
+        <v>1.46</v>
       </c>
       <c r="AR10">
         <v>0.98</v>
@@ -3403,7 +3409,7 @@
         <v>94</v>
       </c>
       <c r="P11" t="s">
-        <v>220</v>
+        <v>222</v>
       </c>
       <c r="Q11">
         <v>6.5</v>
@@ -3481,10 +3487,10 @@
         <v>0</v>
       </c>
       <c r="AP11">
-        <v>1.33</v>
+        <v>1.46</v>
       </c>
       <c r="AQ11">
-        <v>2.17</v>
+        <v>2</v>
       </c>
       <c r="AR11">
         <v>0</v>
@@ -3609,7 +3615,7 @@
         <v>88</v>
       </c>
       <c r="P12" t="s">
-        <v>221</v>
+        <v>223</v>
       </c>
       <c r="Q12">
         <v>2.85</v>
@@ -3687,7 +3693,7 @@
         <v>0</v>
       </c>
       <c r="AP12">
-        <v>0.83</v>
+        <v>0.77</v>
       </c>
       <c r="AQ12">
         <v>0.83</v>
@@ -4021,7 +4027,7 @@
         <v>96</v>
       </c>
       <c r="P14" t="s">
-        <v>222</v>
+        <v>224</v>
       </c>
       <c r="Q14">
         <v>2.45</v>
@@ -4099,7 +4105,7 @@
         <v>3</v>
       </c>
       <c r="AP14">
-        <v>1.42</v>
+        <v>1.54</v>
       </c>
       <c r="AQ14">
         <v>1.38</v>
@@ -4305,10 +4311,10 @@
         <v>0</v>
       </c>
       <c r="AP15">
-        <v>1.58</v>
+        <v>1.46</v>
       </c>
       <c r="AQ15">
-        <v>0.92</v>
+        <v>0.85</v>
       </c>
       <c r="AR15">
         <v>0</v>
@@ -4845,7 +4851,7 @@
         <v>88</v>
       </c>
       <c r="P18" t="s">
-        <v>223</v>
+        <v>225</v>
       </c>
       <c r="Q18">
         <v>5.4</v>
@@ -4923,7 +4929,7 @@
         <v>1</v>
       </c>
       <c r="AP18">
-        <v>1.42</v>
+        <v>1.54</v>
       </c>
       <c r="AQ18">
         <v>2.23</v>
@@ -5132,7 +5138,7 @@
         <v>2.23</v>
       </c>
       <c r="AQ19">
-        <v>0.42</v>
+        <v>0.62</v>
       </c>
       <c r="AR19">
         <v>1.9</v>
@@ -5338,7 +5344,7 @@
         <v>1.5</v>
       </c>
       <c r="AQ20">
-        <v>1.33</v>
+        <v>1.46</v>
       </c>
       <c r="AR20">
         <v>1</v>
@@ -5875,7 +5881,7 @@
         <v>102</v>
       </c>
       <c r="P23" t="s">
-        <v>224</v>
+        <v>226</v>
       </c>
       <c r="Q23">
         <v>2.6</v>
@@ -6081,7 +6087,7 @@
         <v>103</v>
       </c>
       <c r="P24" t="s">
-        <v>225</v>
+        <v>227</v>
       </c>
       <c r="Q24">
         <v>2.75</v>
@@ -6287,7 +6293,7 @@
         <v>88</v>
       </c>
       <c r="P25" t="s">
-        <v>226</v>
+        <v>228</v>
       </c>
       <c r="Q25">
         <v>1.06</v>
@@ -6493,7 +6499,7 @@
         <v>104</v>
       </c>
       <c r="P26" t="s">
-        <v>227</v>
+        <v>229</v>
       </c>
       <c r="Q26">
         <v>6.23</v>
@@ -6574,7 +6580,7 @@
         <v>1.08</v>
       </c>
       <c r="AQ26">
-        <v>2.17</v>
+        <v>2</v>
       </c>
       <c r="AR26">
         <v>1.73</v>
@@ -6777,7 +6783,7 @@
         <v>3</v>
       </c>
       <c r="AP27">
-        <v>1.33</v>
+        <v>1.46</v>
       </c>
       <c r="AQ27">
         <v>1</v>
@@ -7189,10 +7195,10 @@
         <v>0</v>
       </c>
       <c r="AP29">
-        <v>0.83</v>
+        <v>0.77</v>
       </c>
       <c r="AQ29">
-        <v>0.92</v>
+        <v>0.85</v>
       </c>
       <c r="AR29">
         <v>1.22</v>
@@ -7601,7 +7607,7 @@
         <v>0</v>
       </c>
       <c r="AP31">
-        <v>1.58</v>
+        <v>1.46</v>
       </c>
       <c r="AQ31">
         <v>0.08</v>
@@ -8016,7 +8022,7 @@
         <v>1.54</v>
       </c>
       <c r="AQ33">
-        <v>0.42</v>
+        <v>0.62</v>
       </c>
       <c r="AR33">
         <v>1.08</v>
@@ -8141,7 +8147,7 @@
         <v>111</v>
       </c>
       <c r="P34" t="s">
-        <v>228</v>
+        <v>230</v>
       </c>
       <c r="Q34">
         <v>1.45</v>
@@ -8347,7 +8353,7 @@
         <v>112</v>
       </c>
       <c r="P35" t="s">
-        <v>229</v>
+        <v>231</v>
       </c>
       <c r="Q35">
         <v>2.84</v>
@@ -8428,7 +8434,7 @@
         <v>1.46</v>
       </c>
       <c r="AQ35">
-        <v>1.33</v>
+        <v>1.46</v>
       </c>
       <c r="AR35">
         <v>1.93</v>
@@ -8553,7 +8559,7 @@
         <v>113</v>
       </c>
       <c r="P36" t="s">
-        <v>230</v>
+        <v>232</v>
       </c>
       <c r="Q36">
         <v>5.63</v>
@@ -8634,7 +8640,7 @@
         <v>2</v>
       </c>
       <c r="AQ36">
-        <v>2.17</v>
+        <v>2</v>
       </c>
       <c r="AR36">
         <v>1.54</v>
@@ -8759,7 +8765,7 @@
         <v>114</v>
       </c>
       <c r="P37" t="s">
-        <v>231</v>
+        <v>233</v>
       </c>
       <c r="Q37">
         <v>2.58</v>
@@ -9043,7 +9049,7 @@
         <v>1.5</v>
       </c>
       <c r="AP38">
-        <v>1.42</v>
+        <v>1.54</v>
       </c>
       <c r="AQ38">
         <v>0.46</v>
@@ -9171,7 +9177,7 @@
         <v>88</v>
       </c>
       <c r="P39" t="s">
-        <v>232</v>
+        <v>234</v>
       </c>
       <c r="Q39">
         <v>4.75</v>
@@ -9583,7 +9589,7 @@
         <v>117</v>
       </c>
       <c r="P41" t="s">
-        <v>233</v>
+        <v>235</v>
       </c>
       <c r="Q41">
         <v>2.4</v>
@@ -9789,7 +9795,7 @@
         <v>107</v>
       </c>
       <c r="P42" t="s">
-        <v>234</v>
+        <v>236</v>
       </c>
       <c r="Q42">
         <v>2.61</v>
@@ -9867,7 +9873,7 @@
         <v>1.5</v>
       </c>
       <c r="AP42">
-        <v>1.33</v>
+        <v>1.46</v>
       </c>
       <c r="AQ42">
         <v>0.83</v>
@@ -9995,7 +10001,7 @@
         <v>118</v>
       </c>
       <c r="P43" t="s">
-        <v>235</v>
+        <v>237</v>
       </c>
       <c r="Q43">
         <v>1.69</v>
@@ -10076,7 +10082,7 @@
         <v>2.23</v>
       </c>
       <c r="AQ43">
-        <v>0.92</v>
+        <v>0.85</v>
       </c>
       <c r="AR43">
         <v>2.07</v>
@@ -10279,7 +10285,7 @@
         <v>0</v>
       </c>
       <c r="AP44">
-        <v>0.83</v>
+        <v>0.77</v>
       </c>
       <c r="AQ44">
         <v>1</v>
@@ -11106,7 +11112,7 @@
         <v>0.23</v>
       </c>
       <c r="AQ48">
-        <v>1.33</v>
+        <v>1.46</v>
       </c>
       <c r="AR48">
         <v>1.34</v>
@@ -11437,7 +11443,7 @@
         <v>88</v>
       </c>
       <c r="P50" t="s">
-        <v>236</v>
+        <v>238</v>
       </c>
       <c r="Q50">
         <v>5.1</v>
@@ -11518,7 +11524,7 @@
         <v>1.54</v>
       </c>
       <c r="AQ50">
-        <v>2.17</v>
+        <v>2</v>
       </c>
       <c r="AR50">
         <v>1.24</v>
@@ -11724,7 +11730,7 @@
         <v>1.46</v>
       </c>
       <c r="AQ51">
-        <v>0.42</v>
+        <v>0.62</v>
       </c>
       <c r="AR51">
         <v>1.76</v>
@@ -11849,7 +11855,7 @@
         <v>122</v>
       </c>
       <c r="P52" t="s">
-        <v>237</v>
+        <v>239</v>
       </c>
       <c r="Q52">
         <v>3</v>
@@ -12261,7 +12267,7 @@
         <v>124</v>
       </c>
       <c r="P54" t="s">
-        <v>238</v>
+        <v>240</v>
       </c>
       <c r="Q54">
         <v>3</v>
@@ -12339,7 +12345,7 @@
         <v>0</v>
       </c>
       <c r="AP54">
-        <v>1.33</v>
+        <v>1.46</v>
       </c>
       <c r="AQ54">
         <v>1.15</v>
@@ -12545,7 +12551,7 @@
         <v>2.33</v>
       </c>
       <c r="AP55">
-        <v>1.42</v>
+        <v>1.54</v>
       </c>
       <c r="AQ55">
         <v>1.85</v>
@@ -12673,7 +12679,7 @@
         <v>125</v>
       </c>
       <c r="P56" t="s">
-        <v>239</v>
+        <v>216</v>
       </c>
       <c r="Q56">
         <v>1.85</v>
@@ -12879,7 +12885,7 @@
         <v>88</v>
       </c>
       <c r="P57" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="Q57">
         <v>5.88</v>
@@ -12957,7 +12963,7 @@
         <v>2</v>
       </c>
       <c r="AP57">
-        <v>1.58</v>
+        <v>1.46</v>
       </c>
       <c r="AQ57">
         <v>2.23</v>
@@ -13166,7 +13172,7 @@
         <v>1.54</v>
       </c>
       <c r="AQ58">
-        <v>0.92</v>
+        <v>0.85</v>
       </c>
       <c r="AR58">
         <v>1.32</v>
@@ -13291,7 +13297,7 @@
         <v>127</v>
       </c>
       <c r="P59" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="Q59">
         <v>3.86</v>
@@ -13369,7 +13375,7 @@
         <v>0.5</v>
       </c>
       <c r="AP59">
-        <v>1.33</v>
+        <v>1.46</v>
       </c>
       <c r="AQ59">
         <v>1.62</v>
@@ -13909,7 +13915,7 @@
         <v>130</v>
       </c>
       <c r="P62" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="Q62">
         <v>1.83</v>
@@ -13987,7 +13993,7 @@
         <v>0.75</v>
       </c>
       <c r="AP62">
-        <v>1.58</v>
+        <v>1.46</v>
       </c>
       <c r="AQ62">
         <v>0.46</v>
@@ -14115,7 +14121,7 @@
         <v>88</v>
       </c>
       <c r="P63" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="Q63">
         <v>8.77</v>
@@ -14196,7 +14202,7 @@
         <v>0.23</v>
       </c>
       <c r="AQ63">
-        <v>2.17</v>
+        <v>2</v>
       </c>
       <c r="AR63">
         <v>1.37</v>
@@ -14402,7 +14408,7 @@
         <v>1.67</v>
       </c>
       <c r="AQ64">
-        <v>0.42</v>
+        <v>0.62</v>
       </c>
       <c r="AR64">
         <v>1.75</v>
@@ -14527,7 +14533,7 @@
         <v>132</v>
       </c>
       <c r="P65" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="Q65">
         <v>2.4</v>
@@ -14605,10 +14611,10 @@
         <v>1.25</v>
       </c>
       <c r="AP65">
-        <v>1.42</v>
+        <v>1.54</v>
       </c>
       <c r="AQ65">
-        <v>1.33</v>
+        <v>1.46</v>
       </c>
       <c r="AR65">
         <v>1.42</v>
@@ -14733,7 +14739,7 @@
         <v>133</v>
       </c>
       <c r="P66" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="Q66">
         <v>1.55</v>
@@ -14939,7 +14945,7 @@
         <v>134</v>
       </c>
       <c r="P67" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="Q67">
         <v>4</v>
@@ -15145,7 +15151,7 @@
         <v>88</v>
       </c>
       <c r="P68" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="Q68">
         <v>3.1</v>
@@ -15223,7 +15229,7 @@
         <v>0</v>
       </c>
       <c r="AP68">
-        <v>0.83</v>
+        <v>0.77</v>
       </c>
       <c r="AQ68">
         <v>0.77</v>
@@ -15969,7 +15975,7 @@
         <v>124</v>
       </c>
       <c r="P72" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="Q72">
         <v>1.88</v>
@@ -16175,7 +16181,7 @@
         <v>88</v>
       </c>
       <c r="P73" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="Q73">
         <v>7</v>
@@ -16587,7 +16593,7 @@
         <v>138</v>
       </c>
       <c r="P75" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="Q75">
         <v>2.3</v>
@@ -16665,10 +16671,10 @@
         <v>0.25</v>
       </c>
       <c r="AP75">
-        <v>1.33</v>
+        <v>1.46</v>
       </c>
       <c r="AQ75">
-        <v>0.42</v>
+        <v>0.62</v>
       </c>
       <c r="AR75">
         <v>1.49</v>
@@ -16793,7 +16799,7 @@
         <v>88</v>
       </c>
       <c r="P76" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="Q76">
         <v>3.7</v>
@@ -16874,7 +16880,7 @@
         <v>0.23</v>
       </c>
       <c r="AQ76">
-        <v>0.92</v>
+        <v>0.85</v>
       </c>
       <c r="AR76">
         <v>1.29</v>
@@ -16999,7 +17005,7 @@
         <v>88</v>
       </c>
       <c r="P77" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="Q77">
         <v>2.47</v>
@@ -17077,7 +17083,7 @@
         <v>1.4</v>
       </c>
       <c r="AP77">
-        <v>1.42</v>
+        <v>1.54</v>
       </c>
       <c r="AQ77">
         <v>1.25</v>
@@ -17489,7 +17495,7 @@
         <v>1</v>
       </c>
       <c r="AP79">
-        <v>1.58</v>
+        <v>1.46</v>
       </c>
       <c r="AQ79">
         <v>1.62</v>
@@ -17617,7 +17623,7 @@
         <v>140</v>
       </c>
       <c r="P80" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="Q80">
         <v>2.5</v>
@@ -17698,7 +17704,7 @@
         <v>1.67</v>
       </c>
       <c r="AQ80">
-        <v>1.33</v>
+        <v>1.46</v>
       </c>
       <c r="AR80">
         <v>1.66</v>
@@ -17823,7 +17829,7 @@
         <v>141</v>
       </c>
       <c r="P81" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="Q81">
         <v>2.38</v>
@@ -17904,7 +17910,7 @@
         <v>3</v>
       </c>
       <c r="AQ81">
-        <v>2.17</v>
+        <v>2</v>
       </c>
       <c r="AR81">
         <v>2.43</v>
@@ -18029,7 +18035,7 @@
         <v>142</v>
       </c>
       <c r="P82" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="Q82">
         <v>2.8</v>
@@ -18235,7 +18241,7 @@
         <v>143</v>
       </c>
       <c r="P83" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="Q83">
         <v>2.6</v>
@@ -18441,7 +18447,7 @@
         <v>144</v>
       </c>
       <c r="P84" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="Q84">
         <v>3.4</v>
@@ -18853,7 +18859,7 @@
         <v>146</v>
       </c>
       <c r="P86" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="Q86">
         <v>2.88</v>
@@ -19265,7 +19271,7 @@
         <v>88</v>
       </c>
       <c r="P88" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="Q88">
         <v>2.6</v>
@@ -19471,7 +19477,7 @@
         <v>93</v>
       </c>
       <c r="P89" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="Q89">
         <v>6.5</v>
@@ -19755,10 +19761,10 @@
         <v>1.4</v>
       </c>
       <c r="AP90">
-        <v>1.42</v>
+        <v>1.54</v>
       </c>
       <c r="AQ90">
-        <v>0.92</v>
+        <v>0.85</v>
       </c>
       <c r="AR90">
         <v>1.39</v>
@@ -19883,7 +19889,7 @@
         <v>149</v>
       </c>
       <c r="P91" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="Q91">
         <v>4.7</v>
@@ -19961,7 +19967,7 @@
         <v>1</v>
       </c>
       <c r="AP91">
-        <v>0.83</v>
+        <v>0.77</v>
       </c>
       <c r="AQ91">
         <v>1.62</v>
@@ -20089,7 +20095,7 @@
         <v>88</v>
       </c>
       <c r="P92" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="Q92">
         <v>3.8</v>
@@ -20501,7 +20507,7 @@
         <v>150</v>
       </c>
       <c r="P94" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="Q94">
         <v>3</v>
@@ -20579,10 +20585,10 @@
         <v>1.5</v>
       </c>
       <c r="AP94">
-        <v>1.33</v>
+        <v>1.46</v>
       </c>
       <c r="AQ94">
-        <v>1.33</v>
+        <v>1.46</v>
       </c>
       <c r="AR94">
         <v>1.52</v>
@@ -20785,7 +20791,7 @@
         <v>1.5</v>
       </c>
       <c r="AP95">
-        <v>1.58</v>
+        <v>1.46</v>
       </c>
       <c r="AQ95">
         <v>0.83</v>
@@ -20994,7 +21000,7 @@
         <v>3</v>
       </c>
       <c r="AQ96">
-        <v>0.42</v>
+        <v>0.62</v>
       </c>
       <c r="AR96">
         <v>2.31</v>
@@ -21200,7 +21206,7 @@
         <v>2.42</v>
       </c>
       <c r="AQ97">
-        <v>2.17</v>
+        <v>2</v>
       </c>
       <c r="AR97">
         <v>1.81</v>
@@ -21943,7 +21949,7 @@
         <v>156</v>
       </c>
       <c r="P101" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="Q101">
         <v>1.83</v>
@@ -23054,7 +23060,7 @@
         <v>2.5</v>
       </c>
       <c r="AQ106">
-        <v>0.42</v>
+        <v>0.62</v>
       </c>
       <c r="AR106">
         <v>1.87</v>
@@ -23257,7 +23263,7 @@
         <v>1.57</v>
       </c>
       <c r="AP107">
-        <v>0.83</v>
+        <v>0.77</v>
       </c>
       <c r="AQ107">
         <v>1.25</v>
@@ -23463,7 +23469,7 @@
         <v>0.67</v>
       </c>
       <c r="AP108">
-        <v>1.42</v>
+        <v>1.54</v>
       </c>
       <c r="AQ108">
         <v>1</v>
@@ -23591,7 +23597,7 @@
         <v>161</v>
       </c>
       <c r="P109" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="Q109">
         <v>2.24</v>
@@ -23669,7 +23675,7 @@
         <v>0</v>
       </c>
       <c r="AP109">
-        <v>1.33</v>
+        <v>1.46</v>
       </c>
       <c r="AQ109">
         <v>0.08</v>
@@ -23797,7 +23803,7 @@
         <v>162</v>
       </c>
       <c r="P110" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="Q110">
         <v>4.6</v>
@@ -23875,10 +23881,10 @@
         <v>2.14</v>
       </c>
       <c r="AP110">
-        <v>1.58</v>
+        <v>1.46</v>
       </c>
       <c r="AQ110">
-        <v>2.17</v>
+        <v>2</v>
       </c>
       <c r="AR110">
         <v>1.51</v>
@@ -24084,7 +24090,7 @@
         <v>2.42</v>
       </c>
       <c r="AQ111">
-        <v>1.33</v>
+        <v>1.46</v>
       </c>
       <c r="AR111">
         <v>1.73</v>
@@ -24209,7 +24215,7 @@
         <v>164</v>
       </c>
       <c r="P112" t="s">
-        <v>222</v>
+        <v>224</v>
       </c>
       <c r="Q112">
         <v>1.44</v>
@@ -24415,7 +24421,7 @@
         <v>165</v>
       </c>
       <c r="P113" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="Q113">
         <v>3.25</v>
@@ -24621,7 +24627,7 @@
         <v>151</v>
       </c>
       <c r="P114" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="Q114">
         <v>2.88</v>
@@ -24827,7 +24833,7 @@
         <v>99</v>
       </c>
       <c r="P115" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="Q115">
         <v>1.73</v>
@@ -25033,7 +25039,7 @@
         <v>88</v>
       </c>
       <c r="P116" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="Q116">
         <v>4.33</v>
@@ -25320,7 +25326,7 @@
         <v>1.08</v>
       </c>
       <c r="AQ117">
-        <v>0.42</v>
+        <v>0.62</v>
       </c>
       <c r="AR117">
         <v>1.44</v>
@@ -25651,7 +25657,7 @@
         <v>88</v>
       </c>
       <c r="P119" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="Q119">
         <v>15</v>
@@ -25857,7 +25863,7 @@
         <v>168</v>
       </c>
       <c r="P120" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="Q120">
         <v>3</v>
@@ -26144,7 +26150,7 @@
         <v>1.67</v>
       </c>
       <c r="AQ121">
-        <v>0.92</v>
+        <v>0.85</v>
       </c>
       <c r="AR121">
         <v>1.57</v>
@@ -26269,7 +26275,7 @@
         <v>170</v>
       </c>
       <c r="P122" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="Q122">
         <v>3.25</v>
@@ -26350,7 +26356,7 @@
         <v>1.08</v>
       </c>
       <c r="AQ122">
-        <v>0.92</v>
+        <v>0.85</v>
       </c>
       <c r="AR122">
         <v>1.54</v>
@@ -26553,7 +26559,7 @@
         <v>1.14</v>
       </c>
       <c r="AP123">
-        <v>1.33</v>
+        <v>1.46</v>
       </c>
       <c r="AQ123">
         <v>1.38</v>
@@ -26681,7 +26687,7 @@
         <v>172</v>
       </c>
       <c r="P124" t="s">
-        <v>221</v>
+        <v>223</v>
       </c>
       <c r="Q124">
         <v>1.83</v>
@@ -26887,7 +26893,7 @@
         <v>171</v>
       </c>
       <c r="P125" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="Q125">
         <v>6.3</v>
@@ -26968,7 +26974,7 @@
         <v>0.92</v>
       </c>
       <c r="AQ125">
-        <v>2.17</v>
+        <v>2</v>
       </c>
       <c r="AR125">
         <v>1.21</v>
@@ -27377,7 +27383,7 @@
         <v>0.71</v>
       </c>
       <c r="AP127">
-        <v>1.58</v>
+        <v>1.46</v>
       </c>
       <c r="AQ127">
         <v>1</v>
@@ -27583,7 +27589,7 @@
         <v>0</v>
       </c>
       <c r="AP128">
-        <v>0.83</v>
+        <v>0.77</v>
       </c>
       <c r="AQ128">
         <v>0.08</v>
@@ -27711,7 +27717,7 @@
         <v>174</v>
       </c>
       <c r="P129" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="Q129">
         <v>2.1</v>
@@ -27917,7 +27923,7 @@
         <v>175</v>
       </c>
       <c r="P130" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="Q130">
         <v>1.5</v>
@@ -28123,7 +28129,7 @@
         <v>176</v>
       </c>
       <c r="P131" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="Q131">
         <v>3.5</v>
@@ -28201,7 +28207,7 @@
         <v>1</v>
       </c>
       <c r="AP131">
-        <v>0.83</v>
+        <v>0.77</v>
       </c>
       <c r="AQ131">
         <v>1.38</v>
@@ -28329,7 +28335,7 @@
         <v>177</v>
       </c>
       <c r="P132" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="Q132">
         <v>4.04</v>
@@ -28410,7 +28416,7 @@
         <v>0.92</v>
       </c>
       <c r="AQ132">
-        <v>0.92</v>
+        <v>0.85</v>
       </c>
       <c r="AR132">
         <v>1.24</v>
@@ -28741,7 +28747,7 @@
         <v>88</v>
       </c>
       <c r="P134" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="Q134">
         <v>2.75</v>
@@ -29025,7 +29031,7 @@
         <v>1.25</v>
       </c>
       <c r="AP135">
-        <v>1.58</v>
+        <v>1.46</v>
       </c>
       <c r="AQ135">
         <v>1</v>
@@ -29565,7 +29571,7 @@
         <v>91</v>
       </c>
       <c r="P138" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="Q138">
         <v>2.25</v>
@@ -29771,7 +29777,7 @@
         <v>179</v>
       </c>
       <c r="P139" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="Q139">
         <v>1.9</v>
@@ -29852,7 +29858,7 @@
         <v>2</v>
       </c>
       <c r="AQ139">
-        <v>0.42</v>
+        <v>0.62</v>
       </c>
       <c r="AR139">
         <v>1.71</v>
@@ -30058,7 +30064,7 @@
         <v>2.23</v>
       </c>
       <c r="AQ140">
-        <v>1.33</v>
+        <v>1.46</v>
       </c>
       <c r="AR140">
         <v>2.06</v>
@@ -30183,7 +30189,7 @@
         <v>88</v>
       </c>
       <c r="P141" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="Q141">
         <v>4</v>
@@ -30389,7 +30395,7 @@
         <v>117</v>
       </c>
       <c r="P142" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="Q142">
         <v>4</v>
@@ -30673,7 +30679,7 @@
         <v>1</v>
       </c>
       <c r="AP143">
-        <v>1.42</v>
+        <v>1.54</v>
       </c>
       <c r="AQ143">
         <v>0.77</v>
@@ -30801,7 +30807,7 @@
         <v>182</v>
       </c>
       <c r="P144" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="Q144">
         <v>6</v>
@@ -31007,7 +31013,7 @@
         <v>88</v>
       </c>
       <c r="P145" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="Q145">
         <v>3.5</v>
@@ -31213,7 +31219,7 @@
         <v>183</v>
       </c>
       <c r="P146" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="Q146">
         <v>4.33</v>
@@ -31419,7 +31425,7 @@
         <v>184</v>
       </c>
       <c r="P147" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="Q147">
         <v>3.8</v>
@@ -31497,7 +31503,7 @@
         <v>1.11</v>
       </c>
       <c r="AP147">
-        <v>0.83</v>
+        <v>0.77</v>
       </c>
       <c r="AQ147">
         <v>1</v>
@@ -31625,7 +31631,7 @@
         <v>185</v>
       </c>
       <c r="P148" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="Q148">
         <v>2.5</v>
@@ -31831,7 +31837,7 @@
         <v>186</v>
       </c>
       <c r="P149" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="Q149">
         <v>2.05</v>
@@ -31912,7 +31918,7 @@
         <v>2.5</v>
       </c>
       <c r="AQ149">
-        <v>0.92</v>
+        <v>0.85</v>
       </c>
       <c r="AR149">
         <v>1.91</v>
@@ -32037,7 +32043,7 @@
         <v>187</v>
       </c>
       <c r="P150" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="Q150">
         <v>1.95</v>
@@ -32243,7 +32249,7 @@
         <v>188</v>
       </c>
       <c r="P151" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="Q151">
         <v>2.48</v>
@@ -32321,7 +32327,7 @@
         <v>1</v>
       </c>
       <c r="AP151">
-        <v>1.58</v>
+        <v>1.46</v>
       </c>
       <c r="AQ151">
         <v>1.38</v>
@@ -32527,7 +32533,7 @@
         <v>2.56</v>
       </c>
       <c r="AP152">
-        <v>1.33</v>
+        <v>1.46</v>
       </c>
       <c r="AQ152">
         <v>2.23</v>
@@ -32655,7 +32661,7 @@
         <v>190</v>
       </c>
       <c r="P153" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="Q153">
         <v>1.4</v>
@@ -33067,7 +33073,7 @@
         <v>88</v>
       </c>
       <c r="P155" t="s">
-        <v>225</v>
+        <v>227</v>
       </c>
       <c r="Q155">
         <v>3.2</v>
@@ -33145,7 +33151,7 @@
         <v>1.5</v>
       </c>
       <c r="AP155">
-        <v>1.42</v>
+        <v>1.54</v>
       </c>
       <c r="AQ155">
         <v>1.62</v>
@@ -33354,7 +33360,7 @@
         <v>0.23</v>
       </c>
       <c r="AQ156">
-        <v>0.42</v>
+        <v>0.62</v>
       </c>
       <c r="AR156">
         <v>1.34</v>
@@ -33685,7 +33691,7 @@
         <v>88</v>
       </c>
       <c r="P158" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="Q158">
         <v>5</v>
@@ -33766,7 +33772,7 @@
         <v>1.5</v>
       </c>
       <c r="AQ158">
-        <v>2.17</v>
+        <v>2</v>
       </c>
       <c r="AR158">
         <v>1.21</v>
@@ -33891,7 +33897,7 @@
         <v>88</v>
       </c>
       <c r="P159" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="Q159">
         <v>2.38</v>
@@ -33972,7 +33978,7 @@
         <v>2</v>
       </c>
       <c r="AQ159">
-        <v>1.33</v>
+        <v>1.46</v>
       </c>
       <c r="AR159">
         <v>1.67</v>
@@ -34303,7 +34309,7 @@
         <v>193</v>
       </c>
       <c r="P161" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="Q161">
         <v>4.75</v>
@@ -34509,7 +34515,7 @@
         <v>194</v>
       </c>
       <c r="P162" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="Q162">
         <v>2.63</v>
@@ -34587,7 +34593,7 @@
         <v>0.9</v>
       </c>
       <c r="AP162">
-        <v>1.58</v>
+        <v>1.46</v>
       </c>
       <c r="AQ162">
         <v>0.77</v>
@@ -34715,7 +34721,7 @@
         <v>88</v>
       </c>
       <c r="P163" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="Q163">
         <v>11</v>
@@ -34793,7 +34799,7 @@
         <v>2.3</v>
       </c>
       <c r="AP163">
-        <v>0.83</v>
+        <v>0.77</v>
       </c>
       <c r="AQ163">
         <v>2.23</v>
@@ -34921,7 +34927,7 @@
         <v>195</v>
       </c>
       <c r="P164" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="Q164">
         <v>2</v>
@@ -35127,7 +35133,7 @@
         <v>196</v>
       </c>
       <c r="P165" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="Q165">
         <v>2.5</v>
@@ -35208,7 +35214,7 @@
         <v>2</v>
       </c>
       <c r="AQ165">
-        <v>0.92</v>
+        <v>0.85</v>
       </c>
       <c r="AR165">
         <v>1.66</v>
@@ -36238,7 +36244,7 @@
         <v>1.5</v>
       </c>
       <c r="AQ170">
-        <v>0.42</v>
+        <v>0.62</v>
       </c>
       <c r="AR170">
         <v>1.21</v>
@@ -36363,7 +36369,7 @@
         <v>201</v>
       </c>
       <c r="P171" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="Q171">
         <v>5.2</v>
@@ -36569,7 +36575,7 @@
         <v>202</v>
       </c>
       <c r="P172" t="s">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="Q172">
         <v>6.35</v>
@@ -36650,7 +36656,7 @@
         <v>1.46</v>
       </c>
       <c r="AQ172">
-        <v>2.17</v>
+        <v>2</v>
       </c>
       <c r="AR172">
         <v>1.5</v>
@@ -36775,7 +36781,7 @@
         <v>203</v>
       </c>
       <c r="P173" t="s">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="Q173">
         <v>2.6</v>
@@ -36856,7 +36862,7 @@
         <v>1.54</v>
       </c>
       <c r="AQ173">
-        <v>1.33</v>
+        <v>1.46</v>
       </c>
       <c r="AR173">
         <v>1.47</v>
@@ -36981,7 +36987,7 @@
         <v>88</v>
       </c>
       <c r="P174" t="s">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="Q174">
         <v>4.86</v>
@@ -37059,7 +37065,7 @@
         <v>1.7</v>
       </c>
       <c r="AP174">
-        <v>1.33</v>
+        <v>1.46</v>
       </c>
       <c r="AQ174">
         <v>1.85</v>
@@ -37187,7 +37193,7 @@
         <v>204</v>
       </c>
       <c r="P175" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="Q175">
         <v>2.66</v>
@@ -37265,7 +37271,7 @@
         <v>1.2</v>
       </c>
       <c r="AP175">
-        <v>1.42</v>
+        <v>1.54</v>
       </c>
       <c r="AQ175">
         <v>1.15</v>
@@ -37599,7 +37605,7 @@
         <v>171</v>
       </c>
       <c r="P177" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="Q177">
         <v>3.63</v>
@@ -38011,7 +38017,7 @@
         <v>88</v>
       </c>
       <c r="P179" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="Q179">
         <v>3.92</v>
@@ -38089,7 +38095,7 @@
         <v>1.09</v>
       </c>
       <c r="AP179">
-        <v>0.83</v>
+        <v>0.77</v>
       </c>
       <c r="AQ179">
         <v>1.15</v>
@@ -38217,7 +38223,7 @@
         <v>206</v>
       </c>
       <c r="P180" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="Q180">
         <v>1.32</v>
@@ -38835,7 +38841,7 @@
         <v>208</v>
       </c>
       <c r="P183" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="Q183">
         <v>4.3</v>
@@ -39041,7 +39047,7 @@
         <v>88</v>
       </c>
       <c r="P184" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="Q184">
         <v>5.8</v>
@@ -39453,7 +39459,7 @@
         <v>96</v>
       </c>
       <c r="P186" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="Q186">
         <v>4.7</v>
@@ -39534,7 +39540,7 @@
         <v>1.67</v>
       </c>
       <c r="AQ186">
-        <v>2.17</v>
+        <v>2</v>
       </c>
       <c r="AR186">
         <v>1.58</v>
@@ -39737,7 +39743,7 @@
         <v>0.5</v>
       </c>
       <c r="AP187">
-        <v>1.33</v>
+        <v>1.46</v>
       </c>
       <c r="AQ187">
         <v>0.46</v>
@@ -39943,10 +39949,10 @@
         <v>0.36</v>
       </c>
       <c r="AP188">
-        <v>1.42</v>
+        <v>1.54</v>
       </c>
       <c r="AQ188">
-        <v>0.42</v>
+        <v>0.62</v>
       </c>
       <c r="AR188">
         <v>1.49</v>
@@ -40071,7 +40077,7 @@
         <v>88</v>
       </c>
       <c r="P189" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="Q189">
         <v>4.5</v>
@@ -40149,7 +40155,7 @@
         <v>1.82</v>
       </c>
       <c r="AP189">
-        <v>1.58</v>
+        <v>1.46</v>
       </c>
       <c r="AQ189">
         <v>1.85</v>
@@ -40358,7 +40364,7 @@
         <v>1.46</v>
       </c>
       <c r="AQ190">
-        <v>0.92</v>
+        <v>0.85</v>
       </c>
       <c r="AR190">
         <v>1.53</v>
@@ -40564,7 +40570,7 @@
         <v>3</v>
       </c>
       <c r="AQ191">
-        <v>1.33</v>
+        <v>1.46</v>
       </c>
       <c r="AR191">
         <v>2.28</v>
@@ -41513,7 +41519,7 @@
         <v>215</v>
       </c>
       <c r="P196" t="s">
-        <v>221</v>
+        <v>223</v>
       </c>
       <c r="Q196">
         <v>1.95</v>
@@ -41719,7 +41725,7 @@
         <v>88</v>
       </c>
       <c r="P197" t="s">
-        <v>221</v>
+        <v>223</v>
       </c>
       <c r="Q197">
         <v>2.88</v>
@@ -42209,7 +42215,7 @@
         <v>1.92</v>
       </c>
       <c r="AP199">
-        <v>0.83</v>
+        <v>0.77</v>
       </c>
       <c r="AQ199">
         <v>1.85</v>
@@ -42494,6 +42500,830 @@
       </c>
       <c r="BP200">
         <v>1.41</v>
+      </c>
+    </row>
+    <row r="201" spans="1:68">
+      <c r="A201" s="1">
+        <v>200</v>
+      </c>
+      <c r="B201">
+        <v>7468288</v>
+      </c>
+      <c r="C201" t="s">
+        <v>68</v>
+      </c>
+      <c r="D201" t="s">
+        <v>69</v>
+      </c>
+      <c r="E201" s="2">
+        <v>45731.39583333334</v>
+      </c>
+      <c r="F201">
+        <v>26</v>
+      </c>
+      <c r="G201" t="s">
+        <v>82</v>
+      </c>
+      <c r="H201" t="s">
+        <v>73</v>
+      </c>
+      <c r="I201">
+        <v>0</v>
+      </c>
+      <c r="J201">
+        <v>2</v>
+      </c>
+      <c r="K201">
+        <v>2</v>
+      </c>
+      <c r="L201">
+        <v>1</v>
+      </c>
+      <c r="M201">
+        <v>2</v>
+      </c>
+      <c r="N201">
+        <v>3</v>
+      </c>
+      <c r="O201" t="s">
+        <v>158</v>
+      </c>
+      <c r="P201" t="s">
+        <v>307</v>
+      </c>
+      <c r="Q201">
+        <v>2.63</v>
+      </c>
+      <c r="R201">
+        <v>2.3</v>
+      </c>
+      <c r="S201">
+        <v>3.75</v>
+      </c>
+      <c r="T201">
+        <v>1.33</v>
+      </c>
+      <c r="U201">
+        <v>3.25</v>
+      </c>
+      <c r="V201">
+        <v>2.5</v>
+      </c>
+      <c r="W201">
+        <v>1.5</v>
+      </c>
+      <c r="X201">
+        <v>6.5</v>
+      </c>
+      <c r="Y201">
+        <v>1.11</v>
+      </c>
+      <c r="Z201">
+        <v>2</v>
+      </c>
+      <c r="AA201">
+        <v>3.4</v>
+      </c>
+      <c r="AB201">
+        <v>3.3</v>
+      </c>
+      <c r="AC201">
+        <v>0</v>
+      </c>
+      <c r="AD201">
+        <v>0</v>
+      </c>
+      <c r="AE201">
+        <v>0</v>
+      </c>
+      <c r="AF201">
+        <v>0</v>
+      </c>
+      <c r="AG201">
+        <v>1.67</v>
+      </c>
+      <c r="AH201">
+        <v>2.15</v>
+      </c>
+      <c r="AI201">
+        <v>1.57</v>
+      </c>
+      <c r="AJ201">
+        <v>2.25</v>
+      </c>
+      <c r="AK201">
+        <v>0</v>
+      </c>
+      <c r="AL201">
+        <v>0</v>
+      </c>
+      <c r="AM201">
+        <v>0</v>
+      </c>
+      <c r="AN201">
+        <v>1.58</v>
+      </c>
+      <c r="AO201">
+        <v>1.33</v>
+      </c>
+      <c r="AP201">
+        <v>1.46</v>
+      </c>
+      <c r="AQ201">
+        <v>1.46</v>
+      </c>
+      <c r="AR201">
+        <v>1.55</v>
+      </c>
+      <c r="AS201">
+        <v>1.3</v>
+      </c>
+      <c r="AT201">
+        <v>2.85</v>
+      </c>
+      <c r="AU201">
+        <v>11</v>
+      </c>
+      <c r="AV201">
+        <v>6</v>
+      </c>
+      <c r="AW201">
+        <v>11</v>
+      </c>
+      <c r="AX201">
+        <v>4</v>
+      </c>
+      <c r="AY201">
+        <v>22</v>
+      </c>
+      <c r="AZ201">
+        <v>10</v>
+      </c>
+      <c r="BA201">
+        <v>12</v>
+      </c>
+      <c r="BB201">
+        <v>2</v>
+      </c>
+      <c r="BC201">
+        <v>14</v>
+      </c>
+      <c r="BD201">
+        <v>0</v>
+      </c>
+      <c r="BE201">
+        <v>0</v>
+      </c>
+      <c r="BF201">
+        <v>0</v>
+      </c>
+      <c r="BG201">
+        <v>0</v>
+      </c>
+      <c r="BH201">
+        <v>0</v>
+      </c>
+      <c r="BI201">
+        <v>0</v>
+      </c>
+      <c r="BJ201">
+        <v>0</v>
+      </c>
+      <c r="BK201">
+        <v>0</v>
+      </c>
+      <c r="BL201">
+        <v>0</v>
+      </c>
+      <c r="BM201">
+        <v>0</v>
+      </c>
+      <c r="BN201">
+        <v>0</v>
+      </c>
+      <c r="BO201">
+        <v>0</v>
+      </c>
+      <c r="BP201">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="202" spans="1:68">
+      <c r="A202" s="1">
+        <v>201</v>
+      </c>
+      <c r="B202">
+        <v>7468291</v>
+      </c>
+      <c r="C202" t="s">
+        <v>68</v>
+      </c>
+      <c r="D202" t="s">
+        <v>69</v>
+      </c>
+      <c r="E202" s="2">
+        <v>45731.5</v>
+      </c>
+      <c r="F202">
+        <v>26</v>
+      </c>
+      <c r="G202" t="s">
+        <v>78</v>
+      </c>
+      <c r="H202" t="s">
+        <v>76</v>
+      </c>
+      <c r="I202">
+        <v>0</v>
+      </c>
+      <c r="J202">
+        <v>0</v>
+      </c>
+      <c r="K202">
+        <v>0</v>
+      </c>
+      <c r="L202">
+        <v>1</v>
+      </c>
+      <c r="M202">
+        <v>0</v>
+      </c>
+      <c r="N202">
+        <v>1</v>
+      </c>
+      <c r="O202" t="s">
+        <v>216</v>
+      </c>
+      <c r="P202" t="s">
+        <v>88</v>
+      </c>
+      <c r="Q202">
+        <v>2.75</v>
+      </c>
+      <c r="R202">
+        <v>2</v>
+      </c>
+      <c r="S202">
+        <v>4.5</v>
+      </c>
+      <c r="T202">
+        <v>1.5</v>
+      </c>
+      <c r="U202">
+        <v>2.5</v>
+      </c>
+      <c r="V202">
+        <v>3.4</v>
+      </c>
+      <c r="W202">
+        <v>1.3</v>
+      </c>
+      <c r="X202">
+        <v>10</v>
+      </c>
+      <c r="Y202">
+        <v>1.06</v>
+      </c>
+      <c r="Z202">
+        <v>2.05</v>
+      </c>
+      <c r="AA202">
+        <v>3.25</v>
+      </c>
+      <c r="AB202">
+        <v>3.75</v>
+      </c>
+      <c r="AC202">
+        <v>2.3</v>
+      </c>
+      <c r="AD202">
+        <v>1.61</v>
+      </c>
+      <c r="AE202">
+        <v>0</v>
+      </c>
+      <c r="AF202">
+        <v>0</v>
+      </c>
+      <c r="AG202">
+        <v>2.25</v>
+      </c>
+      <c r="AH202">
+        <v>1.62</v>
+      </c>
+      <c r="AI202">
+        <v>2</v>
+      </c>
+      <c r="AJ202">
+        <v>1.75</v>
+      </c>
+      <c r="AK202">
+        <v>1.31</v>
+      </c>
+      <c r="AL202">
+        <v>1.3</v>
+      </c>
+      <c r="AM202">
+        <v>1.76</v>
+      </c>
+      <c r="AN202">
+        <v>1.33</v>
+      </c>
+      <c r="AO202">
+        <v>0.92</v>
+      </c>
+      <c r="AP202">
+        <v>1.46</v>
+      </c>
+      <c r="AQ202">
+        <v>0.85</v>
+      </c>
+      <c r="AR202">
+        <v>1.47</v>
+      </c>
+      <c r="AS202">
+        <v>1.17</v>
+      </c>
+      <c r="AT202">
+        <v>2.64</v>
+      </c>
+      <c r="AU202">
+        <v>3</v>
+      </c>
+      <c r="AV202">
+        <v>2</v>
+      </c>
+      <c r="AW202">
+        <v>9</v>
+      </c>
+      <c r="AX202">
+        <v>8</v>
+      </c>
+      <c r="AY202">
+        <v>12</v>
+      </c>
+      <c r="AZ202">
+        <v>10</v>
+      </c>
+      <c r="BA202">
+        <v>6</v>
+      </c>
+      <c r="BB202">
+        <v>4</v>
+      </c>
+      <c r="BC202">
+        <v>10</v>
+      </c>
+      <c r="BD202">
+        <v>0</v>
+      </c>
+      <c r="BE202">
+        <v>0</v>
+      </c>
+      <c r="BF202">
+        <v>0</v>
+      </c>
+      <c r="BG202">
+        <v>0</v>
+      </c>
+      <c r="BH202">
+        <v>0</v>
+      </c>
+      <c r="BI202">
+        <v>0</v>
+      </c>
+      <c r="BJ202">
+        <v>0</v>
+      </c>
+      <c r="BK202">
+        <v>0</v>
+      </c>
+      <c r="BL202">
+        <v>0</v>
+      </c>
+      <c r="BM202">
+        <v>0</v>
+      </c>
+      <c r="BN202">
+        <v>0</v>
+      </c>
+      <c r="BO202">
+        <v>0</v>
+      </c>
+      <c r="BP202">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="203" spans="1:68">
+      <c r="A203" s="1">
+        <v>202</v>
+      </c>
+      <c r="B203">
+        <v>7468287</v>
+      </c>
+      <c r="C203" t="s">
+        <v>68</v>
+      </c>
+      <c r="D203" t="s">
+        <v>69</v>
+      </c>
+      <c r="E203" s="2">
+        <v>45731.5</v>
+      </c>
+      <c r="F203">
+        <v>26</v>
+      </c>
+      <c r="G203" t="s">
+        <v>79</v>
+      </c>
+      <c r="H203" t="s">
+        <v>74</v>
+      </c>
+      <c r="I203">
+        <v>0</v>
+      </c>
+      <c r="J203">
+        <v>0</v>
+      </c>
+      <c r="K203">
+        <v>0</v>
+      </c>
+      <c r="L203">
+        <v>0</v>
+      </c>
+      <c r="M203">
+        <v>1</v>
+      </c>
+      <c r="N203">
+        <v>1</v>
+      </c>
+      <c r="O203" t="s">
+        <v>88</v>
+      </c>
+      <c r="P203" t="s">
+        <v>248</v>
+      </c>
+      <c r="Q203">
+        <v>2.75</v>
+      </c>
+      <c r="R203">
+        <v>2.2</v>
+      </c>
+      <c r="S203">
+        <v>4</v>
+      </c>
+      <c r="T203">
+        <v>1.4</v>
+      </c>
+      <c r="U203">
+        <v>2.75</v>
+      </c>
+      <c r="V203">
+        <v>2.75</v>
+      </c>
+      <c r="W203">
+        <v>1.4</v>
+      </c>
+      <c r="X203">
+        <v>8</v>
+      </c>
+      <c r="Y203">
+        <v>1.08</v>
+      </c>
+      <c r="Z203">
+        <v>1.95</v>
+      </c>
+      <c r="AA203">
+        <v>3.2</v>
+      </c>
+      <c r="AB203">
+        <v>3.3</v>
+      </c>
+      <c r="AC203">
+        <v>0</v>
+      </c>
+      <c r="AD203">
+        <v>0</v>
+      </c>
+      <c r="AE203">
+        <v>0</v>
+      </c>
+      <c r="AF203">
+        <v>0</v>
+      </c>
+      <c r="AG203">
+        <v>1.91</v>
+      </c>
+      <c r="AH203">
+        <v>1.8</v>
+      </c>
+      <c r="AI203">
+        <v>1.75</v>
+      </c>
+      <c r="AJ203">
+        <v>2</v>
+      </c>
+      <c r="AK203">
+        <v>1.33</v>
+      </c>
+      <c r="AL203">
+        <v>1.34</v>
+      </c>
+      <c r="AM203">
+        <v>1.65</v>
+      </c>
+      <c r="AN203">
+        <v>0.83</v>
+      </c>
+      <c r="AO203">
+        <v>0.42</v>
+      </c>
+      <c r="AP203">
+        <v>0.77</v>
+      </c>
+      <c r="AQ203">
+        <v>0.62</v>
+      </c>
+      <c r="AR203">
+        <v>1.23</v>
+      </c>
+      <c r="AS203">
+        <v>0.91</v>
+      </c>
+      <c r="AT203">
+        <v>2.14</v>
+      </c>
+      <c r="AU203">
+        <v>4</v>
+      </c>
+      <c r="AV203">
+        <v>5</v>
+      </c>
+      <c r="AW203">
+        <v>7</v>
+      </c>
+      <c r="AX203">
+        <v>4</v>
+      </c>
+      <c r="AY203">
+        <v>11</v>
+      </c>
+      <c r="AZ203">
+        <v>9</v>
+      </c>
+      <c r="BA203">
+        <v>4</v>
+      </c>
+      <c r="BB203">
+        <v>4</v>
+      </c>
+      <c r="BC203">
+        <v>8</v>
+      </c>
+      <c r="BD203">
+        <v>0</v>
+      </c>
+      <c r="BE203">
+        <v>0</v>
+      </c>
+      <c r="BF203">
+        <v>0</v>
+      </c>
+      <c r="BG203">
+        <v>0</v>
+      </c>
+      <c r="BH203">
+        <v>0</v>
+      </c>
+      <c r="BI203">
+        <v>0</v>
+      </c>
+      <c r="BJ203">
+        <v>0</v>
+      </c>
+      <c r="BK203">
+        <v>1.58</v>
+      </c>
+      <c r="BL203">
+        <v>2.29</v>
+      </c>
+      <c r="BM203">
+        <v>1.97</v>
+      </c>
+      <c r="BN203">
+        <v>1.83</v>
+      </c>
+      <c r="BO203">
+        <v>2.47</v>
+      </c>
+      <c r="BP203">
+        <v>1.51</v>
+      </c>
+    </row>
+    <row r="204" spans="1:68">
+      <c r="A204" s="1">
+        <v>203</v>
+      </c>
+      <c r="B204">
+        <v>7468290</v>
+      </c>
+      <c r="C204" t="s">
+        <v>68</v>
+      </c>
+      <c r="D204" t="s">
+        <v>69</v>
+      </c>
+      <c r="E204" s="2">
+        <v>45731.625</v>
+      </c>
+      <c r="F204">
+        <v>26</v>
+      </c>
+      <c r="G204" t="s">
+        <v>81</v>
+      </c>
+      <c r="H204" t="s">
+        <v>70</v>
+      </c>
+      <c r="I204">
+        <v>0</v>
+      </c>
+      <c r="J204">
+        <v>0</v>
+      </c>
+      <c r="K204">
+        <v>0</v>
+      </c>
+      <c r="L204">
+        <v>1</v>
+      </c>
+      <c r="M204">
+        <v>0</v>
+      </c>
+      <c r="N204">
+        <v>1</v>
+      </c>
+      <c r="O204" t="s">
+        <v>217</v>
+      </c>
+      <c r="P204" t="s">
+        <v>88</v>
+      </c>
+      <c r="Q204">
+        <v>4.33</v>
+      </c>
+      <c r="R204">
+        <v>2.2</v>
+      </c>
+      <c r="S204">
+        <v>2.6</v>
+      </c>
+      <c r="T204">
+        <v>1.4</v>
+      </c>
+      <c r="U204">
+        <v>2.75</v>
+      </c>
+      <c r="V204">
+        <v>3</v>
+      </c>
+      <c r="W204">
+        <v>1.36</v>
+      </c>
+      <c r="X204">
+        <v>8</v>
+      </c>
+      <c r="Y204">
+        <v>1.08</v>
+      </c>
+      <c r="Z204">
+        <v>3.6</v>
+      </c>
+      <c r="AA204">
+        <v>3.25</v>
+      </c>
+      <c r="AB204">
+        <v>1.85</v>
+      </c>
+      <c r="AC204">
+        <v>1.01</v>
+      </c>
+      <c r="AD204">
+        <v>11</v>
+      </c>
+      <c r="AE204">
+        <v>1.22</v>
+      </c>
+      <c r="AF204">
+        <v>3.75</v>
+      </c>
+      <c r="AG204">
+        <v>1.91</v>
+      </c>
+      <c r="AH204">
+        <v>1.8</v>
+      </c>
+      <c r="AI204">
+        <v>1.8</v>
+      </c>
+      <c r="AJ204">
+        <v>1.95</v>
+      </c>
+      <c r="AK204">
+        <v>2</v>
+      </c>
+      <c r="AL204">
+        <v>1.29</v>
+      </c>
+      <c r="AM204">
+        <v>1.18</v>
+      </c>
+      <c r="AN204">
+        <v>1.42</v>
+      </c>
+      <c r="AO204">
+        <v>2.17</v>
+      </c>
+      <c r="AP204">
+        <v>1.54</v>
+      </c>
+      <c r="AQ204">
+        <v>2</v>
+      </c>
+      <c r="AR204">
+        <v>1.5</v>
+      </c>
+      <c r="AS204">
+        <v>1.68</v>
+      </c>
+      <c r="AT204">
+        <v>3.18</v>
+      </c>
+      <c r="AU204">
+        <v>6</v>
+      </c>
+      <c r="AV204">
+        <v>5</v>
+      </c>
+      <c r="AW204">
+        <v>3</v>
+      </c>
+      <c r="AX204">
+        <v>10</v>
+      </c>
+      <c r="AY204">
+        <v>9</v>
+      </c>
+      <c r="AZ204">
+        <v>15</v>
+      </c>
+      <c r="BA204">
+        <v>2</v>
+      </c>
+      <c r="BB204">
+        <v>5</v>
+      </c>
+      <c r="BC204">
+        <v>7</v>
+      </c>
+      <c r="BD204">
+        <v>2.4</v>
+      </c>
+      <c r="BE204">
+        <v>8.5</v>
+      </c>
+      <c r="BF204">
+        <v>1.7</v>
+      </c>
+      <c r="BG204">
+        <v>1.19</v>
+      </c>
+      <c r="BH204">
+        <v>4.1</v>
+      </c>
+      <c r="BI204">
+        <v>1.3</v>
+      </c>
+      <c r="BJ204">
+        <v>2.97</v>
+      </c>
+      <c r="BK204">
+        <v>1.64</v>
+      </c>
+      <c r="BL204">
+        <v>2.24</v>
+      </c>
+      <c r="BM204">
+        <v>2.01</v>
+      </c>
+      <c r="BN204">
+        <v>1.79</v>
+      </c>
+      <c r="BO204">
+        <v>2.51</v>
+      </c>
+      <c r="BP204">
+        <v>1.44</v>
       </c>
     </row>
   </sheetData>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Czech Republic First League_20242025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Czech Republic First League_20242025.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1286" uniqueCount="308">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1310" uniqueCount="312">
   <si>
     <t>Id_Jogo</t>
   </si>
@@ -670,6 +670,15 @@
     <t>['49']</t>
   </si>
   <si>
+    <t>['62']</t>
+  </si>
+  <si>
+    <t>['2', '37']</t>
+  </si>
+  <si>
+    <t>['9', '18', '34']</t>
+  </si>
+  <si>
     <t>['25']</t>
   </si>
   <si>
@@ -686,9 +695,6 @@
   </si>
   <si>
     <t>['15']</t>
-  </si>
-  <si>
-    <t>['62']</t>
   </si>
   <si>
     <t>['39']</t>
@@ -938,6 +944,12 @@
   </si>
   <si>
     <t>['13', '18']</t>
+  </si>
+  <si>
+    <t>['20', '25']</t>
+  </si>
+  <si>
+    <t>['26', '64', '72']</t>
   </si>
 </sst>
 </file>
@@ -1299,7 +1311,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:BP204"/>
+  <dimension ref="A1:BP208"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:68">
@@ -1555,7 +1567,7 @@
         <v>86</v>
       </c>
       <c r="P2" t="s">
-        <v>218</v>
+        <v>221</v>
       </c>
       <c r="Q2">
         <v>1.53</v>
@@ -1967,7 +1979,7 @@
         <v>88</v>
       </c>
       <c r="P4" t="s">
-        <v>219</v>
+        <v>222</v>
       </c>
       <c r="Q4">
         <v>2.88</v>
@@ -2045,7 +2057,7 @@
         <v>0</v>
       </c>
       <c r="AP4">
-        <v>0.23</v>
+        <v>0.21</v>
       </c>
       <c r="AQ4">
         <v>1.38</v>
@@ -2254,7 +2266,7 @@
         <v>1.08</v>
       </c>
       <c r="AQ5">
-        <v>1.62</v>
+        <v>1.71</v>
       </c>
       <c r="AR5">
         <v>0</v>
@@ -2379,7 +2391,7 @@
         <v>90</v>
       </c>
       <c r="P6" t="s">
-        <v>220</v>
+        <v>223</v>
       </c>
       <c r="Q6">
         <v>5.5</v>
@@ -2585,7 +2597,7 @@
         <v>91</v>
       </c>
       <c r="P7" t="s">
-        <v>221</v>
+        <v>224</v>
       </c>
       <c r="Q7">
         <v>3.2</v>
@@ -3409,7 +3421,7 @@
         <v>94</v>
       </c>
       <c r="P11" t="s">
-        <v>222</v>
+        <v>225</v>
       </c>
       <c r="Q11">
         <v>6.5</v>
@@ -3615,7 +3627,7 @@
         <v>88</v>
       </c>
       <c r="P12" t="s">
-        <v>223</v>
+        <v>226</v>
       </c>
       <c r="Q12">
         <v>2.85</v>
@@ -3696,7 +3708,7 @@
         <v>0.77</v>
       </c>
       <c r="AQ12">
-        <v>0.83</v>
+        <v>1</v>
       </c>
       <c r="AR12">
         <v>0</v>
@@ -4027,7 +4039,7 @@
         <v>96</v>
       </c>
       <c r="P14" t="s">
-        <v>224</v>
+        <v>218</v>
       </c>
       <c r="Q14">
         <v>2.45</v>
@@ -4520,7 +4532,7 @@
         <v>2.5</v>
       </c>
       <c r="AQ16">
-        <v>1.25</v>
+        <v>1.15</v>
       </c>
       <c r="AR16">
         <v>0</v>
@@ -4723,10 +4735,10 @@
         <v>0</v>
       </c>
       <c r="AP17">
-        <v>2.42</v>
+        <v>2.23</v>
       </c>
       <c r="AQ17">
-        <v>1</v>
+        <v>1.17</v>
       </c>
       <c r="AR17">
         <v>0</v>
@@ -4851,7 +4863,7 @@
         <v>88</v>
       </c>
       <c r="P18" t="s">
-        <v>225</v>
+        <v>227</v>
       </c>
       <c r="Q18">
         <v>5.4</v>
@@ -5753,7 +5765,7 @@
         <v>0</v>
       </c>
       <c r="AP22">
-        <v>1.67</v>
+        <v>1.54</v>
       </c>
       <c r="AQ22">
         <v>0.77</v>
@@ -5881,7 +5893,7 @@
         <v>102</v>
       </c>
       <c r="P23" t="s">
-        <v>226</v>
+        <v>228</v>
       </c>
       <c r="Q23">
         <v>2.6</v>
@@ -5959,7 +5971,7 @@
         <v>0</v>
       </c>
       <c r="AP23">
-        <v>0.23</v>
+        <v>0.21</v>
       </c>
       <c r="AQ23">
         <v>0.46</v>
@@ -6087,7 +6099,7 @@
         <v>103</v>
       </c>
       <c r="P24" t="s">
-        <v>227</v>
+        <v>229</v>
       </c>
       <c r="Q24">
         <v>2.75</v>
@@ -6293,7 +6305,7 @@
         <v>88</v>
       </c>
       <c r="P25" t="s">
-        <v>228</v>
+        <v>230</v>
       </c>
       <c r="Q25">
         <v>1.06</v>
@@ -6374,7 +6386,7 @@
         <v>0.92</v>
       </c>
       <c r="AQ25">
-        <v>1.25</v>
+        <v>1.15</v>
       </c>
       <c r="AR25">
         <v>0.93</v>
@@ -6499,7 +6511,7 @@
         <v>104</v>
       </c>
       <c r="P26" t="s">
-        <v>229</v>
+        <v>231</v>
       </c>
       <c r="Q26">
         <v>6.23</v>
@@ -7404,7 +7416,7 @@
         <v>2.5</v>
       </c>
       <c r="AQ30">
-        <v>1</v>
+        <v>1.17</v>
       </c>
       <c r="AR30">
         <v>1.24</v>
@@ -7813,10 +7825,10 @@
         <v>3</v>
       </c>
       <c r="AP32">
-        <v>2.42</v>
+        <v>2.23</v>
       </c>
       <c r="AQ32">
-        <v>0.83</v>
+        <v>1</v>
       </c>
       <c r="AR32">
         <v>1.64</v>
@@ -8147,7 +8159,7 @@
         <v>111</v>
       </c>
       <c r="P34" t="s">
-        <v>230</v>
+        <v>232</v>
       </c>
       <c r="Q34">
         <v>1.45</v>
@@ -8353,7 +8365,7 @@
         <v>112</v>
       </c>
       <c r="P35" t="s">
-        <v>231</v>
+        <v>233</v>
       </c>
       <c r="Q35">
         <v>2.84</v>
@@ -8559,7 +8571,7 @@
         <v>113</v>
       </c>
       <c r="P36" t="s">
-        <v>232</v>
+        <v>234</v>
       </c>
       <c r="Q36">
         <v>5.63</v>
@@ -8765,7 +8777,7 @@
         <v>114</v>
       </c>
       <c r="P37" t="s">
-        <v>233</v>
+        <v>235</v>
       </c>
       <c r="Q37">
         <v>2.58</v>
@@ -8843,7 +8855,7 @@
         <v>0</v>
       </c>
       <c r="AP37">
-        <v>1.67</v>
+        <v>1.54</v>
       </c>
       <c r="AQ37">
         <v>1.15</v>
@@ -9177,7 +9189,7 @@
         <v>88</v>
       </c>
       <c r="P39" t="s">
-        <v>234</v>
+        <v>236</v>
       </c>
       <c r="Q39">
         <v>4.75</v>
@@ -9255,7 +9267,7 @@
         <v>2</v>
       </c>
       <c r="AP39">
-        <v>0.23</v>
+        <v>0.21</v>
       </c>
       <c r="AQ39">
         <v>1.85</v>
@@ -9464,7 +9476,7 @@
         <v>1.5</v>
       </c>
       <c r="AQ40">
-        <v>1.62</v>
+        <v>1.71</v>
       </c>
       <c r="AR40">
         <v>1.19</v>
@@ -9589,7 +9601,7 @@
         <v>117</v>
       </c>
       <c r="P41" t="s">
-        <v>235</v>
+        <v>237</v>
       </c>
       <c r="Q41">
         <v>2.4</v>
@@ -9670,7 +9682,7 @@
         <v>1.08</v>
       </c>
       <c r="AQ41">
-        <v>1.25</v>
+        <v>1.15</v>
       </c>
       <c r="AR41">
         <v>1.49</v>
@@ -9795,7 +9807,7 @@
         <v>107</v>
       </c>
       <c r="P42" t="s">
-        <v>236</v>
+        <v>238</v>
       </c>
       <c r="Q42">
         <v>2.61</v>
@@ -9876,7 +9888,7 @@
         <v>1.46</v>
       </c>
       <c r="AQ42">
-        <v>0.83</v>
+        <v>1</v>
       </c>
       <c r="AR42">
         <v>1.41</v>
@@ -10001,7 +10013,7 @@
         <v>118</v>
       </c>
       <c r="P43" t="s">
-        <v>237</v>
+        <v>239</v>
       </c>
       <c r="Q43">
         <v>1.69</v>
@@ -10288,7 +10300,7 @@
         <v>0.77</v>
       </c>
       <c r="AQ44">
-        <v>1</v>
+        <v>1.17</v>
       </c>
       <c r="AR44">
         <v>1.16</v>
@@ -10906,7 +10918,7 @@
         <v>1.46</v>
       </c>
       <c r="AQ47">
-        <v>1.62</v>
+        <v>1.71</v>
       </c>
       <c r="AR47">
         <v>1.77</v>
@@ -11109,7 +11121,7 @@
         <v>1.33</v>
       </c>
       <c r="AP48">
-        <v>0.23</v>
+        <v>0.21</v>
       </c>
       <c r="AQ48">
         <v>1.46</v>
@@ -11318,7 +11330,7 @@
         <v>1.5</v>
       </c>
       <c r="AQ49">
-        <v>1.25</v>
+        <v>1.15</v>
       </c>
       <c r="AR49">
         <v>1.24</v>
@@ -11443,7 +11455,7 @@
         <v>88</v>
       </c>
       <c r="P50" t="s">
-        <v>238</v>
+        <v>240</v>
       </c>
       <c r="Q50">
         <v>5.1</v>
@@ -11855,7 +11867,7 @@
         <v>122</v>
       </c>
       <c r="P52" t="s">
-        <v>239</v>
+        <v>241</v>
       </c>
       <c r="Q52">
         <v>3</v>
@@ -11933,10 +11945,10 @@
         <v>0.33</v>
       </c>
       <c r="AP52">
-        <v>1.67</v>
+        <v>1.54</v>
       </c>
       <c r="AQ52">
-        <v>1.62</v>
+        <v>1.71</v>
       </c>
       <c r="AR52">
         <v>1.61</v>
@@ -12267,7 +12279,7 @@
         <v>124</v>
       </c>
       <c r="P54" t="s">
-        <v>240</v>
+        <v>242</v>
       </c>
       <c r="Q54">
         <v>3</v>
@@ -12757,7 +12769,7 @@
         <v>1.33</v>
       </c>
       <c r="AP56">
-        <v>2.42</v>
+        <v>2.23</v>
       </c>
       <c r="AQ56">
         <v>1.38</v>
@@ -12885,7 +12897,7 @@
         <v>88</v>
       </c>
       <c r="P57" t="s">
-        <v>241</v>
+        <v>243</v>
       </c>
       <c r="Q57">
         <v>5.88</v>
@@ -13297,7 +13309,7 @@
         <v>127</v>
       </c>
       <c r="P59" t="s">
-        <v>242</v>
+        <v>244</v>
       </c>
       <c r="Q59">
         <v>3.86</v>
@@ -13378,7 +13390,7 @@
         <v>1.46</v>
       </c>
       <c r="AQ59">
-        <v>1.62</v>
+        <v>1.71</v>
       </c>
       <c r="AR59">
         <v>1.44</v>
@@ -13584,7 +13596,7 @@
         <v>1.46</v>
       </c>
       <c r="AQ60">
-        <v>1.25</v>
+        <v>1.15</v>
       </c>
       <c r="AR60">
         <v>1.83</v>
@@ -13915,7 +13927,7 @@
         <v>130</v>
       </c>
       <c r="P62" t="s">
-        <v>243</v>
+        <v>245</v>
       </c>
       <c r="Q62">
         <v>1.83</v>
@@ -14121,7 +14133,7 @@
         <v>88</v>
       </c>
       <c r="P63" t="s">
-        <v>244</v>
+        <v>246</v>
       </c>
       <c r="Q63">
         <v>8.77</v>
@@ -14199,7 +14211,7 @@
         <v>3</v>
       </c>
       <c r="AP63">
-        <v>0.23</v>
+        <v>0.21</v>
       </c>
       <c r="AQ63">
         <v>2</v>
@@ -14405,7 +14417,7 @@
         <v>0.33</v>
       </c>
       <c r="AP64">
-        <v>1.67</v>
+        <v>1.54</v>
       </c>
       <c r="AQ64">
         <v>0.62</v>
@@ -14533,7 +14545,7 @@
         <v>132</v>
       </c>
       <c r="P65" t="s">
-        <v>245</v>
+        <v>247</v>
       </c>
       <c r="Q65">
         <v>2.4</v>
@@ -14739,7 +14751,7 @@
         <v>133</v>
       </c>
       <c r="P66" t="s">
-        <v>246</v>
+        <v>248</v>
       </c>
       <c r="Q66">
         <v>1.55</v>
@@ -14945,7 +14957,7 @@
         <v>134</v>
       </c>
       <c r="P67" t="s">
-        <v>247</v>
+        <v>249</v>
       </c>
       <c r="Q67">
         <v>4</v>
@@ -15151,7 +15163,7 @@
         <v>88</v>
       </c>
       <c r="P68" t="s">
-        <v>248</v>
+        <v>250</v>
       </c>
       <c r="Q68">
         <v>3.1</v>
@@ -15438,7 +15450,7 @@
         <v>1.5</v>
       </c>
       <c r="AQ69">
-        <v>0.83</v>
+        <v>1</v>
       </c>
       <c r="AR69">
         <v>1.16</v>
@@ -15644,7 +15656,7 @@
         <v>2</v>
       </c>
       <c r="AQ70">
-        <v>1</v>
+        <v>1.17</v>
       </c>
       <c r="AR70">
         <v>1.53</v>
@@ -15975,7 +15987,7 @@
         <v>124</v>
       </c>
       <c r="P72" t="s">
-        <v>249</v>
+        <v>251</v>
       </c>
       <c r="Q72">
         <v>1.88</v>
@@ -16053,7 +16065,7 @@
         <v>0.75</v>
       </c>
       <c r="AP72">
-        <v>2.42</v>
+        <v>2.23</v>
       </c>
       <c r="AQ72">
         <v>1.15</v>
@@ -16181,7 +16193,7 @@
         <v>88</v>
       </c>
       <c r="P73" t="s">
-        <v>250</v>
+        <v>252</v>
       </c>
       <c r="Q73">
         <v>7</v>
@@ -16468,7 +16480,7 @@
         <v>1.46</v>
       </c>
       <c r="AQ74">
-        <v>1</v>
+        <v>1.17</v>
       </c>
       <c r="AR74">
         <v>1.81</v>
@@ -16593,7 +16605,7 @@
         <v>138</v>
       </c>
       <c r="P75" t="s">
-        <v>251</v>
+        <v>253</v>
       </c>
       <c r="Q75">
         <v>2.3</v>
@@ -16799,7 +16811,7 @@
         <v>88</v>
       </c>
       <c r="P76" t="s">
-        <v>252</v>
+        <v>254</v>
       </c>
       <c r="Q76">
         <v>3.7</v>
@@ -16877,7 +16889,7 @@
         <v>1</v>
       </c>
       <c r="AP76">
-        <v>0.23</v>
+        <v>0.21</v>
       </c>
       <c r="AQ76">
         <v>0.85</v>
@@ -17005,7 +17017,7 @@
         <v>88</v>
       </c>
       <c r="P77" t="s">
-        <v>253</v>
+        <v>255</v>
       </c>
       <c r="Q77">
         <v>2.47</v>
@@ -17086,7 +17098,7 @@
         <v>1.54</v>
       </c>
       <c r="AQ77">
-        <v>1.25</v>
+        <v>1.15</v>
       </c>
       <c r="AR77">
         <v>1.45</v>
@@ -17289,7 +17301,7 @@
         <v>0.8</v>
       </c>
       <c r="AP78">
-        <v>2.42</v>
+        <v>2.23</v>
       </c>
       <c r="AQ78">
         <v>0.46</v>
@@ -17498,7 +17510,7 @@
         <v>1.46</v>
       </c>
       <c r="AQ79">
-        <v>1.62</v>
+        <v>1.71</v>
       </c>
       <c r="AR79">
         <v>1.49</v>
@@ -17623,7 +17635,7 @@
         <v>140</v>
       </c>
       <c r="P80" t="s">
-        <v>254</v>
+        <v>256</v>
       </c>
       <c r="Q80">
         <v>2.5</v>
@@ -17701,7 +17713,7 @@
         <v>1.2</v>
       </c>
       <c r="AP80">
-        <v>1.67</v>
+        <v>1.54</v>
       </c>
       <c r="AQ80">
         <v>1.46</v>
@@ -17829,7 +17841,7 @@
         <v>141</v>
       </c>
       <c r="P81" t="s">
-        <v>255</v>
+        <v>257</v>
       </c>
       <c r="Q81">
         <v>2.38</v>
@@ -18035,7 +18047,7 @@
         <v>142</v>
       </c>
       <c r="P82" t="s">
-        <v>256</v>
+        <v>258</v>
       </c>
       <c r="Q82">
         <v>2.8</v>
@@ -18241,7 +18253,7 @@
         <v>143</v>
       </c>
       <c r="P83" t="s">
-        <v>257</v>
+        <v>259</v>
       </c>
       <c r="Q83">
         <v>2.6</v>
@@ -18447,7 +18459,7 @@
         <v>144</v>
       </c>
       <c r="P84" t="s">
-        <v>258</v>
+        <v>260</v>
       </c>
       <c r="Q84">
         <v>3.4</v>
@@ -18859,7 +18871,7 @@
         <v>146</v>
       </c>
       <c r="P86" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="Q86">
         <v>2.88</v>
@@ -19271,7 +19283,7 @@
         <v>88</v>
       </c>
       <c r="P88" t="s">
-        <v>260</v>
+        <v>262</v>
       </c>
       <c r="Q88">
         <v>2.6</v>
@@ -19477,7 +19489,7 @@
         <v>93</v>
       </c>
       <c r="P89" t="s">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="Q89">
         <v>6.5</v>
@@ -19889,7 +19901,7 @@
         <v>149</v>
       </c>
       <c r="P91" t="s">
-        <v>262</v>
+        <v>264</v>
       </c>
       <c r="Q91">
         <v>4.7</v>
@@ -19970,7 +19982,7 @@
         <v>0.77</v>
       </c>
       <c r="AQ91">
-        <v>1.62</v>
+        <v>1.71</v>
       </c>
       <c r="AR91">
         <v>1.11</v>
@@ -20095,7 +20107,7 @@
         <v>88</v>
       </c>
       <c r="P92" t="s">
-        <v>263</v>
+        <v>265</v>
       </c>
       <c r="Q92">
         <v>3.8</v>
@@ -20173,10 +20185,10 @@
         <v>0.2</v>
       </c>
       <c r="AP92">
-        <v>0.23</v>
+        <v>0.21</v>
       </c>
       <c r="AQ92">
-        <v>1</v>
+        <v>1.17</v>
       </c>
       <c r="AR92">
         <v>1.33</v>
@@ -20379,10 +20391,10 @@
         <v>1.67</v>
       </c>
       <c r="AP93">
-        <v>1.67</v>
+        <v>1.54</v>
       </c>
       <c r="AQ93">
-        <v>1.25</v>
+        <v>1.15</v>
       </c>
       <c r="AR93">
         <v>1.61</v>
@@ -20507,7 +20519,7 @@
         <v>150</v>
       </c>
       <c r="P94" t="s">
-        <v>264</v>
+        <v>266</v>
       </c>
       <c r="Q94">
         <v>3</v>
@@ -20794,7 +20806,7 @@
         <v>1.46</v>
       </c>
       <c r="AQ95">
-        <v>0.83</v>
+        <v>1</v>
       </c>
       <c r="AR95">
         <v>1.43</v>
@@ -21203,7 +21215,7 @@
         <v>2.5</v>
       </c>
       <c r="AP97">
-        <v>2.42</v>
+        <v>2.23</v>
       </c>
       <c r="AQ97">
         <v>2</v>
@@ -21949,7 +21961,7 @@
         <v>156</v>
       </c>
       <c r="P101" t="s">
-        <v>265</v>
+        <v>267</v>
       </c>
       <c r="Q101">
         <v>1.83</v>
@@ -22030,7 +22042,7 @@
         <v>2.23</v>
       </c>
       <c r="AQ101">
-        <v>1.62</v>
+        <v>1.71</v>
       </c>
       <c r="AR101">
         <v>1.9</v>
@@ -22233,7 +22245,7 @@
         <v>1.2</v>
       </c>
       <c r="AP102">
-        <v>0.23</v>
+        <v>0.21</v>
       </c>
       <c r="AQ102">
         <v>1</v>
@@ -23266,7 +23278,7 @@
         <v>0.77</v>
       </c>
       <c r="AQ107">
-        <v>1.25</v>
+        <v>1.15</v>
       </c>
       <c r="AR107">
         <v>1.14</v>
@@ -23472,7 +23484,7 @@
         <v>1.54</v>
       </c>
       <c r="AQ108">
-        <v>1</v>
+        <v>1.17</v>
       </c>
       <c r="AR108">
         <v>1.5</v>
@@ -23597,7 +23609,7 @@
         <v>161</v>
       </c>
       <c r="P109" t="s">
-        <v>266</v>
+        <v>268</v>
       </c>
       <c r="Q109">
         <v>2.24</v>
@@ -23803,7 +23815,7 @@
         <v>162</v>
       </c>
       <c r="P110" t="s">
-        <v>267</v>
+        <v>269</v>
       </c>
       <c r="Q110">
         <v>4.6</v>
@@ -24087,7 +24099,7 @@
         <v>1.71</v>
       </c>
       <c r="AP111">
-        <v>2.42</v>
+        <v>2.23</v>
       </c>
       <c r="AQ111">
         <v>1.46</v>
@@ -24215,7 +24227,7 @@
         <v>164</v>
       </c>
       <c r="P112" t="s">
-        <v>224</v>
+        <v>218</v>
       </c>
       <c r="Q112">
         <v>1.44</v>
@@ -24296,7 +24308,7 @@
         <v>3</v>
       </c>
       <c r="AQ112">
-        <v>0.83</v>
+        <v>1</v>
       </c>
       <c r="AR112">
         <v>2.21</v>
@@ -24421,7 +24433,7 @@
         <v>165</v>
       </c>
       <c r="P113" t="s">
-        <v>268</v>
+        <v>270</v>
       </c>
       <c r="Q113">
         <v>3.25</v>
@@ -24502,7 +24514,7 @@
         <v>2</v>
       </c>
       <c r="AQ113">
-        <v>1.62</v>
+        <v>1.71</v>
       </c>
       <c r="AR113">
         <v>1.63</v>
@@ -24627,7 +24639,7 @@
         <v>151</v>
       </c>
       <c r="P114" t="s">
-        <v>269</v>
+        <v>271</v>
       </c>
       <c r="Q114">
         <v>2.88</v>
@@ -24833,7 +24845,7 @@
         <v>99</v>
       </c>
       <c r="P115" t="s">
-        <v>270</v>
+        <v>272</v>
       </c>
       <c r="Q115">
         <v>1.73</v>
@@ -25039,7 +25051,7 @@
         <v>88</v>
       </c>
       <c r="P116" t="s">
-        <v>271</v>
+        <v>273</v>
       </c>
       <c r="Q116">
         <v>4.33</v>
@@ -25657,7 +25669,7 @@
         <v>88</v>
       </c>
       <c r="P119" t="s">
-        <v>272</v>
+        <v>274</v>
       </c>
       <c r="Q119">
         <v>15</v>
@@ -25735,7 +25747,7 @@
         <v>2.33</v>
       </c>
       <c r="AP119">
-        <v>0.23</v>
+        <v>0.21</v>
       </c>
       <c r="AQ119">
         <v>2.23</v>
@@ -25863,7 +25875,7 @@
         <v>168</v>
       </c>
       <c r="P120" t="s">
-        <v>273</v>
+        <v>275</v>
       </c>
       <c r="Q120">
         <v>3</v>
@@ -25941,7 +25953,7 @@
         <v>1.17</v>
       </c>
       <c r="AP120">
-        <v>1.67</v>
+        <v>1.54</v>
       </c>
       <c r="AQ120">
         <v>1</v>
@@ -26147,7 +26159,7 @@
         <v>1.17</v>
       </c>
       <c r="AP121">
-        <v>1.67</v>
+        <v>1.54</v>
       </c>
       <c r="AQ121">
         <v>0.85</v>
@@ -26275,7 +26287,7 @@
         <v>170</v>
       </c>
       <c r="P122" t="s">
-        <v>274</v>
+        <v>276</v>
       </c>
       <c r="Q122">
         <v>3.25</v>
@@ -26687,7 +26699,7 @@
         <v>172</v>
       </c>
       <c r="P124" t="s">
-        <v>223</v>
+        <v>226</v>
       </c>
       <c r="Q124">
         <v>1.83</v>
@@ -26768,7 +26780,7 @@
         <v>2.5</v>
       </c>
       <c r="AQ124">
-        <v>0.83</v>
+        <v>1</v>
       </c>
       <c r="AR124">
         <v>1.87</v>
@@ -26893,7 +26905,7 @@
         <v>171</v>
       </c>
       <c r="P125" t="s">
-        <v>275</v>
+        <v>277</v>
       </c>
       <c r="Q125">
         <v>6.3</v>
@@ -27386,7 +27398,7 @@
         <v>1.46</v>
       </c>
       <c r="AQ127">
-        <v>1</v>
+        <v>1.17</v>
       </c>
       <c r="AR127">
         <v>1.5</v>
@@ -27717,7 +27729,7 @@
         <v>174</v>
       </c>
       <c r="P129" t="s">
-        <v>276</v>
+        <v>278</v>
       </c>
       <c r="Q129">
         <v>2.1</v>
@@ -27795,10 +27807,10 @@
         <v>1.38</v>
       </c>
       <c r="AP129">
-        <v>2.42</v>
+        <v>2.23</v>
       </c>
       <c r="AQ129">
-        <v>1.25</v>
+        <v>1.15</v>
       </c>
       <c r="AR129">
         <v>1.69</v>
@@ -27923,7 +27935,7 @@
         <v>175</v>
       </c>
       <c r="P130" t="s">
-        <v>277</v>
+        <v>279</v>
       </c>
       <c r="Q130">
         <v>1.5</v>
@@ -28004,7 +28016,7 @@
         <v>2.23</v>
       </c>
       <c r="AQ130">
-        <v>0.83</v>
+        <v>1</v>
       </c>
       <c r="AR130">
         <v>1.93</v>
@@ -28129,7 +28141,7 @@
         <v>176</v>
       </c>
       <c r="P131" t="s">
-        <v>278</v>
+        <v>280</v>
       </c>
       <c r="Q131">
         <v>3.5</v>
@@ -28335,7 +28347,7 @@
         <v>177</v>
       </c>
       <c r="P132" t="s">
-        <v>279</v>
+        <v>281</v>
       </c>
       <c r="Q132">
         <v>4.04</v>
@@ -28747,7 +28759,7 @@
         <v>88</v>
       </c>
       <c r="P134" t="s">
-        <v>280</v>
+        <v>282</v>
       </c>
       <c r="Q134">
         <v>2.75</v>
@@ -28828,7 +28840,7 @@
         <v>1.08</v>
       </c>
       <c r="AQ134">
-        <v>1</v>
+        <v>1.17</v>
       </c>
       <c r="AR134">
         <v>1.51</v>
@@ -29443,7 +29455,7 @@
         <v>1</v>
       </c>
       <c r="AP137">
-        <v>2.42</v>
+        <v>2.23</v>
       </c>
       <c r="AQ137">
         <v>0.77</v>
@@ -29571,7 +29583,7 @@
         <v>91</v>
       </c>
       <c r="P138" t="s">
-        <v>268</v>
+        <v>270</v>
       </c>
       <c r="Q138">
         <v>2.25</v>
@@ -29777,7 +29789,7 @@
         <v>179</v>
       </c>
       <c r="P139" t="s">
-        <v>277</v>
+        <v>279</v>
       </c>
       <c r="Q139">
         <v>1.9</v>
@@ -30189,7 +30201,7 @@
         <v>88</v>
       </c>
       <c r="P141" t="s">
-        <v>281</v>
+        <v>283</v>
       </c>
       <c r="Q141">
         <v>4</v>
@@ -30267,7 +30279,7 @@
         <v>1.13</v>
       </c>
       <c r="AP141">
-        <v>0.23</v>
+        <v>0.21</v>
       </c>
       <c r="AQ141">
         <v>1.15</v>
@@ -30395,7 +30407,7 @@
         <v>117</v>
       </c>
       <c r="P142" t="s">
-        <v>282</v>
+        <v>284</v>
       </c>
       <c r="Q142">
         <v>4</v>
@@ -30807,7 +30819,7 @@
         <v>182</v>
       </c>
       <c r="P144" t="s">
-        <v>283</v>
+        <v>285</v>
       </c>
       <c r="Q144">
         <v>6</v>
@@ -30885,7 +30897,7 @@
         <v>2.5</v>
       </c>
       <c r="AP144">
-        <v>1.67</v>
+        <v>1.54</v>
       </c>
       <c r="AQ144">
         <v>2.23</v>
@@ -31013,7 +31025,7 @@
         <v>88</v>
       </c>
       <c r="P145" t="s">
-        <v>284</v>
+        <v>286</v>
       </c>
       <c r="Q145">
         <v>3.5</v>
@@ -31094,7 +31106,7 @@
         <v>1.54</v>
       </c>
       <c r="AQ145">
-        <v>1.62</v>
+        <v>1.71</v>
       </c>
       <c r="AR145">
         <v>1.32</v>
@@ -31219,7 +31231,7 @@
         <v>183</v>
       </c>
       <c r="P146" t="s">
-        <v>285</v>
+        <v>287</v>
       </c>
       <c r="Q146">
         <v>4.33</v>
@@ -31300,7 +31312,7 @@
         <v>0.92</v>
       </c>
       <c r="AQ146">
-        <v>1</v>
+        <v>1.17</v>
       </c>
       <c r="AR146">
         <v>1.22</v>
@@ -31425,7 +31437,7 @@
         <v>184</v>
       </c>
       <c r="P147" t="s">
-        <v>286</v>
+        <v>288</v>
       </c>
       <c r="Q147">
         <v>3.8</v>
@@ -31631,7 +31643,7 @@
         <v>185</v>
       </c>
       <c r="P148" t="s">
-        <v>287</v>
+        <v>289</v>
       </c>
       <c r="Q148">
         <v>2.5</v>
@@ -31712,7 +31724,7 @@
         <v>1.08</v>
       </c>
       <c r="AQ148">
-        <v>0.83</v>
+        <v>1</v>
       </c>
       <c r="AR148">
         <v>1.47</v>
@@ -31837,7 +31849,7 @@
         <v>186</v>
       </c>
       <c r="P149" t="s">
-        <v>284</v>
+        <v>286</v>
       </c>
       <c r="Q149">
         <v>2.05</v>
@@ -32043,7 +32055,7 @@
         <v>187</v>
       </c>
       <c r="P150" t="s">
-        <v>288</v>
+        <v>290</v>
       </c>
       <c r="Q150">
         <v>1.95</v>
@@ -32124,7 +32136,7 @@
         <v>2.23</v>
       </c>
       <c r="AQ150">
-        <v>1.25</v>
+        <v>1.15</v>
       </c>
       <c r="AR150">
         <v>1.98</v>
@@ -32249,7 +32261,7 @@
         <v>188</v>
       </c>
       <c r="P151" t="s">
-        <v>289</v>
+        <v>291</v>
       </c>
       <c r="Q151">
         <v>2.48</v>
@@ -32661,7 +32673,7 @@
         <v>190</v>
       </c>
       <c r="P153" t="s">
-        <v>290</v>
+        <v>292</v>
       </c>
       <c r="Q153">
         <v>1.4</v>
@@ -32739,7 +32751,7 @@
         <v>0.13</v>
       </c>
       <c r="AP153">
-        <v>2.42</v>
+        <v>2.23</v>
       </c>
       <c r="AQ153">
         <v>0.08</v>
@@ -33073,7 +33085,7 @@
         <v>88</v>
       </c>
       <c r="P155" t="s">
-        <v>227</v>
+        <v>229</v>
       </c>
       <c r="Q155">
         <v>3.2</v>
@@ -33154,7 +33166,7 @@
         <v>1.54</v>
       </c>
       <c r="AQ155">
-        <v>1.62</v>
+        <v>1.71</v>
       </c>
       <c r="AR155">
         <v>1.51</v>
@@ -33357,7 +33369,7 @@
         <v>0.22</v>
       </c>
       <c r="AP156">
-        <v>0.23</v>
+        <v>0.21</v>
       </c>
       <c r="AQ156">
         <v>0.62</v>
@@ -33691,7 +33703,7 @@
         <v>88</v>
       </c>
       <c r="P158" t="s">
-        <v>291</v>
+        <v>293</v>
       </c>
       <c r="Q158">
         <v>5</v>
@@ -33897,7 +33909,7 @@
         <v>88</v>
       </c>
       <c r="P159" t="s">
-        <v>248</v>
+        <v>250</v>
       </c>
       <c r="Q159">
         <v>2.38</v>
@@ -34309,7 +34321,7 @@
         <v>193</v>
       </c>
       <c r="P161" t="s">
-        <v>275</v>
+        <v>277</v>
       </c>
       <c r="Q161">
         <v>4.75</v>
@@ -34387,7 +34399,7 @@
         <v>1.89</v>
       </c>
       <c r="AP161">
-        <v>1.67</v>
+        <v>1.54</v>
       </c>
       <c r="AQ161">
         <v>1.85</v>
@@ -34515,7 +34527,7 @@
         <v>194</v>
       </c>
       <c r="P162" t="s">
-        <v>292</v>
+        <v>294</v>
       </c>
       <c r="Q162">
         <v>2.63</v>
@@ -34721,7 +34733,7 @@
         <v>88</v>
       </c>
       <c r="P163" t="s">
-        <v>293</v>
+        <v>295</v>
       </c>
       <c r="Q163">
         <v>11</v>
@@ -34927,7 +34939,7 @@
         <v>195</v>
       </c>
       <c r="P164" t="s">
-        <v>294</v>
+        <v>296</v>
       </c>
       <c r="Q164">
         <v>2</v>
@@ -35005,7 +35017,7 @@
         <v>1.1</v>
       </c>
       <c r="AP164">
-        <v>2.42</v>
+        <v>2.23</v>
       </c>
       <c r="AQ164">
         <v>1</v>
@@ -35133,7 +35145,7 @@
         <v>196</v>
       </c>
       <c r="P165" t="s">
-        <v>295</v>
+        <v>297</v>
       </c>
       <c r="Q165">
         <v>2.5</v>
@@ -35832,7 +35844,7 @@
         <v>2.23</v>
       </c>
       <c r="AQ168">
-        <v>1</v>
+        <v>1.17</v>
       </c>
       <c r="AR168">
         <v>1.96</v>
@@ -36035,7 +36047,7 @@
         <v>0.55</v>
       </c>
       <c r="AP169">
-        <v>1.67</v>
+        <v>1.54</v>
       </c>
       <c r="AQ169">
         <v>0.46</v>
@@ -36369,7 +36381,7 @@
         <v>201</v>
       </c>
       <c r="P171" t="s">
-        <v>296</v>
+        <v>298</v>
       </c>
       <c r="Q171">
         <v>5.2</v>
@@ -36447,10 +36459,10 @@
         <v>1.1</v>
       </c>
       <c r="AP171">
-        <v>0.23</v>
+        <v>0.21</v>
       </c>
       <c r="AQ171">
-        <v>1.25</v>
+        <v>1.15</v>
       </c>
       <c r="AR171">
         <v>1.3</v>
@@ -36575,7 +36587,7 @@
         <v>202</v>
       </c>
       <c r="P172" t="s">
-        <v>297</v>
+        <v>299</v>
       </c>
       <c r="Q172">
         <v>6.35</v>
@@ -36781,7 +36793,7 @@
         <v>203</v>
       </c>
       <c r="P173" t="s">
-        <v>298</v>
+        <v>300</v>
       </c>
       <c r="Q173">
         <v>2.6</v>
@@ -36987,7 +36999,7 @@
         <v>88</v>
       </c>
       <c r="P174" t="s">
-        <v>299</v>
+        <v>301</v>
       </c>
       <c r="Q174">
         <v>4.86</v>
@@ -37193,7 +37205,7 @@
         <v>204</v>
       </c>
       <c r="P175" t="s">
-        <v>284</v>
+        <v>286</v>
       </c>
       <c r="Q175">
         <v>2.66</v>
@@ -37480,7 +37492,7 @@
         <v>3</v>
       </c>
       <c r="AQ176">
-        <v>1.62</v>
+        <v>1.71</v>
       </c>
       <c r="AR176">
         <v>2.32</v>
@@ -37605,7 +37617,7 @@
         <v>171</v>
       </c>
       <c r="P177" t="s">
-        <v>300</v>
+        <v>302</v>
       </c>
       <c r="Q177">
         <v>3.63</v>
@@ -38017,7 +38029,7 @@
         <v>88</v>
       </c>
       <c r="P179" t="s">
-        <v>301</v>
+        <v>303</v>
       </c>
       <c r="Q179">
         <v>3.92</v>
@@ -38223,7 +38235,7 @@
         <v>206</v>
       </c>
       <c r="P180" t="s">
-        <v>302</v>
+        <v>304</v>
       </c>
       <c r="Q180">
         <v>1.32</v>
@@ -38716,7 +38728,7 @@
         <v>2</v>
       </c>
       <c r="AQ182">
-        <v>0.83</v>
+        <v>1</v>
       </c>
       <c r="AR182">
         <v>1.67</v>
@@ -38841,7 +38853,7 @@
         <v>208</v>
       </c>
       <c r="P183" t="s">
-        <v>303</v>
+        <v>305</v>
       </c>
       <c r="Q183">
         <v>4.3</v>
@@ -38919,7 +38931,7 @@
         <v>2.36</v>
       </c>
       <c r="AP183">
-        <v>2.42</v>
+        <v>2.23</v>
       </c>
       <c r="AQ183">
         <v>2.23</v>
@@ -39047,7 +39059,7 @@
         <v>88</v>
       </c>
       <c r="P184" t="s">
-        <v>304</v>
+        <v>306</v>
       </c>
       <c r="Q184">
         <v>5.8</v>
@@ -39125,10 +39137,10 @@
         <v>1.5</v>
       </c>
       <c r="AP184">
-        <v>0.23</v>
+        <v>0.21</v>
       </c>
       <c r="AQ184">
-        <v>1.62</v>
+        <v>1.71</v>
       </c>
       <c r="AR184">
         <v>1.24</v>
@@ -39334,7 +39346,7 @@
         <v>1.54</v>
       </c>
       <c r="AQ185">
-        <v>1.25</v>
+        <v>1.15</v>
       </c>
       <c r="AR185">
         <v>1.46</v>
@@ -39459,7 +39471,7 @@
         <v>96</v>
       </c>
       <c r="P186" t="s">
-        <v>305</v>
+        <v>307</v>
       </c>
       <c r="Q186">
         <v>4.7</v>
@@ -39537,7 +39549,7 @@
         <v>2.09</v>
       </c>
       <c r="AP186">
-        <v>1.67</v>
+        <v>1.54</v>
       </c>
       <c r="AQ186">
         <v>2</v>
@@ -40077,7 +40089,7 @@
         <v>88</v>
       </c>
       <c r="P189" t="s">
-        <v>306</v>
+        <v>308</v>
       </c>
       <c r="Q189">
         <v>4.5</v>
@@ -41519,7 +41531,7 @@
         <v>215</v>
       </c>
       <c r="P196" t="s">
-        <v>223</v>
+        <v>226</v>
       </c>
       <c r="Q196">
         <v>1.95</v>
@@ -41725,7 +41737,7 @@
         <v>88</v>
       </c>
       <c r="P197" t="s">
-        <v>223</v>
+        <v>226</v>
       </c>
       <c r="Q197">
         <v>2.88</v>
@@ -42012,7 +42024,7 @@
         <v>1.54</v>
       </c>
       <c r="AQ198">
-        <v>0.83</v>
+        <v>1</v>
       </c>
       <c r="AR198">
         <v>1.45</v>
@@ -42424,7 +42436,7 @@
         <v>0.92</v>
       </c>
       <c r="AQ200">
-        <v>0.83</v>
+        <v>1</v>
       </c>
       <c r="AR200">
         <v>1.2</v>
@@ -42549,7 +42561,7 @@
         <v>158</v>
       </c>
       <c r="P201" t="s">
-        <v>307</v>
+        <v>309</v>
       </c>
       <c r="Q201">
         <v>2.63</v>
@@ -42961,7 +42973,7 @@
         <v>88</v>
       </c>
       <c r="P203" t="s">
-        <v>248</v>
+        <v>250</v>
       </c>
       <c r="Q203">
         <v>2.75</v>
@@ -43324,6 +43336,830 @@
       </c>
       <c r="BP204">
         <v>1.44</v>
+      </c>
+    </row>
+    <row r="205" spans="1:68">
+      <c r="A205" s="1">
+        <v>204</v>
+      </c>
+      <c r="B205">
+        <v>7468292</v>
+      </c>
+      <c r="C205" t="s">
+        <v>68</v>
+      </c>
+      <c r="D205" t="s">
+        <v>69</v>
+      </c>
+      <c r="E205" s="2">
+        <v>45732.375</v>
+      </c>
+      <c r="F205">
+        <v>26</v>
+      </c>
+      <c r="G205" t="s">
+        <v>85</v>
+      </c>
+      <c r="H205" t="s">
+        <v>77</v>
+      </c>
+      <c r="I205">
+        <v>0</v>
+      </c>
+      <c r="J205">
+        <v>2</v>
+      </c>
+      <c r="K205">
+        <v>2</v>
+      </c>
+      <c r="L205">
+        <v>1</v>
+      </c>
+      <c r="M205">
+        <v>2</v>
+      </c>
+      <c r="N205">
+        <v>3</v>
+      </c>
+      <c r="O205" t="s">
+        <v>218</v>
+      </c>
+      <c r="P205" t="s">
+        <v>310</v>
+      </c>
+      <c r="Q205">
+        <v>2.88</v>
+      </c>
+      <c r="R205">
+        <v>2.05</v>
+      </c>
+      <c r="S205">
+        <v>4</v>
+      </c>
+      <c r="T205">
+        <v>1.44</v>
+      </c>
+      <c r="U205">
+        <v>2.63</v>
+      </c>
+      <c r="V205">
+        <v>3.25</v>
+      </c>
+      <c r="W205">
+        <v>1.33</v>
+      </c>
+      <c r="X205">
+        <v>10</v>
+      </c>
+      <c r="Y205">
+        <v>1.06</v>
+      </c>
+      <c r="Z205">
+        <v>2.18</v>
+      </c>
+      <c r="AA205">
+        <v>3.25</v>
+      </c>
+      <c r="AB205">
+        <v>3.45</v>
+      </c>
+      <c r="AC205">
+        <v>1.07</v>
+      </c>
+      <c r="AD205">
+        <v>7.5</v>
+      </c>
+      <c r="AE205">
+        <v>1.36</v>
+      </c>
+      <c r="AF205">
+        <v>2.95</v>
+      </c>
+      <c r="AG205">
+        <v>2.2</v>
+      </c>
+      <c r="AH205">
+        <v>1.58</v>
+      </c>
+      <c r="AI205">
+        <v>1.91</v>
+      </c>
+      <c r="AJ205">
+        <v>1.91</v>
+      </c>
+      <c r="AK205">
+        <v>1.32</v>
+      </c>
+      <c r="AL205">
+        <v>1.32</v>
+      </c>
+      <c r="AM205">
+        <v>1.65</v>
+      </c>
+      <c r="AN205">
+        <v>1.67</v>
+      </c>
+      <c r="AO205">
+        <v>1</v>
+      </c>
+      <c r="AP205">
+        <v>1.54</v>
+      </c>
+      <c r="AQ205">
+        <v>1.17</v>
+      </c>
+      <c r="AR205">
+        <v>1.56</v>
+      </c>
+      <c r="AS205">
+        <v>1.24</v>
+      </c>
+      <c r="AT205">
+        <v>2.8</v>
+      </c>
+      <c r="AU205">
+        <v>3</v>
+      </c>
+      <c r="AV205">
+        <v>5</v>
+      </c>
+      <c r="AW205">
+        <v>9</v>
+      </c>
+      <c r="AX205">
+        <v>8</v>
+      </c>
+      <c r="AY205">
+        <v>12</v>
+      </c>
+      <c r="AZ205">
+        <v>13</v>
+      </c>
+      <c r="BA205">
+        <v>6</v>
+      </c>
+      <c r="BB205">
+        <v>6</v>
+      </c>
+      <c r="BC205">
+        <v>12</v>
+      </c>
+      <c r="BD205">
+        <v>1.8</v>
+      </c>
+      <c r="BE205">
+        <v>8.5</v>
+      </c>
+      <c r="BF205">
+        <v>2.2</v>
+      </c>
+      <c r="BG205">
+        <v>1.2</v>
+      </c>
+      <c r="BH205">
+        <v>3.95</v>
+      </c>
+      <c r="BI205">
+        <v>1.28</v>
+      </c>
+      <c r="BJ205">
+        <v>3.08</v>
+      </c>
+      <c r="BK205">
+        <v>1.52</v>
+      </c>
+      <c r="BL205">
+        <v>2.3</v>
+      </c>
+      <c r="BM205">
+        <v>1.91</v>
+      </c>
+      <c r="BN205">
+        <v>1.8</v>
+      </c>
+      <c r="BO205">
+        <v>2.4</v>
+      </c>
+      <c r="BP205">
+        <v>1.48</v>
+      </c>
+    </row>
+    <row r="206" spans="1:68">
+      <c r="A206" s="1">
+        <v>205</v>
+      </c>
+      <c r="B206">
+        <v>7468286</v>
+      </c>
+      <c r="C206" t="s">
+        <v>68</v>
+      </c>
+      <c r="D206" t="s">
+        <v>69</v>
+      </c>
+      <c r="E206" s="2">
+        <v>45732.47916666666</v>
+      </c>
+      <c r="F206">
+        <v>26</v>
+      </c>
+      <c r="G206" t="s">
+        <v>84</v>
+      </c>
+      <c r="H206" t="s">
+        <v>83</v>
+      </c>
+      <c r="I206">
+        <v>0</v>
+      </c>
+      <c r="J206">
+        <v>1</v>
+      </c>
+      <c r="K206">
+        <v>1</v>
+      </c>
+      <c r="L206">
+        <v>0</v>
+      </c>
+      <c r="M206">
+        <v>1</v>
+      </c>
+      <c r="N206">
+        <v>1</v>
+      </c>
+      <c r="O206" t="s">
+        <v>88</v>
+      </c>
+      <c r="P206" t="s">
+        <v>271</v>
+      </c>
+      <c r="Q206">
+        <v>2.38</v>
+      </c>
+      <c r="R206">
+        <v>2.3</v>
+      </c>
+      <c r="S206">
+        <v>4.5</v>
+      </c>
+      <c r="T206">
+        <v>1.33</v>
+      </c>
+      <c r="U206">
+        <v>3.25</v>
+      </c>
+      <c r="V206">
+        <v>2.63</v>
+      </c>
+      <c r="W206">
+        <v>1.44</v>
+      </c>
+      <c r="X206">
+        <v>6.5</v>
+      </c>
+      <c r="Y206">
+        <v>1.11</v>
+      </c>
+      <c r="Z206">
+        <v>1.75</v>
+      </c>
+      <c r="AA206">
+        <v>3.6</v>
+      </c>
+      <c r="AB206">
+        <v>4</v>
+      </c>
+      <c r="AC206">
+        <v>1.04</v>
+      </c>
+      <c r="AD206">
+        <v>9</v>
+      </c>
+      <c r="AE206">
+        <v>1.22</v>
+      </c>
+      <c r="AF206">
+        <v>4</v>
+      </c>
+      <c r="AG206">
+        <v>1.7</v>
+      </c>
+      <c r="AH206">
+        <v>2.1</v>
+      </c>
+      <c r="AI206">
+        <v>1.7</v>
+      </c>
+      <c r="AJ206">
+        <v>2.05</v>
+      </c>
+      <c r="AK206">
+        <v>1.24</v>
+      </c>
+      <c r="AL206">
+        <v>1.26</v>
+      </c>
+      <c r="AM206">
+        <v>1.93</v>
+      </c>
+      <c r="AN206">
+        <v>2.42</v>
+      </c>
+      <c r="AO206">
+        <v>1.62</v>
+      </c>
+      <c r="AP206">
+        <v>2.23</v>
+      </c>
+      <c r="AQ206">
+        <v>1.71</v>
+      </c>
+      <c r="AR206">
+        <v>1.77</v>
+      </c>
+      <c r="AS206">
+        <v>1.75</v>
+      </c>
+      <c r="AT206">
+        <v>3.52</v>
+      </c>
+      <c r="AU206">
+        <v>5</v>
+      </c>
+      <c r="AV206">
+        <v>2</v>
+      </c>
+      <c r="AW206">
+        <v>10</v>
+      </c>
+      <c r="AX206">
+        <v>7</v>
+      </c>
+      <c r="AY206">
+        <v>15</v>
+      </c>
+      <c r="AZ206">
+        <v>9</v>
+      </c>
+      <c r="BA206">
+        <v>5</v>
+      </c>
+      <c r="BB206">
+        <v>4</v>
+      </c>
+      <c r="BC206">
+        <v>9</v>
+      </c>
+      <c r="BD206">
+        <v>1.67</v>
+      </c>
+      <c r="BE206">
+        <v>8.5</v>
+      </c>
+      <c r="BF206">
+        <v>2.45</v>
+      </c>
+      <c r="BG206">
+        <v>1.17</v>
+      </c>
+      <c r="BH206">
+        <v>4.35</v>
+      </c>
+      <c r="BI206">
+        <v>1.26</v>
+      </c>
+      <c r="BJ206">
+        <v>3.22</v>
+      </c>
+      <c r="BK206">
+        <v>1.53</v>
+      </c>
+      <c r="BL206">
+        <v>2.43</v>
+      </c>
+      <c r="BM206">
+        <v>1.91</v>
+      </c>
+      <c r="BN206">
+        <v>1.89</v>
+      </c>
+      <c r="BO206">
+        <v>2.34</v>
+      </c>
+      <c r="BP206">
+        <v>1.56</v>
+      </c>
+    </row>
+    <row r="207" spans="1:68">
+      <c r="A207" s="1">
+        <v>206</v>
+      </c>
+      <c r="B207">
+        <v>7468293</v>
+      </c>
+      <c r="C207" t="s">
+        <v>68</v>
+      </c>
+      <c r="D207" t="s">
+        <v>69</v>
+      </c>
+      <c r="E207" s="2">
+        <v>45732.47916666666</v>
+      </c>
+      <c r="F207">
+        <v>26</v>
+      </c>
+      <c r="G207" t="s">
+        <v>72</v>
+      </c>
+      <c r="H207" t="s">
+        <v>75</v>
+      </c>
+      <c r="I207">
+        <v>2</v>
+      </c>
+      <c r="J207">
+        <v>1</v>
+      </c>
+      <c r="K207">
+        <v>3</v>
+      </c>
+      <c r="L207">
+        <v>2</v>
+      </c>
+      <c r="M207">
+        <v>3</v>
+      </c>
+      <c r="N207">
+        <v>5</v>
+      </c>
+      <c r="O207" t="s">
+        <v>219</v>
+      </c>
+      <c r="P207" t="s">
+        <v>311</v>
+      </c>
+      <c r="Q207">
+        <v>4.75</v>
+      </c>
+      <c r="R207">
+        <v>2.3</v>
+      </c>
+      <c r="S207">
+        <v>2.3</v>
+      </c>
+      <c r="T207">
+        <v>1.33</v>
+      </c>
+      <c r="U207">
+        <v>3.25</v>
+      </c>
+      <c r="V207">
+        <v>2.63</v>
+      </c>
+      <c r="W207">
+        <v>1.44</v>
+      </c>
+      <c r="X207">
+        <v>6.5</v>
+      </c>
+      <c r="Y207">
+        <v>1.11</v>
+      </c>
+      <c r="Z207">
+        <v>3.83</v>
+      </c>
+      <c r="AA207">
+        <v>3.43</v>
+      </c>
+      <c r="AB207">
+        <v>1.7</v>
+      </c>
+      <c r="AC207">
+        <v>1.05</v>
+      </c>
+      <c r="AD207">
+        <v>8.5</v>
+      </c>
+      <c r="AE207">
+        <v>1.28</v>
+      </c>
+      <c r="AF207">
+        <v>3.4</v>
+      </c>
+      <c r="AG207">
+        <v>1.73</v>
+      </c>
+      <c r="AH207">
+        <v>2.08</v>
+      </c>
+      <c r="AI207">
+        <v>1.7</v>
+      </c>
+      <c r="AJ207">
+        <v>2.05</v>
+      </c>
+      <c r="AK207">
+        <v>1.72</v>
+      </c>
+      <c r="AL207">
+        <v>1.29</v>
+      </c>
+      <c r="AM207">
+        <v>1.3</v>
+      </c>
+      <c r="AN207">
+        <v>0.23</v>
+      </c>
+      <c r="AO207">
+        <v>0.83</v>
+      </c>
+      <c r="AP207">
+        <v>0.21</v>
+      </c>
+      <c r="AQ207">
+        <v>1</v>
+      </c>
+      <c r="AR207">
+        <v>1.21</v>
+      </c>
+      <c r="AS207">
+        <v>1.34</v>
+      </c>
+      <c r="AT207">
+        <v>2.55</v>
+      </c>
+      <c r="AU207">
+        <v>4</v>
+      </c>
+      <c r="AV207">
+        <v>8</v>
+      </c>
+      <c r="AW207">
+        <v>6</v>
+      </c>
+      <c r="AX207">
+        <v>7</v>
+      </c>
+      <c r="AY207">
+        <v>10</v>
+      </c>
+      <c r="AZ207">
+        <v>15</v>
+      </c>
+      <c r="BA207">
+        <v>3</v>
+      </c>
+      <c r="BB207">
+        <v>4</v>
+      </c>
+      <c r="BC207">
+        <v>7</v>
+      </c>
+      <c r="BD207">
+        <v>2.15</v>
+      </c>
+      <c r="BE207">
+        <v>8.5</v>
+      </c>
+      <c r="BF207">
+        <v>1.85</v>
+      </c>
+      <c r="BG207">
+        <v>1.25</v>
+      </c>
+      <c r="BH207">
+        <v>3.45</v>
+      </c>
+      <c r="BI207">
+        <v>1.27</v>
+      </c>
+      <c r="BJ207">
+        <v>3.14</v>
+      </c>
+      <c r="BK207">
+        <v>1.56</v>
+      </c>
+      <c r="BL207">
+        <v>2.36</v>
+      </c>
+      <c r="BM207">
+        <v>1.92</v>
+      </c>
+      <c r="BN207">
+        <v>1.88</v>
+      </c>
+      <c r="BO207">
+        <v>2.39</v>
+      </c>
+      <c r="BP207">
+        <v>1.54</v>
+      </c>
+    </row>
+    <row r="208" spans="1:68">
+      <c r="A208" s="1">
+        <v>207</v>
+      </c>
+      <c r="B208">
+        <v>7468289</v>
+      </c>
+      <c r="C208" t="s">
+        <v>68</v>
+      </c>
+      <c r="D208" t="s">
+        <v>69</v>
+      </c>
+      <c r="E208" s="2">
+        <v>45732.60416666666</v>
+      </c>
+      <c r="F208">
+        <v>26</v>
+      </c>
+      <c r="G208" t="s">
+        <v>80</v>
+      </c>
+      <c r="H208" t="s">
+        <v>71</v>
+      </c>
+      <c r="I208">
+        <v>3</v>
+      </c>
+      <c r="J208">
+        <v>0</v>
+      </c>
+      <c r="K208">
+        <v>3</v>
+      </c>
+      <c r="L208">
+        <v>3</v>
+      </c>
+      <c r="M208">
+        <v>0</v>
+      </c>
+      <c r="N208">
+        <v>3</v>
+      </c>
+      <c r="O208" t="s">
+        <v>220</v>
+      </c>
+      <c r="P208" t="s">
+        <v>88</v>
+      </c>
+      <c r="Q208">
+        <v>1.8</v>
+      </c>
+      <c r="R208">
+        <v>2.5</v>
+      </c>
+      <c r="S208">
+        <v>8.5</v>
+      </c>
+      <c r="T208">
+        <v>1.33</v>
+      </c>
+      <c r="U208">
+        <v>3.25</v>
+      </c>
+      <c r="V208">
+        <v>2.63</v>
+      </c>
+      <c r="W208">
+        <v>1.44</v>
+      </c>
+      <c r="X208">
+        <v>6.5</v>
+      </c>
+      <c r="Y208">
+        <v>1.11</v>
+      </c>
+      <c r="Z208">
+        <v>1.3</v>
+      </c>
+      <c r="AA208">
+        <v>4.8</v>
+      </c>
+      <c r="AB208">
+        <v>10</v>
+      </c>
+      <c r="AC208">
+        <v>1.04</v>
+      </c>
+      <c r="AD208">
+        <v>9.5</v>
+      </c>
+      <c r="AE208">
+        <v>1.22</v>
+      </c>
+      <c r="AF208">
+        <v>3.85</v>
+      </c>
+      <c r="AG208">
+        <v>1.7</v>
+      </c>
+      <c r="AH208">
+        <v>2.1</v>
+      </c>
+      <c r="AI208">
+        <v>2.1</v>
+      </c>
+      <c r="AJ208">
+        <v>1.67</v>
+      </c>
+      <c r="AK208">
+        <v>1.07</v>
+      </c>
+      <c r="AL208">
+        <v>1.16</v>
+      </c>
+      <c r="AM208">
+        <v>3.25</v>
+      </c>
+      <c r="AN208">
+        <v>3</v>
+      </c>
+      <c r="AO208">
+        <v>1.25</v>
+      </c>
+      <c r="AP208">
+        <v>3</v>
+      </c>
+      <c r="AQ208">
+        <v>1.15</v>
+      </c>
+      <c r="AR208">
+        <v>2.31</v>
+      </c>
+      <c r="AS208">
+        <v>1.42</v>
+      </c>
+      <c r="AT208">
+        <v>3.73</v>
+      </c>
+      <c r="AU208">
+        <v>7</v>
+      </c>
+      <c r="AV208">
+        <v>2</v>
+      </c>
+      <c r="AW208">
+        <v>3</v>
+      </c>
+      <c r="AX208">
+        <v>1</v>
+      </c>
+      <c r="AY208">
+        <v>10</v>
+      </c>
+      <c r="AZ208">
+        <v>3</v>
+      </c>
+      <c r="BA208">
+        <v>6</v>
+      </c>
+      <c r="BB208">
+        <v>2</v>
+      </c>
+      <c r="BC208">
+        <v>8</v>
+      </c>
+      <c r="BD208">
+        <v>1.18</v>
+      </c>
+      <c r="BE208">
+        <v>13</v>
+      </c>
+      <c r="BF208">
+        <v>5</v>
+      </c>
+      <c r="BG208">
+        <v>1.22</v>
+      </c>
+      <c r="BH208">
+        <v>3.8</v>
+      </c>
+      <c r="BI208">
+        <v>1.26</v>
+      </c>
+      <c r="BJ208">
+        <v>3.22</v>
+      </c>
+      <c r="BK208">
+        <v>1.48</v>
+      </c>
+      <c r="BL208">
+        <v>2.4</v>
+      </c>
+      <c r="BM208">
+        <v>1.85</v>
+      </c>
+      <c r="BN208">
+        <v>1.85</v>
+      </c>
+      <c r="BO208">
+        <v>2.3</v>
+      </c>
+      <c r="BP208">
+        <v>1.52</v>
       </c>
     </row>
   </sheetData>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Czech Republic First League_20242025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Czech Republic First League_20242025.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1310" uniqueCount="312">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1340" uniqueCount="315">
   <si>
     <t>Id_Jogo</t>
   </si>
@@ -679,6 +679,9 @@
     <t>['9', '18', '34']</t>
   </si>
   <si>
+    <t>['17', '34', '67', '84', '90+1']</t>
+  </si>
+  <si>
     <t>['25']</t>
   </si>
   <si>
@@ -950,6 +953,12 @@
   </si>
   <si>
     <t>['26', '64', '72']</t>
+  </si>
+  <si>
+    <t>['10', '58']</t>
+  </si>
+  <si>
+    <t>['13', '19', '28', '36']</t>
   </si>
 </sst>
 </file>
@@ -1311,7 +1320,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:BP208"/>
+  <dimension ref="A1:BP213"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:68">
@@ -1567,7 +1576,7 @@
         <v>86</v>
       </c>
       <c r="P2" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="Q2">
         <v>1.53</v>
@@ -1648,7 +1657,7 @@
         <v>2.23</v>
       </c>
       <c r="AQ2">
-        <v>0.46</v>
+        <v>0.43</v>
       </c>
       <c r="AR2">
         <v>0</v>
@@ -1851,7 +1860,7 @@
         <v>0</v>
       </c>
       <c r="AP3">
-        <v>2</v>
+        <v>1.93</v>
       </c>
       <c r="AQ3">
         <v>1.15</v>
@@ -1979,7 +1988,7 @@
         <v>88</v>
       </c>
       <c r="P4" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="Q4">
         <v>2.88</v>
@@ -2060,7 +2069,7 @@
         <v>0.21</v>
       </c>
       <c r="AQ4">
-        <v>1.38</v>
+        <v>1.36</v>
       </c>
       <c r="AR4">
         <v>0</v>
@@ -2263,7 +2272,7 @@
         <v>0</v>
       </c>
       <c r="AP5">
-        <v>1.08</v>
+        <v>1.07</v>
       </c>
       <c r="AQ5">
         <v>1.71</v>
@@ -2391,7 +2400,7 @@
         <v>90</v>
       </c>
       <c r="P6" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="Q6">
         <v>5.5</v>
@@ -2469,7 +2478,7 @@
         <v>0</v>
       </c>
       <c r="AP6">
-        <v>0.92</v>
+        <v>0.93</v>
       </c>
       <c r="AQ6">
         <v>1.85</v>
@@ -2597,7 +2606,7 @@
         <v>91</v>
       </c>
       <c r="P7" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="Q7">
         <v>3.2</v>
@@ -2678,7 +2687,7 @@
         <v>1.46</v>
       </c>
       <c r="AQ7">
-        <v>1</v>
+        <v>1.14</v>
       </c>
       <c r="AR7">
         <v>0</v>
@@ -2881,10 +2890,10 @@
         <v>0</v>
       </c>
       <c r="AP8">
-        <v>1.5</v>
+        <v>1.38</v>
       </c>
       <c r="AQ8">
-        <v>2.23</v>
+        <v>2.14</v>
       </c>
       <c r="AR8">
         <v>0</v>
@@ -3090,7 +3099,7 @@
         <v>1.54</v>
       </c>
       <c r="AQ9">
-        <v>0.77</v>
+        <v>0.79</v>
       </c>
       <c r="AR9">
         <v>0</v>
@@ -3293,7 +3302,7 @@
         <v>0</v>
       </c>
       <c r="AP10">
-        <v>0.92</v>
+        <v>0.93</v>
       </c>
       <c r="AQ10">
         <v>1.46</v>
@@ -3421,7 +3430,7 @@
         <v>94</v>
       </c>
       <c r="P11" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="Q11">
         <v>6.5</v>
@@ -3627,7 +3636,7 @@
         <v>88</v>
       </c>
       <c r="P12" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="Q12">
         <v>2.85</v>
@@ -4120,7 +4129,7 @@
         <v>1.54</v>
       </c>
       <c r="AQ14">
-        <v>1.38</v>
+        <v>1.36</v>
       </c>
       <c r="AR14">
         <v>0</v>
@@ -4529,7 +4538,7 @@
         <v>0</v>
       </c>
       <c r="AP16">
-        <v>2.5</v>
+        <v>2.54</v>
       </c>
       <c r="AQ16">
         <v>1.15</v>
@@ -4863,7 +4872,7 @@
         <v>88</v>
       </c>
       <c r="P18" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="Q18">
         <v>5.4</v>
@@ -4944,7 +4953,7 @@
         <v>1.54</v>
       </c>
       <c r="AQ18">
-        <v>2.23</v>
+        <v>2.14</v>
       </c>
       <c r="AR18">
         <v>1.26</v>
@@ -5353,7 +5362,7 @@
         <v>0</v>
       </c>
       <c r="AP20">
-        <v>1.5</v>
+        <v>1.38</v>
       </c>
       <c r="AQ20">
         <v>1.46</v>
@@ -5559,7 +5568,7 @@
         <v>3</v>
       </c>
       <c r="AP21">
-        <v>2</v>
+        <v>1.93</v>
       </c>
       <c r="AQ21">
         <v>1.85</v>
@@ -5768,7 +5777,7 @@
         <v>1.54</v>
       </c>
       <c r="AQ22">
-        <v>0.77</v>
+        <v>0.79</v>
       </c>
       <c r="AR22">
         <v>0</v>
@@ -5893,7 +5902,7 @@
         <v>102</v>
       </c>
       <c r="P23" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="Q23">
         <v>2.6</v>
@@ -5974,7 +5983,7 @@
         <v>0.21</v>
       </c>
       <c r="AQ23">
-        <v>0.46</v>
+        <v>0.43</v>
       </c>
       <c r="AR23">
         <v>1.33</v>
@@ -6099,7 +6108,7 @@
         <v>103</v>
       </c>
       <c r="P24" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="Q24">
         <v>2.75</v>
@@ -6305,7 +6314,7 @@
         <v>88</v>
       </c>
       <c r="P25" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="Q25">
         <v>1.06</v>
@@ -6383,7 +6392,7 @@
         <v>0</v>
       </c>
       <c r="AP25">
-        <v>0.92</v>
+        <v>0.93</v>
       </c>
       <c r="AQ25">
         <v>1.15</v>
@@ -6511,7 +6520,7 @@
         <v>104</v>
       </c>
       <c r="P26" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="Q26">
         <v>6.23</v>
@@ -6589,7 +6598,7 @@
         <v>3</v>
       </c>
       <c r="AP26">
-        <v>1.08</v>
+        <v>1.07</v>
       </c>
       <c r="AQ26">
         <v>2</v>
@@ -6798,7 +6807,7 @@
         <v>1.46</v>
       </c>
       <c r="AQ27">
-        <v>1</v>
+        <v>1.14</v>
       </c>
       <c r="AR27">
         <v>1.06</v>
@@ -7004,7 +7013,7 @@
         <v>3</v>
       </c>
       <c r="AQ28">
-        <v>1.38</v>
+        <v>1.36</v>
       </c>
       <c r="AR28">
         <v>2.4</v>
@@ -7413,7 +7422,7 @@
         <v>0</v>
       </c>
       <c r="AP30">
-        <v>2.5</v>
+        <v>2.54</v>
       </c>
       <c r="AQ30">
         <v>1.17</v>
@@ -8159,7 +8168,7 @@
         <v>111</v>
       </c>
       <c r="P34" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="Q34">
         <v>1.45</v>
@@ -8240,7 +8249,7 @@
         <v>3</v>
       </c>
       <c r="AQ34">
-        <v>0.77</v>
+        <v>0.79</v>
       </c>
       <c r="AR34">
         <v>2.27</v>
@@ -8365,7 +8374,7 @@
         <v>112</v>
       </c>
       <c r="P35" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="Q35">
         <v>2.84</v>
@@ -8571,7 +8580,7 @@
         <v>113</v>
       </c>
       <c r="P36" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="Q36">
         <v>5.63</v>
@@ -8649,7 +8658,7 @@
         <v>3</v>
       </c>
       <c r="AP36">
-        <v>2</v>
+        <v>1.93</v>
       </c>
       <c r="AQ36">
         <v>2</v>
@@ -8777,7 +8786,7 @@
         <v>114</v>
       </c>
       <c r="P37" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="Q37">
         <v>2.58</v>
@@ -9064,7 +9073,7 @@
         <v>1.54</v>
       </c>
       <c r="AQ38">
-        <v>0.46</v>
+        <v>0.43</v>
       </c>
       <c r="AR38">
         <v>1.34</v>
@@ -9189,7 +9198,7 @@
         <v>88</v>
       </c>
       <c r="P39" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="Q39">
         <v>4.75</v>
@@ -9473,7 +9482,7 @@
         <v>0</v>
       </c>
       <c r="AP40">
-        <v>1.5</v>
+        <v>1.38</v>
       </c>
       <c r="AQ40">
         <v>1.71</v>
@@ -9601,7 +9610,7 @@
         <v>117</v>
       </c>
       <c r="P41" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="Q41">
         <v>2.4</v>
@@ -9679,7 +9688,7 @@
         <v>1.5</v>
       </c>
       <c r="AP41">
-        <v>1.08</v>
+        <v>1.07</v>
       </c>
       <c r="AQ41">
         <v>1.15</v>
@@ -9807,7 +9816,7 @@
         <v>107</v>
       </c>
       <c r="P42" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="Q42">
         <v>2.61</v>
@@ -10013,7 +10022,7 @@
         <v>118</v>
       </c>
       <c r="P43" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="Q43">
         <v>1.69</v>
@@ -10503,10 +10512,10 @@
         <v>1.5</v>
       </c>
       <c r="AP45">
-        <v>2.5</v>
+        <v>2.54</v>
       </c>
       <c r="AQ45">
-        <v>1</v>
+        <v>1.14</v>
       </c>
       <c r="AR45">
         <v>1.87</v>
@@ -10709,7 +10718,7 @@
         <v>0</v>
       </c>
       <c r="AP46">
-        <v>0.92</v>
+        <v>0.93</v>
       </c>
       <c r="AQ46">
         <v>0.08</v>
@@ -11327,7 +11336,7 @@
         <v>2</v>
       </c>
       <c r="AP49">
-        <v>1.5</v>
+        <v>1.38</v>
       </c>
       <c r="AQ49">
         <v>1.15</v>
@@ -11455,7 +11464,7 @@
         <v>88</v>
       </c>
       <c r="P50" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="Q50">
         <v>5.1</v>
@@ -11867,7 +11876,7 @@
         <v>122</v>
       </c>
       <c r="P52" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="Q52">
         <v>3</v>
@@ -12154,7 +12163,7 @@
         <v>3</v>
       </c>
       <c r="AQ53">
-        <v>0.46</v>
+        <v>0.43</v>
       </c>
       <c r="AR53">
         <v>2.35</v>
@@ -12279,7 +12288,7 @@
         <v>124</v>
       </c>
       <c r="P54" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="Q54">
         <v>3</v>
@@ -12772,7 +12781,7 @@
         <v>2.23</v>
       </c>
       <c r="AQ56">
-        <v>1.38</v>
+        <v>1.36</v>
       </c>
       <c r="AR56">
         <v>1.85</v>
@@ -12897,7 +12906,7 @@
         <v>88</v>
       </c>
       <c r="P57" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="Q57">
         <v>5.88</v>
@@ -12978,7 +12987,7 @@
         <v>1.46</v>
       </c>
       <c r="AQ57">
-        <v>2.23</v>
+        <v>2.14</v>
       </c>
       <c r="AR57">
         <v>1.7</v>
@@ -13309,7 +13318,7 @@
         <v>127</v>
       </c>
       <c r="P59" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="Q59">
         <v>3.86</v>
@@ -13927,7 +13936,7 @@
         <v>130</v>
       </c>
       <c r="P62" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="Q62">
         <v>1.83</v>
@@ -14008,7 +14017,7 @@
         <v>1.46</v>
       </c>
       <c r="AQ62">
-        <v>0.46</v>
+        <v>0.43</v>
       </c>
       <c r="AR62">
         <v>1.42</v>
@@ -14133,7 +14142,7 @@
         <v>88</v>
       </c>
       <c r="P63" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="Q63">
         <v>8.77</v>
@@ -14545,7 +14554,7 @@
         <v>132</v>
       </c>
       <c r="P65" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="Q65">
         <v>2.4</v>
@@ -14751,7 +14760,7 @@
         <v>133</v>
       </c>
       <c r="P66" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="Q66">
         <v>1.55</v>
@@ -14832,7 +14841,7 @@
         <v>2.23</v>
       </c>
       <c r="AQ66">
-        <v>1.38</v>
+        <v>1.36</v>
       </c>
       <c r="AR66">
         <v>2.05</v>
@@ -14957,7 +14966,7 @@
         <v>134</v>
       </c>
       <c r="P67" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="Q67">
         <v>4</v>
@@ -15035,10 +15044,10 @@
         <v>1</v>
       </c>
       <c r="AP67">
-        <v>0.92</v>
+        <v>0.93</v>
       </c>
       <c r="AQ67">
-        <v>1</v>
+        <v>1.14</v>
       </c>
       <c r="AR67">
         <v>1.08</v>
@@ -15163,7 +15172,7 @@
         <v>88</v>
       </c>
       <c r="P68" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="Q68">
         <v>3.1</v>
@@ -15244,7 +15253,7 @@
         <v>0.77</v>
       </c>
       <c r="AQ68">
-        <v>0.77</v>
+        <v>0.79</v>
       </c>
       <c r="AR68">
         <v>1.23</v>
@@ -15447,7 +15456,7 @@
         <v>2</v>
       </c>
       <c r="AP69">
-        <v>1.5</v>
+        <v>1.38</v>
       </c>
       <c r="AQ69">
         <v>1</v>
@@ -15653,7 +15662,7 @@
         <v>0</v>
       </c>
       <c r="AP70">
-        <v>2</v>
+        <v>1.93</v>
       </c>
       <c r="AQ70">
         <v>1.17</v>
@@ -15859,7 +15868,7 @@
         <v>0</v>
       </c>
       <c r="AP71">
-        <v>2.5</v>
+        <v>2.54</v>
       </c>
       <c r="AQ71">
         <v>0.08</v>
@@ -15987,7 +15996,7 @@
         <v>124</v>
       </c>
       <c r="P72" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="Q72">
         <v>1.88</v>
@@ -16193,7 +16202,7 @@
         <v>88</v>
       </c>
       <c r="P73" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="Q73">
         <v>7</v>
@@ -16271,10 +16280,10 @@
         <v>2.33</v>
       </c>
       <c r="AP73">
-        <v>1.08</v>
+        <v>1.07</v>
       </c>
       <c r="AQ73">
-        <v>2.23</v>
+        <v>2.14</v>
       </c>
       <c r="AR73">
         <v>1.68</v>
@@ -16605,7 +16614,7 @@
         <v>138</v>
       </c>
       <c r="P75" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="Q75">
         <v>2.3</v>
@@ -16811,7 +16820,7 @@
         <v>88</v>
       </c>
       <c r="P76" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="Q76">
         <v>3.7</v>
@@ -17017,7 +17026,7 @@
         <v>88</v>
       </c>
       <c r="P77" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="Q77">
         <v>2.47</v>
@@ -17304,7 +17313,7 @@
         <v>2.23</v>
       </c>
       <c r="AQ78">
-        <v>0.46</v>
+        <v>0.43</v>
       </c>
       <c r="AR78">
         <v>1.78</v>
@@ -17635,7 +17644,7 @@
         <v>140</v>
       </c>
       <c r="P80" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="Q80">
         <v>2.5</v>
@@ -17841,7 +17850,7 @@
         <v>141</v>
       </c>
       <c r="P81" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="Q81">
         <v>2.38</v>
@@ -18047,7 +18056,7 @@
         <v>142</v>
       </c>
       <c r="P82" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="Q82">
         <v>2.8</v>
@@ -18128,7 +18137,7 @@
         <v>1.54</v>
       </c>
       <c r="AQ82">
-        <v>1.38</v>
+        <v>1.36</v>
       </c>
       <c r="AR82">
         <v>1.31</v>
@@ -18253,7 +18262,7 @@
         <v>143</v>
       </c>
       <c r="P83" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="Q83">
         <v>2.6</v>
@@ -18331,10 +18340,10 @@
         <v>0.67</v>
       </c>
       <c r="AP83">
-        <v>0.92</v>
+        <v>0.93</v>
       </c>
       <c r="AQ83">
-        <v>0.46</v>
+        <v>0.43</v>
       </c>
       <c r="AR83">
         <v>1.14</v>
@@ -18459,7 +18468,7 @@
         <v>144</v>
       </c>
       <c r="P84" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="Q84">
         <v>3.4</v>
@@ -18537,7 +18546,7 @@
         <v>1.6</v>
       </c>
       <c r="AP84">
-        <v>2.5</v>
+        <v>2.54</v>
       </c>
       <c r="AQ84">
         <v>1.85</v>
@@ -18746,7 +18755,7 @@
         <v>2.23</v>
       </c>
       <c r="AQ85">
-        <v>1</v>
+        <v>1.14</v>
       </c>
       <c r="AR85">
         <v>2.02</v>
@@ -18871,7 +18880,7 @@
         <v>146</v>
       </c>
       <c r="P86" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="Q86">
         <v>2.88</v>
@@ -18949,7 +18958,7 @@
         <v>0.8</v>
       </c>
       <c r="AP86">
-        <v>1.08</v>
+        <v>1.07</v>
       </c>
       <c r="AQ86">
         <v>1.15</v>
@@ -19283,7 +19292,7 @@
         <v>88</v>
       </c>
       <c r="P88" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="Q88">
         <v>2.6</v>
@@ -19361,10 +19370,10 @@
         <v>0.75</v>
       </c>
       <c r="AP88">
-        <v>1.5</v>
+        <v>1.38</v>
       </c>
       <c r="AQ88">
-        <v>0.77</v>
+        <v>0.79</v>
       </c>
       <c r="AR88">
         <v>1.12</v>
@@ -19489,7 +19498,7 @@
         <v>93</v>
       </c>
       <c r="P89" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="Q89">
         <v>6.5</v>
@@ -19567,10 +19576,10 @@
         <v>2.5</v>
       </c>
       <c r="AP89">
-        <v>2</v>
+        <v>1.93</v>
       </c>
       <c r="AQ89">
-        <v>2.23</v>
+        <v>2.14</v>
       </c>
       <c r="AR89">
         <v>1.74</v>
@@ -19901,7 +19910,7 @@
         <v>149</v>
       </c>
       <c r="P91" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="Q91">
         <v>4.7</v>
@@ -20107,7 +20116,7 @@
         <v>88</v>
       </c>
       <c r="P92" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="Q92">
         <v>3.8</v>
@@ -20519,7 +20528,7 @@
         <v>150</v>
       </c>
       <c r="P94" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="Q94">
         <v>3</v>
@@ -21421,7 +21430,7 @@
         <v>0.83</v>
       </c>
       <c r="AP98">
-        <v>0.92</v>
+        <v>0.93</v>
       </c>
       <c r="AQ98">
         <v>1.15</v>
@@ -21627,10 +21636,10 @@
         <v>1.2</v>
       </c>
       <c r="AP99">
-        <v>2</v>
+        <v>1.93</v>
       </c>
       <c r="AQ99">
-        <v>0.77</v>
+        <v>0.79</v>
       </c>
       <c r="AR99">
         <v>1.65</v>
@@ -21836,7 +21845,7 @@
         <v>1.46</v>
       </c>
       <c r="AQ100">
-        <v>1.38</v>
+        <v>1.36</v>
       </c>
       <c r="AR100">
         <v>1.67</v>
@@ -21961,7 +21970,7 @@
         <v>156</v>
       </c>
       <c r="P101" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="Q101">
         <v>1.83</v>
@@ -22248,7 +22257,7 @@
         <v>0.21</v>
       </c>
       <c r="AQ102">
-        <v>1</v>
+        <v>1.14</v>
       </c>
       <c r="AR102">
         <v>1.41</v>
@@ -22451,10 +22460,10 @@
         <v>0.57</v>
       </c>
       <c r="AP103">
-        <v>1.08</v>
+        <v>1.07</v>
       </c>
       <c r="AQ103">
-        <v>0.46</v>
+        <v>0.43</v>
       </c>
       <c r="AR103">
         <v>1.41</v>
@@ -22657,7 +22666,7 @@
         <v>1.83</v>
       </c>
       <c r="AP104">
-        <v>1.5</v>
+        <v>1.38</v>
       </c>
       <c r="AQ104">
         <v>1.85</v>
@@ -22866,7 +22875,7 @@
         <v>1.54</v>
       </c>
       <c r="AQ105">
-        <v>2.23</v>
+        <v>2.14</v>
       </c>
       <c r="AR105">
         <v>1.41</v>
@@ -23069,7 +23078,7 @@
         <v>0.33</v>
       </c>
       <c r="AP106">
-        <v>2.5</v>
+        <v>2.54</v>
       </c>
       <c r="AQ106">
         <v>0.62</v>
@@ -23609,7 +23618,7 @@
         <v>161</v>
       </c>
       <c r="P109" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="Q109">
         <v>2.24</v>
@@ -23815,7 +23824,7 @@
         <v>162</v>
       </c>
       <c r="P110" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="Q110">
         <v>4.6</v>
@@ -24433,7 +24442,7 @@
         <v>165</v>
       </c>
       <c r="P113" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="Q113">
         <v>3.25</v>
@@ -24511,7 +24520,7 @@
         <v>1.5</v>
       </c>
       <c r="AP113">
-        <v>2</v>
+        <v>1.93</v>
       </c>
       <c r="AQ113">
         <v>1.71</v>
@@ -24639,7 +24648,7 @@
         <v>151</v>
       </c>
       <c r="P114" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="Q114">
         <v>2.88</v>
@@ -24717,7 +24726,7 @@
         <v>1.14</v>
       </c>
       <c r="AP114">
-        <v>1.5</v>
+        <v>1.38</v>
       </c>
       <c r="AQ114">
         <v>1.15</v>
@@ -24845,7 +24854,7 @@
         <v>99</v>
       </c>
       <c r="P115" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="Q115">
         <v>1.73</v>
@@ -24926,7 +24935,7 @@
         <v>2.23</v>
       </c>
       <c r="AQ115">
-        <v>0.77</v>
+        <v>0.79</v>
       </c>
       <c r="AR115">
         <v>1.87</v>
@@ -25051,7 +25060,7 @@
         <v>88</v>
       </c>
       <c r="P116" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="Q116">
         <v>4.33</v>
@@ -25335,7 +25344,7 @@
         <v>0.29</v>
       </c>
       <c r="AP117">
-        <v>1.08</v>
+        <v>1.07</v>
       </c>
       <c r="AQ117">
         <v>0.62</v>
@@ -25544,7 +25553,7 @@
         <v>1.46</v>
       </c>
       <c r="AQ118">
-        <v>0.46</v>
+        <v>0.43</v>
       </c>
       <c r="AR118">
         <v>1.64</v>
@@ -25669,7 +25678,7 @@
         <v>88</v>
       </c>
       <c r="P119" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="Q119">
         <v>15</v>
@@ -25750,7 +25759,7 @@
         <v>0.21</v>
       </c>
       <c r="AQ119">
-        <v>2.23</v>
+        <v>2.14</v>
       </c>
       <c r="AR119">
         <v>1.38</v>
@@ -25875,7 +25884,7 @@
         <v>168</v>
       </c>
       <c r="P120" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="Q120">
         <v>3</v>
@@ -25956,7 +25965,7 @@
         <v>1.54</v>
       </c>
       <c r="AQ120">
-        <v>1</v>
+        <v>1.14</v>
       </c>
       <c r="AR120">
         <v>1.59</v>
@@ -26287,7 +26296,7 @@
         <v>170</v>
       </c>
       <c r="P122" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="Q122">
         <v>3.25</v>
@@ -26365,7 +26374,7 @@
         <v>1</v>
       </c>
       <c r="AP122">
-        <v>1.08</v>
+        <v>1.07</v>
       </c>
       <c r="AQ122">
         <v>0.85</v>
@@ -26574,7 +26583,7 @@
         <v>1.46</v>
       </c>
       <c r="AQ123">
-        <v>1.38</v>
+        <v>1.36</v>
       </c>
       <c r="AR123">
         <v>1.58</v>
@@ -26699,7 +26708,7 @@
         <v>172</v>
       </c>
       <c r="P124" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="Q124">
         <v>1.83</v>
@@ -26777,7 +26786,7 @@
         <v>1.17</v>
       </c>
       <c r="AP124">
-        <v>2.5</v>
+        <v>2.54</v>
       </c>
       <c r="AQ124">
         <v>1</v>
@@ -26905,7 +26914,7 @@
         <v>171</v>
       </c>
       <c r="P125" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="Q125">
         <v>6.3</v>
@@ -26983,7 +26992,7 @@
         <v>2</v>
       </c>
       <c r="AP125">
-        <v>0.92</v>
+        <v>0.93</v>
       </c>
       <c r="AQ125">
         <v>2</v>
@@ -27192,7 +27201,7 @@
         <v>3</v>
       </c>
       <c r="AQ126">
-        <v>1</v>
+        <v>1.14</v>
       </c>
       <c r="AR126">
         <v>2.37</v>
@@ -27729,7 +27738,7 @@
         <v>174</v>
       </c>
       <c r="P129" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="Q129">
         <v>2.1</v>
@@ -27935,7 +27944,7 @@
         <v>175</v>
       </c>
       <c r="P130" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="Q130">
         <v>1.5</v>
@@ -28141,7 +28150,7 @@
         <v>176</v>
       </c>
       <c r="P131" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="Q131">
         <v>3.5</v>
@@ -28222,7 +28231,7 @@
         <v>0.77</v>
       </c>
       <c r="AQ131">
-        <v>1.38</v>
+        <v>1.36</v>
       </c>
       <c r="AR131">
         <v>1.21</v>
@@ -28347,7 +28356,7 @@
         <v>177</v>
       </c>
       <c r="P132" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="Q132">
         <v>4.04</v>
@@ -28425,7 +28434,7 @@
         <v>1</v>
       </c>
       <c r="AP132">
-        <v>0.92</v>
+        <v>0.93</v>
       </c>
       <c r="AQ132">
         <v>0.85</v>
@@ -28631,7 +28640,7 @@
         <v>0.14</v>
       </c>
       <c r="AP133">
-        <v>2</v>
+        <v>1.93</v>
       </c>
       <c r="AQ133">
         <v>0.08</v>
@@ -28759,7 +28768,7 @@
         <v>88</v>
       </c>
       <c r="P134" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="Q134">
         <v>2.75</v>
@@ -28837,7 +28846,7 @@
         <v>0.63</v>
       </c>
       <c r="AP134">
-        <v>1.08</v>
+        <v>1.07</v>
       </c>
       <c r="AQ134">
         <v>1.17</v>
@@ -29046,7 +29055,7 @@
         <v>1.46</v>
       </c>
       <c r="AQ135">
-        <v>1</v>
+        <v>1.14</v>
       </c>
       <c r="AR135">
         <v>1.56</v>
@@ -29249,10 +29258,10 @@
         <v>2.43</v>
       </c>
       <c r="AP136">
-        <v>2.5</v>
+        <v>2.54</v>
       </c>
       <c r="AQ136">
-        <v>2.23</v>
+        <v>2.14</v>
       </c>
       <c r="AR136">
         <v>2.02</v>
@@ -29458,7 +29467,7 @@
         <v>2.23</v>
       </c>
       <c r="AQ137">
-        <v>0.77</v>
+        <v>0.79</v>
       </c>
       <c r="AR137">
         <v>1.7</v>
@@ -29583,7 +29592,7 @@
         <v>91</v>
       </c>
       <c r="P138" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="Q138">
         <v>2.25</v>
@@ -29661,10 +29670,10 @@
         <v>0.5600000000000001</v>
       </c>
       <c r="AP138">
-        <v>1.5</v>
+        <v>1.38</v>
       </c>
       <c r="AQ138">
-        <v>0.46</v>
+        <v>0.43</v>
       </c>
       <c r="AR138">
         <v>1.11</v>
@@ -29789,7 +29798,7 @@
         <v>179</v>
       </c>
       <c r="P139" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="Q139">
         <v>1.9</v>
@@ -29867,7 +29876,7 @@
         <v>0.25</v>
       </c>
       <c r="AP139">
-        <v>2</v>
+        <v>1.93</v>
       </c>
       <c r="AQ139">
         <v>0.62</v>
@@ -30201,7 +30210,7 @@
         <v>88</v>
       </c>
       <c r="P141" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="Q141">
         <v>4</v>
@@ -30407,7 +30416,7 @@
         <v>117</v>
       </c>
       <c r="P142" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="Q142">
         <v>4</v>
@@ -30694,7 +30703,7 @@
         <v>1.54</v>
       </c>
       <c r="AQ143">
-        <v>0.77</v>
+        <v>0.79</v>
       </c>
       <c r="AR143">
         <v>1.52</v>
@@ -30819,7 +30828,7 @@
         <v>182</v>
       </c>
       <c r="P144" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="Q144">
         <v>6</v>
@@ -30900,7 +30909,7 @@
         <v>1.54</v>
       </c>
       <c r="AQ144">
-        <v>2.23</v>
+        <v>2.14</v>
       </c>
       <c r="AR144">
         <v>1.69</v>
@@ -31025,7 +31034,7 @@
         <v>88</v>
       </c>
       <c r="P145" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="Q145">
         <v>3.5</v>
@@ -31231,7 +31240,7 @@
         <v>183</v>
       </c>
       <c r="P146" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="Q146">
         <v>4.33</v>
@@ -31309,7 +31318,7 @@
         <v>0.89</v>
       </c>
       <c r="AP146">
-        <v>0.92</v>
+        <v>0.93</v>
       </c>
       <c r="AQ146">
         <v>1.17</v>
@@ -31437,7 +31446,7 @@
         <v>184</v>
       </c>
       <c r="P147" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="Q147">
         <v>3.8</v>
@@ -31518,7 +31527,7 @@
         <v>0.77</v>
       </c>
       <c r="AQ147">
-        <v>1</v>
+        <v>1.14</v>
       </c>
       <c r="AR147">
         <v>1.26</v>
@@ -31643,7 +31652,7 @@
         <v>185</v>
       </c>
       <c r="P148" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="Q148">
         <v>2.5</v>
@@ -31721,7 +31730,7 @@
         <v>0.88</v>
       </c>
       <c r="AP148">
-        <v>1.08</v>
+        <v>1.07</v>
       </c>
       <c r="AQ148">
         <v>1</v>
@@ -31849,7 +31858,7 @@
         <v>186</v>
       </c>
       <c r="P149" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="Q149">
         <v>2.05</v>
@@ -31927,7 +31936,7 @@
         <v>1.22</v>
       </c>
       <c r="AP149">
-        <v>2.5</v>
+        <v>2.54</v>
       </c>
       <c r="AQ149">
         <v>0.85</v>
@@ -32055,7 +32064,7 @@
         <v>187</v>
       </c>
       <c r="P150" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="Q150">
         <v>1.95</v>
@@ -32261,7 +32270,7 @@
         <v>188</v>
       </c>
       <c r="P151" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="Q151">
         <v>2.48</v>
@@ -32342,7 +32351,7 @@
         <v>1.46</v>
       </c>
       <c r="AQ151">
-        <v>1.38</v>
+        <v>1.36</v>
       </c>
       <c r="AR151">
         <v>1.53</v>
@@ -32548,7 +32557,7 @@
         <v>1.46</v>
       </c>
       <c r="AQ152">
-        <v>2.23</v>
+        <v>2.14</v>
       </c>
       <c r="AR152">
         <v>1.55</v>
@@ -32673,7 +32682,7 @@
         <v>190</v>
       </c>
       <c r="P153" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="Q153">
         <v>1.4</v>
@@ -32960,7 +32969,7 @@
         <v>1.46</v>
       </c>
       <c r="AQ154">
-        <v>0.77</v>
+        <v>0.79</v>
       </c>
       <c r="AR154">
         <v>1.58</v>
@@ -33085,7 +33094,7 @@
         <v>88</v>
       </c>
       <c r="P155" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="Q155">
         <v>3.2</v>
@@ -33578,7 +33587,7 @@
         <v>1.54</v>
       </c>
       <c r="AQ157">
-        <v>0.46</v>
+        <v>0.43</v>
       </c>
       <c r="AR157">
         <v>1.43</v>
@@ -33703,7 +33712,7 @@
         <v>88</v>
       </c>
       <c r="P158" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="Q158">
         <v>5</v>
@@ -33781,7 +33790,7 @@
         <v>1.89</v>
       </c>
       <c r="AP158">
-        <v>1.5</v>
+        <v>1.38</v>
       </c>
       <c r="AQ158">
         <v>2</v>
@@ -33909,7 +33918,7 @@
         <v>88</v>
       </c>
       <c r="P159" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="Q159">
         <v>2.38</v>
@@ -33987,7 +33996,7 @@
         <v>1.33</v>
       </c>
       <c r="AP159">
-        <v>2</v>
+        <v>1.93</v>
       </c>
       <c r="AQ159">
         <v>1.46</v>
@@ -34321,7 +34330,7 @@
         <v>193</v>
       </c>
       <c r="P161" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="Q161">
         <v>4.75</v>
@@ -34527,7 +34536,7 @@
         <v>194</v>
       </c>
       <c r="P162" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="Q162">
         <v>2.63</v>
@@ -34608,7 +34617,7 @@
         <v>1.46</v>
       </c>
       <c r="AQ162">
-        <v>0.77</v>
+        <v>0.79</v>
       </c>
       <c r="AR162">
         <v>1.6</v>
@@ -34733,7 +34742,7 @@
         <v>88</v>
       </c>
       <c r="P163" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="Q163">
         <v>11</v>
@@ -34814,7 +34823,7 @@
         <v>0.77</v>
       </c>
       <c r="AQ163">
-        <v>2.23</v>
+        <v>2.14</v>
       </c>
       <c r="AR163">
         <v>1.29</v>
@@ -34939,7 +34948,7 @@
         <v>195</v>
       </c>
       <c r="P164" t="s">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="Q164">
         <v>2</v>
@@ -35020,7 +35029,7 @@
         <v>2.23</v>
       </c>
       <c r="AQ164">
-        <v>1</v>
+        <v>1.14</v>
       </c>
       <c r="AR164">
         <v>1.81</v>
@@ -35145,7 +35154,7 @@
         <v>196</v>
       </c>
       <c r="P165" t="s">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="Q165">
         <v>2.5</v>
@@ -35223,7 +35232,7 @@
         <v>1.1</v>
       </c>
       <c r="AP165">
-        <v>2</v>
+        <v>1.93</v>
       </c>
       <c r="AQ165">
         <v>0.85</v>
@@ -35429,10 +35438,10 @@
         <v>1.2</v>
       </c>
       <c r="AP166">
-        <v>2.5</v>
+        <v>2.54</v>
       </c>
       <c r="AQ166">
-        <v>1.38</v>
+        <v>1.36</v>
       </c>
       <c r="AR166">
         <v>1.9</v>
@@ -35635,7 +35644,7 @@
         <v>0.11</v>
       </c>
       <c r="AP167">
-        <v>1.08</v>
+        <v>1.07</v>
       </c>
       <c r="AQ167">
         <v>0.08</v>
@@ -36050,7 +36059,7 @@
         <v>1.54</v>
       </c>
       <c r="AQ169">
-        <v>0.46</v>
+        <v>0.43</v>
       </c>
       <c r="AR169">
         <v>1.54</v>
@@ -36253,7 +36262,7 @@
         <v>0.3</v>
       </c>
       <c r="AP170">
-        <v>1.5</v>
+        <v>1.38</v>
       </c>
       <c r="AQ170">
         <v>0.62</v>
@@ -36381,7 +36390,7 @@
         <v>201</v>
       </c>
       <c r="P171" t="s">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="Q171">
         <v>5.2</v>
@@ -36587,7 +36596,7 @@
         <v>202</v>
       </c>
       <c r="P172" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="Q172">
         <v>6.35</v>
@@ -36793,7 +36802,7 @@
         <v>203</v>
       </c>
       <c r="P173" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="Q173">
         <v>2.6</v>
@@ -36999,7 +37008,7 @@
         <v>88</v>
       </c>
       <c r="P174" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="Q174">
         <v>4.86</v>
@@ -37205,7 +37214,7 @@
         <v>204</v>
       </c>
       <c r="P175" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="Q175">
         <v>2.66</v>
@@ -37617,7 +37626,7 @@
         <v>171</v>
       </c>
       <c r="P177" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="Q177">
         <v>3.63</v>
@@ -37695,10 +37704,10 @@
         <v>1.09</v>
       </c>
       <c r="AP177">
-        <v>0.92</v>
+        <v>0.93</v>
       </c>
       <c r="AQ177">
-        <v>1.38</v>
+        <v>1.36</v>
       </c>
       <c r="AR177">
         <v>1.28</v>
@@ -37901,10 +37910,10 @@
         <v>0.82</v>
       </c>
       <c r="AP178">
-        <v>2.5</v>
+        <v>2.54</v>
       </c>
       <c r="AQ178">
-        <v>0.77</v>
+        <v>0.79</v>
       </c>
       <c r="AR178">
         <v>1.82</v>
@@ -38029,7 +38038,7 @@
         <v>88</v>
       </c>
       <c r="P179" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="Q179">
         <v>3.92</v>
@@ -38235,7 +38244,7 @@
         <v>206</v>
       </c>
       <c r="P180" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="Q180">
         <v>1.32</v>
@@ -38519,10 +38528,10 @@
         <v>1</v>
       </c>
       <c r="AP181">
-        <v>1.08</v>
+        <v>1.07</v>
       </c>
       <c r="AQ181">
-        <v>1</v>
+        <v>1.14</v>
       </c>
       <c r="AR181">
         <v>1.62</v>
@@ -38725,7 +38734,7 @@
         <v>0.89</v>
       </c>
       <c r="AP182">
-        <v>2</v>
+        <v>1.93</v>
       </c>
       <c r="AQ182">
         <v>1</v>
@@ -38853,7 +38862,7 @@
         <v>208</v>
       </c>
       <c r="P183" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="Q183">
         <v>4.3</v>
@@ -38934,7 +38943,7 @@
         <v>2.23</v>
       </c>
       <c r="AQ183">
-        <v>2.23</v>
+        <v>2.14</v>
       </c>
       <c r="AR183">
         <v>1.82</v>
@@ -39059,7 +39068,7 @@
         <v>88</v>
       </c>
       <c r="P184" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="Q184">
         <v>5.8</v>
@@ -39471,7 +39480,7 @@
         <v>96</v>
       </c>
       <c r="P186" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="Q186">
         <v>4.7</v>
@@ -39758,7 +39767,7 @@
         <v>1.46</v>
       </c>
       <c r="AQ187">
-        <v>0.46</v>
+        <v>0.43</v>
       </c>
       <c r="AR187">
         <v>1.45</v>
@@ -40089,7 +40098,7 @@
         <v>88</v>
       </c>
       <c r="P189" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="Q189">
         <v>4.5</v>
@@ -40785,10 +40794,10 @@
         <v>0.75</v>
       </c>
       <c r="AP192">
-        <v>0.92</v>
+        <v>0.93</v>
       </c>
       <c r="AQ192">
-        <v>0.77</v>
+        <v>0.79</v>
       </c>
       <c r="AR192">
         <v>1.24</v>
@@ -40991,10 +41000,10 @@
         <v>1</v>
       </c>
       <c r="AP193">
-        <v>2</v>
+        <v>1.93</v>
       </c>
       <c r="AQ193">
-        <v>1</v>
+        <v>1.14</v>
       </c>
       <c r="AR193">
         <v>1.7</v>
@@ -41197,7 +41206,7 @@
         <v>0.09</v>
       </c>
       <c r="AP194">
-        <v>1.5</v>
+        <v>1.38</v>
       </c>
       <c r="AQ194">
         <v>0.08</v>
@@ -41406,7 +41415,7 @@
         <v>2.23</v>
       </c>
       <c r="AQ195">
-        <v>2.23</v>
+        <v>2.14</v>
       </c>
       <c r="AR195">
         <v>2.09</v>
@@ -41531,7 +41540,7 @@
         <v>215</v>
       </c>
       <c r="P196" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="Q196">
         <v>1.95</v>
@@ -41609,7 +41618,7 @@
         <v>1.25</v>
       </c>
       <c r="AP196">
-        <v>2.5</v>
+        <v>2.54</v>
       </c>
       <c r="AQ196">
         <v>1.15</v>
@@ -41737,7 +41746,7 @@
         <v>88</v>
       </c>
       <c r="P197" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="Q197">
         <v>2.88</v>
@@ -41815,10 +41824,10 @@
         <v>1.25</v>
       </c>
       <c r="AP197">
-        <v>1.08</v>
+        <v>1.07</v>
       </c>
       <c r="AQ197">
-        <v>1.38</v>
+        <v>1.36</v>
       </c>
       <c r="AR197">
         <v>1.61</v>
@@ -42433,7 +42442,7 @@
         <v>0.82</v>
       </c>
       <c r="AP200">
-        <v>0.92</v>
+        <v>0.93</v>
       </c>
       <c r="AQ200">
         <v>1</v>
@@ -42561,7 +42570,7 @@
         <v>158</v>
       </c>
       <c r="P201" t="s">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="Q201">
         <v>2.63</v>
@@ -42973,7 +42982,7 @@
         <v>88</v>
       </c>
       <c r="P203" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="Q203">
         <v>2.75</v>
@@ -43385,7 +43394,7 @@
         <v>218</v>
       </c>
       <c r="P205" t="s">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="Q205">
         <v>2.88</v>
@@ -43591,7 +43600,7 @@
         <v>88</v>
       </c>
       <c r="P206" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="Q206">
         <v>2.38</v>
@@ -43797,7 +43806,7 @@
         <v>219</v>
       </c>
       <c r="P207" t="s">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="Q207">
         <v>4.75</v>
@@ -44160,6 +44169,1036 @@
       </c>
       <c r="BP208">
         <v>1.52</v>
+      </c>
+    </row>
+    <row r="209" spans="1:68">
+      <c r="A209" s="1">
+        <v>208</v>
+      </c>
+      <c r="B209">
+        <v>7468295</v>
+      </c>
+      <c r="C209" t="s">
+        <v>68</v>
+      </c>
+      <c r="D209" t="s">
+        <v>69</v>
+      </c>
+      <c r="E209" s="2">
+        <v>45745.39583333334</v>
+      </c>
+      <c r="F209">
+        <v>27</v>
+      </c>
+      <c r="G209" t="s">
+        <v>71</v>
+      </c>
+      <c r="H209" t="s">
+        <v>85</v>
+      </c>
+      <c r="I209">
+        <v>0</v>
+      </c>
+      <c r="J209">
+        <v>0</v>
+      </c>
+      <c r="K209">
+        <v>0</v>
+      </c>
+      <c r="L209">
+        <v>0</v>
+      </c>
+      <c r="M209">
+        <v>0</v>
+      </c>
+      <c r="N209">
+        <v>0</v>
+      </c>
+      <c r="O209" t="s">
+        <v>88</v>
+      </c>
+      <c r="P209" t="s">
+        <v>88</v>
+      </c>
+      <c r="Q209">
+        <v>2.4</v>
+      </c>
+      <c r="R209">
+        <v>2.2</v>
+      </c>
+      <c r="S209">
+        <v>4.75</v>
+      </c>
+      <c r="T209">
+        <v>1.4</v>
+      </c>
+      <c r="U209">
+        <v>2.75</v>
+      </c>
+      <c r="V209">
+        <v>3</v>
+      </c>
+      <c r="W209">
+        <v>1.36</v>
+      </c>
+      <c r="X209">
+        <v>8</v>
+      </c>
+      <c r="Y209">
+        <v>1.08</v>
+      </c>
+      <c r="Z209">
+        <v>1.78</v>
+      </c>
+      <c r="AA209">
+        <v>3.6</v>
+      </c>
+      <c r="AB209">
+        <v>4.54</v>
+      </c>
+      <c r="AC209">
+        <v>3.42</v>
+      </c>
+      <c r="AD209">
+        <v>1.31</v>
+      </c>
+      <c r="AE209">
+        <v>0</v>
+      </c>
+      <c r="AF209">
+        <v>0</v>
+      </c>
+      <c r="AG209">
+        <v>1.98</v>
+      </c>
+      <c r="AH209">
+        <v>1.84</v>
+      </c>
+      <c r="AI209">
+        <v>1.91</v>
+      </c>
+      <c r="AJ209">
+        <v>1.91</v>
+      </c>
+      <c r="AK209">
+        <v>0</v>
+      </c>
+      <c r="AL209">
+        <v>0</v>
+      </c>
+      <c r="AM209">
+        <v>0</v>
+      </c>
+      <c r="AN209">
+        <v>2</v>
+      </c>
+      <c r="AO209">
+        <v>1.38</v>
+      </c>
+      <c r="AP209">
+        <v>1.93</v>
+      </c>
+      <c r="AQ209">
+        <v>1.36</v>
+      </c>
+      <c r="AR209">
+        <v>1.67</v>
+      </c>
+      <c r="AS209">
+        <v>1.22</v>
+      </c>
+      <c r="AT209">
+        <v>2.89</v>
+      </c>
+      <c r="AU209">
+        <v>5</v>
+      </c>
+      <c r="AV209">
+        <v>3</v>
+      </c>
+      <c r="AW209">
+        <v>5</v>
+      </c>
+      <c r="AX209">
+        <v>4</v>
+      </c>
+      <c r="AY209">
+        <v>10</v>
+      </c>
+      <c r="AZ209">
+        <v>7</v>
+      </c>
+      <c r="BA209">
+        <v>3</v>
+      </c>
+      <c r="BB209">
+        <v>3</v>
+      </c>
+      <c r="BC209">
+        <v>6</v>
+      </c>
+      <c r="BD209">
+        <v>0</v>
+      </c>
+      <c r="BE209">
+        <v>0</v>
+      </c>
+      <c r="BF209">
+        <v>0</v>
+      </c>
+      <c r="BG209">
+        <v>0</v>
+      </c>
+      <c r="BH209">
+        <v>0</v>
+      </c>
+      <c r="BI209">
+        <v>0</v>
+      </c>
+      <c r="BJ209">
+        <v>0</v>
+      </c>
+      <c r="BK209">
+        <v>0</v>
+      </c>
+      <c r="BL209">
+        <v>0</v>
+      </c>
+      <c r="BM209">
+        <v>0</v>
+      </c>
+      <c r="BN209">
+        <v>0</v>
+      </c>
+      <c r="BO209">
+        <v>0</v>
+      </c>
+      <c r="BP209">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="210" spans="1:68">
+      <c r="A210" s="1">
+        <v>209</v>
+      </c>
+      <c r="B210">
+        <v>7468297</v>
+      </c>
+      <c r="C210" t="s">
+        <v>68</v>
+      </c>
+      <c r="D210" t="s">
+        <v>69</v>
+      </c>
+      <c r="E210" s="2">
+        <v>45745.5</v>
+      </c>
+      <c r="F210">
+        <v>27</v>
+      </c>
+      <c r="G210" t="s">
+        <v>73</v>
+      </c>
+      <c r="H210" t="s">
+        <v>78</v>
+      </c>
+      <c r="I210">
+        <v>0</v>
+      </c>
+      <c r="J210">
+        <v>1</v>
+      </c>
+      <c r="K210">
+        <v>1</v>
+      </c>
+      <c r="L210">
+        <v>1</v>
+      </c>
+      <c r="M210">
+        <v>1</v>
+      </c>
+      <c r="N210">
+        <v>2</v>
+      </c>
+      <c r="O210" t="s">
+        <v>90</v>
+      </c>
+      <c r="P210" t="s">
+        <v>110</v>
+      </c>
+      <c r="Q210">
+        <v>2.88</v>
+      </c>
+      <c r="R210">
+        <v>2.1</v>
+      </c>
+      <c r="S210">
+        <v>4</v>
+      </c>
+      <c r="T210">
+        <v>1.44</v>
+      </c>
+      <c r="U210">
+        <v>2.63</v>
+      </c>
+      <c r="V210">
+        <v>3.25</v>
+      </c>
+      <c r="W210">
+        <v>1.33</v>
+      </c>
+      <c r="X210">
+        <v>9</v>
+      </c>
+      <c r="Y210">
+        <v>1.07</v>
+      </c>
+      <c r="Z210">
+        <v>2.15</v>
+      </c>
+      <c r="AA210">
+        <v>3.25</v>
+      </c>
+      <c r="AB210">
+        <v>3.4</v>
+      </c>
+      <c r="AC210">
+        <v>0</v>
+      </c>
+      <c r="AD210">
+        <v>0</v>
+      </c>
+      <c r="AE210">
+        <v>0</v>
+      </c>
+      <c r="AF210">
+        <v>0</v>
+      </c>
+      <c r="AG210">
+        <v>2.08</v>
+      </c>
+      <c r="AH210">
+        <v>1.73</v>
+      </c>
+      <c r="AI210">
+        <v>1.91</v>
+      </c>
+      <c r="AJ210">
+        <v>1.91</v>
+      </c>
+      <c r="AK210">
+        <v>0</v>
+      </c>
+      <c r="AL210">
+        <v>0</v>
+      </c>
+      <c r="AM210">
+        <v>0</v>
+      </c>
+      <c r="AN210">
+        <v>1.08</v>
+      </c>
+      <c r="AO210">
+        <v>0.77</v>
+      </c>
+      <c r="AP210">
+        <v>1.07</v>
+      </c>
+      <c r="AQ210">
+        <v>0.79</v>
+      </c>
+      <c r="AR210">
+        <v>1.59</v>
+      </c>
+      <c r="AS210">
+        <v>1.34</v>
+      </c>
+      <c r="AT210">
+        <v>2.93</v>
+      </c>
+      <c r="AU210">
+        <v>6</v>
+      </c>
+      <c r="AV210">
+        <v>4</v>
+      </c>
+      <c r="AW210">
+        <v>3</v>
+      </c>
+      <c r="AX210">
+        <v>5</v>
+      </c>
+      <c r="AY210">
+        <v>9</v>
+      </c>
+      <c r="AZ210">
+        <v>9</v>
+      </c>
+      <c r="BA210">
+        <v>6</v>
+      </c>
+      <c r="BB210">
+        <v>1</v>
+      </c>
+      <c r="BC210">
+        <v>7</v>
+      </c>
+      <c r="BD210">
+        <v>0</v>
+      </c>
+      <c r="BE210">
+        <v>0</v>
+      </c>
+      <c r="BF210">
+        <v>0</v>
+      </c>
+      <c r="BG210">
+        <v>0</v>
+      </c>
+      <c r="BH210">
+        <v>0</v>
+      </c>
+      <c r="BI210">
+        <v>0</v>
+      </c>
+      <c r="BJ210">
+        <v>0</v>
+      </c>
+      <c r="BK210">
+        <v>0</v>
+      </c>
+      <c r="BL210">
+        <v>0</v>
+      </c>
+      <c r="BM210">
+        <v>0</v>
+      </c>
+      <c r="BN210">
+        <v>0</v>
+      </c>
+      <c r="BO210">
+        <v>0</v>
+      </c>
+      <c r="BP210">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="211" spans="1:68">
+      <c r="A211" s="1">
+        <v>210</v>
+      </c>
+      <c r="B211">
+        <v>7468299</v>
+      </c>
+      <c r="C211" t="s">
+        <v>68</v>
+      </c>
+      <c r="D211" t="s">
+        <v>69</v>
+      </c>
+      <c r="E211" s="2">
+        <v>45745.5</v>
+      </c>
+      <c r="F211">
+        <v>27</v>
+      </c>
+      <c r="G211" t="s">
+        <v>83</v>
+      </c>
+      <c r="H211" t="s">
+        <v>79</v>
+      </c>
+      <c r="I211">
+        <v>2</v>
+      </c>
+      <c r="J211">
+        <v>1</v>
+      </c>
+      <c r="K211">
+        <v>3</v>
+      </c>
+      <c r="L211">
+        <v>5</v>
+      </c>
+      <c r="M211">
+        <v>2</v>
+      </c>
+      <c r="N211">
+        <v>7</v>
+      </c>
+      <c r="O211" t="s">
+        <v>221</v>
+      </c>
+      <c r="P211" t="s">
+        <v>313</v>
+      </c>
+      <c r="Q211">
+        <v>1.57</v>
+      </c>
+      <c r="R211">
+        <v>2.88</v>
+      </c>
+      <c r="S211">
+        <v>10</v>
+      </c>
+      <c r="T211">
+        <v>1.25</v>
+      </c>
+      <c r="U211">
+        <v>3.75</v>
+      </c>
+      <c r="V211">
+        <v>2.1</v>
+      </c>
+      <c r="W211">
+        <v>1.67</v>
+      </c>
+      <c r="X211">
+        <v>4.5</v>
+      </c>
+      <c r="Y211">
+        <v>1.18</v>
+      </c>
+      <c r="Z211">
+        <v>1.2</v>
+      </c>
+      <c r="AA211">
+        <v>6.25</v>
+      </c>
+      <c r="AB211">
+        <v>15</v>
+      </c>
+      <c r="AC211">
+        <v>0</v>
+      </c>
+      <c r="AD211">
+        <v>0</v>
+      </c>
+      <c r="AE211">
+        <v>0</v>
+      </c>
+      <c r="AF211">
+        <v>0</v>
+      </c>
+      <c r="AG211">
+        <v>1.44</v>
+      </c>
+      <c r="AH211">
+        <v>2.7</v>
+      </c>
+      <c r="AI211">
+        <v>2</v>
+      </c>
+      <c r="AJ211">
+        <v>1.75</v>
+      </c>
+      <c r="AK211">
+        <v>0</v>
+      </c>
+      <c r="AL211">
+        <v>0</v>
+      </c>
+      <c r="AM211">
+        <v>0</v>
+      </c>
+      <c r="AN211">
+        <v>2.5</v>
+      </c>
+      <c r="AO211">
+        <v>0.46</v>
+      </c>
+      <c r="AP211">
+        <v>2.54</v>
+      </c>
+      <c r="AQ211">
+        <v>0.43</v>
+      </c>
+      <c r="AR211">
+        <v>1.83</v>
+      </c>
+      <c r="AS211">
+        <v>1.01</v>
+      </c>
+      <c r="AT211">
+        <v>2.84</v>
+      </c>
+      <c r="AU211">
+        <v>7</v>
+      </c>
+      <c r="AV211">
+        <v>3</v>
+      </c>
+      <c r="AW211">
+        <v>10</v>
+      </c>
+      <c r="AX211">
+        <v>2</v>
+      </c>
+      <c r="AY211">
+        <v>17</v>
+      </c>
+      <c r="AZ211">
+        <v>5</v>
+      </c>
+      <c r="BA211">
+        <v>6</v>
+      </c>
+      <c r="BB211">
+        <v>3</v>
+      </c>
+      <c r="BC211">
+        <v>9</v>
+      </c>
+      <c r="BD211">
+        <v>0</v>
+      </c>
+      <c r="BE211">
+        <v>0</v>
+      </c>
+      <c r="BF211">
+        <v>0</v>
+      </c>
+      <c r="BG211">
+        <v>0</v>
+      </c>
+      <c r="BH211">
+        <v>0</v>
+      </c>
+      <c r="BI211">
+        <v>0</v>
+      </c>
+      <c r="BJ211">
+        <v>0</v>
+      </c>
+      <c r="BK211">
+        <v>0</v>
+      </c>
+      <c r="BL211">
+        <v>0</v>
+      </c>
+      <c r="BM211">
+        <v>0</v>
+      </c>
+      <c r="BN211">
+        <v>0</v>
+      </c>
+      <c r="BO211">
+        <v>0</v>
+      </c>
+      <c r="BP211">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="212" spans="1:68">
+      <c r="A212" s="1">
+        <v>211</v>
+      </c>
+      <c r="B212">
+        <v>7468296</v>
+      </c>
+      <c r="C212" t="s">
+        <v>68</v>
+      </c>
+      <c r="D212" t="s">
+        <v>69</v>
+      </c>
+      <c r="E212" s="2">
+        <v>45745.625</v>
+      </c>
+      <c r="F212">
+        <v>27</v>
+      </c>
+      <c r="G212" t="s">
+        <v>74</v>
+      </c>
+      <c r="H212" t="s">
+        <v>80</v>
+      </c>
+      <c r="I212">
+        <v>0</v>
+      </c>
+      <c r="J212">
+        <v>0</v>
+      </c>
+      <c r="K212">
+        <v>0</v>
+      </c>
+      <c r="L212">
+        <v>0</v>
+      </c>
+      <c r="M212">
+        <v>0</v>
+      </c>
+      <c r="N212">
+        <v>0</v>
+      </c>
+      <c r="O212" t="s">
+        <v>88</v>
+      </c>
+      <c r="P212" t="s">
+        <v>88</v>
+      </c>
+      <c r="Q212">
+        <v>11</v>
+      </c>
+      <c r="R212">
+        <v>2.6</v>
+      </c>
+      <c r="S212">
+        <v>1.67</v>
+      </c>
+      <c r="T212">
+        <v>1.33</v>
+      </c>
+      <c r="U212">
+        <v>3.25</v>
+      </c>
+      <c r="V212">
+        <v>2.5</v>
+      </c>
+      <c r="W212">
+        <v>1.5</v>
+      </c>
+      <c r="X212">
+        <v>6.5</v>
+      </c>
+      <c r="Y212">
+        <v>1.11</v>
+      </c>
+      <c r="Z212">
+        <v>12</v>
+      </c>
+      <c r="AA212">
+        <v>6</v>
+      </c>
+      <c r="AB212">
+        <v>1.22</v>
+      </c>
+      <c r="AC212">
+        <v>0</v>
+      </c>
+      <c r="AD212">
+        <v>0</v>
+      </c>
+      <c r="AE212">
+        <v>0</v>
+      </c>
+      <c r="AF212">
+        <v>0</v>
+      </c>
+      <c r="AG212">
+        <v>1.7</v>
+      </c>
+      <c r="AH212">
+        <v>2.1</v>
+      </c>
+      <c r="AI212">
+        <v>2.38</v>
+      </c>
+      <c r="AJ212">
+        <v>1.53</v>
+      </c>
+      <c r="AK212">
+        <v>0</v>
+      </c>
+      <c r="AL212">
+        <v>0</v>
+      </c>
+      <c r="AM212">
+        <v>0</v>
+      </c>
+      <c r="AN212">
+        <v>0.92</v>
+      </c>
+      <c r="AO212">
+        <v>2.23</v>
+      </c>
+      <c r="AP212">
+        <v>0.93</v>
+      </c>
+      <c r="AQ212">
+        <v>2.14</v>
+      </c>
+      <c r="AR212">
+        <v>1.26</v>
+      </c>
+      <c r="AS212">
+        <v>1.78</v>
+      </c>
+      <c r="AT212">
+        <v>3.04</v>
+      </c>
+      <c r="AU212">
+        <v>6</v>
+      </c>
+      <c r="AV212">
+        <v>4</v>
+      </c>
+      <c r="AW212">
+        <v>10</v>
+      </c>
+      <c r="AX212">
+        <v>9</v>
+      </c>
+      <c r="AY212">
+        <v>16</v>
+      </c>
+      <c r="AZ212">
+        <v>13</v>
+      </c>
+      <c r="BA212">
+        <v>4</v>
+      </c>
+      <c r="BB212">
+        <v>6</v>
+      </c>
+      <c r="BC212">
+        <v>10</v>
+      </c>
+      <c r="BD212">
+        <v>0</v>
+      </c>
+      <c r="BE212">
+        <v>0</v>
+      </c>
+      <c r="BF212">
+        <v>0</v>
+      </c>
+      <c r="BG212">
+        <v>0</v>
+      </c>
+      <c r="BH212">
+        <v>0</v>
+      </c>
+      <c r="BI212">
+        <v>0</v>
+      </c>
+      <c r="BJ212">
+        <v>0</v>
+      </c>
+      <c r="BK212">
+        <v>0</v>
+      </c>
+      <c r="BL212">
+        <v>0</v>
+      </c>
+      <c r="BM212">
+        <v>0</v>
+      </c>
+      <c r="BN212">
+        <v>0</v>
+      </c>
+      <c r="BO212">
+        <v>0</v>
+      </c>
+      <c r="BP212">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="213" spans="1:68">
+      <c r="A213" s="1">
+        <v>212</v>
+      </c>
+      <c r="B213">
+        <v>7468294</v>
+      </c>
+      <c r="C213" t="s">
+        <v>68</v>
+      </c>
+      <c r="D213" t="s">
+        <v>69</v>
+      </c>
+      <c r="E213" s="2">
+        <v>45746.33333333334</v>
+      </c>
+      <c r="F213">
+        <v>27</v>
+      </c>
+      <c r="G213" t="s">
+        <v>76</v>
+      </c>
+      <c r="H213" t="s">
+        <v>81</v>
+      </c>
+      <c r="I213">
+        <v>0</v>
+      </c>
+      <c r="J213">
+        <v>4</v>
+      </c>
+      <c r="K213">
+        <v>4</v>
+      </c>
+      <c r="L213">
+        <v>0</v>
+      </c>
+      <c r="M213">
+        <v>4</v>
+      </c>
+      <c r="N213">
+        <v>4</v>
+      </c>
+      <c r="O213" t="s">
+        <v>88</v>
+      </c>
+      <c r="P213" t="s">
+        <v>314</v>
+      </c>
+      <c r="Q213">
+        <v>3.5</v>
+      </c>
+      <c r="R213">
+        <v>2</v>
+      </c>
+      <c r="S213">
+        <v>3.25</v>
+      </c>
+      <c r="T213">
+        <v>1.5</v>
+      </c>
+      <c r="U213">
+        <v>2.5</v>
+      </c>
+      <c r="V213">
+        <v>3.4</v>
+      </c>
+      <c r="W213">
+        <v>1.3</v>
+      </c>
+      <c r="X213">
+        <v>10</v>
+      </c>
+      <c r="Y213">
+        <v>1.06</v>
+      </c>
+      <c r="Z213">
+        <v>2.8</v>
+      </c>
+      <c r="AA213">
+        <v>3.1</v>
+      </c>
+      <c r="AB213">
+        <v>2.55</v>
+      </c>
+      <c r="AC213">
+        <v>0</v>
+      </c>
+      <c r="AD213">
+        <v>0</v>
+      </c>
+      <c r="AE213">
+        <v>0</v>
+      </c>
+      <c r="AF213">
+        <v>0</v>
+      </c>
+      <c r="AG213">
+        <v>2.2</v>
+      </c>
+      <c r="AH213">
+        <v>1.65</v>
+      </c>
+      <c r="AI213">
+        <v>1.91</v>
+      </c>
+      <c r="AJ213">
+        <v>1.91</v>
+      </c>
+      <c r="AK213">
+        <v>0</v>
+      </c>
+      <c r="AL213">
+        <v>0</v>
+      </c>
+      <c r="AM213">
+        <v>0</v>
+      </c>
+      <c r="AN213">
+        <v>1.5</v>
+      </c>
+      <c r="AO213">
+        <v>1</v>
+      </c>
+      <c r="AP213">
+        <v>1.38</v>
+      </c>
+      <c r="AQ213">
+        <v>1.14</v>
+      </c>
+      <c r="AR213">
+        <v>1.18</v>
+      </c>
+      <c r="AS213">
+        <v>1.44</v>
+      </c>
+      <c r="AT213">
+        <v>2.62</v>
+      </c>
+      <c r="AU213">
+        <v>3</v>
+      </c>
+      <c r="AV213">
+        <v>8</v>
+      </c>
+      <c r="AW213">
+        <v>13</v>
+      </c>
+      <c r="AX213">
+        <v>3</v>
+      </c>
+      <c r="AY213">
+        <v>16</v>
+      </c>
+      <c r="AZ213">
+        <v>11</v>
+      </c>
+      <c r="BA213">
+        <v>5</v>
+      </c>
+      <c r="BB213">
+        <v>2</v>
+      </c>
+      <c r="BC213">
+        <v>7</v>
+      </c>
+      <c r="BD213">
+        <v>0</v>
+      </c>
+      <c r="BE213">
+        <v>0</v>
+      </c>
+      <c r="BF213">
+        <v>0</v>
+      </c>
+      <c r="BG213">
+        <v>0</v>
+      </c>
+      <c r="BH213">
+        <v>0</v>
+      </c>
+      <c r="BI213">
+        <v>0</v>
+      </c>
+      <c r="BJ213">
+        <v>0</v>
+      </c>
+      <c r="BK213">
+        <v>0</v>
+      </c>
+      <c r="BL213">
+        <v>0</v>
+      </c>
+      <c r="BM213">
+        <v>0</v>
+      </c>
+      <c r="BN213">
+        <v>0</v>
+      </c>
+      <c r="BO213">
+        <v>0</v>
+      </c>
+      <c r="BP213">
+        <v>0</v>
       </c>
     </row>
   </sheetData>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Czech Republic First League_20242025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Czech Republic First League_20242025.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1340" uniqueCount="315">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1358" uniqueCount="318">
   <si>
     <t>Id_Jogo</t>
   </si>
@@ -682,6 +682,15 @@
     <t>['17', '34', '67', '84', '90+1']</t>
   </si>
   <si>
+    <t>['35', '56', '61']</t>
+  </si>
+  <si>
+    <t>['34']</t>
+  </si>
+  <si>
+    <t>['8', '48']</t>
+  </si>
+  <si>
     <t>['25']</t>
   </si>
   <si>
@@ -889,9 +898,6 @@
     <t>['26', '30', '38']</t>
   </si>
   <si>
-    <t>['34']</t>
-  </si>
-  <si>
     <t>['4', '27', '73']</t>
   </si>
   <si>
@@ -959,6 +965,9 @@
   </si>
   <si>
     <t>['13', '19', '28', '36']</t>
+  </si>
+  <si>
+    <t>['14', '37', '53', '61']</t>
   </si>
 </sst>
 </file>
@@ -1320,7 +1329,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:BP213"/>
+  <dimension ref="A1:BP216"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:68">
@@ -1576,7 +1585,7 @@
         <v>86</v>
       </c>
       <c r="P2" t="s">
-        <v>222</v>
+        <v>225</v>
       </c>
       <c r="Q2">
         <v>1.53</v>
@@ -1654,7 +1663,7 @@
         <v>0</v>
       </c>
       <c r="AP2">
-        <v>2.23</v>
+        <v>2.07</v>
       </c>
       <c r="AQ2">
         <v>0.43</v>
@@ -1863,7 +1872,7 @@
         <v>1.93</v>
       </c>
       <c r="AQ3">
-        <v>1.15</v>
+        <v>1.07</v>
       </c>
       <c r="AR3">
         <v>0</v>
@@ -1988,7 +1997,7 @@
         <v>88</v>
       </c>
       <c r="P4" t="s">
-        <v>223</v>
+        <v>226</v>
       </c>
       <c r="Q4">
         <v>2.88</v>
@@ -2400,7 +2409,7 @@
         <v>90</v>
       </c>
       <c r="P6" t="s">
-        <v>224</v>
+        <v>227</v>
       </c>
       <c r="Q6">
         <v>5.5</v>
@@ -2481,7 +2490,7 @@
         <v>0.93</v>
       </c>
       <c r="AQ6">
-        <v>1.85</v>
+        <v>1.93</v>
       </c>
       <c r="AR6">
         <v>0</v>
@@ -2606,7 +2615,7 @@
         <v>91</v>
       </c>
       <c r="P7" t="s">
-        <v>225</v>
+        <v>228</v>
       </c>
       <c r="Q7">
         <v>3.2</v>
@@ -2684,7 +2693,7 @@
         <v>0</v>
       </c>
       <c r="AP7">
-        <v>1.46</v>
+        <v>1.57</v>
       </c>
       <c r="AQ7">
         <v>1.14</v>
@@ -3096,7 +3105,7 @@
         <v>0</v>
       </c>
       <c r="AP9">
-        <v>1.54</v>
+        <v>1.64</v>
       </c>
       <c r="AQ9">
         <v>0.79</v>
@@ -3430,7 +3439,7 @@
         <v>94</v>
       </c>
       <c r="P11" t="s">
-        <v>226</v>
+        <v>229</v>
       </c>
       <c r="Q11">
         <v>6.5</v>
@@ -3636,7 +3645,7 @@
         <v>88</v>
       </c>
       <c r="P12" t="s">
-        <v>227</v>
+        <v>230</v>
       </c>
       <c r="Q12">
         <v>2.85</v>
@@ -4872,7 +4881,7 @@
         <v>88</v>
       </c>
       <c r="P18" t="s">
-        <v>228</v>
+        <v>231</v>
       </c>
       <c r="Q18">
         <v>5.4</v>
@@ -5156,7 +5165,7 @@
         <v>0</v>
       </c>
       <c r="AP19">
-        <v>2.23</v>
+        <v>2.07</v>
       </c>
       <c r="AQ19">
         <v>0.62</v>
@@ -5571,7 +5580,7 @@
         <v>1.93</v>
       </c>
       <c r="AQ21">
-        <v>1.85</v>
+        <v>1.93</v>
       </c>
       <c r="AR21">
         <v>1.81</v>
@@ -5902,7 +5911,7 @@
         <v>102</v>
       </c>
       <c r="P23" t="s">
-        <v>229</v>
+        <v>232</v>
       </c>
       <c r="Q23">
         <v>2.6</v>
@@ -6108,7 +6117,7 @@
         <v>103</v>
       </c>
       <c r="P24" t="s">
-        <v>230</v>
+        <v>233</v>
       </c>
       <c r="Q24">
         <v>2.75</v>
@@ -6186,10 +6195,10 @@
         <v>0</v>
       </c>
       <c r="AP24">
-        <v>1.54</v>
+        <v>1.64</v>
       </c>
       <c r="AQ24">
-        <v>1.15</v>
+        <v>1.07</v>
       </c>
       <c r="AR24">
         <v>1.19</v>
@@ -6314,7 +6323,7 @@
         <v>88</v>
       </c>
       <c r="P25" t="s">
-        <v>231</v>
+        <v>234</v>
       </c>
       <c r="Q25">
         <v>1.06</v>
@@ -6520,7 +6529,7 @@
         <v>104</v>
       </c>
       <c r="P26" t="s">
-        <v>232</v>
+        <v>235</v>
       </c>
       <c r="Q26">
         <v>6.23</v>
@@ -8040,7 +8049,7 @@
         <v>0</v>
       </c>
       <c r="AP33">
-        <v>1.54</v>
+        <v>1.64</v>
       </c>
       <c r="AQ33">
         <v>0.62</v>
@@ -8168,7 +8177,7 @@
         <v>111</v>
       </c>
       <c r="P34" t="s">
-        <v>233</v>
+        <v>236</v>
       </c>
       <c r="Q34">
         <v>1.45</v>
@@ -8374,7 +8383,7 @@
         <v>112</v>
       </c>
       <c r="P35" t="s">
-        <v>234</v>
+        <v>237</v>
       </c>
       <c r="Q35">
         <v>2.84</v>
@@ -8452,7 +8461,7 @@
         <v>0.5</v>
       </c>
       <c r="AP35">
-        <v>1.46</v>
+        <v>1.57</v>
       </c>
       <c r="AQ35">
         <v>1.46</v>
@@ -8580,7 +8589,7 @@
         <v>113</v>
       </c>
       <c r="P36" t="s">
-        <v>235</v>
+        <v>238</v>
       </c>
       <c r="Q36">
         <v>5.63</v>
@@ -8786,7 +8795,7 @@
         <v>114</v>
       </c>
       <c r="P37" t="s">
-        <v>236</v>
+        <v>239</v>
       </c>
       <c r="Q37">
         <v>2.58</v>
@@ -8867,7 +8876,7 @@
         <v>1.54</v>
       </c>
       <c r="AQ37">
-        <v>1.15</v>
+        <v>1.07</v>
       </c>
       <c r="AR37">
         <v>1.25</v>
@@ -9198,7 +9207,7 @@
         <v>88</v>
       </c>
       <c r="P39" t="s">
-        <v>237</v>
+        <v>240</v>
       </c>
       <c r="Q39">
         <v>4.75</v>
@@ -9279,7 +9288,7 @@
         <v>0.21</v>
       </c>
       <c r="AQ39">
-        <v>1.85</v>
+        <v>1.93</v>
       </c>
       <c r="AR39">
         <v>1.46</v>
@@ -9610,7 +9619,7 @@
         <v>117</v>
       </c>
       <c r="P41" t="s">
-        <v>238</v>
+        <v>241</v>
       </c>
       <c r="Q41">
         <v>2.4</v>
@@ -9816,7 +9825,7 @@
         <v>107</v>
       </c>
       <c r="P42" t="s">
-        <v>239</v>
+        <v>242</v>
       </c>
       <c r="Q42">
         <v>2.61</v>
@@ -10022,7 +10031,7 @@
         <v>118</v>
       </c>
       <c r="P43" t="s">
-        <v>240</v>
+        <v>243</v>
       </c>
       <c r="Q43">
         <v>1.69</v>
@@ -10100,7 +10109,7 @@
         <v>1.5</v>
       </c>
       <c r="AP43">
-        <v>2.23</v>
+        <v>2.07</v>
       </c>
       <c r="AQ43">
         <v>0.85</v>
@@ -10924,7 +10933,7 @@
         <v>0</v>
       </c>
       <c r="AP47">
-        <v>1.46</v>
+        <v>1.57</v>
       </c>
       <c r="AQ47">
         <v>1.71</v>
@@ -11464,7 +11473,7 @@
         <v>88</v>
       </c>
       <c r="P50" t="s">
-        <v>241</v>
+        <v>244</v>
       </c>
       <c r="Q50">
         <v>5.1</v>
@@ -11542,7 +11551,7 @@
         <v>3</v>
       </c>
       <c r="AP50">
-        <v>1.54</v>
+        <v>1.64</v>
       </c>
       <c r="AQ50">
         <v>2</v>
@@ -11748,7 +11757,7 @@
         <v>0</v>
       </c>
       <c r="AP51">
-        <v>1.46</v>
+        <v>1.57</v>
       </c>
       <c r="AQ51">
         <v>0.62</v>
@@ -11876,7 +11885,7 @@
         <v>122</v>
       </c>
       <c r="P52" t="s">
-        <v>242</v>
+        <v>245</v>
       </c>
       <c r="Q52">
         <v>3</v>
@@ -12288,7 +12297,7 @@
         <v>124</v>
       </c>
       <c r="P54" t="s">
-        <v>243</v>
+        <v>246</v>
       </c>
       <c r="Q54">
         <v>3</v>
@@ -12369,7 +12378,7 @@
         <v>1.46</v>
       </c>
       <c r="AQ54">
-        <v>1.15</v>
+        <v>1.07</v>
       </c>
       <c r="AR54">
         <v>1.4</v>
@@ -12575,7 +12584,7 @@
         <v>1.54</v>
       </c>
       <c r="AQ55">
-        <v>1.85</v>
+        <v>1.93</v>
       </c>
       <c r="AR55">
         <v>1.32</v>
@@ -12906,7 +12915,7 @@
         <v>88</v>
       </c>
       <c r="P57" t="s">
-        <v>244</v>
+        <v>247</v>
       </c>
       <c r="Q57">
         <v>5.88</v>
@@ -13190,7 +13199,7 @@
         <v>1.33</v>
       </c>
       <c r="AP58">
-        <v>1.54</v>
+        <v>1.64</v>
       </c>
       <c r="AQ58">
         <v>0.85</v>
@@ -13318,7 +13327,7 @@
         <v>127</v>
       </c>
       <c r="P59" t="s">
-        <v>245</v>
+        <v>248</v>
       </c>
       <c r="Q59">
         <v>3.86</v>
@@ -13602,7 +13611,7 @@
         <v>1.75</v>
       </c>
       <c r="AP60">
-        <v>1.46</v>
+        <v>1.57</v>
       </c>
       <c r="AQ60">
         <v>1.15</v>
@@ -13811,7 +13820,7 @@
         <v>3</v>
       </c>
       <c r="AQ61">
-        <v>1.85</v>
+        <v>1.93</v>
       </c>
       <c r="AR61">
         <v>2.33</v>
@@ -13936,7 +13945,7 @@
         <v>130</v>
       </c>
       <c r="P62" t="s">
-        <v>246</v>
+        <v>249</v>
       </c>
       <c r="Q62">
         <v>1.83</v>
@@ -14142,7 +14151,7 @@
         <v>88</v>
       </c>
       <c r="P63" t="s">
-        <v>247</v>
+        <v>250</v>
       </c>
       <c r="Q63">
         <v>8.77</v>
@@ -14554,7 +14563,7 @@
         <v>132</v>
       </c>
       <c r="P65" t="s">
-        <v>248</v>
+        <v>251</v>
       </c>
       <c r="Q65">
         <v>2.4</v>
@@ -14760,7 +14769,7 @@
         <v>133</v>
       </c>
       <c r="P66" t="s">
-        <v>249</v>
+        <v>252</v>
       </c>
       <c r="Q66">
         <v>1.55</v>
@@ -14838,7 +14847,7 @@
         <v>1</v>
       </c>
       <c r="AP66">
-        <v>2.23</v>
+        <v>2.07</v>
       </c>
       <c r="AQ66">
         <v>1.36</v>
@@ -14966,7 +14975,7 @@
         <v>134</v>
       </c>
       <c r="P67" t="s">
-        <v>250</v>
+        <v>253</v>
       </c>
       <c r="Q67">
         <v>4</v>
@@ -15172,7 +15181,7 @@
         <v>88</v>
       </c>
       <c r="P68" t="s">
-        <v>251</v>
+        <v>254</v>
       </c>
       <c r="Q68">
         <v>3.1</v>
@@ -15996,7 +16005,7 @@
         <v>124</v>
       </c>
       <c r="P72" t="s">
-        <v>252</v>
+        <v>255</v>
       </c>
       <c r="Q72">
         <v>1.88</v>
@@ -16077,7 +16086,7 @@
         <v>2.23</v>
       </c>
       <c r="AQ72">
-        <v>1.15</v>
+        <v>1.07</v>
       </c>
       <c r="AR72">
         <v>1.84</v>
@@ -16202,7 +16211,7 @@
         <v>88</v>
       </c>
       <c r="P73" t="s">
-        <v>253</v>
+        <v>256</v>
       </c>
       <c r="Q73">
         <v>7</v>
@@ -16486,7 +16495,7 @@
         <v>0</v>
       </c>
       <c r="AP74">
-        <v>1.46</v>
+        <v>1.57</v>
       </c>
       <c r="AQ74">
         <v>1.17</v>
@@ -16614,7 +16623,7 @@
         <v>138</v>
       </c>
       <c r="P75" t="s">
-        <v>254</v>
+        <v>257</v>
       </c>
       <c r="Q75">
         <v>2.3</v>
@@ -16820,7 +16829,7 @@
         <v>88</v>
       </c>
       <c r="P76" t="s">
-        <v>255</v>
+        <v>258</v>
       </c>
       <c r="Q76">
         <v>3.7</v>
@@ -17026,7 +17035,7 @@
         <v>88</v>
       </c>
       <c r="P77" t="s">
-        <v>256</v>
+        <v>259</v>
       </c>
       <c r="Q77">
         <v>2.47</v>
@@ -17644,7 +17653,7 @@
         <v>140</v>
       </c>
       <c r="P80" t="s">
-        <v>257</v>
+        <v>260</v>
       </c>
       <c r="Q80">
         <v>2.5</v>
@@ -17850,7 +17859,7 @@
         <v>141</v>
       </c>
       <c r="P81" t="s">
-        <v>258</v>
+        <v>261</v>
       </c>
       <c r="Q81">
         <v>2.38</v>
@@ -18056,7 +18065,7 @@
         <v>142</v>
       </c>
       <c r="P82" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="Q82">
         <v>2.8</v>
@@ -18134,7 +18143,7 @@
         <v>1.4</v>
       </c>
       <c r="AP82">
-        <v>1.54</v>
+        <v>1.64</v>
       </c>
       <c r="AQ82">
         <v>1.36</v>
@@ -18262,7 +18271,7 @@
         <v>143</v>
       </c>
       <c r="P83" t="s">
-        <v>260</v>
+        <v>263</v>
       </c>
       <c r="Q83">
         <v>2.6</v>
@@ -18468,7 +18477,7 @@
         <v>144</v>
       </c>
       <c r="P84" t="s">
-        <v>261</v>
+        <v>264</v>
       </c>
       <c r="Q84">
         <v>3.4</v>
@@ -18549,7 +18558,7 @@
         <v>2.54</v>
       </c>
       <c r="AQ84">
-        <v>1.85</v>
+        <v>1.93</v>
       </c>
       <c r="AR84">
         <v>1.81</v>
@@ -18752,7 +18761,7 @@
         <v>1.5</v>
       </c>
       <c r="AP85">
-        <v>2.23</v>
+        <v>2.07</v>
       </c>
       <c r="AQ85">
         <v>1.14</v>
@@ -18880,7 +18889,7 @@
         <v>146</v>
       </c>
       <c r="P86" t="s">
-        <v>262</v>
+        <v>265</v>
       </c>
       <c r="Q86">
         <v>2.88</v>
@@ -18961,7 +18970,7 @@
         <v>1.07</v>
       </c>
       <c r="AQ86">
-        <v>1.15</v>
+        <v>1.07</v>
       </c>
       <c r="AR86">
         <v>1.41</v>
@@ -19164,7 +19173,7 @@
         <v>0</v>
       </c>
       <c r="AP87">
-        <v>1.46</v>
+        <v>1.57</v>
       </c>
       <c r="AQ87">
         <v>0.08</v>
@@ -19292,7 +19301,7 @@
         <v>88</v>
       </c>
       <c r="P88" t="s">
-        <v>263</v>
+        <v>266</v>
       </c>
       <c r="Q88">
         <v>2.6</v>
@@ -19498,7 +19507,7 @@
         <v>93</v>
       </c>
       <c r="P89" t="s">
-        <v>264</v>
+        <v>267</v>
       </c>
       <c r="Q89">
         <v>6.5</v>
@@ -19910,7 +19919,7 @@
         <v>149</v>
       </c>
       <c r="P91" t="s">
-        <v>265</v>
+        <v>268</v>
       </c>
       <c r="Q91">
         <v>4.7</v>
@@ -20116,7 +20125,7 @@
         <v>88</v>
       </c>
       <c r="P92" t="s">
-        <v>266</v>
+        <v>269</v>
       </c>
       <c r="Q92">
         <v>3.8</v>
@@ -20528,7 +20537,7 @@
         <v>150</v>
       </c>
       <c r="P94" t="s">
-        <v>267</v>
+        <v>270</v>
       </c>
       <c r="Q94">
         <v>3</v>
@@ -21433,7 +21442,7 @@
         <v>0.93</v>
       </c>
       <c r="AQ98">
-        <v>1.15</v>
+        <v>1.07</v>
       </c>
       <c r="AR98">
         <v>1.15</v>
@@ -21842,7 +21851,7 @@
         <v>1.33</v>
       </c>
       <c r="AP100">
-        <v>1.46</v>
+        <v>1.57</v>
       </c>
       <c r="AQ100">
         <v>1.36</v>
@@ -21970,7 +21979,7 @@
         <v>156</v>
       </c>
       <c r="P101" t="s">
-        <v>268</v>
+        <v>271</v>
       </c>
       <c r="Q101">
         <v>1.83</v>
@@ -22048,7 +22057,7 @@
         <v>1.29</v>
       </c>
       <c r="AP101">
-        <v>2.23</v>
+        <v>2.07</v>
       </c>
       <c r="AQ101">
         <v>1.71</v>
@@ -22669,7 +22678,7 @@
         <v>1.38</v>
       </c>
       <c r="AQ104">
-        <v>1.85</v>
+        <v>1.93</v>
       </c>
       <c r="AR104">
         <v>1.15</v>
@@ -22872,7 +22881,7 @@
         <v>2.6</v>
       </c>
       <c r="AP105">
-        <v>1.54</v>
+        <v>1.64</v>
       </c>
       <c r="AQ105">
         <v>2.14</v>
@@ -23618,7 +23627,7 @@
         <v>161</v>
       </c>
       <c r="P109" t="s">
-        <v>269</v>
+        <v>272</v>
       </c>
       <c r="Q109">
         <v>2.24</v>
@@ -23824,7 +23833,7 @@
         <v>162</v>
       </c>
       <c r="P110" t="s">
-        <v>270</v>
+        <v>273</v>
       </c>
       <c r="Q110">
         <v>4.6</v>
@@ -24442,7 +24451,7 @@
         <v>165</v>
       </c>
       <c r="P113" t="s">
-        <v>271</v>
+        <v>274</v>
       </c>
       <c r="Q113">
         <v>3.25</v>
@@ -24648,7 +24657,7 @@
         <v>151</v>
       </c>
       <c r="P114" t="s">
-        <v>272</v>
+        <v>275</v>
       </c>
       <c r="Q114">
         <v>2.88</v>
@@ -24729,7 +24738,7 @@
         <v>1.38</v>
       </c>
       <c r="AQ114">
-        <v>1.15</v>
+        <v>1.07</v>
       </c>
       <c r="AR114">
         <v>1.11</v>
@@ -24854,7 +24863,7 @@
         <v>99</v>
       </c>
       <c r="P115" t="s">
-        <v>273</v>
+        <v>276</v>
       </c>
       <c r="Q115">
         <v>1.73</v>
@@ -24932,7 +24941,7 @@
         <v>1</v>
       </c>
       <c r="AP115">
-        <v>2.23</v>
+        <v>2.07</v>
       </c>
       <c r="AQ115">
         <v>0.79</v>
@@ -25060,7 +25069,7 @@
         <v>88</v>
       </c>
       <c r="P116" t="s">
-        <v>274</v>
+        <v>277</v>
       </c>
       <c r="Q116">
         <v>4.33</v>
@@ -25138,10 +25147,10 @@
         <v>1.57</v>
       </c>
       <c r="AP116">
-        <v>1.54</v>
+        <v>1.64</v>
       </c>
       <c r="AQ116">
-        <v>1.85</v>
+        <v>1.93</v>
       </c>
       <c r="AR116">
         <v>1.34</v>
@@ -25550,7 +25559,7 @@
         <v>0.63</v>
       </c>
       <c r="AP118">
-        <v>1.46</v>
+        <v>1.57</v>
       </c>
       <c r="AQ118">
         <v>0.43</v>
@@ -25678,7 +25687,7 @@
         <v>88</v>
       </c>
       <c r="P119" t="s">
-        <v>275</v>
+        <v>278</v>
       </c>
       <c r="Q119">
         <v>15</v>
@@ -25884,7 +25893,7 @@
         <v>168</v>
       </c>
       <c r="P120" t="s">
-        <v>276</v>
+        <v>279</v>
       </c>
       <c r="Q120">
         <v>3</v>
@@ -26296,7 +26305,7 @@
         <v>170</v>
       </c>
       <c r="P122" t="s">
-        <v>277</v>
+        <v>280</v>
       </c>
       <c r="Q122">
         <v>3.25</v>
@@ -26708,7 +26717,7 @@
         <v>172</v>
       </c>
       <c r="P124" t="s">
-        <v>227</v>
+        <v>230</v>
       </c>
       <c r="Q124">
         <v>1.83</v>
@@ -26914,7 +26923,7 @@
         <v>171</v>
       </c>
       <c r="P125" t="s">
-        <v>278</v>
+        <v>281</v>
       </c>
       <c r="Q125">
         <v>6.3</v>
@@ -27738,7 +27747,7 @@
         <v>174</v>
       </c>
       <c r="P129" t="s">
-        <v>279</v>
+        <v>282</v>
       </c>
       <c r="Q129">
         <v>2.1</v>
@@ -27944,7 +27953,7 @@
         <v>175</v>
       </c>
       <c r="P130" t="s">
-        <v>280</v>
+        <v>283</v>
       </c>
       <c r="Q130">
         <v>1.5</v>
@@ -28022,7 +28031,7 @@
         <v>1</v>
       </c>
       <c r="AP130">
-        <v>2.23</v>
+        <v>2.07</v>
       </c>
       <c r="AQ130">
         <v>1</v>
@@ -28150,7 +28159,7 @@
         <v>176</v>
       </c>
       <c r="P131" t="s">
-        <v>281</v>
+        <v>284</v>
       </c>
       <c r="Q131">
         <v>3.5</v>
@@ -28356,7 +28365,7 @@
         <v>177</v>
       </c>
       <c r="P132" t="s">
-        <v>282</v>
+        <v>285</v>
       </c>
       <c r="Q132">
         <v>4.04</v>
@@ -28768,7 +28777,7 @@
         <v>88</v>
       </c>
       <c r="P134" t="s">
-        <v>283</v>
+        <v>286</v>
       </c>
       <c r="Q134">
         <v>2.75</v>
@@ -29592,7 +29601,7 @@
         <v>91</v>
       </c>
       <c r="P138" t="s">
-        <v>271</v>
+        <v>274</v>
       </c>
       <c r="Q138">
         <v>2.25</v>
@@ -29798,7 +29807,7 @@
         <v>179</v>
       </c>
       <c r="P139" t="s">
-        <v>280</v>
+        <v>283</v>
       </c>
       <c r="Q139">
         <v>1.9</v>
@@ -30082,7 +30091,7 @@
         <v>1.5</v>
       </c>
       <c r="AP140">
-        <v>2.23</v>
+        <v>2.07</v>
       </c>
       <c r="AQ140">
         <v>1.46</v>
@@ -30210,7 +30219,7 @@
         <v>88</v>
       </c>
       <c r="P141" t="s">
-        <v>284</v>
+        <v>287</v>
       </c>
       <c r="Q141">
         <v>4</v>
@@ -30291,7 +30300,7 @@
         <v>0.21</v>
       </c>
       <c r="AQ141">
-        <v>1.15</v>
+        <v>1.07</v>
       </c>
       <c r="AR141">
         <v>1.34</v>
@@ -30416,7 +30425,7 @@
         <v>117</v>
       </c>
       <c r="P142" t="s">
-        <v>285</v>
+        <v>288</v>
       </c>
       <c r="Q142">
         <v>4</v>
@@ -30494,10 +30503,10 @@
         <v>1.75</v>
       </c>
       <c r="AP142">
-        <v>1.46</v>
+        <v>1.57</v>
       </c>
       <c r="AQ142">
-        <v>1.85</v>
+        <v>1.93</v>
       </c>
       <c r="AR142">
         <v>1.59</v>
@@ -30828,7 +30837,7 @@
         <v>182</v>
       </c>
       <c r="P144" t="s">
-        <v>286</v>
+        <v>289</v>
       </c>
       <c r="Q144">
         <v>6</v>
@@ -31034,7 +31043,7 @@
         <v>88</v>
       </c>
       <c r="P145" t="s">
-        <v>287</v>
+        <v>290</v>
       </c>
       <c r="Q145">
         <v>3.5</v>
@@ -31112,7 +31121,7 @@
         <v>1.33</v>
       </c>
       <c r="AP145">
-        <v>1.54</v>
+        <v>1.64</v>
       </c>
       <c r="AQ145">
         <v>1.71</v>
@@ -31240,7 +31249,7 @@
         <v>183</v>
       </c>
       <c r="P146" t="s">
-        <v>288</v>
+        <v>291</v>
       </c>
       <c r="Q146">
         <v>4.33</v>
@@ -31446,7 +31455,7 @@
         <v>184</v>
       </c>
       <c r="P147" t="s">
-        <v>289</v>
+        <v>292</v>
       </c>
       <c r="Q147">
         <v>3.8</v>
@@ -31652,7 +31661,7 @@
         <v>185</v>
       </c>
       <c r="P148" t="s">
-        <v>290</v>
+        <v>293</v>
       </c>
       <c r="Q148">
         <v>2.5</v>
@@ -31858,7 +31867,7 @@
         <v>186</v>
       </c>
       <c r="P149" t="s">
-        <v>287</v>
+        <v>290</v>
       </c>
       <c r="Q149">
         <v>2.05</v>
@@ -32064,7 +32073,7 @@
         <v>187</v>
       </c>
       <c r="P150" t="s">
-        <v>291</v>
+        <v>223</v>
       </c>
       <c r="Q150">
         <v>1.95</v>
@@ -32142,7 +32151,7 @@
         <v>1.22</v>
       </c>
       <c r="AP150">
-        <v>2.23</v>
+        <v>2.07</v>
       </c>
       <c r="AQ150">
         <v>1.15</v>
@@ -32270,7 +32279,7 @@
         <v>188</v>
       </c>
       <c r="P151" t="s">
-        <v>292</v>
+        <v>294</v>
       </c>
       <c r="Q151">
         <v>2.48</v>
@@ -32682,7 +32691,7 @@
         <v>190</v>
       </c>
       <c r="P153" t="s">
-        <v>293</v>
+        <v>295</v>
       </c>
       <c r="Q153">
         <v>1.4</v>
@@ -32966,7 +32975,7 @@
         <v>0.89</v>
       </c>
       <c r="AP154">
-        <v>1.46</v>
+        <v>1.57</v>
       </c>
       <c r="AQ154">
         <v>0.79</v>
@@ -33094,7 +33103,7 @@
         <v>88</v>
       </c>
       <c r="P155" t="s">
-        <v>230</v>
+        <v>233</v>
       </c>
       <c r="Q155">
         <v>3.2</v>
@@ -33584,7 +33593,7 @@
         <v>0.6</v>
       </c>
       <c r="AP157">
-        <v>1.54</v>
+        <v>1.64</v>
       </c>
       <c r="AQ157">
         <v>0.43</v>
@@ -33712,7 +33721,7 @@
         <v>88</v>
       </c>
       <c r="P158" t="s">
-        <v>294</v>
+        <v>296</v>
       </c>
       <c r="Q158">
         <v>5</v>
@@ -33918,7 +33927,7 @@
         <v>88</v>
       </c>
       <c r="P159" t="s">
-        <v>251</v>
+        <v>254</v>
       </c>
       <c r="Q159">
         <v>2.38</v>
@@ -34205,7 +34214,7 @@
         <v>3</v>
       </c>
       <c r="AQ160">
-        <v>1.15</v>
+        <v>1.07</v>
       </c>
       <c r="AR160">
         <v>2.39</v>
@@ -34330,7 +34339,7 @@
         <v>193</v>
       </c>
       <c r="P161" t="s">
-        <v>278</v>
+        <v>281</v>
       </c>
       <c r="Q161">
         <v>4.75</v>
@@ -34411,7 +34420,7 @@
         <v>1.54</v>
       </c>
       <c r="AQ161">
-        <v>1.85</v>
+        <v>1.93</v>
       </c>
       <c r="AR161">
         <v>1.6</v>
@@ -34536,7 +34545,7 @@
         <v>194</v>
       </c>
       <c r="P162" t="s">
-        <v>295</v>
+        <v>297</v>
       </c>
       <c r="Q162">
         <v>2.63</v>
@@ -34742,7 +34751,7 @@
         <v>88</v>
       </c>
       <c r="P163" t="s">
-        <v>296</v>
+        <v>298</v>
       </c>
       <c r="Q163">
         <v>11</v>
@@ -34948,7 +34957,7 @@
         <v>195</v>
       </c>
       <c r="P164" t="s">
-        <v>297</v>
+        <v>299</v>
       </c>
       <c r="Q164">
         <v>2</v>
@@ -35154,7 +35163,7 @@
         <v>196</v>
       </c>
       <c r="P165" t="s">
-        <v>298</v>
+        <v>300</v>
       </c>
       <c r="Q165">
         <v>2.5</v>
@@ -35850,7 +35859,7 @@
         <v>1.1</v>
       </c>
       <c r="AP168">
-        <v>2.23</v>
+        <v>2.07</v>
       </c>
       <c r="AQ168">
         <v>1.17</v>
@@ -36390,7 +36399,7 @@
         <v>201</v>
       </c>
       <c r="P171" t="s">
-        <v>299</v>
+        <v>301</v>
       </c>
       <c r="Q171">
         <v>5.2</v>
@@ -36596,7 +36605,7 @@
         <v>202</v>
       </c>
       <c r="P172" t="s">
-        <v>300</v>
+        <v>302</v>
       </c>
       <c r="Q172">
         <v>6.35</v>
@@ -36674,7 +36683,7 @@
         <v>2</v>
       </c>
       <c r="AP172">
-        <v>1.46</v>
+        <v>1.57</v>
       </c>
       <c r="AQ172">
         <v>2</v>
@@ -36802,7 +36811,7 @@
         <v>203</v>
       </c>
       <c r="P173" t="s">
-        <v>301</v>
+        <v>303</v>
       </c>
       <c r="Q173">
         <v>2.6</v>
@@ -36880,7 +36889,7 @@
         <v>1.5</v>
       </c>
       <c r="AP173">
-        <v>1.54</v>
+        <v>1.64</v>
       </c>
       <c r="AQ173">
         <v>1.46</v>
@@ -37008,7 +37017,7 @@
         <v>88</v>
       </c>
       <c r="P174" t="s">
-        <v>302</v>
+        <v>304</v>
       </c>
       <c r="Q174">
         <v>4.86</v>
@@ -37089,7 +37098,7 @@
         <v>1.46</v>
       </c>
       <c r="AQ174">
-        <v>1.85</v>
+        <v>1.93</v>
       </c>
       <c r="AR174">
         <v>1.47</v>
@@ -37214,7 +37223,7 @@
         <v>204</v>
       </c>
       <c r="P175" t="s">
-        <v>287</v>
+        <v>290</v>
       </c>
       <c r="Q175">
         <v>2.66</v>
@@ -37295,7 +37304,7 @@
         <v>1.54</v>
       </c>
       <c r="AQ175">
-        <v>1.15</v>
+        <v>1.07</v>
       </c>
       <c r="AR175">
         <v>1.42</v>
@@ -37626,7 +37635,7 @@
         <v>171</v>
       </c>
       <c r="P177" t="s">
-        <v>303</v>
+        <v>305</v>
       </c>
       <c r="Q177">
         <v>3.63</v>
@@ -38038,7 +38047,7 @@
         <v>88</v>
       </c>
       <c r="P179" t="s">
-        <v>304</v>
+        <v>306</v>
       </c>
       <c r="Q179">
         <v>3.92</v>
@@ -38119,7 +38128,7 @@
         <v>0.77</v>
       </c>
       <c r="AQ179">
-        <v>1.15</v>
+        <v>1.07</v>
       </c>
       <c r="AR179">
         <v>1.2</v>
@@ -38244,7 +38253,7 @@
         <v>206</v>
       </c>
       <c r="P180" t="s">
-        <v>305</v>
+        <v>307</v>
       </c>
       <c r="Q180">
         <v>1.32</v>
@@ -38322,7 +38331,7 @@
         <v>0.1</v>
       </c>
       <c r="AP180">
-        <v>2.23</v>
+        <v>2.07</v>
       </c>
       <c r="AQ180">
         <v>0.08</v>
@@ -38862,7 +38871,7 @@
         <v>208</v>
       </c>
       <c r="P183" t="s">
-        <v>306</v>
+        <v>308</v>
       </c>
       <c r="Q183">
         <v>4.3</v>
@@ -39068,7 +39077,7 @@
         <v>88</v>
       </c>
       <c r="P184" t="s">
-        <v>307</v>
+        <v>309</v>
       </c>
       <c r="Q184">
         <v>5.8</v>
@@ -39352,7 +39361,7 @@
         <v>1.27</v>
       </c>
       <c r="AP185">
-        <v>1.54</v>
+        <v>1.64</v>
       </c>
       <c r="AQ185">
         <v>1.15</v>
@@ -39480,7 +39489,7 @@
         <v>96</v>
       </c>
       <c r="P186" t="s">
-        <v>308</v>
+        <v>310</v>
       </c>
       <c r="Q186">
         <v>4.7</v>
@@ -40098,7 +40107,7 @@
         <v>88</v>
       </c>
       <c r="P189" t="s">
-        <v>309</v>
+        <v>311</v>
       </c>
       <c r="Q189">
         <v>4.5</v>
@@ -40179,7 +40188,7 @@
         <v>1.46</v>
       </c>
       <c r="AQ189">
-        <v>1.85</v>
+        <v>1.93</v>
       </c>
       <c r="AR189">
         <v>1.57</v>
@@ -40382,7 +40391,7 @@
         <v>1</v>
       </c>
       <c r="AP190">
-        <v>1.46</v>
+        <v>1.57</v>
       </c>
       <c r="AQ190">
         <v>0.85</v>
@@ -41412,7 +41421,7 @@
         <v>2.42</v>
       </c>
       <c r="AP195">
-        <v>2.23</v>
+        <v>2.07</v>
       </c>
       <c r="AQ195">
         <v>2.14</v>
@@ -41540,7 +41549,7 @@
         <v>215</v>
       </c>
       <c r="P196" t="s">
-        <v>227</v>
+        <v>230</v>
       </c>
       <c r="Q196">
         <v>1.95</v>
@@ -41621,7 +41630,7 @@
         <v>2.54</v>
       </c>
       <c r="AQ196">
-        <v>1.15</v>
+        <v>1.07</v>
       </c>
       <c r="AR196">
         <v>1.76</v>
@@ -41746,7 +41755,7 @@
         <v>88</v>
       </c>
       <c r="P197" t="s">
-        <v>227</v>
+        <v>230</v>
       </c>
       <c r="Q197">
         <v>2.88</v>
@@ -42030,7 +42039,7 @@
         <v>0.8</v>
       </c>
       <c r="AP198">
-        <v>1.54</v>
+        <v>1.64</v>
       </c>
       <c r="AQ198">
         <v>1</v>
@@ -42239,7 +42248,7 @@
         <v>0.77</v>
       </c>
       <c r="AQ199">
-        <v>1.85</v>
+        <v>1.93</v>
       </c>
       <c r="AR199">
         <v>1.23</v>
@@ -42570,7 +42579,7 @@
         <v>158</v>
       </c>
       <c r="P201" t="s">
-        <v>310</v>
+        <v>312</v>
       </c>
       <c r="Q201">
         <v>2.63</v>
@@ -42982,7 +42991,7 @@
         <v>88</v>
       </c>
       <c r="P203" t="s">
-        <v>251</v>
+        <v>254</v>
       </c>
       <c r="Q203">
         <v>2.75</v>
@@ -43394,7 +43403,7 @@
         <v>218</v>
       </c>
       <c r="P205" t="s">
-        <v>311</v>
+        <v>313</v>
       </c>
       <c r="Q205">
         <v>2.88</v>
@@ -43600,7 +43609,7 @@
         <v>88</v>
       </c>
       <c r="P206" t="s">
-        <v>272</v>
+        <v>275</v>
       </c>
       <c r="Q206">
         <v>2.38</v>
@@ -43806,7 +43815,7 @@
         <v>219</v>
       </c>
       <c r="P207" t="s">
-        <v>312</v>
+        <v>314</v>
       </c>
       <c r="Q207">
         <v>4.75</v>
@@ -44630,7 +44639,7 @@
         <v>221</v>
       </c>
       <c r="P211" t="s">
-        <v>313</v>
+        <v>315</v>
       </c>
       <c r="Q211">
         <v>1.57</v>
@@ -45042,7 +45051,7 @@
         <v>88</v>
       </c>
       <c r="P213" t="s">
-        <v>314</v>
+        <v>316</v>
       </c>
       <c r="Q213">
         <v>3.5</v>
@@ -45198,6 +45207,624 @@
         <v>0</v>
       </c>
       <c r="BP213">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="214" spans="1:68">
+      <c r="A214" s="1">
+        <v>213</v>
+      </c>
+      <c r="B214">
+        <v>7468298</v>
+      </c>
+      <c r="C214" t="s">
+        <v>68</v>
+      </c>
+      <c r="D214" t="s">
+        <v>69</v>
+      </c>
+      <c r="E214" s="2">
+        <v>45746.4375</v>
+      </c>
+      <c r="F214">
+        <v>27</v>
+      </c>
+      <c r="G214" t="s">
+        <v>75</v>
+      </c>
+      <c r="H214" t="s">
+        <v>82</v>
+      </c>
+      <c r="I214">
+        <v>1</v>
+      </c>
+      <c r="J214">
+        <v>1</v>
+      </c>
+      <c r="K214">
+        <v>2</v>
+      </c>
+      <c r="L214">
+        <v>3</v>
+      </c>
+      <c r="M214">
+        <v>1</v>
+      </c>
+      <c r="N214">
+        <v>4</v>
+      </c>
+      <c r="O214" t="s">
+        <v>222</v>
+      </c>
+      <c r="P214" t="s">
+        <v>153</v>
+      </c>
+      <c r="Q214">
+        <v>2.88</v>
+      </c>
+      <c r="R214">
+        <v>2.3</v>
+      </c>
+      <c r="S214">
+        <v>3.25</v>
+      </c>
+      <c r="T214">
+        <v>1.3</v>
+      </c>
+      <c r="U214">
+        <v>3.4</v>
+      </c>
+      <c r="V214">
+        <v>2.5</v>
+      </c>
+      <c r="W214">
+        <v>1.5</v>
+      </c>
+      <c r="X214">
+        <v>6</v>
+      </c>
+      <c r="Y214">
+        <v>1.13</v>
+      </c>
+      <c r="Z214">
+        <v>2.3</v>
+      </c>
+      <c r="AA214">
+        <v>3.5</v>
+      </c>
+      <c r="AB214">
+        <v>2.9</v>
+      </c>
+      <c r="AC214">
+        <v>0</v>
+      </c>
+      <c r="AD214">
+        <v>0</v>
+      </c>
+      <c r="AE214">
+        <v>0</v>
+      </c>
+      <c r="AF214">
+        <v>0</v>
+      </c>
+      <c r="AG214">
+        <v>1.62</v>
+      </c>
+      <c r="AH214">
+        <v>2.25</v>
+      </c>
+      <c r="AI214">
+        <v>1.53</v>
+      </c>
+      <c r="AJ214">
+        <v>2.38</v>
+      </c>
+      <c r="AK214">
+        <v>0</v>
+      </c>
+      <c r="AL214">
+        <v>0</v>
+      </c>
+      <c r="AM214">
+        <v>0</v>
+      </c>
+      <c r="AN214">
+        <v>1.46</v>
+      </c>
+      <c r="AO214">
+        <v>1.15</v>
+      </c>
+      <c r="AP214">
+        <v>1.57</v>
+      </c>
+      <c r="AQ214">
+        <v>1.07</v>
+      </c>
+      <c r="AR214">
+        <v>1.57</v>
+      </c>
+      <c r="AS214">
+        <v>1.36</v>
+      </c>
+      <c r="AT214">
+        <v>2.93</v>
+      </c>
+      <c r="AU214">
+        <v>9</v>
+      </c>
+      <c r="AV214">
+        <v>4</v>
+      </c>
+      <c r="AW214">
+        <v>5</v>
+      </c>
+      <c r="AX214">
+        <v>4</v>
+      </c>
+      <c r="AY214">
+        <v>14</v>
+      </c>
+      <c r="AZ214">
+        <v>8</v>
+      </c>
+      <c r="BA214">
+        <v>7</v>
+      </c>
+      <c r="BB214">
+        <v>5</v>
+      </c>
+      <c r="BC214">
+        <v>12</v>
+      </c>
+      <c r="BD214">
+        <v>0</v>
+      </c>
+      <c r="BE214">
+        <v>0</v>
+      </c>
+      <c r="BF214">
+        <v>0</v>
+      </c>
+      <c r="BG214">
+        <v>0</v>
+      </c>
+      <c r="BH214">
+        <v>0</v>
+      </c>
+      <c r="BI214">
+        <v>0</v>
+      </c>
+      <c r="BJ214">
+        <v>0</v>
+      </c>
+      <c r="BK214">
+        <v>0</v>
+      </c>
+      <c r="BL214">
+        <v>0</v>
+      </c>
+      <c r="BM214">
+        <v>0</v>
+      </c>
+      <c r="BN214">
+        <v>0</v>
+      </c>
+      <c r="BO214">
+        <v>0</v>
+      </c>
+      <c r="BP214">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="215" spans="1:68">
+      <c r="A215" s="1">
+        <v>214</v>
+      </c>
+      <c r="B215">
+        <v>7468301</v>
+      </c>
+      <c r="C215" t="s">
+        <v>68</v>
+      </c>
+      <c r="D215" t="s">
+        <v>69</v>
+      </c>
+      <c r="E215" s="2">
+        <v>45746.4375</v>
+      </c>
+      <c r="F215">
+        <v>27</v>
+      </c>
+      <c r="G215" t="s">
+        <v>77</v>
+      </c>
+      <c r="H215" t="s">
+        <v>72</v>
+      </c>
+      <c r="I215">
+        <v>1</v>
+      </c>
+      <c r="J215">
+        <v>0</v>
+      </c>
+      <c r="K215">
+        <v>1</v>
+      </c>
+      <c r="L215">
+        <v>1</v>
+      </c>
+      <c r="M215">
+        <v>0</v>
+      </c>
+      <c r="N215">
+        <v>1</v>
+      </c>
+      <c r="O215" t="s">
+        <v>223</v>
+      </c>
+      <c r="P215" t="s">
+        <v>88</v>
+      </c>
+      <c r="Q215">
+        <v>1.91</v>
+      </c>
+      <c r="R215">
+        <v>2.4</v>
+      </c>
+      <c r="S215">
+        <v>7</v>
+      </c>
+      <c r="T215">
+        <v>1.33</v>
+      </c>
+      <c r="U215">
+        <v>3.25</v>
+      </c>
+      <c r="V215">
+        <v>2.63</v>
+      </c>
+      <c r="W215">
+        <v>1.44</v>
+      </c>
+      <c r="X215">
+        <v>6.5</v>
+      </c>
+      <c r="Y215">
+        <v>1.11</v>
+      </c>
+      <c r="Z215">
+        <v>1.42</v>
+      </c>
+      <c r="AA215">
+        <v>4.71</v>
+      </c>
+      <c r="AB215">
+        <v>6.88</v>
+      </c>
+      <c r="AC215">
+        <v>0</v>
+      </c>
+      <c r="AD215">
+        <v>0</v>
+      </c>
+      <c r="AE215">
+        <v>2</v>
+      </c>
+      <c r="AF215">
+        <v>1.8</v>
+      </c>
+      <c r="AG215">
+        <v>1.75</v>
+      </c>
+      <c r="AH215">
+        <v>2.05</v>
+      </c>
+      <c r="AI215">
+        <v>2</v>
+      </c>
+      <c r="AJ215">
+        <v>1.75</v>
+      </c>
+      <c r="AK215">
+        <v>0</v>
+      </c>
+      <c r="AL215">
+        <v>0</v>
+      </c>
+      <c r="AM215">
+        <v>0</v>
+      </c>
+      <c r="AN215">
+        <v>1.54</v>
+      </c>
+      <c r="AO215">
+        <v>0.08</v>
+      </c>
+      <c r="AP215">
+        <v>1.64</v>
+      </c>
+      <c r="AQ215">
+        <v>0.08</v>
+      </c>
+      <c r="AR215">
+        <v>1.53</v>
+      </c>
+      <c r="AS215">
+        <v>1</v>
+      </c>
+      <c r="AT215">
+        <v>2.53</v>
+      </c>
+      <c r="AU215">
+        <v>6</v>
+      </c>
+      <c r="AV215">
+        <v>0</v>
+      </c>
+      <c r="AW215">
+        <v>7</v>
+      </c>
+      <c r="AX215">
+        <v>8</v>
+      </c>
+      <c r="AY215">
+        <v>13</v>
+      </c>
+      <c r="AZ215">
+        <v>8</v>
+      </c>
+      <c r="BA215">
+        <v>5</v>
+      </c>
+      <c r="BB215">
+        <v>4</v>
+      </c>
+      <c r="BC215">
+        <v>9</v>
+      </c>
+      <c r="BD215">
+        <v>0</v>
+      </c>
+      <c r="BE215">
+        <v>0</v>
+      </c>
+      <c r="BF215">
+        <v>0</v>
+      </c>
+      <c r="BG215">
+        <v>0</v>
+      </c>
+      <c r="BH215">
+        <v>0</v>
+      </c>
+      <c r="BI215">
+        <v>0</v>
+      </c>
+      <c r="BJ215">
+        <v>0</v>
+      </c>
+      <c r="BK215">
+        <v>0</v>
+      </c>
+      <c r="BL215">
+        <v>0</v>
+      </c>
+      <c r="BM215">
+        <v>0</v>
+      </c>
+      <c r="BN215">
+        <v>0</v>
+      </c>
+      <c r="BO215">
+        <v>0</v>
+      </c>
+      <c r="BP215">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="216" spans="1:68">
+      <c r="A216" s="1">
+        <v>215</v>
+      </c>
+      <c r="B216">
+        <v>7468300</v>
+      </c>
+      <c r="C216" t="s">
+        <v>68</v>
+      </c>
+      <c r="D216" t="s">
+        <v>69</v>
+      </c>
+      <c r="E216" s="2">
+        <v>45746.5625</v>
+      </c>
+      <c r="F216">
+        <v>27</v>
+      </c>
+      <c r="G216" t="s">
+        <v>70</v>
+      </c>
+      <c r="H216" t="s">
+        <v>84</v>
+      </c>
+      <c r="I216">
+        <v>1</v>
+      </c>
+      <c r="J216">
+        <v>2</v>
+      </c>
+      <c r="K216">
+        <v>3</v>
+      </c>
+      <c r="L216">
+        <v>2</v>
+      </c>
+      <c r="M216">
+        <v>4</v>
+      </c>
+      <c r="N216">
+        <v>6</v>
+      </c>
+      <c r="O216" t="s">
+        <v>224</v>
+      </c>
+      <c r="P216" t="s">
+        <v>317</v>
+      </c>
+      <c r="Q216">
+        <v>2.75</v>
+      </c>
+      <c r="R216">
+        <v>2.2</v>
+      </c>
+      <c r="S216">
+        <v>4</v>
+      </c>
+      <c r="T216">
+        <v>1.4</v>
+      </c>
+      <c r="U216">
+        <v>2.75</v>
+      </c>
+      <c r="V216">
+        <v>3</v>
+      </c>
+      <c r="W216">
+        <v>1.36</v>
+      </c>
+      <c r="X216">
+        <v>8</v>
+      </c>
+      <c r="Y216">
+        <v>1.08</v>
+      </c>
+      <c r="Z216">
+        <v>2.1</v>
+      </c>
+      <c r="AA216">
+        <v>3.4</v>
+      </c>
+      <c r="AB216">
+        <v>3.4</v>
+      </c>
+      <c r="AC216">
+        <v>0</v>
+      </c>
+      <c r="AD216">
+        <v>0</v>
+      </c>
+      <c r="AE216">
+        <v>0</v>
+      </c>
+      <c r="AF216">
+        <v>0</v>
+      </c>
+      <c r="AG216">
+        <v>1.95</v>
+      </c>
+      <c r="AH216">
+        <v>1.85</v>
+      </c>
+      <c r="AI216">
+        <v>1.75</v>
+      </c>
+      <c r="AJ216">
+        <v>2</v>
+      </c>
+      <c r="AK216">
+        <v>0</v>
+      </c>
+      <c r="AL216">
+        <v>0</v>
+      </c>
+      <c r="AM216">
+        <v>0</v>
+      </c>
+      <c r="AN216">
+        <v>2.23</v>
+      </c>
+      <c r="AO216">
+        <v>1.85</v>
+      </c>
+      <c r="AP216">
+        <v>2.07</v>
+      </c>
+      <c r="AQ216">
+        <v>1.93</v>
+      </c>
+      <c r="AR216">
+        <v>2.04</v>
+      </c>
+      <c r="AS216">
+        <v>1.45</v>
+      </c>
+      <c r="AT216">
+        <v>3.49</v>
+      </c>
+      <c r="AU216">
+        <v>6</v>
+      </c>
+      <c r="AV216">
+        <v>7</v>
+      </c>
+      <c r="AW216">
+        <v>4</v>
+      </c>
+      <c r="AX216">
+        <v>3</v>
+      </c>
+      <c r="AY216">
+        <v>10</v>
+      </c>
+      <c r="AZ216">
+        <v>10</v>
+      </c>
+      <c r="BA216">
+        <v>2</v>
+      </c>
+      <c r="BB216">
+        <v>3</v>
+      </c>
+      <c r="BC216">
+        <v>5</v>
+      </c>
+      <c r="BD216">
+        <v>0</v>
+      </c>
+      <c r="BE216">
+        <v>0</v>
+      </c>
+      <c r="BF216">
+        <v>0</v>
+      </c>
+      <c r="BG216">
+        <v>0</v>
+      </c>
+      <c r="BH216">
+        <v>0</v>
+      </c>
+      <c r="BI216">
+        <v>0</v>
+      </c>
+      <c r="BJ216">
+        <v>0</v>
+      </c>
+      <c r="BK216">
+        <v>0</v>
+      </c>
+      <c r="BL216">
+        <v>0</v>
+      </c>
+      <c r="BM216">
+        <v>0</v>
+      </c>
+      <c r="BN216">
+        <v>0</v>
+      </c>
+      <c r="BO216">
+        <v>0</v>
+      </c>
+      <c r="BP216">
         <v>0</v>
       </c>
     </row>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Czech Republic First League_20242025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Czech Republic First League_20242025.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1358" uniqueCount="318">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1388" uniqueCount="324">
   <si>
     <t>Id_Jogo</t>
   </si>
@@ -691,6 +691,18 @@
     <t>['8', '48']</t>
   </si>
   <si>
+    <t>['15', '71']</t>
+  </si>
+  <si>
+    <t>['33']</t>
+  </si>
+  <si>
+    <t>['32', '70']</t>
+  </si>
+  <si>
+    <t>['24', '58']</t>
+  </si>
+  <si>
     <t>['25']</t>
   </si>
   <si>
@@ -968,6 +980,12 @@
   </si>
   <si>
     <t>['14', '37', '53', '61']</t>
+  </si>
+  <si>
+    <t>['15', '82']</t>
+  </si>
+  <si>
+    <t>['51']</t>
   </si>
 </sst>
 </file>
@@ -1329,7 +1347,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:BP216"/>
+  <dimension ref="A1:BP221"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:68">
@@ -1585,7 +1603,7 @@
         <v>86</v>
       </c>
       <c r="P2" t="s">
-        <v>225</v>
+        <v>229</v>
       </c>
       <c r="Q2">
         <v>1.53</v>
@@ -1997,7 +2015,7 @@
         <v>88</v>
       </c>
       <c r="P4" t="s">
-        <v>226</v>
+        <v>230</v>
       </c>
       <c r="Q4">
         <v>2.88</v>
@@ -2409,7 +2427,7 @@
         <v>90</v>
       </c>
       <c r="P6" t="s">
-        <v>227</v>
+        <v>231</v>
       </c>
       <c r="Q6">
         <v>5.5</v>
@@ -2615,7 +2633,7 @@
         <v>91</v>
       </c>
       <c r="P7" t="s">
-        <v>228</v>
+        <v>232</v>
       </c>
       <c r="Q7">
         <v>3.2</v>
@@ -3314,7 +3332,7 @@
         <v>0.93</v>
       </c>
       <c r="AQ10">
-        <v>1.46</v>
+        <v>1.36</v>
       </c>
       <c r="AR10">
         <v>0.98</v>
@@ -3439,7 +3457,7 @@
         <v>94</v>
       </c>
       <c r="P11" t="s">
-        <v>229</v>
+        <v>233</v>
       </c>
       <c r="Q11">
         <v>6.5</v>
@@ -3520,7 +3538,7 @@
         <v>1.46</v>
       </c>
       <c r="AQ11">
-        <v>2</v>
+        <v>1.93</v>
       </c>
       <c r="AR11">
         <v>0</v>
@@ -3645,7 +3663,7 @@
         <v>88</v>
       </c>
       <c r="P12" t="s">
-        <v>230</v>
+        <v>234</v>
       </c>
       <c r="Q12">
         <v>2.85</v>
@@ -3723,10 +3741,10 @@
         <v>0</v>
       </c>
       <c r="AP12">
-        <v>0.77</v>
+        <v>0.93</v>
       </c>
       <c r="AQ12">
-        <v>1</v>
+        <v>1.14</v>
       </c>
       <c r="AR12">
         <v>0</v>
@@ -3932,7 +3950,7 @@
         <v>3</v>
       </c>
       <c r="AQ13">
-        <v>0.08</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="AR13">
         <v>0</v>
@@ -4135,7 +4153,7 @@
         <v>3</v>
       </c>
       <c r="AP14">
-        <v>1.54</v>
+        <v>1.64</v>
       </c>
       <c r="AQ14">
         <v>1.36</v>
@@ -4547,7 +4565,7 @@
         <v>0</v>
       </c>
       <c r="AP16">
-        <v>2.54</v>
+        <v>2.43</v>
       </c>
       <c r="AQ16">
         <v>1.15</v>
@@ -4756,7 +4774,7 @@
         <v>2.23</v>
       </c>
       <c r="AQ17">
-        <v>1.17</v>
+        <v>1.08</v>
       </c>
       <c r="AR17">
         <v>0</v>
@@ -4881,7 +4899,7 @@
         <v>88</v>
       </c>
       <c r="P18" t="s">
-        <v>231</v>
+        <v>235</v>
       </c>
       <c r="Q18">
         <v>5.4</v>
@@ -4959,7 +4977,7 @@
         <v>1</v>
       </c>
       <c r="AP18">
-        <v>1.54</v>
+        <v>1.64</v>
       </c>
       <c r="AQ18">
         <v>2.14</v>
@@ -5374,7 +5392,7 @@
         <v>1.38</v>
       </c>
       <c r="AQ20">
-        <v>1.46</v>
+        <v>1.36</v>
       </c>
       <c r="AR20">
         <v>1</v>
@@ -5783,7 +5801,7 @@
         <v>0</v>
       </c>
       <c r="AP22">
-        <v>1.54</v>
+        <v>1.43</v>
       </c>
       <c r="AQ22">
         <v>0.79</v>
@@ -5911,7 +5929,7 @@
         <v>102</v>
       </c>
       <c r="P23" t="s">
-        <v>232</v>
+        <v>236</v>
       </c>
       <c r="Q23">
         <v>2.6</v>
@@ -6117,7 +6135,7 @@
         <v>103</v>
       </c>
       <c r="P24" t="s">
-        <v>233</v>
+        <v>237</v>
       </c>
       <c r="Q24">
         <v>2.75</v>
@@ -6323,7 +6341,7 @@
         <v>88</v>
       </c>
       <c r="P25" t="s">
-        <v>234</v>
+        <v>238</v>
       </c>
       <c r="Q25">
         <v>1.06</v>
@@ -6529,7 +6547,7 @@
         <v>104</v>
       </c>
       <c r="P26" t="s">
-        <v>235</v>
+        <v>239</v>
       </c>
       <c r="Q26">
         <v>6.23</v>
@@ -6610,7 +6628,7 @@
         <v>1.07</v>
       </c>
       <c r="AQ26">
-        <v>2</v>
+        <v>1.93</v>
       </c>
       <c r="AR26">
         <v>1.73</v>
@@ -7225,7 +7243,7 @@
         <v>0</v>
       </c>
       <c r="AP29">
-        <v>0.77</v>
+        <v>0.93</v>
       </c>
       <c r="AQ29">
         <v>0.85</v>
@@ -7431,10 +7449,10 @@
         <v>0</v>
       </c>
       <c r="AP30">
-        <v>2.54</v>
+        <v>2.43</v>
       </c>
       <c r="AQ30">
-        <v>1.17</v>
+        <v>1.08</v>
       </c>
       <c r="AR30">
         <v>1.24</v>
@@ -7640,7 +7658,7 @@
         <v>1.46</v>
       </c>
       <c r="AQ31">
-        <v>0.08</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="AR31">
         <v>1.76</v>
@@ -7846,7 +7864,7 @@
         <v>2.23</v>
       </c>
       <c r="AQ32">
-        <v>1</v>
+        <v>1.14</v>
       </c>
       <c r="AR32">
         <v>1.64</v>
@@ -8177,7 +8195,7 @@
         <v>111</v>
       </c>
       <c r="P34" t="s">
-        <v>236</v>
+        <v>240</v>
       </c>
       <c r="Q34">
         <v>1.45</v>
@@ -8383,7 +8401,7 @@
         <v>112</v>
       </c>
       <c r="P35" t="s">
-        <v>237</v>
+        <v>241</v>
       </c>
       <c r="Q35">
         <v>2.84</v>
@@ -8464,7 +8482,7 @@
         <v>1.57</v>
       </c>
       <c r="AQ35">
-        <v>1.46</v>
+        <v>1.36</v>
       </c>
       <c r="AR35">
         <v>1.93</v>
@@ -8589,7 +8607,7 @@
         <v>113</v>
       </c>
       <c r="P36" t="s">
-        <v>238</v>
+        <v>242</v>
       </c>
       <c r="Q36">
         <v>5.63</v>
@@ -8670,7 +8688,7 @@
         <v>1.93</v>
       </c>
       <c r="AQ36">
-        <v>2</v>
+        <v>1.93</v>
       </c>
       <c r="AR36">
         <v>1.54</v>
@@ -8795,7 +8813,7 @@
         <v>114</v>
       </c>
       <c r="P37" t="s">
-        <v>239</v>
+        <v>243</v>
       </c>
       <c r="Q37">
         <v>2.58</v>
@@ -8873,7 +8891,7 @@
         <v>0</v>
       </c>
       <c r="AP37">
-        <v>1.54</v>
+        <v>1.43</v>
       </c>
       <c r="AQ37">
         <v>1.07</v>
@@ -9079,7 +9097,7 @@
         <v>1.5</v>
       </c>
       <c r="AP38">
-        <v>1.54</v>
+        <v>1.64</v>
       </c>
       <c r="AQ38">
         <v>0.43</v>
@@ -9207,7 +9225,7 @@
         <v>88</v>
       </c>
       <c r="P39" t="s">
-        <v>240</v>
+        <v>244</v>
       </c>
       <c r="Q39">
         <v>4.75</v>
@@ -9619,7 +9637,7 @@
         <v>117</v>
       </c>
       <c r="P41" t="s">
-        <v>241</v>
+        <v>245</v>
       </c>
       <c r="Q41">
         <v>2.4</v>
@@ -9825,7 +9843,7 @@
         <v>107</v>
       </c>
       <c r="P42" t="s">
-        <v>242</v>
+        <v>246</v>
       </c>
       <c r="Q42">
         <v>2.61</v>
@@ -9906,7 +9924,7 @@
         <v>1.46</v>
       </c>
       <c r="AQ42">
-        <v>1</v>
+        <v>1.14</v>
       </c>
       <c r="AR42">
         <v>1.41</v>
@@ -10031,7 +10049,7 @@
         <v>118</v>
       </c>
       <c r="P43" t="s">
-        <v>243</v>
+        <v>247</v>
       </c>
       <c r="Q43">
         <v>1.69</v>
@@ -10315,10 +10333,10 @@
         <v>0</v>
       </c>
       <c r="AP44">
-        <v>0.77</v>
+        <v>0.93</v>
       </c>
       <c r="AQ44">
-        <v>1.17</v>
+        <v>1.08</v>
       </c>
       <c r="AR44">
         <v>1.16</v>
@@ -10521,7 +10539,7 @@
         <v>1.5</v>
       </c>
       <c r="AP45">
-        <v>2.54</v>
+        <v>2.43</v>
       </c>
       <c r="AQ45">
         <v>1.14</v>
@@ -10730,7 +10748,7 @@
         <v>0.93</v>
       </c>
       <c r="AQ46">
-        <v>0.08</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="AR46">
         <v>0.97</v>
@@ -11142,7 +11160,7 @@
         <v>0.21</v>
       </c>
       <c r="AQ48">
-        <v>1.46</v>
+        <v>1.36</v>
       </c>
       <c r="AR48">
         <v>1.34</v>
@@ -11473,7 +11491,7 @@
         <v>88</v>
       </c>
       <c r="P50" t="s">
-        <v>244</v>
+        <v>248</v>
       </c>
       <c r="Q50">
         <v>5.1</v>
@@ -11554,7 +11572,7 @@
         <v>1.64</v>
       </c>
       <c r="AQ50">
-        <v>2</v>
+        <v>1.93</v>
       </c>
       <c r="AR50">
         <v>1.24</v>
@@ -11885,7 +11903,7 @@
         <v>122</v>
       </c>
       <c r="P52" t="s">
-        <v>245</v>
+        <v>249</v>
       </c>
       <c r="Q52">
         <v>3</v>
@@ -11963,7 +11981,7 @@
         <v>0.33</v>
       </c>
       <c r="AP52">
-        <v>1.54</v>
+        <v>1.43</v>
       </c>
       <c r="AQ52">
         <v>1.71</v>
@@ -12297,7 +12315,7 @@
         <v>124</v>
       </c>
       <c r="P54" t="s">
-        <v>246</v>
+        <v>250</v>
       </c>
       <c r="Q54">
         <v>3</v>
@@ -12581,7 +12599,7 @@
         <v>2.33</v>
       </c>
       <c r="AP55">
-        <v>1.54</v>
+        <v>1.64</v>
       </c>
       <c r="AQ55">
         <v>1.93</v>
@@ -12915,7 +12933,7 @@
         <v>88</v>
       </c>
       <c r="P57" t="s">
-        <v>247</v>
+        <v>251</v>
       </c>
       <c r="Q57">
         <v>5.88</v>
@@ -13327,7 +13345,7 @@
         <v>127</v>
       </c>
       <c r="P59" t="s">
-        <v>248</v>
+        <v>252</v>
       </c>
       <c r="Q59">
         <v>3.86</v>
@@ -13945,7 +13963,7 @@
         <v>130</v>
       </c>
       <c r="P62" t="s">
-        <v>249</v>
+        <v>253</v>
       </c>
       <c r="Q62">
         <v>1.83</v>
@@ -14151,7 +14169,7 @@
         <v>88</v>
       </c>
       <c r="P63" t="s">
-        <v>250</v>
+        <v>254</v>
       </c>
       <c r="Q63">
         <v>8.77</v>
@@ -14232,7 +14250,7 @@
         <v>0.21</v>
       </c>
       <c r="AQ63">
-        <v>2</v>
+        <v>1.93</v>
       </c>
       <c r="AR63">
         <v>1.37</v>
@@ -14435,7 +14453,7 @@
         <v>0.33</v>
       </c>
       <c r="AP64">
-        <v>1.54</v>
+        <v>1.43</v>
       </c>
       <c r="AQ64">
         <v>0.62</v>
@@ -14563,7 +14581,7 @@
         <v>132</v>
       </c>
       <c r="P65" t="s">
-        <v>251</v>
+        <v>255</v>
       </c>
       <c r="Q65">
         <v>2.4</v>
@@ -14641,10 +14659,10 @@
         <v>1.25</v>
       </c>
       <c r="AP65">
-        <v>1.54</v>
+        <v>1.64</v>
       </c>
       <c r="AQ65">
-        <v>1.46</v>
+        <v>1.36</v>
       </c>
       <c r="AR65">
         <v>1.42</v>
@@ -14769,7 +14787,7 @@
         <v>133</v>
       </c>
       <c r="P66" t="s">
-        <v>252</v>
+        <v>256</v>
       </c>
       <c r="Q66">
         <v>1.55</v>
@@ -14975,7 +14993,7 @@
         <v>134</v>
       </c>
       <c r="P67" t="s">
-        <v>253</v>
+        <v>257</v>
       </c>
       <c r="Q67">
         <v>4</v>
@@ -15181,7 +15199,7 @@
         <v>88</v>
       </c>
       <c r="P68" t="s">
-        <v>254</v>
+        <v>258</v>
       </c>
       <c r="Q68">
         <v>3.1</v>
@@ -15259,7 +15277,7 @@
         <v>0</v>
       </c>
       <c r="AP68">
-        <v>0.77</v>
+        <v>0.93</v>
       </c>
       <c r="AQ68">
         <v>0.79</v>
@@ -15468,7 +15486,7 @@
         <v>1.38</v>
       </c>
       <c r="AQ69">
-        <v>1</v>
+        <v>1.14</v>
       </c>
       <c r="AR69">
         <v>1.16</v>
@@ -15674,7 +15692,7 @@
         <v>1.93</v>
       </c>
       <c r="AQ70">
-        <v>1.17</v>
+        <v>1.08</v>
       </c>
       <c r="AR70">
         <v>1.53</v>
@@ -15877,10 +15895,10 @@
         <v>0</v>
       </c>
       <c r="AP71">
-        <v>2.54</v>
+        <v>2.43</v>
       </c>
       <c r="AQ71">
-        <v>0.08</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="AR71">
         <v>1.82</v>
@@ -16005,7 +16023,7 @@
         <v>124</v>
       </c>
       <c r="P72" t="s">
-        <v>255</v>
+        <v>259</v>
       </c>
       <c r="Q72">
         <v>1.88</v>
@@ -16211,7 +16229,7 @@
         <v>88</v>
       </c>
       <c r="P73" t="s">
-        <v>256</v>
+        <v>260</v>
       </c>
       <c r="Q73">
         <v>7</v>
@@ -16498,7 +16516,7 @@
         <v>1.57</v>
       </c>
       <c r="AQ74">
-        <v>1.17</v>
+        <v>1.08</v>
       </c>
       <c r="AR74">
         <v>1.81</v>
@@ -16623,7 +16641,7 @@
         <v>138</v>
       </c>
       <c r="P75" t="s">
-        <v>257</v>
+        <v>261</v>
       </c>
       <c r="Q75">
         <v>2.3</v>
@@ -16829,7 +16847,7 @@
         <v>88</v>
       </c>
       <c r="P76" t="s">
-        <v>258</v>
+        <v>262</v>
       </c>
       <c r="Q76">
         <v>3.7</v>
@@ -17035,7 +17053,7 @@
         <v>88</v>
       </c>
       <c r="P77" t="s">
-        <v>259</v>
+        <v>263</v>
       </c>
       <c r="Q77">
         <v>2.47</v>
@@ -17113,7 +17131,7 @@
         <v>1.4</v>
       </c>
       <c r="AP77">
-        <v>1.54</v>
+        <v>1.64</v>
       </c>
       <c r="AQ77">
         <v>1.15</v>
@@ -17653,7 +17671,7 @@
         <v>140</v>
       </c>
       <c r="P80" t="s">
-        <v>260</v>
+        <v>264</v>
       </c>
       <c r="Q80">
         <v>2.5</v>
@@ -17731,10 +17749,10 @@
         <v>1.2</v>
       </c>
       <c r="AP80">
-        <v>1.54</v>
+        <v>1.43</v>
       </c>
       <c r="AQ80">
-        <v>1.46</v>
+        <v>1.36</v>
       </c>
       <c r="AR80">
         <v>1.66</v>
@@ -17859,7 +17877,7 @@
         <v>141</v>
       </c>
       <c r="P81" t="s">
-        <v>261</v>
+        <v>265</v>
       </c>
       <c r="Q81">
         <v>2.38</v>
@@ -17940,7 +17958,7 @@
         <v>3</v>
       </c>
       <c r="AQ81">
-        <v>2</v>
+        <v>1.93</v>
       </c>
       <c r="AR81">
         <v>2.43</v>
@@ -18065,7 +18083,7 @@
         <v>142</v>
       </c>
       <c r="P82" t="s">
-        <v>262</v>
+        <v>266</v>
       </c>
       <c r="Q82">
         <v>2.8</v>
@@ -18271,7 +18289,7 @@
         <v>143</v>
       </c>
       <c r="P83" t="s">
-        <v>263</v>
+        <v>267</v>
       </c>
       <c r="Q83">
         <v>2.6</v>
@@ -18477,7 +18495,7 @@
         <v>144</v>
       </c>
       <c r="P84" t="s">
-        <v>264</v>
+        <v>268</v>
       </c>
       <c r="Q84">
         <v>3.4</v>
@@ -18555,7 +18573,7 @@
         <v>1.6</v>
       </c>
       <c r="AP84">
-        <v>2.54</v>
+        <v>2.43</v>
       </c>
       <c r="AQ84">
         <v>1.93</v>
@@ -18889,7 +18907,7 @@
         <v>146</v>
       </c>
       <c r="P86" t="s">
-        <v>265</v>
+        <v>269</v>
       </c>
       <c r="Q86">
         <v>2.88</v>
@@ -19176,7 +19194,7 @@
         <v>1.57</v>
       </c>
       <c r="AQ87">
-        <v>0.08</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="AR87">
         <v>1.73</v>
@@ -19301,7 +19319,7 @@
         <v>88</v>
       </c>
       <c r="P88" t="s">
-        <v>266</v>
+        <v>270</v>
       </c>
       <c r="Q88">
         <v>2.6</v>
@@ -19507,7 +19525,7 @@
         <v>93</v>
       </c>
       <c r="P89" t="s">
-        <v>267</v>
+        <v>271</v>
       </c>
       <c r="Q89">
         <v>6.5</v>
@@ -19791,7 +19809,7 @@
         <v>1.4</v>
       </c>
       <c r="AP90">
-        <v>1.54</v>
+        <v>1.64</v>
       </c>
       <c r="AQ90">
         <v>0.85</v>
@@ -19919,7 +19937,7 @@
         <v>149</v>
       </c>
       <c r="P91" t="s">
-        <v>268</v>
+        <v>272</v>
       </c>
       <c r="Q91">
         <v>4.7</v>
@@ -19997,7 +20015,7 @@
         <v>1</v>
       </c>
       <c r="AP91">
-        <v>0.77</v>
+        <v>0.93</v>
       </c>
       <c r="AQ91">
         <v>1.71</v>
@@ -20125,7 +20143,7 @@
         <v>88</v>
       </c>
       <c r="P92" t="s">
-        <v>269</v>
+        <v>273</v>
       </c>
       <c r="Q92">
         <v>3.8</v>
@@ -20206,7 +20224,7 @@
         <v>0.21</v>
       </c>
       <c r="AQ92">
-        <v>1.17</v>
+        <v>1.08</v>
       </c>
       <c r="AR92">
         <v>1.33</v>
@@ -20409,7 +20427,7 @@
         <v>1.67</v>
       </c>
       <c r="AP93">
-        <v>1.54</v>
+        <v>1.43</v>
       </c>
       <c r="AQ93">
         <v>1.15</v>
@@ -20537,7 +20555,7 @@
         <v>150</v>
       </c>
       <c r="P94" t="s">
-        <v>270</v>
+        <v>274</v>
       </c>
       <c r="Q94">
         <v>3</v>
@@ -20618,7 +20636,7 @@
         <v>1.46</v>
       </c>
       <c r="AQ94">
-        <v>1.46</v>
+        <v>1.36</v>
       </c>
       <c r="AR94">
         <v>1.52</v>
@@ -20824,7 +20842,7 @@
         <v>1.46</v>
       </c>
       <c r="AQ95">
-        <v>1</v>
+        <v>1.14</v>
       </c>
       <c r="AR95">
         <v>1.43</v>
@@ -21236,7 +21254,7 @@
         <v>2.23</v>
       </c>
       <c r="AQ97">
-        <v>2</v>
+        <v>1.93</v>
       </c>
       <c r="AR97">
         <v>1.81</v>
@@ -21979,7 +21997,7 @@
         <v>156</v>
       </c>
       <c r="P101" t="s">
-        <v>271</v>
+        <v>275</v>
       </c>
       <c r="Q101">
         <v>1.83</v>
@@ -23087,7 +23105,7 @@
         <v>0.33</v>
       </c>
       <c r="AP106">
-        <v>2.54</v>
+        <v>2.43</v>
       </c>
       <c r="AQ106">
         <v>0.62</v>
@@ -23293,7 +23311,7 @@
         <v>1.57</v>
       </c>
       <c r="AP107">
-        <v>0.77</v>
+        <v>0.93</v>
       </c>
       <c r="AQ107">
         <v>1.15</v>
@@ -23499,10 +23517,10 @@
         <v>0.67</v>
       </c>
       <c r="AP108">
-        <v>1.54</v>
+        <v>1.64</v>
       </c>
       <c r="AQ108">
-        <v>1.17</v>
+        <v>1.08</v>
       </c>
       <c r="AR108">
         <v>1.5</v>
@@ -23627,7 +23645,7 @@
         <v>161</v>
       </c>
       <c r="P109" t="s">
-        <v>272</v>
+        <v>276</v>
       </c>
       <c r="Q109">
         <v>2.24</v>
@@ -23708,7 +23726,7 @@
         <v>1.46</v>
       </c>
       <c r="AQ109">
-        <v>0.08</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="AR109">
         <v>1.51</v>
@@ -23833,7 +23851,7 @@
         <v>162</v>
       </c>
       <c r="P110" t="s">
-        <v>273</v>
+        <v>277</v>
       </c>
       <c r="Q110">
         <v>4.6</v>
@@ -23914,7 +23932,7 @@
         <v>1.46</v>
       </c>
       <c r="AQ110">
-        <v>2</v>
+        <v>1.93</v>
       </c>
       <c r="AR110">
         <v>1.51</v>
@@ -24120,7 +24138,7 @@
         <v>2.23</v>
       </c>
       <c r="AQ111">
-        <v>1.46</v>
+        <v>1.36</v>
       </c>
       <c r="AR111">
         <v>1.73</v>
@@ -24326,7 +24344,7 @@
         <v>3</v>
       </c>
       <c r="AQ112">
-        <v>1</v>
+        <v>1.14</v>
       </c>
       <c r="AR112">
         <v>2.21</v>
@@ -24451,7 +24469,7 @@
         <v>165</v>
       </c>
       <c r="P113" t="s">
-        <v>274</v>
+        <v>278</v>
       </c>
       <c r="Q113">
         <v>3.25</v>
@@ -24657,7 +24675,7 @@
         <v>151</v>
       </c>
       <c r="P114" t="s">
-        <v>275</v>
+        <v>279</v>
       </c>
       <c r="Q114">
         <v>2.88</v>
@@ -24863,7 +24881,7 @@
         <v>99</v>
       </c>
       <c r="P115" t="s">
-        <v>276</v>
+        <v>280</v>
       </c>
       <c r="Q115">
         <v>1.73</v>
@@ -25069,7 +25087,7 @@
         <v>88</v>
       </c>
       <c r="P116" t="s">
-        <v>277</v>
+        <v>281</v>
       </c>
       <c r="Q116">
         <v>4.33</v>
@@ -25687,7 +25705,7 @@
         <v>88</v>
       </c>
       <c r="P119" t="s">
-        <v>278</v>
+        <v>282</v>
       </c>
       <c r="Q119">
         <v>15</v>
@@ -25893,7 +25911,7 @@
         <v>168</v>
       </c>
       <c r="P120" t="s">
-        <v>279</v>
+        <v>283</v>
       </c>
       <c r="Q120">
         <v>3</v>
@@ -25971,7 +25989,7 @@
         <v>1.17</v>
       </c>
       <c r="AP120">
-        <v>1.54</v>
+        <v>1.43</v>
       </c>
       <c r="AQ120">
         <v>1.14</v>
@@ -26177,7 +26195,7 @@
         <v>1.17</v>
       </c>
       <c r="AP121">
-        <v>1.54</v>
+        <v>1.43</v>
       </c>
       <c r="AQ121">
         <v>0.85</v>
@@ -26305,7 +26323,7 @@
         <v>170</v>
       </c>
       <c r="P122" t="s">
-        <v>280</v>
+        <v>284</v>
       </c>
       <c r="Q122">
         <v>3.25</v>
@@ -26717,7 +26735,7 @@
         <v>172</v>
       </c>
       <c r="P124" t="s">
-        <v>230</v>
+        <v>234</v>
       </c>
       <c r="Q124">
         <v>1.83</v>
@@ -26795,10 +26813,10 @@
         <v>1.17</v>
       </c>
       <c r="AP124">
-        <v>2.54</v>
+        <v>2.43</v>
       </c>
       <c r="AQ124">
-        <v>1</v>
+        <v>1.14</v>
       </c>
       <c r="AR124">
         <v>1.87</v>
@@ -26923,7 +26941,7 @@
         <v>171</v>
       </c>
       <c r="P125" t="s">
-        <v>281</v>
+        <v>285</v>
       </c>
       <c r="Q125">
         <v>6.3</v>
@@ -27004,7 +27022,7 @@
         <v>0.93</v>
       </c>
       <c r="AQ125">
-        <v>2</v>
+        <v>1.93</v>
       </c>
       <c r="AR125">
         <v>1.21</v>
@@ -27416,7 +27434,7 @@
         <v>1.46</v>
       </c>
       <c r="AQ127">
-        <v>1.17</v>
+        <v>1.08</v>
       </c>
       <c r="AR127">
         <v>1.5</v>
@@ -27619,10 +27637,10 @@
         <v>0</v>
       </c>
       <c r="AP128">
-        <v>0.77</v>
+        <v>0.93</v>
       </c>
       <c r="AQ128">
-        <v>0.08</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="AR128">
         <v>1.1</v>
@@ -27747,7 +27765,7 @@
         <v>174</v>
       </c>
       <c r="P129" t="s">
-        <v>282</v>
+        <v>286</v>
       </c>
       <c r="Q129">
         <v>2.1</v>
@@ -27953,7 +27971,7 @@
         <v>175</v>
       </c>
       <c r="P130" t="s">
-        <v>283</v>
+        <v>287</v>
       </c>
       <c r="Q130">
         <v>1.5</v>
@@ -28034,7 +28052,7 @@
         <v>2.07</v>
       </c>
       <c r="AQ130">
-        <v>1</v>
+        <v>1.14</v>
       </c>
       <c r="AR130">
         <v>1.93</v>
@@ -28159,7 +28177,7 @@
         <v>176</v>
       </c>
       <c r="P131" t="s">
-        <v>284</v>
+        <v>288</v>
       </c>
       <c r="Q131">
         <v>3.5</v>
@@ -28237,7 +28255,7 @@
         <v>1</v>
       </c>
       <c r="AP131">
-        <v>0.77</v>
+        <v>0.93</v>
       </c>
       <c r="AQ131">
         <v>1.36</v>
@@ -28365,7 +28383,7 @@
         <v>177</v>
       </c>
       <c r="P132" t="s">
-        <v>285</v>
+        <v>289</v>
       </c>
       <c r="Q132">
         <v>4.04</v>
@@ -28652,7 +28670,7 @@
         <v>1.93</v>
       </c>
       <c r="AQ133">
-        <v>0.08</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="AR133">
         <v>1.63</v>
@@ -28777,7 +28795,7 @@
         <v>88</v>
       </c>
       <c r="P134" t="s">
-        <v>286</v>
+        <v>290</v>
       </c>
       <c r="Q134">
         <v>2.75</v>
@@ -28858,7 +28876,7 @@
         <v>1.07</v>
       </c>
       <c r="AQ134">
-        <v>1.17</v>
+        <v>1.08</v>
       </c>
       <c r="AR134">
         <v>1.51</v>
@@ -29267,7 +29285,7 @@
         <v>2.43</v>
       </c>
       <c r="AP136">
-        <v>2.54</v>
+        <v>2.43</v>
       </c>
       <c r="AQ136">
         <v>2.14</v>
@@ -29601,7 +29619,7 @@
         <v>91</v>
       </c>
       <c r="P138" t="s">
-        <v>274</v>
+        <v>278</v>
       </c>
       <c r="Q138">
         <v>2.25</v>
@@ -29807,7 +29825,7 @@
         <v>179</v>
       </c>
       <c r="P139" t="s">
-        <v>283</v>
+        <v>287</v>
       </c>
       <c r="Q139">
         <v>1.9</v>
@@ -30094,7 +30112,7 @@
         <v>2.07</v>
       </c>
       <c r="AQ140">
-        <v>1.46</v>
+        <v>1.36</v>
       </c>
       <c r="AR140">
         <v>2.06</v>
@@ -30219,7 +30237,7 @@
         <v>88</v>
       </c>
       <c r="P141" t="s">
-        <v>287</v>
+        <v>291</v>
       </c>
       <c r="Q141">
         <v>4</v>
@@ -30425,7 +30443,7 @@
         <v>117</v>
       </c>
       <c r="P142" t="s">
-        <v>288</v>
+        <v>292</v>
       </c>
       <c r="Q142">
         <v>4</v>
@@ -30709,7 +30727,7 @@
         <v>1</v>
       </c>
       <c r="AP143">
-        <v>1.54</v>
+        <v>1.64</v>
       </c>
       <c r="AQ143">
         <v>0.79</v>
@@ -30837,7 +30855,7 @@
         <v>182</v>
       </c>
       <c r="P144" t="s">
-        <v>289</v>
+        <v>293</v>
       </c>
       <c r="Q144">
         <v>6</v>
@@ -30915,7 +30933,7 @@
         <v>2.5</v>
       </c>
       <c r="AP144">
-        <v>1.54</v>
+        <v>1.43</v>
       </c>
       <c r="AQ144">
         <v>2.14</v>
@@ -31043,7 +31061,7 @@
         <v>88</v>
       </c>
       <c r="P145" t="s">
-        <v>290</v>
+        <v>294</v>
       </c>
       <c r="Q145">
         <v>3.5</v>
@@ -31249,7 +31267,7 @@
         <v>183</v>
       </c>
       <c r="P146" t="s">
-        <v>291</v>
+        <v>295</v>
       </c>
       <c r="Q146">
         <v>4.33</v>
@@ -31330,7 +31348,7 @@
         <v>0.93</v>
       </c>
       <c r="AQ146">
-        <v>1.17</v>
+        <v>1.08</v>
       </c>
       <c r="AR146">
         <v>1.22</v>
@@ -31455,7 +31473,7 @@
         <v>184</v>
       </c>
       <c r="P147" t="s">
-        <v>292</v>
+        <v>296</v>
       </c>
       <c r="Q147">
         <v>3.8</v>
@@ -31533,7 +31551,7 @@
         <v>1.11</v>
       </c>
       <c r="AP147">
-        <v>0.77</v>
+        <v>0.93</v>
       </c>
       <c r="AQ147">
         <v>1.14</v>
@@ -31661,7 +31679,7 @@
         <v>185</v>
       </c>
       <c r="P148" t="s">
-        <v>293</v>
+        <v>297</v>
       </c>
       <c r="Q148">
         <v>2.5</v>
@@ -31742,7 +31760,7 @@
         <v>1.07</v>
       </c>
       <c r="AQ148">
-        <v>1</v>
+        <v>1.14</v>
       </c>
       <c r="AR148">
         <v>1.47</v>
@@ -31867,7 +31885,7 @@
         <v>186</v>
       </c>
       <c r="P149" t="s">
-        <v>290</v>
+        <v>294</v>
       </c>
       <c r="Q149">
         <v>2.05</v>
@@ -31945,7 +31963,7 @@
         <v>1.22</v>
       </c>
       <c r="AP149">
-        <v>2.54</v>
+        <v>2.43</v>
       </c>
       <c r="AQ149">
         <v>0.85</v>
@@ -32279,7 +32297,7 @@
         <v>188</v>
       </c>
       <c r="P151" t="s">
-        <v>294</v>
+        <v>298</v>
       </c>
       <c r="Q151">
         <v>2.48</v>
@@ -32691,7 +32709,7 @@
         <v>190</v>
       </c>
       <c r="P153" t="s">
-        <v>295</v>
+        <v>299</v>
       </c>
       <c r="Q153">
         <v>1.4</v>
@@ -32772,7 +32790,7 @@
         <v>2.23</v>
       </c>
       <c r="AQ153">
-        <v>0.08</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="AR153">
         <v>1.75</v>
@@ -33103,7 +33121,7 @@
         <v>88</v>
       </c>
       <c r="P155" t="s">
-        <v>233</v>
+        <v>237</v>
       </c>
       <c r="Q155">
         <v>3.2</v>
@@ -33181,7 +33199,7 @@
         <v>1.5</v>
       </c>
       <c r="AP155">
-        <v>1.54</v>
+        <v>1.64</v>
       </c>
       <c r="AQ155">
         <v>1.71</v>
@@ -33721,7 +33739,7 @@
         <v>88</v>
       </c>
       <c r="P158" t="s">
-        <v>296</v>
+        <v>300</v>
       </c>
       <c r="Q158">
         <v>5</v>
@@ -33802,7 +33820,7 @@
         <v>1.38</v>
       </c>
       <c r="AQ158">
-        <v>2</v>
+        <v>1.93</v>
       </c>
       <c r="AR158">
         <v>1.21</v>
@@ -33927,7 +33945,7 @@
         <v>88</v>
       </c>
       <c r="P159" t="s">
-        <v>254</v>
+        <v>258</v>
       </c>
       <c r="Q159">
         <v>2.38</v>
@@ -34008,7 +34026,7 @@
         <v>1.93</v>
       </c>
       <c r="AQ159">
-        <v>1.46</v>
+        <v>1.36</v>
       </c>
       <c r="AR159">
         <v>1.67</v>
@@ -34339,7 +34357,7 @@
         <v>193</v>
       </c>
       <c r="P161" t="s">
-        <v>281</v>
+        <v>285</v>
       </c>
       <c r="Q161">
         <v>4.75</v>
@@ -34417,7 +34435,7 @@
         <v>1.89</v>
       </c>
       <c r="AP161">
-        <v>1.54</v>
+        <v>1.43</v>
       </c>
       <c r="AQ161">
         <v>1.93</v>
@@ -34545,7 +34563,7 @@
         <v>194</v>
       </c>
       <c r="P162" t="s">
-        <v>297</v>
+        <v>301</v>
       </c>
       <c r="Q162">
         <v>2.63</v>
@@ -34751,7 +34769,7 @@
         <v>88</v>
       </c>
       <c r="P163" t="s">
-        <v>298</v>
+        <v>302</v>
       </c>
       <c r="Q163">
         <v>11</v>
@@ -34829,7 +34847,7 @@
         <v>2.3</v>
       </c>
       <c r="AP163">
-        <v>0.77</v>
+        <v>0.93</v>
       </c>
       <c r="AQ163">
         <v>2.14</v>
@@ -34957,7 +34975,7 @@
         <v>195</v>
       </c>
       <c r="P164" t="s">
-        <v>299</v>
+        <v>303</v>
       </c>
       <c r="Q164">
         <v>2</v>
@@ -35163,7 +35181,7 @@
         <v>196</v>
       </c>
       <c r="P165" t="s">
-        <v>300</v>
+        <v>304</v>
       </c>
       <c r="Q165">
         <v>2.5</v>
@@ -35447,7 +35465,7 @@
         <v>1.2</v>
       </c>
       <c r="AP166">
-        <v>2.54</v>
+        <v>2.43</v>
       </c>
       <c r="AQ166">
         <v>1.36</v>
@@ -35656,7 +35674,7 @@
         <v>1.07</v>
       </c>
       <c r="AQ167">
-        <v>0.08</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="AR167">
         <v>1.6</v>
@@ -35862,7 +35880,7 @@
         <v>2.07</v>
       </c>
       <c r="AQ168">
-        <v>1.17</v>
+        <v>1.08</v>
       </c>
       <c r="AR168">
         <v>1.96</v>
@@ -36065,7 +36083,7 @@
         <v>0.55</v>
       </c>
       <c r="AP169">
-        <v>1.54</v>
+        <v>1.43</v>
       </c>
       <c r="AQ169">
         <v>0.43</v>
@@ -36399,7 +36417,7 @@
         <v>201</v>
       </c>
       <c r="P171" t="s">
-        <v>301</v>
+        <v>305</v>
       </c>
       <c r="Q171">
         <v>5.2</v>
@@ -36605,7 +36623,7 @@
         <v>202</v>
       </c>
       <c r="P172" t="s">
-        <v>302</v>
+        <v>306</v>
       </c>
       <c r="Q172">
         <v>6.35</v>
@@ -36686,7 +36704,7 @@
         <v>1.57</v>
       </c>
       <c r="AQ172">
-        <v>2</v>
+        <v>1.93</v>
       </c>
       <c r="AR172">
         <v>1.5</v>
@@ -36811,7 +36829,7 @@
         <v>203</v>
       </c>
       <c r="P173" t="s">
-        <v>303</v>
+        <v>307</v>
       </c>
       <c r="Q173">
         <v>2.6</v>
@@ -36892,7 +36910,7 @@
         <v>1.64</v>
       </c>
       <c r="AQ173">
-        <v>1.46</v>
+        <v>1.36</v>
       </c>
       <c r="AR173">
         <v>1.47</v>
@@ -37017,7 +37035,7 @@
         <v>88</v>
       </c>
       <c r="P174" t="s">
-        <v>304</v>
+        <v>308</v>
       </c>
       <c r="Q174">
         <v>4.86</v>
@@ -37223,7 +37241,7 @@
         <v>204</v>
       </c>
       <c r="P175" t="s">
-        <v>290</v>
+        <v>294</v>
       </c>
       <c r="Q175">
         <v>2.66</v>
@@ -37301,7 +37319,7 @@
         <v>1.2</v>
       </c>
       <c r="AP175">
-        <v>1.54</v>
+        <v>1.64</v>
       </c>
       <c r="AQ175">
         <v>1.07</v>
@@ -37635,7 +37653,7 @@
         <v>171</v>
       </c>
       <c r="P177" t="s">
-        <v>305</v>
+        <v>309</v>
       </c>
       <c r="Q177">
         <v>3.63</v>
@@ -37919,7 +37937,7 @@
         <v>0.82</v>
       </c>
       <c r="AP178">
-        <v>2.54</v>
+        <v>2.43</v>
       </c>
       <c r="AQ178">
         <v>0.79</v>
@@ -38047,7 +38065,7 @@
         <v>88</v>
       </c>
       <c r="P179" t="s">
-        <v>306</v>
+        <v>310</v>
       </c>
       <c r="Q179">
         <v>3.92</v>
@@ -38125,7 +38143,7 @@
         <v>1.09</v>
       </c>
       <c r="AP179">
-        <v>0.77</v>
+        <v>0.93</v>
       </c>
       <c r="AQ179">
         <v>1.07</v>
@@ -38253,7 +38271,7 @@
         <v>206</v>
       </c>
       <c r="P180" t="s">
-        <v>307</v>
+        <v>311</v>
       </c>
       <c r="Q180">
         <v>1.32</v>
@@ -38334,7 +38352,7 @@
         <v>2.07</v>
       </c>
       <c r="AQ180">
-        <v>0.08</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="AR180">
         <v>2.04</v>
@@ -38746,7 +38764,7 @@
         <v>1.93</v>
       </c>
       <c r="AQ182">
-        <v>1</v>
+        <v>1.14</v>
       </c>
       <c r="AR182">
         <v>1.67</v>
@@ -38871,7 +38889,7 @@
         <v>208</v>
       </c>
       <c r="P183" t="s">
-        <v>308</v>
+        <v>312</v>
       </c>
       <c r="Q183">
         <v>4.3</v>
@@ -39077,7 +39095,7 @@
         <v>88</v>
       </c>
       <c r="P184" t="s">
-        <v>309</v>
+        <v>313</v>
       </c>
       <c r="Q184">
         <v>5.8</v>
@@ -39489,7 +39507,7 @@
         <v>96</v>
       </c>
       <c r="P186" t="s">
-        <v>310</v>
+        <v>314</v>
       </c>
       <c r="Q186">
         <v>4.7</v>
@@ -39567,10 +39585,10 @@
         <v>2.09</v>
       </c>
       <c r="AP186">
-        <v>1.54</v>
+        <v>1.43</v>
       </c>
       <c r="AQ186">
-        <v>2</v>
+        <v>1.93</v>
       </c>
       <c r="AR186">
         <v>1.58</v>
@@ -39979,7 +39997,7 @@
         <v>0.36</v>
       </c>
       <c r="AP188">
-        <v>1.54</v>
+        <v>1.64</v>
       </c>
       <c r="AQ188">
         <v>0.62</v>
@@ -40107,7 +40125,7 @@
         <v>88</v>
       </c>
       <c r="P189" t="s">
-        <v>311</v>
+        <v>315</v>
       </c>
       <c r="Q189">
         <v>4.5</v>
@@ -40600,7 +40618,7 @@
         <v>3</v>
       </c>
       <c r="AQ191">
-        <v>1.46</v>
+        <v>1.36</v>
       </c>
       <c r="AR191">
         <v>2.28</v>
@@ -41218,7 +41236,7 @@
         <v>1.38</v>
       </c>
       <c r="AQ194">
-        <v>0.08</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="AR194">
         <v>1.2</v>
@@ -41549,7 +41567,7 @@
         <v>215</v>
       </c>
       <c r="P196" t="s">
-        <v>230</v>
+        <v>234</v>
       </c>
       <c r="Q196">
         <v>1.95</v>
@@ -41627,7 +41645,7 @@
         <v>1.25</v>
       </c>
       <c r="AP196">
-        <v>2.54</v>
+        <v>2.43</v>
       </c>
       <c r="AQ196">
         <v>1.07</v>
@@ -41755,7 +41773,7 @@
         <v>88</v>
       </c>
       <c r="P197" t="s">
-        <v>230</v>
+        <v>234</v>
       </c>
       <c r="Q197">
         <v>2.88</v>
@@ -42042,7 +42060,7 @@
         <v>1.64</v>
       </c>
       <c r="AQ198">
-        <v>1</v>
+        <v>1.14</v>
       </c>
       <c r="AR198">
         <v>1.45</v>
@@ -42245,7 +42263,7 @@
         <v>1.92</v>
       </c>
       <c r="AP199">
-        <v>0.77</v>
+        <v>0.93</v>
       </c>
       <c r="AQ199">
         <v>1.93</v>
@@ -42454,7 +42472,7 @@
         <v>0.93</v>
       </c>
       <c r="AQ200">
-        <v>1</v>
+        <v>1.14</v>
       </c>
       <c r="AR200">
         <v>1.2</v>
@@ -42579,7 +42597,7 @@
         <v>158</v>
       </c>
       <c r="P201" t="s">
-        <v>312</v>
+        <v>316</v>
       </c>
       <c r="Q201">
         <v>2.63</v>
@@ -42660,7 +42678,7 @@
         <v>1.46</v>
       </c>
       <c r="AQ201">
-        <v>1.46</v>
+        <v>1.36</v>
       </c>
       <c r="AR201">
         <v>1.55</v>
@@ -42991,7 +43009,7 @@
         <v>88</v>
       </c>
       <c r="P203" t="s">
-        <v>254</v>
+        <v>258</v>
       </c>
       <c r="Q203">
         <v>2.75</v>
@@ -43069,7 +43087,7 @@
         <v>0.42</v>
       </c>
       <c r="AP203">
-        <v>0.77</v>
+        <v>0.93</v>
       </c>
       <c r="AQ203">
         <v>0.62</v>
@@ -43275,10 +43293,10 @@
         <v>2.17</v>
       </c>
       <c r="AP204">
-        <v>1.54</v>
+        <v>1.64</v>
       </c>
       <c r="AQ204">
-        <v>2</v>
+        <v>1.93</v>
       </c>
       <c r="AR204">
         <v>1.5</v>
@@ -43403,7 +43421,7 @@
         <v>218</v>
       </c>
       <c r="P205" t="s">
-        <v>313</v>
+        <v>317</v>
       </c>
       <c r="Q205">
         <v>2.88</v>
@@ -43481,10 +43499,10 @@
         <v>1</v>
       </c>
       <c r="AP205">
-        <v>1.54</v>
+        <v>1.43</v>
       </c>
       <c r="AQ205">
-        <v>1.17</v>
+        <v>1.08</v>
       </c>
       <c r="AR205">
         <v>1.56</v>
@@ -43609,7 +43627,7 @@
         <v>88</v>
       </c>
       <c r="P206" t="s">
-        <v>275</v>
+        <v>279</v>
       </c>
       <c r="Q206">
         <v>2.38</v>
@@ -43815,7 +43833,7 @@
         <v>219</v>
       </c>
       <c r="P207" t="s">
-        <v>314</v>
+        <v>318</v>
       </c>
       <c r="Q207">
         <v>4.75</v>
@@ -43896,7 +43914,7 @@
         <v>0.21</v>
       </c>
       <c r="AQ207">
-        <v>1</v>
+        <v>1.14</v>
       </c>
       <c r="AR207">
         <v>1.21</v>
@@ -44639,7 +44657,7 @@
         <v>221</v>
       </c>
       <c r="P211" t="s">
-        <v>315</v>
+        <v>319</v>
       </c>
       <c r="Q211">
         <v>1.57</v>
@@ -44717,7 +44735,7 @@
         <v>0.46</v>
       </c>
       <c r="AP211">
-        <v>2.54</v>
+        <v>2.43</v>
       </c>
       <c r="AQ211">
         <v>0.43</v>
@@ -45051,7 +45069,7 @@
         <v>88</v>
       </c>
       <c r="P213" t="s">
-        <v>316</v>
+        <v>320</v>
       </c>
       <c r="Q213">
         <v>3.5</v>
@@ -45544,7 +45562,7 @@
         <v>1.64</v>
       </c>
       <c r="AQ215">
-        <v>0.08</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="AR215">
         <v>1.53</v>
@@ -45669,7 +45687,7 @@
         <v>224</v>
       </c>
       <c r="P216" t="s">
-        <v>317</v>
+        <v>321</v>
       </c>
       <c r="Q216">
         <v>2.75</v>
@@ -45826,6 +45844,1036 @@
       </c>
       <c r="BP216">
         <v>0</v>
+      </c>
+    </row>
+    <row r="217" spans="1:68">
+      <c r="A217" s="1">
+        <v>216</v>
+      </c>
+      <c r="B217">
+        <v>7468303</v>
+      </c>
+      <c r="C217" t="s">
+        <v>68</v>
+      </c>
+      <c r="D217" t="s">
+        <v>69</v>
+      </c>
+      <c r="E217" s="2">
+        <v>45752.35416666666</v>
+      </c>
+      <c r="F217">
+        <v>28</v>
+      </c>
+      <c r="G217" t="s">
+        <v>79</v>
+      </c>
+      <c r="H217" t="s">
+        <v>73</v>
+      </c>
+      <c r="I217">
+        <v>1</v>
+      </c>
+      <c r="J217">
+        <v>0</v>
+      </c>
+      <c r="K217">
+        <v>1</v>
+      </c>
+      <c r="L217">
+        <v>2</v>
+      </c>
+      <c r="M217">
+        <v>0</v>
+      </c>
+      <c r="N217">
+        <v>2</v>
+      </c>
+      <c r="O217" t="s">
+        <v>225</v>
+      </c>
+      <c r="P217" t="s">
+        <v>88</v>
+      </c>
+      <c r="Q217">
+        <v>4</v>
+      </c>
+      <c r="R217">
+        <v>2.1</v>
+      </c>
+      <c r="S217">
+        <v>2.75</v>
+      </c>
+      <c r="T217">
+        <v>1.4</v>
+      </c>
+      <c r="U217">
+        <v>2.75</v>
+      </c>
+      <c r="V217">
+        <v>3</v>
+      </c>
+      <c r="W217">
+        <v>1.36</v>
+      </c>
+      <c r="X217">
+        <v>8</v>
+      </c>
+      <c r="Y217">
+        <v>1.08</v>
+      </c>
+      <c r="Z217">
+        <v>3.5</v>
+      </c>
+      <c r="AA217">
+        <v>3.2</v>
+      </c>
+      <c r="AB217">
+        <v>2.05</v>
+      </c>
+      <c r="AC217">
+        <v>0</v>
+      </c>
+      <c r="AD217">
+        <v>0</v>
+      </c>
+      <c r="AE217">
+        <v>1.32</v>
+      </c>
+      <c r="AF217">
+        <v>3.44</v>
+      </c>
+      <c r="AG217">
+        <v>2.01</v>
+      </c>
+      <c r="AH217">
+        <v>1.82</v>
+      </c>
+      <c r="AI217">
+        <v>1.75</v>
+      </c>
+      <c r="AJ217">
+        <v>2</v>
+      </c>
+      <c r="AK217">
+        <v>1.71</v>
+      </c>
+      <c r="AL217">
+        <v>1.31</v>
+      </c>
+      <c r="AM217">
+        <v>1.3</v>
+      </c>
+      <c r="AN217">
+        <v>0.77</v>
+      </c>
+      <c r="AO217">
+        <v>1.46</v>
+      </c>
+      <c r="AP217">
+        <v>0.93</v>
+      </c>
+      <c r="AQ217">
+        <v>1.36</v>
+      </c>
+      <c r="AR217">
+        <v>1.24</v>
+      </c>
+      <c r="AS217">
+        <v>1.3</v>
+      </c>
+      <c r="AT217">
+        <v>2.54</v>
+      </c>
+      <c r="AU217">
+        <v>5</v>
+      </c>
+      <c r="AV217">
+        <v>3</v>
+      </c>
+      <c r="AW217">
+        <v>1</v>
+      </c>
+      <c r="AX217">
+        <v>12</v>
+      </c>
+      <c r="AY217">
+        <v>6</v>
+      </c>
+      <c r="AZ217">
+        <v>15</v>
+      </c>
+      <c r="BA217">
+        <v>2</v>
+      </c>
+      <c r="BB217">
+        <v>7</v>
+      </c>
+      <c r="BC217">
+        <v>9</v>
+      </c>
+      <c r="BD217">
+        <v>2.5</v>
+      </c>
+      <c r="BE217">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="BF217">
+        <v>1.69</v>
+      </c>
+      <c r="BG217">
+        <v>0</v>
+      </c>
+      <c r="BH217">
+        <v>0</v>
+      </c>
+      <c r="BI217">
+        <v>1.29</v>
+      </c>
+      <c r="BJ217">
+        <v>3.04</v>
+      </c>
+      <c r="BK217">
+        <v>1.55</v>
+      </c>
+      <c r="BL217">
+        <v>2.23</v>
+      </c>
+      <c r="BM217">
+        <v>1.93</v>
+      </c>
+      <c r="BN217">
+        <v>1.78</v>
+      </c>
+      <c r="BO217">
+        <v>2.48</v>
+      </c>
+      <c r="BP217">
+        <v>1.45</v>
+      </c>
+    </row>
+    <row r="218" spans="1:68">
+      <c r="A218" s="1">
+        <v>217</v>
+      </c>
+      <c r="B218">
+        <v>7468308</v>
+      </c>
+      <c r="C218" t="s">
+        <v>68</v>
+      </c>
+      <c r="D218" t="s">
+        <v>69</v>
+      </c>
+      <c r="E218" s="2">
+        <v>45752.35416666666</v>
+      </c>
+      <c r="F218">
+        <v>28</v>
+      </c>
+      <c r="G218" t="s">
+        <v>85</v>
+      </c>
+      <c r="H218" t="s">
+        <v>75</v>
+      </c>
+      <c r="I218">
+        <v>1</v>
+      </c>
+      <c r="J218">
+        <v>1</v>
+      </c>
+      <c r="K218">
+        <v>2</v>
+      </c>
+      <c r="L218">
+        <v>1</v>
+      </c>
+      <c r="M218">
+        <v>2</v>
+      </c>
+      <c r="N218">
+        <v>3</v>
+      </c>
+      <c r="O218" t="s">
+        <v>124</v>
+      </c>
+      <c r="P218" t="s">
+        <v>322</v>
+      </c>
+      <c r="Q218">
+        <v>2.4</v>
+      </c>
+      <c r="R218">
+        <v>2.25</v>
+      </c>
+      <c r="S218">
+        <v>4.5</v>
+      </c>
+      <c r="T218">
+        <v>1.36</v>
+      </c>
+      <c r="U218">
+        <v>3</v>
+      </c>
+      <c r="V218">
+        <v>2.63</v>
+      </c>
+      <c r="W218">
+        <v>1.44</v>
+      </c>
+      <c r="X218">
+        <v>7</v>
+      </c>
+      <c r="Y218">
+        <v>1.1</v>
+      </c>
+      <c r="Z218">
+        <v>1.83</v>
+      </c>
+      <c r="AA218">
+        <v>3.72</v>
+      </c>
+      <c r="AB218">
+        <v>4.08</v>
+      </c>
+      <c r="AC218">
+        <v>0</v>
+      </c>
+      <c r="AD218">
+        <v>0</v>
+      </c>
+      <c r="AE218">
+        <v>1.25</v>
+      </c>
+      <c r="AF218">
+        <v>4.06</v>
+      </c>
+      <c r="AG218">
+        <v>1.8</v>
+      </c>
+      <c r="AH218">
+        <v>2</v>
+      </c>
+      <c r="AI218">
+        <v>1.7</v>
+      </c>
+      <c r="AJ218">
+        <v>2.05</v>
+      </c>
+      <c r="AK218">
+        <v>1.25</v>
+      </c>
+      <c r="AL218">
+        <v>1.28</v>
+      </c>
+      <c r="AM218">
+        <v>1.83</v>
+      </c>
+      <c r="AN218">
+        <v>1.54</v>
+      </c>
+      <c r="AO218">
+        <v>1</v>
+      </c>
+      <c r="AP218">
+        <v>1.43</v>
+      </c>
+      <c r="AQ218">
+        <v>1.14</v>
+      </c>
+      <c r="AR218">
+        <v>1.55</v>
+      </c>
+      <c r="AS218">
+        <v>1.39</v>
+      </c>
+      <c r="AT218">
+        <v>2.94</v>
+      </c>
+      <c r="AU218">
+        <v>6</v>
+      </c>
+      <c r="AV218">
+        <v>4</v>
+      </c>
+      <c r="AW218">
+        <v>7</v>
+      </c>
+      <c r="AX218">
+        <v>2</v>
+      </c>
+      <c r="AY218">
+        <v>13</v>
+      </c>
+      <c r="AZ218">
+        <v>6</v>
+      </c>
+      <c r="BA218">
+        <v>5</v>
+      </c>
+      <c r="BB218">
+        <v>5</v>
+      </c>
+      <c r="BC218">
+        <v>10</v>
+      </c>
+      <c r="BD218">
+        <v>1.46</v>
+      </c>
+      <c r="BE218">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="BF218">
+        <v>3.2</v>
+      </c>
+      <c r="BG218">
+        <v>0</v>
+      </c>
+      <c r="BH218">
+        <v>0</v>
+      </c>
+      <c r="BI218">
+        <v>1.32</v>
+      </c>
+      <c r="BJ218">
+        <v>2.88</v>
+      </c>
+      <c r="BK218">
+        <v>1.58</v>
+      </c>
+      <c r="BL218">
+        <v>2.17</v>
+      </c>
+      <c r="BM218">
+        <v>1.99</v>
+      </c>
+      <c r="BN218">
+        <v>1.73</v>
+      </c>
+      <c r="BO218">
+        <v>2.57</v>
+      </c>
+      <c r="BP218">
+        <v>1.42</v>
+      </c>
+    </row>
+    <row r="219" spans="1:68">
+      <c r="A219" s="1">
+        <v>218</v>
+      </c>
+      <c r="B219">
+        <v>7468304</v>
+      </c>
+      <c r="C219" t="s">
+        <v>68</v>
+      </c>
+      <c r="D219" t="s">
+        <v>69</v>
+      </c>
+      <c r="E219" s="2">
+        <v>45752.45833333334</v>
+      </c>
+      <c r="F219">
+        <v>28</v>
+      </c>
+      <c r="G219" t="s">
+        <v>83</v>
+      </c>
+      <c r="H219" t="s">
+        <v>70</v>
+      </c>
+      <c r="I219">
+        <v>1</v>
+      </c>
+      <c r="J219">
+        <v>0</v>
+      </c>
+      <c r="K219">
+        <v>1</v>
+      </c>
+      <c r="L219">
+        <v>1</v>
+      </c>
+      <c r="M219">
+        <v>1</v>
+      </c>
+      <c r="N219">
+        <v>2</v>
+      </c>
+      <c r="O219" t="s">
+        <v>226</v>
+      </c>
+      <c r="P219" t="s">
+        <v>323</v>
+      </c>
+      <c r="Q219">
+        <v>3</v>
+      </c>
+      <c r="R219">
+        <v>2.2</v>
+      </c>
+      <c r="S219">
+        <v>3.4</v>
+      </c>
+      <c r="T219">
+        <v>1.36</v>
+      </c>
+      <c r="U219">
+        <v>3</v>
+      </c>
+      <c r="V219">
+        <v>2.63</v>
+      </c>
+      <c r="W219">
+        <v>1.44</v>
+      </c>
+      <c r="X219">
+        <v>7</v>
+      </c>
+      <c r="Y219">
+        <v>1.1</v>
+      </c>
+      <c r="Z219">
+        <v>2.38</v>
+      </c>
+      <c r="AA219">
+        <v>3.3</v>
+      </c>
+      <c r="AB219">
+        <v>2.75</v>
+      </c>
+      <c r="AC219">
+        <v>0</v>
+      </c>
+      <c r="AD219">
+        <v>0</v>
+      </c>
+      <c r="AE219">
+        <v>1.24</v>
+      </c>
+      <c r="AF219">
+        <v>4.2</v>
+      </c>
+      <c r="AG219">
+        <v>1.8</v>
+      </c>
+      <c r="AH219">
+        <v>2</v>
+      </c>
+      <c r="AI219">
+        <v>1.62</v>
+      </c>
+      <c r="AJ219">
+        <v>2.2</v>
+      </c>
+      <c r="AK219">
+        <v>1.46</v>
+      </c>
+      <c r="AL219">
+        <v>1.28</v>
+      </c>
+      <c r="AM219">
+        <v>1.53</v>
+      </c>
+      <c r="AN219">
+        <v>2.54</v>
+      </c>
+      <c r="AO219">
+        <v>2</v>
+      </c>
+      <c r="AP219">
+        <v>2.43</v>
+      </c>
+      <c r="AQ219">
+        <v>1.93</v>
+      </c>
+      <c r="AR219">
+        <v>1.85</v>
+      </c>
+      <c r="AS219">
+        <v>1.7</v>
+      </c>
+      <c r="AT219">
+        <v>3.55</v>
+      </c>
+      <c r="AU219">
+        <v>6</v>
+      </c>
+      <c r="AV219">
+        <v>7</v>
+      </c>
+      <c r="AW219">
+        <v>10</v>
+      </c>
+      <c r="AX219">
+        <v>13</v>
+      </c>
+      <c r="AY219">
+        <v>19</v>
+      </c>
+      <c r="AZ219">
+        <v>32</v>
+      </c>
+      <c r="BA219">
+        <v>3</v>
+      </c>
+      <c r="BB219">
+        <v>10</v>
+      </c>
+      <c r="BC219">
+        <v>13</v>
+      </c>
+      <c r="BD219">
+        <v>1.79</v>
+      </c>
+      <c r="BE219">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="BF219">
+        <v>2.31</v>
+      </c>
+      <c r="BG219">
+        <v>0</v>
+      </c>
+      <c r="BH219">
+        <v>0</v>
+      </c>
+      <c r="BI219">
+        <v>1.27</v>
+      </c>
+      <c r="BJ219">
+        <v>3.14</v>
+      </c>
+      <c r="BK219">
+        <v>1.5</v>
+      </c>
+      <c r="BL219">
+        <v>2.35</v>
+      </c>
+      <c r="BM219">
+        <v>1.86</v>
+      </c>
+      <c r="BN219">
+        <v>1.84</v>
+      </c>
+      <c r="BO219">
+        <v>2.38</v>
+      </c>
+      <c r="BP219">
+        <v>1.49</v>
+      </c>
+    </row>
+    <row r="220" spans="1:68">
+      <c r="A220" s="1">
+        <v>219</v>
+      </c>
+      <c r="B220">
+        <v>7468309</v>
+      </c>
+      <c r="C220" t="s">
+        <v>68</v>
+      </c>
+      <c r="D220" t="s">
+        <v>69</v>
+      </c>
+      <c r="E220" s="2">
+        <v>45752.45833333334</v>
+      </c>
+      <c r="F220">
+        <v>28</v>
+      </c>
+      <c r="G220" t="s">
+        <v>81</v>
+      </c>
+      <c r="H220" t="s">
+        <v>72</v>
+      </c>
+      <c r="I220">
+        <v>1</v>
+      </c>
+      <c r="J220">
+        <v>0</v>
+      </c>
+      <c r="K220">
+        <v>1</v>
+      </c>
+      <c r="L220">
+        <v>2</v>
+      </c>
+      <c r="M220">
+        <v>0</v>
+      </c>
+      <c r="N220">
+        <v>2</v>
+      </c>
+      <c r="O220" t="s">
+        <v>227</v>
+      </c>
+      <c r="P220" t="s">
+        <v>88</v>
+      </c>
+      <c r="Q220">
+        <v>1.73</v>
+      </c>
+      <c r="R220">
+        <v>2.6</v>
+      </c>
+      <c r="S220">
+        <v>10</v>
+      </c>
+      <c r="T220">
+        <v>1.3</v>
+      </c>
+      <c r="U220">
+        <v>3.4</v>
+      </c>
+      <c r="V220">
+        <v>2.5</v>
+      </c>
+      <c r="W220">
+        <v>1.5</v>
+      </c>
+      <c r="X220">
+        <v>6</v>
+      </c>
+      <c r="Y220">
+        <v>1.13</v>
+      </c>
+      <c r="Z220">
+        <v>1.25</v>
+      </c>
+      <c r="AA220">
+        <v>5</v>
+      </c>
+      <c r="AB220">
+        <v>11</v>
+      </c>
+      <c r="AC220">
+        <v>0</v>
+      </c>
+      <c r="AD220">
+        <v>0</v>
+      </c>
+      <c r="AE220">
+        <v>1.2</v>
+      </c>
+      <c r="AF220">
+        <v>4.68</v>
+      </c>
+      <c r="AG220">
+        <v>1.7</v>
+      </c>
+      <c r="AH220">
+        <v>2.1</v>
+      </c>
+      <c r="AI220">
+        <v>2.25</v>
+      </c>
+      <c r="AJ220">
+        <v>1.57</v>
+      </c>
+      <c r="AK220">
+        <v>1.02</v>
+      </c>
+      <c r="AL220">
+        <v>1.12</v>
+      </c>
+      <c r="AM220">
+        <v>4.1</v>
+      </c>
+      <c r="AN220">
+        <v>1.54</v>
+      </c>
+      <c r="AO220">
+        <v>0.08</v>
+      </c>
+      <c r="AP220">
+        <v>1.64</v>
+      </c>
+      <c r="AQ220">
+        <v>0.07000000000000001</v>
+      </c>
+      <c r="AR220">
+        <v>1.48</v>
+      </c>
+      <c r="AS220">
+        <v>0.99</v>
+      </c>
+      <c r="AT220">
+        <v>2.47</v>
+      </c>
+      <c r="AU220">
+        <v>6</v>
+      </c>
+      <c r="AV220">
+        <v>0</v>
+      </c>
+      <c r="AW220">
+        <v>5</v>
+      </c>
+      <c r="AX220">
+        <v>10</v>
+      </c>
+      <c r="AY220">
+        <v>16</v>
+      </c>
+      <c r="AZ220">
+        <v>16</v>
+      </c>
+      <c r="BA220">
+        <v>5</v>
+      </c>
+      <c r="BB220">
+        <v>5</v>
+      </c>
+      <c r="BC220">
+        <v>10</v>
+      </c>
+      <c r="BD220">
+        <v>1.19</v>
+      </c>
+      <c r="BE220">
+        <v>12</v>
+      </c>
+      <c r="BF220">
+        <v>5.55</v>
+      </c>
+      <c r="BG220">
+        <v>0</v>
+      </c>
+      <c r="BH220">
+        <v>0</v>
+      </c>
+      <c r="BI220">
+        <v>1.22</v>
+      </c>
+      <c r="BJ220">
+        <v>3.5</v>
+      </c>
+      <c r="BK220">
+        <v>1.43</v>
+      </c>
+      <c r="BL220">
+        <v>2.54</v>
+      </c>
+      <c r="BM220">
+        <v>1.74</v>
+      </c>
+      <c r="BN220">
+        <v>1.98</v>
+      </c>
+      <c r="BO220">
+        <v>2.15</v>
+      </c>
+      <c r="BP220">
+        <v>1.59</v>
+      </c>
+    </row>
+    <row r="221" spans="1:68">
+      <c r="A221" s="1">
+        <v>220</v>
+      </c>
+      <c r="B221">
+        <v>7468307</v>
+      </c>
+      <c r="C221" t="s">
+        <v>68</v>
+      </c>
+      <c r="D221" t="s">
+        <v>69</v>
+      </c>
+      <c r="E221" s="2">
+        <v>45752.58333333334</v>
+      </c>
+      <c r="F221">
+        <v>28</v>
+      </c>
+      <c r="G221" t="s">
+        <v>80</v>
+      </c>
+      <c r="H221" t="s">
+        <v>77</v>
+      </c>
+      <c r="I221">
+        <v>1</v>
+      </c>
+      <c r="J221">
+        <v>1</v>
+      </c>
+      <c r="K221">
+        <v>2</v>
+      </c>
+      <c r="L221">
+        <v>2</v>
+      </c>
+      <c r="M221">
+        <v>1</v>
+      </c>
+      <c r="N221">
+        <v>3</v>
+      </c>
+      <c r="O221" t="s">
+        <v>228</v>
+      </c>
+      <c r="P221" t="s">
+        <v>237</v>
+      </c>
+      <c r="Q221">
+        <v>1.67</v>
+      </c>
+      <c r="R221">
+        <v>2.6</v>
+      </c>
+      <c r="S221">
+        <v>12</v>
+      </c>
+      <c r="T221">
+        <v>1.33</v>
+      </c>
+      <c r="U221">
+        <v>3.25</v>
+      </c>
+      <c r="V221">
+        <v>2.63</v>
+      </c>
+      <c r="W221">
+        <v>1.44</v>
+      </c>
+      <c r="X221">
+        <v>6.5</v>
+      </c>
+      <c r="Y221">
+        <v>1.11</v>
+      </c>
+      <c r="Z221">
+        <v>1.22</v>
+      </c>
+      <c r="AA221">
+        <v>5.5</v>
+      </c>
+      <c r="AB221">
+        <v>15</v>
+      </c>
+      <c r="AC221">
+        <v>0</v>
+      </c>
+      <c r="AD221">
+        <v>0</v>
+      </c>
+      <c r="AE221">
+        <v>1.22</v>
+      </c>
+      <c r="AF221">
+        <v>4.31</v>
+      </c>
+      <c r="AG221">
+        <v>1.73</v>
+      </c>
+      <c r="AH221">
+        <v>2.08</v>
+      </c>
+      <c r="AI221">
+        <v>2.5</v>
+      </c>
+      <c r="AJ221">
+        <v>1.5</v>
+      </c>
+      <c r="AK221">
+        <v>1</v>
+      </c>
+      <c r="AL221">
+        <v>1.11</v>
+      </c>
+      <c r="AM221">
+        <v>4.45</v>
+      </c>
+      <c r="AN221">
+        <v>3</v>
+      </c>
+      <c r="AO221">
+        <v>1.17</v>
+      </c>
+      <c r="AP221">
+        <v>3</v>
+      </c>
+      <c r="AQ221">
+        <v>1.08</v>
+      </c>
+      <c r="AR221">
+        <v>2.26</v>
+      </c>
+      <c r="AS221">
+        <v>1.27</v>
+      </c>
+      <c r="AT221">
+        <v>3.53</v>
+      </c>
+      <c r="AU221">
+        <v>7</v>
+      </c>
+      <c r="AV221">
+        <v>2</v>
+      </c>
+      <c r="AW221">
+        <v>11</v>
+      </c>
+      <c r="AX221">
+        <v>3</v>
+      </c>
+      <c r="AY221">
+        <v>18</v>
+      </c>
+      <c r="AZ221">
+        <v>5</v>
+      </c>
+      <c r="BA221">
+        <v>4</v>
+      </c>
+      <c r="BB221">
+        <v>2</v>
+      </c>
+      <c r="BC221">
+        <v>6</v>
+      </c>
+      <c r="BD221">
+        <v>1.04</v>
+      </c>
+      <c r="BE221">
+        <v>17.5</v>
+      </c>
+      <c r="BF221">
+        <v>12</v>
+      </c>
+      <c r="BG221">
+        <v>0</v>
+      </c>
+      <c r="BH221">
+        <v>0</v>
+      </c>
+      <c r="BI221">
+        <v>1.26</v>
+      </c>
+      <c r="BJ221">
+        <v>3.22</v>
+      </c>
+      <c r="BK221">
+        <v>1.49</v>
+      </c>
+      <c r="BL221">
+        <v>2.38</v>
+      </c>
+      <c r="BM221">
+        <v>1.85</v>
+      </c>
+      <c r="BN221">
+        <v>1.85</v>
+      </c>
+      <c r="BO221">
+        <v>2.32</v>
+      </c>
+      <c r="BP221">
+        <v>1.51</v>
       </c>
     </row>
   </sheetData>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Czech Republic First League_20242025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Czech Republic First League_20242025.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1388" uniqueCount="324">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1406" uniqueCount="325">
   <si>
     <t>Id_Jogo</t>
   </si>
@@ -703,6 +703,9 @@
     <t>['24', '58']</t>
   </si>
   <si>
+    <t>['14', '43']</t>
+  </si>
+  <si>
     <t>['25']</t>
   </si>
   <si>
@@ -1347,7 +1350,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:BP221"/>
+  <dimension ref="A1:BP224"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:68">
@@ -1603,7 +1606,7 @@
         <v>86</v>
       </c>
       <c r="P2" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="Q2">
         <v>1.53</v>
@@ -2015,7 +2018,7 @@
         <v>88</v>
       </c>
       <c r="P4" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="Q4">
         <v>2.88</v>
@@ -2427,7 +2430,7 @@
         <v>90</v>
       </c>
       <c r="P6" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="Q6">
         <v>5.5</v>
@@ -2633,7 +2636,7 @@
         <v>91</v>
       </c>
       <c r="P7" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="Q7">
         <v>3.2</v>
@@ -3457,7 +3460,7 @@
         <v>94</v>
       </c>
       <c r="P11" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="Q11">
         <v>6.5</v>
@@ -3535,7 +3538,7 @@
         <v>0</v>
       </c>
       <c r="AP11">
-        <v>1.46</v>
+        <v>1.36</v>
       </c>
       <c r="AQ11">
         <v>1.93</v>
@@ -3663,7 +3666,7 @@
         <v>88</v>
       </c>
       <c r="P12" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="Q12">
         <v>2.85</v>
@@ -4359,10 +4362,10 @@
         <v>0</v>
       </c>
       <c r="AP15">
-        <v>1.46</v>
+        <v>1.36</v>
       </c>
       <c r="AQ15">
-        <v>0.85</v>
+        <v>0.79</v>
       </c>
       <c r="AR15">
         <v>0</v>
@@ -4568,7 +4571,7 @@
         <v>2.43</v>
       </c>
       <c r="AQ16">
-        <v>1.15</v>
+        <v>1.29</v>
       </c>
       <c r="AR16">
         <v>0</v>
@@ -4771,7 +4774,7 @@
         <v>0</v>
       </c>
       <c r="AP17">
-        <v>2.23</v>
+        <v>2.29</v>
       </c>
       <c r="AQ17">
         <v>1.08</v>
@@ -4899,7 +4902,7 @@
         <v>88</v>
       </c>
       <c r="P18" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="Q18">
         <v>5.4</v>
@@ -5186,7 +5189,7 @@
         <v>2.07</v>
       </c>
       <c r="AQ19">
-        <v>0.62</v>
+        <v>0.79</v>
       </c>
       <c r="AR19">
         <v>1.9</v>
@@ -5929,7 +5932,7 @@
         <v>102</v>
       </c>
       <c r="P23" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="Q23">
         <v>2.6</v>
@@ -6135,7 +6138,7 @@
         <v>103</v>
       </c>
       <c r="P24" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="Q24">
         <v>2.75</v>
@@ -6341,7 +6344,7 @@
         <v>88</v>
       </c>
       <c r="P25" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="Q25">
         <v>1.06</v>
@@ -6422,7 +6425,7 @@
         <v>0.93</v>
       </c>
       <c r="AQ25">
-        <v>1.15</v>
+        <v>1.29</v>
       </c>
       <c r="AR25">
         <v>0.93</v>
@@ -6547,7 +6550,7 @@
         <v>104</v>
       </c>
       <c r="P26" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="Q26">
         <v>6.23</v>
@@ -6831,7 +6834,7 @@
         <v>3</v>
       </c>
       <c r="AP27">
-        <v>1.46</v>
+        <v>1.36</v>
       </c>
       <c r="AQ27">
         <v>1.14</v>
@@ -7246,7 +7249,7 @@
         <v>0.93</v>
       </c>
       <c r="AQ29">
-        <v>0.85</v>
+        <v>0.79</v>
       </c>
       <c r="AR29">
         <v>1.22</v>
@@ -7655,7 +7658,7 @@
         <v>0</v>
       </c>
       <c r="AP31">
-        <v>1.46</v>
+        <v>1.36</v>
       </c>
       <c r="AQ31">
         <v>0.07000000000000001</v>
@@ -7861,7 +7864,7 @@
         <v>3</v>
       </c>
       <c r="AP32">
-        <v>2.23</v>
+        <v>2.29</v>
       </c>
       <c r="AQ32">
         <v>1.14</v>
@@ -8070,7 +8073,7 @@
         <v>1.64</v>
       </c>
       <c r="AQ33">
-        <v>0.62</v>
+        <v>0.79</v>
       </c>
       <c r="AR33">
         <v>1.08</v>
@@ -8195,7 +8198,7 @@
         <v>111</v>
       </c>
       <c r="P34" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="Q34">
         <v>1.45</v>
@@ -8401,7 +8404,7 @@
         <v>112</v>
       </c>
       <c r="P35" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="Q35">
         <v>2.84</v>
@@ -8607,7 +8610,7 @@
         <v>113</v>
       </c>
       <c r="P36" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="Q36">
         <v>5.63</v>
@@ -8813,7 +8816,7 @@
         <v>114</v>
       </c>
       <c r="P37" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="Q37">
         <v>2.58</v>
@@ -9225,7 +9228,7 @@
         <v>88</v>
       </c>
       <c r="P39" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="Q39">
         <v>4.75</v>
@@ -9637,7 +9640,7 @@
         <v>117</v>
       </c>
       <c r="P41" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="Q41">
         <v>2.4</v>
@@ -9718,7 +9721,7 @@
         <v>1.07</v>
       </c>
       <c r="AQ41">
-        <v>1.15</v>
+        <v>1.29</v>
       </c>
       <c r="AR41">
         <v>1.49</v>
@@ -9843,7 +9846,7 @@
         <v>107</v>
       </c>
       <c r="P42" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="Q42">
         <v>2.61</v>
@@ -9921,7 +9924,7 @@
         <v>1.5</v>
       </c>
       <c r="AP42">
-        <v>1.46</v>
+        <v>1.36</v>
       </c>
       <c r="AQ42">
         <v>1.14</v>
@@ -10049,7 +10052,7 @@
         <v>118</v>
       </c>
       <c r="P43" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="Q43">
         <v>1.69</v>
@@ -10130,7 +10133,7 @@
         <v>2.07</v>
       </c>
       <c r="AQ43">
-        <v>0.85</v>
+        <v>0.79</v>
       </c>
       <c r="AR43">
         <v>2.07</v>
@@ -11366,7 +11369,7 @@
         <v>1.38</v>
       </c>
       <c r="AQ49">
-        <v>1.15</v>
+        <v>1.29</v>
       </c>
       <c r="AR49">
         <v>1.24</v>
@@ -11491,7 +11494,7 @@
         <v>88</v>
       </c>
       <c r="P50" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="Q50">
         <v>5.1</v>
@@ -11778,7 +11781,7 @@
         <v>1.57</v>
       </c>
       <c r="AQ51">
-        <v>0.62</v>
+        <v>0.79</v>
       </c>
       <c r="AR51">
         <v>1.76</v>
@@ -11903,7 +11906,7 @@
         <v>122</v>
       </c>
       <c r="P52" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="Q52">
         <v>3</v>
@@ -12315,7 +12318,7 @@
         <v>124</v>
       </c>
       <c r="P54" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="Q54">
         <v>3</v>
@@ -12393,7 +12396,7 @@
         <v>0</v>
       </c>
       <c r="AP54">
-        <v>1.46</v>
+        <v>1.36</v>
       </c>
       <c r="AQ54">
         <v>1.07</v>
@@ -12805,7 +12808,7 @@
         <v>1.33</v>
       </c>
       <c r="AP56">
-        <v>2.23</v>
+        <v>2.29</v>
       </c>
       <c r="AQ56">
         <v>1.36</v>
@@ -12933,7 +12936,7 @@
         <v>88</v>
       </c>
       <c r="P57" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="Q57">
         <v>5.88</v>
@@ -13011,7 +13014,7 @@
         <v>2</v>
       </c>
       <c r="AP57">
-        <v>1.46</v>
+        <v>1.36</v>
       </c>
       <c r="AQ57">
         <v>2.14</v>
@@ -13220,7 +13223,7 @@
         <v>1.64</v>
       </c>
       <c r="AQ58">
-        <v>0.85</v>
+        <v>0.79</v>
       </c>
       <c r="AR58">
         <v>1.32</v>
@@ -13345,7 +13348,7 @@
         <v>127</v>
       </c>
       <c r="P59" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="Q59">
         <v>3.86</v>
@@ -13423,7 +13426,7 @@
         <v>0.5</v>
       </c>
       <c r="AP59">
-        <v>1.46</v>
+        <v>1.36</v>
       </c>
       <c r="AQ59">
         <v>1.71</v>
@@ -13632,7 +13635,7 @@
         <v>1.57</v>
       </c>
       <c r="AQ60">
-        <v>1.15</v>
+        <v>1.29</v>
       </c>
       <c r="AR60">
         <v>1.83</v>
@@ -13963,7 +13966,7 @@
         <v>130</v>
       </c>
       <c r="P62" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="Q62">
         <v>1.83</v>
@@ -14041,7 +14044,7 @@
         <v>0.75</v>
       </c>
       <c r="AP62">
-        <v>1.46</v>
+        <v>1.36</v>
       </c>
       <c r="AQ62">
         <v>0.43</v>
@@ -14169,7 +14172,7 @@
         <v>88</v>
       </c>
       <c r="P63" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="Q63">
         <v>8.77</v>
@@ -14456,7 +14459,7 @@
         <v>1.43</v>
       </c>
       <c r="AQ64">
-        <v>0.62</v>
+        <v>0.79</v>
       </c>
       <c r="AR64">
         <v>1.75</v>
@@ -14581,7 +14584,7 @@
         <v>132</v>
       </c>
       <c r="P65" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="Q65">
         <v>2.4</v>
@@ -14787,7 +14790,7 @@
         <v>133</v>
       </c>
       <c r="P66" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="Q66">
         <v>1.55</v>
@@ -14993,7 +14996,7 @@
         <v>134</v>
       </c>
       <c r="P67" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="Q67">
         <v>4</v>
@@ -15199,7 +15202,7 @@
         <v>88</v>
       </c>
       <c r="P68" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="Q68">
         <v>3.1</v>
@@ -16023,7 +16026,7 @@
         <v>124</v>
       </c>
       <c r="P72" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="Q72">
         <v>1.88</v>
@@ -16101,7 +16104,7 @@
         <v>0.75</v>
       </c>
       <c r="AP72">
-        <v>2.23</v>
+        <v>2.29</v>
       </c>
       <c r="AQ72">
         <v>1.07</v>
@@ -16229,7 +16232,7 @@
         <v>88</v>
       </c>
       <c r="P73" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="Q73">
         <v>7</v>
@@ -16641,7 +16644,7 @@
         <v>138</v>
       </c>
       <c r="P75" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="Q75">
         <v>2.3</v>
@@ -16719,10 +16722,10 @@
         <v>0.25</v>
       </c>
       <c r="AP75">
-        <v>1.46</v>
+        <v>1.36</v>
       </c>
       <c r="AQ75">
-        <v>0.62</v>
+        <v>0.79</v>
       </c>
       <c r="AR75">
         <v>1.49</v>
@@ -16847,7 +16850,7 @@
         <v>88</v>
       </c>
       <c r="P76" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="Q76">
         <v>3.7</v>
@@ -16928,7 +16931,7 @@
         <v>0.21</v>
       </c>
       <c r="AQ76">
-        <v>0.85</v>
+        <v>0.79</v>
       </c>
       <c r="AR76">
         <v>1.29</v>
@@ -17053,7 +17056,7 @@
         <v>88</v>
       </c>
       <c r="P77" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="Q77">
         <v>2.47</v>
@@ -17134,7 +17137,7 @@
         <v>1.64</v>
       </c>
       <c r="AQ77">
-        <v>1.15</v>
+        <v>1.29</v>
       </c>
       <c r="AR77">
         <v>1.45</v>
@@ -17337,7 +17340,7 @@
         <v>0.8</v>
       </c>
       <c r="AP78">
-        <v>2.23</v>
+        <v>2.29</v>
       </c>
       <c r="AQ78">
         <v>0.43</v>
@@ -17543,7 +17546,7 @@
         <v>1</v>
       </c>
       <c r="AP79">
-        <v>1.46</v>
+        <v>1.36</v>
       </c>
       <c r="AQ79">
         <v>1.71</v>
@@ -17671,7 +17674,7 @@
         <v>140</v>
       </c>
       <c r="P80" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="Q80">
         <v>2.5</v>
@@ -17877,7 +17880,7 @@
         <v>141</v>
       </c>
       <c r="P81" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="Q81">
         <v>2.38</v>
@@ -18083,7 +18086,7 @@
         <v>142</v>
       </c>
       <c r="P82" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="Q82">
         <v>2.8</v>
@@ -18289,7 +18292,7 @@
         <v>143</v>
       </c>
       <c r="P83" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="Q83">
         <v>2.6</v>
@@ -18495,7 +18498,7 @@
         <v>144</v>
       </c>
       <c r="P84" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="Q84">
         <v>3.4</v>
@@ -18907,7 +18910,7 @@
         <v>146</v>
       </c>
       <c r="P86" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="Q86">
         <v>2.88</v>
@@ -19319,7 +19322,7 @@
         <v>88</v>
       </c>
       <c r="P88" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="Q88">
         <v>2.6</v>
@@ -19525,7 +19528,7 @@
         <v>93</v>
       </c>
       <c r="P89" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="Q89">
         <v>6.5</v>
@@ -19812,7 +19815,7 @@
         <v>1.64</v>
       </c>
       <c r="AQ90">
-        <v>0.85</v>
+        <v>0.79</v>
       </c>
       <c r="AR90">
         <v>1.39</v>
@@ -19937,7 +19940,7 @@
         <v>149</v>
       </c>
       <c r="P91" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="Q91">
         <v>4.7</v>
@@ -20143,7 +20146,7 @@
         <v>88</v>
       </c>
       <c r="P92" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="Q92">
         <v>3.8</v>
@@ -20430,7 +20433,7 @@
         <v>1.43</v>
       </c>
       <c r="AQ93">
-        <v>1.15</v>
+        <v>1.29</v>
       </c>
       <c r="AR93">
         <v>1.61</v>
@@ -20555,7 +20558,7 @@
         <v>150</v>
       </c>
       <c r="P94" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="Q94">
         <v>3</v>
@@ -20633,7 +20636,7 @@
         <v>1.5</v>
       </c>
       <c r="AP94">
-        <v>1.46</v>
+        <v>1.36</v>
       </c>
       <c r="AQ94">
         <v>1.36</v>
@@ -20839,7 +20842,7 @@
         <v>1.5</v>
       </c>
       <c r="AP95">
-        <v>1.46</v>
+        <v>1.36</v>
       </c>
       <c r="AQ95">
         <v>1.14</v>
@@ -21048,7 +21051,7 @@
         <v>3</v>
       </c>
       <c r="AQ96">
-        <v>0.62</v>
+        <v>0.79</v>
       </c>
       <c r="AR96">
         <v>2.31</v>
@@ -21251,7 +21254,7 @@
         <v>2.5</v>
       </c>
       <c r="AP97">
-        <v>2.23</v>
+        <v>2.29</v>
       </c>
       <c r="AQ97">
         <v>1.93</v>
@@ -21997,7 +22000,7 @@
         <v>156</v>
       </c>
       <c r="P101" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="Q101">
         <v>1.83</v>
@@ -23108,7 +23111,7 @@
         <v>2.43</v>
       </c>
       <c r="AQ106">
-        <v>0.62</v>
+        <v>0.79</v>
       </c>
       <c r="AR106">
         <v>1.87</v>
@@ -23314,7 +23317,7 @@
         <v>0.93</v>
       </c>
       <c r="AQ107">
-        <v>1.15</v>
+        <v>1.29</v>
       </c>
       <c r="AR107">
         <v>1.14</v>
@@ -23645,7 +23648,7 @@
         <v>161</v>
       </c>
       <c r="P109" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="Q109">
         <v>2.24</v>
@@ -23723,7 +23726,7 @@
         <v>0</v>
       </c>
       <c r="AP109">
-        <v>1.46</v>
+        <v>1.36</v>
       </c>
       <c r="AQ109">
         <v>0.07000000000000001</v>
@@ -23851,7 +23854,7 @@
         <v>162</v>
       </c>
       <c r="P110" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="Q110">
         <v>4.6</v>
@@ -23929,7 +23932,7 @@
         <v>2.14</v>
       </c>
       <c r="AP110">
-        <v>1.46</v>
+        <v>1.36</v>
       </c>
       <c r="AQ110">
         <v>1.93</v>
@@ -24135,7 +24138,7 @@
         <v>1.71</v>
       </c>
       <c r="AP111">
-        <v>2.23</v>
+        <v>2.29</v>
       </c>
       <c r="AQ111">
         <v>1.36</v>
@@ -24469,7 +24472,7 @@
         <v>165</v>
       </c>
       <c r="P113" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="Q113">
         <v>3.25</v>
@@ -24675,7 +24678,7 @@
         <v>151</v>
       </c>
       <c r="P114" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="Q114">
         <v>2.88</v>
@@ -24881,7 +24884,7 @@
         <v>99</v>
       </c>
       <c r="P115" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="Q115">
         <v>1.73</v>
@@ -25087,7 +25090,7 @@
         <v>88</v>
       </c>
       <c r="P116" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="Q116">
         <v>4.33</v>
@@ -25374,7 +25377,7 @@
         <v>1.07</v>
       </c>
       <c r="AQ117">
-        <v>0.62</v>
+        <v>0.79</v>
       </c>
       <c r="AR117">
         <v>1.44</v>
@@ -25705,7 +25708,7 @@
         <v>88</v>
       </c>
       <c r="P119" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="Q119">
         <v>15</v>
@@ -25911,7 +25914,7 @@
         <v>168</v>
       </c>
       <c r="P120" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="Q120">
         <v>3</v>
@@ -26198,7 +26201,7 @@
         <v>1.43</v>
       </c>
       <c r="AQ121">
-        <v>0.85</v>
+        <v>0.79</v>
       </c>
       <c r="AR121">
         <v>1.57</v>
@@ -26323,7 +26326,7 @@
         <v>170</v>
       </c>
       <c r="P122" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="Q122">
         <v>3.25</v>
@@ -26404,7 +26407,7 @@
         <v>1.07</v>
       </c>
       <c r="AQ122">
-        <v>0.85</v>
+        <v>0.79</v>
       </c>
       <c r="AR122">
         <v>1.54</v>
@@ -26607,7 +26610,7 @@
         <v>1.14</v>
       </c>
       <c r="AP123">
-        <v>1.46</v>
+        <v>1.36</v>
       </c>
       <c r="AQ123">
         <v>1.36</v>
@@ -26735,7 +26738,7 @@
         <v>172</v>
       </c>
       <c r="P124" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="Q124">
         <v>1.83</v>
@@ -26941,7 +26944,7 @@
         <v>171</v>
       </c>
       <c r="P125" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="Q125">
         <v>6.3</v>
@@ -27431,7 +27434,7 @@
         <v>0.71</v>
       </c>
       <c r="AP127">
-        <v>1.46</v>
+        <v>1.36</v>
       </c>
       <c r="AQ127">
         <v>1.08</v>
@@ -27765,7 +27768,7 @@
         <v>174</v>
       </c>
       <c r="P129" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="Q129">
         <v>2.1</v>
@@ -27843,10 +27846,10 @@
         <v>1.38</v>
       </c>
       <c r="AP129">
-        <v>2.23</v>
+        <v>2.29</v>
       </c>
       <c r="AQ129">
-        <v>1.15</v>
+        <v>1.29</v>
       </c>
       <c r="AR129">
         <v>1.69</v>
@@ -27971,7 +27974,7 @@
         <v>175</v>
       </c>
       <c r="P130" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="Q130">
         <v>1.5</v>
@@ -28177,7 +28180,7 @@
         <v>176</v>
       </c>
       <c r="P131" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="Q131">
         <v>3.5</v>
@@ -28383,7 +28386,7 @@
         <v>177</v>
       </c>
       <c r="P132" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="Q132">
         <v>4.04</v>
@@ -28464,7 +28467,7 @@
         <v>0.93</v>
       </c>
       <c r="AQ132">
-        <v>0.85</v>
+        <v>0.79</v>
       </c>
       <c r="AR132">
         <v>1.24</v>
@@ -28795,7 +28798,7 @@
         <v>88</v>
       </c>
       <c r="P134" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="Q134">
         <v>2.75</v>
@@ -29079,7 +29082,7 @@
         <v>1.25</v>
       </c>
       <c r="AP135">
-        <v>1.46</v>
+        <v>1.36</v>
       </c>
       <c r="AQ135">
         <v>1.14</v>
@@ -29491,7 +29494,7 @@
         <v>1</v>
       </c>
       <c r="AP137">
-        <v>2.23</v>
+        <v>2.29</v>
       </c>
       <c r="AQ137">
         <v>0.79</v>
@@ -29619,7 +29622,7 @@
         <v>91</v>
       </c>
       <c r="P138" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="Q138">
         <v>2.25</v>
@@ -29825,7 +29828,7 @@
         <v>179</v>
       </c>
       <c r="P139" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="Q139">
         <v>1.9</v>
@@ -29906,7 +29909,7 @@
         <v>1.93</v>
       </c>
       <c r="AQ139">
-        <v>0.62</v>
+        <v>0.79</v>
       </c>
       <c r="AR139">
         <v>1.71</v>
@@ -30237,7 +30240,7 @@
         <v>88</v>
       </c>
       <c r="P141" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="Q141">
         <v>4</v>
@@ -30443,7 +30446,7 @@
         <v>117</v>
       </c>
       <c r="P142" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="Q142">
         <v>4</v>
@@ -30855,7 +30858,7 @@
         <v>182</v>
       </c>
       <c r="P144" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="Q144">
         <v>6</v>
@@ -31061,7 +31064,7 @@
         <v>88</v>
       </c>
       <c r="P145" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="Q145">
         <v>3.5</v>
@@ -31267,7 +31270,7 @@
         <v>183</v>
       </c>
       <c r="P146" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="Q146">
         <v>4.33</v>
@@ -31473,7 +31476,7 @@
         <v>184</v>
       </c>
       <c r="P147" t="s">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="Q147">
         <v>3.8</v>
@@ -31679,7 +31682,7 @@
         <v>185</v>
       </c>
       <c r="P148" t="s">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="Q148">
         <v>2.5</v>
@@ -31885,7 +31888,7 @@
         <v>186</v>
       </c>
       <c r="P149" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="Q149">
         <v>2.05</v>
@@ -31966,7 +31969,7 @@
         <v>2.43</v>
       </c>
       <c r="AQ149">
-        <v>0.85</v>
+        <v>0.79</v>
       </c>
       <c r="AR149">
         <v>1.91</v>
@@ -32172,7 +32175,7 @@
         <v>2.07</v>
       </c>
       <c r="AQ150">
-        <v>1.15</v>
+        <v>1.29</v>
       </c>
       <c r="AR150">
         <v>1.98</v>
@@ -32297,7 +32300,7 @@
         <v>188</v>
       </c>
       <c r="P151" t="s">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="Q151">
         <v>2.48</v>
@@ -32375,7 +32378,7 @@
         <v>1</v>
       </c>
       <c r="AP151">
-        <v>1.46</v>
+        <v>1.36</v>
       </c>
       <c r="AQ151">
         <v>1.36</v>
@@ -32581,7 +32584,7 @@
         <v>2.56</v>
       </c>
       <c r="AP152">
-        <v>1.46</v>
+        <v>1.36</v>
       </c>
       <c r="AQ152">
         <v>2.14</v>
@@ -32709,7 +32712,7 @@
         <v>190</v>
       </c>
       <c r="P153" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="Q153">
         <v>1.4</v>
@@ -32787,7 +32790,7 @@
         <v>0.13</v>
       </c>
       <c r="AP153">
-        <v>2.23</v>
+        <v>2.29</v>
       </c>
       <c r="AQ153">
         <v>0.07000000000000001</v>
@@ -33121,7 +33124,7 @@
         <v>88</v>
       </c>
       <c r="P155" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="Q155">
         <v>3.2</v>
@@ -33408,7 +33411,7 @@
         <v>0.21</v>
       </c>
       <c r="AQ156">
-        <v>0.62</v>
+        <v>0.79</v>
       </c>
       <c r="AR156">
         <v>1.34</v>
@@ -33739,7 +33742,7 @@
         <v>88</v>
       </c>
       <c r="P158" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="Q158">
         <v>5</v>
@@ -33945,7 +33948,7 @@
         <v>88</v>
       </c>
       <c r="P159" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="Q159">
         <v>2.38</v>
@@ -34357,7 +34360,7 @@
         <v>193</v>
       </c>
       <c r="P161" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="Q161">
         <v>4.75</v>
@@ -34563,7 +34566,7 @@
         <v>194</v>
       </c>
       <c r="P162" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="Q162">
         <v>2.63</v>
@@ -34641,7 +34644,7 @@
         <v>0.9</v>
       </c>
       <c r="AP162">
-        <v>1.46</v>
+        <v>1.36</v>
       </c>
       <c r="AQ162">
         <v>0.79</v>
@@ -34769,7 +34772,7 @@
         <v>88</v>
       </c>
       <c r="P163" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="Q163">
         <v>11</v>
@@ -34975,7 +34978,7 @@
         <v>195</v>
       </c>
       <c r="P164" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="Q164">
         <v>2</v>
@@ -35053,7 +35056,7 @@
         <v>1.1</v>
       </c>
       <c r="AP164">
-        <v>2.23</v>
+        <v>2.29</v>
       </c>
       <c r="AQ164">
         <v>1.14</v>
@@ -35181,7 +35184,7 @@
         <v>196</v>
       </c>
       <c r="P165" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="Q165">
         <v>2.5</v>
@@ -35262,7 +35265,7 @@
         <v>1.93</v>
       </c>
       <c r="AQ165">
-        <v>0.85</v>
+        <v>0.79</v>
       </c>
       <c r="AR165">
         <v>1.66</v>
@@ -36292,7 +36295,7 @@
         <v>1.38</v>
       </c>
       <c r="AQ170">
-        <v>0.62</v>
+        <v>0.79</v>
       </c>
       <c r="AR170">
         <v>1.21</v>
@@ -36417,7 +36420,7 @@
         <v>201</v>
       </c>
       <c r="P171" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="Q171">
         <v>5.2</v>
@@ -36498,7 +36501,7 @@
         <v>0.21</v>
       </c>
       <c r="AQ171">
-        <v>1.15</v>
+        <v>1.29</v>
       </c>
       <c r="AR171">
         <v>1.3</v>
@@ -36623,7 +36626,7 @@
         <v>202</v>
       </c>
       <c r="P172" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="Q172">
         <v>6.35</v>
@@ -36829,7 +36832,7 @@
         <v>203</v>
       </c>
       <c r="P173" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="Q173">
         <v>2.6</v>
@@ -37035,7 +37038,7 @@
         <v>88</v>
       </c>
       <c r="P174" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="Q174">
         <v>4.86</v>
@@ -37113,7 +37116,7 @@
         <v>1.7</v>
       </c>
       <c r="AP174">
-        <v>1.46</v>
+        <v>1.36</v>
       </c>
       <c r="AQ174">
         <v>1.93</v>
@@ -37241,7 +37244,7 @@
         <v>204</v>
       </c>
       <c r="P175" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="Q175">
         <v>2.66</v>
@@ -37653,7 +37656,7 @@
         <v>171</v>
       </c>
       <c r="P177" t="s">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="Q177">
         <v>3.63</v>
@@ -38065,7 +38068,7 @@
         <v>88</v>
       </c>
       <c r="P179" t="s">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="Q179">
         <v>3.92</v>
@@ -38271,7 +38274,7 @@
         <v>206</v>
       </c>
       <c r="P180" t="s">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="Q180">
         <v>1.32</v>
@@ -38889,7 +38892,7 @@
         <v>208</v>
       </c>
       <c r="P183" t="s">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="Q183">
         <v>4.3</v>
@@ -38967,7 +38970,7 @@
         <v>2.36</v>
       </c>
       <c r="AP183">
-        <v>2.23</v>
+        <v>2.29</v>
       </c>
       <c r="AQ183">
         <v>2.14</v>
@@ -39095,7 +39098,7 @@
         <v>88</v>
       </c>
       <c r="P184" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="Q184">
         <v>5.8</v>
@@ -39382,7 +39385,7 @@
         <v>1.64</v>
       </c>
       <c r="AQ185">
-        <v>1.15</v>
+        <v>1.29</v>
       </c>
       <c r="AR185">
         <v>1.46</v>
@@ -39507,7 +39510,7 @@
         <v>96</v>
       </c>
       <c r="P186" t="s">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="Q186">
         <v>4.7</v>
@@ -39791,7 +39794,7 @@
         <v>0.5</v>
       </c>
       <c r="AP187">
-        <v>1.46</v>
+        <v>1.36</v>
       </c>
       <c r="AQ187">
         <v>0.43</v>
@@ -40000,7 +40003,7 @@
         <v>1.64</v>
       </c>
       <c r="AQ188">
-        <v>0.62</v>
+        <v>0.79</v>
       </c>
       <c r="AR188">
         <v>1.49</v>
@@ -40125,7 +40128,7 @@
         <v>88</v>
       </c>
       <c r="P189" t="s">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="Q189">
         <v>4.5</v>
@@ -40203,7 +40206,7 @@
         <v>1.82</v>
       </c>
       <c r="AP189">
-        <v>1.46</v>
+        <v>1.36</v>
       </c>
       <c r="AQ189">
         <v>1.93</v>
@@ -40412,7 +40415,7 @@
         <v>1.57</v>
       </c>
       <c r="AQ190">
-        <v>0.85</v>
+        <v>0.79</v>
       </c>
       <c r="AR190">
         <v>1.53</v>
@@ -41567,7 +41570,7 @@
         <v>215</v>
       </c>
       <c r="P196" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="Q196">
         <v>1.95</v>
@@ -41773,7 +41776,7 @@
         <v>88</v>
       </c>
       <c r="P197" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="Q197">
         <v>2.88</v>
@@ -42597,7 +42600,7 @@
         <v>158</v>
       </c>
       <c r="P201" t="s">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="Q201">
         <v>2.63</v>
@@ -42675,7 +42678,7 @@
         <v>1.33</v>
       </c>
       <c r="AP201">
-        <v>1.46</v>
+        <v>1.36</v>
       </c>
       <c r="AQ201">
         <v>1.36</v>
@@ -42881,10 +42884,10 @@
         <v>0.92</v>
       </c>
       <c r="AP202">
-        <v>1.46</v>
+        <v>1.36</v>
       </c>
       <c r="AQ202">
-        <v>0.85</v>
+        <v>0.79</v>
       </c>
       <c r="AR202">
         <v>1.47</v>
@@ -43009,7 +43012,7 @@
         <v>88</v>
       </c>
       <c r="P203" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="Q203">
         <v>2.75</v>
@@ -43090,7 +43093,7 @@
         <v>0.93</v>
       </c>
       <c r="AQ203">
-        <v>0.62</v>
+        <v>0.79</v>
       </c>
       <c r="AR203">
         <v>1.23</v>
@@ -43421,7 +43424,7 @@
         <v>218</v>
       </c>
       <c r="P205" t="s">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="Q205">
         <v>2.88</v>
@@ -43627,7 +43630,7 @@
         <v>88</v>
       </c>
       <c r="P206" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="Q206">
         <v>2.38</v>
@@ -43705,7 +43708,7 @@
         <v>1.62</v>
       </c>
       <c r="AP206">
-        <v>2.23</v>
+        <v>2.29</v>
       </c>
       <c r="AQ206">
         <v>1.71</v>
@@ -43833,7 +43836,7 @@
         <v>219</v>
       </c>
       <c r="P207" t="s">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="Q207">
         <v>4.75</v>
@@ -44120,7 +44123,7 @@
         <v>3</v>
       </c>
       <c r="AQ208">
-        <v>1.15</v>
+        <v>1.29</v>
       </c>
       <c r="AR208">
         <v>2.31</v>
@@ -44657,7 +44660,7 @@
         <v>221</v>
       </c>
       <c r="P211" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="Q211">
         <v>1.57</v>
@@ -45069,7 +45072,7 @@
         <v>88</v>
       </c>
       <c r="P213" t="s">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="Q213">
         <v>3.5</v>
@@ -45687,7 +45690,7 @@
         <v>224</v>
       </c>
       <c r="P216" t="s">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="Q216">
         <v>2.75</v>
@@ -46099,7 +46102,7 @@
         <v>124</v>
       </c>
       <c r="P218" t="s">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="Q218">
         <v>2.4</v>
@@ -46305,7 +46308,7 @@
         <v>226</v>
       </c>
       <c r="P219" t="s">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="Q219">
         <v>3</v>
@@ -46717,7 +46720,7 @@
         <v>228</v>
       </c>
       <c r="P221" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="Q221">
         <v>1.67</v>
@@ -46874,6 +46877,624 @@
       </c>
       <c r="BP221">
         <v>1.51</v>
+      </c>
+    </row>
+    <row r="222" spans="1:68">
+      <c r="A222" s="1">
+        <v>221</v>
+      </c>
+      <c r="B222">
+        <v>7468305</v>
+      </c>
+      <c r="C222" t="s">
+        <v>68</v>
+      </c>
+      <c r="D222" t="s">
+        <v>69</v>
+      </c>
+      <c r="E222" s="2">
+        <v>45753.33333333334</v>
+      </c>
+      <c r="F222">
+        <v>28</v>
+      </c>
+      <c r="G222" t="s">
+        <v>78</v>
+      </c>
+      <c r="H222" t="s">
+        <v>71</v>
+      </c>
+      <c r="I222">
+        <v>0</v>
+      </c>
+      <c r="J222">
+        <v>1</v>
+      </c>
+      <c r="K222">
+        <v>1</v>
+      </c>
+      <c r="L222">
+        <v>0</v>
+      </c>
+      <c r="M222">
+        <v>1</v>
+      </c>
+      <c r="N222">
+        <v>1</v>
+      </c>
+      <c r="O222" t="s">
+        <v>88</v>
+      </c>
+      <c r="P222" t="s">
+        <v>110</v>
+      </c>
+      <c r="Q222">
+        <v>3.4</v>
+      </c>
+      <c r="R222">
+        <v>2.05</v>
+      </c>
+      <c r="S222">
+        <v>3.4</v>
+      </c>
+      <c r="T222">
+        <v>1.5</v>
+      </c>
+      <c r="U222">
+        <v>2.5</v>
+      </c>
+      <c r="V222">
+        <v>3.4</v>
+      </c>
+      <c r="W222">
+        <v>1.3</v>
+      </c>
+      <c r="X222">
+        <v>10</v>
+      </c>
+      <c r="Y222">
+        <v>1.06</v>
+      </c>
+      <c r="Z222">
+        <v>2.63</v>
+      </c>
+      <c r="AA222">
+        <v>3.2</v>
+      </c>
+      <c r="AB222">
+        <v>2.7</v>
+      </c>
+      <c r="AC222">
+        <v>1.03</v>
+      </c>
+      <c r="AD222">
+        <v>7.3</v>
+      </c>
+      <c r="AE222">
+        <v>1.35</v>
+      </c>
+      <c r="AF222">
+        <v>2.75</v>
+      </c>
+      <c r="AG222">
+        <v>2.15</v>
+      </c>
+      <c r="AH222">
+        <v>1.67</v>
+      </c>
+      <c r="AI222">
+        <v>1.91</v>
+      </c>
+      <c r="AJ222">
+        <v>1.91</v>
+      </c>
+      <c r="AK222">
+        <v>1.44</v>
+      </c>
+      <c r="AL222">
+        <v>1.36</v>
+      </c>
+      <c r="AM222">
+        <v>1.44</v>
+      </c>
+      <c r="AN222">
+        <v>1.46</v>
+      </c>
+      <c r="AO222">
+        <v>1.15</v>
+      </c>
+      <c r="AP222">
+        <v>1.36</v>
+      </c>
+      <c r="AQ222">
+        <v>1.29</v>
+      </c>
+      <c r="AR222">
+        <v>1.47</v>
+      </c>
+      <c r="AS222">
+        <v>1.35</v>
+      </c>
+      <c r="AT222">
+        <v>2.82</v>
+      </c>
+      <c r="AU222">
+        <v>2</v>
+      </c>
+      <c r="AV222">
+        <v>6</v>
+      </c>
+      <c r="AW222">
+        <v>2</v>
+      </c>
+      <c r="AX222">
+        <v>11</v>
+      </c>
+      <c r="AY222">
+        <v>4</v>
+      </c>
+      <c r="AZ222">
+        <v>17</v>
+      </c>
+      <c r="BA222">
+        <v>2</v>
+      </c>
+      <c r="BB222">
+        <v>9</v>
+      </c>
+      <c r="BC222">
+        <v>11</v>
+      </c>
+      <c r="BD222">
+        <v>2.02</v>
+      </c>
+      <c r="BE222">
+        <v>6.5</v>
+      </c>
+      <c r="BF222">
+        <v>2.19</v>
+      </c>
+      <c r="BG222">
+        <v>1.26</v>
+      </c>
+      <c r="BH222">
+        <v>3.4</v>
+      </c>
+      <c r="BI222">
+        <v>1.35</v>
+      </c>
+      <c r="BJ222">
+        <v>2.74</v>
+      </c>
+      <c r="BK222">
+        <v>1.64</v>
+      </c>
+      <c r="BL222">
+        <v>2.07</v>
+      </c>
+      <c r="BM222">
+        <v>2.09</v>
+      </c>
+      <c r="BN222">
+        <v>1.66</v>
+      </c>
+      <c r="BO222">
+        <v>2.71</v>
+      </c>
+      <c r="BP222">
+        <v>1.38</v>
+      </c>
+    </row>
+    <row r="223" spans="1:68">
+      <c r="A223" s="1">
+        <v>222</v>
+      </c>
+      <c r="B223">
+        <v>7468302</v>
+      </c>
+      <c r="C223" t="s">
+        <v>68</v>
+      </c>
+      <c r="D223" t="s">
+        <v>69</v>
+      </c>
+      <c r="E223" s="2">
+        <v>45753.4375</v>
+      </c>
+      <c r="F223">
+        <v>28</v>
+      </c>
+      <c r="G223" t="s">
+        <v>82</v>
+      </c>
+      <c r="H223" t="s">
+        <v>74</v>
+      </c>
+      <c r="I223">
+        <v>0</v>
+      </c>
+      <c r="J223">
+        <v>0</v>
+      </c>
+      <c r="K223">
+        <v>0</v>
+      </c>
+      <c r="L223">
+        <v>0</v>
+      </c>
+      <c r="M223">
+        <v>1</v>
+      </c>
+      <c r="N223">
+        <v>1</v>
+      </c>
+      <c r="O223" t="s">
+        <v>88</v>
+      </c>
+      <c r="P223" t="s">
+        <v>295</v>
+      </c>
+      <c r="Q223">
+        <v>2.3</v>
+      </c>
+      <c r="R223">
+        <v>2.3</v>
+      </c>
+      <c r="S223">
+        <v>4.5</v>
+      </c>
+      <c r="T223">
+        <v>1.33</v>
+      </c>
+      <c r="U223">
+        <v>3.25</v>
+      </c>
+      <c r="V223">
+        <v>2.5</v>
+      </c>
+      <c r="W223">
+        <v>1.5</v>
+      </c>
+      <c r="X223">
+        <v>6.5</v>
+      </c>
+      <c r="Y223">
+        <v>1.11</v>
+      </c>
+      <c r="Z223">
+        <v>1.73</v>
+      </c>
+      <c r="AA223">
+        <v>3.75</v>
+      </c>
+      <c r="AB223">
+        <v>4.5</v>
+      </c>
+      <c r="AC223">
+        <v>1.01</v>
+      </c>
+      <c r="AD223">
+        <v>11</v>
+      </c>
+      <c r="AE223">
+        <v>1.16</v>
+      </c>
+      <c r="AF223">
+        <v>4.15</v>
+      </c>
+      <c r="AG223">
+        <v>1.7</v>
+      </c>
+      <c r="AH223">
+        <v>2.1</v>
+      </c>
+      <c r="AI223">
+        <v>1.67</v>
+      </c>
+      <c r="AJ223">
+        <v>2.1</v>
+      </c>
+      <c r="AK223">
+        <v>1.22</v>
+      </c>
+      <c r="AL223">
+        <v>1.25</v>
+      </c>
+      <c r="AM223">
+        <v>2</v>
+      </c>
+      <c r="AN223">
+        <v>1.46</v>
+      </c>
+      <c r="AO223">
+        <v>0.62</v>
+      </c>
+      <c r="AP223">
+        <v>1.36</v>
+      </c>
+      <c r="AQ223">
+        <v>0.79</v>
+      </c>
+      <c r="AR223">
+        <v>1.65</v>
+      </c>
+      <c r="AS223">
+        <v>0.93</v>
+      </c>
+      <c r="AT223">
+        <v>2.58</v>
+      </c>
+      <c r="AU223">
+        <v>5</v>
+      </c>
+      <c r="AV223">
+        <v>6</v>
+      </c>
+      <c r="AW223">
+        <v>7</v>
+      </c>
+      <c r="AX223">
+        <v>7</v>
+      </c>
+      <c r="AY223">
+        <v>12</v>
+      </c>
+      <c r="AZ223">
+        <v>13</v>
+      </c>
+      <c r="BA223">
+        <v>7</v>
+      </c>
+      <c r="BB223">
+        <v>6</v>
+      </c>
+      <c r="BC223">
+        <v>13</v>
+      </c>
+      <c r="BD223">
+        <v>1.54</v>
+      </c>
+      <c r="BE223">
+        <v>9.4</v>
+      </c>
+      <c r="BF223">
+        <v>2.86</v>
+      </c>
+      <c r="BG223">
+        <v>1.15</v>
+      </c>
+      <c r="BH223">
+        <v>4.6</v>
+      </c>
+      <c r="BI223">
+        <v>1.21</v>
+      </c>
+      <c r="BJ223">
+        <v>3.58</v>
+      </c>
+      <c r="BK223">
+        <v>1.42</v>
+      </c>
+      <c r="BL223">
+        <v>2.57</v>
+      </c>
+      <c r="BM223">
+        <v>1.75</v>
+      </c>
+      <c r="BN223">
+        <v>2.04</v>
+      </c>
+      <c r="BO223">
+        <v>2.18</v>
+      </c>
+      <c r="BP223">
+        <v>1.65</v>
+      </c>
+    </row>
+    <row r="224" spans="1:68">
+      <c r="A224" s="1">
+        <v>223</v>
+      </c>
+      <c r="B224">
+        <v>7468306</v>
+      </c>
+      <c r="C224" t="s">
+        <v>68</v>
+      </c>
+      <c r="D224" t="s">
+        <v>69</v>
+      </c>
+      <c r="E224" s="2">
+        <v>45753.5625</v>
+      </c>
+      <c r="F224">
+        <v>28</v>
+      </c>
+      <c r="G224" t="s">
+        <v>84</v>
+      </c>
+      <c r="H224" t="s">
+        <v>76</v>
+      </c>
+      <c r="I224">
+        <v>2</v>
+      </c>
+      <c r="J224">
+        <v>0</v>
+      </c>
+      <c r="K224">
+        <v>2</v>
+      </c>
+      <c r="L224">
+        <v>2</v>
+      </c>
+      <c r="M224">
+        <v>0</v>
+      </c>
+      <c r="N224">
+        <v>2</v>
+      </c>
+      <c r="O224" t="s">
+        <v>229</v>
+      </c>
+      <c r="P224" t="s">
+        <v>88</v>
+      </c>
+      <c r="Q224">
+        <v>1.67</v>
+      </c>
+      <c r="R224">
+        <v>2.6</v>
+      </c>
+      <c r="S224">
+        <v>10</v>
+      </c>
+      <c r="T224">
+        <v>1.3</v>
+      </c>
+      <c r="U224">
+        <v>3.4</v>
+      </c>
+      <c r="V224">
+        <v>2.5</v>
+      </c>
+      <c r="W224">
+        <v>1.5</v>
+      </c>
+      <c r="X224">
+        <v>6</v>
+      </c>
+      <c r="Y224">
+        <v>1.13</v>
+      </c>
+      <c r="Z224">
+        <v>1.22</v>
+      </c>
+      <c r="AA224">
+        <v>5</v>
+      </c>
+      <c r="AB224">
+        <v>13</v>
+      </c>
+      <c r="AC224">
+        <v>1.01</v>
+      </c>
+      <c r="AD224">
+        <v>13</v>
+      </c>
+      <c r="AE224">
+        <v>1.16</v>
+      </c>
+      <c r="AF224">
+        <v>4.2</v>
+      </c>
+      <c r="AG224">
+        <v>1.67</v>
+      </c>
+      <c r="AH224">
+        <v>2.15</v>
+      </c>
+      <c r="AI224">
+        <v>2.25</v>
+      </c>
+      <c r="AJ224">
+        <v>1.57</v>
+      </c>
+      <c r="AK224">
+        <v>1.04</v>
+      </c>
+      <c r="AL224">
+        <v>1.15</v>
+      </c>
+      <c r="AM224">
+        <v>3.8</v>
+      </c>
+      <c r="AN224">
+        <v>2.23</v>
+      </c>
+      <c r="AO224">
+        <v>0.85</v>
+      </c>
+      <c r="AP224">
+        <v>2.29</v>
+      </c>
+      <c r="AQ224">
+        <v>0.79</v>
+      </c>
+      <c r="AR224">
+        <v>1.77</v>
+      </c>
+      <c r="AS224">
+        <v>1.17</v>
+      </c>
+      <c r="AT224">
+        <v>2.94</v>
+      </c>
+      <c r="AU224">
+        <v>6</v>
+      </c>
+      <c r="AV224">
+        <v>0</v>
+      </c>
+      <c r="AW224">
+        <v>7</v>
+      </c>
+      <c r="AX224">
+        <v>6</v>
+      </c>
+      <c r="AY224">
+        <v>13</v>
+      </c>
+      <c r="AZ224">
+        <v>6</v>
+      </c>
+      <c r="BA224">
+        <v>8</v>
+      </c>
+      <c r="BB224">
+        <v>5</v>
+      </c>
+      <c r="BC224">
+        <v>13</v>
+      </c>
+      <c r="BD224">
+        <v>1.14</v>
+      </c>
+      <c r="BE224">
+        <v>13</v>
+      </c>
+      <c r="BF224">
+        <v>6.75</v>
+      </c>
+      <c r="BG224">
+        <v>1.19</v>
+      </c>
+      <c r="BH224">
+        <v>4.1</v>
+      </c>
+      <c r="BI224">
+        <v>1.25</v>
+      </c>
+      <c r="BJ224">
+        <v>3.28</v>
+      </c>
+      <c r="BK224">
+        <v>1.51</v>
+      </c>
+      <c r="BL224">
+        <v>2.47</v>
+      </c>
+      <c r="BM224">
+        <v>1.87</v>
+      </c>
+      <c r="BN224">
+        <v>1.93</v>
+      </c>
+      <c r="BO224">
+        <v>2.35</v>
+      </c>
+      <c r="BP224">
+        <v>1.56</v>
       </c>
     </row>
   </sheetData>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Czech Republic First League_20242025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Czech Republic First League_20242025.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1406" uniqueCount="325">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1412" uniqueCount="326">
   <si>
     <t>Id_Jogo</t>
   </si>
@@ -990,6 +990,9 @@
   <si>
     <t>['51']</t>
   </si>
+  <si>
+    <t>['17', '24', '30', '84', '90+4']</t>
+  </si>
 </sst>
 </file>
 
@@ -1350,7 +1353,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:BP224"/>
+  <dimension ref="A1:BP225"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:68">
@@ -2920,7 +2923,7 @@
         <v>0</v>
       </c>
       <c r="AP8">
-        <v>1.38</v>
+        <v>1.29</v>
       </c>
       <c r="AQ8">
         <v>2.14</v>
@@ -4777,7 +4780,7 @@
         <v>2.29</v>
       </c>
       <c r="AQ17">
-        <v>1.08</v>
+        <v>1.21</v>
       </c>
       <c r="AR17">
         <v>0</v>
@@ -5392,7 +5395,7 @@
         <v>0</v>
       </c>
       <c r="AP20">
-        <v>1.38</v>
+        <v>1.29</v>
       </c>
       <c r="AQ20">
         <v>1.36</v>
@@ -7455,7 +7458,7 @@
         <v>2.43</v>
       </c>
       <c r="AQ30">
-        <v>1.08</v>
+        <v>1.21</v>
       </c>
       <c r="AR30">
         <v>1.24</v>
@@ -9512,7 +9515,7 @@
         <v>0</v>
       </c>
       <c r="AP40">
-        <v>1.38</v>
+        <v>1.29</v>
       </c>
       <c r="AQ40">
         <v>1.71</v>
@@ -10339,7 +10342,7 @@
         <v>0.93</v>
       </c>
       <c r="AQ44">
-        <v>1.08</v>
+        <v>1.21</v>
       </c>
       <c r="AR44">
         <v>1.16</v>
@@ -11366,7 +11369,7 @@
         <v>2</v>
       </c>
       <c r="AP49">
-        <v>1.38</v>
+        <v>1.29</v>
       </c>
       <c r="AQ49">
         <v>1.29</v>
@@ -15486,7 +15489,7 @@
         <v>2</v>
       </c>
       <c r="AP69">
-        <v>1.38</v>
+        <v>1.29</v>
       </c>
       <c r="AQ69">
         <v>1.14</v>
@@ -15695,7 +15698,7 @@
         <v>1.93</v>
       </c>
       <c r="AQ70">
-        <v>1.08</v>
+        <v>1.21</v>
       </c>
       <c r="AR70">
         <v>1.53</v>
@@ -16519,7 +16522,7 @@
         <v>1.57</v>
       </c>
       <c r="AQ74">
-        <v>1.08</v>
+        <v>1.21</v>
       </c>
       <c r="AR74">
         <v>1.81</v>
@@ -19400,7 +19403,7 @@
         <v>0.75</v>
       </c>
       <c r="AP88">
-        <v>1.38</v>
+        <v>1.29</v>
       </c>
       <c r="AQ88">
         <v>0.79</v>
@@ -20227,7 +20230,7 @@
         <v>0.21</v>
       </c>
       <c r="AQ92">
-        <v>1.08</v>
+        <v>1.21</v>
       </c>
       <c r="AR92">
         <v>1.33</v>
@@ -22696,7 +22699,7 @@
         <v>1.83</v>
       </c>
       <c r="AP104">
-        <v>1.38</v>
+        <v>1.29</v>
       </c>
       <c r="AQ104">
         <v>1.93</v>
@@ -23523,7 +23526,7 @@
         <v>1.64</v>
       </c>
       <c r="AQ108">
-        <v>1.08</v>
+        <v>1.21</v>
       </c>
       <c r="AR108">
         <v>1.5</v>
@@ -24756,7 +24759,7 @@
         <v>1.14</v>
       </c>
       <c r="AP114">
-        <v>1.38</v>
+        <v>1.29</v>
       </c>
       <c r="AQ114">
         <v>1.07</v>
@@ -27437,7 +27440,7 @@
         <v>1.36</v>
       </c>
       <c r="AQ127">
-        <v>1.08</v>
+        <v>1.21</v>
       </c>
       <c r="AR127">
         <v>1.5</v>
@@ -28879,7 +28882,7 @@
         <v>1.07</v>
       </c>
       <c r="AQ134">
-        <v>1.08</v>
+        <v>1.21</v>
       </c>
       <c r="AR134">
         <v>1.51</v>
@@ -29700,7 +29703,7 @@
         <v>0.5600000000000001</v>
       </c>
       <c r="AP138">
-        <v>1.38</v>
+        <v>1.29</v>
       </c>
       <c r="AQ138">
         <v>0.43</v>
@@ -31351,7 +31354,7 @@
         <v>0.93</v>
       </c>
       <c r="AQ146">
-        <v>1.08</v>
+        <v>1.21</v>
       </c>
       <c r="AR146">
         <v>1.22</v>
@@ -33820,7 +33823,7 @@
         <v>1.89</v>
       </c>
       <c r="AP158">
-        <v>1.38</v>
+        <v>1.29</v>
       </c>
       <c r="AQ158">
         <v>1.93</v>
@@ -35883,7 +35886,7 @@
         <v>2.07</v>
       </c>
       <c r="AQ168">
-        <v>1.08</v>
+        <v>1.21</v>
       </c>
       <c r="AR168">
         <v>1.96</v>
@@ -36292,7 +36295,7 @@
         <v>0.3</v>
       </c>
       <c r="AP170">
-        <v>1.38</v>
+        <v>1.29</v>
       </c>
       <c r="AQ170">
         <v>0.79</v>
@@ -41236,7 +41239,7 @@
         <v>0.09</v>
       </c>
       <c r="AP194">
-        <v>1.38</v>
+        <v>1.29</v>
       </c>
       <c r="AQ194">
         <v>0.07000000000000001</v>
@@ -43505,7 +43508,7 @@
         <v>1.43</v>
       </c>
       <c r="AQ205">
-        <v>1.08</v>
+        <v>1.21</v>
       </c>
       <c r="AR205">
         <v>1.56</v>
@@ -45150,7 +45153,7 @@
         <v>1</v>
       </c>
       <c r="AP213">
-        <v>1.38</v>
+        <v>1.29</v>
       </c>
       <c r="AQ213">
         <v>1.14</v>
@@ -46801,7 +46804,7 @@
         <v>3</v>
       </c>
       <c r="AQ221">
-        <v>1.08</v>
+        <v>1.21</v>
       </c>
       <c r="AR221">
         <v>2.26</v>
@@ -47495,6 +47498,212 @@
       </c>
       <c r="BP224">
         <v>1.56</v>
+      </c>
+    </row>
+    <row r="225" spans="1:68">
+      <c r="A225" s="1">
+        <v>224</v>
+      </c>
+      <c r="B225">
+        <v>7468268</v>
+      </c>
+      <c r="C225" t="s">
+        <v>68</v>
+      </c>
+      <c r="D225" t="s">
+        <v>69</v>
+      </c>
+      <c r="E225" s="2">
+        <v>45756.54166666666</v>
+      </c>
+      <c r="F225">
+        <v>23</v>
+      </c>
+      <c r="G225" t="s">
+        <v>76</v>
+      </c>
+      <c r="H225" t="s">
+        <v>77</v>
+      </c>
+      <c r="I225">
+        <v>0</v>
+      </c>
+      <c r="J225">
+        <v>3</v>
+      </c>
+      <c r="K225">
+        <v>3</v>
+      </c>
+      <c r="L225">
+        <v>1</v>
+      </c>
+      <c r="M225">
+        <v>5</v>
+      </c>
+      <c r="N225">
+        <v>6</v>
+      </c>
+      <c r="O225" t="s">
+        <v>218</v>
+      </c>
+      <c r="P225" t="s">
+        <v>325</v>
+      </c>
+      <c r="Q225">
+        <v>3.3</v>
+      </c>
+      <c r="R225">
+        <v>2.03</v>
+      </c>
+      <c r="S225">
+        <v>3.5</v>
+      </c>
+      <c r="T225">
+        <v>1.49</v>
+      </c>
+      <c r="U225">
+        <v>2.45</v>
+      </c>
+      <c r="V225">
+        <v>3.1</v>
+      </c>
+      <c r="W225">
+        <v>1.32</v>
+      </c>
+      <c r="X225">
+        <v>9</v>
+      </c>
+      <c r="Y225">
+        <v>1.06</v>
+      </c>
+      <c r="Z225">
+        <v>2.55</v>
+      </c>
+      <c r="AA225">
+        <v>2.9</v>
+      </c>
+      <c r="AB225">
+        <v>2.7</v>
+      </c>
+      <c r="AC225">
+        <v>1.03</v>
+      </c>
+      <c r="AD225">
+        <v>7.7</v>
+      </c>
+      <c r="AE225">
+        <v>1.39</v>
+      </c>
+      <c r="AF225">
+        <v>2.75</v>
+      </c>
+      <c r="AG225">
+        <v>2.2</v>
+      </c>
+      <c r="AH225">
+        <v>1.62</v>
+      </c>
+      <c r="AI225">
+        <v>1.88</v>
+      </c>
+      <c r="AJ225">
+        <v>1.83</v>
+      </c>
+      <c r="AK225">
+        <v>1.42</v>
+      </c>
+      <c r="AL225">
+        <v>1.33</v>
+      </c>
+      <c r="AM225">
+        <v>1.47</v>
+      </c>
+      <c r="AN225">
+        <v>1.38</v>
+      </c>
+      <c r="AO225">
+        <v>1.08</v>
+      </c>
+      <c r="AP225">
+        <v>1.29</v>
+      </c>
+      <c r="AQ225">
+        <v>1.21</v>
+      </c>
+      <c r="AR225">
+        <v>1.23</v>
+      </c>
+      <c r="AS225">
+        <v>1.23</v>
+      </c>
+      <c r="AT225">
+        <v>2.46</v>
+      </c>
+      <c r="AU225">
+        <v>5</v>
+      </c>
+      <c r="AV225">
+        <v>9</v>
+      </c>
+      <c r="AW225">
+        <v>8</v>
+      </c>
+      <c r="AX225">
+        <v>6</v>
+      </c>
+      <c r="AY225">
+        <v>13</v>
+      </c>
+      <c r="AZ225">
+        <v>15</v>
+      </c>
+      <c r="BA225">
+        <v>7</v>
+      </c>
+      <c r="BB225">
+        <v>6</v>
+      </c>
+      <c r="BC225">
+        <v>13</v>
+      </c>
+      <c r="BD225">
+        <v>1.94</v>
+      </c>
+      <c r="BE225">
+        <v>6.1</v>
+      </c>
+      <c r="BF225">
+        <v>2.1</v>
+      </c>
+      <c r="BG225">
+        <v>1.46</v>
+      </c>
+      <c r="BH225">
+        <v>2.5</v>
+      </c>
+      <c r="BI225">
+        <v>1.77</v>
+      </c>
+      <c r="BJ225">
+        <v>1.92</v>
+      </c>
+      <c r="BK225">
+        <v>2.23</v>
+      </c>
+      <c r="BL225">
+        <v>1.56</v>
+      </c>
+      <c r="BM225">
+        <v>2.9</v>
+      </c>
+      <c r="BN225">
+        <v>1.34</v>
+      </c>
+      <c r="BO225">
+        <v>3.9</v>
+      </c>
+      <c r="BP225">
+        <v>1.21</v>
       </c>
     </row>
   </sheetData>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Czech Republic First League_20242025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Czech Republic First League_20242025.xlsx
@@ -42812,46 +42812,46 @@
         <v>88</v>
       </c>
       <c r="Q202">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="R202">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="S202">
-        <v>4.5</v>
+        <v>0</v>
       </c>
       <c r="T202">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="U202">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="V202">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="W202">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="X202">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="Y202">
-        <v>1.06</v>
+        <v>0</v>
       </c>
       <c r="Z202">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AA202">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="AB202">
-        <v>3.75</v>
+        <v>0</v>
       </c>
       <c r="AC202">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AD202">
-        <v>1.61</v>
+        <v>0</v>
       </c>
       <c r="AE202">
         <v>0</v>
@@ -42860,25 +42860,25 @@
         <v>0</v>
       </c>
       <c r="AG202">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="AH202">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="AI202">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AJ202">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AK202">
-        <v>1.31</v>
+        <v>0</v>
       </c>
       <c r="AL202">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="AM202">
-        <v>1.76</v>
+        <v>0</v>
       </c>
       <c r="AN202">
         <v>1.33</v>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Czech Republic First League_20242025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Czech Republic First League_20242025.xlsx
@@ -1882,19 +1882,19 @@
         <v>3</v>
       </c>
       <c r="AY2">
-        <v>24</v>
+        <v>14</v>
       </c>
       <c r="AZ2">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="BA2">
         <v>5</v>
       </c>
       <c r="BB2">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="BC2">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="BD2">
         <v>1.12</v>
@@ -2088,10 +2088,10 @@
         <v>3</v>
       </c>
       <c r="AY3">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="AZ3">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="BA3">
         <v>4</v>
@@ -2294,10 +2294,10 @@
         <v>9</v>
       </c>
       <c r="AY4">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="AZ4">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="BA4">
         <v>6</v>
@@ -2500,10 +2500,10 @@
         <v>3</v>
       </c>
       <c r="AY5">
-        <v>19</v>
+        <v>13</v>
       </c>
       <c r="AZ5">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="BA5">
         <v>7</v>
@@ -2706,10 +2706,10 @@
         <v>5</v>
       </c>
       <c r="AY6">
+        <v>8</v>
+      </c>
+      <c r="AZ6">
         <v>10</v>
-      </c>
-      <c r="AZ6">
-        <v>13</v>
       </c>
       <c r="BA6">
         <v>3</v>
@@ -2912,10 +2912,10 @@
         <v>5</v>
       </c>
       <c r="AY7">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="AZ7">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="BA7">
         <v>8</v>
@@ -3118,10 +3118,10 @@
         <v>5</v>
       </c>
       <c r="AY8">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AZ8">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="BA8">
         <v>1</v>
@@ -3324,10 +3324,10 @@
         <v>3</v>
       </c>
       <c r="AY9">
+        <v>7</v>
+      </c>
+      <c r="AZ9">
         <v>8</v>
-      </c>
-      <c r="AZ9">
-        <v>12</v>
       </c>
       <c r="BA9">
         <v>7</v>
@@ -3530,10 +3530,10 @@
         <v>9</v>
       </c>
       <c r="AY10">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="AZ10">
-        <v>22</v>
+        <v>14</v>
       </c>
       <c r="BA10">
         <v>2</v>
@@ -3736,10 +3736,10 @@
         <v>8</v>
       </c>
       <c r="AY11">
-        <v>13</v>
+        <v>7</v>
       </c>
       <c r="AZ11">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="BA11">
         <v>5</v>
@@ -3942,10 +3942,10 @@
         <v>9</v>
       </c>
       <c r="AY12">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AZ12">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="BA12">
         <v>4</v>
@@ -4148,10 +4148,10 @@
         <v>0</v>
       </c>
       <c r="AY13">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="AZ13">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="BA13">
         <v>10</v>
@@ -4354,10 +4354,10 @@
         <v>1</v>
       </c>
       <c r="AY14">
-        <v>16</v>
+        <v>10</v>
       </c>
       <c r="AZ14">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="BA14">
         <v>7</v>
@@ -4560,10 +4560,10 @@
         <v>2</v>
       </c>
       <c r="AY15">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="AZ15">
-        <v>11</v>
+        <v>4</v>
       </c>
       <c r="BA15">
         <v>3</v>
@@ -4766,10 +4766,10 @@
         <v>5</v>
       </c>
       <c r="AY16">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="AZ16">
-        <v>19</v>
+        <v>9</v>
       </c>
       <c r="BA16">
         <v>4</v>
@@ -5178,7 +5178,7 @@
         <v>3</v>
       </c>
       <c r="AY18">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="AZ18">
         <v>6</v>
@@ -5384,10 +5384,10 @@
         <v>5</v>
       </c>
       <c r="AY19">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="AZ19">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="BA19">
         <v>4</v>
@@ -5590,10 +5590,10 @@
         <v>6</v>
       </c>
       <c r="AY20">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="AZ20">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="BA20">
         <v>6</v>
@@ -5796,10 +5796,10 @@
         <v>4</v>
       </c>
       <c r="AY21">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="AZ21">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="BA21">
         <v>8</v>
@@ -6002,10 +6002,10 @@
         <v>7</v>
       </c>
       <c r="AY22">
+        <v>8</v>
+      </c>
+      <c r="AZ22">
         <v>12</v>
-      </c>
-      <c r="AZ22">
-        <v>17</v>
       </c>
       <c r="BA22">
         <v>6</v>
@@ -6208,10 +6208,10 @@
         <v>3</v>
       </c>
       <c r="AY23">
-        <v>16</v>
+        <v>8</v>
       </c>
       <c r="AZ23">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="BA23">
         <v>11</v>
@@ -6414,10 +6414,10 @@
         <v>8</v>
       </c>
       <c r="AY24">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AZ24">
-        <v>24</v>
+        <v>16</v>
       </c>
       <c r="BA24">
         <v>4</v>
@@ -6620,10 +6620,10 @@
         <v>4</v>
       </c>
       <c r="AY25">
+        <v>7</v>
+      </c>
+      <c r="AZ25">
         <v>10</v>
-      </c>
-      <c r="AZ25">
-        <v>17</v>
       </c>
       <c r="BA25">
         <v>4</v>
@@ -6826,10 +6826,10 @@
         <v>8</v>
       </c>
       <c r="AY26">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="AZ26">
-        <v>18</v>
+        <v>12</v>
       </c>
       <c r="BA26">
         <v>5</v>
@@ -7032,10 +7032,10 @@
         <v>8</v>
       </c>
       <c r="AY27">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="AZ27">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="BA27">
         <v>2</v>
@@ -7238,7 +7238,7 @@
         <v>4</v>
       </c>
       <c r="AY28">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="AZ28">
         <v>4</v>
@@ -7444,10 +7444,10 @@
         <v>2</v>
       </c>
       <c r="AY29">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="AZ29">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="BA29">
         <v>3</v>
@@ -7650,10 +7650,10 @@
         <v>5</v>
       </c>
       <c r="AY30">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="AZ30">
-        <v>16</v>
+        <v>8</v>
       </c>
       <c r="BA30">
         <v>2</v>
@@ -7856,10 +7856,10 @@
         <v>0</v>
       </c>
       <c r="AY31">
-        <v>29</v>
+        <v>23</v>
       </c>
       <c r="AZ31">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="BA31">
         <v>13</v>
@@ -8062,7 +8062,7 @@
         <v>6</v>
       </c>
       <c r="AY32">
-        <v>23</v>
+        <v>16</v>
       </c>
       <c r="AZ32">
         <v>9</v>
@@ -8268,10 +8268,10 @@
         <v>5</v>
       </c>
       <c r="AY33">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="AZ33">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="BA33">
         <v>6</v>
@@ -8474,10 +8474,10 @@
         <v>3</v>
       </c>
       <c r="AY34">
-        <v>19</v>
+        <v>10</v>
       </c>
       <c r="AZ34">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="BA34">
         <v>8</v>
@@ -8680,10 +8680,10 @@
         <v>5</v>
       </c>
       <c r="AY35">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="AZ35">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="BA35">
         <v>8</v>
@@ -8886,10 +8886,10 @@
         <v>8</v>
       </c>
       <c r="AY36">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="AZ36">
-        <v>21</v>
+        <v>16</v>
       </c>
       <c r="BA36">
         <v>6</v>
@@ -9092,10 +9092,10 @@
         <v>6</v>
       </c>
       <c r="AY37">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="AZ37">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="BA37">
         <v>10</v>
@@ -9298,10 +9298,10 @@
         <v>7</v>
       </c>
       <c r="AY38">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="AZ38">
-        <v>19</v>
+        <v>12</v>
       </c>
       <c r="BA38">
         <v>8</v>
@@ -9504,10 +9504,10 @@
         <v>6</v>
       </c>
       <c r="AY39">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="AZ39">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="BA39">
         <v>3</v>
@@ -9710,10 +9710,10 @@
         <v>5</v>
       </c>
       <c r="AY40">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="AZ40">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="BA40">
         <v>4</v>
@@ -9916,10 +9916,10 @@
         <v>4</v>
       </c>
       <c r="AY41">
-        <v>24</v>
+        <v>17</v>
       </c>
       <c r="AZ41">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="BA41">
         <v>6</v>
@@ -10122,10 +10122,10 @@
         <v>4</v>
       </c>
       <c r="AY42">
-        <v>14</v>
+        <v>9</v>
       </c>
       <c r="AZ42">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="BA42">
         <v>7</v>
@@ -10328,10 +10328,10 @@
         <v>2</v>
       </c>
       <c r="AY43">
-        <v>18</v>
+        <v>13</v>
       </c>
       <c r="AZ43">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="BA43">
         <v>9</v>
@@ -10534,10 +10534,10 @@
         <v>4</v>
       </c>
       <c r="AY44">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="AZ44">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="BA44">
         <v>5</v>
@@ -10740,10 +10740,10 @@
         <v>6</v>
       </c>
       <c r="AY45">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="AZ45">
-        <v>14</v>
+        <v>9</v>
       </c>
       <c r="BA45">
         <v>9</v>
@@ -10946,10 +10946,10 @@
         <v>4</v>
       </c>
       <c r="AY46">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="AZ46">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="BA46">
         <v>3</v>
@@ -11152,10 +11152,10 @@
         <v>2</v>
       </c>
       <c r="AY47">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="AZ47">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="BA47">
         <v>12</v>
@@ -11358,10 +11358,10 @@
         <v>12</v>
       </c>
       <c r="AY48">
+        <v>11</v>
+      </c>
+      <c r="AZ48">
         <v>14</v>
-      </c>
-      <c r="AZ48">
-        <v>23</v>
       </c>
       <c r="BA48">
         <v>6</v>
@@ -11564,10 +11564,10 @@
         <v>6</v>
       </c>
       <c r="AY49">
-        <v>14</v>
+        <v>7</v>
       </c>
       <c r="AZ49">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="BA49">
         <v>4</v>
@@ -11770,10 +11770,10 @@
         <v>3</v>
       </c>
       <c r="AY50">
-        <v>17</v>
+        <v>11</v>
       </c>
       <c r="AZ50">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="BA50">
         <v>7</v>
@@ -11976,10 +11976,10 @@
         <v>2</v>
       </c>
       <c r="AY51">
-        <v>21</v>
+        <v>16</v>
       </c>
       <c r="AZ51">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="BA51">
         <v>8</v>
@@ -12182,10 +12182,10 @@
         <v>5</v>
       </c>
       <c r="AY52">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="AZ52">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="BA52">
         <v>6</v>
@@ -12388,10 +12388,10 @@
         <v>4</v>
       </c>
       <c r="AY53">
-        <v>21</v>
+        <v>16</v>
       </c>
       <c r="AZ53">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="BA53">
         <v>6</v>
@@ -12594,10 +12594,10 @@
         <v>4</v>
       </c>
       <c r="AY54">
-        <v>19</v>
+        <v>13</v>
       </c>
       <c r="AZ54">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="BA54">
         <v>7</v>
@@ -12800,19 +12800,19 @@
         <v>2</v>
       </c>
       <c r="AY55">
-        <v>20</v>
+        <v>12</v>
       </c>
       <c r="AZ55">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="BA55">
         <v>8</v>
       </c>
       <c r="BB55">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="BC55">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="BD55">
         <v>2</v>
@@ -13006,10 +13006,10 @@
         <v>5</v>
       </c>
       <c r="AY56">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AZ56">
-        <v>16</v>
+        <v>11</v>
       </c>
       <c r="BA56">
         <v>6</v>
@@ -13212,10 +13212,10 @@
         <v>7</v>
       </c>
       <c r="AY57">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AZ57">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="BA57">
         <v>4</v>
@@ -13418,10 +13418,10 @@
         <v>4</v>
       </c>
       <c r="AY58">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AZ58">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="BA58">
         <v>8</v>
@@ -13624,10 +13624,10 @@
         <v>6</v>
       </c>
       <c r="AY59">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="AZ59">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="BA59">
         <v>4</v>
@@ -13833,7 +13833,7 @@
         <v>12</v>
       </c>
       <c r="AZ60">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="BA60">
         <v>4</v>
@@ -14036,10 +14036,10 @@
         <v>3</v>
       </c>
       <c r="AY61">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="AZ61">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="BA61">
         <v>14</v>
@@ -14242,10 +14242,10 @@
         <v>1</v>
       </c>
       <c r="AY62">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="AZ62">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="BA62">
         <v>6</v>
@@ -14448,10 +14448,10 @@
         <v>0</v>
       </c>
       <c r="AY63">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="AZ63">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="BA63">
         <v>6</v>
@@ -14654,10 +14654,10 @@
         <v>9</v>
       </c>
       <c r="AY64">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="AZ64">
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="BA64">
         <v>4</v>
@@ -14860,10 +14860,10 @@
         <v>4</v>
       </c>
       <c r="AY65">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="AZ65">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="BA65">
         <v>4</v>
@@ -15066,10 +15066,10 @@
         <v>1</v>
       </c>
       <c r="AY66">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="AZ66">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="BA66">
         <v>10</v>
@@ -15272,10 +15272,10 @@
         <v>8</v>
       </c>
       <c r="AY67">
+        <v>11</v>
+      </c>
+      <c r="AZ67">
         <v>19</v>
-      </c>
-      <c r="AZ67">
-        <v>24</v>
       </c>
       <c r="BA67">
         <v>5</v>
@@ -15481,7 +15481,7 @@
         <v>7</v>
       </c>
       <c r="AZ68">
-        <v>21</v>
+        <v>14</v>
       </c>
       <c r="BA68">
         <v>3</v>
@@ -15687,7 +15687,7 @@
         <v>6</v>
       </c>
       <c r="AZ69">
-        <v>21</v>
+        <v>11</v>
       </c>
       <c r="BA69">
         <v>0</v>
@@ -15890,10 +15890,10 @@
         <v>6</v>
       </c>
       <c r="AY70">
-        <v>26</v>
+        <v>21</v>
       </c>
       <c r="AZ70">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="BA70">
         <v>7</v>
@@ -16096,10 +16096,10 @@
         <v>7</v>
       </c>
       <c r="AY71">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="AZ71">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="BA71">
         <v>7</v>
@@ -16508,10 +16508,10 @@
         <v>10</v>
       </c>
       <c r="AY73">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="AZ73">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="BA73">
         <v>5</v>
@@ -16714,10 +16714,10 @@
         <v>6</v>
       </c>
       <c r="AY74">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="AZ74">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="BA74">
         <v>11</v>
@@ -16920,10 +16920,10 @@
         <v>4</v>
       </c>
       <c r="AY75">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="AZ75">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="BA75">
         <v>6</v>
@@ -17126,10 +17126,10 @@
         <v>2</v>
       </c>
       <c r="AY76">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="AZ76">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="BA76">
         <v>5</v>
@@ -17332,10 +17332,10 @@
         <v>3</v>
       </c>
       <c r="AY77">
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="AZ77">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="BA77">
         <v>2</v>
@@ -17538,10 +17538,10 @@
         <v>7</v>
       </c>
       <c r="AY78">
-        <v>20</v>
+        <v>13</v>
       </c>
       <c r="AZ78">
-        <v>16</v>
+        <v>10</v>
       </c>
       <c r="BA78">
         <v>9</v>
@@ -17744,10 +17744,10 @@
         <v>7</v>
       </c>
       <c r="AY79">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AZ79">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="BA79">
         <v>8</v>
@@ -17950,10 +17950,10 @@
         <v>12</v>
       </c>
       <c r="AY80">
-        <v>15</v>
+        <v>8</v>
       </c>
       <c r="AZ80">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="BA80">
         <v>5</v>
@@ -18156,10 +18156,10 @@
         <v>3</v>
       </c>
       <c r="AY81">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="AZ81">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="BA81">
         <v>5</v>
@@ -18362,10 +18362,10 @@
         <v>2</v>
       </c>
       <c r="AY82">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="AZ82">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="BA82">
         <v>8</v>
@@ -18568,10 +18568,10 @@
         <v>3</v>
       </c>
       <c r="AY83">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="AZ83">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="BA83">
         <v>4</v>
@@ -18774,10 +18774,10 @@
         <v>3</v>
       </c>
       <c r="AY84">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="AZ84">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="BA84">
         <v>4</v>
@@ -18980,10 +18980,10 @@
         <v>2</v>
       </c>
       <c r="AY85">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="AZ85">
-        <v>11</v>
+        <v>6</v>
       </c>
       <c r="BA85">
         <v>4</v>
@@ -20010,10 +20010,10 @@
         <v>4</v>
       </c>
       <c r="AY90">
-        <v>25</v>
+        <v>17</v>
       </c>
       <c r="AZ90">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="BA90">
         <v>11</v>
@@ -20216,10 +20216,10 @@
         <v>4</v>
       </c>
       <c r="AY91">
-        <v>21</v>
+        <v>16</v>
       </c>
       <c r="AZ91">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="BA91">
         <v>3</v>
@@ -20628,10 +20628,10 @@
         <v>2</v>
       </c>
       <c r="AY93">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="AZ93">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="BA93">
         <v>12</v>
@@ -20834,19 +20834,19 @@
         <v>4</v>
       </c>
       <c r="AY94">
-        <v>21</v>
+        <v>12</v>
       </c>
       <c r="AZ94">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="BA94">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="BB94">
         <v>3</v>
       </c>
       <c r="BC94">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="BD94">
         <v>1.83</v>
@@ -21040,19 +21040,19 @@
         <v>3</v>
       </c>
       <c r="AY95">
-        <v>20</v>
+        <v>14</v>
       </c>
       <c r="AZ95">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="BA95">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="BB95">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="BC95">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="BD95">
         <v>1.05</v>
@@ -21246,10 +21246,10 @@
         <v>12</v>
       </c>
       <c r="AY96">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="AZ96">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="BA96">
         <v>4</v>
@@ -21452,10 +21452,10 @@
         <v>6</v>
       </c>
       <c r="AY97">
-        <v>14</v>
+        <v>9</v>
       </c>
       <c r="AZ97">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="BA97">
         <v>3</v>
@@ -21658,10 +21658,10 @@
         <v>7</v>
       </c>
       <c r="AY98">
-        <v>17</v>
+        <v>11</v>
       </c>
       <c r="AZ98">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="BA98">
         <v>8</v>
@@ -21864,10 +21864,10 @@
         <v>9</v>
       </c>
       <c r="AY99">
+        <v>11</v>
+      </c>
+      <c r="AZ99">
         <v>12</v>
-      </c>
-      <c r="AZ99">
-        <v>15</v>
       </c>
       <c r="BA99">
         <v>4</v>
@@ -22070,10 +22070,10 @@
         <v>8</v>
       </c>
       <c r="AY100">
+        <v>12</v>
+      </c>
+      <c r="AZ100">
         <v>14</v>
-      </c>
-      <c r="AZ100">
-        <v>15</v>
       </c>
       <c r="BA100">
         <v>3</v>
@@ -22276,10 +22276,10 @@
         <v>5</v>
       </c>
       <c r="AY101">
-        <v>17</v>
+        <v>11</v>
       </c>
       <c r="AZ101">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="BA101">
         <v>4</v>
@@ -22482,10 +22482,10 @@
         <v>6</v>
       </c>
       <c r="AY102">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="AZ102">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="BA102">
         <v>2</v>
@@ -22688,10 +22688,10 @@
         <v>7</v>
       </c>
       <c r="AY103">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AZ103">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="BA103">
         <v>1</v>
@@ -22894,10 +22894,10 @@
         <v>2</v>
       </c>
       <c r="AY104">
-        <v>14</v>
+        <v>9</v>
       </c>
       <c r="AZ104">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="BA104">
         <v>5</v>
@@ -23100,10 +23100,10 @@
         <v>7</v>
       </c>
       <c r="AY105">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="AZ105">
-        <v>17</v>
+        <v>11</v>
       </c>
       <c r="BA105">
         <v>2</v>
@@ -23306,10 +23306,10 @@
         <v>1</v>
       </c>
       <c r="AY106">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="AZ106">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="BA106">
         <v>5</v>
@@ -23512,10 +23512,10 @@
         <v>8</v>
       </c>
       <c r="AY107">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="AZ107">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="BA107">
         <v>1</v>
@@ -23718,10 +23718,10 @@
         <v>3</v>
       </c>
       <c r="AY108">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="AZ108">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="BA108">
         <v>3</v>
@@ -23924,7 +23924,7 @@
         <v>1</v>
       </c>
       <c r="AY109">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="AZ109">
         <v>6</v>
@@ -24130,10 +24130,10 @@
         <v>1</v>
       </c>
       <c r="AY110">
-        <v>17</v>
+        <v>11</v>
       </c>
       <c r="AZ110">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="BA110">
         <v>8</v>
@@ -24336,10 +24336,10 @@
         <v>7</v>
       </c>
       <c r="AY111">
-        <v>18</v>
+        <v>9</v>
       </c>
       <c r="AZ111">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="BA111">
         <v>4</v>
@@ -24542,19 +24542,19 @@
         <v>0</v>
       </c>
       <c r="AY112">
-        <v>33</v>
+        <v>27</v>
       </c>
       <c r="AZ112">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="BA112">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="BB112">
         <v>3</v>
       </c>
       <c r="BC112">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="BD112">
         <v>1.08</v>
@@ -24960,13 +24960,13 @@
         <v>-1</v>
       </c>
       <c r="BA114">
-        <v>3</v>
+        <v>-1</v>
       </c>
       <c r="BB114">
-        <v>9</v>
+        <v>-1</v>
       </c>
       <c r="BC114">
-        <v>12</v>
+        <v>-1</v>
       </c>
       <c r="BD114">
         <v>0</v>
@@ -25778,10 +25778,10 @@
         <v>4</v>
       </c>
       <c r="AY118">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="AZ118">
-        <v>16</v>
+        <v>11</v>
       </c>
       <c r="BA118">
         <v>5</v>
@@ -25987,7 +25987,7 @@
         <v>10</v>
       </c>
       <c r="AZ119">
-        <v>11</v>
+        <v>6</v>
       </c>
       <c r="BA119">
         <v>3</v>
@@ -26190,10 +26190,10 @@
         <v>3</v>
       </c>
       <c r="AY120">
+        <v>11</v>
+      </c>
+      <c r="AZ120">
         <v>13</v>
-      </c>
-      <c r="AZ120">
-        <v>15</v>
       </c>
       <c r="BA120">
         <v>4</v>
@@ -26396,10 +26396,10 @@
         <v>2</v>
       </c>
       <c r="AY121">
-        <v>24</v>
+        <v>17</v>
       </c>
       <c r="AZ121">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="BA121">
         <v>7</v>
@@ -26602,10 +26602,10 @@
         <v>6</v>
       </c>
       <c r="AY122">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="AZ122">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="BA122">
         <v>8</v>
@@ -26808,10 +26808,10 @@
         <v>3</v>
       </c>
       <c r="AY123">
-        <v>37</v>
+        <v>21</v>
       </c>
       <c r="AZ123">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="BA123">
         <v>16</v>
@@ -27014,10 +27014,10 @@
         <v>2</v>
       </c>
       <c r="AY124">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="AZ124">
-        <v>11</v>
+        <v>6</v>
       </c>
       <c r="BA124">
         <v>6</v>
@@ -27220,10 +27220,10 @@
         <v>2</v>
       </c>
       <c r="AY125">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="AZ125">
-        <v>13</v>
+        <v>6</v>
       </c>
       <c r="BA125">
         <v>10</v>
@@ -27426,10 +27426,10 @@
         <v>3</v>
       </c>
       <c r="AY126">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="AZ126">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="BA126">
         <v>6</v>
@@ -27632,10 +27632,10 @@
         <v>2</v>
       </c>
       <c r="AY127">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="AZ127">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="BA127">
         <v>9</v>
@@ -27838,10 +27838,10 @@
         <v>7</v>
       </c>
       <c r="AY128">
-        <v>20</v>
+        <v>13</v>
       </c>
       <c r="AZ128">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="BA128">
         <v>7</v>
@@ -28044,10 +28044,10 @@
         <v>4</v>
       </c>
       <c r="AY129">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="AZ129">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="BA129">
         <v>3</v>
@@ -28250,10 +28250,10 @@
         <v>3</v>
       </c>
       <c r="AY130">
-        <v>30</v>
+        <v>24</v>
       </c>
       <c r="AZ130">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="BA130">
         <v>8</v>
@@ -28456,10 +28456,10 @@
         <v>3</v>
       </c>
       <c r="AY131">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="AZ131">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="BA131">
         <v>8</v>
@@ -28662,10 +28662,10 @@
         <v>2</v>
       </c>
       <c r="AY132">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="AZ132">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="BA132">
         <v>6</v>
@@ -28871,7 +28871,7 @@
         <v>7</v>
       </c>
       <c r="AZ133">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="BA133">
         <v>3</v>
@@ -29074,10 +29074,10 @@
         <v>4</v>
       </c>
       <c r="AY134">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="AZ134">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="BA134">
         <v>8</v>
@@ -29280,10 +29280,10 @@
         <v>2</v>
       </c>
       <c r="AY135">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="AZ135">
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="BA135">
         <v>4</v>
@@ -29486,10 +29486,10 @@
         <v>4</v>
       </c>
       <c r="AY136">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="AZ136">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="BA136">
         <v>6</v>
@@ -29692,10 +29692,10 @@
         <v>7</v>
       </c>
       <c r="AY137">
-        <v>20</v>
+        <v>13</v>
       </c>
       <c r="AZ137">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="BA137">
         <v>12</v>
@@ -29898,10 +29898,10 @@
         <v>3</v>
       </c>
       <c r="AY138">
-        <v>21</v>
+        <v>16</v>
       </c>
       <c r="AZ138">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="BA138">
         <v>9</v>
@@ -30104,10 +30104,10 @@
         <v>5</v>
       </c>
       <c r="AY139">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="AZ139">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="BA139">
         <v>8</v>
@@ -30310,10 +30310,10 @@
         <v>7</v>
       </c>
       <c r="AY140">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="AZ140">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="BA140">
         <v>9</v>
@@ -30516,10 +30516,10 @@
         <v>6</v>
       </c>
       <c r="AY141">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="AZ141">
-        <v>21</v>
+        <v>13</v>
       </c>
       <c r="BA141">
         <v>5</v>
@@ -30722,10 +30722,10 @@
         <v>8</v>
       </c>
       <c r="AY142">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="AZ142">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="BA142">
         <v>3</v>
@@ -30928,10 +30928,10 @@
         <v>6</v>
       </c>
       <c r="AY143">
-        <v>15</v>
+        <v>8</v>
       </c>
       <c r="AZ143">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="BA143">
         <v>3</v>
@@ -31134,7 +31134,7 @@
         <v>6</v>
       </c>
       <c r="AY144">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="AZ144">
         <v>12</v>
@@ -31340,10 +31340,10 @@
         <v>6</v>
       </c>
       <c r="AY145">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="AZ145">
-        <v>16</v>
+        <v>10</v>
       </c>
       <c r="BA145">
         <v>3</v>
@@ -31546,7 +31546,7 @@
         <v>3</v>
       </c>
       <c r="AY146">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="AZ146">
         <v>10</v>
@@ -31752,10 +31752,10 @@
         <v>3</v>
       </c>
       <c r="AY147">
-        <v>26</v>
+        <v>19</v>
       </c>
       <c r="AZ147">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="BA147">
         <v>10</v>
@@ -31958,10 +31958,10 @@
         <v>8</v>
       </c>
       <c r="AY148">
-        <v>18</v>
+        <v>13</v>
       </c>
       <c r="AZ148">
-        <v>18</v>
+        <v>13</v>
       </c>
       <c r="BA148">
         <v>8</v>
@@ -32164,10 +32164,10 @@
         <v>4</v>
       </c>
       <c r="AY149">
-        <v>20</v>
+        <v>14</v>
       </c>
       <c r="AZ149">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="BA149">
         <v>6</v>
@@ -32370,10 +32370,10 @@
         <v>2</v>
       </c>
       <c r="AY150">
-        <v>19</v>
+        <v>12</v>
       </c>
       <c r="AZ150">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="BA150">
         <v>10</v>
@@ -32576,10 +32576,10 @@
         <v>3</v>
       </c>
       <c r="AY151">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="AZ151">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="BA151">
         <v>8</v>
@@ -32782,10 +32782,10 @@
         <v>14</v>
       </c>
       <c r="AY152">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AZ152">
-        <v>26</v>
+        <v>20</v>
       </c>
       <c r="BA152">
         <v>1</v>
@@ -32988,7 +32988,7 @@
         <v>2</v>
       </c>
       <c r="AY153">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="AZ153">
         <v>6</v>
@@ -36696,7 +36696,7 @@
         <v>2</v>
       </c>
       <c r="AY171">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="AZ171">
         <v>7</v>
@@ -40204,13 +40204,13 @@
         <v>-1</v>
       </c>
       <c r="BA188">
-        <v>6</v>
+        <v>-1</v>
       </c>
       <c r="BB188">
-        <v>3</v>
+        <v>-1</v>
       </c>
       <c r="BC188">
-        <v>9</v>
+        <v>-1</v>
       </c>
       <c r="BD188">
         <v>1.36</v>
@@ -46584,10 +46584,10 @@
         <v>13</v>
       </c>
       <c r="AY219">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="AZ219">
-        <v>32</v>
+        <v>20</v>
       </c>
       <c r="BA219">
         <v>3</v>
@@ -46790,10 +46790,10 @@
         <v>10</v>
       </c>
       <c r="AY220">
-        <v>16</v>
+        <v>11</v>
       </c>
       <c r="AZ220">
-        <v>16</v>
+        <v>10</v>
       </c>
       <c r="BA220">
         <v>5</v>
@@ -48026,10 +48026,10 @@
         <v>2</v>
       </c>
       <c r="AY226">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AZ226">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="BA226">
         <v>8</v>
@@ -48232,10 +48232,10 @@
         <v>14</v>
       </c>
       <c r="AY227">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="AZ227">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="BA227">
         <v>5</v>
@@ -49268,13 +49268,13 @@
         <v>11</v>
       </c>
       <c r="BA232">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="BB232">
         <v>6</v>
       </c>
       <c r="BC232">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="BD232">
         <v>0</v>
@@ -50089,7 +50089,7 @@
         <v>9</v>
       </c>
       <c r="AZ236">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="BA236">
         <v>7</v>
@@ -51737,7 +51737,7 @@
         <v>0</v>
       </c>
       <c r="AZ244">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="BA244">
         <v>2</v>
@@ -52970,7 +52970,7 @@
         <v>4</v>
       </c>
       <c r="AY250">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="AZ250">
         <v>10</v>
@@ -54618,7 +54618,7 @@
         <v>1</v>
       </c>
       <c r="AY258">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="AZ258">
         <v>4</v>
@@ -58326,10 +58326,10 @@
         <v>4</v>
       </c>
       <c r="AY276">
-        <v>21</v>
+        <v>16</v>
       </c>
       <c r="AZ276">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="BA276">
         <v>2</v>
